--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -215,10 +215,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -688,138 +702,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1156,86 +1188,86 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>4105.48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>2714.1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>2533.85</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>2183.01</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>2136.24</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>1966.62</v>
       </c>
     </row>
@@ -1408,142 +1440,142 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>953.78</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>950.09</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>927.15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="A23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>907.94</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="6">
         <v>848.93</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" t="s">
+      <c r="A25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="6">
         <v>552.79</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" t="s">
+      <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="6">
         <v>407.35</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" t="s">
+      <c r="A27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="6">
         <v>363.88</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" t="s">
+      <c r="A28" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>305.29</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" t="s">
+      <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>262.39</v>
       </c>
     </row>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12345"/>
+    <workbookView windowWidth="28800" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -69,21 +69,30 @@
     <t>中大氪</t>
   </si>
   <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
     <t>145区</t>
   </si>
   <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
     <t>古月星辰</t>
   </si>
   <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
     <t>151区</t>
   </si>
   <si>
@@ -93,85 +102,76 @@
     <t>中低氪</t>
   </si>
   <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>何斌</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>念苍生</t>
+  </si>
+  <si>
     <t>150区</t>
   </si>
   <si>
     <t>开飞机的贝塔</t>
   </si>
   <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>星空</t>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
   </si>
   <si>
     <t>[永恒]</t>
   </si>
   <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>念苍生</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>何斌</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>秋雨</t>
   </si>
   <si>
     <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -218,10 +218,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -274,6 +274,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -282,15 +290,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -298,7 +298,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,7 +306,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,30 +336,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,14 +360,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -403,9 +374,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -426,13 +426,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +540,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,145 +582,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,6 +611,60 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -633,22 +687,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,30 +697,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -696,21 +711,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -719,10 +719,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,133 +731,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1268,32 +1268,32 @@
         <v>4105.48</v>
       </c>
       <c r="E2" s="2">
-        <f t="shared" ref="E2:E28" si="0">F2-D2</f>
+        <f>F2-D2</f>
         <v>181.21</v>
       </c>
       <c r="F2" s="2">
         <v>4286.69</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G28" si="1">H2-F2</f>
+        <f>H2-F2</f>
         <v>139.09</v>
       </c>
       <c r="H2" s="2">
         <v>4425.78</v>
       </c>
       <c r="I2" s="2">
-        <f t="shared" ref="I2:I28" si="2">J2-H2</f>
+        <f>J2-H2</f>
         <v>54.8800000000001</v>
       </c>
       <c r="J2" s="2">
         <v>4480.66</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K28" si="3">J2-F2</f>
+        <f>J2-F2</f>
         <v>193.97</v>
       </c>
       <c r="L2" s="2">
-        <f t="shared" ref="L2:L28" si="4">J2-D2</f>
+        <f>J2-D2</f>
         <v>375.18</v>
       </c>
     </row>
@@ -1311,32 +1311,32 @@
         <v>2714.1</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" si="0"/>
+        <f>F3-D3</f>
         <v>123.29</v>
       </c>
       <c r="F3" s="3">
         <v>2837.39</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" si="1"/>
+        <f>H3-F3</f>
         <v>95.8499999999999</v>
       </c>
       <c r="H3" s="3">
         <v>2933.24</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" si="2"/>
+        <f>J3-H3</f>
         <v>92.46</v>
       </c>
       <c r="J3" s="3">
         <v>3025.7</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" si="3"/>
+        <f>J3-F3</f>
         <v>188.31</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" si="4"/>
+        <f>J3-D3</f>
         <v>311.6</v>
       </c>
       <c r="M3" s="1"/>
@@ -1344,46 +1344,46 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1754.54</v>
-      </c>
-      <c r="E4" s="1">
-        <f t="shared" si="0"/>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1807.91</v>
-      </c>
-      <c r="G4" s="1">
-        <f t="shared" si="1"/>
-        <v>90.24</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1898.15</v>
-      </c>
-      <c r="I4" s="1">
-        <f t="shared" si="2"/>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1988.53</v>
-      </c>
-      <c r="K4" s="1">
-        <f t="shared" si="3"/>
-        <v>180.62</v>
-      </c>
-      <c r="L4" s="1">
-        <f t="shared" si="4"/>
-        <v>233.99</v>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2533.85</v>
+      </c>
+      <c r="E4" s="4">
+        <f>F4-D4</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2583.9</v>
+      </c>
+      <c r="G4" s="4">
+        <f>H4-F4</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2669.66</v>
+      </c>
+      <c r="I4" s="4">
+        <f>J4-H4</f>
+        <v>81.79</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2751.45</v>
+      </c>
+      <c r="K4" s="4">
+        <f>J4-F4</f>
+        <v>167.55</v>
+      </c>
+      <c r="L4" s="4">
+        <f>J4-D4</f>
+        <v>217.6</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -1391,183 +1391,183 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="4">
-        <v>2533.85</v>
+        <v>2136.24</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" si="0"/>
-        <v>50.0500000000002</v>
+        <f>F5-D5</f>
+        <v>40.8200000000002</v>
       </c>
       <c r="F5" s="4">
-        <v>2583.9</v>
+        <v>2177.06</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="1"/>
-        <v>85.7599999999998</v>
+        <f>H5-F5</f>
+        <v>62.5999999999999</v>
       </c>
       <c r="H5" s="4">
-        <v>2669.66</v>
+        <v>2239.66</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" si="2"/>
-        <v>81.79</v>
+        <f>J5-H5</f>
+        <v>47.0700000000002</v>
       </c>
       <c r="J5" s="4">
-        <v>2751.45</v>
+        <v>2286.73</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" si="3"/>
-        <v>167.55</v>
+        <f>J5-F5</f>
+        <v>109.67</v>
       </c>
       <c r="L5" s="4">
-        <f t="shared" si="4"/>
-        <v>217.6</v>
+        <f>J5-D5</f>
+        <v>150.49</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1735.94</v>
-      </c>
-      <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>48.5999999999999</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1784.54</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" si="1"/>
-        <v>74.1600000000001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1858.7</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="2"/>
-        <v>65.55</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1924.25</v>
-      </c>
-      <c r="K6" s="1">
-        <f t="shared" si="3"/>
-        <v>139.71</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="4"/>
-        <v>188.31</v>
+      <c r="D6" s="4">
+        <v>2183.01</v>
+      </c>
+      <c r="E6" s="4">
+        <f>F6-D6</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2207.13</v>
+      </c>
+      <c r="G6" s="4">
+        <f>H6-F6</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2229.99</v>
+      </c>
+      <c r="I6" s="4">
+        <f>J6-H6</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2241.77</v>
+      </c>
+      <c r="K6" s="4">
+        <f>J6-F6</f>
+        <v>34.6399999999999</v>
+      </c>
+      <c r="L6" s="4">
+        <f>J6-D6</f>
+        <v>58.7599999999998</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1">
-        <v>953.78</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>28.97</v>
-      </c>
-      <c r="F7" s="1">
-        <v>982.75</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="1"/>
-        <v>83.9300000000001</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1066.68</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="2"/>
-        <v>42.8399999999999</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1109.52</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" si="3"/>
-        <v>126.77</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="4"/>
-        <v>155.74</v>
+      <c r="A7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1966.62</v>
+      </c>
+      <c r="E7" s="4">
+        <f>F7-D7</f>
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2015.64</v>
+      </c>
+      <c r="G7" s="4">
+        <f>H7-F7</f>
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2049.8</v>
+      </c>
+      <c r="I7" s="4">
+        <f>J7-H7</f>
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2139.9</v>
+      </c>
+      <c r="K7" s="4">
+        <f>J7-F7</f>
+        <v>124.26</v>
+      </c>
+      <c r="L7" s="4">
+        <f>J7-D7</f>
+        <v>173.28</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1966.62</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" si="0"/>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2015.64</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="1"/>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H8" s="4">
-        <v>2049.8</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="2"/>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J8" s="4">
-        <v>2139.9</v>
-      </c>
-      <c r="K8" s="4">
-        <f t="shared" si="3"/>
-        <v>124.26</v>
-      </c>
-      <c r="L8" s="4">
-        <f t="shared" si="4"/>
-        <v>173.28</v>
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1754.54</v>
+      </c>
+      <c r="E8" s="1">
+        <f>F8-D8</f>
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1807.91</v>
+      </c>
+      <c r="G8" s="1">
+        <f>H8-F8</f>
+        <v>90.24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1898.15</v>
+      </c>
+      <c r="I8" s="1">
+        <f>J8-H8</f>
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1988.53</v>
+      </c>
+      <c r="K8" s="1">
+        <f>J8-F8</f>
+        <v>180.62</v>
+      </c>
+      <c r="L8" s="1">
+        <f>J8-D8</f>
+        <v>233.99</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1575,91 +1575,91 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1">
-        <v>1726.42</v>
+        <v>1735.94</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
-        <v>56.28</v>
+        <f>F9-D9</f>
+        <v>48.5999999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>1782.7</v>
+        <v>1784.54</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="1"/>
-        <v>70.9199999999998</v>
+        <f>H9-F9</f>
+        <v>74.1600000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>1853.62</v>
+        <v>1858.7</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="2"/>
-        <v>49.5800000000002</v>
+        <f>J9-H9</f>
+        <v>65.55</v>
       </c>
       <c r="J9" s="1">
-        <v>1903.2</v>
+        <v>1924.25</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="3"/>
-        <v>120.5</v>
+        <f>J9-F9</f>
+        <v>139.71</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="4"/>
-        <v>176.78</v>
+        <f>J9-D9</f>
+        <v>188.31</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2136.24</v>
-      </c>
-      <c r="E10" s="4">
-        <f t="shared" si="0"/>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2177.06</v>
-      </c>
-      <c r="G10" s="4">
-        <f t="shared" si="1"/>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2239.66</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="2"/>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J10" s="4">
-        <v>2286.73</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="3"/>
-        <v>109.67</v>
-      </c>
-      <c r="L10" s="4">
-        <f t="shared" si="4"/>
-        <v>150.49</v>
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1726.42</v>
+      </c>
+      <c r="E10" s="1">
+        <f>F10-D10</f>
+        <v>56.28</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1782.7</v>
+      </c>
+      <c r="G10" s="1">
+        <f>H10-F10</f>
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1853.62</v>
+      </c>
+      <c r="I10" s="1">
+        <f>J10-H10</f>
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1903.2</v>
+      </c>
+      <c r="K10" s="1">
+        <f>J10-F10</f>
+        <v>120.5</v>
+      </c>
+      <c r="L10" s="1">
+        <f>J10-D10</f>
+        <v>176.78</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -1670,42 +1670,42 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1">
-        <v>1156.57</v>
+        <v>1576.18</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
-        <v>40.4400000000001</v>
+        <f>F11-D11</f>
+        <v>38.8399999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>1197.01</v>
+        <v>1615.02</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
-        <v>46.97</v>
+        <f>H11-F11</f>
+        <v>35.5999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>1243.98</v>
+        <v>1650.62</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="2"/>
-        <v>58.49</v>
+        <f>J11-H11</f>
+        <v>37.47</v>
       </c>
       <c r="J11" s="1">
-        <v>1302.47</v>
+        <v>1688.09</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="3"/>
-        <v>105.46</v>
+        <f>J11-F11</f>
+        <v>73.0699999999999</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="4"/>
-        <v>145.9</v>
+        <f>J11-D11</f>
+        <v>111.91</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
@@ -1725,32 +1725,32 @@
         <v>1425.22</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="0"/>
+        <f>F12-D12</f>
         <v>64.8599999999999</v>
       </c>
       <c r="F12" s="1">
         <v>1490.08</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
+        <f>H12-F12</f>
         <v>46</v>
       </c>
       <c r="H12" s="1">
         <v>1536.08</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="2"/>
+        <f>J12-H12</f>
         <v>50.8500000000001</v>
       </c>
       <c r="J12" s="1">
         <v>1586.93</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="3"/>
+        <f>J12-F12</f>
         <v>96.8500000000001</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="4"/>
+        <f>J12-D12</f>
         <v>161.71</v>
       </c>
       <c r="M12" s="3"/>
@@ -1759,45 +1759,45 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1">
-        <v>1350.52</v>
+        <v>1446.65</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>52.6800000000001</v>
+        <f>F13-D13</f>
+        <v>28.1799999999998</v>
       </c>
       <c r="F13" s="1">
-        <v>1403.2</v>
+        <v>1474.83</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
-        <v>55.3199999999999</v>
+        <f>H13-F13</f>
+        <v>63.8200000000002</v>
       </c>
       <c r="H13" s="1">
-        <v>1458.52</v>
+        <v>1538.65</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="2"/>
-        <v>32.6800000000001</v>
+        <f>J13-H13</f>
+        <v>22.9199999999998</v>
       </c>
       <c r="J13" s="1">
-        <v>1491.2</v>
+        <v>1561.57</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="3"/>
-        <v>88</v>
+        <f>J13-F13</f>
+        <v>86.74</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="4"/>
-        <v>140.68</v>
+        <f>J13-D13</f>
+        <v>114.92</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -1805,91 +1805,91 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
-        <v>1446.65</v>
+        <v>1350.52</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" si="0"/>
-        <v>28.1799999999998</v>
+        <f>F14-D14</f>
+        <v>52.6800000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>1474.83</v>
+        <v>1403.2</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="1"/>
-        <v>63.8200000000002</v>
+        <f>H14-F14</f>
+        <v>55.3199999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>1538.65</v>
+        <v>1458.52</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" si="2"/>
-        <v>22.9199999999998</v>
+        <f>J14-H14</f>
+        <v>32.6800000000001</v>
       </c>
       <c r="J14" s="1">
-        <v>1561.57</v>
+        <v>1491.2</v>
       </c>
       <c r="K14" s="1">
-        <f t="shared" si="3"/>
-        <v>86.74</v>
+        <f>J14-F14</f>
+        <v>88</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="4"/>
-        <v>114.92</v>
+        <f>J14-D14</f>
+        <v>140.68</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="5">
-        <v>848.93</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" si="0"/>
-        <v>34.5600000000001</v>
-      </c>
-      <c r="F15" s="5">
-        <v>883.49</v>
-      </c>
-      <c r="G15" s="5">
-        <f t="shared" si="1"/>
-        <v>46.08</v>
-      </c>
-      <c r="H15" s="5">
-        <v>929.57</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="2"/>
-        <v>27.7399999999999</v>
-      </c>
-      <c r="J15" s="5">
-        <v>957.31</v>
-      </c>
-      <c r="K15" s="5">
-        <f t="shared" si="3"/>
-        <v>73.8199999999999</v>
-      </c>
-      <c r="L15" s="5">
-        <f t="shared" si="4"/>
-        <v>108.38</v>
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1349.35</v>
+      </c>
+      <c r="E15" s="1">
+        <f>F15-D15</f>
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1398.97</v>
+      </c>
+      <c r="G15" s="1">
+        <f>H15-F15</f>
+        <v>27.79</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1426.76</v>
+      </c>
+      <c r="I15" s="1">
+        <f>J15-H15</f>
+        <v>29.02</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1455.78</v>
+      </c>
+      <c r="K15" s="1">
+        <f>J15-F15</f>
+        <v>56.8099999999999</v>
+      </c>
+      <c r="L15" s="1">
+        <f>J15-D15</f>
+        <v>106.43</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1897,45 +1897,45 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1">
-        <v>1576.18</v>
+        <v>1317.56</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="0"/>
-        <v>38.8399999999999</v>
+        <f>F16-D16</f>
+        <v>15.77</v>
       </c>
       <c r="F16" s="1">
-        <v>1615.02</v>
+        <v>1333.33</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="1"/>
-        <v>35.5999999999999</v>
+        <f>H16-F16</f>
+        <v>15.1700000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>1650.62</v>
+        <v>1348.5</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="2"/>
-        <v>37.47</v>
+        <f>J16-H16</f>
+        <v>28.9300000000001</v>
       </c>
       <c r="J16" s="1">
-        <v>1688.09</v>
+        <v>1377.43</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" si="3"/>
-        <v>73.0699999999999</v>
+        <f>J16-F16</f>
+        <v>44.1000000000001</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="4"/>
-        <v>111.91</v>
+        <f>J16-D16</f>
+        <v>59.8700000000001</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1943,45 +1943,45 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="1">
-        <v>1060.77</v>
+        <v>1156.57</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="0"/>
-        <v>63.24</v>
+        <f>F17-D17</f>
+        <v>40.4400000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>1124.01</v>
+        <v>1197.01</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="1"/>
-        <v>19.6700000000001</v>
+        <f>H17-F17</f>
+        <v>46.97</v>
       </c>
       <c r="H17" s="1">
-        <v>1143.68</v>
+        <v>1243.98</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="2"/>
-        <v>47.76</v>
+        <f>J17-H17</f>
+        <v>58.49</v>
       </c>
       <c r="J17" s="1">
-        <v>1191.44</v>
+        <v>1302.47</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="3"/>
-        <v>67.4300000000001</v>
+        <f>J17-F17</f>
+        <v>105.46</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="4"/>
-        <v>130.67</v>
+        <f>J17-D17</f>
+        <v>145.9</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1989,45 +1989,45 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1">
-        <v>907.94</v>
+        <v>1060.77</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="0"/>
-        <v>64.0799999999999</v>
+        <f>F18-D18</f>
+        <v>63.24</v>
       </c>
       <c r="F18" s="1">
-        <v>972.02</v>
+        <v>1124.01</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
-        <v>36.26</v>
+        <f>H18-F18</f>
+        <v>19.6700000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>1008.28</v>
+        <v>1143.68</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="2"/>
-        <v>28.8</v>
+        <f>J18-H18</f>
+        <v>47.76</v>
       </c>
       <c r="J18" s="1">
-        <v>1037.08</v>
+        <v>1191.44</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="3"/>
-        <v>65.0599999999999</v>
+        <f>J18-F18</f>
+        <v>67.4300000000001</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="4"/>
-        <v>129.14</v>
+        <f>J18-D18</f>
+        <v>130.67</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -2035,45 +2035,45 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1">
-        <v>950.09</v>
+        <v>953.78</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="0"/>
-        <v>42.4</v>
+        <f>F19-D19</f>
+        <v>28.97</v>
       </c>
       <c r="F19" s="1">
-        <v>992.49</v>
+        <v>982.75</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="1"/>
-        <v>38.5899999999999</v>
+        <f>H19-F19</f>
+        <v>83.9300000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>1031.08</v>
+        <v>1066.68</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="2"/>
-        <v>22.6000000000001</v>
+        <f>J19-H19</f>
+        <v>42.8399999999999</v>
       </c>
       <c r="J19" s="1">
-        <v>1053.68</v>
+        <v>1109.52</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="3"/>
-        <v>61.1900000000001</v>
+        <f>J19-F19</f>
+        <v>126.77</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="4"/>
-        <v>103.59</v>
+        <f>J19-D19</f>
+        <v>155.74</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -2081,183 +2081,183 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1">
-        <v>1349.35</v>
+        <v>950.09</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="0"/>
-        <v>49.6200000000001</v>
+        <f>F20-D20</f>
+        <v>42.4</v>
       </c>
       <c r="F20" s="1">
-        <v>1398.97</v>
+        <v>992.49</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="1"/>
-        <v>27.79</v>
+        <f>H20-F20</f>
+        <v>38.5899999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>1426.76</v>
+        <v>1031.08</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="2"/>
-        <v>29.02</v>
+        <f>J20-H20</f>
+        <v>22.6000000000001</v>
       </c>
       <c r="J20" s="1">
-        <v>1455.78</v>
+        <v>1053.68</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="3"/>
-        <v>56.8099999999999</v>
+        <f>J20-F20</f>
+        <v>61.1900000000001</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="4"/>
-        <v>106.43</v>
+        <f>J20-D20</f>
+        <v>103.59</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="5">
-        <v>927.15</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="0"/>
-        <v>17.9300000000001</v>
-      </c>
-      <c r="F21" s="5">
-        <v>945.08</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="1"/>
-        <v>24.04</v>
-      </c>
-      <c r="H21" s="5">
-        <v>969.12</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="2"/>
-        <v>26.96</v>
-      </c>
-      <c r="J21" s="5">
-        <v>996.08</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="4"/>
-        <v>68.9300000000001</v>
+      <c r="C21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="1">
+        <v>907.94</v>
+      </c>
+      <c r="E21" s="1">
+        <f>F21-D21</f>
+        <v>64.0799999999999</v>
+      </c>
+      <c r="F21" s="1">
+        <v>972.02</v>
+      </c>
+      <c r="G21" s="1">
+        <f>H21-F21</f>
+        <v>36.26</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1008.28</v>
+      </c>
+      <c r="I21" s="1">
+        <f>J21-H21</f>
+        <v>28.8</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1037.08</v>
+      </c>
+      <c r="K21" s="1">
+        <f>J21-F21</f>
+        <v>65.0599999999999</v>
+      </c>
+      <c r="L21" s="1">
+        <f>J21-D21</f>
+        <v>129.14</v>
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1317.56</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="0"/>
-        <v>15.77</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1333.33</v>
-      </c>
-      <c r="G22" s="1">
-        <f t="shared" si="1"/>
-        <v>15.1700000000001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1348.5</v>
-      </c>
-      <c r="I22" s="1">
-        <f t="shared" si="2"/>
-        <v>28.9300000000001</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1377.43</v>
-      </c>
-      <c r="K22" s="1">
-        <f t="shared" si="3"/>
-        <v>44.1000000000001</v>
-      </c>
-      <c r="L22" s="1">
-        <f t="shared" si="4"/>
-        <v>59.8700000000001</v>
+      <c r="D22" s="5">
+        <v>927.15</v>
+      </c>
+      <c r="E22" s="5">
+        <f>F22-D22</f>
+        <v>17.9300000000001</v>
+      </c>
+      <c r="F22" s="5">
+        <v>945.08</v>
+      </c>
+      <c r="G22" s="5">
+        <f>H22-F22</f>
+        <v>24.04</v>
+      </c>
+      <c r="H22" s="5">
+        <v>969.12</v>
+      </c>
+      <c r="I22" s="5">
+        <f>J22-H22</f>
+        <v>26.96</v>
+      </c>
+      <c r="J22" s="5">
+        <v>996.08</v>
+      </c>
+      <c r="K22" s="5">
+        <f>J22-F22</f>
+        <v>51</v>
+      </c>
+      <c r="L22" s="5">
+        <f>J22-D22</f>
+        <v>68.9300000000001</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2183.01</v>
-      </c>
-      <c r="E23" s="4">
-        <f t="shared" si="0"/>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F23" s="4">
-        <v>2207.13</v>
-      </c>
-      <c r="G23" s="4">
-        <f t="shared" si="1"/>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H23" s="4">
-        <v>2229.99</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="2"/>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J23" s="4">
-        <v>2241.77</v>
-      </c>
-      <c r="K23" s="4">
-        <f t="shared" si="3"/>
-        <v>34.6399999999999</v>
-      </c>
-      <c r="L23" s="4">
-        <f t="shared" si="4"/>
-        <v>58.7599999999998</v>
+      <c r="C23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="5">
+        <v>848.93</v>
+      </c>
+      <c r="E23" s="5">
+        <f>F23-D23</f>
+        <v>34.5600000000001</v>
+      </c>
+      <c r="F23" s="5">
+        <v>883.49</v>
+      </c>
+      <c r="G23" s="5">
+        <f>H23-F23</f>
+        <v>46.08</v>
+      </c>
+      <c r="H23" s="5">
+        <v>929.57</v>
+      </c>
+      <c r="I23" s="5">
+        <f>J23-H23</f>
+        <v>27.7399999999999</v>
+      </c>
+      <c r="J23" s="5">
+        <v>957.31</v>
+      </c>
+      <c r="K23" s="5">
+        <f>J23-F23</f>
+        <v>73.8199999999999</v>
+      </c>
+      <c r="L23" s="5">
+        <f>J23-D23</f>
+        <v>108.38</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2265,45 +2265,45 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" s="5">
-        <v>262.39</v>
+        <v>552.79</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
+        <f>F24-D24</f>
+        <v>15.9400000000001</v>
       </c>
       <c r="F24" s="5">
-        <v>273.89</v>
+        <v>568.73</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="1"/>
-        <v>13.97</v>
+        <f>H24-F24</f>
+        <v>1.61000000000001</v>
       </c>
       <c r="H24" s="5">
-        <v>287.86</v>
+        <v>570.34</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="2"/>
-        <v>16.24</v>
+        <f>J24-H24</f>
+        <v>7.13999999999999</v>
       </c>
       <c r="J24" s="5">
-        <v>304.1</v>
+        <v>577.48</v>
       </c>
       <c r="K24" s="5">
-        <f t="shared" si="3"/>
-        <v>30.21</v>
+        <f>J24-F24</f>
+        <v>8.75</v>
       </c>
       <c r="L24" s="5">
-        <f t="shared" si="4"/>
-        <v>41.71</v>
+        <f>J24-D24</f>
+        <v>24.6900000000001</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>46</v>
@@ -2323,21 +2323,21 @@
         <v>407.35</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="0"/>
+        <f>F25-D25</f>
         <v>13.86</v>
       </c>
       <c r="F25" s="5">
         <v>421.21</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="1"/>
+        <f>H25-F25</f>
         <v>16.43</v>
       </c>
       <c r="H25" s="5">
         <v>437.64</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="2"/>
+        <f>J25-H25</f>
         <v>13.64</v>
       </c>
       <c r="J25" s="5">
@@ -2348,7 +2348,7 @@
         <v>30.07</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="4"/>
+        <f>J25-D25</f>
         <v>43.9299999999999</v>
       </c>
       <c r="M25" s="1"/>
@@ -2357,45 +2357,45 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D26" s="5">
-        <v>305.29</v>
+        <v>363.88</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="0"/>
-        <v>17.97</v>
+        <f>F26-D26</f>
+        <v>14.21</v>
       </c>
       <c r="F26" s="5">
-        <v>323.26</v>
+        <v>378.09</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="1"/>
-        <v>10.82</v>
+        <f>H26-F26</f>
+        <v>11.22</v>
       </c>
       <c r="H26" s="5">
-        <v>334.08</v>
+        <v>389.31</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="2"/>
-        <v>16.2</v>
+        <f>J26-H26</f>
+        <v>13.62</v>
       </c>
       <c r="J26" s="5">
-        <v>350.28</v>
+        <v>402.93</v>
       </c>
       <c r="K26" s="5">
-        <f t="shared" si="3"/>
-        <v>27.02</v>
+        <f>J26-F26</f>
+        <v>24.84</v>
       </c>
       <c r="L26" s="5">
-        <f t="shared" si="4"/>
-        <v>44.99</v>
+        <f>J26-D26</f>
+        <v>39.05</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2403,45 +2403,45 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D27" s="5">
-        <v>363.88</v>
+        <v>305.29</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="0"/>
-        <v>14.21</v>
+        <f>F27-D27</f>
+        <v>17.97</v>
       </c>
       <c r="F27" s="5">
-        <v>378.09</v>
+        <v>323.26</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="1"/>
-        <v>11.22</v>
+        <f>H27-F27</f>
+        <v>10.82</v>
       </c>
       <c r="H27" s="5">
-        <v>389.31</v>
+        <v>334.08</v>
       </c>
       <c r="I27" s="5">
-        <f t="shared" si="2"/>
-        <v>13.62</v>
+        <f>J27-H27</f>
+        <v>16.2</v>
       </c>
       <c r="J27" s="5">
-        <v>402.93</v>
+        <v>350.28</v>
       </c>
       <c r="K27" s="5">
-        <f t="shared" si="3"/>
-        <v>24.84</v>
+        <f>J27-F27</f>
+        <v>27.02</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" si="4"/>
-        <v>39.05</v>
+        <f>J27-D27</f>
+        <v>44.99</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -2449,45 +2449,45 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" s="5">
-        <v>552.79</v>
+        <v>262.39</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="0"/>
-        <v>15.9400000000001</v>
+        <f>F28-D28</f>
+        <v>11.5</v>
       </c>
       <c r="F28" s="5">
-        <v>568.73</v>
+        <v>273.89</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="1"/>
-        <v>1.61000000000001</v>
+        <f>H28-F28</f>
+        <v>13.97</v>
       </c>
       <c r="H28" s="5">
-        <v>570.34</v>
+        <v>287.86</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="2"/>
-        <v>7.13999999999999</v>
+        <f>J28-H28</f>
+        <v>16.24</v>
       </c>
       <c r="J28" s="5">
-        <v>577.48</v>
+        <v>304.1</v>
       </c>
       <c r="K28" s="5">
-        <f t="shared" si="3"/>
-        <v>8.75</v>
+        <f>J28-F28</f>
+        <v>30.21</v>
       </c>
       <c r="L28" s="5">
-        <f t="shared" si="4"/>
-        <v>24.6900000000001</v>
+        <f>J28-D28</f>
+        <v>41.71</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
@@ -2575,7 +2575,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:L28">
-    <sortCondition ref="K2" descending="1"/>
+    <sortCondition ref="J2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="77">
   <si>
     <t>区服</t>
   </si>
@@ -45,12 +45,15 @@
     <t>战力（2025.4.16）</t>
   </si>
   <si>
-    <t>半月提升值</t>
+    <t>战力（2025.4.23）</t>
   </si>
   <si>
     <t>累计提升</t>
   </si>
   <si>
+    <t>首席英雄（流派）</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
     <t>大氪</t>
   </si>
   <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
     <t>148区</t>
   </si>
   <si>
@@ -69,18 +75,27 @@
     <t>中大氪</t>
   </si>
   <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
     <t>149区</t>
   </si>
   <si>
     <t>灰企鹅呆瓜</t>
   </si>
   <si>
+    <t>狐狸（快攻）</t>
+  </si>
+  <si>
     <t>145区</t>
   </si>
   <si>
     <t>Mr.Go</t>
   </si>
   <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
     <t>水煮肉片</t>
   </si>
   <si>
@@ -93,6 +108,9 @@
     <t>古月星辰</t>
   </si>
   <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
     <t>151区</t>
   </si>
   <si>
@@ -102,25 +120,43 @@
     <t>中低氪</t>
   </si>
   <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
     <t>杜佳捷</t>
   </si>
   <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
     <t>玩玩</t>
   </si>
   <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
     <t>1。</t>
   </si>
   <si>
     <t>低氪</t>
   </si>
   <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
     <t>星空</t>
   </si>
   <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
     <t>请叫我阿奎</t>
   </si>
   <si>
-    <t>小黑</t>
+    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>何斌</t>
@@ -138,15 +174,15 @@
     <t>开飞机的贝塔</t>
   </si>
   <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
     <t>152区</t>
   </si>
   <si>
     <t>养乐多</t>
   </si>
   <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
     <t>朱</t>
   </si>
   <si>
@@ -160,6 +196,9 @@
   </si>
   <si>
     <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
   </si>
   <si>
     <t>白夜</t>
@@ -219,9 +258,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -268,6 +307,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -283,7 +344,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,8 +365,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,35 +403,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -361,51 +428,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -420,187 +459,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,6 +650,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -653,21 +703,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -686,8 +721,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -695,19 +745,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -719,10 +758,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,137 +770,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -880,8 +919,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1199,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -1209,14 +1263,15 @@
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10.75" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
-    <col min="10" max="10" width="18.125" customWidth="1"/>
-    <col min="11" max="12" width="14.125" customWidth="1"/>
-    <col min="15" max="15" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.75" hidden="1" customWidth="1"/>
+    <col min="10" max="12" width="18.125" customWidth="1"/>
+    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="18.625" customWidth="1"/>
+    <col min="16" max="16" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1248,21 +1303,27 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>4105.48</v>
@@ -1289,23 +1350,29 @@
         <v>4480.66</v>
       </c>
       <c r="K2" s="2">
-        <f>J2-F2</f>
-        <v>193.97</v>
+        <f>L2-J2</f>
+        <v>104.900000000001</v>
       </c>
       <c r="L2" s="2">
-        <f>J2-D2</f>
-        <v>375.18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>4585.56</v>
+      </c>
+      <c r="M2" s="2">
+        <f>L2-D2</f>
+        <v>480.080000000001</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>2714.1</v>
@@ -1332,26 +1399,31 @@
         <v>3025.7</v>
       </c>
       <c r="K3" s="3">
-        <f>J3-F3</f>
-        <v>188.31</v>
+        <f>L3-J3</f>
+        <v>90.4100000000003</v>
       </c>
       <c r="L3" s="3">
-        <f>J3-D3</f>
-        <v>311.6</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
+        <v>3116.11</v>
+      </c>
+      <c r="M3" s="3">
+        <f>L3-D3</f>
+        <v>402.01</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="D4" s="4">
         <v>2533.85</v>
@@ -1378,26 +1450,31 @@
         <v>2751.45</v>
       </c>
       <c r="K4" s="4">
-        <f>J4-F4</f>
-        <v>167.55</v>
+        <f>L4-J4</f>
+        <v>83.1700000000001</v>
       </c>
       <c r="L4" s="4">
-        <f>J4-D4</f>
-        <v>217.6</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+        <v>2834.62</v>
+      </c>
+      <c r="M4" s="4">
+        <f>L4-D4</f>
+        <v>300.77</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4">
         <v>2136.24</v>
@@ -1424,26 +1501,31 @@
         <v>2286.73</v>
       </c>
       <c r="K5" s="4">
-        <f>J5-F5</f>
-        <v>109.67</v>
+        <f>L5-J5</f>
+        <v>25.52</v>
       </c>
       <c r="L5" s="4">
-        <f>J5-D5</f>
-        <v>150.49</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+        <v>2312.25</v>
+      </c>
+      <c r="M5" s="4">
+        <f>L5-D5</f>
+        <v>176.01</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4">
         <v>2183.01</v>
@@ -1470,26 +1552,31 @@
         <v>2241.77</v>
       </c>
       <c r="K6" s="4">
-        <f>J6-F6</f>
-        <v>34.6399999999999</v>
+        <f>L6-J6</f>
+        <v>13.0100000000002</v>
       </c>
       <c r="L6" s="4">
-        <f>J6-D6</f>
-        <v>58.7599999999998</v>
-      </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+        <v>2254.78</v>
+      </c>
+      <c r="M6" s="4">
+        <f>L6-D6</f>
+        <v>71.77</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4">
         <v>1966.62</v>
@@ -1516,72 +1603,82 @@
         <v>2139.9</v>
       </c>
       <c r="K7" s="4">
-        <f>J7-F7</f>
-        <v>124.26</v>
+        <f>L7-J7</f>
+        <v>53.1700000000001</v>
       </c>
       <c r="L7" s="4">
-        <f>J7-D7</f>
-        <v>173.28</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+        <v>2193.07</v>
+      </c>
+      <c r="M7" s="4">
+        <f>L7-D7</f>
+        <v>226.45</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
         <v>1754.54</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="4">
         <f>F8-D8</f>
         <v>53.3700000000001</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>1807.91</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="4">
         <f>H8-F8</f>
         <v>90.24</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="4">
         <v>1898.15</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="4">
         <f>J8-H8</f>
         <v>90.3799999999999</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="4">
         <v>1988.53</v>
       </c>
-      <c r="K8" s="1">
-        <f>J8-F8</f>
-        <v>180.62</v>
-      </c>
-      <c r="L8" s="1">
-        <f>J8-D8</f>
-        <v>233.99</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="K8" s="4">
+        <f>L8-J8</f>
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L8" s="4">
+        <v>2048.24</v>
+      </c>
+      <c r="M8" s="4">
+        <f>L8-D8</f>
+        <v>293.7</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1">
         <v>1735.94</v>
@@ -1608,26 +1705,31 @@
         <v>1924.25</v>
       </c>
       <c r="K9" s="1">
-        <f>J9-F9</f>
-        <v>139.71</v>
+        <f>L9-J9</f>
+        <v>35.73</v>
       </c>
       <c r="L9" s="1">
-        <f>J9-D9</f>
-        <v>188.31</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
+        <v>1959.98</v>
+      </c>
+      <c r="M9" s="1">
+        <f>L9-D9</f>
+        <v>224.04</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1">
         <v>1726.42</v>
@@ -1654,26 +1756,31 @@
         <v>1903.2</v>
       </c>
       <c r="K10" s="1">
-        <f>J10-F10</f>
-        <v>120.5</v>
+        <f>L10-J10</f>
+        <v>40.4099999999999</v>
       </c>
       <c r="L10" s="1">
-        <f>J10-D10</f>
-        <v>176.78</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+        <v>1943.61</v>
+      </c>
+      <c r="M10" s="1">
+        <f>L10-D10</f>
+        <v>217.19</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D11" s="1">
         <v>1576.18</v>
@@ -1700,26 +1807,31 @@
         <v>1688.09</v>
       </c>
       <c r="K11" s="1">
-        <f>J11-F11</f>
-        <v>73.0699999999999</v>
+        <f>L11-J11</f>
+        <v>21.49</v>
       </c>
       <c r="L11" s="1">
-        <f>J11-D11</f>
-        <v>111.91</v>
-      </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
+        <v>1709.58</v>
+      </c>
+      <c r="M11" s="1">
+        <f>L11-D11</f>
+        <v>133.4</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1">
         <v>1425.22</v>
@@ -1746,26 +1858,31 @@
         <v>1586.93</v>
       </c>
       <c r="K12" s="1">
-        <f>J12-F12</f>
-        <v>96.8500000000001</v>
+        <f>L12-J12</f>
+        <v>86.5599999999999</v>
       </c>
       <c r="L12" s="1">
-        <f>J12-D12</f>
-        <v>161.71</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+        <v>1673.49</v>
+      </c>
+      <c r="M12" s="1">
+        <f>L12-D12</f>
+        <v>248.27</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1">
         <v>1446.65</v>
@@ -1792,118 +1909,133 @@
         <v>1561.57</v>
       </c>
       <c r="K13" s="1">
-        <f>J13-F13</f>
-        <v>86.74</v>
+        <f>L13-J13</f>
+        <v>70.8600000000001</v>
       </c>
       <c r="L13" s="1">
-        <f>J13-D13</f>
-        <v>114.92</v>
-      </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+        <v>1632.43</v>
+      </c>
+      <c r="M13" s="1">
+        <f>L13-D13</f>
+        <v>185.78</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D14" s="1">
-        <v>1350.52</v>
+        <v>1349.35</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>52.6800000000001</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>1403.2</v>
+        <v>1398.97</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>55.3199999999999</v>
+        <v>27.79</v>
       </c>
       <c r="H14" s="1">
-        <v>1458.52</v>
+        <v>1426.76</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>32.6800000000001</v>
+        <v>29.02</v>
       </c>
       <c r="J14" s="1">
-        <v>1491.2</v>
+        <v>1455.78</v>
       </c>
       <c r="K14" s="1">
-        <f>J14-F14</f>
-        <v>88</v>
+        <f>L14-J14</f>
+        <v>97.8800000000001</v>
       </c>
       <c r="L14" s="1">
-        <f>J14-D14</f>
-        <v>140.68</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+        <v>1553.66</v>
+      </c>
+      <c r="M14" s="1">
+        <f>L14-D14</f>
+        <v>204.31</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1">
-        <v>1349.35</v>
+        <v>1350.52</v>
       </c>
       <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>49.6200000000001</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>1398.97</v>
+        <v>1403.2</v>
       </c>
       <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>27.79</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>1426.76</v>
+        <v>1458.52</v>
       </c>
       <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>29.02</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J15" s="1">
-        <v>1455.78</v>
+        <v>1491.2</v>
       </c>
       <c r="K15" s="1">
-        <f>J15-F15</f>
-        <v>56.8099999999999</v>
+        <f>L15-J15</f>
+        <v>54.96</v>
       </c>
       <c r="L15" s="1">
-        <f>J15-D15</f>
-        <v>106.43</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+        <v>1546.16</v>
+      </c>
+      <c r="M15" s="1">
+        <f>L15-D15</f>
+        <v>195.64</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D16" s="1">
         <v>1317.56</v>
@@ -1930,26 +2062,31 @@
         <v>1377.43</v>
       </c>
       <c r="K16" s="1">
-        <f>J16-F16</f>
-        <v>44.1000000000001</v>
+        <f>L16-J16</f>
+        <v>9.14999999999986</v>
       </c>
       <c r="L16" s="1">
-        <f>J16-D16</f>
-        <v>59.8700000000001</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+        <v>1386.58</v>
+      </c>
+      <c r="M16" s="1">
+        <f>L16-D16</f>
+        <v>69.02</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1">
         <v>1156.57</v>
@@ -1976,26 +2113,31 @@
         <v>1302.47</v>
       </c>
       <c r="K17" s="1">
-        <f>J17-F17</f>
-        <v>105.46</v>
+        <f>L17-J17</f>
+        <v>36.6399999999999</v>
       </c>
       <c r="L17" s="1">
-        <f>J17-D17</f>
-        <v>145.9</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
+        <v>1339.11</v>
+      </c>
+      <c r="M17" s="1">
+        <f>L17-D17</f>
+        <v>182.54</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1">
         <v>1060.77</v>
@@ -2022,26 +2164,31 @@
         <v>1191.44</v>
       </c>
       <c r="K18" s="1">
-        <f>J18-F18</f>
-        <v>67.4300000000001</v>
+        <f>L18-J18</f>
+        <v>40.22</v>
       </c>
       <c r="L18" s="1">
-        <f>J18-D18</f>
-        <v>130.67</v>
-      </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
+        <v>1231.66</v>
+      </c>
+      <c r="M18" s="1">
+        <f>L18-D18</f>
+        <v>170.89</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1">
         <v>953.78</v>
@@ -2068,210 +2215,235 @@
         <v>1109.52</v>
       </c>
       <c r="K19" s="1">
-        <f>J19-F19</f>
-        <v>126.77</v>
+        <f>L19-J19</f>
+        <v>36.46</v>
       </c>
       <c r="L19" s="1">
-        <f>J19-D19</f>
-        <v>155.74</v>
-      </c>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-    </row>
-    <row r="20" spans="1:15">
+        <v>1145.98</v>
+      </c>
+      <c r="M19" s="1">
+        <f>L19-D19</f>
+        <v>192.2</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1">
-        <v>950.09</v>
+        <v>907.94</v>
       </c>
       <c r="E20" s="1">
         <f>F20-D20</f>
-        <v>42.4</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>992.49</v>
+        <v>972.02</v>
       </c>
       <c r="G20" s="1">
         <f>H20-F20</f>
-        <v>38.5899999999999</v>
+        <v>36.26</v>
       </c>
       <c r="H20" s="1">
-        <v>1031.08</v>
+        <v>1008.28</v>
       </c>
       <c r="I20" s="1">
         <f>J20-H20</f>
-        <v>22.6000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="J20" s="1">
-        <v>1053.68</v>
+        <v>1037.08</v>
       </c>
       <c r="K20" s="1">
-        <f>J20-F20</f>
-        <v>61.1900000000001</v>
+        <f>L20-J20</f>
+        <v>40.1000000000001</v>
       </c>
       <c r="L20" s="1">
-        <f>J20-D20</f>
-        <v>103.59</v>
-      </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
+        <v>1077.18</v>
+      </c>
+      <c r="M20" s="1">
+        <f>L20-D20</f>
+        <v>169.24</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="O20" s="4"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20" s="4"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1">
-        <v>907.94</v>
+        <v>950.09</v>
       </c>
       <c r="E21" s="1">
         <f>F21-D21</f>
-        <v>64.0799999999999</v>
+        <v>42.4</v>
       </c>
       <c r="F21" s="1">
-        <v>972.02</v>
+        <v>992.49</v>
       </c>
       <c r="G21" s="1">
         <f>H21-F21</f>
-        <v>36.26</v>
+        <v>38.5899999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>1008.28</v>
+        <v>1031.08</v>
       </c>
       <c r="I21" s="1">
         <f>J21-H21</f>
-        <v>28.8</v>
+        <v>22.6000000000001</v>
       </c>
       <c r="J21" s="1">
-        <v>1037.08</v>
+        <v>1053.68</v>
       </c>
       <c r="K21" s="1">
-        <f>J21-F21</f>
-        <v>65.0599999999999</v>
+        <f>L21-J21</f>
+        <v>10.9299999999998</v>
       </c>
       <c r="L21" s="1">
-        <f>J21-D21</f>
-        <v>129.14</v>
-      </c>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+        <v>1064.61</v>
+      </c>
+      <c r="M21" s="1">
+        <f>L21-D21</f>
+        <v>114.52</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="1">
         <v>927.15</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="1">
         <f>F22-D22</f>
         <v>17.9300000000001</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="1">
         <v>945.08</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="1">
         <f>H22-F22</f>
         <v>24.04</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="1">
         <v>969.12</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="1">
         <f>J22-H22</f>
         <v>26.96</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="1">
         <v>996.08</v>
       </c>
-      <c r="K22" s="5">
-        <f>J22-F22</f>
-        <v>51</v>
-      </c>
-      <c r="L22" s="5">
-        <f>J22-D22</f>
-        <v>68.9300000000001</v>
-      </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
+      <c r="K22" s="1">
+        <f>L22-J22</f>
+        <v>23.3499999999999</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1019.43</v>
+      </c>
+      <c r="M22" s="1">
+        <f>L22-D22</f>
+        <v>92.28</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="O22" s="4"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="1">
         <v>848.93</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="1">
         <f>F23-D23</f>
         <v>34.5600000000001</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="1">
         <v>883.49</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="1">
         <f>H23-F23</f>
         <v>46.08</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="1">
         <v>929.57</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="1">
         <f>J23-H23</f>
         <v>27.7399999999999</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="1">
         <v>957.31</v>
       </c>
-      <c r="K23" s="5">
-        <f>J23-F23</f>
-        <v>73.8199999999999</v>
-      </c>
-      <c r="L23" s="5">
-        <f>J23-D23</f>
-        <v>108.38</v>
-      </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="K23" s="1">
+        <f>L23-J23</f>
+        <v>47.36</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1004.67</v>
+      </c>
+      <c r="M23" s="1">
+        <f>L23-D23</f>
+        <v>155.74</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5">
         <v>552.79</v>
@@ -2298,26 +2470,31 @@
         <v>577.48</v>
       </c>
       <c r="K24" s="5">
-        <f>J24-F24</f>
-        <v>8.75</v>
+        <f>L24-J24</f>
+        <v>2.88999999999999</v>
       </c>
       <c r="L24" s="5">
-        <f>J24-D24</f>
-        <v>24.6900000000001</v>
-      </c>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
+        <v>580.37</v>
+      </c>
+      <c r="M24" s="5">
+        <f>L24-D24</f>
+        <v>27.58</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D25" s="5">
         <v>407.35</v>
@@ -2344,26 +2521,31 @@
         <v>451.28</v>
       </c>
       <c r="K25" s="5">
-        <f>J25-F25</f>
-        <v>30.07</v>
+        <f>L25-J25</f>
+        <v>11.6</v>
       </c>
       <c r="L25" s="5">
-        <f>J25-D25</f>
-        <v>43.9299999999999</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
+        <v>462.88</v>
+      </c>
+      <c r="M25" s="5">
+        <f>L25-D25</f>
+        <v>55.53</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D26" s="5">
         <v>363.88</v>
@@ -2390,26 +2572,31 @@
         <v>402.93</v>
       </c>
       <c r="K26" s="5">
-        <f>J26-F26</f>
-        <v>24.84</v>
+        <f>L26-J26</f>
+        <v>11.13</v>
       </c>
       <c r="L26" s="5">
-        <f>J26-D26</f>
-        <v>39.05</v>
-      </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
+        <v>414.06</v>
+      </c>
+      <c r="M26" s="5">
+        <f>L26-D26</f>
+        <v>50.18</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D27" s="5">
         <v>305.29</v>
@@ -2436,26 +2623,31 @@
         <v>350.28</v>
       </c>
       <c r="K27" s="5">
-        <f>J27-F27</f>
-        <v>27.02</v>
+        <f>L27-J27</f>
+        <v>10.8</v>
       </c>
       <c r="L27" s="5">
-        <f>J27-D27</f>
-        <v>44.99</v>
-      </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
+        <v>361.08</v>
+      </c>
+      <c r="M27" s="5">
+        <f>L27-D27</f>
+        <v>55.79</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="O27" s="5"/>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D28" s="5">
         <v>262.39</v>
@@ -2482,100 +2674,105 @@
         <v>304.1</v>
       </c>
       <c r="K28" s="5">
-        <f>J28-F28</f>
-        <v>30.21</v>
+        <f>L28-J28</f>
+        <v>12.65</v>
       </c>
       <c r="L28" s="5">
-        <f>J28-D28</f>
-        <v>41.71</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+        <v>316.75</v>
+      </c>
+      <c r="M28" s="5">
+        <f>L28-D28</f>
+        <v>54.36</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:L28">
-    <sortCondition ref="J2" descending="1"/>
+  <sortState ref="A2:N28">
+    <sortCondition ref="L2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380"/>
+    <workbookView windowWidth="28800" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'19星域战力标'!$F$1:$F$28</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -66,6 +79,18 @@
     <t>圣母（杂糅）</t>
   </si>
   <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
     <t>148区</t>
   </si>
   <si>
@@ -78,6 +103,12 @@
     <t>眼镜妹（跳费）</t>
   </si>
   <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
     <t>149区</t>
   </si>
   <si>
@@ -87,130 +118,112 @@
     <t>狐狸（快攻）</t>
   </si>
   <si>
-    <t>145区</t>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>念苍生</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
   </si>
   <si>
     <t>Mr.Go</t>
   </si>
   <si>
-    <t>魔尊（快攻）</t>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
   </si>
   <si>
     <t>水煮肉片</t>
   </si>
   <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>秋雨</t>
   </si>
   <si>
     <t>何斌</t>
   </si>
   <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>念苍生</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
     <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -255,12 +268,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -306,52 +319,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -366,6 +367,29 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
@@ -374,20 +398,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -403,25 +413,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,17 +435,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,25 +472,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,157 +646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,13 +666,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -679,30 +714,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -714,15 +725,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -745,8 +747,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -755,148 +768,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -922,13 +935,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -940,52 +953,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1365,49 +1378,49 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3">
-        <v>2714.1</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="1">
+        <v>1349.35</v>
+      </c>
+      <c r="E3" s="1">
         <f>F3-D3</f>
-        <v>123.29</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2837.39</v>
-      </c>
-      <c r="G3" s="3">
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1398.97</v>
+      </c>
+      <c r="G3" s="1">
         <f>H3-F3</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2933.24</v>
-      </c>
-      <c r="I3" s="3">
+        <v>27.79</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1426.76</v>
+      </c>
+      <c r="I3" s="1">
         <f>J3-H3</f>
-        <v>92.46</v>
-      </c>
-      <c r="J3" s="3">
-        <v>3025.7</v>
-      </c>
-      <c r="K3" s="3">
+        <v>29.02</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1455.78</v>
+      </c>
+      <c r="K3" s="1">
         <f>L3-J3</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L3" s="3">
-        <v>3116.11</v>
-      </c>
-      <c r="M3" s="3">
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1553.66</v>
+      </c>
+      <c r="M3" s="1">
         <f>L3-D3</f>
-        <v>402.01</v>
+        <v>204.31</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>18</v>
@@ -1416,218 +1429,218 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2533.85</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2714.1</v>
+      </c>
+      <c r="E4" s="3">
         <f>F4-D4</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2583.9</v>
-      </c>
-      <c r="G4" s="4">
+        <v>123.29</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2837.39</v>
+      </c>
+      <c r="G4" s="3">
         <f>H4-F4</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H4" s="4">
-        <v>2669.66</v>
-      </c>
-      <c r="I4" s="4">
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2933.24</v>
+      </c>
+      <c r="I4" s="3">
         <f>J4-H4</f>
-        <v>81.79</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2751.45</v>
-      </c>
-      <c r="K4" s="4">
+        <v>92.46</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3025.7</v>
+      </c>
+      <c r="K4" s="3">
         <f>L4-J4</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L4" s="4">
-        <v>2834.62</v>
-      </c>
-      <c r="M4" s="4">
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L4" s="3">
+        <v>3116.11</v>
+      </c>
+      <c r="M4" s="3">
         <f>L4-D4</f>
-        <v>300.77</v>
+        <v>402.01</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2136.24</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1425.22</v>
+      </c>
+      <c r="E5" s="1">
         <f>F5-D5</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2177.06</v>
-      </c>
-      <c r="G5" s="4">
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1490.08</v>
+      </c>
+      <c r="G5" s="1">
         <f>H5-F5</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2239.66</v>
-      </c>
-      <c r="I5" s="4">
+        <v>46</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1536.08</v>
+      </c>
+      <c r="I5" s="1">
         <f>J5-H5</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J5" s="4">
-        <v>2286.73</v>
-      </c>
-      <c r="K5" s="4">
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1586.93</v>
+      </c>
+      <c r="K5" s="1">
         <f>L5-J5</f>
-        <v>25.52</v>
-      </c>
-      <c r="L5" s="4">
-        <v>2312.25</v>
-      </c>
-      <c r="M5" s="4">
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1673.49</v>
+      </c>
+      <c r="M5" s="1">
         <f>L5-D5</f>
-        <v>176.01</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>24</v>
+        <v>248.27</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4">
-        <v>2183.01</v>
+        <v>2533.85</v>
       </c>
       <c r="E6" s="4">
         <f>F6-D6</f>
-        <v>24.1199999999999</v>
+        <v>50.0500000000002</v>
       </c>
       <c r="F6" s="4">
-        <v>2207.13</v>
+        <v>2583.9</v>
       </c>
       <c r="G6" s="4">
         <f>H6-F6</f>
-        <v>22.8599999999997</v>
+        <v>85.7599999999998</v>
       </c>
       <c r="H6" s="4">
-        <v>2229.99</v>
+        <v>2669.66</v>
       </c>
       <c r="I6" s="4">
         <f>J6-H6</f>
-        <v>11.7800000000002</v>
+        <v>81.79</v>
       </c>
       <c r="J6" s="4">
-        <v>2241.77</v>
+        <v>2751.45</v>
       </c>
       <c r="K6" s="4">
         <f>L6-J6</f>
-        <v>13.0100000000002</v>
+        <v>83.1700000000001</v>
       </c>
       <c r="L6" s="4">
-        <v>2254.78</v>
+        <v>2834.62</v>
       </c>
       <c r="M6" s="4">
         <f>L6-D6</f>
-        <v>71.77</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>18</v>
+        <v>300.77</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4">
-        <v>1966.62</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="1">
+        <v>1446.65</v>
+      </c>
+      <c r="E7" s="1">
         <f>F7-D7</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2015.64</v>
-      </c>
-      <c r="G7" s="4">
+        <v>28.1799999999998</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1474.83</v>
+      </c>
+      <c r="G7" s="1">
         <f>H7-F7</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H7" s="4">
-        <v>2049.8</v>
-      </c>
-      <c r="I7" s="4">
+        <v>63.8200000000002</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1538.65</v>
+      </c>
+      <c r="I7" s="1">
         <f>J7-H7</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J7" s="4">
-        <v>2139.9</v>
-      </c>
-      <c r="K7" s="4">
+        <v>22.9199999999998</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1561.57</v>
+      </c>
+      <c r="K7" s="1">
         <f>L7-J7</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L7" s="4">
-        <v>2193.07</v>
-      </c>
-      <c r="M7" s="4">
+        <v>70.8600000000001</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1632.43</v>
+      </c>
+      <c r="M7" s="1">
         <f>L7-D7</f>
-        <v>226.45</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>24</v>
+        <v>185.78</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4">
         <v>1754.54</v>
@@ -1664,110 +1677,110 @@
         <f>L8-D8</f>
         <v>293.7</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>29</v>
+      <c r="N8" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1">
-        <v>1735.94</v>
+        <v>1350.52</v>
       </c>
       <c r="E9" s="1">
         <f>F9-D9</f>
-        <v>48.5999999999999</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F9" s="1">
-        <v>1784.54</v>
+        <v>1403.2</v>
       </c>
       <c r="G9" s="1">
         <f>H9-F9</f>
-        <v>74.1600000000001</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>1858.7</v>
+        <v>1458.52</v>
       </c>
       <c r="I9" s="1">
         <f>J9-H9</f>
-        <v>65.55</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J9" s="1">
-        <v>1924.25</v>
+        <v>1491.2</v>
       </c>
       <c r="K9" s="1">
         <f>L9-J9</f>
-        <v>35.73</v>
+        <v>54.96</v>
       </c>
       <c r="L9" s="1">
-        <v>1959.98</v>
+        <v>1546.16</v>
       </c>
       <c r="M9" s="1">
         <f>L9-D9</f>
-        <v>224.04</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>33</v>
+        <v>195.64</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1726.42</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1966.62</v>
+      </c>
+      <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>56.28</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1782.7</v>
-      </c>
-      <c r="G10" s="1">
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2015.64</v>
+      </c>
+      <c r="G10" s="4">
         <f>H10-F10</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1853.62</v>
-      </c>
-      <c r="I10" s="1">
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2049.8</v>
+      </c>
+      <c r="I10" s="4">
         <f>J10-H10</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1903.2</v>
-      </c>
-      <c r="K10" s="1">
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2139.9</v>
+      </c>
+      <c r="K10" s="4">
         <f>L10-J10</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1943.61</v>
-      </c>
-      <c r="M10" s="1">
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L10" s="4">
+        <v>2193.07</v>
+      </c>
+      <c r="M10" s="4">
         <f>L10-D10</f>
-        <v>217.19</v>
+        <v>226.45</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1777,98 +1790,98 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1">
-        <v>1576.18</v>
+        <v>848.93</v>
       </c>
       <c r="E11" s="1">
         <f>F11-D11</f>
-        <v>38.8399999999999</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>1615.02</v>
+        <v>883.49</v>
       </c>
       <c r="G11" s="1">
         <f>H11-F11</f>
-        <v>35.5999999999999</v>
+        <v>46.08</v>
       </c>
       <c r="H11" s="1">
-        <v>1650.62</v>
+        <v>929.57</v>
       </c>
       <c r="I11" s="1">
         <f>J11-H11</f>
-        <v>37.47</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J11" s="1">
-        <v>1688.09</v>
+        <v>957.31</v>
       </c>
       <c r="K11" s="1">
         <f>L11-J11</f>
-        <v>21.49</v>
+        <v>47.36</v>
       </c>
       <c r="L11" s="1">
-        <v>1709.58</v>
+        <v>1004.67</v>
       </c>
       <c r="M11" s="1">
         <f>L11-D11</f>
-        <v>133.4</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>37</v>
+        <v>155.74</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1">
-        <v>1425.22</v>
+        <v>1726.42</v>
       </c>
       <c r="E12" s="1">
         <f>F12-D12</f>
-        <v>64.8599999999999</v>
+        <v>56.28</v>
       </c>
       <c r="F12" s="1">
-        <v>1490.08</v>
+        <v>1782.7</v>
       </c>
       <c r="G12" s="1">
         <f>H12-F12</f>
-        <v>46</v>
+        <v>70.9199999999998</v>
       </c>
       <c r="H12" s="1">
-        <v>1536.08</v>
+        <v>1853.62</v>
       </c>
       <c r="I12" s="1">
         <f>J12-H12</f>
-        <v>50.8500000000001</v>
+        <v>49.5800000000002</v>
       </c>
       <c r="J12" s="1">
-        <v>1586.93</v>
+        <v>1903.2</v>
       </c>
       <c r="K12" s="1">
         <f>L12-J12</f>
-        <v>86.5599999999999</v>
+        <v>40.4099999999999</v>
       </c>
       <c r="L12" s="1">
-        <v>1673.49</v>
+        <v>1943.61</v>
       </c>
       <c r="M12" s="1">
         <f>L12-D12</f>
-        <v>248.27</v>
-      </c>
-      <c r="N12" s="9" t="s">
+        <v>217.19</v>
+      </c>
+      <c r="N12" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O12" s="3"/>
@@ -1876,561 +1889,561 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
-        <v>1446.65</v>
+        <v>1060.77</v>
       </c>
       <c r="E13" s="1">
         <f>F13-D13</f>
-        <v>28.1799999999998</v>
+        <v>63.24</v>
       </c>
       <c r="F13" s="1">
-        <v>1474.83</v>
+        <v>1124.01</v>
       </c>
       <c r="G13" s="1">
         <f>H13-F13</f>
-        <v>63.8200000000002</v>
+        <v>19.6700000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>1538.65</v>
+        <v>1143.68</v>
       </c>
       <c r="I13" s="1">
         <f>J13-H13</f>
-        <v>22.9199999999998</v>
+        <v>47.76</v>
       </c>
       <c r="J13" s="1">
-        <v>1561.57</v>
+        <v>1191.44</v>
       </c>
       <c r="K13" s="1">
         <f>L13-J13</f>
-        <v>70.8600000000001</v>
+        <v>40.22</v>
       </c>
       <c r="L13" s="1">
-        <v>1632.43</v>
+        <v>1231.66</v>
       </c>
       <c r="M13" s="1">
         <f>L13-D13</f>
-        <v>185.78</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>42</v>
+        <v>170.89</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
-        <v>1349.35</v>
+        <v>907.94</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>49.6200000000001</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>1398.97</v>
+        <v>972.02</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>27.79</v>
+        <v>36.26</v>
       </c>
       <c r="H14" s="1">
-        <v>1426.76</v>
+        <v>1008.28</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>29.02</v>
+        <v>28.8</v>
       </c>
       <c r="J14" s="1">
-        <v>1455.78</v>
+        <v>1037.08</v>
       </c>
       <c r="K14" s="1">
         <f>L14-J14</f>
-        <v>97.8800000000001</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>1553.66</v>
+        <v>1077.18</v>
       </c>
       <c r="M14" s="1">
         <f>L14-D14</f>
-        <v>204.31</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>40</v>
+        <v>169.24</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1">
-        <v>1350.52</v>
+        <v>1156.57</v>
       </c>
       <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>52.6800000000001</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>1403.2</v>
+        <v>1197.01</v>
       </c>
       <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>55.3199999999999</v>
+        <v>46.97</v>
       </c>
       <c r="H15" s="1">
-        <v>1458.52</v>
+        <v>1243.98</v>
       </c>
       <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>32.6800000000001</v>
+        <v>58.49</v>
       </c>
       <c r="J15" s="1">
-        <v>1491.2</v>
+        <v>1302.47</v>
       </c>
       <c r="K15" s="1">
         <f>L15-J15</f>
-        <v>54.96</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L15" s="1">
-        <v>1546.16</v>
+        <v>1339.11</v>
       </c>
       <c r="M15" s="1">
         <f>L15-D15</f>
-        <v>195.64</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>45</v>
+        <v>182.54</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1">
-        <v>1317.56</v>
+        <v>953.78</v>
       </c>
       <c r="E16" s="1">
         <f>F16-D16</f>
-        <v>15.77</v>
+        <v>28.97</v>
       </c>
       <c r="F16" s="1">
-        <v>1333.33</v>
+        <v>982.75</v>
       </c>
       <c r="G16" s="1">
         <f>H16-F16</f>
-        <v>15.1700000000001</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>1348.5</v>
+        <v>1066.68</v>
       </c>
       <c r="I16" s="1">
         <f>J16-H16</f>
-        <v>28.9300000000001</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J16" s="1">
-        <v>1377.43</v>
+        <v>1109.52</v>
       </c>
       <c r="K16" s="1">
         <f>L16-J16</f>
-        <v>9.14999999999986</v>
+        <v>36.46</v>
       </c>
       <c r="L16" s="1">
-        <v>1386.58</v>
+        <v>1145.98</v>
       </c>
       <c r="M16" s="1">
         <f>L16-D16</f>
-        <v>69.02</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>35</v>
+        <v>192.2</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
-        <v>1156.57</v>
+        <v>1735.94</v>
       </c>
       <c r="E17" s="1">
         <f>F17-D17</f>
-        <v>40.4400000000001</v>
+        <v>48.5999999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>1197.01</v>
+        <v>1784.54</v>
       </c>
       <c r="G17" s="1">
         <f>H17-F17</f>
-        <v>46.97</v>
+        <v>74.1600000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>1243.98</v>
+        <v>1858.7</v>
       </c>
       <c r="I17" s="1">
         <f>J17-H17</f>
-        <v>58.49</v>
+        <v>65.55</v>
       </c>
       <c r="J17" s="1">
-        <v>1302.47</v>
+        <v>1924.25</v>
       </c>
       <c r="K17" s="1">
         <f>L17-J17</f>
-        <v>36.6399999999999</v>
+        <v>35.73</v>
       </c>
       <c r="L17" s="1">
-        <v>1339.11</v>
+        <v>1959.98</v>
       </c>
       <c r="M17" s="1">
         <f>L17-D17</f>
-        <v>182.54</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>40</v>
+        <v>224.04</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1060.77</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="C18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2136.24</v>
+      </c>
+      <c r="E18" s="4">
         <f>F18-D18</f>
-        <v>63.24</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1124.01</v>
-      </c>
-      <c r="G18" s="1">
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2177.06</v>
+      </c>
+      <c r="G18" s="4">
         <f>H18-F18</f>
-        <v>19.6700000000001</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1143.68</v>
-      </c>
-      <c r="I18" s="1">
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H18" s="4">
+        <v>2239.66</v>
+      </c>
+      <c r="I18" s="4">
         <f>J18-H18</f>
-        <v>47.76</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1191.44</v>
-      </c>
-      <c r="K18" s="1">
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J18" s="4">
+        <v>2286.73</v>
+      </c>
+      <c r="K18" s="4">
         <f>L18-J18</f>
-        <v>40.22</v>
-      </c>
-      <c r="L18" s="1">
-        <v>1231.66</v>
-      </c>
-      <c r="M18" s="1">
+        <v>25.52</v>
+      </c>
+      <c r="L18" s="4">
+        <v>2312.25</v>
+      </c>
+      <c r="M18" s="4">
         <f>L18-D18</f>
-        <v>170.89</v>
+        <v>176.01</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="D19" s="1">
-        <v>953.78</v>
+        <v>927.15</v>
       </c>
       <c r="E19" s="1">
         <f>F19-D19</f>
-        <v>28.97</v>
+        <v>17.9300000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>982.75</v>
+        <v>945.08</v>
       </c>
       <c r="G19" s="1">
         <f>H19-F19</f>
-        <v>83.9300000000001</v>
+        <v>24.04</v>
       </c>
       <c r="H19" s="1">
-        <v>1066.68</v>
+        <v>969.12</v>
       </c>
       <c r="I19" s="1">
         <f>J19-H19</f>
-        <v>42.8399999999999</v>
+        <v>26.96</v>
       </c>
       <c r="J19" s="1">
-        <v>1109.52</v>
+        <v>996.08</v>
       </c>
       <c r="K19" s="1">
         <f>L19-J19</f>
-        <v>36.46</v>
+        <v>23.3499999999999</v>
       </c>
       <c r="L19" s="1">
-        <v>1145.98</v>
+        <v>1019.43</v>
       </c>
       <c r="M19" s="1">
         <f>L19-D19</f>
-        <v>192.2</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>42</v>
+        <v>92.28</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1">
-        <v>907.94</v>
+        <v>1576.18</v>
       </c>
       <c r="E20" s="1">
         <f>F20-D20</f>
-        <v>64.0799999999999</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>972.02</v>
+        <v>1615.02</v>
       </c>
       <c r="G20" s="1">
         <f>H20-F20</f>
-        <v>36.26</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>1008.28</v>
+        <v>1650.62</v>
       </c>
       <c r="I20" s="1">
         <f>J20-H20</f>
-        <v>28.8</v>
+        <v>37.47</v>
       </c>
       <c r="J20" s="1">
-        <v>1037.08</v>
+        <v>1688.09</v>
       </c>
       <c r="K20" s="1">
         <f>L20-J20</f>
-        <v>40.1000000000001</v>
+        <v>21.49</v>
       </c>
       <c r="L20" s="1">
-        <v>1077.18</v>
+        <v>1709.58</v>
       </c>
       <c r="M20" s="1">
         <f>L20-D20</f>
-        <v>169.24</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>18</v>
+        <v>133.4</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="1">
-        <v>950.09</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D21" s="4">
+        <v>2183.01</v>
+      </c>
+      <c r="E21" s="4">
         <f>F21-D21</f>
-        <v>42.4</v>
-      </c>
-      <c r="F21" s="1">
-        <v>992.49</v>
-      </c>
-      <c r="G21" s="1">
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2207.13</v>
+      </c>
+      <c r="G21" s="4">
         <f>H21-F21</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H21" s="1">
-        <v>1031.08</v>
-      </c>
-      <c r="I21" s="1">
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H21" s="4">
+        <v>2229.99</v>
+      </c>
+      <c r="I21" s="4">
         <f>J21-H21</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1053.68</v>
-      </c>
-      <c r="K21" s="1">
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J21" s="4">
+        <v>2241.77</v>
+      </c>
+      <c r="K21" s="4">
         <f>L21-J21</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L21" s="1">
-        <v>1064.61</v>
-      </c>
-      <c r="M21" s="1">
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L21" s="4">
+        <v>2254.78</v>
+      </c>
+      <c r="M21" s="4">
         <f>L21-D21</f>
-        <v>114.52</v>
+        <v>71.77</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="1">
-        <v>927.15</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="C22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="5">
+        <v>262.39</v>
+      </c>
+      <c r="E22" s="5">
         <f>F22-D22</f>
-        <v>17.9300000000001</v>
-      </c>
-      <c r="F22" s="1">
-        <v>945.08</v>
-      </c>
-      <c r="G22" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="F22" s="5">
+        <v>273.89</v>
+      </c>
+      <c r="G22" s="5">
         <f>H22-F22</f>
-        <v>24.04</v>
-      </c>
-      <c r="H22" s="1">
-        <v>969.12</v>
-      </c>
-      <c r="I22" s="1">
+        <v>13.97</v>
+      </c>
+      <c r="H22" s="5">
+        <v>287.86</v>
+      </c>
+      <c r="I22" s="5">
         <f>J22-H22</f>
-        <v>26.96</v>
-      </c>
-      <c r="J22" s="1">
-        <v>996.08</v>
-      </c>
-      <c r="K22" s="1">
+        <v>16.24</v>
+      </c>
+      <c r="J22" s="5">
+        <v>304.1</v>
+      </c>
+      <c r="K22" s="5">
         <f>L22-J22</f>
-        <v>23.3499999999999</v>
-      </c>
-      <c r="L22" s="1">
-        <v>1019.43</v>
-      </c>
-      <c r="M22" s="1">
+        <v>12.65</v>
+      </c>
+      <c r="L22" s="5">
+        <v>316.75</v>
+      </c>
+      <c r="M22" s="5">
         <f>L22-D22</f>
-        <v>92.28</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>40</v>
+        <v>54.36</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="5">
+        <v>407.35</v>
+      </c>
+      <c r="E23" s="5">
+        <f>F23-D23</f>
+        <v>13.86</v>
+      </c>
+      <c r="F23" s="5">
+        <v>421.21</v>
+      </c>
+      <c r="G23" s="5">
+        <f>H23-F23</f>
+        <v>16.43</v>
+      </c>
+      <c r="H23" s="5">
+        <v>437.64</v>
+      </c>
+      <c r="I23" s="5">
+        <f>J23-H23</f>
+        <v>13.64</v>
+      </c>
+      <c r="J23" s="5">
+        <v>451.28</v>
+      </c>
+      <c r="K23" s="5">
+        <f>L23-J23</f>
+        <v>11.6</v>
+      </c>
+      <c r="L23" s="5">
+        <v>462.88</v>
+      </c>
+      <c r="M23" s="5">
+        <f>L23-D23</f>
+        <v>55.53</v>
+      </c>
+      <c r="N23" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="1">
-        <v>848.93</v>
-      </c>
-      <c r="E23" s="1">
-        <f>F23-D23</f>
-        <v>34.5600000000001</v>
-      </c>
-      <c r="F23" s="1">
-        <v>883.49</v>
-      </c>
-      <c r="G23" s="1">
-        <f>H23-F23</f>
-        <v>46.08</v>
-      </c>
-      <c r="H23" s="1">
-        <v>929.57</v>
-      </c>
-      <c r="I23" s="1">
-        <f>J23-H23</f>
-        <v>27.7399999999999</v>
-      </c>
-      <c r="J23" s="1">
-        <v>957.31</v>
-      </c>
-      <c r="K23" s="1">
-        <f>L23-J23</f>
-        <v>47.36</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1004.67</v>
-      </c>
-      <c r="M23" s="1">
-        <f>L23-D23</f>
-        <v>155.74</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -2443,197 +2456,197 @@
         <v>57</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D24" s="5">
-        <v>552.79</v>
+        <v>363.88</v>
       </c>
       <c r="E24" s="5">
         <f>F24-D24</f>
-        <v>15.9400000000001</v>
+        <v>14.21</v>
       </c>
       <c r="F24" s="5">
-        <v>568.73</v>
+        <v>378.09</v>
       </c>
       <c r="G24" s="5">
         <f>H24-F24</f>
-        <v>1.61000000000001</v>
+        <v>11.22</v>
       </c>
       <c r="H24" s="5">
-        <v>570.34</v>
+        <v>389.31</v>
       </c>
       <c r="I24" s="5">
         <f>J24-H24</f>
-        <v>7.13999999999999</v>
+        <v>13.62</v>
       </c>
       <c r="J24" s="5">
-        <v>577.48</v>
+        <v>402.93</v>
       </c>
       <c r="K24" s="5">
         <f>L24-J24</f>
-        <v>2.88999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="L24" s="5">
-        <v>580.37</v>
+        <v>414.06</v>
       </c>
       <c r="M24" s="5">
         <f>L24-D24</f>
-        <v>27.58</v>
+        <v>50.18</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="5">
-        <v>407.35</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1">
+        <v>950.09</v>
+      </c>
+      <c r="E25" s="1">
         <f>F25-D25</f>
-        <v>13.86</v>
-      </c>
-      <c r="F25" s="5">
-        <v>421.21</v>
-      </c>
-      <c r="G25" s="5">
+        <v>42.4</v>
+      </c>
+      <c r="F25" s="1">
+        <v>992.49</v>
+      </c>
+      <c r="G25" s="1">
         <f>H25-F25</f>
-        <v>16.43</v>
-      </c>
-      <c r="H25" s="5">
-        <v>437.64</v>
-      </c>
-      <c r="I25" s="5">
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1031.08</v>
+      </c>
+      <c r="I25" s="1">
         <f>J25-H25</f>
-        <v>13.64</v>
-      </c>
-      <c r="J25" s="5">
-        <v>451.28</v>
-      </c>
-      <c r="K25" s="5">
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1053.68</v>
+      </c>
+      <c r="K25" s="1">
         <f>L25-J25</f>
-        <v>11.6</v>
-      </c>
-      <c r="L25" s="5">
-        <v>462.88</v>
-      </c>
-      <c r="M25" s="5">
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1064.61</v>
+      </c>
+      <c r="M25" s="1">
         <f>L25-D25</f>
-        <v>55.53</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>59</v>
+        <v>114.52</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D26" s="5">
-        <v>363.88</v>
+        <v>305.29</v>
       </c>
       <c r="E26" s="5">
         <f>F26-D26</f>
-        <v>14.21</v>
+        <v>17.97</v>
       </c>
       <c r="F26" s="5">
-        <v>378.09</v>
+        <v>323.26</v>
       </c>
       <c r="G26" s="5">
         <f>H26-F26</f>
-        <v>11.22</v>
+        <v>10.82</v>
       </c>
       <c r="H26" s="5">
-        <v>389.31</v>
+        <v>334.08</v>
       </c>
       <c r="I26" s="5">
         <f>J26-H26</f>
-        <v>13.62</v>
+        <v>16.2</v>
       </c>
       <c r="J26" s="5">
-        <v>402.93</v>
+        <v>350.28</v>
       </c>
       <c r="K26" s="5">
         <f>L26-J26</f>
-        <v>11.13</v>
+        <v>10.8</v>
       </c>
       <c r="L26" s="5">
-        <v>414.06</v>
+        <v>361.08</v>
       </c>
       <c r="M26" s="5">
         <f>L26-D26</f>
-        <v>50.18</v>
+        <v>55.79</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="5">
-        <v>305.29</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="C27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1317.56</v>
+      </c>
+      <c r="E27" s="1">
         <f>F27-D27</f>
-        <v>17.97</v>
-      </c>
-      <c r="F27" s="5">
-        <v>323.26</v>
-      </c>
-      <c r="G27" s="5">
+        <v>15.77</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1333.33</v>
+      </c>
+      <c r="G27" s="1">
         <f>H27-F27</f>
-        <v>10.82</v>
-      </c>
-      <c r="H27" s="5">
-        <v>334.08</v>
-      </c>
-      <c r="I27" s="5">
+        <v>15.1700000000001</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1348.5</v>
+      </c>
+      <c r="I27" s="1">
         <f>J27-H27</f>
-        <v>16.2</v>
-      </c>
-      <c r="J27" s="5">
-        <v>350.28</v>
-      </c>
-      <c r="K27" s="5">
+        <v>28.9300000000001</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1377.43</v>
+      </c>
+      <c r="K27" s="1">
         <f>L27-J27</f>
-        <v>10.8</v>
-      </c>
-      <c r="L27" s="5">
-        <v>361.08</v>
-      </c>
-      <c r="M27" s="5">
+        <v>9.14999999999986</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1386.58</v>
+      </c>
+      <c r="M27" s="1">
         <f>L27-D27</f>
-        <v>55.79</v>
-      </c>
-      <c r="N27" s="11" t="s">
+        <v>69.02</v>
+      </c>
+      <c r="N27" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O27" s="5"/>
@@ -2641,51 +2654,51 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="5" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D28" s="5">
-        <v>262.39</v>
+        <v>552.79</v>
       </c>
       <c r="E28" s="5">
         <f>F28-D28</f>
-        <v>11.5</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F28" s="5">
-        <v>273.89</v>
+        <v>568.73</v>
       </c>
       <c r="G28" s="5">
         <f>H28-F28</f>
-        <v>13.97</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H28" s="5">
-        <v>287.86</v>
+        <v>570.34</v>
       </c>
       <c r="I28" s="5">
         <f>J28-H28</f>
-        <v>16.24</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J28" s="5">
-        <v>304.1</v>
+        <v>577.48</v>
       </c>
       <c r="K28" s="5">
         <f>L28-J28</f>
-        <v>12.65</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L28" s="5">
-        <v>316.75</v>
+        <v>580.37</v>
       </c>
       <c r="M28" s="5">
         <f>L28-D28</f>
-        <v>54.36</v>
+        <v>27.58</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
@@ -2700,7 +2713,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>66</v>
@@ -2708,7 +2721,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -2716,7 +2729,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
         <v>68</v>
@@ -2724,7 +2737,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>69</v>
@@ -2732,7 +2745,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
         <v>70</v>
@@ -2740,7 +2753,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
         <v>71</v>
@@ -2772,7 +2785,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:N28">
-    <sortCondition ref="L2" descending="1"/>
+    <sortCondition ref="K2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -79,151 +79,151 @@
     <t>圣母（杂糅）</t>
   </si>
   <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>狐狸（快攻）</t>
+  </si>
+  <si>
     <t>145区</t>
   </si>
   <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
     <t>小黑</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>狐狸（快攻）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
-  </si>
-  <si>
     <t>请叫我阿奎</t>
   </si>
   <si>
     <t>丽娅（杂糅）</t>
   </si>
   <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
+    <t>何斌</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>念苍生</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
   </si>
   <si>
     <t>[永恒]</t>
   </si>
   <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>念苍生</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>秋雨</t>
   </si>
   <si>
     <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>何斌</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -935,13 +935,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1378,49 +1378,49 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1">
-        <v>1349.35</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="3">
+        <v>2714.1</v>
+      </c>
+      <c r="E3" s="3">
         <f>F3-D3</f>
-        <v>49.6200000000001</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1398.97</v>
-      </c>
-      <c r="G3" s="1">
+        <v>123.29</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2837.39</v>
+      </c>
+      <c r="G3" s="3">
         <f>H3-F3</f>
-        <v>27.79</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1426.76</v>
-      </c>
-      <c r="I3" s="1">
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2933.24</v>
+      </c>
+      <c r="I3" s="3">
         <f>J3-H3</f>
-        <v>29.02</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1455.78</v>
-      </c>
-      <c r="K3" s="1">
+        <v>92.46</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3025.7</v>
+      </c>
+      <c r="K3" s="3">
         <f>L3-J3</f>
-        <v>97.8800000000001</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1553.66</v>
-      </c>
-      <c r="M3" s="1">
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3116.11</v>
+      </c>
+      <c r="M3" s="3">
         <f>L3-D3</f>
-        <v>204.31</v>
+        <v>402.01</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>18</v>
@@ -1429,218 +1429,218 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2533.85</v>
+      </c>
+      <c r="E4" s="4">
+        <f>F4-D4</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2583.9</v>
+      </c>
+      <c r="G4" s="4">
+        <f>H4-F4</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2669.66</v>
+      </c>
+      <c r="I4" s="4">
+        <f>J4-H4</f>
+        <v>81.79</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2751.45</v>
+      </c>
+      <c r="K4" s="4">
+        <f>L4-J4</f>
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L4" s="4">
+        <v>2834.62</v>
+      </c>
+      <c r="M4" s="4">
+        <f>L4-D4</f>
+        <v>300.77</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2714.1</v>
-      </c>
-      <c r="E4" s="3">
-        <f>F4-D4</f>
-        <v>123.29</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2837.39</v>
-      </c>
-      <c r="G4" s="3">
-        <f>H4-F4</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2933.24</v>
-      </c>
-      <c r="I4" s="3">
-        <f>J4-H4</f>
-        <v>92.46</v>
-      </c>
-      <c r="J4" s="3">
-        <v>3025.7</v>
-      </c>
-      <c r="K4" s="3">
-        <f>L4-J4</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L4" s="3">
-        <v>3116.11</v>
-      </c>
-      <c r="M4" s="3">
-        <f>L4-D4</f>
-        <v>402.01</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2136.24</v>
+      </c>
+      <c r="E5" s="4">
+        <f>F5-D5</f>
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2177.06</v>
+      </c>
+      <c r="G5" s="4">
+        <f>H5-F5</f>
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2239.66</v>
+      </c>
+      <c r="I5" s="4">
+        <f>J5-H5</f>
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J5" s="4">
+        <v>2286.73</v>
+      </c>
+      <c r="K5" s="4">
+        <f>L5-J5</f>
+        <v>25.52</v>
+      </c>
+      <c r="L5" s="4">
+        <v>2312.25</v>
+      </c>
+      <c r="M5" s="4">
+        <f>L5-D5</f>
+        <v>176.01</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1425.22</v>
-      </c>
-      <c r="E5" s="1">
-        <f>F5-D5</f>
-        <v>64.8599999999999</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1490.08</v>
-      </c>
-      <c r="G5" s="1">
-        <f>H5-F5</f>
-        <v>46</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1536.08</v>
-      </c>
-      <c r="I5" s="1">
-        <f>J5-H5</f>
-        <v>50.8500000000001</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1586.93</v>
-      </c>
-      <c r="K5" s="1">
-        <f>L5-J5</f>
-        <v>86.5599999999999</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1673.49</v>
-      </c>
-      <c r="M5" s="1">
-        <f>L5-D5</f>
-        <v>248.27</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" s="4">
-        <v>2533.85</v>
+        <v>2183.01</v>
       </c>
       <c r="E6" s="4">
         <f>F6-D6</f>
-        <v>50.0500000000002</v>
+        <v>24.1199999999999</v>
       </c>
       <c r="F6" s="4">
-        <v>2583.9</v>
+        <v>2207.13</v>
       </c>
       <c r="G6" s="4">
         <f>H6-F6</f>
-        <v>85.7599999999998</v>
+        <v>22.8599999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>2669.66</v>
+        <v>2229.99</v>
       </c>
       <c r="I6" s="4">
         <f>J6-H6</f>
-        <v>81.79</v>
+        <v>11.7800000000002</v>
       </c>
       <c r="J6" s="4">
-        <v>2751.45</v>
+        <v>2241.77</v>
       </c>
       <c r="K6" s="4">
         <f>L6-J6</f>
-        <v>83.1700000000001</v>
+        <v>13.0100000000002</v>
       </c>
       <c r="L6" s="4">
-        <v>2834.62</v>
+        <v>2254.78</v>
       </c>
       <c r="M6" s="4">
         <f>L6-D6</f>
-        <v>300.77</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>27</v>
+        <v>71.77</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1">
-        <v>1446.65</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="4">
+        <v>1966.62</v>
+      </c>
+      <c r="E7" s="4">
         <f>F7-D7</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1474.83</v>
-      </c>
-      <c r="G7" s="1">
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2015.64</v>
+      </c>
+      <c r="G7" s="4">
         <f>H7-F7</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1538.65</v>
-      </c>
-      <c r="I7" s="1">
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2049.8</v>
+      </c>
+      <c r="I7" s="4">
         <f>J7-H7</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1561.57</v>
-      </c>
-      <c r="K7" s="1">
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2139.9</v>
+      </c>
+      <c r="K7" s="4">
         <f>L7-J7</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1632.43</v>
-      </c>
-      <c r="M7" s="1">
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L7" s="4">
+        <v>2193.07</v>
+      </c>
+      <c r="M7" s="4">
         <f>L7-D7</f>
-        <v>185.78</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>30</v>
+        <v>226.45</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4">
         <v>1754.54</v>
@@ -1677,110 +1677,110 @@
         <f>L8-D8</f>
         <v>293.7</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>33</v>
+      <c r="N8" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1">
-        <v>1350.52</v>
+        <v>1735.94</v>
       </c>
       <c r="E9" s="1">
         <f>F9-D9</f>
-        <v>52.6800000000001</v>
+        <v>48.5999999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>1403.2</v>
+        <v>1784.54</v>
       </c>
       <c r="G9" s="1">
         <f>H9-F9</f>
-        <v>55.3199999999999</v>
+        <v>74.1600000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>1458.52</v>
+        <v>1858.7</v>
       </c>
       <c r="I9" s="1">
         <f>J9-H9</f>
-        <v>32.6800000000001</v>
+        <v>65.55</v>
       </c>
       <c r="J9" s="1">
-        <v>1491.2</v>
+        <v>1924.25</v>
       </c>
       <c r="K9" s="1">
         <f>L9-J9</f>
-        <v>54.96</v>
+        <v>35.73</v>
       </c>
       <c r="L9" s="1">
-        <v>1546.16</v>
+        <v>1959.98</v>
       </c>
       <c r="M9" s="1">
         <f>L9-D9</f>
-        <v>195.64</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>35</v>
+        <v>224.04</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1966.62</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1726.42</v>
+      </c>
+      <c r="E10" s="1">
         <f>F10-D10</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2015.64</v>
-      </c>
-      <c r="G10" s="4">
+        <v>56.28</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1782.7</v>
+      </c>
+      <c r="G10" s="1">
         <f>H10-F10</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2049.8</v>
-      </c>
-      <c r="I10" s="4">
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1853.62</v>
+      </c>
+      <c r="I10" s="1">
         <f>J10-H10</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J10" s="4">
-        <v>2139.9</v>
-      </c>
-      <c r="K10" s="4">
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1903.2</v>
+      </c>
+      <c r="K10" s="1">
         <f>L10-J10</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L10" s="4">
-        <v>2193.07</v>
-      </c>
-      <c r="M10" s="4">
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1943.61</v>
+      </c>
+      <c r="M10" s="1">
         <f>L10-D10</f>
-        <v>226.45</v>
+        <v>217.19</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1790,98 +1790,98 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1">
-        <v>848.93</v>
+        <v>1576.18</v>
       </c>
       <c r="E11" s="1">
         <f>F11-D11</f>
-        <v>34.5600000000001</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>883.49</v>
+        <v>1615.02</v>
       </c>
       <c r="G11" s="1">
         <f>H11-F11</f>
-        <v>46.08</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>929.57</v>
+        <v>1650.62</v>
       </c>
       <c r="I11" s="1">
         <f>J11-H11</f>
-        <v>27.7399999999999</v>
+        <v>37.47</v>
       </c>
       <c r="J11" s="1">
-        <v>957.31</v>
+        <v>1688.09</v>
       </c>
       <c r="K11" s="1">
         <f>L11-J11</f>
-        <v>47.36</v>
+        <v>21.49</v>
       </c>
       <c r="L11" s="1">
-        <v>1004.67</v>
+        <v>1709.58</v>
       </c>
       <c r="M11" s="1">
         <f>L11-D11</f>
-        <v>155.74</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>30</v>
+        <v>133.4</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D12" s="1">
-        <v>1726.42</v>
+        <v>1425.22</v>
       </c>
       <c r="E12" s="1">
         <f>F12-D12</f>
-        <v>56.28</v>
+        <v>64.8599999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>1782.7</v>
+        <v>1490.08</v>
       </c>
       <c r="G12" s="1">
         <f>H12-F12</f>
-        <v>70.9199999999998</v>
+        <v>46</v>
       </c>
       <c r="H12" s="1">
-        <v>1853.62</v>
+        <v>1536.08</v>
       </c>
       <c r="I12" s="1">
         <f>J12-H12</f>
-        <v>49.5800000000002</v>
+        <v>50.8500000000001</v>
       </c>
       <c r="J12" s="1">
-        <v>1903.2</v>
+        <v>1586.93</v>
       </c>
       <c r="K12" s="1">
         <f>L12-J12</f>
-        <v>40.4099999999999</v>
+        <v>86.5599999999999</v>
       </c>
       <c r="L12" s="1">
-        <v>1943.61</v>
+        <v>1673.49</v>
       </c>
       <c r="M12" s="1">
         <f>L12-D12</f>
-        <v>217.19</v>
-      </c>
-      <c r="N12" s="7" t="s">
+        <v>248.27</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>40</v>
       </c>
       <c r="O12" s="3"/>
@@ -1889,561 +1889,561 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1">
-        <v>1060.77</v>
+        <v>1446.65</v>
       </c>
       <c r="E13" s="1">
         <f>F13-D13</f>
-        <v>63.24</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F13" s="1">
-        <v>1124.01</v>
+        <v>1474.83</v>
       </c>
       <c r="G13" s="1">
         <f>H13-F13</f>
-        <v>19.6700000000001</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H13" s="1">
-        <v>1143.68</v>
+        <v>1538.65</v>
       </c>
       <c r="I13" s="1">
         <f>J13-H13</f>
-        <v>47.76</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J13" s="1">
-        <v>1191.44</v>
+        <v>1561.57</v>
       </c>
       <c r="K13" s="1">
         <f>L13-J13</f>
-        <v>40.22</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L13" s="1">
-        <v>1231.66</v>
+        <v>1632.43</v>
       </c>
       <c r="M13" s="1">
         <f>L13-D13</f>
-        <v>170.89</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>18</v>
+        <v>185.78</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1">
-        <v>907.94</v>
+        <v>1349.35</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>64.0799999999999</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>972.02</v>
+        <v>1398.97</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>36.26</v>
+        <v>27.79</v>
       </c>
       <c r="H14" s="1">
-        <v>1008.28</v>
+        <v>1426.76</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>28.8</v>
+        <v>29.02</v>
       </c>
       <c r="J14" s="1">
-        <v>1037.08</v>
+        <v>1455.78</v>
       </c>
       <c r="K14" s="1">
         <f>L14-J14</f>
-        <v>40.1000000000001</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>1077.18</v>
+        <v>1553.66</v>
       </c>
       <c r="M14" s="1">
         <f>L14-D14</f>
-        <v>169.24</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>22</v>
+        <v>204.31</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1">
-        <v>1156.57</v>
+        <v>1350.52</v>
       </c>
       <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>40.4400000000001</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>1197.01</v>
+        <v>1403.2</v>
       </c>
       <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>46.97</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>1243.98</v>
+        <v>1458.52</v>
       </c>
       <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>58.49</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J15" s="1">
-        <v>1302.47</v>
+        <v>1491.2</v>
       </c>
       <c r="K15" s="1">
         <f>L15-J15</f>
-        <v>36.6399999999999</v>
+        <v>54.96</v>
       </c>
       <c r="L15" s="1">
-        <v>1339.11</v>
+        <v>1546.16</v>
       </c>
       <c r="M15" s="1">
         <f>L15-D15</f>
-        <v>182.54</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>18</v>
+        <v>195.64</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D16" s="1">
-        <v>953.78</v>
+        <v>1317.56</v>
       </c>
       <c r="E16" s="1">
         <f>F16-D16</f>
-        <v>28.97</v>
+        <v>15.77</v>
       </c>
       <c r="F16" s="1">
-        <v>982.75</v>
+        <v>1333.33</v>
       </c>
       <c r="G16" s="1">
         <f>H16-F16</f>
-        <v>83.9300000000001</v>
+        <v>15.1700000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>1066.68</v>
+        <v>1348.5</v>
       </c>
       <c r="I16" s="1">
         <f>J16-H16</f>
-        <v>42.8399999999999</v>
+        <v>28.9300000000001</v>
       </c>
       <c r="J16" s="1">
-        <v>1109.52</v>
+        <v>1377.43</v>
       </c>
       <c r="K16" s="1">
         <f>L16-J16</f>
-        <v>36.46</v>
+        <v>9.14999999999986</v>
       </c>
       <c r="L16" s="1">
-        <v>1145.98</v>
+        <v>1386.58</v>
       </c>
       <c r="M16" s="1">
         <f>L16-D16</f>
-        <v>192.2</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>30</v>
+        <v>69.02</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1">
-        <v>1735.94</v>
+        <v>1156.57</v>
       </c>
       <c r="E17" s="1">
         <f>F17-D17</f>
-        <v>48.5999999999999</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>1784.54</v>
+        <v>1197.01</v>
       </c>
       <c r="G17" s="1">
         <f>H17-F17</f>
-        <v>74.1600000000001</v>
+        <v>46.97</v>
       </c>
       <c r="H17" s="1">
-        <v>1858.7</v>
+        <v>1243.98</v>
       </c>
       <c r="I17" s="1">
         <f>J17-H17</f>
-        <v>65.55</v>
+        <v>58.49</v>
       </c>
       <c r="J17" s="1">
-        <v>1924.25</v>
+        <v>1302.47</v>
       </c>
       <c r="K17" s="1">
         <f>L17-J17</f>
-        <v>35.73</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L17" s="1">
-        <v>1959.98</v>
+        <v>1339.11</v>
       </c>
       <c r="M17" s="1">
         <f>L17-D17</f>
-        <v>224.04</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>47</v>
+        <v>182.54</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="4">
-        <v>2136.24</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1060.77</v>
+      </c>
+      <c r="E18" s="1">
         <f>F18-D18</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F18" s="4">
-        <v>2177.06</v>
-      </c>
-      <c r="G18" s="4">
+        <v>63.24</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1124.01</v>
+      </c>
+      <c r="G18" s="1">
         <f>H18-F18</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H18" s="4">
-        <v>2239.66</v>
-      </c>
-      <c r="I18" s="4">
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1143.68</v>
+      </c>
+      <c r="I18" s="1">
         <f>J18-H18</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J18" s="4">
-        <v>2286.73</v>
-      </c>
-      <c r="K18" s="4">
+        <v>47.76</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1191.44</v>
+      </c>
+      <c r="K18" s="1">
         <f>L18-J18</f>
-        <v>25.52</v>
-      </c>
-      <c r="L18" s="4">
-        <v>2312.25</v>
-      </c>
-      <c r="M18" s="4">
+        <v>40.22</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1231.66</v>
+      </c>
+      <c r="M18" s="1">
         <f>L18-D18</f>
-        <v>176.01</v>
+        <v>170.89</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1">
-        <v>927.15</v>
+        <v>953.78</v>
       </c>
       <c r="E19" s="1">
         <f>F19-D19</f>
-        <v>17.9300000000001</v>
+        <v>28.97</v>
       </c>
       <c r="F19" s="1">
-        <v>945.08</v>
+        <v>982.75</v>
       </c>
       <c r="G19" s="1">
         <f>H19-F19</f>
-        <v>24.04</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>969.12</v>
+        <v>1066.68</v>
       </c>
       <c r="I19" s="1">
         <f>J19-H19</f>
-        <v>26.96</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J19" s="1">
-        <v>996.08</v>
+        <v>1109.52</v>
       </c>
       <c r="K19" s="1">
         <f>L19-J19</f>
-        <v>23.3499999999999</v>
+        <v>36.46</v>
       </c>
       <c r="L19" s="1">
-        <v>1019.43</v>
+        <v>1145.98</v>
       </c>
       <c r="M19" s="1">
         <f>L19-D19</f>
-        <v>92.28</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>18</v>
+        <v>192.2</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1">
-        <v>1576.18</v>
+        <v>907.94</v>
       </c>
       <c r="E20" s="1">
         <f>F20-D20</f>
-        <v>38.8399999999999</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>1615.02</v>
+        <v>972.02</v>
       </c>
       <c r="G20" s="1">
         <f>H20-F20</f>
-        <v>35.5999999999999</v>
+        <v>36.26</v>
       </c>
       <c r="H20" s="1">
-        <v>1650.62</v>
+        <v>1008.28</v>
       </c>
       <c r="I20" s="1">
         <f>J20-H20</f>
-        <v>37.47</v>
+        <v>28.8</v>
       </c>
       <c r="J20" s="1">
-        <v>1688.09</v>
+        <v>1037.08</v>
       </c>
       <c r="K20" s="1">
         <f>L20-J20</f>
-        <v>21.49</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L20" s="1">
-        <v>1709.58</v>
+        <v>1077.18</v>
       </c>
       <c r="M20" s="1">
         <f>L20-D20</f>
-        <v>133.4</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>52</v>
+        <v>169.24</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="4">
-        <v>2183.01</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D21" s="1">
+        <v>950.09</v>
+      </c>
+      <c r="E21" s="1">
         <f>F21-D21</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2207.13</v>
-      </c>
-      <c r="G21" s="4">
+        <v>42.4</v>
+      </c>
+      <c r="F21" s="1">
+        <v>992.49</v>
+      </c>
+      <c r="G21" s="1">
         <f>H21-F21</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H21" s="4">
-        <v>2229.99</v>
-      </c>
-      <c r="I21" s="4">
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1031.08</v>
+      </c>
+      <c r="I21" s="1">
         <f>J21-H21</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J21" s="4">
-        <v>2241.77</v>
-      </c>
-      <c r="K21" s="4">
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1053.68</v>
+      </c>
+      <c r="K21" s="1">
         <f>L21-J21</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L21" s="4">
-        <v>2254.78</v>
-      </c>
-      <c r="M21" s="4">
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1064.61</v>
+      </c>
+      <c r="M21" s="1">
         <f>L21-D21</f>
-        <v>71.77</v>
+        <v>114.52</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="5">
-        <v>262.39</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="C22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="1">
+        <v>927.15</v>
+      </c>
+      <c r="E22" s="1">
         <f>F22-D22</f>
-        <v>11.5</v>
-      </c>
-      <c r="F22" s="5">
-        <v>273.89</v>
-      </c>
-      <c r="G22" s="5">
+        <v>17.9300000000001</v>
+      </c>
+      <c r="F22" s="1">
+        <v>945.08</v>
+      </c>
+      <c r="G22" s="1">
         <f>H22-F22</f>
-        <v>13.97</v>
-      </c>
-      <c r="H22" s="5">
-        <v>287.86</v>
-      </c>
-      <c r="I22" s="5">
+        <v>24.04</v>
+      </c>
+      <c r="H22" s="1">
+        <v>969.12</v>
+      </c>
+      <c r="I22" s="1">
         <f>J22-H22</f>
-        <v>16.24</v>
-      </c>
-      <c r="J22" s="5">
-        <v>304.1</v>
-      </c>
-      <c r="K22" s="5">
+        <v>26.96</v>
+      </c>
+      <c r="J22" s="1">
+        <v>996.08</v>
+      </c>
+      <c r="K22" s="1">
         <f>L22-J22</f>
-        <v>12.65</v>
-      </c>
-      <c r="L22" s="5">
-        <v>316.75</v>
-      </c>
-      <c r="M22" s="5">
+        <v>23.3499999999999</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1019.43</v>
+      </c>
+      <c r="M22" s="1">
         <f>L22-D22</f>
-        <v>54.36</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>35</v>
+        <v>92.28</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="5">
-        <v>407.35</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="1">
+        <v>848.93</v>
+      </c>
+      <c r="E23" s="1">
         <f>F23-D23</f>
-        <v>13.86</v>
-      </c>
-      <c r="F23" s="5">
-        <v>421.21</v>
-      </c>
-      <c r="G23" s="5">
+        <v>34.5600000000001</v>
+      </c>
+      <c r="F23" s="1">
+        <v>883.49</v>
+      </c>
+      <c r="G23" s="1">
         <f>H23-F23</f>
-        <v>16.43</v>
-      </c>
-      <c r="H23" s="5">
-        <v>437.64</v>
-      </c>
-      <c r="I23" s="5">
+        <v>46.08</v>
+      </c>
+      <c r="H23" s="1">
+        <v>929.57</v>
+      </c>
+      <c r="I23" s="1">
         <f>J23-H23</f>
-        <v>13.64</v>
-      </c>
-      <c r="J23" s="5">
-        <v>451.28</v>
-      </c>
-      <c r="K23" s="5">
+        <v>27.7399999999999</v>
+      </c>
+      <c r="J23" s="1">
+        <v>957.31</v>
+      </c>
+      <c r="K23" s="1">
         <f>L23-J23</f>
-        <v>11.6</v>
-      </c>
-      <c r="L23" s="5">
-        <v>462.88</v>
-      </c>
-      <c r="M23" s="5">
+        <v>47.36</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1004.67</v>
+      </c>
+      <c r="M23" s="1">
         <f>L23-D23</f>
-        <v>55.53</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>56</v>
+        <v>155.74</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -2456,197 +2456,197 @@
         <v>57</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5">
-        <v>363.88</v>
+        <v>552.79</v>
       </c>
       <c r="E24" s="5">
         <f>F24-D24</f>
-        <v>14.21</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F24" s="5">
-        <v>378.09</v>
+        <v>568.73</v>
       </c>
       <c r="G24" s="5">
         <f>H24-F24</f>
-        <v>11.22</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H24" s="5">
-        <v>389.31</v>
+        <v>570.34</v>
       </c>
       <c r="I24" s="5">
         <f>J24-H24</f>
-        <v>13.62</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J24" s="5">
-        <v>402.93</v>
+        <v>577.48</v>
       </c>
       <c r="K24" s="5">
         <f>L24-J24</f>
-        <v>11.13</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L24" s="5">
-        <v>414.06</v>
+        <v>580.37</v>
       </c>
       <c r="M24" s="5">
         <f>L24-D24</f>
-        <v>50.18</v>
+        <v>27.58</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="5">
+        <v>407.35</v>
+      </c>
+      <c r="E25" s="5">
+        <f>F25-D25</f>
+        <v>13.86</v>
+      </c>
+      <c r="F25" s="5">
+        <v>421.21</v>
+      </c>
+      <c r="G25" s="5">
+        <f>H25-F25</f>
+        <v>16.43</v>
+      </c>
+      <c r="H25" s="5">
+        <v>437.64</v>
+      </c>
+      <c r="I25" s="5">
+        <f>J25-H25</f>
+        <v>13.64</v>
+      </c>
+      <c r="J25" s="5">
+        <v>451.28</v>
+      </c>
+      <c r="K25" s="5">
+        <f>L25-J25</f>
+        <v>11.6</v>
+      </c>
+      <c r="L25" s="5">
+        <v>462.88</v>
+      </c>
+      <c r="M25" s="5">
+        <f>L25-D25</f>
+        <v>55.53</v>
+      </c>
+      <c r="N25" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="1">
-        <v>950.09</v>
-      </c>
-      <c r="E25" s="1">
-        <f>F25-D25</f>
-        <v>42.4</v>
-      </c>
-      <c r="F25" s="1">
-        <v>992.49</v>
-      </c>
-      <c r="G25" s="1">
-        <f>H25-F25</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1031.08</v>
-      </c>
-      <c r="I25" s="1">
-        <f>J25-H25</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1053.68</v>
-      </c>
-      <c r="K25" s="1">
-        <f>L25-J25</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L25" s="1">
-        <v>1064.61</v>
-      </c>
-      <c r="M25" s="1">
-        <f>L25-D25</f>
-        <v>114.52</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D26" s="5">
-        <v>305.29</v>
+        <v>363.88</v>
       </c>
       <c r="E26" s="5">
         <f>F26-D26</f>
-        <v>17.97</v>
+        <v>14.21</v>
       </c>
       <c r="F26" s="5">
-        <v>323.26</v>
+        <v>378.09</v>
       </c>
       <c r="G26" s="5">
         <f>H26-F26</f>
-        <v>10.82</v>
+        <v>11.22</v>
       </c>
       <c r="H26" s="5">
-        <v>334.08</v>
+        <v>389.31</v>
       </c>
       <c r="I26" s="5">
         <f>J26-H26</f>
-        <v>16.2</v>
+        <v>13.62</v>
       </c>
       <c r="J26" s="5">
-        <v>350.28</v>
+        <v>402.93</v>
       </c>
       <c r="K26" s="5">
         <f>L26-J26</f>
-        <v>10.8</v>
+        <v>11.13</v>
       </c>
       <c r="L26" s="5">
-        <v>361.08</v>
+        <v>414.06</v>
       </c>
       <c r="M26" s="5">
         <f>L26-D26</f>
-        <v>55.79</v>
+        <v>50.18</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1317.56</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="C27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="5">
+        <v>305.29</v>
+      </c>
+      <c r="E27" s="5">
         <f>F27-D27</f>
-        <v>15.77</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1333.33</v>
-      </c>
-      <c r="G27" s="1">
+        <v>17.97</v>
+      </c>
+      <c r="F27" s="5">
+        <v>323.26</v>
+      </c>
+      <c r="G27" s="5">
         <f>H27-F27</f>
-        <v>15.1700000000001</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1348.5</v>
-      </c>
-      <c r="I27" s="1">
+        <v>10.82</v>
+      </c>
+      <c r="H27" s="5">
+        <v>334.08</v>
+      </c>
+      <c r="I27" s="5">
         <f>J27-H27</f>
-        <v>28.9300000000001</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1377.43</v>
-      </c>
-      <c r="K27" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="J27" s="5">
+        <v>350.28</v>
+      </c>
+      <c r="K27" s="5">
         <f>L27-J27</f>
-        <v>9.14999999999986</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1386.58</v>
-      </c>
-      <c r="M27" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="L27" s="5">
+        <v>361.08</v>
+      </c>
+      <c r="M27" s="5">
         <f>L27-D27</f>
-        <v>69.02</v>
-      </c>
-      <c r="N27" s="7" t="s">
+        <v>55.79</v>
+      </c>
+      <c r="N27" s="11" t="s">
         <v>40</v>
       </c>
       <c r="O27" s="5"/>
@@ -2654,51 +2654,51 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="5" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D28" s="5">
-        <v>552.79</v>
+        <v>262.39</v>
       </c>
       <c r="E28" s="5">
         <f>F28-D28</f>
-        <v>15.9400000000001</v>
+        <v>11.5</v>
       </c>
       <c r="F28" s="5">
-        <v>568.73</v>
+        <v>273.89</v>
       </c>
       <c r="G28" s="5">
         <f>H28-F28</f>
-        <v>1.61000000000001</v>
+        <v>13.97</v>
       </c>
       <c r="H28" s="5">
-        <v>570.34</v>
+        <v>287.86</v>
       </c>
       <c r="I28" s="5">
         <f>J28-H28</f>
-        <v>7.13999999999999</v>
+        <v>16.24</v>
       </c>
       <c r="J28" s="5">
-        <v>577.48</v>
+        <v>304.1</v>
       </c>
       <c r="K28" s="5">
         <f>L28-J28</f>
-        <v>2.88999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="L28" s="5">
-        <v>580.37</v>
+        <v>316.75</v>
       </c>
       <c r="M28" s="5">
         <f>L28-D28</f>
-        <v>27.58</v>
+        <v>54.36</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
@@ -2713,7 +2713,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
         <v>66</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
         <v>68</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
         <v>69</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
         <v>70</v>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
         <v>71</v>
@@ -2785,7 +2785,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:N28">
-    <sortCondition ref="K2" descending="1"/>
+    <sortCondition ref="L3" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13395"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
   <si>
     <t>区服</t>
   </si>
@@ -61,12 +61,21 @@
     <t>战力（2025.4.23）</t>
   </si>
   <si>
+    <t>战力（2025.4.30）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
     <t>首席英雄（流派）</t>
   </si>
   <si>
+    <t>首席英雄战力</t>
+  </si>
+  <si>
+    <t>飞值</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
@@ -121,81 +130,87 @@
     <t>古月星辰</t>
   </si>
   <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>梅（杂糅）</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>何斌</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
     <t>梅（养神）</t>
   </si>
   <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
-  </si>
-  <si>
-    <t>何斌</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>念苍生</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
     <t>朱</t>
   </si>
   <si>
@@ -232,6 +247,9 @@
     <t>金额：</t>
   </si>
   <si>
+    <t>飞值：（以开飞机的贝塔总英雄战力除以首席英雄战力的值【2.84】为基准值再除以每个人的）：越高说明越专一，越低越是七边形战神。</t>
+  </si>
+  <si>
     <t>0-99</t>
   </si>
   <si>
@@ -239,6 +257,9 @@
   </si>
   <si>
     <t>1K-2999</t>
+  </si>
+  <si>
+    <t>颜色区域划分：（每1000万战力区分一个档位【炫金、黑耀、红色、橙色、紫色、蓝色】）</t>
   </si>
   <si>
     <t>3K-9999</t>
@@ -269,11 +290,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -913,7 +935,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -931,6 +953,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -944,11 +969,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1266,25 +1303,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="13.25" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="13.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="11.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="13.2545454545455" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.75" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7545454545455" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.75" hidden="1" customWidth="1"/>
-    <col min="10" max="12" width="18.125" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="18.625" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="16.6272727272727" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7545454545455" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1272727272727" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6363636363636" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.2727272727273" customWidth="1"/>
+    <col min="13" max="13" width="14.8181818181818" customWidth="1"/>
+    <col min="14" max="14" width="17.4545454545455" customWidth="1"/>
+    <col min="15" max="15" width="14.1272727272727" customWidth="1"/>
+    <col min="16" max="16" width="18.3636363636364" customWidth="1"/>
+    <col min="17" max="17" width="14.5454545454545" customWidth="1"/>
+    <col min="18" max="18" width="14.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1322,21 +1364,33 @@
         <v>8</v>
       </c>
       <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>4105.48</v>
@@ -1370,22 +1424,36 @@
         <v>4585.56</v>
       </c>
       <c r="M2" s="2">
+        <f>N2-L2</f>
+        <v>70.29</v>
+      </c>
+      <c r="N2" s="2">
+        <v>4655.85</v>
+      </c>
+      <c r="O2" s="2">
         <f>L2-D2</f>
         <v>480.080000000001</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="P2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1332.72</v>
+      </c>
+      <c r="R2" s="12">
+        <f>2.84/(N2/Q2)</f>
+        <v>0.812939592126035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
         <v>2714.1</v>
@@ -1419,24 +1487,36 @@
         <v>3116.11</v>
       </c>
       <c r="M3" s="3">
+        <f>N3-L3</f>
+        <v>103.54</v>
+      </c>
+      <c r="N3" s="3">
+        <v>3219.65</v>
+      </c>
+      <c r="O3" s="3">
         <f>L3-D3</f>
         <v>402.01</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="P3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>648.02</v>
+      </c>
+      <c r="R3" s="13">
+        <f>2.84/(N3/Q3)</f>
+        <v>0.57160772133617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="4">
         <v>2533.85</v>
@@ -1470,24 +1550,36 @@
         <v>2834.62</v>
       </c>
       <c r="M4" s="4">
+        <f>N4-L4</f>
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2891.61</v>
+      </c>
+      <c r="O4" s="4">
         <f>L4-D4</f>
         <v>300.77</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="P4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>613.72</v>
+      </c>
+      <c r="R4" s="14">
+        <f>2.84/(N4/Q4)</f>
+        <v>0.602766209827743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4">
         <v>2136.24</v>
@@ -1521,24 +1613,36 @@
         <v>2312.25</v>
       </c>
       <c r="M5" s="4">
+        <f>N5-L5</f>
+        <v>36.7800000000002</v>
+      </c>
+      <c r="N5" s="4">
+        <v>2349.03</v>
+      </c>
+      <c r="O5" s="4">
         <f>L5-D5</f>
         <v>176.01</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="P5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>731.07</v>
+      </c>
+      <c r="R5" s="14">
+        <f>2.84/(N5/Q5)</f>
+        <v>0.883870704077853</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4">
         <v>2183.01</v>
@@ -1572,24 +1676,36 @@
         <v>2254.78</v>
       </c>
       <c r="M6" s="4">
+        <f>N6-L6</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N6" s="4">
+        <v>2317.42</v>
+      </c>
+      <c r="O6" s="4">
         <f>L6-D6</f>
         <v>71.77</v>
       </c>
-      <c r="N6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="P6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>545.02</v>
+      </c>
+      <c r="R6" s="14">
+        <f>2.84/(N6/Q6)</f>
+        <v>0.667922430979279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4">
         <v>1966.62</v>
@@ -1623,24 +1739,36 @@
         <v>2193.07</v>
       </c>
       <c r="M7" s="4">
+        <f>N7-L7</f>
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N7" s="4">
+        <v>2256.98</v>
+      </c>
+      <c r="O7" s="4">
         <f>L7-D7</f>
         <v>226.45</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="P7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>783.52</v>
+      </c>
+      <c r="R7" s="14">
+        <f>2.84/(N7/Q7)</f>
+        <v>0.985917819386968</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4">
         <v>1754.54</v>
@@ -1674,75 +1802,99 @@
         <v>2048.24</v>
       </c>
       <c r="M8" s="4">
+        <f>N8-L8</f>
+        <v>153.99</v>
+      </c>
+      <c r="N8" s="4">
+        <v>2202.23</v>
+      </c>
+      <c r="O8" s="4">
         <f>L8-D8</f>
         <v>293.7</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="P8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1">
+      <c r="Q8" s="4">
+        <v>357.14</v>
+      </c>
+      <c r="R8" s="14">
+        <f>2.84/(N8/Q8)</f>
+        <v>0.460568423824941</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4">
         <v>1735.94</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="4">
         <f>F9-D9</f>
         <v>48.5999999999999</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>1784.54</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
         <f>H9-F9</f>
         <v>74.1600000000001</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="4">
         <v>1858.7</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="4">
         <f>J9-H9</f>
         <v>65.55</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="4">
         <v>1924.25</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
         <f>L9-J9</f>
         <v>35.73</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="4">
         <v>1959.98</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="4">
+        <f>N9-L9</f>
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N9" s="4">
+        <v>2001.86</v>
+      </c>
+      <c r="O9" s="4">
         <f>L9-D9</f>
         <v>224.04</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="P9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>468.37</v>
+      </c>
+      <c r="R9" s="14">
+        <f>2.84/(N9/Q9)</f>
+        <v>0.664467445275894</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>1726.42</v>
@@ -1776,24 +1928,36 @@
         <v>1943.61</v>
       </c>
       <c r="M10" s="1">
+        <f>N10-L10</f>
+        <v>30.01</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1973.62</v>
+      </c>
+      <c r="O10" s="1">
         <f>L10-D10</f>
         <v>217.19</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="P10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>455.77</v>
+      </c>
+      <c r="R10" s="15">
+        <f>2.84/(N10/Q10)</f>
+        <v>0.655843982124218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1">
         <v>1576.18</v>
@@ -1827,24 +1991,36 @@
         <v>1709.58</v>
       </c>
       <c r="M11" s="1">
+        <f>N11-L11</f>
+        <v>24.53</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1734.11</v>
+      </c>
+      <c r="O11" s="1">
         <f>L11-D11</f>
         <v>133.4</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="P11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>397.27</v>
+      </c>
+      <c r="R11" s="15">
+        <f>2.84/(N11/Q11)</f>
+        <v>0.650620087537699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1">
         <v>1425.22</v>
@@ -1878,24 +2054,36 @@
         <v>1673.49</v>
       </c>
       <c r="M12" s="1">
+        <f>N12-L12</f>
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1712.05</v>
+      </c>
+      <c r="O12" s="1">
         <f>L12-D12</f>
         <v>248.27</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="P12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>408.54</v>
+      </c>
+      <c r="R12" s="15">
+        <f>2.84/(N12/Q12)</f>
+        <v>0.677698431704681</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1">
         <v>1446.65</v>
@@ -1929,126 +2117,162 @@
         <v>1632.43</v>
       </c>
       <c r="M13" s="1">
+        <f>N13-L13</f>
+        <v>37.4099999999999</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1669.84</v>
+      </c>
+      <c r="O13" s="1">
         <f>L13-D13</f>
         <v>185.78</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="P13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>651.87</v>
+      </c>
+      <c r="R13" s="15">
+        <f>2.84/(N13/Q13)</f>
+        <v>1.10867556173047</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1">
-        <v>1349.35</v>
+        <v>1350.52</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>49.6200000000001</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>1398.97</v>
+        <v>1403.2</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>27.79</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>1426.76</v>
+        <v>1458.52</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>29.02</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J14" s="1">
-        <v>1455.78</v>
+        <v>1491.2</v>
       </c>
       <c r="K14" s="1">
         <f>L14-J14</f>
-        <v>97.8800000000001</v>
+        <v>54.96</v>
       </c>
       <c r="L14" s="1">
-        <v>1553.66</v>
+        <v>1546.16</v>
       </c>
       <c r="M14" s="1">
+        <f>N14-L14</f>
+        <v>92.1299999999999</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1638.29</v>
+      </c>
+      <c r="O14" s="1">
         <f>L14-D14</f>
-        <v>204.31</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16">
+        <v>195.64</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>520.82</v>
+      </c>
+      <c r="R14" s="15">
+        <f>2.84/(N14/Q14)</f>
+        <v>0.902849190314291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1">
-        <v>1350.52</v>
+        <v>1349.35</v>
       </c>
       <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>52.6800000000001</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>1403.2</v>
+        <v>1398.97</v>
       </c>
       <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>55.3199999999999</v>
+        <v>27.79</v>
       </c>
       <c r="H15" s="1">
-        <v>1458.52</v>
+        <v>1426.76</v>
       </c>
       <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>32.6800000000001</v>
+        <v>29.02</v>
       </c>
       <c r="J15" s="1">
-        <v>1491.2</v>
+        <v>1455.78</v>
       </c>
       <c r="K15" s="1">
         <f>L15-J15</f>
-        <v>54.96</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L15" s="1">
-        <v>1546.16</v>
+        <v>1553.66</v>
       </c>
       <c r="M15" s="1">
+        <f>N15-L15</f>
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1596.02</v>
+      </c>
+      <c r="O15" s="1">
         <f>L15-D15</f>
-        <v>195.64</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16">
+        <v>204.31</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>379.07</v>
+      </c>
+      <c r="R15" s="15">
+        <f>2.84/(N15/Q15)</f>
+        <v>0.674527136251425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>1317.56</v>
@@ -2082,24 +2306,36 @@
         <v>1386.58</v>
       </c>
       <c r="M16" s="1">
+        <f>N16-L16</f>
+        <v>29.4100000000001</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1415.99</v>
+      </c>
+      <c r="O16" s="1">
         <f>L16-D16</f>
         <v>69.02</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="P16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>271.82</v>
+      </c>
+      <c r="R16" s="15">
+        <f>2.84/(N16/Q16)</f>
+        <v>0.545179556352799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <v>1156.57</v>
@@ -2133,24 +2369,36 @@
         <v>1339.11</v>
       </c>
       <c r="M17" s="1">
+        <f>N17-L17</f>
+        <v>33.99</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1373.1</v>
+      </c>
+      <c r="O17" s="1">
         <f>L17-D17</f>
         <v>182.54</v>
       </c>
-      <c r="N17" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="P17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>331.97</v>
+      </c>
+      <c r="R17" s="15">
+        <f>2.84/(N17/Q17)</f>
+        <v>0.686617726312723</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1">
         <v>1060.77</v>
@@ -2184,24 +2432,36 @@
         <v>1231.66</v>
       </c>
       <c r="M18" s="1">
+        <f>N18-L18</f>
+        <v>44.8</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1276.46</v>
+      </c>
+      <c r="O18" s="1">
         <f>L18-D18</f>
         <v>170.89</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="P18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>254.72</v>
+      </c>
+      <c r="R18" s="15">
+        <f>2.84/(N18/Q18)</f>
+        <v>0.566727355342118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1">
         <v>953.78</v>
@@ -2235,24 +2495,36 @@
         <v>1145.98</v>
       </c>
       <c r="M19" s="1">
+        <f>N19-L19</f>
+        <v>37.49</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1183.47</v>
+      </c>
+      <c r="O19" s="1">
         <f>L19-D19</f>
         <v>192.2</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="P19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>416.72</v>
+      </c>
+      <c r="R19" s="15">
+        <f>2.84/(N19/Q19)</f>
+        <v>1.00001250559794</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1">
         <v>907.94</v>
@@ -2286,24 +2558,36 @@
         <v>1077.18</v>
       </c>
       <c r="M20" s="1">
+        <f>N20-L20</f>
+        <v>26.03</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1103.21</v>
+      </c>
+      <c r="O20" s="1">
         <f>L20-D20</f>
         <v>169.24</v>
       </c>
-      <c r="N20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="P20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>380.52</v>
+      </c>
+      <c r="R20" s="15">
+        <f>2.84/(N20/Q20)</f>
+        <v>0.979574876949991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <v>950.09</v>
@@ -2337,24 +2621,36 @@
         <v>1064.61</v>
       </c>
       <c r="M21" s="1">
+        <f>N21-L21</f>
+        <v>16.1800000000001</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1080.79</v>
+      </c>
+      <c r="O21" s="1">
         <f>L21-D21</f>
         <v>114.52</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="P21" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>417.17</v>
+      </c>
+      <c r="R21" s="15">
+        <f>2.84/(N21/Q21)</f>
+        <v>1.0962007420498</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1">
         <v>927.15</v>
@@ -2388,24 +2684,36 @@
         <v>1019.43</v>
       </c>
       <c r="M22" s="1">
+        <f>N22-L22</f>
+        <v>23.7400000000001</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1043.17</v>
+      </c>
+      <c r="O22" s="1">
         <f>L22-D22</f>
         <v>92.28</v>
       </c>
-      <c r="N22" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="P22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>308.77</v>
+      </c>
+      <c r="R22" s="15">
+        <f>2.84/(N22/Q22)</f>
+        <v>0.840617349041863</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D23" s="1">
         <v>848.93</v>
@@ -2439,24 +2747,36 @@
         <v>1004.67</v>
       </c>
       <c r="M23" s="1">
+        <f>N23-L23</f>
+        <v>25.9399999999999</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1030.61</v>
+      </c>
+      <c r="O23" s="1">
         <f>L23-D23</f>
         <v>155.74</v>
       </c>
-      <c r="N23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="P23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>348.62</v>
+      </c>
+      <c r="R23" s="15">
+        <f>2.84/(N23/Q23)</f>
+        <v>0.960674551964371</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D24" s="5">
         <v>552.79</v>
@@ -2490,24 +2810,36 @@
         <v>580.37</v>
       </c>
       <c r="M24" s="5">
+        <f>N24-L24</f>
+        <v>2.55999999999995</v>
+      </c>
+      <c r="N24" s="5">
+        <v>582.93</v>
+      </c>
+      <c r="O24" s="5">
         <f>L24-D24</f>
         <v>27.58</v>
       </c>
-      <c r="N24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="P24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>135.65</v>
+      </c>
+      <c r="R24" s="16">
+        <f>2.84/(N24/Q24)</f>
+        <v>0.660878664676719</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D25" s="5">
         <v>407.35</v>
@@ -2541,24 +2873,36 @@
         <v>462.88</v>
       </c>
       <c r="M25" s="5">
+        <f>N25-L25</f>
+        <v>47.68</v>
+      </c>
+      <c r="N25" s="5">
+        <v>510.56</v>
+      </c>
+      <c r="O25" s="5">
         <f>L25-D25</f>
         <v>55.53</v>
       </c>
-      <c r="N25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="P25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>225.74</v>
+      </c>
+      <c r="R25" s="16">
+        <f>2.84/(N25/Q25)</f>
+        <v>1.25568317141962</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D26" s="5">
         <v>363.88</v>
@@ -2592,24 +2936,36 @@
         <v>414.06</v>
       </c>
       <c r="M26" s="5">
+        <f>N26-L26</f>
+        <v>17.39</v>
+      </c>
+      <c r="N26" s="5">
+        <v>431.45</v>
+      </c>
+      <c r="O26" s="5">
         <f>L26-D26</f>
         <v>50.18</v>
       </c>
-      <c r="N26" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="P26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>111.89</v>
+      </c>
+      <c r="R26" s="16">
+        <f>2.84/(N26/Q26)</f>
+        <v>0.736510835554525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D27" s="5">
         <v>305.29</v>
@@ -2643,24 +2999,36 @@
         <v>361.08</v>
       </c>
       <c r="M27" s="5">
+        <f>N27-L27</f>
+        <v>9.98000000000002</v>
+      </c>
+      <c r="N27" s="5">
+        <v>371.06</v>
+      </c>
+      <c r="O27" s="5">
         <f>L27-D27</f>
         <v>55.79</v>
       </c>
-      <c r="N27" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="P27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>93.39</v>
+      </c>
+      <c r="R27" s="16">
+        <f>2.84/(N27/Q27)</f>
+        <v>0.714783592949927</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D28" s="5">
         <v>262.39</v>
@@ -2694,99 +3062,149 @@
         <v>316.75</v>
       </c>
       <c r="M28" s="5">
+        <f>N28-L28</f>
+        <v>9.99000000000001</v>
+      </c>
+      <c r="N28" s="5">
+        <v>326.74</v>
+      </c>
+      <c r="O28" s="5">
         <f>L28-D28</f>
         <v>54.36</v>
       </c>
-      <c r="N28" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="P28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>113.04</v>
+      </c>
+      <c r="R28" s="16">
+        <f>2.84/(N28/Q28)</f>
+        <v>0.982535349207321</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:N28">
-    <sortCondition ref="L3" descending="1"/>
+  <sortState ref="A2:R28">
+    <sortCondition ref="N2" descending="1"/>
   </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="C31:R31"/>
+    <mergeCell ref="C34:P34"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2797,7 +3215,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2809,7 +3227,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -1304,26 +1304,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="13.2545454545455" customWidth="1"/>
-    <col min="3" max="3" width="11.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="13.2545454545455" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.2583333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.5416666666667" customWidth="1"/>
+    <col min="4" max="4" width="13.2583333333333" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7545454545455" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7583333333333" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6272727272727" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7545454545455" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.1272727272727" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6363636363636" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.2727272727273" customWidth="1"/>
-    <col min="13" max="13" width="14.8181818181818" customWidth="1"/>
-    <col min="14" max="14" width="17.4545454545455" customWidth="1"/>
-    <col min="15" max="15" width="14.1272727272727" customWidth="1"/>
-    <col min="16" max="16" width="18.3636363636364" customWidth="1"/>
-    <col min="17" max="17" width="14.5454545454545" customWidth="1"/>
-    <col min="18" max="18" width="14.1818181818182" customWidth="1"/>
+    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7583333333333" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6333333333333" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.275" customWidth="1"/>
+    <col min="13" max="13" width="14.8166666666667" customWidth="1"/>
+    <col min="14" max="14" width="17.4583333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.125" customWidth="1"/>
+    <col min="16" max="16" width="18.3666666666667" customWidth="1"/>
+    <col min="17" max="17" width="14.5416666666667" customWidth="1"/>
+    <col min="18" max="18" width="14.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1396,42 +1396,42 @@
         <v>4105.48</v>
       </c>
       <c r="E2" s="2">
-        <f>F2-D2</f>
+        <f t="shared" ref="E2:E28" si="0">F2-D2</f>
         <v>181.21</v>
       </c>
       <c r="F2" s="2">
         <v>4286.69</v>
       </c>
       <c r="G2" s="2">
-        <f>H2-F2</f>
+        <f t="shared" ref="G2:G28" si="1">H2-F2</f>
         <v>139.09</v>
       </c>
       <c r="H2" s="2">
         <v>4425.78</v>
       </c>
       <c r="I2" s="2">
-        <f>J2-H2</f>
+        <f t="shared" ref="I2:I28" si="2">J2-H2</f>
         <v>54.8800000000001</v>
       </c>
       <c r="J2" s="2">
         <v>4480.66</v>
       </c>
       <c r="K2" s="2">
-        <f>L2-J2</f>
+        <f t="shared" ref="K2:K28" si="3">L2-J2</f>
         <v>104.900000000001</v>
       </c>
       <c r="L2" s="2">
         <v>4585.56</v>
       </c>
       <c r="M2" s="2">
-        <f>N2-L2</f>
+        <f t="shared" ref="M2:M28" si="4">N2-L2</f>
         <v>70.29</v>
       </c>
       <c r="N2" s="2">
         <v>4655.85</v>
       </c>
       <c r="O2" s="2">
-        <f>L2-D2</f>
+        <f t="shared" ref="O2:O28" si="5">L2-D2</f>
         <v>480.080000000001</v>
       </c>
       <c r="P2" s="7" t="s">
@@ -1441,7 +1441,7 @@
         <v>1332.72</v>
       </c>
       <c r="R2" s="12">
-        <f>2.84/(N2/Q2)</f>
+        <f t="shared" ref="R2:R28" si="6">2.84/(N2/Q2)</f>
         <v>0.812939592126035</v>
       </c>
     </row>
@@ -1459,42 +1459,42 @@
         <v>2714.1</v>
       </c>
       <c r="E3" s="3">
-        <f>F3-D3</f>
+        <f t="shared" si="0"/>
         <v>123.29</v>
       </c>
       <c r="F3" s="3">
         <v>2837.39</v>
       </c>
       <c r="G3" s="3">
-        <f>H3-F3</f>
+        <f t="shared" si="1"/>
         <v>95.8499999999999</v>
       </c>
       <c r="H3" s="3">
         <v>2933.24</v>
       </c>
       <c r="I3" s="3">
-        <f>J3-H3</f>
+        <f t="shared" si="2"/>
         <v>92.46</v>
       </c>
       <c r="J3" s="3">
         <v>3025.7</v>
       </c>
       <c r="K3" s="3">
-        <f>L3-J3</f>
+        <f t="shared" si="3"/>
         <v>90.4100000000003</v>
       </c>
       <c r="L3" s="3">
         <v>3116.11</v>
       </c>
       <c r="M3" s="3">
-        <f>N3-L3</f>
+        <f t="shared" si="4"/>
         <v>103.54</v>
       </c>
       <c r="N3" s="3">
         <v>3219.65</v>
       </c>
       <c r="O3" s="3">
-        <f>L3-D3</f>
+        <f t="shared" si="5"/>
         <v>402.01</v>
       </c>
       <c r="P3" s="8" t="s">
@@ -1504,7 +1504,7 @@
         <v>648.02</v>
       </c>
       <c r="R3" s="13">
-        <f>2.84/(N3/Q3)</f>
+        <f t="shared" si="6"/>
         <v>0.57160772133617</v>
       </c>
     </row>
@@ -1522,42 +1522,42 @@
         <v>2533.85</v>
       </c>
       <c r="E4" s="4">
-        <f>F4-D4</f>
+        <f t="shared" si="0"/>
         <v>50.0500000000002</v>
       </c>
       <c r="F4" s="4">
         <v>2583.9</v>
       </c>
       <c r="G4" s="4">
-        <f>H4-F4</f>
+        <f t="shared" si="1"/>
         <v>85.7599999999998</v>
       </c>
       <c r="H4" s="4">
         <v>2669.66</v>
       </c>
       <c r="I4" s="4">
-        <f>J4-H4</f>
+        <f t="shared" si="2"/>
         <v>81.79</v>
       </c>
       <c r="J4" s="4">
         <v>2751.45</v>
       </c>
       <c r="K4" s="4">
-        <f>L4-J4</f>
+        <f t="shared" si="3"/>
         <v>83.1700000000001</v>
       </c>
       <c r="L4" s="4">
         <v>2834.62</v>
       </c>
       <c r="M4" s="4">
-        <f>N4-L4</f>
+        <f t="shared" si="4"/>
         <v>56.9900000000002</v>
       </c>
       <c r="N4" s="4">
         <v>2891.61</v>
       </c>
       <c r="O4" s="4">
-        <f>L4-D4</f>
+        <f t="shared" si="5"/>
         <v>300.77</v>
       </c>
       <c r="P4" s="9" t="s">
@@ -1567,7 +1567,7 @@
         <v>613.72</v>
       </c>
       <c r="R4" s="14">
-        <f>2.84/(N4/Q4)</f>
+        <f t="shared" si="6"/>
         <v>0.602766209827743</v>
       </c>
     </row>
@@ -1579,48 +1579,48 @@
         <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4">
         <v>2136.24</v>
       </c>
       <c r="E5" s="4">
-        <f>F5-D5</f>
+        <f t="shared" si="0"/>
         <v>40.8200000000002</v>
       </c>
       <c r="F5" s="4">
         <v>2177.06</v>
       </c>
       <c r="G5" s="4">
-        <f>H5-F5</f>
+        <f t="shared" si="1"/>
         <v>62.5999999999999</v>
       </c>
       <c r="H5" s="4">
         <v>2239.66</v>
       </c>
       <c r="I5" s="4">
-        <f>J5-H5</f>
+        <f t="shared" si="2"/>
         <v>47.0700000000002</v>
       </c>
       <c r="J5" s="4">
         <v>2286.73</v>
       </c>
       <c r="K5" s="4">
-        <f>L5-J5</f>
+        <f t="shared" si="3"/>
         <v>25.52</v>
       </c>
       <c r="L5" s="4">
         <v>2312.25</v>
       </c>
       <c r="M5" s="4">
-        <f>N5-L5</f>
+        <f t="shared" si="4"/>
         <v>36.7800000000002</v>
       </c>
       <c r="N5" s="4">
         <v>2349.03</v>
       </c>
       <c r="O5" s="4">
-        <f>L5-D5</f>
+        <f t="shared" si="5"/>
         <v>176.01</v>
       </c>
       <c r="P5" s="9" t="s">
@@ -1630,7 +1630,7 @@
         <v>731.07</v>
       </c>
       <c r="R5" s="14">
-        <f>2.84/(N5/Q5)</f>
+        <f t="shared" si="6"/>
         <v>0.883870704077853</v>
       </c>
     </row>
@@ -1648,42 +1648,42 @@
         <v>2183.01</v>
       </c>
       <c r="E6" s="4">
-        <f>F6-D6</f>
+        <f t="shared" si="0"/>
         <v>24.1199999999999</v>
       </c>
       <c r="F6" s="4">
         <v>2207.13</v>
       </c>
       <c r="G6" s="4">
-        <f>H6-F6</f>
+        <f t="shared" si="1"/>
         <v>22.8599999999997</v>
       </c>
       <c r="H6" s="4">
         <v>2229.99</v>
       </c>
       <c r="I6" s="4">
-        <f>J6-H6</f>
+        <f t="shared" si="2"/>
         <v>11.7800000000002</v>
       </c>
       <c r="J6" s="4">
         <v>2241.77</v>
       </c>
       <c r="K6" s="4">
-        <f>L6-J6</f>
+        <f t="shared" si="3"/>
         <v>13.0100000000002</v>
       </c>
       <c r="L6" s="4">
         <v>2254.78</v>
       </c>
       <c r="M6" s="4">
-        <f>N6-L6</f>
+        <f t="shared" si="4"/>
         <v>62.6399999999999</v>
       </c>
       <c r="N6" s="4">
         <v>2317.42</v>
       </c>
       <c r="O6" s="4">
-        <f>L6-D6</f>
+        <f t="shared" si="5"/>
         <v>71.77</v>
       </c>
       <c r="P6" s="9" t="s">
@@ -1693,7 +1693,7 @@
         <v>545.02</v>
       </c>
       <c r="R6" s="14">
-        <f>2.84/(N6/Q6)</f>
+        <f t="shared" si="6"/>
         <v>0.667922430979279</v>
       </c>
     </row>
@@ -1711,42 +1711,42 @@
         <v>1966.62</v>
       </c>
       <c r="E7" s="4">
-        <f>F7-D7</f>
+        <f t="shared" si="0"/>
         <v>49.0200000000002</v>
       </c>
       <c r="F7" s="4">
         <v>2015.64</v>
       </c>
       <c r="G7" s="4">
-        <f>H7-F7</f>
+        <f t="shared" si="1"/>
         <v>34.1600000000001</v>
       </c>
       <c r="H7" s="4">
         <v>2049.8</v>
       </c>
       <c r="I7" s="4">
-        <f>J7-H7</f>
+        <f t="shared" si="2"/>
         <v>90.0999999999999</v>
       </c>
       <c r="J7" s="4">
         <v>2139.9</v>
       </c>
       <c r="K7" s="4">
-        <f>L7-J7</f>
+        <f t="shared" si="3"/>
         <v>53.1700000000001</v>
       </c>
       <c r="L7" s="4">
         <v>2193.07</v>
       </c>
       <c r="M7" s="4">
-        <f>N7-L7</f>
+        <f t="shared" si="4"/>
         <v>63.9099999999999</v>
       </c>
       <c r="N7" s="4">
         <v>2256.98</v>
       </c>
       <c r="O7" s="4">
-        <f>L7-D7</f>
+        <f t="shared" si="5"/>
         <v>226.45</v>
       </c>
       <c r="P7" s="9" t="s">
@@ -1756,7 +1756,7 @@
         <v>783.52</v>
       </c>
       <c r="R7" s="14">
-        <f>2.84/(N7/Q7)</f>
+        <f t="shared" si="6"/>
         <v>0.985917819386968</v>
       </c>
     </row>
@@ -1774,42 +1774,42 @@
         <v>1754.54</v>
       </c>
       <c r="E8" s="4">
-        <f>F8-D8</f>
+        <f t="shared" si="0"/>
         <v>53.3700000000001</v>
       </c>
       <c r="F8" s="4">
         <v>1807.91</v>
       </c>
       <c r="G8" s="4">
-        <f>H8-F8</f>
+        <f t="shared" si="1"/>
         <v>90.24</v>
       </c>
       <c r="H8" s="4">
         <v>1898.15</v>
       </c>
       <c r="I8" s="4">
-        <f>J8-H8</f>
+        <f t="shared" si="2"/>
         <v>90.3799999999999</v>
       </c>
       <c r="J8" s="4">
         <v>1988.53</v>
       </c>
       <c r="K8" s="4">
-        <f>L8-J8</f>
+        <f t="shared" si="3"/>
         <v>59.7099999999998</v>
       </c>
       <c r="L8" s="4">
         <v>2048.24</v>
       </c>
       <c r="M8" s="4">
-        <f>N8-L8</f>
+        <f t="shared" si="4"/>
         <v>153.99</v>
       </c>
       <c r="N8" s="4">
         <v>2202.23</v>
       </c>
       <c r="O8" s="4">
-        <f>L8-D8</f>
+        <f t="shared" si="5"/>
         <v>293.7</v>
       </c>
       <c r="P8" s="9" t="s">
@@ -1819,7 +1819,7 @@
         <v>357.14</v>
       </c>
       <c r="R8" s="14">
-        <f>2.84/(N8/Q8)</f>
+        <f t="shared" si="6"/>
         <v>0.460568423824941</v>
       </c>
     </row>
@@ -1837,42 +1837,42 @@
         <v>1735.94</v>
       </c>
       <c r="E9" s="4">
-        <f>F9-D9</f>
+        <f t="shared" si="0"/>
         <v>48.5999999999999</v>
       </c>
       <c r="F9" s="4">
         <v>1784.54</v>
       </c>
       <c r="G9" s="4">
-        <f>H9-F9</f>
+        <f t="shared" si="1"/>
         <v>74.1600000000001</v>
       </c>
       <c r="H9" s="4">
         <v>1858.7</v>
       </c>
       <c r="I9" s="4">
-        <f>J9-H9</f>
+        <f t="shared" si="2"/>
         <v>65.55</v>
       </c>
       <c r="J9" s="4">
         <v>1924.25</v>
       </c>
       <c r="K9" s="4">
-        <f>L9-J9</f>
+        <f t="shared" si="3"/>
         <v>35.73</v>
       </c>
       <c r="L9" s="4">
         <v>1959.98</v>
       </c>
       <c r="M9" s="4">
-        <f>N9-L9</f>
+        <f t="shared" si="4"/>
         <v>41.8799999999999</v>
       </c>
       <c r="N9" s="4">
         <v>2001.86</v>
       </c>
       <c r="O9" s="4">
-        <f>L9-D9</f>
+        <f t="shared" si="5"/>
         <v>224.04</v>
       </c>
       <c r="P9" s="9" t="s">
@@ -1882,7 +1882,7 @@
         <v>468.37</v>
       </c>
       <c r="R9" s="14">
-        <f>2.84/(N9/Q9)</f>
+        <f t="shared" si="6"/>
         <v>0.664467445275894</v>
       </c>
     </row>
@@ -1900,42 +1900,42 @@
         <v>1726.42</v>
       </c>
       <c r="E10" s="1">
-        <f>F10-D10</f>
+        <f t="shared" si="0"/>
         <v>56.28</v>
       </c>
       <c r="F10" s="1">
         <v>1782.7</v>
       </c>
       <c r="G10" s="1">
-        <f>H10-F10</f>
+        <f t="shared" si="1"/>
         <v>70.9199999999998</v>
       </c>
       <c r="H10" s="1">
         <v>1853.62</v>
       </c>
       <c r="I10" s="1">
-        <f>J10-H10</f>
+        <f t="shared" si="2"/>
         <v>49.5800000000002</v>
       </c>
       <c r="J10" s="1">
         <v>1903.2</v>
       </c>
       <c r="K10" s="1">
-        <f>L10-J10</f>
+        <f t="shared" si="3"/>
         <v>40.4099999999999</v>
       </c>
       <c r="L10" s="1">
         <v>1943.61</v>
       </c>
       <c r="M10" s="1">
-        <f>N10-L10</f>
+        <f t="shared" si="4"/>
         <v>30.01</v>
       </c>
       <c r="N10" s="1">
         <v>1973.62</v>
       </c>
       <c r="O10" s="1">
-        <f>L10-D10</f>
+        <f t="shared" si="5"/>
         <v>217.19</v>
       </c>
       <c r="P10" s="10" t="s">
@@ -1945,7 +1945,7 @@
         <v>455.77</v>
       </c>
       <c r="R10" s="15">
-        <f>2.84/(N10/Q10)</f>
+        <f t="shared" si="6"/>
         <v>0.655843982124218</v>
       </c>
     </row>
@@ -1963,42 +1963,42 @@
         <v>1576.18</v>
       </c>
       <c r="E11" s="1">
-        <f>F11-D11</f>
+        <f t="shared" si="0"/>
         <v>38.8399999999999</v>
       </c>
       <c r="F11" s="1">
         <v>1615.02</v>
       </c>
       <c r="G11" s="1">
-        <f>H11-F11</f>
+        <f t="shared" si="1"/>
         <v>35.5999999999999</v>
       </c>
       <c r="H11" s="1">
         <v>1650.62</v>
       </c>
       <c r="I11" s="1">
-        <f>J11-H11</f>
+        <f t="shared" si="2"/>
         <v>37.47</v>
       </c>
       <c r="J11" s="1">
         <v>1688.09</v>
       </c>
       <c r="K11" s="1">
-        <f>L11-J11</f>
+        <f t="shared" si="3"/>
         <v>21.49</v>
       </c>
       <c r="L11" s="1">
         <v>1709.58</v>
       </c>
       <c r="M11" s="1">
-        <f>N11-L11</f>
+        <f t="shared" si="4"/>
         <v>24.53</v>
       </c>
       <c r="N11" s="1">
         <v>1734.11</v>
       </c>
       <c r="O11" s="1">
-        <f>L11-D11</f>
+        <f t="shared" si="5"/>
         <v>133.4</v>
       </c>
       <c r="P11" s="10" t="s">
@@ -2008,7 +2008,7 @@
         <v>397.27</v>
       </c>
       <c r="R11" s="15">
-        <f>2.84/(N11/Q11)</f>
+        <f t="shared" si="6"/>
         <v>0.650620087537699</v>
       </c>
     </row>
@@ -2026,42 +2026,42 @@
         <v>1425.22</v>
       </c>
       <c r="E12" s="1">
-        <f>F12-D12</f>
+        <f t="shared" si="0"/>
         <v>64.8599999999999</v>
       </c>
       <c r="F12" s="1">
         <v>1490.08</v>
       </c>
       <c r="G12" s="1">
-        <f>H12-F12</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="H12" s="1">
         <v>1536.08</v>
       </c>
       <c r="I12" s="1">
-        <f>J12-H12</f>
+        <f t="shared" si="2"/>
         <v>50.8500000000001</v>
       </c>
       <c r="J12" s="1">
         <v>1586.93</v>
       </c>
       <c r="K12" s="1">
-        <f>L12-J12</f>
+        <f t="shared" si="3"/>
         <v>86.5599999999999</v>
       </c>
       <c r="L12" s="1">
         <v>1673.49</v>
       </c>
       <c r="M12" s="1">
-        <f>N12-L12</f>
+        <f t="shared" si="4"/>
         <v>38.5599999999999</v>
       </c>
       <c r="N12" s="1">
         <v>1712.05</v>
       </c>
       <c r="O12" s="1">
-        <f>L12-D12</f>
+        <f t="shared" si="5"/>
         <v>248.27</v>
       </c>
       <c r="P12" s="10" t="s">
@@ -2071,7 +2071,7 @@
         <v>408.54</v>
       </c>
       <c r="R12" s="15">
-        <f>2.84/(N12/Q12)</f>
+        <f t="shared" si="6"/>
         <v>0.677698431704681</v>
       </c>
     </row>
@@ -2089,42 +2089,42 @@
         <v>1446.65</v>
       </c>
       <c r="E13" s="1">
-        <f>F13-D13</f>
+        <f t="shared" si="0"/>
         <v>28.1799999999998</v>
       </c>
       <c r="F13" s="1">
         <v>1474.83</v>
       </c>
       <c r="G13" s="1">
-        <f>H13-F13</f>
+        <f t="shared" si="1"/>
         <v>63.8200000000002</v>
       </c>
       <c r="H13" s="1">
         <v>1538.65</v>
       </c>
       <c r="I13" s="1">
-        <f>J13-H13</f>
+        <f t="shared" si="2"/>
         <v>22.9199999999998</v>
       </c>
       <c r="J13" s="1">
         <v>1561.57</v>
       </c>
       <c r="K13" s="1">
-        <f>L13-J13</f>
+        <f t="shared" si="3"/>
         <v>70.8600000000001</v>
       </c>
       <c r="L13" s="1">
         <v>1632.43</v>
       </c>
       <c r="M13" s="1">
-        <f>N13-L13</f>
+        <f t="shared" si="4"/>
         <v>37.4099999999999</v>
       </c>
       <c r="N13" s="1">
         <v>1669.84</v>
       </c>
       <c r="O13" s="1">
-        <f>L13-D13</f>
+        <f t="shared" si="5"/>
         <v>185.78</v>
       </c>
       <c r="P13" s="10" t="s">
@@ -2134,7 +2134,7 @@
         <v>651.87</v>
       </c>
       <c r="R13" s="15">
-        <f>2.84/(N13/Q13)</f>
+        <f t="shared" si="6"/>
         <v>1.10867556173047</v>
       </c>
     </row>
@@ -2152,42 +2152,42 @@
         <v>1350.52</v>
       </c>
       <c r="E14" s="1">
-        <f>F14-D14</f>
+        <f t="shared" si="0"/>
         <v>52.6800000000001</v>
       </c>
       <c r="F14" s="1">
         <v>1403.2</v>
       </c>
       <c r="G14" s="1">
-        <f>H14-F14</f>
+        <f t="shared" si="1"/>
         <v>55.3199999999999</v>
       </c>
       <c r="H14" s="1">
         <v>1458.52</v>
       </c>
       <c r="I14" s="1">
-        <f>J14-H14</f>
+        <f t="shared" si="2"/>
         <v>32.6800000000001</v>
       </c>
       <c r="J14" s="1">
         <v>1491.2</v>
       </c>
       <c r="K14" s="1">
-        <f>L14-J14</f>
+        <f t="shared" si="3"/>
         <v>54.96</v>
       </c>
       <c r="L14" s="1">
         <v>1546.16</v>
       </c>
       <c r="M14" s="1">
-        <f>N14-L14</f>
+        <f t="shared" si="4"/>
         <v>92.1299999999999</v>
       </c>
       <c r="N14" s="1">
         <v>1638.29</v>
       </c>
       <c r="O14" s="1">
-        <f>L14-D14</f>
+        <f t="shared" si="5"/>
         <v>195.64</v>
       </c>
       <c r="P14" s="10" t="s">
@@ -2197,7 +2197,7 @@
         <v>520.82</v>
       </c>
       <c r="R14" s="15">
-        <f>2.84/(N14/Q14)</f>
+        <f t="shared" si="6"/>
         <v>0.902849190314291</v>
       </c>
     </row>
@@ -2215,42 +2215,42 @@
         <v>1349.35</v>
       </c>
       <c r="E15" s="1">
-        <f>F15-D15</f>
+        <f t="shared" si="0"/>
         <v>49.6200000000001</v>
       </c>
       <c r="F15" s="1">
         <v>1398.97</v>
       </c>
       <c r="G15" s="1">
-        <f>H15-F15</f>
+        <f t="shared" si="1"/>
         <v>27.79</v>
       </c>
       <c r="H15" s="1">
         <v>1426.76</v>
       </c>
       <c r="I15" s="1">
-        <f>J15-H15</f>
+        <f t="shared" si="2"/>
         <v>29.02</v>
       </c>
       <c r="J15" s="1">
         <v>1455.78</v>
       </c>
       <c r="K15" s="1">
-        <f>L15-J15</f>
+        <f t="shared" si="3"/>
         <v>97.8800000000001</v>
       </c>
       <c r="L15" s="1">
         <v>1553.66</v>
       </c>
       <c r="M15" s="1">
-        <f>N15-L15</f>
+        <f t="shared" si="4"/>
         <v>42.3599999999999</v>
       </c>
       <c r="N15" s="1">
         <v>1596.02</v>
       </c>
       <c r="O15" s="1">
-        <f>L15-D15</f>
+        <f t="shared" si="5"/>
         <v>204.31</v>
       </c>
       <c r="P15" s="10" t="s">
@@ -2260,7 +2260,7 @@
         <v>379.07</v>
       </c>
       <c r="R15" s="15">
-        <f>2.84/(N15/Q15)</f>
+        <f t="shared" si="6"/>
         <v>0.674527136251425</v>
       </c>
     </row>
@@ -2278,42 +2278,42 @@
         <v>1317.56</v>
       </c>
       <c r="E16" s="1">
-        <f>F16-D16</f>
+        <f t="shared" si="0"/>
         <v>15.77</v>
       </c>
       <c r="F16" s="1">
         <v>1333.33</v>
       </c>
       <c r="G16" s="1">
-        <f>H16-F16</f>
+        <f t="shared" si="1"/>
         <v>15.1700000000001</v>
       </c>
       <c r="H16" s="1">
         <v>1348.5</v>
       </c>
       <c r="I16" s="1">
-        <f>J16-H16</f>
+        <f t="shared" si="2"/>
         <v>28.9300000000001</v>
       </c>
       <c r="J16" s="1">
         <v>1377.43</v>
       </c>
       <c r="K16" s="1">
-        <f>L16-J16</f>
+        <f t="shared" si="3"/>
         <v>9.14999999999986</v>
       </c>
       <c r="L16" s="1">
         <v>1386.58</v>
       </c>
       <c r="M16" s="1">
-        <f>N16-L16</f>
+        <f t="shared" si="4"/>
         <v>29.4100000000001</v>
       </c>
       <c r="N16" s="1">
         <v>1415.99</v>
       </c>
       <c r="O16" s="1">
-        <f>L16-D16</f>
+        <f t="shared" si="5"/>
         <v>69.02</v>
       </c>
       <c r="P16" s="10" t="s">
@@ -2323,7 +2323,7 @@
         <v>271.82</v>
       </c>
       <c r="R16" s="15">
-        <f>2.84/(N16/Q16)</f>
+        <f t="shared" si="6"/>
         <v>0.545179556352799</v>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
         <v>1156.57</v>
       </c>
       <c r="E17" s="1">
-        <f>F17-D17</f>
+        <f t="shared" si="0"/>
         <v>40.4400000000001</v>
       </c>
       <c r="F17" s="1">
         <v>1197.01</v>
       </c>
       <c r="G17" s="1">
-        <f>H17-F17</f>
+        <f t="shared" si="1"/>
         <v>46.97</v>
       </c>
       <c r="H17" s="1">
         <v>1243.98</v>
       </c>
       <c r="I17" s="1">
-        <f>J17-H17</f>
+        <f t="shared" si="2"/>
         <v>58.49</v>
       </c>
       <c r="J17" s="1">
         <v>1302.47</v>
       </c>
       <c r="K17" s="1">
-        <f>L17-J17</f>
+        <f t="shared" si="3"/>
         <v>36.6399999999999</v>
       </c>
       <c r="L17" s="1">
         <v>1339.11</v>
       </c>
       <c r="M17" s="1">
-        <f>N17-L17</f>
+        <f t="shared" si="4"/>
         <v>33.99</v>
       </c>
       <c r="N17" s="1">
         <v>1373.1</v>
       </c>
       <c r="O17" s="1">
-        <f>L17-D17</f>
+        <f t="shared" si="5"/>
         <v>182.54</v>
       </c>
       <c r="P17" s="10" t="s">
@@ -2386,7 +2386,7 @@
         <v>331.97</v>
       </c>
       <c r="R17" s="15">
-        <f>2.84/(N17/Q17)</f>
+        <f t="shared" si="6"/>
         <v>0.686617726312723</v>
       </c>
     </row>
@@ -2404,42 +2404,42 @@
         <v>1060.77</v>
       </c>
       <c r="E18" s="1">
-        <f>F18-D18</f>
+        <f t="shared" si="0"/>
         <v>63.24</v>
       </c>
       <c r="F18" s="1">
         <v>1124.01</v>
       </c>
       <c r="G18" s="1">
-        <f>H18-F18</f>
+        <f t="shared" si="1"/>
         <v>19.6700000000001</v>
       </c>
       <c r="H18" s="1">
         <v>1143.68</v>
       </c>
       <c r="I18" s="1">
-        <f>J18-H18</f>
+        <f t="shared" si="2"/>
         <v>47.76</v>
       </c>
       <c r="J18" s="1">
         <v>1191.44</v>
       </c>
       <c r="K18" s="1">
-        <f>L18-J18</f>
+        <f t="shared" si="3"/>
         <v>40.22</v>
       </c>
       <c r="L18" s="1">
         <v>1231.66</v>
       </c>
       <c r="M18" s="1">
-        <f>N18-L18</f>
+        <f t="shared" si="4"/>
         <v>44.8</v>
       </c>
       <c r="N18" s="1">
         <v>1276.46</v>
       </c>
       <c r="O18" s="1">
-        <f>L18-D18</f>
+        <f t="shared" si="5"/>
         <v>170.89</v>
       </c>
       <c r="P18" s="10" t="s">
@@ -2449,7 +2449,7 @@
         <v>254.72</v>
       </c>
       <c r="R18" s="15">
-        <f>2.84/(N18/Q18)</f>
+        <f t="shared" si="6"/>
         <v>0.566727355342118</v>
       </c>
     </row>
@@ -2467,42 +2467,42 @@
         <v>953.78</v>
       </c>
       <c r="E19" s="1">
-        <f>F19-D19</f>
+        <f t="shared" si="0"/>
         <v>28.97</v>
       </c>
       <c r="F19" s="1">
         <v>982.75</v>
       </c>
       <c r="G19" s="1">
-        <f>H19-F19</f>
+        <f t="shared" si="1"/>
         <v>83.9300000000001</v>
       </c>
       <c r="H19" s="1">
         <v>1066.68</v>
       </c>
       <c r="I19" s="1">
-        <f>J19-H19</f>
+        <f t="shared" si="2"/>
         <v>42.8399999999999</v>
       </c>
       <c r="J19" s="1">
         <v>1109.52</v>
       </c>
       <c r="K19" s="1">
-        <f>L19-J19</f>
+        <f t="shared" si="3"/>
         <v>36.46</v>
       </c>
       <c r="L19" s="1">
         <v>1145.98</v>
       </c>
       <c r="M19" s="1">
-        <f>N19-L19</f>
+        <f t="shared" si="4"/>
         <v>37.49</v>
       </c>
       <c r="N19" s="1">
         <v>1183.47</v>
       </c>
       <c r="O19" s="1">
-        <f>L19-D19</f>
+        <f t="shared" si="5"/>
         <v>192.2</v>
       </c>
       <c r="P19" s="10" t="s">
@@ -2512,7 +2512,7 @@
         <v>416.72</v>
       </c>
       <c r="R19" s="15">
-        <f>2.84/(N19/Q19)</f>
+        <f t="shared" si="6"/>
         <v>1.00001250559794</v>
       </c>
     </row>
@@ -2530,42 +2530,42 @@
         <v>907.94</v>
       </c>
       <c r="E20" s="1">
-        <f>F20-D20</f>
+        <f t="shared" si="0"/>
         <v>64.0799999999999</v>
       </c>
       <c r="F20" s="1">
         <v>972.02</v>
       </c>
       <c r="G20" s="1">
-        <f>H20-F20</f>
+        <f t="shared" si="1"/>
         <v>36.26</v>
       </c>
       <c r="H20" s="1">
         <v>1008.28</v>
       </c>
       <c r="I20" s="1">
-        <f>J20-H20</f>
+        <f t="shared" si="2"/>
         <v>28.8</v>
       </c>
       <c r="J20" s="1">
         <v>1037.08</v>
       </c>
       <c r="K20" s="1">
-        <f>L20-J20</f>
+        <f t="shared" si="3"/>
         <v>40.1000000000001</v>
       </c>
       <c r="L20" s="1">
         <v>1077.18</v>
       </c>
       <c r="M20" s="1">
-        <f>N20-L20</f>
+        <f t="shared" si="4"/>
         <v>26.03</v>
       </c>
       <c r="N20" s="1">
         <v>1103.21</v>
       </c>
       <c r="O20" s="1">
-        <f>L20-D20</f>
+        <f t="shared" si="5"/>
         <v>169.24</v>
       </c>
       <c r="P20" s="10" t="s">
@@ -2575,7 +2575,7 @@
         <v>380.52</v>
       </c>
       <c r="R20" s="15">
-        <f>2.84/(N20/Q20)</f>
+        <f t="shared" si="6"/>
         <v>0.979574876949991</v>
       </c>
     </row>
@@ -2593,42 +2593,42 @@
         <v>950.09</v>
       </c>
       <c r="E21" s="1">
-        <f>F21-D21</f>
+        <f t="shared" si="0"/>
         <v>42.4</v>
       </c>
       <c r="F21" s="1">
         <v>992.49</v>
       </c>
       <c r="G21" s="1">
-        <f>H21-F21</f>
+        <f t="shared" si="1"/>
         <v>38.5899999999999</v>
       </c>
       <c r="H21" s="1">
         <v>1031.08</v>
       </c>
       <c r="I21" s="1">
-        <f>J21-H21</f>
+        <f t="shared" si="2"/>
         <v>22.6000000000001</v>
       </c>
       <c r="J21" s="1">
         <v>1053.68</v>
       </c>
       <c r="K21" s="1">
-        <f>L21-J21</f>
+        <f t="shared" si="3"/>
         <v>10.9299999999998</v>
       </c>
       <c r="L21" s="1">
         <v>1064.61</v>
       </c>
       <c r="M21" s="1">
-        <f>N21-L21</f>
+        <f t="shared" si="4"/>
         <v>16.1800000000001</v>
       </c>
       <c r="N21" s="1">
         <v>1080.79</v>
       </c>
       <c r="O21" s="1">
-        <f>L21-D21</f>
+        <f t="shared" si="5"/>
         <v>114.52</v>
       </c>
       <c r="P21" s="10" t="s">
@@ -2638,7 +2638,7 @@
         <v>417.17</v>
       </c>
       <c r="R21" s="15">
-        <f>2.84/(N21/Q21)</f>
+        <f t="shared" si="6"/>
         <v>1.0962007420498</v>
       </c>
     </row>
@@ -2656,42 +2656,42 @@
         <v>927.15</v>
       </c>
       <c r="E22" s="1">
-        <f>F22-D22</f>
+        <f t="shared" si="0"/>
         <v>17.9300000000001</v>
       </c>
       <c r="F22" s="1">
         <v>945.08</v>
       </c>
       <c r="G22" s="1">
-        <f>H22-F22</f>
+        <f t="shared" si="1"/>
         <v>24.04</v>
       </c>
       <c r="H22" s="1">
         <v>969.12</v>
       </c>
       <c r="I22" s="1">
-        <f>J22-H22</f>
+        <f t="shared" si="2"/>
         <v>26.96</v>
       </c>
       <c r="J22" s="1">
         <v>996.08</v>
       </c>
       <c r="K22" s="1">
-        <f>L22-J22</f>
+        <f t="shared" si="3"/>
         <v>23.3499999999999</v>
       </c>
       <c r="L22" s="1">
         <v>1019.43</v>
       </c>
       <c r="M22" s="1">
-        <f>N22-L22</f>
+        <f t="shared" si="4"/>
         <v>23.7400000000001</v>
       </c>
       <c r="N22" s="1">
         <v>1043.17</v>
       </c>
       <c r="O22" s="1">
-        <f>L22-D22</f>
+        <f t="shared" si="5"/>
         <v>92.28</v>
       </c>
       <c r="P22" s="10" t="s">
@@ -2701,7 +2701,7 @@
         <v>308.77</v>
       </c>
       <c r="R22" s="15">
-        <f>2.84/(N22/Q22)</f>
+        <f t="shared" si="6"/>
         <v>0.840617349041863</v>
       </c>
     </row>
@@ -2719,42 +2719,42 @@
         <v>848.93</v>
       </c>
       <c r="E23" s="1">
-        <f>F23-D23</f>
+        <f t="shared" si="0"/>
         <v>34.5600000000001</v>
       </c>
       <c r="F23" s="1">
         <v>883.49</v>
       </c>
       <c r="G23" s="1">
-        <f>H23-F23</f>
+        <f t="shared" si="1"/>
         <v>46.08</v>
       </c>
       <c r="H23" s="1">
         <v>929.57</v>
       </c>
       <c r="I23" s="1">
-        <f>J23-H23</f>
+        <f t="shared" si="2"/>
         <v>27.7399999999999</v>
       </c>
       <c r="J23" s="1">
         <v>957.31</v>
       </c>
       <c r="K23" s="1">
-        <f>L23-J23</f>
+        <f t="shared" si="3"/>
         <v>47.36</v>
       </c>
       <c r="L23" s="1">
         <v>1004.67</v>
       </c>
       <c r="M23" s="1">
-        <f>N23-L23</f>
+        <f t="shared" si="4"/>
         <v>25.9399999999999</v>
       </c>
       <c r="N23" s="1">
         <v>1030.61</v>
       </c>
       <c r="O23" s="1">
-        <f>L23-D23</f>
+        <f t="shared" si="5"/>
         <v>155.74</v>
       </c>
       <c r="P23" s="10" t="s">
@@ -2764,7 +2764,7 @@
         <v>348.62</v>
       </c>
       <c r="R23" s="15">
-        <f>2.84/(N23/Q23)</f>
+        <f t="shared" si="6"/>
         <v>0.960674551964371</v>
       </c>
     </row>
@@ -2782,42 +2782,42 @@
         <v>552.79</v>
       </c>
       <c r="E24" s="5">
-        <f>F24-D24</f>
+        <f t="shared" si="0"/>
         <v>15.9400000000001</v>
       </c>
       <c r="F24" s="5">
         <v>568.73</v>
       </c>
       <c r="G24" s="5">
-        <f>H24-F24</f>
+        <f t="shared" si="1"/>
         <v>1.61000000000001</v>
       </c>
       <c r="H24" s="5">
         <v>570.34</v>
       </c>
       <c r="I24" s="5">
-        <f>J24-H24</f>
+        <f t="shared" si="2"/>
         <v>7.13999999999999</v>
       </c>
       <c r="J24" s="5">
         <v>577.48</v>
       </c>
       <c r="K24" s="5">
-        <f>L24-J24</f>
+        <f t="shared" si="3"/>
         <v>2.88999999999999</v>
       </c>
       <c r="L24" s="5">
         <v>580.37</v>
       </c>
       <c r="M24" s="5">
-        <f>N24-L24</f>
+        <f t="shared" si="4"/>
         <v>2.55999999999995</v>
       </c>
       <c r="N24" s="5">
         <v>582.93</v>
       </c>
       <c r="O24" s="5">
-        <f>L24-D24</f>
+        <f t="shared" si="5"/>
         <v>27.58</v>
       </c>
       <c r="P24" s="11" t="s">
@@ -2827,7 +2827,7 @@
         <v>135.65</v>
       </c>
       <c r="R24" s="16">
-        <f>2.84/(N24/Q24)</f>
+        <f t="shared" si="6"/>
         <v>0.660878664676719</v>
       </c>
     </row>
@@ -2845,42 +2845,42 @@
         <v>407.35</v>
       </c>
       <c r="E25" s="5">
-        <f>F25-D25</f>
+        <f t="shared" si="0"/>
         <v>13.86</v>
       </c>
       <c r="F25" s="5">
         <v>421.21</v>
       </c>
       <c r="G25" s="5">
-        <f>H25-F25</f>
+        <f t="shared" si="1"/>
         <v>16.43</v>
       </c>
       <c r="H25" s="5">
         <v>437.64</v>
       </c>
       <c r="I25" s="5">
-        <f>J25-H25</f>
+        <f t="shared" si="2"/>
         <v>13.64</v>
       </c>
       <c r="J25" s="5">
         <v>451.28</v>
       </c>
       <c r="K25" s="5">
-        <f>L25-J25</f>
+        <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
       <c r="L25" s="5">
         <v>462.88</v>
       </c>
       <c r="M25" s="5">
-        <f>N25-L25</f>
+        <f t="shared" si="4"/>
         <v>47.68</v>
       </c>
       <c r="N25" s="5">
         <v>510.56</v>
       </c>
       <c r="O25" s="5">
-        <f>L25-D25</f>
+        <f t="shared" si="5"/>
         <v>55.53</v>
       </c>
       <c r="P25" s="11" t="s">
@@ -2890,7 +2890,7 @@
         <v>225.74</v>
       </c>
       <c r="R25" s="16">
-        <f>2.84/(N25/Q25)</f>
+        <f t="shared" si="6"/>
         <v>1.25568317141962</v>
       </c>
     </row>
@@ -2908,42 +2908,42 @@
         <v>363.88</v>
       </c>
       <c r="E26" s="5">
-        <f>F26-D26</f>
+        <f t="shared" si="0"/>
         <v>14.21</v>
       </c>
       <c r="F26" s="5">
         <v>378.09</v>
       </c>
       <c r="G26" s="5">
-        <f>H26-F26</f>
+        <f t="shared" si="1"/>
         <v>11.22</v>
       </c>
       <c r="H26" s="5">
         <v>389.31</v>
       </c>
       <c r="I26" s="5">
-        <f>J26-H26</f>
+        <f t="shared" si="2"/>
         <v>13.62</v>
       </c>
       <c r="J26" s="5">
         <v>402.93</v>
       </c>
       <c r="K26" s="5">
-        <f>L26-J26</f>
+        <f t="shared" si="3"/>
         <v>11.13</v>
       </c>
       <c r="L26" s="5">
         <v>414.06</v>
       </c>
       <c r="M26" s="5">
-        <f>N26-L26</f>
+        <f t="shared" si="4"/>
         <v>17.39</v>
       </c>
       <c r="N26" s="5">
         <v>431.45</v>
       </c>
       <c r="O26" s="5">
-        <f>L26-D26</f>
+        <f t="shared" si="5"/>
         <v>50.18</v>
       </c>
       <c r="P26" s="11" t="s">
@@ -2953,7 +2953,7 @@
         <v>111.89</v>
       </c>
       <c r="R26" s="16">
-        <f>2.84/(N26/Q26)</f>
+        <f t="shared" si="6"/>
         <v>0.736510835554525</v>
       </c>
     </row>
@@ -2971,42 +2971,42 @@
         <v>305.29</v>
       </c>
       <c r="E27" s="5">
-        <f>F27-D27</f>
+        <f t="shared" si="0"/>
         <v>17.97</v>
       </c>
       <c r="F27" s="5">
         <v>323.26</v>
       </c>
       <c r="G27" s="5">
-        <f>H27-F27</f>
+        <f t="shared" si="1"/>
         <v>10.82</v>
       </c>
       <c r="H27" s="5">
         <v>334.08</v>
       </c>
       <c r="I27" s="5">
-        <f>J27-H27</f>
+        <f t="shared" si="2"/>
         <v>16.2</v>
       </c>
       <c r="J27" s="5">
         <v>350.28</v>
       </c>
       <c r="K27" s="5">
-        <f>L27-J27</f>
+        <f t="shared" si="3"/>
         <v>10.8</v>
       </c>
       <c r="L27" s="5">
         <v>361.08</v>
       </c>
       <c r="M27" s="5">
-        <f>N27-L27</f>
+        <f t="shared" si="4"/>
         <v>9.98000000000002</v>
       </c>
       <c r="N27" s="5">
         <v>371.06</v>
       </c>
       <c r="O27" s="5">
-        <f>L27-D27</f>
+        <f t="shared" si="5"/>
         <v>55.79</v>
       </c>
       <c r="P27" s="11" t="s">
@@ -3016,7 +3016,7 @@
         <v>93.39</v>
       </c>
       <c r="R27" s="16">
-        <f>2.84/(N27/Q27)</f>
+        <f t="shared" si="6"/>
         <v>0.714783592949927</v>
       </c>
     </row>
@@ -3034,42 +3034,42 @@
         <v>262.39</v>
       </c>
       <c r="E28" s="5">
-        <f>F28-D28</f>
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
       <c r="F28" s="5">
         <v>273.89</v>
       </c>
       <c r="G28" s="5">
-        <f>H28-F28</f>
+        <f t="shared" si="1"/>
         <v>13.97</v>
       </c>
       <c r="H28" s="5">
         <v>287.86</v>
       </c>
       <c r="I28" s="5">
-        <f>J28-H28</f>
+        <f t="shared" si="2"/>
         <v>16.24</v>
       </c>
       <c r="J28" s="5">
         <v>304.1</v>
       </c>
       <c r="K28" s="5">
-        <f>L28-J28</f>
+        <f t="shared" si="3"/>
         <v>12.65</v>
       </c>
       <c r="L28" s="5">
         <v>316.75</v>
       </c>
       <c r="M28" s="5">
-        <f>N28-L28</f>
+        <f t="shared" si="4"/>
         <v>9.99000000000001</v>
       </c>
       <c r="N28" s="5">
         <v>326.74</v>
       </c>
       <c r="O28" s="5">
-        <f>L28-D28</f>
+        <f t="shared" si="5"/>
         <v>54.36</v>
       </c>
       <c r="P28" s="11" t="s">
@@ -3079,7 +3079,7 @@
         <v>113.04</v>
       </c>
       <c r="R28" s="16">
-        <f>2.84/(N28/Q28)</f>
+        <f t="shared" si="6"/>
         <v>0.982535349207321</v>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3227,7 +3227,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15390" windowHeight="11070"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
   <si>
     <t>区服</t>
   </si>
@@ -67,6 +67,9 @@
     <t>战力（2025.5.7）</t>
   </si>
   <si>
+    <t>战力（2025.5.14）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -76,9 +79,6 @@
     <t>首席英雄战力</t>
   </si>
   <si>
-    <t>飞值</t>
-  </si>
-  <si>
     <t>146区</t>
   </si>
   <si>
@@ -91,169 +91,166 @@
     <t>圣母（杂糅）</t>
   </si>
   <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>瓦斯兰（快攻）</t>
+  </si>
+  <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
     <t>江南</t>
   </si>
   <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
   </si>
   <si>
     <t>151区</t>
   </si>
   <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>梅（杂糅）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
     <t>星空</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>狐狸（快攻）</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>何斌</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>迅（养神）</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>秋雨</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
   </si>
   <si>
     <t>丽娅（杂糅）</t>
   </si>
   <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>梅（杂糅）</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>白处尊（养神）</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>何斌</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
     <t>氪度表：</t>
   </si>
   <si>
     <t>金额：</t>
-  </si>
-  <si>
-    <t>飞值：（以开飞机的贝塔总英雄战力除以首席英雄战力的值【2.834】为基准值再除以每个人的）：越高说明越专一，越低越是七边形战神。</t>
   </si>
   <si>
     <t>0-99</t>
@@ -296,12 +293,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -320,14 +316,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFC000"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFC000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -934,7 +930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -959,32 +955,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1302,32 +1283,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.2583333333333" customWidth="1"/>
-    <col min="3" max="3" width="11.5416666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.2583333333333" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="13.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="11.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="13.2545454545455" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7583333333333" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7545454545455" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7583333333333" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6333333333333" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.275" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="0.25" customWidth="1"/>
-    <col min="14" max="14" width="17.4583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.125" customWidth="1"/>
-    <col min="16" max="16" width="15.5" customWidth="1"/>
-    <col min="17" max="17" width="14.125" customWidth="1"/>
-    <col min="18" max="18" width="18.3666666666667" customWidth="1"/>
-    <col min="19" max="19" width="14.5416666666667" customWidth="1"/>
-    <col min="20" max="20" width="14.1833333333333" customWidth="1"/>
+    <col min="8" max="8" width="16.6272727272727" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7545454545455" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1272727272727" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6363636363636" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.2727272727273" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0.254545454545455" customWidth="1"/>
+    <col min="14" max="14" width="17.4545454545455" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1272727272727" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3545454545455" customWidth="1"/>
+    <col min="17" max="17" width="16.9909090909091" customWidth="1"/>
+    <col min="18" max="18" width="17.8636363636364" customWidth="1"/>
+    <col min="19" max="19" width="18.0181818181818" customWidth="1"/>
+    <col min="20" max="20" width="18.8909090909091" customWidth="1"/>
+    <col min="21" max="21" width="14.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1377,19 +1359,22 @@
         <v>10</v>
       </c>
       <c r="Q1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:20">
+    <row r="2" s="1" customFormat="1" spans="1:21">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1445,1639 +1430,1711 @@
         <v>4705.02</v>
       </c>
       <c r="Q2" s="2">
-        <f>P2-D2</f>
-        <v>599.540000000001</v>
-      </c>
-      <c r="R2" s="7" t="s">
+        <f>R2-P2</f>
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4743.24</v>
+      </c>
+      <c r="S2" s="2">
+        <f>R2-D2</f>
+        <v>637.76</v>
+      </c>
+      <c r="T2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="2">
-        <v>1328.92</v>
-      </c>
-      <c r="T2" s="8">
-        <f>2.834/(P2/S2)</f>
-        <v>0.80045553047596</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2" s="2">
+        <v>1352.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3">
-        <v>1966.62</v>
+        <v>2714.1</v>
       </c>
       <c r="E3" s="3">
         <f>F3-D3</f>
-        <v>49.0200000000002</v>
+        <v>123.29</v>
       </c>
       <c r="F3" s="3">
-        <v>2015.64</v>
+        <v>2837.39</v>
       </c>
       <c r="G3" s="3">
         <f>H3-F3</f>
-        <v>34.1600000000001</v>
+        <v>95.8499999999999</v>
       </c>
       <c r="H3" s="3">
-        <v>2049.8</v>
+        <v>2933.24</v>
       </c>
       <c r="I3" s="3">
         <f>J3-H3</f>
-        <v>90.0999999999999</v>
+        <v>92.46</v>
       </c>
       <c r="J3" s="3">
-        <v>2139.9</v>
+        <v>3025.7</v>
       </c>
       <c r="K3" s="3">
         <f>L3-J3</f>
-        <v>53.1700000000001</v>
+        <v>90.4100000000003</v>
       </c>
       <c r="L3" s="3">
-        <v>2193.07</v>
+        <v>3116.11</v>
       </c>
       <c r="M3" s="3">
         <f>N3-L3</f>
-        <v>63.9099999999999</v>
+        <v>103.54</v>
       </c>
       <c r="N3" s="3">
-        <v>2256.98</v>
+        <v>3219.65</v>
       </c>
       <c r="O3" s="3">
         <f>P3-N3</f>
-        <v>45.71</v>
+        <v>75.6599999999999</v>
       </c>
       <c r="P3" s="3">
-        <v>2302.69</v>
+        <v>3295.31</v>
       </c>
       <c r="Q3" s="3">
-        <f>P3-D3</f>
-        <v>336.07</v>
-      </c>
-      <c r="R3" s="9" t="s">
+        <f>R3-P3</f>
+        <v>88.98</v>
+      </c>
+      <c r="R3" s="3">
+        <v>3384.29</v>
+      </c>
+      <c r="S3" s="3">
+        <f>R3-D3</f>
+        <v>670.19</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" s="3">
+        <v>640.72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="3">
-        <v>824.67</v>
-      </c>
-      <c r="T3" s="10">
-        <f>2.834/(P3/S3)</f>
-        <v>1.01494981087337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2714.1</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="3">
+        <v>2533.85</v>
+      </c>
+      <c r="E4" s="3">
         <f>F4-D4</f>
-        <v>123.29</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2837.39</v>
-      </c>
-      <c r="G4" s="4">
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2583.9</v>
+      </c>
+      <c r="G4" s="3">
         <f>H4-F4</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H4" s="4">
-        <v>2933.24</v>
-      </c>
-      <c r="I4" s="4">
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2669.66</v>
+      </c>
+      <c r="I4" s="3">
         <f>J4-H4</f>
-        <v>92.46</v>
-      </c>
-      <c r="J4" s="4">
-        <v>3025.7</v>
-      </c>
-      <c r="K4" s="4">
+        <v>81.79</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2751.45</v>
+      </c>
+      <c r="K4" s="3">
         <f>L4-J4</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L4" s="4">
-        <v>3116.11</v>
-      </c>
-      <c r="M4" s="4">
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2834.62</v>
+      </c>
+      <c r="M4" s="3">
         <f>N4-L4</f>
-        <v>103.54</v>
-      </c>
-      <c r="N4" s="4">
-        <v>3219.65</v>
-      </c>
-      <c r="O4" s="4">
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N4" s="3">
+        <v>2891.61</v>
+      </c>
+      <c r="O4" s="3">
         <f>P4-N4</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P4" s="4">
-        <v>3295.31</v>
-      </c>
-      <c r="Q4" s="4">
-        <f>P4-D4</f>
-        <v>581.21</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="4">
-        <v>675.52</v>
-      </c>
-      <c r="T4" s="12">
-        <f>2.834/(P4/S4)</f>
-        <v>0.580954046811984</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" s="3" t="s">
+        <v>103.98</v>
+      </c>
+      <c r="P4" s="3">
+        <v>2995.59</v>
+      </c>
+      <c r="Q4" s="3">
+        <f>R4-P4</f>
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R4" s="3">
+        <v>3064.44</v>
+      </c>
+      <c r="S4" s="3">
+        <f>R4-D4</f>
+        <v>530.59</v>
+      </c>
+      <c r="T4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="U4" s="3">
+        <v>607.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>2136.24</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <f>F5-D5</f>
         <v>40.8200000000002</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>2177.06</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <f>H5-F5</f>
         <v>62.5999999999999</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>2239.66</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <f>J5-H5</f>
         <v>47.0700000000002</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <v>2286.73</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="4">
         <f>L5-J5</f>
         <v>25.52</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <v>2312.25</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="4">
         <f>N5-L5</f>
         <v>36.7800000000002</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="4">
         <v>2349.03</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <f>P5-N5</f>
         <v>-18.02</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="4">
         <v>2331.01</v>
       </c>
-      <c r="Q5" s="3">
-        <f>P5-D5</f>
-        <v>194.77</v>
-      </c>
-      <c r="R5" s="9" t="s">
+      <c r="Q5" s="4">
+        <f>R5-P5</f>
+        <v>62.7599999999998</v>
+      </c>
+      <c r="R5" s="4">
+        <v>2393.77</v>
+      </c>
+      <c r="S5" s="4">
+        <f>R5-D5</f>
+        <v>257.53</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="U5" s="4">
+        <v>708.07</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2183.01</v>
+      </c>
+      <c r="E6" s="4">
+        <f>F6-D6</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2207.13</v>
+      </c>
+      <c r="G6" s="4">
+        <f>H6-F6</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2229.99</v>
+      </c>
+      <c r="I6" s="4">
+        <f>J6-H6</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2241.77</v>
+      </c>
+      <c r="K6" s="4">
+        <f>L6-J6</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L6" s="4">
+        <v>2254.78</v>
+      </c>
+      <c r="M6" s="4">
+        <f>N6-L6</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N6" s="4">
+        <v>2317.42</v>
+      </c>
+      <c r="O6" s="4">
+        <f>P6-N6</f>
+        <v>16.27</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2333.69</v>
+      </c>
+      <c r="Q6" s="4">
+        <f>R6-P6</f>
+        <v>36.5</v>
+      </c>
+      <c r="R6" s="4">
+        <v>2370.19</v>
+      </c>
+      <c r="S6" s="4">
+        <f>R6-D6</f>
+        <v>187.18</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" s="4">
+        <v>593.07</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="3">
-        <v>674.42</v>
-      </c>
-      <c r="T5" s="10">
-        <f>2.834/(P5/S5)</f>
-        <v>0.819947696492078</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="D7" s="4">
+        <v>1966.62</v>
+      </c>
+      <c r="E7" s="4">
+        <f>F7-D7</f>
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2015.64</v>
+      </c>
+      <c r="G7" s="4">
+        <f>H7-F7</f>
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2049.8</v>
+      </c>
+      <c r="I7" s="4">
+        <f>J7-H7</f>
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2139.9</v>
+      </c>
+      <c r="K7" s="4">
+        <f>L7-J7</f>
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L7" s="4">
+        <v>2193.07</v>
+      </c>
+      <c r="M7" s="4">
+        <f>N7-L7</f>
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N7" s="4">
+        <v>2256.98</v>
+      </c>
+      <c r="O7" s="4">
+        <f>P7-N7</f>
+        <v>45.71</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2302.69</v>
+      </c>
+      <c r="Q7" s="4">
+        <f>R7-P7</f>
+        <v>37.2199999999998</v>
+      </c>
+      <c r="R7" s="4">
+        <v>2339.91</v>
+      </c>
+      <c r="S7" s="4">
+        <f>R7-D7</f>
+        <v>373.29</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1446.65</v>
-      </c>
-      <c r="E6" s="1">
-        <f>F6-D6</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1474.83</v>
-      </c>
-      <c r="G6" s="1">
-        <f>H6-F6</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1538.65</v>
-      </c>
-      <c r="I6" s="1">
-        <f>J6-H6</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1561.57</v>
-      </c>
-      <c r="K6" s="1">
-        <f>L6-J6</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1632.43</v>
-      </c>
-      <c r="M6" s="1">
-        <f>N6-L6</f>
-        <v>37.4099999999999</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1669.84</v>
-      </c>
-      <c r="O6" s="1">
-        <f>P6-N6</f>
-        <v>32.8300000000002</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1702.67</v>
-      </c>
-      <c r="Q6" s="1">
-        <f>P6-D6</f>
-        <v>256.02</v>
-      </c>
-      <c r="R6" s="13" t="s">
+      <c r="U7" s="4">
+        <v>830.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="S6" s="1">
-        <v>669.37</v>
-      </c>
-      <c r="T6" s="14">
-        <f>2.834/(P6/S6)</f>
-        <v>1.11412932629341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2533.85</v>
-      </c>
-      <c r="E7" s="3">
-        <f>F7-D7</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2583.9</v>
-      </c>
-      <c r="G7" s="3">
-        <f>H7-F7</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2669.66</v>
-      </c>
-      <c r="I7" s="3">
-        <f>J7-H7</f>
-        <v>81.79</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2751.45</v>
-      </c>
-      <c r="K7" s="3">
-        <f>L7-J7</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L7" s="3">
-        <v>2834.62</v>
-      </c>
-      <c r="M7" s="3">
-        <f>N7-L7</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N7" s="3">
-        <v>2891.61</v>
-      </c>
-      <c r="O7" s="3">
-        <f>P7-N7</f>
-        <v>103.98</v>
-      </c>
-      <c r="P7" s="3">
-        <v>2995.59</v>
-      </c>
-      <c r="Q7" s="3">
-        <f>P7-D7</f>
-        <v>461.74</v>
-      </c>
-      <c r="R7" s="9" t="s">
+      <c r="D8" s="4">
+        <v>1754.54</v>
+      </c>
+      <c r="E8" s="4">
+        <f>F8-D8</f>
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1807.91</v>
+      </c>
+      <c r="G8" s="4">
+        <f>H8-F8</f>
+        <v>90.24</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1898.15</v>
+      </c>
+      <c r="I8" s="4">
+        <f>J8-H8</f>
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1988.53</v>
+      </c>
+      <c r="K8" s="4">
+        <f>L8-J8</f>
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L8" s="4">
+        <v>2048.24</v>
+      </c>
+      <c r="M8" s="4">
+        <f>N8-L8</f>
+        <v>153.99</v>
+      </c>
+      <c r="N8" s="4">
+        <v>2202.23</v>
+      </c>
+      <c r="O8" s="4">
+        <f>P8-N8</f>
+        <v>64.21</v>
+      </c>
+      <c r="P8" s="4">
+        <v>2266.44</v>
+      </c>
+      <c r="Q8" s="4">
+        <f>R8-P8</f>
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2314</v>
+      </c>
+      <c r="S8" s="4">
+        <f>R8-D8</f>
+        <v>559.46</v>
+      </c>
+      <c r="T8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="3">
-        <v>620.62</v>
-      </c>
-      <c r="T7" s="10">
-        <f>2.834/(P7/S7)</f>
-        <v>0.587142125591286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="U8" s="4">
+        <v>371.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3">
-        <v>2183.01</v>
-      </c>
-      <c r="E8" s="3">
-        <f>F8-D8</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2207.13</v>
-      </c>
-      <c r="G8" s="3">
-        <f>H8-F8</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2229.99</v>
-      </c>
-      <c r="I8" s="3">
-        <f>J8-H8</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2241.77</v>
-      </c>
-      <c r="K8" s="3">
-        <f>L8-J8</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2254.78</v>
-      </c>
-      <c r="M8" s="3">
-        <f>N8-L8</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2317.42</v>
-      </c>
-      <c r="O8" s="3">
-        <f>P8-N8</f>
-        <v>16.27</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2333.69</v>
-      </c>
-      <c r="Q8" s="3">
-        <f>P8-D8</f>
-        <v>150.68</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="3">
-        <v>563.62</v>
-      </c>
-      <c r="T8" s="10">
-        <f>2.834/(P8/S8)</f>
-        <v>0.684452125175152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1350.52</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="4">
+        <v>1735.94</v>
+      </c>
+      <c r="E9" s="4">
         <f>F9-D9</f>
-        <v>52.6800000000001</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1403.2</v>
-      </c>
-      <c r="G9" s="1">
+        <v>48.5999999999999</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1784.54</v>
+      </c>
+      <c r="G9" s="4">
         <f>H9-F9</f>
-        <v>55.3199999999999</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1458.52</v>
-      </c>
-      <c r="I9" s="1">
+        <v>74.1600000000001</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1858.7</v>
+      </c>
+      <c r="I9" s="4">
         <f>J9-H9</f>
-        <v>32.6800000000001</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1491.2</v>
-      </c>
-      <c r="K9" s="1">
+        <v>65.55</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1924.25</v>
+      </c>
+      <c r="K9" s="4">
         <f>L9-J9</f>
-        <v>54.96</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1546.16</v>
-      </c>
-      <c r="M9" s="1">
+        <v>35.73</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1959.98</v>
+      </c>
+      <c r="M9" s="4">
         <f>N9-L9</f>
-        <v>92.1299999999999</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1638.29</v>
-      </c>
-      <c r="O9" s="1">
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N9" s="4">
+        <v>2001.86</v>
+      </c>
+      <c r="O9" s="4">
         <f>P9-N9</f>
-        <v>59.4400000000001</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1697.73</v>
-      </c>
-      <c r="Q9" s="1">
-        <f>P9-D9</f>
-        <v>347.21</v>
-      </c>
-      <c r="R9" s="13" t="s">
+        <v>74.6600000000001</v>
+      </c>
+      <c r="P9" s="4">
+        <v>2076.52</v>
+      </c>
+      <c r="Q9" s="4">
+        <f>R9-P9</f>
+        <v>48.71</v>
+      </c>
+      <c r="R9" s="4">
+        <v>2125.23</v>
+      </c>
+      <c r="S9" s="4">
+        <f>R9-D9</f>
+        <v>389.29</v>
+      </c>
+      <c r="T9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="S9" s="1">
-        <v>545.82</v>
-      </c>
-      <c r="T9" s="14">
-        <f>2.834/(P9/S9)</f>
-        <v>0.911130674488876</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="U9" s="4">
+        <v>523.92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1735.94</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1726.42</v>
+      </c>
+      <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>48.5999999999999</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1784.54</v>
-      </c>
-      <c r="G10" s="3">
+        <v>56.28</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1782.7</v>
+      </c>
+      <c r="G10" s="4">
         <f>H10-F10</f>
-        <v>74.1600000000001</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1858.7</v>
-      </c>
-      <c r="I10" s="3">
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1853.62</v>
+      </c>
+      <c r="I10" s="4">
         <f>J10-H10</f>
-        <v>65.55</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1924.25</v>
-      </c>
-      <c r="K10" s="3">
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1903.2</v>
+      </c>
+      <c r="K10" s="4">
         <f>L10-J10</f>
-        <v>35.73</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1959.98</v>
-      </c>
-      <c r="M10" s="3">
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1943.61</v>
+      </c>
+      <c r="M10" s="4">
         <f>N10-L10</f>
-        <v>41.8799999999999</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2001.86</v>
-      </c>
-      <c r="O10" s="3">
+        <v>30.01</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1973.62</v>
+      </c>
+      <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>74.6600000000001</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2076.52</v>
-      </c>
-      <c r="Q10" s="3">
-        <f>P10-D10</f>
-        <v>340.58</v>
-      </c>
-      <c r="R10" s="9" t="s">
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P10" s="4">
+        <v>2056.9</v>
+      </c>
+      <c r="Q10" s="4">
+        <f>R10-P10</f>
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R10" s="4">
+        <v>2082.54</v>
+      </c>
+      <c r="S10" s="4">
+        <f>R10-D10</f>
+        <v>356.12</v>
+      </c>
+      <c r="T10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="S10" s="3">
-        <v>511.12</v>
-      </c>
-      <c r="T10" s="10">
-        <f>2.834/(P10/S10)</f>
-        <v>0.697568085065398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="U10" s="4">
+        <v>461.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1726.42</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1425.22</v>
+      </c>
+      <c r="E11" s="1">
         <f>F11-D11</f>
-        <v>56.28</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1782.7</v>
-      </c>
-      <c r="G11" s="3">
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1490.08</v>
+      </c>
+      <c r="G11" s="1">
         <f>H11-F11</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1853.62</v>
-      </c>
-      <c r="I11" s="3">
+        <v>46</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1536.08</v>
+      </c>
+      <c r="I11" s="1">
         <f>J11-H11</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1903.2</v>
-      </c>
-      <c r="K11" s="3">
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1586.93</v>
+      </c>
+      <c r="K11" s="1">
         <f>L11-J11</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1943.61</v>
-      </c>
-      <c r="M11" s="3">
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1673.49</v>
+      </c>
+      <c r="M11" s="1">
         <f>N11-L11</f>
-        <v>30.01</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1973.62</v>
-      </c>
-      <c r="O11" s="3">
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1712.05</v>
+      </c>
+      <c r="O11" s="1">
         <f>P11-N11</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P11" s="3">
-        <v>2056.9</v>
-      </c>
-      <c r="Q11" s="3">
-        <f>P11-D11</f>
-        <v>330.48</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="S11" s="3">
-        <v>461.67</v>
-      </c>
-      <c r="T11" s="10">
-        <f>2.834/(P11/S11)</f>
-        <v>0.636089639749137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1769.14</v>
+      </c>
+      <c r="Q11" s="1">
+        <f>R11-P11</f>
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1820.01</v>
+      </c>
+      <c r="S11" s="1">
+        <f>R11-D11</f>
+        <v>394.79</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11" s="1">
+        <v>441.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1">
-        <v>953.78</v>
+        <v>1576.18</v>
       </c>
       <c r="E12" s="1">
         <f>F12-D12</f>
-        <v>28.97</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>982.75</v>
+        <v>1615.02</v>
       </c>
       <c r="G12" s="1">
         <f>H12-F12</f>
-        <v>83.9300000000001</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>1066.68</v>
+        <v>1650.62</v>
       </c>
       <c r="I12" s="1">
         <f>J12-H12</f>
-        <v>42.8399999999999</v>
+        <v>37.47</v>
       </c>
       <c r="J12" s="1">
-        <v>1109.52</v>
+        <v>1688.09</v>
       </c>
       <c r="K12" s="1">
         <f>L12-J12</f>
-        <v>36.46</v>
+        <v>21.49</v>
       </c>
       <c r="L12" s="1">
-        <v>1145.98</v>
+        <v>1709.58</v>
       </c>
       <c r="M12" s="1">
         <f>N12-L12</f>
-        <v>37.49</v>
+        <v>24.53</v>
       </c>
       <c r="N12" s="1">
-        <v>1183.47</v>
+        <v>1734.11</v>
       </c>
       <c r="O12" s="1">
         <f>P12-N12</f>
-        <v>33.3699999999999</v>
+        <v>19.5300000000002</v>
       </c>
       <c r="P12" s="1">
-        <v>1216.84</v>
+        <v>1753.64</v>
       </c>
       <c r="Q12" s="1">
-        <f>P12-D12</f>
-        <v>263.06</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>30</v>
+        <f>R12-P12</f>
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1818.75</v>
       </c>
       <c r="S12" s="1">
-        <v>429.37</v>
-      </c>
-      <c r="T12" s="14">
-        <f>2.834/(P12/S12)</f>
-        <v>0.999995545840045</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <f>R12-D12</f>
+        <v>242.57</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="U12" s="1">
+        <v>365.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1">
-        <v>1425.22</v>
+        <v>1350.52</v>
       </c>
       <c r="E13" s="1">
         <f>F13-D13</f>
-        <v>64.8599999999999</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>1490.08</v>
+        <v>1403.2</v>
       </c>
       <c r="G13" s="1">
         <f>H13-F13</f>
-        <v>46</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>1536.08</v>
+        <v>1458.52</v>
       </c>
       <c r="I13" s="1">
         <f>J13-H13</f>
-        <v>50.8500000000001</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J13" s="1">
-        <v>1586.93</v>
+        <v>1491.2</v>
       </c>
       <c r="K13" s="1">
         <f>L13-J13</f>
-        <v>86.5599999999999</v>
+        <v>54.96</v>
       </c>
       <c r="L13" s="1">
-        <v>1673.49</v>
+        <v>1546.16</v>
       </c>
       <c r="M13" s="1">
         <f>N13-L13</f>
-        <v>38.5599999999999</v>
+        <v>92.1299999999999</v>
       </c>
       <c r="N13" s="1">
-        <v>1712.05</v>
+        <v>1638.29</v>
       </c>
       <c r="O13" s="1">
         <f>P13-N13</f>
-        <v>57.0900000000001</v>
+        <v>59.4400000000001</v>
       </c>
       <c r="P13" s="1">
-        <v>1769.14</v>
+        <v>1697.73</v>
       </c>
       <c r="Q13" s="1">
-        <f>P13-D13</f>
-        <v>343.92</v>
-      </c>
-      <c r="R13" s="13" t="s">
+        <f>R13-P13</f>
+        <v>71.3399999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1769.07</v>
+      </c>
+      <c r="S13" s="1">
+        <f>R13-D13</f>
+        <v>418.55</v>
+      </c>
+      <c r="T13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U13" s="1">
+        <v>553.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S13" s="1">
-        <v>427.57</v>
-      </c>
-      <c r="T13" s="14">
-        <f>2.834/(P13/S13)</f>
-        <v>0.684927919780232</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1">
-        <v>950.09</v>
+        <v>1446.65</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>42.4</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F14" s="1">
-        <v>992.49</v>
+        <v>1474.83</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>38.5899999999999</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H14" s="1">
-        <v>1031.08</v>
+        <v>1538.65</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>22.6000000000001</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J14" s="1">
-        <v>1053.68</v>
+        <v>1561.57</v>
       </c>
       <c r="K14" s="1">
         <f>L14-J14</f>
-        <v>10.9299999999998</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>1064.61</v>
+        <v>1632.43</v>
       </c>
       <c r="M14" s="1">
         <f>N14-L14</f>
-        <v>16.1800000000001</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N14" s="1">
-        <v>1080.79</v>
+        <v>1669.84</v>
       </c>
       <c r="O14" s="1">
         <f>P14-N14</f>
-        <v>13.6700000000001</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P14" s="1">
-        <v>1094.46</v>
+        <v>1702.67</v>
       </c>
       <c r="Q14" s="1">
-        <f>P14-D14</f>
-        <v>144.37</v>
-      </c>
-      <c r="R14" s="13" t="s">
-        <v>49</v>
+        <f>R14-P14</f>
+        <v>51.9499999999998</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1754.62</v>
       </c>
       <c r="S14" s="1">
-        <v>417.17</v>
-      </c>
-      <c r="T14" s="14">
-        <f>2.834/(P14/S14)</f>
-        <v>1.08022200902728</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <f>R14-D14</f>
+        <v>307.97</v>
+      </c>
+      <c r="T14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U14" s="1">
+        <v>679.57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1">
-        <v>1576.18</v>
+        <v>1349.35</v>
       </c>
       <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>38.8399999999999</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>1615.02</v>
+        <v>1398.97</v>
       </c>
       <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>35.5999999999999</v>
+        <v>27.79</v>
       </c>
       <c r="H15" s="1">
-        <v>1650.62</v>
+        <v>1426.76</v>
       </c>
       <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>37.47</v>
+        <v>29.02</v>
       </c>
       <c r="J15" s="1">
-        <v>1688.09</v>
+        <v>1455.78</v>
       </c>
       <c r="K15" s="1">
         <f>L15-J15</f>
-        <v>21.49</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L15" s="1">
-        <v>1709.58</v>
+        <v>1553.66</v>
       </c>
       <c r="M15" s="1">
         <f>N15-L15</f>
-        <v>24.53</v>
+        <v>42.3599999999999</v>
       </c>
       <c r="N15" s="1">
-        <v>1734.11</v>
+        <v>1596.02</v>
       </c>
       <c r="O15" s="1">
         <f>P15-N15</f>
-        <v>19.5300000000002</v>
+        <v>54.22</v>
       </c>
       <c r="P15" s="1">
-        <v>1753.64</v>
+        <v>1650.24</v>
       </c>
       <c r="Q15" s="1">
-        <f>P15-D15</f>
-        <v>177.46</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>51</v>
+        <f>R15-P15</f>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1685.83</v>
       </c>
       <c r="S15" s="1">
-        <v>407.37</v>
-      </c>
-      <c r="T15" s="14">
-        <f>2.834/(P15/S15)</f>
-        <v>0.658337275609589</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <f>R15-D15</f>
+        <v>336.48</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="U15" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1">
-        <v>1349.35</v>
+        <v>1156.57</v>
       </c>
       <c r="E16" s="1">
         <f>F16-D16</f>
-        <v>49.6200000000001</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>1398.97</v>
+        <v>1197.01</v>
       </c>
       <c r="G16" s="1">
         <f>H16-F16</f>
-        <v>27.79</v>
+        <v>46.97</v>
       </c>
       <c r="H16" s="1">
-        <v>1426.76</v>
+        <v>1243.98</v>
       </c>
       <c r="I16" s="1">
         <f>J16-H16</f>
-        <v>29.02</v>
+        <v>58.49</v>
       </c>
       <c r="J16" s="1">
-        <v>1455.78</v>
+        <v>1302.47</v>
       </c>
       <c r="K16" s="1">
         <f>L16-J16</f>
-        <v>97.8800000000001</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L16" s="1">
-        <v>1553.66</v>
+        <v>1339.11</v>
       </c>
       <c r="M16" s="1">
         <f>N16-L16</f>
-        <v>42.3599999999999</v>
+        <v>33.99</v>
       </c>
       <c r="N16" s="1">
-        <v>1596.02</v>
+        <v>1373.1</v>
       </c>
       <c r="O16" s="1">
         <f>P16-N16</f>
-        <v>54.22</v>
+        <v>30.0600000000002</v>
       </c>
       <c r="P16" s="1">
-        <v>1650.24</v>
+        <v>1403.16</v>
       </c>
       <c r="Q16" s="1">
-        <f>P16-D16</f>
-        <v>300.89</v>
-      </c>
-      <c r="R16" s="13" t="s">
+        <f>R16-P16</f>
+        <v>47.3</v>
+      </c>
+      <c r="R16" s="1">
+        <v>1450.46</v>
+      </c>
+      <c r="S16" s="1">
+        <f>R16-D16</f>
+        <v>293.89</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="U16" s="1">
+        <v>357.57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1317.56</v>
+      </c>
+      <c r="E17" s="1">
+        <f>F17-D17</f>
+        <v>15.77</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1333.33</v>
+      </c>
+      <c r="G17" s="1">
+        <f>H17-F17</f>
+        <v>15.1700000000001</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1348.5</v>
+      </c>
+      <c r="I17" s="1">
+        <f>J17-H17</f>
+        <v>28.9300000000001</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1377.43</v>
+      </c>
+      <c r="K17" s="1">
+        <f>L17-J17</f>
+        <v>9.14999999999986</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1386.58</v>
+      </c>
+      <c r="M17" s="1">
+        <f>N17-L17</f>
+        <v>29.4100000000001</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1415.99</v>
+      </c>
+      <c r="O17" s="1">
+        <f>P17-N17</f>
+        <v>8.81999999999994</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1424.81</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>R17-P17</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1424.81</v>
+      </c>
+      <c r="S17" s="1">
+        <f>R17-D17</f>
+        <v>107.25</v>
+      </c>
+      <c r="T17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="S16" s="1">
-        <v>402.48</v>
-      </c>
-      <c r="T16" s="14">
-        <f>2.834/(P16/S16)</f>
-        <v>0.691189354275742</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1754.54</v>
-      </c>
-      <c r="E17" s="3">
-        <f>F17-D17</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1807.91</v>
-      </c>
-      <c r="G17" s="3">
-        <f>H17-F17</f>
-        <v>90.24</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1898.15</v>
-      </c>
-      <c r="I17" s="3">
-        <f>J17-H17</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1988.53</v>
-      </c>
-      <c r="K17" s="3">
-        <f>L17-J17</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2048.24</v>
-      </c>
-      <c r="M17" s="3">
-        <f>N17-L17</f>
-        <v>153.99</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2202.23</v>
-      </c>
-      <c r="O17" s="3">
-        <f>P17-N17</f>
-        <v>64.21</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2266.44</v>
-      </c>
-      <c r="Q17" s="3">
-        <f>P17-D17</f>
-        <v>511.9</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S17" s="3">
-        <v>389.97</v>
-      </c>
-      <c r="T17" s="10">
-        <f>2.834/(P17/S17)</f>
-        <v>0.487625959654789</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17" s="1">
+        <v>271.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1">
-        <v>907.94</v>
+        <v>1060.77</v>
       </c>
       <c r="E18" s="1">
         <f>F18-D18</f>
-        <v>64.0799999999999</v>
+        <v>63.24</v>
       </c>
       <c r="F18" s="1">
-        <v>972.02</v>
+        <v>1124.01</v>
       </c>
       <c r="G18" s="1">
         <f>H18-F18</f>
-        <v>36.26</v>
+        <v>19.6700000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>1008.28</v>
+        <v>1143.68</v>
       </c>
       <c r="I18" s="1">
         <f>J18-H18</f>
-        <v>28.8</v>
+        <v>47.76</v>
       </c>
       <c r="J18" s="1">
-        <v>1037.08</v>
+        <v>1191.44</v>
       </c>
       <c r="K18" s="1">
         <f>L18-J18</f>
-        <v>40.1000000000001</v>
+        <v>40.22</v>
       </c>
       <c r="L18" s="1">
-        <v>1077.18</v>
+        <v>1231.66</v>
       </c>
       <c r="M18" s="1">
         <f>N18-L18</f>
-        <v>26.03</v>
+        <v>44.8</v>
       </c>
       <c r="N18" s="1">
-        <v>1103.21</v>
+        <v>1276.46</v>
       </c>
       <c r="O18" s="1">
         <f>P18-N18</f>
-        <v>28.3499999999999</v>
+        <v>28.03</v>
       </c>
       <c r="P18" s="1">
-        <v>1131.56</v>
+        <v>1304.49</v>
       </c>
       <c r="Q18" s="1">
-        <f>P18-D18</f>
-        <v>223.62</v>
-      </c>
-      <c r="R18" s="13" t="s">
-        <v>24</v>
+        <f>R18-P18</f>
+        <v>31.78</v>
+      </c>
+      <c r="R18" s="1">
+        <v>1336.27</v>
       </c>
       <c r="S18" s="1">
-        <v>377.22</v>
-      </c>
-      <c r="T18" s="14">
-        <f>2.834/(P18/S18)</f>
-        <v>0.944750150235074</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <f>R18-D18</f>
+        <v>275.5</v>
+      </c>
+      <c r="T18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="U18" s="1">
+        <v>264.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1">
-        <v>848.93</v>
+        <v>953.78</v>
       </c>
       <c r="E19" s="1">
         <f>F19-D19</f>
-        <v>34.5600000000001</v>
+        <v>28.97</v>
       </c>
       <c r="F19" s="1">
-        <v>883.49</v>
+        <v>982.75</v>
       </c>
       <c r="G19" s="1">
         <f>H19-F19</f>
-        <v>46.08</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>929.57</v>
+        <v>1066.68</v>
       </c>
       <c r="I19" s="1">
         <f>J19-H19</f>
-        <v>27.7399999999999</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J19" s="1">
-        <v>957.31</v>
+        <v>1109.52</v>
       </c>
       <c r="K19" s="1">
         <f>L19-J19</f>
-        <v>47.36</v>
+        <v>36.46</v>
       </c>
       <c r="L19" s="1">
-        <v>1004.67</v>
+        <v>1145.98</v>
       </c>
       <c r="M19" s="1">
         <f>N19-L19</f>
-        <v>25.9399999999999</v>
+        <v>37.49</v>
       </c>
       <c r="N19" s="1">
-        <v>1030.61</v>
+        <v>1183.47</v>
       </c>
       <c r="O19" s="1">
         <f>P19-N19</f>
-        <v>37.71</v>
+        <v>33.3699999999999</v>
       </c>
       <c r="P19" s="1">
-        <v>1068.32</v>
+        <v>1216.84</v>
       </c>
       <c r="Q19" s="1">
-        <f>P19-D19</f>
-        <v>219.39</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>30</v>
+        <f>R19-P19</f>
+        <v>24.8900000000001</v>
+      </c>
+      <c r="R19" s="1">
+        <v>1241.73</v>
       </c>
       <c r="S19" s="1">
-        <v>364.12</v>
-      </c>
-      <c r="T19" s="14">
-        <f>2.834/(P19/S19)</f>
-        <v>0.965924142579003</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <f>R19-D19</f>
+        <v>287.95</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U19" s="1">
+        <v>438.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
-        <v>1156.57</v>
+        <v>907.94</v>
       </c>
       <c r="E20" s="1">
         <f>F20-D20</f>
-        <v>40.4400000000001</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>1197.01</v>
+        <v>972.02</v>
       </c>
       <c r="G20" s="1">
         <f>H20-F20</f>
-        <v>46.97</v>
+        <v>36.26</v>
       </c>
       <c r="H20" s="1">
-        <v>1243.98</v>
+        <v>1008.28</v>
       </c>
       <c r="I20" s="1">
         <f>J20-H20</f>
-        <v>58.49</v>
+        <v>28.8</v>
       </c>
       <c r="J20" s="1">
-        <v>1302.47</v>
+        <v>1037.08</v>
       </c>
       <c r="K20" s="1">
         <f>L20-J20</f>
-        <v>36.6399999999999</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L20" s="1">
-        <v>1339.11</v>
+        <v>1077.18</v>
       </c>
       <c r="M20" s="1">
         <f>N20-L20</f>
-        <v>33.99</v>
+        <v>26.03</v>
       </c>
       <c r="N20" s="1">
-        <v>1373.1</v>
+        <v>1103.21</v>
       </c>
       <c r="O20" s="1">
         <f>P20-N20</f>
-        <v>30.0600000000002</v>
+        <v>28.3499999999999</v>
       </c>
       <c r="P20" s="1">
-        <v>1403.16</v>
+        <v>1131.56</v>
       </c>
       <c r="Q20" s="1">
-        <f>P20-D20</f>
-        <v>246.59</v>
-      </c>
-      <c r="R20" s="13" t="s">
+        <f>R20-P20</f>
+        <v>50.1900000000001</v>
+      </c>
+      <c r="R20" s="1">
+        <v>1181.75</v>
+      </c>
+      <c r="S20" s="1">
+        <f>R20-D20</f>
+        <v>273.81</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="U20" s="1">
+        <v>376.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S20" s="1">
-        <v>342.27</v>
-      </c>
-      <c r="T20" s="14">
-        <f>2.834/(P20/S20)</f>
-        <v>0.691291926793808</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
-        <v>927.15</v>
+        <v>950.09</v>
       </c>
       <c r="E21" s="1">
         <f>F21-D21</f>
-        <v>17.9300000000001</v>
+        <v>42.4</v>
       </c>
       <c r="F21" s="1">
-        <v>945.08</v>
+        <v>992.49</v>
       </c>
       <c r="G21" s="1">
         <f>H21-F21</f>
-        <v>24.04</v>
+        <v>38.5899999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>969.12</v>
+        <v>1031.08</v>
       </c>
       <c r="I21" s="1">
         <f>J21-H21</f>
-        <v>26.96</v>
+        <v>22.6000000000001</v>
       </c>
       <c r="J21" s="1">
-        <v>996.08</v>
+        <v>1053.68</v>
       </c>
       <c r="K21" s="1">
         <f>L21-J21</f>
-        <v>23.3499999999999</v>
+        <v>10.9299999999998</v>
       </c>
       <c r="L21" s="1">
-        <v>1019.43</v>
+        <v>1064.61</v>
       </c>
       <c r="M21" s="1">
         <f>N21-L21</f>
-        <v>23.7400000000001</v>
+        <v>16.1800000000001</v>
       </c>
       <c r="N21" s="1">
-        <v>1043.17</v>
+        <v>1080.79</v>
       </c>
       <c r="O21" s="1">
         <f>P21-N21</f>
-        <v>24.99</v>
+        <v>13.6700000000001</v>
       </c>
       <c r="P21" s="1">
-        <v>1068.16</v>
+        <v>1094.46</v>
       </c>
       <c r="Q21" s="1">
-        <f>P21-D21</f>
-        <v>141.01</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>46</v>
+        <f>R21-P21</f>
+        <v>56.26</v>
+      </c>
+      <c r="R21" s="1">
+        <v>1150.72</v>
       </c>
       <c r="S21" s="1">
-        <v>312.62</v>
-      </c>
-      <c r="T21" s="14">
-        <f>2.834/(P21/S21)</f>
-        <v>0.829431059017376</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <f>R21-D21</f>
+        <v>200.63</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="U21" s="1">
+        <v>459.72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D22" s="1">
-        <v>1317.56</v>
+        <v>927.15</v>
       </c>
       <c r="E22" s="1">
         <f>F22-D22</f>
-        <v>15.77</v>
+        <v>17.9300000000001</v>
       </c>
       <c r="F22" s="1">
-        <v>1333.33</v>
+        <v>945.08</v>
       </c>
       <c r="G22" s="1">
         <f>H22-F22</f>
-        <v>15.1700000000001</v>
+        <v>24.04</v>
       </c>
       <c r="H22" s="1">
-        <v>1348.5</v>
+        <v>969.12</v>
       </c>
       <c r="I22" s="1">
         <f>J22-H22</f>
-        <v>28.9300000000001</v>
+        <v>26.96</v>
       </c>
       <c r="J22" s="1">
-        <v>1377.43</v>
+        <v>996.08</v>
       </c>
       <c r="K22" s="1">
         <f>L22-J22</f>
-        <v>9.14999999999986</v>
+        <v>23.3499999999999</v>
       </c>
       <c r="L22" s="1">
-        <v>1386.58</v>
+        <v>1019.43</v>
       </c>
       <c r="M22" s="1">
         <f>N22-L22</f>
-        <v>29.4100000000001</v>
+        <v>23.7400000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>1415.99</v>
+        <v>1043.17</v>
       </c>
       <c r="O22" s="1">
         <f>P22-N22</f>
-        <v>8.81999999999994</v>
+        <v>24.99</v>
       </c>
       <c r="P22" s="1">
-        <v>1424.81</v>
+        <v>1068.16</v>
       </c>
       <c r="Q22" s="1">
-        <f>P22-D22</f>
-        <v>107.25</v>
-      </c>
-      <c r="R22" s="13" t="s">
+        <f>R22-P22</f>
+        <v>25.3499999999999</v>
+      </c>
+      <c r="R22" s="1">
+        <v>1093.51</v>
+      </c>
+      <c r="S22" s="1">
+        <f>R22-D22</f>
+        <v>166.36</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="U22" s="1">
+        <v>320.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="S22" s="1">
-        <v>271.82</v>
-      </c>
-      <c r="T22" s="14">
-        <f>2.834/(P22/S22)</f>
-        <v>0.540660073974776</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1">
-        <v>1060.77</v>
+        <v>848.93</v>
       </c>
       <c r="E23" s="1">
         <f>F23-D23</f>
-        <v>63.24</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F23" s="1">
-        <v>1124.01</v>
+        <v>883.49</v>
       </c>
       <c r="G23" s="1">
         <f>H23-F23</f>
-        <v>19.6700000000001</v>
+        <v>46.08</v>
       </c>
       <c r="H23" s="1">
-        <v>1143.68</v>
+        <v>929.57</v>
       </c>
       <c r="I23" s="1">
         <f>J23-H23</f>
-        <v>47.76</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J23" s="1">
-        <v>1191.44</v>
+        <v>957.31</v>
       </c>
       <c r="K23" s="1">
         <f>L23-J23</f>
-        <v>40.22</v>
+        <v>47.36</v>
       </c>
       <c r="L23" s="1">
-        <v>1231.66</v>
+        <v>1004.67</v>
       </c>
       <c r="M23" s="1">
         <f>N23-L23</f>
-        <v>44.8</v>
+        <v>25.9399999999999</v>
       </c>
       <c r="N23" s="1">
-        <v>1276.46</v>
+        <v>1030.61</v>
       </c>
       <c r="O23" s="1">
         <f>P23-N23</f>
-        <v>28.03</v>
+        <v>37.71</v>
       </c>
       <c r="P23" s="1">
-        <v>1304.49</v>
+        <v>1068.32</v>
       </c>
       <c r="Q23" s="1">
-        <f>P23-D23</f>
-        <v>243.72</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>51</v>
+        <f>R23-P23</f>
+        <v>18.3800000000001</v>
+      </c>
+      <c r="R23" s="1">
+        <v>1086.7</v>
       </c>
       <c r="S23" s="1">
-        <v>257.82</v>
-      </c>
-      <c r="T23" s="14">
-        <f>2.834/(P23/S23)</f>
-        <v>0.560113055676931</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <f>R23-D23</f>
+        <v>237.77</v>
+      </c>
+      <c r="T23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U23" s="1">
+        <v>370.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D24" s="5">
-        <v>407.35</v>
+        <v>552.79</v>
       </c>
       <c r="E24" s="5">
         <f>F24-D24</f>
-        <v>13.86</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F24" s="5">
-        <v>421.21</v>
+        <v>568.73</v>
       </c>
       <c r="G24" s="5">
         <f>H24-F24</f>
-        <v>16.43</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H24" s="5">
-        <v>437.64</v>
+        <v>570.34</v>
       </c>
       <c r="I24" s="5">
         <f>J24-H24</f>
-        <v>13.64</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J24" s="5">
-        <v>451.28</v>
+        <v>577.48</v>
       </c>
       <c r="K24" s="5">
         <f>L24-J24</f>
-        <v>11.6</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L24" s="5">
-        <v>462.88</v>
+        <v>580.37</v>
       </c>
       <c r="M24" s="5">
         <f>N24-L24</f>
-        <v>47.68</v>
+        <v>2.55999999999995</v>
       </c>
       <c r="N24" s="5">
-        <v>510.56</v>
+        <v>582.93</v>
       </c>
       <c r="O24" s="5">
         <f>P24-N24</f>
-        <v>20.51</v>
+        <v>24.99</v>
       </c>
       <c r="P24" s="5">
-        <v>531.07</v>
+        <v>607.92</v>
       </c>
       <c r="Q24" s="5">
-        <f>P24-D24</f>
-        <v>123.72</v>
-      </c>
-      <c r="R24" s="15" t="s">
-        <v>65</v>
+        <f>R24-P24</f>
+        <v>0.330000000000041</v>
+      </c>
+      <c r="R24" s="5">
+        <v>608.25</v>
       </c>
       <c r="S24" s="5">
-        <v>230.81</v>
-      </c>
-      <c r="T24" s="16">
-        <f>2.834/(P24/S24)</f>
-        <v>1.2316936373736</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <f>R24-D24</f>
+        <v>55.46</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U24" s="5">
+        <v>131.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D25" s="5">
-        <v>552.79</v>
+        <v>407.35</v>
       </c>
       <c r="E25" s="5">
         <f>F25-D25</f>
-        <v>15.9400000000001</v>
+        <v>13.86</v>
       </c>
       <c r="F25" s="5">
-        <v>568.73</v>
+        <v>421.21</v>
       </c>
       <c r="G25" s="5">
         <f>H25-F25</f>
-        <v>1.61000000000001</v>
+        <v>16.43</v>
       </c>
       <c r="H25" s="5">
-        <v>570.34</v>
+        <v>437.64</v>
       </c>
       <c r="I25" s="5">
         <f>J25-H25</f>
-        <v>7.13999999999999</v>
+        <v>13.64</v>
       </c>
       <c r="J25" s="5">
-        <v>577.48</v>
+        <v>451.28</v>
       </c>
       <c r="K25" s="5">
         <f>L25-J25</f>
-        <v>2.88999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="L25" s="5">
-        <v>580.37</v>
+        <v>462.88</v>
       </c>
       <c r="M25" s="5">
         <f>N25-L25</f>
-        <v>2.55999999999995</v>
+        <v>47.68</v>
       </c>
       <c r="N25" s="5">
-        <v>582.93</v>
+        <v>510.56</v>
       </c>
       <c r="O25" s="5">
         <f>P25-N25</f>
-        <v>24.99</v>
+        <v>20.51</v>
       </c>
       <c r="P25" s="5">
-        <v>607.92</v>
+        <v>531.07</v>
       </c>
       <c r="Q25" s="5">
-        <f>P25-D25</f>
-        <v>55.13</v>
-      </c>
-      <c r="R25" s="15" t="s">
-        <v>46</v>
+        <f>R25-P25</f>
+        <v>18.6099999999999</v>
+      </c>
+      <c r="R25" s="5">
+        <v>549.68</v>
       </c>
       <c r="S25" s="5">
-        <v>135.65</v>
-      </c>
-      <c r="T25" s="16">
-        <f>2.834/(P25/S25)</f>
-        <v>0.632372845111199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <f>R25-D25</f>
+        <v>142.33</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="U25" s="5">
+        <v>233.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="D26" s="5">
         <v>363.88</v>
@@ -3125,170 +3182,177 @@
         <v>437.78</v>
       </c>
       <c r="Q26" s="5">
-        <f>P26-D26</f>
-        <v>73.9</v>
-      </c>
-      <c r="R26" s="15" t="s">
-        <v>46</v>
+        <f>R26-P26</f>
+        <v>53.01</v>
+      </c>
+      <c r="R26" s="5">
+        <v>490.79</v>
       </c>
       <c r="S26" s="5">
-        <v>115.25</v>
-      </c>
-      <c r="T26" s="16">
-        <f>2.834/(P26/S26)</f>
-        <v>0.746079080816849</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <f>R26-D26</f>
+        <v>126.91</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U26" s="5">
+        <v>139.89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5">
-        <v>262.39</v>
+        <v>305.29</v>
       </c>
       <c r="E27" s="5">
         <f>F27-D27</f>
-        <v>11.5</v>
+        <v>17.97</v>
       </c>
       <c r="F27" s="5">
-        <v>273.89</v>
+        <v>323.26</v>
       </c>
       <c r="G27" s="5">
         <f>H27-F27</f>
-        <v>13.97</v>
+        <v>10.82</v>
       </c>
       <c r="H27" s="5">
-        <v>287.86</v>
+        <v>334.08</v>
       </c>
       <c r="I27" s="5">
         <f>J27-H27</f>
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="J27" s="5">
-        <v>304.1</v>
+        <v>350.28</v>
       </c>
       <c r="K27" s="5">
         <f>L27-J27</f>
-        <v>12.65</v>
+        <v>10.8</v>
       </c>
       <c r="L27" s="5">
-        <v>316.75</v>
+        <v>361.08</v>
       </c>
       <c r="M27" s="5">
         <f>N27-L27</f>
-        <v>9.99000000000001</v>
+        <v>9.98000000000002</v>
       </c>
       <c r="N27" s="5">
-        <v>326.74</v>
+        <v>371.06</v>
       </c>
       <c r="O27" s="5">
         <f>P27-N27</f>
-        <v>6.31999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="P27" s="5">
-        <v>333.06</v>
+        <v>381.23</v>
       </c>
       <c r="Q27" s="5">
-        <f>P27-D27</f>
-        <v>70.67</v>
-      </c>
-      <c r="R27" s="15" t="s">
-        <v>37</v>
+        <f>R27-P27</f>
+        <v>20.97</v>
+      </c>
+      <c r="R27" s="5">
+        <v>402.2</v>
       </c>
       <c r="S27" s="5">
-        <v>111.04</v>
-      </c>
-      <c r="T27" s="16">
-        <f>2.834/(P27/S27)</f>
-        <v>0.944836846213895</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <f>R27-D27</f>
+        <v>96.91</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U27" s="5">
+        <v>111.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="5" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="5">
-        <v>305.29</v>
+        <v>262.39</v>
       </c>
       <c r="E28" s="5">
         <f>F28-D28</f>
-        <v>17.97</v>
+        <v>11.5</v>
       </c>
       <c r="F28" s="5">
-        <v>323.26</v>
+        <v>273.89</v>
       </c>
       <c r="G28" s="5">
         <f>H28-F28</f>
-        <v>10.82</v>
+        <v>13.97</v>
       </c>
       <c r="H28" s="5">
-        <v>334.08</v>
+        <v>287.86</v>
       </c>
       <c r="I28" s="5">
         <f>J28-H28</f>
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="J28" s="5">
-        <v>350.28</v>
+        <v>304.1</v>
       </c>
       <c r="K28" s="5">
         <f>L28-J28</f>
-        <v>10.8</v>
+        <v>12.65</v>
       </c>
       <c r="L28" s="5">
-        <v>361.08</v>
+        <v>316.75</v>
       </c>
       <c r="M28" s="5">
         <f>N28-L28</f>
-        <v>9.98000000000002</v>
+        <v>9.99000000000001</v>
       </c>
       <c r="N28" s="5">
-        <v>371.06</v>
+        <v>326.74</v>
       </c>
       <c r="O28" s="5">
         <f>P28-N28</f>
-        <v>10.17</v>
+        <v>6.31999999999999</v>
       </c>
       <c r="P28" s="5">
-        <v>381.23</v>
+        <v>333.06</v>
       </c>
       <c r="Q28" s="5">
-        <f>P28-D28</f>
-        <v>75.94</v>
-      </c>
-      <c r="R28" s="15" t="s">
-        <v>46</v>
+        <f>R28-P28</f>
+        <v>21.13</v>
+      </c>
+      <c r="R28" s="5">
+        <v>354.19</v>
       </c>
       <c r="S28" s="5">
-        <v>92.77</v>
-      </c>
-      <c r="T28" s="16">
-        <f>2.834/(P28/S28)</f>
-        <v>0.689636649791464</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <f>R28-D28</f>
+        <v>91.8</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" s="5">
+        <v>127.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
         <v>71</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -3306,32 +3370,33 @@
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3348,29 +3413,31 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3378,32 +3445,31 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" t="s">
         <v>82</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" t="s">
         <v>84</v>
       </c>
-      <c r="B40" t="s">
-        <v>85</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:T28">
-    <sortCondition ref="S2" descending="1"/>
+  <sortState ref="A2:U28">
+    <sortCondition ref="R2" descending="1"/>
   </sortState>
-  <mergeCells count="2">
-    <mergeCell ref="C31:T31"/>
-    <mergeCell ref="C34:R34"/>
+  <mergeCells count="1">
+    <mergeCell ref="C34:T34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3415,7 +3481,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3427,7 +3493,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
   <si>
     <t>区服</t>
   </si>
@@ -70,6 +70,9 @@
     <t>战力（2025.5.14）</t>
   </si>
   <si>
+    <t>战力（2025.5.21）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -85,6 +88,12 @@
     <t>肝值（小时）</t>
   </si>
   <si>
+    <t>抽卡数</t>
+  </si>
+  <si>
+    <t>星值</t>
+  </si>
+  <si>
     <t>148区</t>
   </si>
   <si>
@@ -97,15 +106,69 @@
     <t>眼镜妹（跳费）</t>
   </si>
   <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
     <t>请叫我阿奎</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
     <t>丽娅（人海）</t>
   </si>
   <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
     <t>149区</t>
   </si>
   <si>
@@ -115,34 +178,67 @@
     <t>瓦斯兰（快攻）</t>
   </si>
   <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
     <t>玩玩</t>
   </si>
   <si>
-    <t>大氪</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
   </si>
   <si>
     <t>白夜</t>
@@ -151,108 +247,15 @@
     <t>零氪</t>
   </si>
   <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>146区</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>圣母（杂糅）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>迅（养神）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>梅（杂糅）</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
-  </si>
-  <si>
     <t>秋雨</t>
   </si>
   <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
     <t>桂林碧桂园</t>
   </si>
   <si>
     <t>何斌</t>
   </si>
   <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
     <t>氪度表：</t>
   </si>
   <si>
@@ -262,7 +265,7 @@
     <t>0-99</t>
   </si>
   <si>
-    <t>肝值：每日游戏时长，(单位：小时)具体表现：竞技场+天梯+科研+群聊天+异界平均+每日游戏时间+世界赛平均+每天挂机看卡发呆</t>
+    <t>星值：星空总战力除以抽卡数作为参考基值的比值（164.158）（值越大代表潜力越大或者神器越强）</t>
   </si>
   <si>
     <t>100-999</t>
@@ -302,13 +305,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +337,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -809,137 +820,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -955,41 +966,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1307,35 +1333,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AA40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.65" customWidth="1"/>
-    <col min="4" max="4" width="13.2583333333333" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="13.5818181818182" customWidth="1"/>
+    <col min="3" max="3" width="10.6454545454545" customWidth="1"/>
+    <col min="4" max="4" width="13.2545454545455" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7583333333333" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7545454545455" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7583333333333" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6333333333333" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.275" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="0.258333333333333" customWidth="1"/>
-    <col min="14" max="14" width="17.4583333333333" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.3583333333333" customWidth="1"/>
-    <col min="17" max="17" width="16.9916666666667" customWidth="1"/>
-    <col min="18" max="18" width="17.8666666666667" customWidth="1"/>
-    <col min="19" max="19" width="18.0166666666667" customWidth="1"/>
-    <col min="20" max="20" width="18.8916666666667" customWidth="1"/>
-    <col min="21" max="21" width="14.5416666666667" customWidth="1"/>
-    <col min="22" max="22" width="11.625" customWidth="1"/>
-    <col min="23" max="23" width="12.6083333333333" customWidth="1"/>
+    <col min="8" max="8" width="16.6272727272727" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7545454545455" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1272727272727" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6363636363636" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.2727272727273" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0.254545454545455" customWidth="1"/>
+    <col min="14" max="14" width="17.4545454545455" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1272727272727" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3545454545455" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="16.9909090909091" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="17.8636363636364" customWidth="1"/>
+    <col min="19" max="21" width="18.0181818181818" customWidth="1"/>
+    <col min="22" max="22" width="18.8909090909091" customWidth="1"/>
+    <col min="23" max="23" width="14.5454545454545" customWidth="1"/>
+    <col min="24" max="24" width="11.6272727272727" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="12.6090909090909" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="15.0181818181818" customWidth="1"/>
+    <col min="27" max="27" width="19.5181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1391,30 +1419,42 @@
         <v>11</v>
       </c>
       <c r="S1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" t="s">
         <v>12</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
+      <c r="Y1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:23">
+    <row r="2" s="1" customFormat="1" spans="1:27">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2">
         <v>2714.1</v>
@@ -1469,900 +1509,1068 @@
         <v>3384.29</v>
       </c>
       <c r="S2" s="2">
-        <f>R2-D2</f>
-        <v>670.19</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>20</v>
+        <f>T2-R2</f>
+        <v>102.46</v>
+      </c>
+      <c r="T2" s="2">
+        <v>3486.75</v>
       </c>
       <c r="U2" s="2">
-        <v>640.72</v>
-      </c>
-      <c r="V2" s="9">
+        <f>T2-D2</f>
+        <v>772.65</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="2">
+        <v>746.62</v>
+      </c>
+      <c r="X2" s="2">
         <v>500</v>
       </c>
-      <c r="W2" s="9">
+      <c r="Y2" s="2">
         <v>8.6</v>
       </c>
+      <c r="Z2" s="12">
+        <v>191519</v>
+      </c>
+      <c r="AA2" s="13">
+        <f>T2*10000/Z2/164.158</f>
+        <v>1.10903918696675</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:27">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1">
-        <v>1350.52</v>
+        <v>1425.22</v>
       </c>
       <c r="E3" s="1">
         <f>F3-D3</f>
-        <v>52.6800000000001</v>
+        <v>64.8599999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>1403.2</v>
+        <v>1490.08</v>
       </c>
       <c r="G3" s="1">
         <f>H3-F3</f>
-        <v>55.3199999999999</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1">
-        <v>1458.52</v>
+        <v>1536.08</v>
       </c>
       <c r="I3" s="1">
         <f>J3-H3</f>
-        <v>32.6800000000001</v>
+        <v>50.8500000000001</v>
       </c>
       <c r="J3" s="1">
-        <v>1491.2</v>
+        <v>1586.93</v>
       </c>
       <c r="K3" s="1">
         <f>L3-J3</f>
-        <v>54.96</v>
+        <v>86.5599999999999</v>
       </c>
       <c r="L3" s="1">
-        <v>1546.16</v>
+        <v>1673.49</v>
       </c>
       <c r="M3" s="1">
         <f>N3-L3</f>
-        <v>92.1299999999999</v>
+        <v>38.5599999999999</v>
       </c>
       <c r="N3" s="1">
-        <v>1638.29</v>
+        <v>1712.05</v>
       </c>
       <c r="O3" s="1">
         <f>P3-N3</f>
-        <v>59.4400000000001</v>
+        <v>57.0900000000001</v>
       </c>
       <c r="P3" s="1">
-        <v>1697.73</v>
+        <v>1769.14</v>
       </c>
       <c r="Q3" s="1">
         <f>R3-P3</f>
-        <v>71.3399999999999</v>
+        <v>50.8699999999999</v>
       </c>
       <c r="R3" s="1">
-        <v>1769.07</v>
+        <v>1820.01</v>
       </c>
       <c r="S3" s="1">
-        <f>R3-D3</f>
-        <v>418.55</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>23</v>
+        <f>T3-R3</f>
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T3" s="1">
+        <v>1914.44</v>
       </c>
       <c r="U3" s="1">
-        <v>553.92</v>
-      </c>
-      <c r="V3" s="11">
-        <v>65</v>
-      </c>
-      <c r="W3" s="11">
-        <v>1.4</v>
+        <f>T3-D3</f>
+        <v>489.22</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1">
+        <v>463.4</v>
+      </c>
+      <c r="X3" s="1">
+        <v>20</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>106867</v>
+      </c>
+      <c r="AA3" s="15">
+        <f>T3*10000/Z3/164.158</f>
+        <v>1.09127973276278</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:27">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2533.85</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1349.35</v>
+      </c>
+      <c r="E4" s="1">
         <f>F4-D4</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2583.9</v>
-      </c>
-      <c r="G4" s="2">
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1398.97</v>
+      </c>
+      <c r="G4" s="1">
         <f>H4-F4</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2669.66</v>
-      </c>
-      <c r="I4" s="2">
+        <v>27.79</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1426.76</v>
+      </c>
+      <c r="I4" s="1">
         <f>J4-H4</f>
-        <v>81.79</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2751.45</v>
-      </c>
-      <c r="K4" s="2">
+        <v>29.02</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1455.78</v>
+      </c>
+      <c r="K4" s="1">
         <f>L4-J4</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L4" s="2">
-        <v>2834.62</v>
-      </c>
-      <c r="M4" s="2">
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1553.66</v>
+      </c>
+      <c r="M4" s="1">
         <f>N4-L4</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N4" s="2">
-        <v>2891.61</v>
-      </c>
-      <c r="O4" s="2">
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1596.02</v>
+      </c>
+      <c r="O4" s="1">
         <f>P4-N4</f>
-        <v>103.98</v>
-      </c>
-      <c r="P4" s="2">
-        <v>2995.59</v>
-      </c>
-      <c r="Q4" s="2">
+        <v>54.22</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1650.24</v>
+      </c>
+      <c r="Q4" s="1">
         <f>R4-P4</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R4" s="2">
-        <v>3064.44</v>
-      </c>
-      <c r="S4" s="2">
-        <f>R4-D4</f>
-        <v>530.59</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="2">
-        <v>607.87</v>
-      </c>
-      <c r="V4" s="9">
-        <v>200</v>
-      </c>
-      <c r="W4" s="9">
-        <v>1.6</v>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1685.83</v>
+      </c>
+      <c r="S4" s="1">
+        <f>T4-R4</f>
+        <v>68.1300000000001</v>
+      </c>
+      <c r="T4" s="1">
+        <v>1753.96</v>
+      </c>
+      <c r="U4" s="1">
+        <f>T4-D4</f>
+        <v>404.61</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" s="1">
+        <v>439.9</v>
+      </c>
+      <c r="X4" s="1">
+        <v>20</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="Z4" s="14">
+        <v>109106</v>
+      </c>
+      <c r="AA4" s="15">
+        <f>T4*10000/Z4/164.158</f>
+        <v>0.979284765626509</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1576.18</v>
-      </c>
-      <c r="E5" s="1">
+    <row r="5" spans="1:27">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1726.42</v>
+      </c>
+      <c r="E5" s="3">
         <f>F5-D5</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1615.02</v>
-      </c>
-      <c r="G5" s="1">
+        <v>56.28</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1782.7</v>
+      </c>
+      <c r="G5" s="3">
         <f>H5-F5</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1650.62</v>
-      </c>
-      <c r="I5" s="1">
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1853.62</v>
+      </c>
+      <c r="I5" s="3">
         <f>J5-H5</f>
-        <v>37.47</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1688.09</v>
-      </c>
-      <c r="K5" s="1">
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1903.2</v>
+      </c>
+      <c r="K5" s="3">
         <f>L5-J5</f>
-        <v>21.49</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1709.58</v>
-      </c>
-      <c r="M5" s="1">
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1943.61</v>
+      </c>
+      <c r="M5" s="3">
         <f>N5-L5</f>
-        <v>24.53</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1734.11</v>
-      </c>
-      <c r="O5" s="1">
+        <v>30.01</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1973.62</v>
+      </c>
+      <c r="O5" s="3">
         <f>P5-N5</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1753.64</v>
-      </c>
-      <c r="Q5" s="1">
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P5" s="3">
+        <v>2056.9</v>
+      </c>
+      <c r="Q5" s="3">
         <f>R5-P5</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R5" s="1">
-        <v>1818.75</v>
-      </c>
-      <c r="S5" s="1">
-        <f>R5-D5</f>
-        <v>242.57</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" s="1">
-        <v>365.57</v>
-      </c>
-      <c r="V5" s="11">
-        <v>0</v>
-      </c>
-      <c r="W5" s="11">
-        <v>0</v>
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2082.54</v>
+      </c>
+      <c r="S5" s="3">
+        <f>T5-R5</f>
+        <v>66.46</v>
+      </c>
+      <c r="T5" s="3">
+        <v>2149</v>
+      </c>
+      <c r="U5" s="3">
+        <f>T5-D5</f>
+        <v>422.58</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" s="3">
+        <v>493.22</v>
+      </c>
+      <c r="X5" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" s="16">
+        <v>124763</v>
+      </c>
+      <c r="AA5" s="17">
+        <f>T5*10000/Z5/164.158</f>
+        <v>1.0492731363367</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:27">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3">
-        <v>2136.24</v>
+        <v>2183.01</v>
       </c>
       <c r="E6" s="3">
         <f>F6-D6</f>
-        <v>40.8200000000002</v>
+        <v>24.1199999999999</v>
       </c>
       <c r="F6" s="3">
-        <v>2177.06</v>
+        <v>2207.13</v>
       </c>
       <c r="G6" s="3">
         <f>H6-F6</f>
-        <v>62.5999999999999</v>
+        <v>22.8599999999997</v>
       </c>
       <c r="H6" s="3">
-        <v>2239.66</v>
+        <v>2229.99</v>
       </c>
       <c r="I6" s="3">
         <f>J6-H6</f>
-        <v>47.0700000000002</v>
+        <v>11.7800000000002</v>
       </c>
       <c r="J6" s="3">
-        <v>2286.73</v>
+        <v>2241.77</v>
       </c>
       <c r="K6" s="3">
         <f>L6-J6</f>
-        <v>25.52</v>
+        <v>13.0100000000002</v>
       </c>
       <c r="L6" s="3">
-        <v>2312.25</v>
+        <v>2254.78</v>
       </c>
       <c r="M6" s="3">
         <f>N6-L6</f>
-        <v>36.7800000000002</v>
+        <v>62.6399999999999</v>
       </c>
       <c r="N6" s="3">
-        <v>2349.03</v>
+        <v>2317.42</v>
       </c>
       <c r="O6" s="3">
         <f>P6-N6</f>
-        <v>-18.02</v>
+        <v>16.27</v>
       </c>
       <c r="P6" s="3">
-        <v>2331.01</v>
+        <v>2333.69</v>
       </c>
       <c r="Q6" s="3">
         <f>R6-P6</f>
-        <v>62.7599999999998</v>
+        <v>36.5</v>
       </c>
       <c r="R6" s="3">
-        <v>2393.77</v>
+        <v>2370.19</v>
       </c>
       <c r="S6" s="3">
-        <f>R6-D6</f>
-        <v>257.53</v>
-      </c>
-      <c r="T6" s="12" t="s">
-        <v>32</v>
+        <f>T6-R6</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T6" s="3">
+        <v>2435.38</v>
       </c>
       <c r="U6" s="3">
-        <v>708.07</v>
-      </c>
-      <c r="V6" s="13">
+        <f>T6-D6</f>
+        <v>252.37</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="W6" s="3">
+        <v>596.97</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="16">
+        <v>133781</v>
+      </c>
+      <c r="AA6" s="17">
+        <f>T6*10000/Z6/164.158</f>
+        <v>1.10894560728839</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W6" s="13">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1">
-        <v>950.09</v>
+        <v>1350.52</v>
       </c>
       <c r="E7" s="1">
         <f>F7-D7</f>
-        <v>42.4</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>992.49</v>
+        <v>1403.2</v>
       </c>
       <c r="G7" s="1">
         <f>H7-F7</f>
-        <v>38.5899999999999</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>1031.08</v>
+        <v>1458.52</v>
       </c>
       <c r="I7" s="1">
         <f>J7-H7</f>
-        <v>22.6000000000001</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J7" s="1">
-        <v>1053.68</v>
+        <v>1491.2</v>
       </c>
       <c r="K7" s="1">
         <f>L7-J7</f>
-        <v>10.9299999999998</v>
+        <v>54.96</v>
       </c>
       <c r="L7" s="1">
-        <v>1064.61</v>
+        <v>1546.16</v>
       </c>
       <c r="M7" s="1">
         <f>N7-L7</f>
-        <v>16.1800000000001</v>
+        <v>92.1299999999999</v>
       </c>
       <c r="N7" s="1">
-        <v>1080.79</v>
+        <v>1638.29</v>
       </c>
       <c r="O7" s="1">
         <f>P7-N7</f>
-        <v>13.6700000000001</v>
+        <v>59.4400000000001</v>
       </c>
       <c r="P7" s="1">
-        <v>1094.46</v>
+        <v>1697.73</v>
       </c>
       <c r="Q7" s="1">
         <f>R7-P7</f>
-        <v>56.26</v>
+        <v>71.3399999999999</v>
       </c>
       <c r="R7" s="1">
-        <v>1150.72</v>
+        <v>1769.07</v>
       </c>
       <c r="S7" s="1">
-        <f>R7-D7</f>
-        <v>200.63</v>
-      </c>
-      <c r="T7" s="10" t="s">
+        <f>T7-R7</f>
+        <v>62.9000000000001</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1831.97</v>
+      </c>
+      <c r="U7" s="1">
+        <f>T7-D7</f>
+        <v>481.45</v>
+      </c>
+      <c r="V7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="U7" s="1">
-        <v>459.72</v>
-      </c>
-      <c r="V7" s="11">
-        <v>10</v>
-      </c>
-      <c r="W7" s="11">
+      <c r="W7" s="1">
+        <v>576.12</v>
+      </c>
+      <c r="X7" s="1">
+        <v>65</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>127603</v>
+      </c>
+      <c r="AA7" s="15">
+        <f>T7*10000/Z7/164.158</f>
+        <v>0.8745717003899</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1754.54</v>
+      </c>
+      <c r="E8" s="3">
+        <f>F8-D8</f>
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1807.91</v>
+      </c>
+      <c r="G8" s="3">
+        <f>H8-F8</f>
+        <v>90.24</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1898.15</v>
+      </c>
+      <c r="I8" s="3">
+        <f>J8-H8</f>
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1988.53</v>
+      </c>
+      <c r="K8" s="3">
+        <f>L8-J8</f>
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2048.24</v>
+      </c>
+      <c r="M8" s="3">
+        <f>N8-L8</f>
+        <v>153.99</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2202.23</v>
+      </c>
+      <c r="O8" s="3">
+        <f>P8-N8</f>
+        <v>64.21</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2266.44</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>R8-P8</f>
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2314</v>
+      </c>
+      <c r="S8" s="3">
+        <f>T8-R8</f>
+        <v>59.6500000000001</v>
+      </c>
+      <c r="T8" s="3">
+        <v>2373.65</v>
+      </c>
+      <c r="U8" s="3">
+        <f>T8-D8</f>
+        <v>619.11</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="W8" s="3">
+        <v>409.56</v>
+      </c>
+      <c r="X8" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y8" s="3">
         <v>2.2</v>
       </c>
+      <c r="Z8" s="16">
+        <v>132783</v>
+      </c>
+      <c r="AA8" s="17">
+        <f>T8*10000/Z8/164.158</f>
+        <v>1.08896056516498</v>
+      </c>
     </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="4">
-        <v>363.88</v>
-      </c>
-      <c r="E8" s="4">
-        <f>F8-D8</f>
-        <v>14.21</v>
-      </c>
-      <c r="F8" s="4">
-        <v>378.09</v>
-      </c>
-      <c r="G8" s="4">
-        <f>H8-F8</f>
-        <v>11.22</v>
-      </c>
-      <c r="H8" s="4">
-        <v>389.31</v>
-      </c>
-      <c r="I8" s="4">
-        <f>J8-H8</f>
-        <v>13.62</v>
-      </c>
-      <c r="J8" s="4">
-        <v>402.93</v>
-      </c>
-      <c r="K8" s="4">
-        <f>L8-J8</f>
-        <v>11.13</v>
-      </c>
-      <c r="L8" s="4">
-        <v>414.06</v>
-      </c>
-      <c r="M8" s="4">
-        <f>N8-L8</f>
-        <v>17.39</v>
-      </c>
-      <c r="N8" s="4">
-        <v>431.45</v>
-      </c>
-      <c r="O8" s="4">
-        <f>P8-N8</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P8" s="4">
-        <v>437.78</v>
-      </c>
-      <c r="Q8" s="4">
-        <f>R8-P8</f>
-        <v>53.01</v>
-      </c>
-      <c r="R8" s="4">
-        <v>490.79</v>
-      </c>
-      <c r="S8" s="4">
-        <f>R8-D8</f>
-        <v>126.91</v>
-      </c>
-      <c r="T8" s="14" t="s">
+    <row r="9" spans="1:27">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="U8" s="4">
-        <v>139.89</v>
-      </c>
-      <c r="V8" s="15">
-        <v>0</v>
-      </c>
-      <c r="W8" s="15">
-        <v>1</v>
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1735.94</v>
+      </c>
+      <c r="E9" s="3">
+        <f>F9-D9</f>
+        <v>48.5999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1784.54</v>
+      </c>
+      <c r="G9" s="3">
+        <f>H9-F9</f>
+        <v>74.1600000000001</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1858.7</v>
+      </c>
+      <c r="I9" s="3">
+        <f>J9-H9</f>
+        <v>65.55</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1924.25</v>
+      </c>
+      <c r="K9" s="3">
+        <f>L9-J9</f>
+        <v>35.73</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1959.98</v>
+      </c>
+      <c r="M9" s="3">
+        <f>N9-L9</f>
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N9" s="3">
+        <v>2001.86</v>
+      </c>
+      <c r="O9" s="3">
+        <f>P9-N9</f>
+        <v>74.6600000000001</v>
+      </c>
+      <c r="P9" s="3">
+        <v>2076.52</v>
+      </c>
+      <c r="Q9" s="3">
+        <f>R9-P9</f>
+        <v>48.71</v>
+      </c>
+      <c r="R9" s="3">
+        <v>2125.23</v>
+      </c>
+      <c r="S9" s="3">
+        <f>T9-R9</f>
+        <v>57.4200000000001</v>
+      </c>
+      <c r="T9" s="3">
+        <v>2182.65</v>
+      </c>
+      <c r="U9" s="3">
+        <f>T9-D9</f>
+        <v>446.71</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="W9" s="3">
+        <v>515.22</v>
+      </c>
+      <c r="X9" s="3">
+        <v>80</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="Z9" s="16">
+        <v>150192</v>
+      </c>
+      <c r="AA9" s="17">
+        <f>T9*10000/Z9/164.158</f>
+        <v>0.885268980487198</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="1" t="s">
+    <row r="10" spans="1:27">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2136.24</v>
+      </c>
+      <c r="E10" s="3">
+        <f>F10-D10</f>
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2177.06</v>
+      </c>
+      <c r="G10" s="3">
+        <f>H10-F10</f>
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2239.66</v>
+      </c>
+      <c r="I10" s="3">
+        <f>J10-H10</f>
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2286.73</v>
+      </c>
+      <c r="K10" s="3">
+        <f>L10-J10</f>
+        <v>25.52</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2312.25</v>
+      </c>
+      <c r="M10" s="3">
+        <f>N10-L10</f>
+        <v>36.7800000000002</v>
+      </c>
+      <c r="N10" s="3">
+        <v>2349.03</v>
+      </c>
+      <c r="O10" s="3">
+        <f>P10-N10</f>
+        <v>-18.02</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2331.01</v>
+      </c>
+      <c r="Q10" s="3">
+        <f>R10-P10</f>
+        <v>62.7599999999998</v>
+      </c>
+      <c r="R10" s="3">
+        <v>2393.77</v>
+      </c>
+      <c r="S10" s="3">
+        <f>T10-R10</f>
+        <v>55.5599999999999</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2449.33</v>
+      </c>
+      <c r="U10" s="3">
+        <f>T10-D10</f>
+        <v>313.09</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W10" s="3">
+        <v>712.42</v>
+      </c>
+      <c r="X10" s="3">
+        <v>20</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>153852</v>
+      </c>
+      <c r="AA10" s="17">
+        <f>T10*10000/Z10/164.158</f>
+        <v>0.969799829339937</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1">
-        <v>1446.65</v>
-      </c>
-      <c r="E9" s="1">
-        <f>F9-D9</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1474.83</v>
-      </c>
-      <c r="G9" s="1">
-        <f>H9-F9</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1538.65</v>
-      </c>
-      <c r="I9" s="1">
-        <f>J9-H9</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1561.57</v>
-      </c>
-      <c r="K9" s="1">
-        <f>L9-J9</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1632.43</v>
-      </c>
-      <c r="M9" s="1">
-        <f>N9-L9</f>
-        <v>37.4099999999999</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1669.84</v>
-      </c>
-      <c r="O9" s="1">
-        <f>P9-N9</f>
-        <v>32.8300000000002</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1702.67</v>
-      </c>
-      <c r="Q9" s="1">
-        <f>R9-P9</f>
-        <v>51.9499999999998</v>
-      </c>
-      <c r="R9" s="1">
-        <v>1754.62</v>
-      </c>
-      <c r="S9" s="1">
-        <f>R9-D9</f>
-        <v>307.97</v>
-      </c>
-      <c r="T9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="U9" s="1">
-        <v>679.57</v>
-      </c>
-      <c r="V9" s="11">
-        <v>65</v>
-      </c>
-      <c r="W9" s="11">
-        <v>1.4</v>
+      <c r="D11" s="2">
+        <v>2533.85</v>
+      </c>
+      <c r="E11" s="2">
+        <f>F11-D11</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2583.9</v>
+      </c>
+      <c r="G11" s="2">
+        <f>H11-F11</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2669.66</v>
+      </c>
+      <c r="I11" s="2">
+        <f>J11-H11</f>
+        <v>81.79</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2751.45</v>
+      </c>
+      <c r="K11" s="2">
+        <f>L11-J11</f>
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2834.62</v>
+      </c>
+      <c r="M11" s="2">
+        <f>N11-L11</f>
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2891.61</v>
+      </c>
+      <c r="O11" s="2">
+        <f>P11-N11</f>
+        <v>103.98</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2995.59</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>R11-P11</f>
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R11" s="2">
+        <v>3064.44</v>
+      </c>
+      <c r="S11" s="2">
+        <f>T11-R11</f>
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T11" s="2">
+        <v>3112.05</v>
+      </c>
+      <c r="U11" s="2">
+        <f>T11-D11</f>
+        <v>578.2</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="2">
+        <v>647.97</v>
+      </c>
+      <c r="X11" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>172501</v>
+      </c>
+      <c r="AA11" s="13">
+        <f>T11*10000/Z11/164.158</f>
+        <v>1.09898786419624</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
-      <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1425.22</v>
-      </c>
-      <c r="E10" s="1">
-        <f>F10-D10</f>
-        <v>64.8599999999999</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1490.08</v>
-      </c>
-      <c r="G10" s="1">
-        <f>H10-F10</f>
-        <v>46</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1536.08</v>
-      </c>
-      <c r="I10" s="1">
-        <f>J10-H10</f>
-        <v>50.8500000000001</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1586.93</v>
-      </c>
-      <c r="K10" s="1">
-        <f>L10-J10</f>
-        <v>86.5599999999999</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1673.49</v>
-      </c>
-      <c r="M10" s="1">
-        <f>N10-L10</f>
-        <v>38.5599999999999</v>
-      </c>
-      <c r="N10" s="1">
-        <v>1712.05</v>
-      </c>
-      <c r="O10" s="1">
-        <f>P10-N10</f>
-        <v>57.0900000000001</v>
-      </c>
-      <c r="P10" s="1">
-        <v>1769.14</v>
-      </c>
-      <c r="Q10" s="1">
-        <f>R10-P10</f>
-        <v>50.8699999999999</v>
-      </c>
-      <c r="R10" s="1">
-        <v>1820.01</v>
-      </c>
-      <c r="S10" s="1">
-        <f>R10-D10</f>
-        <v>394.79</v>
-      </c>
-      <c r="T10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="U10" s="1">
-        <v>441.25</v>
-      </c>
-      <c r="V10" s="11">
-        <v>20</v>
-      </c>
-      <c r="W10" s="11">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1">
-        <v>907.94</v>
-      </c>
-      <c r="E11" s="1">
-        <f>F11-D11</f>
-        <v>64.0799999999999</v>
-      </c>
-      <c r="F11" s="1">
-        <v>972.02</v>
-      </c>
-      <c r="G11" s="1">
-        <f>H11-F11</f>
-        <v>36.26</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1008.28</v>
-      </c>
-      <c r="I11" s="1">
-        <f>J11-H11</f>
-        <v>28.8</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1037.08</v>
-      </c>
-      <c r="K11" s="1">
-        <f>L11-J11</f>
-        <v>40.1000000000001</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1077.18</v>
-      </c>
-      <c r="M11" s="1">
-        <f>N11-L11</f>
-        <v>26.03</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1103.21</v>
-      </c>
-      <c r="O11" s="1">
-        <f>P11-N11</f>
-        <v>28.3499999999999</v>
-      </c>
-      <c r="P11" s="1">
-        <v>1131.56</v>
-      </c>
-      <c r="Q11" s="1">
-        <f>R11-P11</f>
-        <v>50.1900000000001</v>
-      </c>
-      <c r="R11" s="1">
-        <v>1181.75</v>
-      </c>
-      <c r="S11" s="1">
-        <f>R11-D11</f>
-        <v>273.81</v>
-      </c>
-      <c r="T11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="U11" s="1">
-        <v>376.97</v>
-      </c>
-      <c r="V11" s="11">
-        <v>35</v>
-      </c>
-      <c r="W11" s="11">
-        <v>8.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:27">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="3">
-        <v>1735.94</v>
+        <v>1966.62</v>
       </c>
       <c r="E12" s="3">
         <f>F12-D12</f>
-        <v>48.5999999999999</v>
+        <v>49.0200000000002</v>
       </c>
       <c r="F12" s="3">
-        <v>1784.54</v>
+        <v>2015.64</v>
       </c>
       <c r="G12" s="3">
         <f>H12-F12</f>
-        <v>74.1600000000001</v>
+        <v>34.1600000000001</v>
       </c>
       <c r="H12" s="3">
-        <v>1858.7</v>
+        <v>2049.8</v>
       </c>
       <c r="I12" s="3">
         <f>J12-H12</f>
-        <v>65.55</v>
+        <v>90.0999999999999</v>
       </c>
       <c r="J12" s="3">
-        <v>1924.25</v>
+        <v>2139.9</v>
       </c>
       <c r="K12" s="3">
         <f>L12-J12</f>
-        <v>35.73</v>
+        <v>53.1700000000001</v>
       </c>
       <c r="L12" s="3">
-        <v>1959.98</v>
+        <v>2193.07</v>
       </c>
       <c r="M12" s="3">
         <f>N12-L12</f>
-        <v>41.8799999999999</v>
+        <v>63.9099999999999</v>
       </c>
       <c r="N12" s="3">
-        <v>2001.86</v>
+        <v>2256.98</v>
       </c>
       <c r="O12" s="3">
         <f>P12-N12</f>
-        <v>74.6600000000001</v>
+        <v>45.71</v>
       </c>
       <c r="P12" s="3">
-        <v>2076.52</v>
+        <v>2302.69</v>
       </c>
       <c r="Q12" s="3">
         <f>R12-P12</f>
-        <v>48.71</v>
+        <v>37.2199999999998</v>
       </c>
       <c r="R12" s="3">
-        <v>2125.23</v>
+        <v>2339.91</v>
       </c>
       <c r="S12" s="3">
-        <f>R12-D12</f>
-        <v>389.29</v>
-      </c>
-      <c r="T12" s="12" t="s">
-        <v>45</v>
+        <f>T12-R12</f>
+        <v>47.3099999999999</v>
+      </c>
+      <c r="T12" s="3">
+        <v>2387.22</v>
       </c>
       <c r="U12" s="3">
-        <v>523.92</v>
-      </c>
-      <c r="V12" s="13">
-        <v>80</v>
-      </c>
-      <c r="W12" s="13">
-        <v>7.2</v>
+        <f>T12-D12</f>
+        <v>420.6</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W12" s="3">
+        <v>837.27</v>
+      </c>
+      <c r="X12" s="3">
+        <v>65</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" s="16">
+        <v>130589</v>
+      </c>
+      <c r="AA12" s="17">
+        <f>T12*10000/Z12/164.158</f>
+        <v>1.11358608572767</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
-      <c r="A13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1754.54</v>
-      </c>
-      <c r="E13" s="3">
+    <row r="13" spans="1:27">
+      <c r="A13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1">
+        <v>927.15</v>
+      </c>
+      <c r="E13" s="1">
         <f>F13-D13</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1807.91</v>
-      </c>
-      <c r="G13" s="3">
+        <v>17.9300000000001</v>
+      </c>
+      <c r="F13" s="1">
+        <v>945.08</v>
+      </c>
+      <c r="G13" s="1">
         <f>H13-F13</f>
-        <v>90.24</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1898.15</v>
-      </c>
-      <c r="I13" s="3">
+        <v>24.04</v>
+      </c>
+      <c r="H13" s="1">
+        <v>969.12</v>
+      </c>
+      <c r="I13" s="1">
         <f>J13-H13</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1988.53</v>
-      </c>
-      <c r="K13" s="3">
+        <v>26.96</v>
+      </c>
+      <c r="J13" s="1">
+        <v>996.08</v>
+      </c>
+      <c r="K13" s="1">
         <f>L13-J13</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L13" s="3">
-        <v>2048.24</v>
-      </c>
-      <c r="M13" s="3">
+        <v>23.3499999999999</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1019.43</v>
+      </c>
+      <c r="M13" s="1">
         <f>N13-L13</f>
-        <v>153.99</v>
-      </c>
-      <c r="N13" s="3">
-        <v>2202.23</v>
-      </c>
-      <c r="O13" s="3">
+        <v>23.7400000000001</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1043.17</v>
+      </c>
+      <c r="O13" s="1">
         <f>P13-N13</f>
-        <v>64.21</v>
-      </c>
-      <c r="P13" s="3">
-        <v>2266.44</v>
-      </c>
-      <c r="Q13" s="3">
+        <v>24.99</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1068.16</v>
+      </c>
+      <c r="Q13" s="1">
         <f>R13-P13</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R13" s="3">
-        <v>2314</v>
-      </c>
-      <c r="S13" s="3">
-        <f>R13-D13</f>
-        <v>559.46</v>
-      </c>
-      <c r="T13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="U13" s="3">
-        <v>371.08</v>
-      </c>
-      <c r="V13" s="13">
-        <v>300</v>
-      </c>
-      <c r="W13" s="13">
-        <v>2.2</v>
+        <v>25.3499999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1093.51</v>
+      </c>
+      <c r="S13" s="1">
+        <f>T13-R13</f>
+        <v>46.8499999999999</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1140.36</v>
+      </c>
+      <c r="U13" s="1">
+        <f>T13-D13</f>
+        <v>213.21</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="1">
+        <v>323.37</v>
+      </c>
+      <c r="X13" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>80664</v>
+      </c>
+      <c r="AA13" s="15">
+        <f>T13*10000/Z13/164.158</f>
+        <v>0.86119236096077</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
         <v>1156.57</v>
@@ -2417,1058 +2625,1254 @@
         <v>1450.46</v>
       </c>
       <c r="S14" s="1">
-        <f>R14-D14</f>
-        <v>293.89</v>
-      </c>
-      <c r="T14" s="10" t="s">
-        <v>49</v>
+        <f>T14-R14</f>
+        <v>46.8299999999999</v>
+      </c>
+      <c r="T14" s="1">
+        <v>1497.29</v>
       </c>
       <c r="U14" s="1">
-        <v>357.57</v>
-      </c>
-      <c r="V14" s="11">
+        <f>T14-D14</f>
+        <v>340.72</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="W14" s="1">
+        <v>369.22</v>
+      </c>
+      <c r="X14" s="1">
         <v>25</v>
       </c>
-      <c r="W14" s="11">
+      <c r="Y14" s="1">
         <v>3</v>
       </c>
+      <c r="Z14" s="14">
+        <v>100457</v>
+      </c>
+      <c r="AA14" s="15">
+        <f>T14*10000/Z14/164.158</f>
+        <v>0.907953625893773</v>
+      </c>
     </row>
-    <row r="15" spans="1:23">
-      <c r="A15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="5">
+    <row r="15" spans="1:27">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="4">
         <v>4105.48</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f>F15-D15</f>
         <v>181.21</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>4286.69</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <f>H15-F15</f>
         <v>139.09</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>4425.78</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <f>J15-H15</f>
         <v>54.8800000000001</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>4480.66</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
         <f>L15-J15</f>
         <v>104.900000000001</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="4">
         <v>4585.56</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="4">
         <f>N15-L15</f>
         <v>70.29</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="4">
         <v>4655.85</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="4">
         <f>P15-N15</f>
         <v>49.1700000000001</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P15" s="4">
         <v>4705.02</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="Q15" s="4">
         <f>R15-P15</f>
         <v>38.2199999999993</v>
       </c>
-      <c r="R15" s="5">
+      <c r="R15" s="4">
         <v>4743.24</v>
       </c>
-      <c r="S15" s="5">
-        <f>R15-D15</f>
-        <v>637.76</v>
-      </c>
-      <c r="T15" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="U15" s="5">
-        <v>1352.62</v>
-      </c>
-      <c r="V15" s="5">
+      <c r="S15" s="4">
+        <f>T15-R15</f>
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T15" s="4">
+        <v>4788.86</v>
+      </c>
+      <c r="U15" s="4">
+        <f>T15-D15</f>
+        <v>683.38</v>
+      </c>
+      <c r="V15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="W15" s="4">
+        <v>1364.72</v>
+      </c>
+      <c r="X15" s="4">
         <v>400</v>
       </c>
-      <c r="W15" s="5">
+      <c r="Y15" s="4">
         <v>1.2</v>
       </c>
+      <c r="Z15" s="18">
+        <v>186759</v>
+      </c>
+      <c r="AA15" s="19">
+        <f>T15*10000/Z15/164.158</f>
+        <v>1.56202704397778</v>
+      </c>
     </row>
-    <row r="16" spans="1:23">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:27">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1060.77</v>
+      </c>
+      <c r="E16" s="1">
+        <f>F16-D16</f>
+        <v>63.24</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1124.01</v>
+      </c>
+      <c r="G16" s="1">
+        <f>H16-F16</f>
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1143.68</v>
+      </c>
+      <c r="I16" s="1">
+        <f>J16-H16</f>
+        <v>47.76</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1191.44</v>
+      </c>
+      <c r="K16" s="1">
+        <f>L16-J16</f>
+        <v>40.22</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1231.66</v>
+      </c>
+      <c r="M16" s="1">
+        <f>N16-L16</f>
+        <v>44.8</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1276.46</v>
+      </c>
+      <c r="O16" s="1">
+        <f>P16-N16</f>
+        <v>28.03</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1304.49</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>R16-P16</f>
+        <v>31.78</v>
+      </c>
+      <c r="R16" s="1">
+        <v>1336.27</v>
+      </c>
+      <c r="S16" s="1">
+        <f>T16-R16</f>
+        <v>44.9000000000001</v>
+      </c>
+      <c r="T16" s="1">
+        <v>1381.17</v>
+      </c>
+      <c r="U16" s="1">
+        <f>T16-D16</f>
+        <v>320.4</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="W16" s="1">
+        <v>275.86</v>
+      </c>
+      <c r="X16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>71153</v>
+      </c>
+      <c r="AA16" s="15">
+        <f>T16*10000/Z16/164.158</f>
+        <v>1.18247473011041</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1966.62</v>
-      </c>
-      <c r="E16" s="3">
-        <f>F16-D16</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F16" s="3">
-        <v>2015.64</v>
-      </c>
-      <c r="G16" s="3">
-        <f>H16-F16</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H16" s="3">
-        <v>2049.8</v>
-      </c>
-      <c r="I16" s="3">
-        <f>J16-H16</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J16" s="3">
-        <v>2139.9</v>
-      </c>
-      <c r="K16" s="3">
-        <f>L16-J16</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L16" s="3">
-        <v>2193.07</v>
-      </c>
-      <c r="M16" s="3">
-        <f>N16-L16</f>
-        <v>63.9099999999999</v>
-      </c>
-      <c r="N16" s="3">
-        <v>2256.98</v>
-      </c>
-      <c r="O16" s="3">
-        <f>P16-N16</f>
-        <v>45.71</v>
-      </c>
-      <c r="P16" s="3">
-        <v>2302.69</v>
-      </c>
-      <c r="Q16" s="3">
-        <f>R16-P16</f>
-        <v>37.2199999999998</v>
-      </c>
-      <c r="R16" s="3">
-        <v>2339.91</v>
-      </c>
-      <c r="S16" s="3">
-        <f>R16-D16</f>
-        <v>373.29</v>
-      </c>
-      <c r="T16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="U16" s="3">
-        <v>830.02</v>
-      </c>
-      <c r="V16" s="13">
-        <v>65</v>
-      </c>
-      <c r="W16" s="13">
-        <v>1.2</v>
+      <c r="B17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1">
+        <v>953.78</v>
+      </c>
+      <c r="E17" s="1">
+        <f>F17-D17</f>
+        <v>28.97</v>
+      </c>
+      <c r="F17" s="1">
+        <v>982.75</v>
+      </c>
+      <c r="G17" s="1">
+        <f>H17-F17</f>
+        <v>83.9300000000001</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1066.68</v>
+      </c>
+      <c r="I17" s="1">
+        <f>J17-H17</f>
+        <v>42.8399999999999</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1109.52</v>
+      </c>
+      <c r="K17" s="1">
+        <f>L17-J17</f>
+        <v>36.46</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1145.98</v>
+      </c>
+      <c r="M17" s="1">
+        <f>N17-L17</f>
+        <v>37.49</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1183.47</v>
+      </c>
+      <c r="O17" s="1">
+        <f>P17-N17</f>
+        <v>33.3699999999999</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1216.84</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>R17-P17</f>
+        <v>24.8900000000001</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1241.73</v>
+      </c>
+      <c r="S17" s="1">
+        <f>T17-R17</f>
+        <v>42.3099999999999</v>
+      </c>
+      <c r="T17" s="1">
+        <v>1284.04</v>
+      </c>
+      <c r="U17" s="1">
+        <f>T17-D17</f>
+        <v>330.26</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="1">
+        <v>455.12</v>
+      </c>
+      <c r="X17" s="1">
+        <v>30</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>105419</v>
+      </c>
+      <c r="AA17" s="15">
+        <f>T17*10000/Z17/164.158</f>
+        <v>0.741989241844566</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2183.01</v>
-      </c>
-      <c r="E17" s="3">
-        <f>F17-D17</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2207.13</v>
-      </c>
-      <c r="G17" s="3">
-        <f>H17-F17</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2229.99</v>
-      </c>
-      <c r="I17" s="3">
-        <f>J17-H17</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2241.77</v>
-      </c>
-      <c r="K17" s="3">
-        <f>L17-J17</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2254.78</v>
-      </c>
-      <c r="M17" s="3">
-        <f>N17-L17</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2317.42</v>
-      </c>
-      <c r="O17" s="3">
-        <f>P17-N17</f>
-        <v>16.27</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2333.69</v>
-      </c>
-      <c r="Q17" s="3">
-        <f>R17-P17</f>
-        <v>36.5</v>
-      </c>
-      <c r="R17" s="3">
-        <v>2370.19</v>
-      </c>
-      <c r="S17" s="3">
-        <f>R17-D17</f>
-        <v>187.18</v>
-      </c>
-      <c r="T17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="U17" s="3">
-        <v>593.07</v>
-      </c>
-      <c r="V17" s="13">
-        <v>0</v>
-      </c>
-      <c r="W17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:27">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1">
-        <v>1349.35</v>
+        <v>950.09</v>
       </c>
       <c r="E18" s="1">
         <f>F18-D18</f>
-        <v>49.6200000000001</v>
+        <v>42.4</v>
       </c>
       <c r="F18" s="1">
-        <v>1398.97</v>
+        <v>992.49</v>
       </c>
       <c r="G18" s="1">
         <f>H18-F18</f>
-        <v>27.79</v>
+        <v>38.5899999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>1426.76</v>
+        <v>1031.08</v>
       </c>
       <c r="I18" s="1">
         <f>J18-H18</f>
-        <v>29.02</v>
+        <v>22.6000000000001</v>
       </c>
       <c r="J18" s="1">
-        <v>1455.78</v>
+        <v>1053.68</v>
       </c>
       <c r="K18" s="1">
         <f>L18-J18</f>
-        <v>97.8800000000001</v>
+        <v>10.9299999999998</v>
       </c>
       <c r="L18" s="1">
-        <v>1553.66</v>
+        <v>1064.61</v>
       </c>
       <c r="M18" s="1">
         <f>N18-L18</f>
-        <v>42.3599999999999</v>
+        <v>16.1800000000001</v>
       </c>
       <c r="N18" s="1">
-        <v>1596.02</v>
+        <v>1080.79</v>
       </c>
       <c r="O18" s="1">
         <f>P18-N18</f>
-        <v>54.22</v>
+        <v>13.6700000000001</v>
       </c>
       <c r="P18" s="1">
-        <v>1650.24</v>
+        <v>1094.46</v>
       </c>
       <c r="Q18" s="1">
         <f>R18-P18</f>
-        <v>35.5899999999999</v>
+        <v>56.26</v>
       </c>
       <c r="R18" s="1">
-        <v>1685.83</v>
+        <v>1150.72</v>
       </c>
       <c r="S18" s="1">
-        <f>R18-D18</f>
-        <v>336.48</v>
-      </c>
-      <c r="T18" s="10" t="s">
+        <f>T18-R18</f>
+        <v>41.27</v>
+      </c>
+      <c r="T18" s="1">
+        <v>1191.99</v>
+      </c>
+      <c r="U18" s="1">
+        <f>T18-D18</f>
+        <v>241.9</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="W18" s="1">
+        <v>457.32</v>
+      </c>
+      <c r="X18" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>86194</v>
+      </c>
+      <c r="AA18" s="15">
+        <f>T18*10000/Z18/164.158</f>
+        <v>0.842429418076795</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U18" s="1">
-        <v>420</v>
-      </c>
-      <c r="V18" s="11">
-        <v>20</v>
-      </c>
-      <c r="W18" s="11">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="D19" s="1">
-        <v>1060.77</v>
+        <v>1446.65</v>
       </c>
       <c r="E19" s="1">
         <f>F19-D19</f>
-        <v>63.24</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F19" s="1">
-        <v>1124.01</v>
+        <v>1474.83</v>
       </c>
       <c r="G19" s="1">
         <f>H19-F19</f>
-        <v>19.6700000000001</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H19" s="1">
-        <v>1143.68</v>
+        <v>1538.65</v>
       </c>
       <c r="I19" s="1">
         <f>J19-H19</f>
-        <v>47.76</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J19" s="1">
-        <v>1191.44</v>
+        <v>1561.57</v>
       </c>
       <c r="K19" s="1">
         <f>L19-J19</f>
-        <v>40.22</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L19" s="1">
-        <v>1231.66</v>
+        <v>1632.43</v>
       </c>
       <c r="M19" s="1">
         <f>N19-L19</f>
-        <v>44.8</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N19" s="1">
-        <v>1276.46</v>
+        <v>1669.84</v>
       </c>
       <c r="O19" s="1">
         <f>P19-N19</f>
-        <v>28.03</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P19" s="1">
-        <v>1304.49</v>
+        <v>1702.67</v>
       </c>
       <c r="Q19" s="1">
         <f>R19-P19</f>
-        <v>31.78</v>
+        <v>51.9499999999998</v>
       </c>
       <c r="R19" s="1">
-        <v>1336.27</v>
+        <v>1754.62</v>
       </c>
       <c r="S19" s="1">
-        <f>R19-D19</f>
-        <v>275.5</v>
-      </c>
-      <c r="T19" s="10" t="s">
-        <v>57</v>
+        <f>T19-R19</f>
+        <v>40.1200000000001</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1794.74</v>
       </c>
       <c r="U19" s="1">
-        <v>264.22</v>
-      </c>
-      <c r="V19" s="11">
-        <v>10</v>
-      </c>
-      <c r="W19" s="11">
-        <v>1.3</v>
+        <f>T19-D19</f>
+        <v>348.09</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19" s="1">
+        <v>687.67</v>
+      </c>
+      <c r="X19" s="1">
+        <v>65</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>109333</v>
+      </c>
+      <c r="AA19" s="15">
+        <f>T19*10000/Z19/164.158</f>
+        <v>0.999972887392791</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:27">
+      <c r="A20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1576.18</v>
+      </c>
+      <c r="E20" s="1">
+        <f>F20-D20</f>
+        <v>38.8399999999999</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1615.02</v>
+      </c>
+      <c r="G20" s="1">
+        <f>H20-F20</f>
+        <v>35.5999999999999</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1650.62</v>
+      </c>
+      <c r="I20" s="1">
+        <f>J20-H20</f>
+        <v>37.47</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1688.09</v>
+      </c>
+      <c r="K20" s="1">
+        <f>L20-J20</f>
+        <v>21.49</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1709.58</v>
+      </c>
+      <c r="M20" s="1">
+        <f>N20-L20</f>
+        <v>24.53</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1734.11</v>
+      </c>
+      <c r="O20" s="1">
+        <f>P20-N20</f>
+        <v>19.5300000000002</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1753.64</v>
+      </c>
+      <c r="Q20" s="1">
+        <f>R20-P20</f>
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R20" s="1">
+        <v>1818.75</v>
+      </c>
+      <c r="S20" s="1">
+        <f>T20-R20</f>
+        <v>34.3699999999999</v>
+      </c>
+      <c r="T20" s="1">
+        <v>1853.12</v>
+      </c>
+      <c r="U20" s="1">
+        <f>T20-D20</f>
+        <v>276.94</v>
+      </c>
+      <c r="V20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1726.42</v>
-      </c>
-      <c r="E20" s="3">
-        <f>F20-D20</f>
-        <v>56.28</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1782.7</v>
-      </c>
-      <c r="G20" s="3">
-        <f>H20-F20</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1853.62</v>
-      </c>
-      <c r="I20" s="3">
-        <f>J20-H20</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1903.2</v>
-      </c>
-      <c r="K20" s="3">
-        <f>L20-J20</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1943.61</v>
-      </c>
-      <c r="M20" s="3">
-        <f>N20-L20</f>
-        <v>30.01</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1973.62</v>
-      </c>
-      <c r="O20" s="3">
-        <f>P20-N20</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2056.9</v>
-      </c>
-      <c r="Q20" s="3">
-        <f>R20-P20</f>
-        <v>25.6399999999999</v>
-      </c>
-      <c r="R20" s="3">
-        <v>2082.54</v>
-      </c>
-      <c r="S20" s="3">
-        <f>R20-D20</f>
-        <v>356.12</v>
-      </c>
-      <c r="T20" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="U20" s="3">
-        <v>461.67</v>
-      </c>
-      <c r="V20" s="13">
-        <v>50</v>
-      </c>
-      <c r="W20" s="13">
-        <v>1.3</v>
+      <c r="W20" s="1">
+        <v>374.52</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>127369</v>
+      </c>
+      <c r="AA20" s="15">
+        <f>T20*10000/Z20/164.158</f>
+        <v>0.886293882927787</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:27">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1">
-        <v>927.15</v>
+        <v>907.94</v>
       </c>
       <c r="E21" s="1">
         <f>F21-D21</f>
-        <v>17.9300000000001</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F21" s="1">
-        <v>945.08</v>
+        <v>972.02</v>
       </c>
       <c r="G21" s="1">
         <f>H21-F21</f>
-        <v>24.04</v>
+        <v>36.26</v>
       </c>
       <c r="H21" s="1">
-        <v>969.12</v>
+        <v>1008.28</v>
       </c>
       <c r="I21" s="1">
         <f>J21-H21</f>
-        <v>26.96</v>
+        <v>28.8</v>
       </c>
       <c r="J21" s="1">
-        <v>996.08</v>
+        <v>1037.08</v>
       </c>
       <c r="K21" s="1">
         <f>L21-J21</f>
-        <v>23.3499999999999</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L21" s="1">
-        <v>1019.43</v>
+        <v>1077.18</v>
       </c>
       <c r="M21" s="1">
         <f>N21-L21</f>
-        <v>23.7400000000001</v>
+        <v>26.03</v>
       </c>
       <c r="N21" s="1">
-        <v>1043.17</v>
+        <v>1103.21</v>
       </c>
       <c r="O21" s="1">
         <f>P21-N21</f>
-        <v>24.99</v>
+        <v>28.3499999999999</v>
       </c>
       <c r="P21" s="1">
-        <v>1068.16</v>
+        <v>1131.56</v>
       </c>
       <c r="Q21" s="1">
         <f>R21-P21</f>
-        <v>25.3499999999999</v>
+        <v>50.1900000000001</v>
       </c>
       <c r="R21" s="1">
-        <v>1093.51</v>
+        <v>1181.75</v>
       </c>
       <c r="S21" s="1">
-        <f>R21-D21</f>
-        <v>166.36</v>
-      </c>
-      <c r="T21" s="10" t="s">
-        <v>39</v>
+        <f>T21-R21</f>
+        <v>26.8699999999999</v>
+      </c>
+      <c r="T21" s="1">
+        <v>1208.62</v>
       </c>
       <c r="U21" s="1">
-        <v>320.42</v>
-      </c>
-      <c r="V21" s="11">
-        <v>10</v>
-      </c>
-      <c r="W21" s="11">
-        <v>1.1</v>
+        <f>T21-D21</f>
+        <v>300.68</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="W21" s="1">
+        <v>403.82</v>
+      </c>
+      <c r="X21" s="1">
+        <v>35</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>8.2</v>
+      </c>
+      <c r="Z21" s="14">
+        <v>65285</v>
+      </c>
+      <c r="AA21" s="15">
+        <f>T21*10000/Z21/164.158</f>
+        <v>1.1277538433989</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:27">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
-        <v>953.78</v>
+        <v>848.93</v>
       </c>
       <c r="E22" s="1">
         <f>F22-D22</f>
-        <v>28.97</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F22" s="1">
-        <v>982.75</v>
+        <v>883.49</v>
       </c>
       <c r="G22" s="1">
         <f>H22-F22</f>
-        <v>83.9300000000001</v>
+        <v>46.08</v>
       </c>
       <c r="H22" s="1">
-        <v>1066.68</v>
+        <v>929.57</v>
       </c>
       <c r="I22" s="1">
         <f>J22-H22</f>
-        <v>42.8399999999999</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J22" s="1">
-        <v>1109.52</v>
+        <v>957.31</v>
       </c>
       <c r="K22" s="1">
         <f>L22-J22</f>
-        <v>36.46</v>
+        <v>47.36</v>
       </c>
       <c r="L22" s="1">
-        <v>1145.98</v>
+        <v>1004.67</v>
       </c>
       <c r="M22" s="1">
         <f>N22-L22</f>
-        <v>37.49</v>
+        <v>25.9399999999999</v>
       </c>
       <c r="N22" s="1">
-        <v>1183.47</v>
+        <v>1030.61</v>
       </c>
       <c r="O22" s="1">
         <f>P22-N22</f>
-        <v>33.3699999999999</v>
+        <v>37.71</v>
       </c>
       <c r="P22" s="1">
-        <v>1216.84</v>
+        <v>1068.32</v>
       </c>
       <c r="Q22" s="1">
         <f>R22-P22</f>
-        <v>24.8900000000001</v>
+        <v>18.3800000000001</v>
       </c>
       <c r="R22" s="1">
-        <v>1241.73</v>
+        <v>1086.7</v>
       </c>
       <c r="S22" s="1">
-        <f>R22-D22</f>
-        <v>287.95</v>
-      </c>
-      <c r="T22" s="10" t="s">
-        <v>23</v>
+        <f>T22-R22</f>
+        <v>21.04</v>
+      </c>
+      <c r="T22" s="1">
+        <v>1107.74</v>
       </c>
       <c r="U22" s="1">
-        <v>438.07</v>
-      </c>
-      <c r="V22" s="11">
+        <f>T22-D22</f>
+        <v>258.81</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" s="1">
+        <v>378.87</v>
+      </c>
+      <c r="X22" s="1">
         <v>30</v>
       </c>
-      <c r="W22" s="11">
-        <v>1</v>
+      <c r="Y22" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="Z22" s="14">
+        <v>78989</v>
+      </c>
+      <c r="AA22" s="15">
+        <f>T22*10000/Z22/164.158</f>
+        <v>0.854297568333938</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="4">
+    <row r="23" spans="1:27">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="5">
         <v>262.39</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <f>F23-D23</f>
         <v>11.5</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>273.89</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <f>H23-F23</f>
         <v>13.97</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="5">
         <v>287.86</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <f>J23-H23</f>
         <v>16.24</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="5">
         <v>304.1</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="5">
         <f>L23-J23</f>
         <v>12.65</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="5">
         <v>316.75</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="5">
         <f>N23-L23</f>
         <v>9.99000000000001</v>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="5">
         <v>326.74</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="5">
         <f>P23-N23</f>
         <v>6.31999999999999</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="5">
         <v>333.06</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="Q23" s="5">
         <f>R23-P23</f>
         <v>21.13</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="5">
         <v>354.19</v>
       </c>
-      <c r="S23" s="4">
-        <f>R23-D23</f>
-        <v>91.8</v>
-      </c>
-      <c r="T23" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U23" s="4">
-        <v>127.6</v>
-      </c>
-      <c r="V23" s="15">
+      <c r="S23" s="5">
+        <f>T23-R23</f>
+        <v>17.68</v>
+      </c>
+      <c r="T23" s="5">
+        <v>371.87</v>
+      </c>
+      <c r="U23" s="5">
+        <f>T23-D23</f>
+        <v>109.48</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" s="5">
+        <v>130.16</v>
+      </c>
+      <c r="X23" s="5">
         <v>0</v>
       </c>
-      <c r="W23" s="15">
+      <c r="Y23" s="5">
         <v>1</v>
       </c>
+      <c r="Z23" s="20">
+        <v>36684</v>
+      </c>
+      <c r="AA23" s="21">
+        <f>T23*10000/Z23/164.158</f>
+        <v>0.617521960503705</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
-      <c r="A24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="4">
+    <row r="24" spans="1:27">
+      <c r="A24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="5">
+        <v>407.35</v>
+      </c>
+      <c r="E24" s="5">
+        <f>F24-D24</f>
+        <v>13.86</v>
+      </c>
+      <c r="F24" s="5">
+        <v>421.21</v>
+      </c>
+      <c r="G24" s="5">
+        <f>H24-F24</f>
+        <v>16.43</v>
+      </c>
+      <c r="H24" s="5">
+        <v>437.64</v>
+      </c>
+      <c r="I24" s="5">
+        <f>J24-H24</f>
+        <v>13.64</v>
+      </c>
+      <c r="J24" s="5">
+        <v>451.28</v>
+      </c>
+      <c r="K24" s="5">
+        <f>L24-J24</f>
+        <v>11.6</v>
+      </c>
+      <c r="L24" s="5">
+        <v>462.88</v>
+      </c>
+      <c r="M24" s="5">
+        <f>N24-L24</f>
+        <v>47.68</v>
+      </c>
+      <c r="N24" s="5">
+        <v>510.56</v>
+      </c>
+      <c r="O24" s="5">
+        <f>P24-N24</f>
+        <v>20.51</v>
+      </c>
+      <c r="P24" s="5">
+        <v>531.07</v>
+      </c>
+      <c r="Q24" s="5">
+        <f>R24-P24</f>
+        <v>18.6099999999999</v>
+      </c>
+      <c r="R24" s="5">
+        <v>549.68</v>
+      </c>
+      <c r="S24" s="5">
+        <f>T24-R24</f>
+        <v>11.9400000000001</v>
+      </c>
+      <c r="T24" s="5">
+        <v>561.62</v>
+      </c>
+      <c r="U24" s="5">
+        <f>T24-D24</f>
+        <v>154.27</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W24" s="5">
+        <v>237.66</v>
+      </c>
+      <c r="X24" s="5">
+        <v>30</v>
+      </c>
+      <c r="Y24" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="Z24" s="20">
+        <v>43895</v>
+      </c>
+      <c r="AA24" s="21">
+        <f>T24*10000/Z24/164.158</f>
+        <v>0.779409077439543</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="5">
+        <v>363.88</v>
+      </c>
+      <c r="E25" s="5">
+        <f>F25-D25</f>
+        <v>14.21</v>
+      </c>
+      <c r="F25" s="5">
+        <v>378.09</v>
+      </c>
+      <c r="G25" s="5">
+        <f>H25-F25</f>
+        <v>11.22</v>
+      </c>
+      <c r="H25" s="5">
+        <v>389.31</v>
+      </c>
+      <c r="I25" s="5">
+        <f>J25-H25</f>
+        <v>13.62</v>
+      </c>
+      <c r="J25" s="5">
+        <v>402.93</v>
+      </c>
+      <c r="K25" s="5">
+        <f>L25-J25</f>
+        <v>11.13</v>
+      </c>
+      <c r="L25" s="5">
+        <v>414.06</v>
+      </c>
+      <c r="M25" s="5">
+        <f>N25-L25</f>
+        <v>17.39</v>
+      </c>
+      <c r="N25" s="5">
+        <v>431.45</v>
+      </c>
+      <c r="O25" s="5">
+        <f>P25-N25</f>
+        <v>6.32999999999998</v>
+      </c>
+      <c r="P25" s="5">
+        <v>437.78</v>
+      </c>
+      <c r="Q25" s="5">
+        <f>R25-P25</f>
+        <v>53.01</v>
+      </c>
+      <c r="R25" s="5">
+        <v>490.79</v>
+      </c>
+      <c r="S25" s="5">
+        <f>T25-R25</f>
+        <v>11.82</v>
+      </c>
+      <c r="T25" s="5">
+        <v>502.61</v>
+      </c>
+      <c r="U25" s="5">
+        <f>T25-D25</f>
+        <v>138.73</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="W25" s="5">
+        <v>139.29</v>
+      </c>
+      <c r="X25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="20">
+        <v>47256</v>
+      </c>
+      <c r="AA25" s="21">
+        <f>T25*10000/Z25/164.158</f>
+        <v>0.647906168874828</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="5">
         <v>305.29</v>
       </c>
-      <c r="E24" s="4">
-        <f>F24-D24</f>
+      <c r="E26" s="5">
+        <f>F26-D26</f>
         <v>17.97</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F26" s="5">
         <v>323.26</v>
       </c>
-      <c r="G24" s="4">
-        <f>H24-F24</f>
+      <c r="G26" s="5">
+        <f>H26-F26</f>
         <v>10.82</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H26" s="5">
         <v>334.08</v>
       </c>
-      <c r="I24" s="4">
-        <f>J24-H24</f>
+      <c r="I26" s="5">
+        <f>J26-H26</f>
         <v>16.2</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J26" s="5">
         <v>350.28</v>
       </c>
-      <c r="K24" s="4">
-        <f>L24-J24</f>
+      <c r="K26" s="5">
+        <f>L26-J26</f>
         <v>10.8</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L26" s="5">
         <v>361.08</v>
       </c>
-      <c r="M24" s="4">
-        <f>N24-L24</f>
+      <c r="M26" s="5">
+        <f>N26-L26</f>
         <v>9.98000000000002</v>
       </c>
-      <c r="N24" s="4">
+      <c r="N26" s="5">
         <v>371.06</v>
       </c>
-      <c r="O24" s="4">
-        <f>P24-N24</f>
+      <c r="O26" s="5">
+        <f>P26-N26</f>
         <v>10.17</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P26" s="5">
         <v>381.23</v>
       </c>
-      <c r="Q24" s="4">
-        <f>R24-P24</f>
+      <c r="Q26" s="5">
+        <f>R26-P26</f>
         <v>20.97</v>
       </c>
-      <c r="R24" s="4">
+      <c r="R26" s="5">
         <v>402.2</v>
       </c>
-      <c r="S24" s="4">
-        <f>R24-D24</f>
-        <v>96.91</v>
-      </c>
-      <c r="T24" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="U24" s="4">
-        <v>111.49</v>
-      </c>
-      <c r="V24" s="15">
+      <c r="S26" s="5">
+        <f>T26-R26</f>
+        <v>5.68000000000001</v>
+      </c>
+      <c r="T26" s="5">
+        <v>407.88</v>
+      </c>
+      <c r="U26" s="5">
+        <f>T26-D26</f>
+        <v>102.59</v>
+      </c>
+      <c r="V26" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="W26" s="5">
+        <v>114.59</v>
+      </c>
+      <c r="X26" s="5">
         <v>0</v>
       </c>
-      <c r="W24" s="15">
+      <c r="Y26" s="5">
         <v>1</v>
       </c>
+      <c r="Z26" s="20">
+        <v>28066</v>
+      </c>
+      <c r="AA26" s="21">
+        <f>T26*10000/Z26/164.158</f>
+        <v>0.885298722383714</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
-      <c r="A25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="4">
-        <v>407.35</v>
-      </c>
-      <c r="E25" s="4">
-        <f>F25-D25</f>
-        <v>13.86</v>
-      </c>
-      <c r="F25" s="4">
-        <v>421.21</v>
-      </c>
-      <c r="G25" s="4">
-        <f>H25-F25</f>
-        <v>16.43</v>
-      </c>
-      <c r="H25" s="4">
-        <v>437.64</v>
-      </c>
-      <c r="I25" s="4">
-        <f>J25-H25</f>
-        <v>13.64</v>
-      </c>
-      <c r="J25" s="4">
-        <v>451.28</v>
-      </c>
-      <c r="K25" s="4">
-        <f>L25-J25</f>
-        <v>11.6</v>
-      </c>
-      <c r="L25" s="4">
-        <v>462.88</v>
-      </c>
-      <c r="M25" s="4">
-        <f>N25-L25</f>
-        <v>47.68</v>
-      </c>
-      <c r="N25" s="4">
-        <v>510.56</v>
-      </c>
-      <c r="O25" s="4">
-        <f>P25-N25</f>
-        <v>20.51</v>
-      </c>
-      <c r="P25" s="4">
-        <v>531.07</v>
-      </c>
-      <c r="Q25" s="4">
-        <f>R25-P25</f>
-        <v>18.6099999999999</v>
-      </c>
-      <c r="R25" s="4">
-        <v>549.68</v>
-      </c>
-      <c r="S25" s="4">
-        <f>R25-D25</f>
-        <v>142.33</v>
-      </c>
-      <c r="T25" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="U25" s="4">
-        <v>233.16</v>
-      </c>
-      <c r="V25" s="15">
-        <v>30</v>
-      </c>
-      <c r="W25" s="15">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="1">
-        <v>848.93</v>
-      </c>
-      <c r="E26" s="1">
-        <f>F26-D26</f>
-        <v>34.5600000000001</v>
-      </c>
-      <c r="F26" s="1">
-        <v>883.49</v>
-      </c>
-      <c r="G26" s="1">
-        <f>H26-F26</f>
-        <v>46.08</v>
-      </c>
-      <c r="H26" s="1">
-        <v>929.57</v>
-      </c>
-      <c r="I26" s="1">
-        <f>J26-H26</f>
-        <v>27.7399999999999</v>
-      </c>
-      <c r="J26" s="1">
-        <v>957.31</v>
-      </c>
-      <c r="K26" s="1">
-        <f>L26-J26</f>
-        <v>47.36</v>
-      </c>
-      <c r="L26" s="1">
-        <v>1004.67</v>
-      </c>
-      <c r="M26" s="1">
-        <f>N26-L26</f>
-        <v>25.9399999999999</v>
-      </c>
-      <c r="N26" s="1">
-        <v>1030.61</v>
-      </c>
-      <c r="O26" s="1">
-        <f>P26-N26</f>
-        <v>37.71</v>
-      </c>
-      <c r="P26" s="1">
-        <v>1068.32</v>
-      </c>
-      <c r="Q26" s="1">
-        <f>R26-P26</f>
-        <v>18.3800000000001</v>
-      </c>
-      <c r="R26" s="1">
-        <v>1086.7</v>
-      </c>
-      <c r="S26" s="1">
-        <f>R26-D26</f>
-        <v>237.77</v>
-      </c>
-      <c r="T26" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="U26" s="1">
-        <v>370.52</v>
-      </c>
-      <c r="V26" s="11">
-        <v>30</v>
-      </c>
-      <c r="W26" s="11">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
-      <c r="A27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="4">
+    <row r="27" spans="1:27">
+      <c r="A27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="5">
         <v>552.79</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <f>F27-D27</f>
         <v>15.9400000000001</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <v>568.73</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <f>H27-F27</f>
         <v>1.61000000000001</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="5">
         <v>570.34</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="5">
         <f>J27-H27</f>
         <v>7.13999999999999</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="5">
         <v>577.48</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="5">
         <f>L27-J27</f>
         <v>2.88999999999999</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="5">
         <v>580.37</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="5">
         <f>N27-L27</f>
         <v>2.55999999999995</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="5">
         <v>582.93</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O27" s="5">
         <f>P27-N27</f>
         <v>24.99</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="5">
         <v>607.92</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="Q27" s="5">
         <f>R27-P27</f>
         <v>0.330000000000041</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R27" s="5">
         <v>608.25</v>
       </c>
-      <c r="S27" s="4">
-        <f>R27-D27</f>
-        <v>55.46</v>
-      </c>
-      <c r="T27" s="14" t="s">
+      <c r="S27" s="5">
+        <f>T27-R27</f>
+        <v>1.80999999999995</v>
+      </c>
+      <c r="T27" s="5">
+        <v>610.06</v>
+      </c>
+      <c r="U27" s="5">
+        <f>T27-D27</f>
+        <v>57.27</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="W27" s="5">
+        <v>131.95</v>
+      </c>
+      <c r="X27" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Z27" s="20">
+        <v>49654</v>
+      </c>
+      <c r="AA27" s="21">
+        <f>T27*10000/Z27/164.158</f>
+        <v>0.74843873870761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U27" s="4">
-        <v>131.95</v>
-      </c>
-      <c r="V27" s="15">
-        <v>0</v>
-      </c>
-      <c r="W27" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1">
         <v>1317.56</v>
@@ -3523,28 +3927,42 @@
         <v>1424.81</v>
       </c>
       <c r="S28" s="1">
-        <f>R28-D28</f>
+        <f>T28-R28</f>
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>1424.81</v>
+      </c>
+      <c r="U28" s="1">
+        <f>T28-D28</f>
         <v>107.25</v>
       </c>
-      <c r="T28" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="U28" s="1">
+      <c r="V28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="W28" s="1">
         <v>271.82</v>
       </c>
-      <c r="V28" s="11">
+      <c r="X28" s="1">
         <v>0</v>
       </c>
-      <c r="W28" s="11">
+      <c r="Y28" s="1">
         <v>0</v>
       </c>
+      <c r="Z28" s="14">
+        <v>136029</v>
+      </c>
+      <c r="AA28" s="15">
+        <f>T28*10000/Z28/164.158</f>
+        <v>0.638062758131816</v>
+      </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:23">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -3565,41 +3983,45 @@
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="P32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
+      <c r="P32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3618,62 +4040,64 @@
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
       <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:W28">
-    <sortCondition ref="Q2" descending="1"/>
+  <sortState ref="A2:AA28">
+    <sortCondition ref="S2" descending="1"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="P32:V32"/>
-    <mergeCell ref="C34:T34"/>
+    <mergeCell ref="P32:X32"/>
+    <mergeCell ref="C34:V34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3685,7 +4109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3697,7 +4121,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'19星域战力标'!$F$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'19星域战力标'!$F$1:$F$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
   <si>
     <t>区服</t>
   </si>
@@ -94,61 +94,142 @@
     <t>星值</t>
   </si>
   <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
     <t>148区</t>
   </si>
   <si>
     <t>大核桃</t>
   </si>
   <si>
-    <t>中大氪</t>
-  </si>
-  <si>
     <t>眼镜妹（跳费）</t>
   </si>
   <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
     <t>水煮肉片</t>
   </si>
   <si>
-    <t>中氪</t>
+    <t>玩玩</t>
   </si>
   <si>
     <t>请叫我阿奎</t>
   </si>
   <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>瓦斯兰（快攻）</t>
+  </si>
+  <si>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>151区</t>
@@ -160,100 +241,16 @@
     <t>洞察妹（洞察）</t>
   </si>
   <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>大氪</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>瓦斯兰（快攻）</t>
-  </si>
-  <si>
-    <t>146区</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>圣母（杂糅）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>秋雨</t>
   </si>
   <si>
     <t>152区</t>
   </si>
   <si>
     <t>养乐多</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>何斌</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -329,14 +326,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFC000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFC000"/>
+      <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -350,7 +347,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -950,7 +947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -987,31 +984,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1333,34 +1315,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:AA39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="13.5818181818182" customWidth="1"/>
-    <col min="3" max="3" width="10.6454545454545" customWidth="1"/>
-    <col min="4" max="4" width="13.2545454545455" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.6416666666667" customWidth="1"/>
+    <col min="4" max="4" width="13.2583333333333" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7545454545455" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7583333333333" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6272727272727" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7545454545455" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.1272727272727" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6363636363636" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.2727272727273" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="0.254545454545455" customWidth="1"/>
-    <col min="14" max="14" width="17.4545454545455" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1272727272727" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.3545454545455" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="16.9909090909091" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="17.8636363636364" customWidth="1"/>
-    <col min="19" max="21" width="18.0181818181818" customWidth="1"/>
-    <col min="22" max="22" width="18.8909090909091" customWidth="1"/>
-    <col min="23" max="23" width="14.5454545454545" customWidth="1"/>
-    <col min="24" max="24" width="11.6272727272727" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="12.6090909090909" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="15.0181818181818" customWidth="1"/>
-    <col min="27" max="27" width="19.5181818181818" customWidth="1"/>
+    <col min="8" max="8" width="16.625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7583333333333" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6333333333333" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.275" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0.258333333333333" customWidth="1"/>
+    <col min="14" max="14" width="17.4583333333333" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3583333333333" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="16.9916666666667" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="17.8666666666667" customWidth="1"/>
+    <col min="19" max="21" width="18.0166666666667" customWidth="1"/>
+    <col min="22" max="22" width="18.8916666666667" customWidth="1"/>
+    <col min="23" max="23" width="14.5416666666667" customWidth="1"/>
+    <col min="24" max="24" width="11.625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="15.0166666666667" customWidth="1"/>
+    <col min="27" max="27" width="19.5166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -1457,458 +1439,458 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>2714.1</v>
+        <v>2136.24</v>
       </c>
       <c r="E2" s="2">
         <f>F2-D2</f>
-        <v>123.29</v>
+        <v>40.8200000000002</v>
       </c>
       <c r="F2" s="2">
-        <v>2837.39</v>
+        <v>2177.06</v>
       </c>
       <c r="G2" s="2">
         <f>H2-F2</f>
-        <v>95.8499999999999</v>
+        <v>62.5999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>2933.24</v>
+        <v>2239.66</v>
       </c>
       <c r="I2" s="2">
         <f>J2-H2</f>
-        <v>92.46</v>
+        <v>47.0700000000002</v>
       </c>
       <c r="J2" s="2">
-        <v>3025.7</v>
+        <v>2286.73</v>
       </c>
       <c r="K2" s="2">
         <f>L2-J2</f>
-        <v>90.4100000000003</v>
+        <v>25.52</v>
       </c>
       <c r="L2" s="2">
-        <v>3116.11</v>
+        <v>2312.25</v>
       </c>
       <c r="M2" s="2">
         <f>N2-L2</f>
-        <v>103.54</v>
+        <v>36.7800000000002</v>
       </c>
       <c r="N2" s="2">
-        <v>3219.65</v>
+        <v>2349.03</v>
       </c>
       <c r="O2" s="2">
         <f>P2-N2</f>
-        <v>75.6599999999999</v>
+        <v>-18.02</v>
       </c>
       <c r="P2" s="2">
-        <v>3295.31</v>
+        <v>2331.01</v>
       </c>
       <c r="Q2" s="2">
         <f>R2-P2</f>
-        <v>88.98</v>
+        <v>62.7599999999998</v>
       </c>
       <c r="R2" s="2">
-        <v>3384.29</v>
+        <v>2393.77</v>
       </c>
       <c r="S2" s="2">
         <f>T2-R2</f>
-        <v>102.46</v>
+        <v>55.5599999999999</v>
       </c>
       <c r="T2" s="2">
-        <v>3486.75</v>
+        <v>2449.33</v>
       </c>
       <c r="U2" s="2">
         <f>T2-D2</f>
-        <v>772.65</v>
+        <v>313.09</v>
       </c>
       <c r="V2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="W2" s="2">
-        <v>746.62</v>
+        <v>712.42</v>
       </c>
       <c r="X2" s="2">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="Y2" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="Z2" s="12">
-        <v>191519</v>
-      </c>
-      <c r="AA2" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>153852</v>
+      </c>
+      <c r="AA2" s="12">
         <f>T2*10000/Z2/164.158</f>
-        <v>1.10903918696675</v>
+        <v>0.969799829339937</v>
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="2">
+        <v>1754.54</v>
+      </c>
+      <c r="E3" s="2">
+        <f>F3-D3</f>
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1807.91</v>
+      </c>
+      <c r="G3" s="2">
+        <f>H3-F3</f>
+        <v>90.24</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1898.15</v>
+      </c>
+      <c r="I3" s="2">
+        <f>J3-H3</f>
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1988.53</v>
+      </c>
+      <c r="K3" s="2">
+        <f>L3-J3</f>
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2048.24</v>
+      </c>
+      <c r="M3" s="2">
+        <f>N3-L3</f>
+        <v>153.99</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2202.23</v>
+      </c>
+      <c r="O3" s="2">
+        <f>P3-N3</f>
+        <v>64.21</v>
+      </c>
+      <c r="P3" s="2">
+        <v>2266.44</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>R3-P3</f>
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2314</v>
+      </c>
+      <c r="S3" s="2">
+        <f>T3-R3</f>
+        <v>59.6500000000001</v>
+      </c>
+      <c r="T3" s="2">
+        <v>2373.65</v>
+      </c>
+      <c r="U3" s="2">
+        <f>T3-D3</f>
+        <v>619.11</v>
+      </c>
+      <c r="V3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="1">
-        <v>1425.22</v>
-      </c>
-      <c r="E3" s="1">
-        <f>F3-D3</f>
-        <v>64.8599999999999</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1490.08</v>
-      </c>
-      <c r="G3" s="1">
-        <f>H3-F3</f>
-        <v>46</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1536.08</v>
-      </c>
-      <c r="I3" s="1">
-        <f>J3-H3</f>
-        <v>50.8500000000001</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1586.93</v>
-      </c>
-      <c r="K3" s="1">
-        <f>L3-J3</f>
-        <v>86.5599999999999</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1673.49</v>
-      </c>
-      <c r="M3" s="1">
-        <f>N3-L3</f>
-        <v>38.5599999999999</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1712.05</v>
-      </c>
-      <c r="O3" s="1">
-        <f>P3-N3</f>
-        <v>57.0900000000001</v>
-      </c>
-      <c r="P3" s="1">
-        <v>1769.14</v>
-      </c>
-      <c r="Q3" s="1">
-        <f>R3-P3</f>
-        <v>50.8699999999999</v>
-      </c>
-      <c r="R3" s="1">
-        <v>1820.01</v>
-      </c>
-      <c r="S3" s="1">
-        <f>T3-R3</f>
-        <v>94.4300000000001</v>
-      </c>
-      <c r="T3" s="1">
-        <v>1914.44</v>
-      </c>
-      <c r="U3" s="1">
-        <f>T3-D3</f>
-        <v>489.22</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="W3" s="1">
-        <v>463.4</v>
-      </c>
-      <c r="X3" s="1">
-        <v>20</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="Z3" s="14">
-        <v>106867</v>
-      </c>
-      <c r="AA3" s="15">
+      <c r="W3" s="2">
+        <v>409.56</v>
+      </c>
+      <c r="X3" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>132783</v>
+      </c>
+      <c r="AA3" s="12">
         <f>T3*10000/Z3/164.158</f>
-        <v>1.09127973276278</v>
+        <v>1.08896056516498</v>
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="2">
+        <v>1726.42</v>
+      </c>
+      <c r="E4" s="2">
+        <f>F4-D4</f>
+        <v>56.28</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1782.7</v>
+      </c>
+      <c r="G4" s="2">
+        <f>H4-F4</f>
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1853.62</v>
+      </c>
+      <c r="I4" s="2">
+        <f>J4-H4</f>
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1903.2</v>
+      </c>
+      <c r="K4" s="2">
+        <f>L4-J4</f>
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1943.61</v>
+      </c>
+      <c r="M4" s="2">
+        <f>N4-L4</f>
+        <v>30.01</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1973.62</v>
+      </c>
+      <c r="O4" s="2">
+        <f>P4-N4</f>
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2056.9</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>R4-P4</f>
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2082.54</v>
+      </c>
+      <c r="S4" s="2">
+        <f>T4-R4</f>
+        <v>66.46</v>
+      </c>
+      <c r="T4" s="2">
+        <v>2149</v>
+      </c>
+      <c r="U4" s="2">
+        <f>T4-D4</f>
+        <v>422.58</v>
+      </c>
+      <c r="V4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="1">
-        <v>1349.35</v>
-      </c>
-      <c r="E4" s="1">
-        <f>F4-D4</f>
-        <v>49.6200000000001</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1398.97</v>
-      </c>
-      <c r="G4" s="1">
-        <f>H4-F4</f>
-        <v>27.79</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1426.76</v>
-      </c>
-      <c r="I4" s="1">
-        <f>J4-H4</f>
-        <v>29.02</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1455.78</v>
-      </c>
-      <c r="K4" s="1">
-        <f>L4-J4</f>
-        <v>97.8800000000001</v>
-      </c>
-      <c r="L4" s="1">
-        <v>1553.66</v>
-      </c>
-      <c r="M4" s="1">
-        <f>N4-L4</f>
-        <v>42.3599999999999</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1596.02</v>
-      </c>
-      <c r="O4" s="1">
-        <f>P4-N4</f>
-        <v>54.22</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1650.24</v>
-      </c>
-      <c r="Q4" s="1">
-        <f>R4-P4</f>
-        <v>35.5899999999999</v>
-      </c>
-      <c r="R4" s="1">
-        <v>1685.83</v>
-      </c>
-      <c r="S4" s="1">
-        <f>T4-R4</f>
-        <v>68.1300000000001</v>
-      </c>
-      <c r="T4" s="1">
-        <v>1753.96</v>
-      </c>
-      <c r="U4" s="1">
-        <f>T4-D4</f>
-        <v>404.61</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="W4" s="1">
-        <v>439.9</v>
-      </c>
-      <c r="X4" s="1">
-        <v>20</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="Z4" s="14">
-        <v>109106</v>
-      </c>
-      <c r="AA4" s="15">
+      <c r="W4" s="2">
+        <v>493.22</v>
+      </c>
+      <c r="X4" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>124763</v>
+      </c>
+      <c r="AA4" s="12">
         <f>T4*10000/Z4/164.158</f>
-        <v>0.979284765626509</v>
+        <v>1.0492731363367</v>
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1726.42</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="1">
+        <v>1425.22</v>
+      </c>
+      <c r="E5" s="1">
         <f>F5-D5</f>
-        <v>56.28</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1782.7</v>
-      </c>
-      <c r="G5" s="3">
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1490.08</v>
+      </c>
+      <c r="G5" s="1">
         <f>H5-F5</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1853.62</v>
-      </c>
-      <c r="I5" s="3">
+        <v>46</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1536.08</v>
+      </c>
+      <c r="I5" s="1">
         <f>J5-H5</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1903.2</v>
-      </c>
-      <c r="K5" s="3">
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1586.93</v>
+      </c>
+      <c r="K5" s="1">
         <f>L5-J5</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1943.61</v>
-      </c>
-      <c r="M5" s="3">
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1673.49</v>
+      </c>
+      <c r="M5" s="1">
         <f>N5-L5</f>
-        <v>30.01</v>
-      </c>
-      <c r="N5" s="3">
-        <v>1973.62</v>
-      </c>
-      <c r="O5" s="3">
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1712.05</v>
+      </c>
+      <c r="O5" s="1">
         <f>P5-N5</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P5" s="3">
-        <v>2056.9</v>
-      </c>
-      <c r="Q5" s="3">
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1769.14</v>
+      </c>
+      <c r="Q5" s="1">
         <f>R5-P5</f>
-        <v>25.6399999999999</v>
-      </c>
-      <c r="R5" s="3">
-        <v>2082.54</v>
-      </c>
-      <c r="S5" s="3">
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1820.01</v>
+      </c>
+      <c r="S5" s="1">
         <f>T5-R5</f>
-        <v>66.46</v>
-      </c>
-      <c r="T5" s="3">
-        <v>2149</v>
-      </c>
-      <c r="U5" s="3">
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1914.44</v>
+      </c>
+      <c r="U5" s="1">
         <f>T5-D5</f>
-        <v>422.58</v>
-      </c>
-      <c r="V5" s="9" t="s">
+        <v>489.22</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="W5" s="3">
-        <v>493.22</v>
-      </c>
-      <c r="X5" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" s="16">
-        <v>124763</v>
-      </c>
-      <c r="AA5" s="17">
+      <c r="W5" s="1">
+        <v>463.4</v>
+      </c>
+      <c r="X5" s="1">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>106867</v>
+      </c>
+      <c r="AA5" s="13">
         <f>T5*10000/Z5/164.158</f>
-        <v>1.0492731363367</v>
+        <v>1.09127973276278</v>
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1349.35</v>
+      </c>
+      <c r="E6" s="1">
+        <f>F6-D6</f>
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1398.97</v>
+      </c>
+      <c r="G6" s="1">
+        <f>H6-F6</f>
+        <v>27.79</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1426.76</v>
+      </c>
+      <c r="I6" s="1">
+        <f>J6-H6</f>
+        <v>29.02</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1455.78</v>
+      </c>
+      <c r="K6" s="1">
+        <f>L6-J6</f>
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1553.66</v>
+      </c>
+      <c r="M6" s="1">
+        <f>N6-L6</f>
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1596.02</v>
+      </c>
+      <c r="O6" s="1">
+        <f>P6-N6</f>
+        <v>54.22</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1650.24</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>R6-P6</f>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1685.83</v>
+      </c>
+      <c r="S6" s="1">
+        <f>T6-R6</f>
+        <v>68.1300000000001</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1753.96</v>
+      </c>
+      <c r="U6" s="1">
+        <f>T6-D6</f>
+        <v>404.61</v>
+      </c>
+      <c r="V6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3">
-        <v>2183.01</v>
-      </c>
-      <c r="E6" s="3">
-        <f>F6-D6</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2207.13</v>
-      </c>
-      <c r="G6" s="3">
-        <f>H6-F6</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H6" s="3">
-        <v>2229.99</v>
-      </c>
-      <c r="I6" s="3">
-        <f>J6-H6</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J6" s="3">
-        <v>2241.77</v>
-      </c>
-      <c r="K6" s="3">
-        <f>L6-J6</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L6" s="3">
-        <v>2254.78</v>
-      </c>
-      <c r="M6" s="3">
-        <f>N6-L6</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N6" s="3">
-        <v>2317.42</v>
-      </c>
-      <c r="O6" s="3">
-        <f>P6-N6</f>
-        <v>16.27</v>
-      </c>
-      <c r="P6" s="3">
-        <v>2333.69</v>
-      </c>
-      <c r="Q6" s="3">
-        <f>R6-P6</f>
-        <v>36.5</v>
-      </c>
-      <c r="R6" s="3">
-        <v>2370.19</v>
-      </c>
-      <c r="S6" s="3">
-        <f>T6-R6</f>
-        <v>65.1900000000001</v>
-      </c>
-      <c r="T6" s="3">
-        <v>2435.38</v>
-      </c>
-      <c r="U6" s="3">
-        <f>T6-D6</f>
-        <v>252.37</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="W6" s="3">
-        <v>596.97</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="16">
-        <v>133781</v>
-      </c>
-      <c r="AA6" s="17">
+      <c r="W6" s="1">
+        <v>439.9</v>
+      </c>
+      <c r="X6" s="1">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>109106</v>
+      </c>
+      <c r="AA6" s="13">
         <f>T6*10000/Z6/164.158</f>
-        <v>1.10894560728839</v>
+        <v>0.979284765626509</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1919,2065 +1901,1990 @@
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
-        <v>1350.52</v>
+        <v>848.93</v>
       </c>
       <c r="E7" s="1">
         <f>F7-D7</f>
-        <v>52.6800000000001</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>1403.2</v>
+        <v>883.49</v>
       </c>
       <c r="G7" s="1">
         <f>H7-F7</f>
-        <v>55.3199999999999</v>
+        <v>46.08</v>
       </c>
       <c r="H7" s="1">
-        <v>1458.52</v>
+        <v>929.57</v>
       </c>
       <c r="I7" s="1">
         <f>J7-H7</f>
-        <v>32.6800000000001</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J7" s="1">
-        <v>1491.2</v>
+        <v>957.31</v>
       </c>
       <c r="K7" s="1">
         <f>L7-J7</f>
-        <v>54.96</v>
+        <v>47.36</v>
       </c>
       <c r="L7" s="1">
-        <v>1546.16</v>
+        <v>1004.67</v>
       </c>
       <c r="M7" s="1">
         <f>N7-L7</f>
-        <v>92.1299999999999</v>
+        <v>25.9399999999999</v>
       </c>
       <c r="N7" s="1">
-        <v>1638.29</v>
+        <v>1030.61</v>
       </c>
       <c r="O7" s="1">
         <f>P7-N7</f>
-        <v>59.4400000000001</v>
+        <v>37.71</v>
       </c>
       <c r="P7" s="1">
-        <v>1697.73</v>
+        <v>1068.32</v>
       </c>
       <c r="Q7" s="1">
         <f>R7-P7</f>
-        <v>71.3399999999999</v>
+        <v>18.3800000000001</v>
       </c>
       <c r="R7" s="1">
-        <v>1769.07</v>
+        <v>1086.7</v>
       </c>
       <c r="S7" s="1">
         <f>T7-R7</f>
-        <v>62.9000000000001</v>
+        <v>21.04</v>
       </c>
       <c r="T7" s="1">
-        <v>1831.97</v>
+        <v>1107.74</v>
       </c>
       <c r="U7" s="1">
         <f>T7-D7</f>
-        <v>481.45</v>
+        <v>258.81</v>
       </c>
       <c r="V7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="W7" s="1">
-        <v>576.12</v>
+        <v>378.87</v>
       </c>
       <c r="X7" s="1">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Y7" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="Z7" s="14">
-        <v>127603</v>
-      </c>
-      <c r="AA7" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>78989</v>
+      </c>
+      <c r="AA7" s="13">
         <f>T7*10000/Z7/164.158</f>
-        <v>0.8745717003899</v>
+        <v>0.854297568333938</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3">
-        <v>1754.54</v>
+        <v>407.35</v>
       </c>
       <c r="E8" s="3">
         <f>F8-D8</f>
-        <v>53.3700000000001</v>
+        <v>13.86</v>
       </c>
       <c r="F8" s="3">
-        <v>1807.91</v>
+        <v>421.21</v>
       </c>
       <c r="G8" s="3">
         <f>H8-F8</f>
-        <v>90.24</v>
+        <v>16.43</v>
       </c>
       <c r="H8" s="3">
-        <v>1898.15</v>
+        <v>437.64</v>
       </c>
       <c r="I8" s="3">
         <f>J8-H8</f>
-        <v>90.3799999999999</v>
+        <v>13.64</v>
       </c>
       <c r="J8" s="3">
-        <v>1988.53</v>
+        <v>451.28</v>
       </c>
       <c r="K8" s="3">
         <f>L8-J8</f>
-        <v>59.7099999999998</v>
+        <v>11.6</v>
       </c>
       <c r="L8" s="3">
-        <v>2048.24</v>
+        <v>462.88</v>
       </c>
       <c r="M8" s="3">
         <f>N8-L8</f>
-        <v>153.99</v>
+        <v>47.68</v>
       </c>
       <c r="N8" s="3">
-        <v>2202.23</v>
+        <v>510.56</v>
       </c>
       <c r="O8" s="3">
         <f>P8-N8</f>
-        <v>64.21</v>
+        <v>20.51</v>
       </c>
       <c r="P8" s="3">
-        <v>2266.44</v>
+        <v>531.07</v>
       </c>
       <c r="Q8" s="3">
         <f>R8-P8</f>
-        <v>47.5599999999999</v>
+        <v>18.6099999999999</v>
       </c>
       <c r="R8" s="3">
-        <v>2314</v>
+        <v>549.68</v>
       </c>
       <c r="S8" s="3">
         <f>T8-R8</f>
-        <v>59.6500000000001</v>
+        <v>11.9400000000001</v>
       </c>
       <c r="T8" s="3">
-        <v>2373.65</v>
+        <v>561.62</v>
       </c>
       <c r="U8" s="3">
         <f>T8-D8</f>
-        <v>619.11</v>
+        <v>154.27</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="W8" s="3">
-        <v>409.56</v>
+        <v>237.66</v>
       </c>
       <c r="X8" s="3">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="Y8" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="Z8" s="16">
-        <v>132783</v>
-      </c>
-      <c r="AA8" s="17">
+        <v>2.4</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>43895</v>
+      </c>
+      <c r="AA8" s="14">
         <f>T8*10000/Z8/164.158</f>
-        <v>1.08896056516498</v>
+        <v>0.779409077439543</v>
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1735.94</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4">
+        <v>4105.48</v>
+      </c>
+      <c r="E9" s="4">
         <f>F9-D9</f>
-        <v>48.5999999999999</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1784.54</v>
-      </c>
-      <c r="G9" s="3">
+        <v>181.21</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4286.69</v>
+      </c>
+      <c r="G9" s="4">
         <f>H9-F9</f>
-        <v>74.1600000000001</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1858.7</v>
-      </c>
-      <c r="I9" s="3">
+        <v>139.09</v>
+      </c>
+      <c r="H9" s="4">
+        <v>4425.78</v>
+      </c>
+      <c r="I9" s="4">
         <f>J9-H9</f>
-        <v>65.55</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1924.25</v>
-      </c>
-      <c r="K9" s="3">
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J9" s="4">
+        <v>4480.66</v>
+      </c>
+      <c r="K9" s="4">
         <f>L9-J9</f>
-        <v>35.73</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1959.98</v>
-      </c>
-      <c r="M9" s="3">
+        <v>104.900000000001</v>
+      </c>
+      <c r="L9" s="4">
+        <v>4585.56</v>
+      </c>
+      <c r="M9" s="4">
         <f>N9-L9</f>
-        <v>41.8799999999999</v>
-      </c>
-      <c r="N9" s="3">
-        <v>2001.86</v>
-      </c>
-      <c r="O9" s="3">
+        <v>70.29</v>
+      </c>
+      <c r="N9" s="4">
+        <v>4655.85</v>
+      </c>
+      <c r="O9" s="4">
         <f>P9-N9</f>
-        <v>74.6600000000001</v>
-      </c>
-      <c r="P9" s="3">
-        <v>2076.52</v>
-      </c>
-      <c r="Q9" s="3">
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P9" s="4">
+        <v>4705.02</v>
+      </c>
+      <c r="Q9" s="4">
         <f>R9-P9</f>
-        <v>48.71</v>
-      </c>
-      <c r="R9" s="3">
-        <v>2125.23</v>
-      </c>
-      <c r="S9" s="3">
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R9" s="4">
+        <v>4743.24</v>
+      </c>
+      <c r="S9" s="4">
         <f>T9-R9</f>
-        <v>57.4200000000001</v>
-      </c>
-      <c r="T9" s="3">
-        <v>2182.65</v>
-      </c>
-      <c r="U9" s="3">
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T9" s="4">
+        <v>4788.86</v>
+      </c>
+      <c r="U9" s="4">
         <f>T9-D9</f>
-        <v>446.71</v>
-      </c>
-      <c r="V9" s="9" t="s">
+        <v>683.38</v>
+      </c>
+      <c r="V9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="3">
-        <v>515.22</v>
-      </c>
-      <c r="X9" s="3">
-        <v>80</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="Z9" s="16">
-        <v>150192</v>
-      </c>
-      <c r="AA9" s="17">
+      <c r="W9" s="4">
+        <v>1364.72</v>
+      </c>
+      <c r="X9" s="4">
+        <v>400</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>186759</v>
+      </c>
+      <c r="AA9" s="15">
         <f>T9*10000/Z9/164.158</f>
-        <v>0.885268980487198</v>
+        <v>1.56202704397778</v>
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="3">
-        <v>2136.24</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="2">
+        <v>1966.62</v>
+      </c>
+      <c r="E10" s="2">
         <f>F10-D10</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2177.06</v>
-      </c>
-      <c r="G10" s="3">
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2015.64</v>
+      </c>
+      <c r="G10" s="2">
         <f>H10-F10</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2239.66</v>
-      </c>
-      <c r="I10" s="3">
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2049.8</v>
+      </c>
+      <c r="I10" s="2">
         <f>J10-H10</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2286.73</v>
-      </c>
-      <c r="K10" s="3">
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J10" s="2">
+        <v>2139.9</v>
+      </c>
+      <c r="K10" s="2">
         <f>L10-J10</f>
-        <v>25.52</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2312.25</v>
-      </c>
-      <c r="M10" s="3">
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2193.07</v>
+      </c>
+      <c r="M10" s="2">
         <f>N10-L10</f>
-        <v>36.7800000000002</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2349.03</v>
-      </c>
-      <c r="O10" s="3">
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2256.98</v>
+      </c>
+      <c r="O10" s="2">
         <f>P10-N10</f>
-        <v>-18.02</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2331.01</v>
-      </c>
-      <c r="Q10" s="3">
+        <v>45.71</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2302.69</v>
+      </c>
+      <c r="Q10" s="2">
         <f>R10-P10</f>
-        <v>62.7599999999998</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2393.77</v>
-      </c>
-      <c r="S10" s="3">
+        <v>37.2199999999998</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2339.91</v>
+      </c>
+      <c r="S10" s="2">
         <f>T10-R10</f>
-        <v>55.5599999999999</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2449.33</v>
-      </c>
-      <c r="U10" s="3">
+        <v>47.3099999999999</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2387.22</v>
+      </c>
+      <c r="U10" s="2">
         <f>T10-D10</f>
-        <v>313.09</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W10" s="3">
-        <v>712.42</v>
-      </c>
-      <c r="X10" s="3">
-        <v>20</v>
-      </c>
-      <c r="Y10" s="3">
+        <v>420.6</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="W10" s="2">
+        <v>837.27</v>
+      </c>
+      <c r="X10" s="2">
+        <v>65</v>
+      </c>
+      <c r="Y10" s="2">
         <v>1.2</v>
       </c>
-      <c r="Z10" s="3">
-        <v>153852</v>
-      </c>
-      <c r="AA10" s="17">
+      <c r="Z10" s="2">
+        <v>130589</v>
+      </c>
+      <c r="AA10" s="12">
         <f>T10*10000/Z10/164.158</f>
-        <v>0.969799829339937</v>
+        <v>1.11358608572767</v>
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2533.85</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1060.77</v>
+      </c>
+      <c r="E11" s="1">
         <f>F11-D11</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2583.9</v>
-      </c>
-      <c r="G11" s="2">
+        <v>63.24</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1124.01</v>
+      </c>
+      <c r="G11" s="1">
         <f>H11-F11</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2669.66</v>
-      </c>
-      <c r="I11" s="2">
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1143.68</v>
+      </c>
+      <c r="I11" s="1">
         <f>J11-H11</f>
-        <v>81.79</v>
-      </c>
-      <c r="J11" s="2">
-        <v>2751.45</v>
-      </c>
-      <c r="K11" s="2">
+        <v>47.76</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1191.44</v>
+      </c>
+      <c r="K11" s="1">
         <f>L11-J11</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L11" s="2">
-        <v>2834.62</v>
-      </c>
-      <c r="M11" s="2">
+        <v>40.22</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1231.66</v>
+      </c>
+      <c r="M11" s="1">
         <f>N11-L11</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N11" s="2">
-        <v>2891.61</v>
-      </c>
-      <c r="O11" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1276.46</v>
+      </c>
+      <c r="O11" s="1">
         <f>P11-N11</f>
-        <v>103.98</v>
-      </c>
-      <c r="P11" s="2">
-        <v>2995.59</v>
-      </c>
-      <c r="Q11" s="2">
+        <v>28.03</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1304.49</v>
+      </c>
+      <c r="Q11" s="1">
         <f>R11-P11</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R11" s="2">
-        <v>3064.44</v>
-      </c>
-      <c r="S11" s="2">
+        <v>31.78</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1336.27</v>
+      </c>
+      <c r="S11" s="1">
         <f>T11-R11</f>
-        <v>47.6100000000001</v>
-      </c>
-      <c r="T11" s="2">
-        <v>3112.05</v>
-      </c>
-      <c r="U11" s="2">
+        <v>44.9000000000001</v>
+      </c>
+      <c r="T11" s="1">
+        <v>1381.17</v>
+      </c>
+      <c r="U11" s="1">
         <f>T11-D11</f>
-        <v>578.2</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="W11" s="2">
-        <v>647.97</v>
-      </c>
-      <c r="X11" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>172501</v>
+        <v>320.4</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="W11" s="1">
+        <v>275.86</v>
+      </c>
+      <c r="X11" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>71153</v>
       </c>
       <c r="AA11" s="13">
         <f>T11*10000/Z11/164.158</f>
-        <v>1.09898786419624</v>
+        <v>1.18247473011041</v>
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1966.62</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2714.1</v>
+      </c>
+      <c r="E12" s="5">
         <f>F12-D12</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2015.64</v>
-      </c>
-      <c r="G12" s="3">
+        <v>123.29</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2837.39</v>
+      </c>
+      <c r="G12" s="5">
         <f>H12-F12</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2049.8</v>
-      </c>
-      <c r="I12" s="3">
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2933.24</v>
+      </c>
+      <c r="I12" s="5">
         <f>J12-H12</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2139.9</v>
-      </c>
-      <c r="K12" s="3">
+        <v>92.46</v>
+      </c>
+      <c r="J12" s="5">
+        <v>3025.7</v>
+      </c>
+      <c r="K12" s="5">
         <f>L12-J12</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2193.07</v>
-      </c>
-      <c r="M12" s="3">
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3116.11</v>
+      </c>
+      <c r="M12" s="5">
         <f>N12-L12</f>
-        <v>63.9099999999999</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2256.98</v>
-      </c>
-      <c r="O12" s="3">
+        <v>103.54</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3219.65</v>
+      </c>
+      <c r="O12" s="5">
         <f>P12-N12</f>
-        <v>45.71</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2302.69</v>
-      </c>
-      <c r="Q12" s="3">
+        <v>75.6599999999999</v>
+      </c>
+      <c r="P12" s="5">
+        <v>3295.31</v>
+      </c>
+      <c r="Q12" s="5">
         <f>R12-P12</f>
-        <v>37.2199999999998</v>
-      </c>
-      <c r="R12" s="3">
-        <v>2339.91</v>
-      </c>
-      <c r="S12" s="3">
+        <v>88.98</v>
+      </c>
+      <c r="R12" s="5">
+        <v>3384.29</v>
+      </c>
+      <c r="S12" s="5">
         <f>T12-R12</f>
-        <v>47.3099999999999</v>
-      </c>
-      <c r="T12" s="3">
-        <v>2387.22</v>
-      </c>
-      <c r="U12" s="3">
+        <v>102.46</v>
+      </c>
+      <c r="T12" s="5">
+        <v>3486.75</v>
+      </c>
+      <c r="U12" s="5">
         <f>T12-D12</f>
-        <v>420.6</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W12" s="3">
-        <v>837.27</v>
-      </c>
-      <c r="X12" s="3">
-        <v>65</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" s="16">
-        <v>130589</v>
-      </c>
-      <c r="AA12" s="17">
+        <v>772.65</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" s="5">
+        <v>746.62</v>
+      </c>
+      <c r="X12" s="5">
+        <v>500</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>8.6</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>191519</v>
+      </c>
+      <c r="AA12" s="16">
         <f>T12*10000/Z12/164.158</f>
-        <v>1.11358608572767</v>
+        <v>1.10903918696675</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="1">
-        <v>927.15</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E13" s="2">
         <f>F13-D13</f>
-        <v>17.9300000000001</v>
-      </c>
-      <c r="F13" s="1">
-        <v>945.08</v>
-      </c>
-      <c r="G13" s="1">
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G13" s="2">
         <f>H13-F13</f>
-        <v>24.04</v>
-      </c>
-      <c r="H13" s="1">
-        <v>969.12</v>
-      </c>
-      <c r="I13" s="1">
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H13" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I13" s="2">
         <f>J13-H13</f>
-        <v>26.96</v>
-      </c>
-      <c r="J13" s="1">
-        <v>996.08</v>
-      </c>
-      <c r="K13" s="1">
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K13" s="2">
         <f>L13-J13</f>
-        <v>23.3499999999999</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1019.43</v>
-      </c>
-      <c r="M13" s="1">
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M13" s="2">
         <f>N13-L13</f>
-        <v>23.7400000000001</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1043.17</v>
-      </c>
-      <c r="O13" s="1">
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N13" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O13" s="2">
         <f>P13-N13</f>
-        <v>24.99</v>
-      </c>
-      <c r="P13" s="1">
-        <v>1068.16</v>
-      </c>
-      <c r="Q13" s="1">
+        <v>16.27</v>
+      </c>
+      <c r="P13" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q13" s="2">
         <f>R13-P13</f>
-        <v>25.3499999999999</v>
-      </c>
-      <c r="R13" s="1">
-        <v>1093.51</v>
-      </c>
-      <c r="S13" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="R13" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S13" s="2">
         <f>T13-R13</f>
-        <v>46.8499999999999</v>
-      </c>
-      <c r="T13" s="1">
-        <v>1140.36</v>
-      </c>
-      <c r="U13" s="1">
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T13" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U13" s="2">
         <f>T13-D13</f>
-        <v>213.21</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="W13" s="1">
-        <v>323.37</v>
-      </c>
-      <c r="X13" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="Z13" s="14">
-        <v>80664</v>
-      </c>
-      <c r="AA13" s="15">
+        <v>252.37</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W13" s="2">
+        <v>596.97</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>133781</v>
+      </c>
+      <c r="AA13" s="12">
         <f>T13*10000/Z13/164.158</f>
-        <v>0.86119236096077</v>
+        <v>1.10894560728839</v>
       </c>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1">
-        <v>1156.57</v>
+        <v>1576.18</v>
       </c>
       <c r="E14" s="1">
         <f>F14-D14</f>
-        <v>40.4400000000001</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>1197.01</v>
+        <v>1615.02</v>
       </c>
       <c r="G14" s="1">
         <f>H14-F14</f>
-        <v>46.97</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>1243.98</v>
+        <v>1650.62</v>
       </c>
       <c r="I14" s="1">
         <f>J14-H14</f>
-        <v>58.49</v>
+        <v>37.47</v>
       </c>
       <c r="J14" s="1">
-        <v>1302.47</v>
+        <v>1688.09</v>
       </c>
       <c r="K14" s="1">
         <f>L14-J14</f>
-        <v>36.6399999999999</v>
+        <v>21.49</v>
       </c>
       <c r="L14" s="1">
-        <v>1339.11</v>
+        <v>1709.58</v>
       </c>
       <c r="M14" s="1">
         <f>N14-L14</f>
-        <v>33.99</v>
+        <v>24.53</v>
       </c>
       <c r="N14" s="1">
-        <v>1373.1</v>
+        <v>1734.11</v>
       </c>
       <c r="O14" s="1">
         <f>P14-N14</f>
-        <v>30.0600000000002</v>
+        <v>19.5300000000002</v>
       </c>
       <c r="P14" s="1">
-        <v>1403.16</v>
+        <v>1753.64</v>
       </c>
       <c r="Q14" s="1">
         <f>R14-P14</f>
-        <v>47.3</v>
+        <v>65.1099999999999</v>
       </c>
       <c r="R14" s="1">
-        <v>1450.46</v>
+        <v>1818.75</v>
       </c>
       <c r="S14" s="1">
         <f>T14-R14</f>
-        <v>46.8299999999999</v>
+        <v>34.3699999999999</v>
       </c>
       <c r="T14" s="1">
-        <v>1497.29</v>
+        <v>1853.12</v>
       </c>
       <c r="U14" s="1">
         <f>T14-D14</f>
-        <v>340.72</v>
+        <v>276.94</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="W14" s="1">
-        <v>369.22</v>
+        <v>374.52</v>
       </c>
       <c r="X14" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="14">
-        <v>100457</v>
-      </c>
-      <c r="AA14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>127369</v>
+      </c>
+      <c r="AA14" s="13">
         <f>T14*10000/Z14/164.158</f>
-        <v>0.907953625893773</v>
+        <v>0.886293882927787</v>
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4">
-        <v>4105.48</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1350.52</v>
+      </c>
+      <c r="E15" s="1">
         <f>F15-D15</f>
-        <v>181.21</v>
-      </c>
-      <c r="F15" s="4">
-        <v>4286.69</v>
-      </c>
-      <c r="G15" s="4">
+        <v>52.6800000000001</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1403.2</v>
+      </c>
+      <c r="G15" s="1">
         <f>H15-F15</f>
-        <v>139.09</v>
-      </c>
-      <c r="H15" s="4">
-        <v>4425.78</v>
-      </c>
-      <c r="I15" s="4">
+        <v>55.3199999999999</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1458.52</v>
+      </c>
+      <c r="I15" s="1">
         <f>J15-H15</f>
-        <v>54.8800000000001</v>
-      </c>
-      <c r="J15" s="4">
-        <v>4480.66</v>
-      </c>
-      <c r="K15" s="4">
+        <v>32.6800000000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1491.2</v>
+      </c>
+      <c r="K15" s="1">
         <f>L15-J15</f>
-        <v>104.900000000001</v>
-      </c>
-      <c r="L15" s="4">
-        <v>4585.56</v>
-      </c>
-      <c r="M15" s="4">
+        <v>54.96</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1546.16</v>
+      </c>
+      <c r="M15" s="1">
         <f>N15-L15</f>
-        <v>70.29</v>
-      </c>
-      <c r="N15" s="4">
-        <v>4655.85</v>
-      </c>
-      <c r="O15" s="4">
+        <v>92.1299999999999</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1638.29</v>
+      </c>
+      <c r="O15" s="1">
         <f>P15-N15</f>
-        <v>49.1700000000001</v>
-      </c>
-      <c r="P15" s="4">
-        <v>4705.02</v>
-      </c>
-      <c r="Q15" s="4">
+        <v>59.4400000000001</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1697.73</v>
+      </c>
+      <c r="Q15" s="1">
         <f>R15-P15</f>
-        <v>38.2199999999993</v>
-      </c>
-      <c r="R15" s="4">
-        <v>4743.24</v>
-      </c>
-      <c r="S15" s="4">
+        <v>71.3399999999999</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1769.07</v>
+      </c>
+      <c r="S15" s="1">
         <f>T15-R15</f>
-        <v>45.6199999999999</v>
-      </c>
-      <c r="T15" s="4">
-        <v>4788.86</v>
-      </c>
-      <c r="U15" s="4">
+        <v>62.9000000000001</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1831.97</v>
+      </c>
+      <c r="U15" s="1">
         <f>T15-D15</f>
-        <v>683.38</v>
-      </c>
-      <c r="V15" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="W15" s="4">
-        <v>1364.72</v>
-      </c>
-      <c r="X15" s="4">
-        <v>400</v>
-      </c>
-      <c r="Y15" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" s="18">
-        <v>186759</v>
-      </c>
-      <c r="AA15" s="19">
+        <v>481.45</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="1">
+        <v>576.12</v>
+      </c>
+      <c r="X15" s="1">
+        <v>65</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>127603</v>
+      </c>
+      <c r="AA15" s="13">
         <f>T15*10000/Z15/164.158</f>
-        <v>1.56202704397778</v>
+        <v>0.8745717003899</v>
       </c>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1">
-        <v>1060.77</v>
+        <v>1156.57</v>
       </c>
       <c r="E16" s="1">
         <f>F16-D16</f>
-        <v>63.24</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>1124.01</v>
+        <v>1197.01</v>
       </c>
       <c r="G16" s="1">
         <f>H16-F16</f>
-        <v>19.6700000000001</v>
+        <v>46.97</v>
       </c>
       <c r="H16" s="1">
-        <v>1143.68</v>
+        <v>1243.98</v>
       </c>
       <c r="I16" s="1">
         <f>J16-H16</f>
-        <v>47.76</v>
+        <v>58.49</v>
       </c>
       <c r="J16" s="1">
-        <v>1191.44</v>
+        <v>1302.47</v>
       </c>
       <c r="K16" s="1">
         <f>L16-J16</f>
-        <v>40.22</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L16" s="1">
-        <v>1231.66</v>
+        <v>1339.11</v>
       </c>
       <c r="M16" s="1">
         <f>N16-L16</f>
-        <v>44.8</v>
+        <v>33.99</v>
       </c>
       <c r="N16" s="1">
-        <v>1276.46</v>
+        <v>1373.1</v>
       </c>
       <c r="O16" s="1">
         <f>P16-N16</f>
-        <v>28.03</v>
+        <v>30.0600000000002</v>
       </c>
       <c r="P16" s="1">
-        <v>1304.49</v>
+        <v>1403.16</v>
       </c>
       <c r="Q16" s="1">
         <f>R16-P16</f>
-        <v>31.78</v>
+        <v>47.3</v>
       </c>
       <c r="R16" s="1">
-        <v>1336.27</v>
+        <v>1450.46</v>
       </c>
       <c r="S16" s="1">
         <f>T16-R16</f>
-        <v>44.9000000000001</v>
+        <v>46.8299999999999</v>
       </c>
       <c r="T16" s="1">
-        <v>1381.17</v>
+        <v>1497.29</v>
       </c>
       <c r="U16" s="1">
         <f>T16-D16</f>
-        <v>320.4</v>
+        <v>340.72</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="W16" s="1">
-        <v>275.86</v>
+        <v>369.22</v>
       </c>
       <c r="X16" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Y16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" s="14">
-        <v>71153</v>
-      </c>
-      <c r="AA16" s="15">
+        <v>3</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>100457</v>
+      </c>
+      <c r="AA16" s="13">
         <f>T16*10000/Z16/164.158</f>
-        <v>1.18247473011041</v>
+        <v>0.907953625893773</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
-        <v>953.78</v>
+        <v>907.94</v>
       </c>
       <c r="E17" s="1">
         <f>F17-D17</f>
-        <v>28.97</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>982.75</v>
+        <v>972.02</v>
       </c>
       <c r="G17" s="1">
         <f>H17-F17</f>
-        <v>83.9300000000001</v>
+        <v>36.26</v>
       </c>
       <c r="H17" s="1">
-        <v>1066.68</v>
+        <v>1008.28</v>
       </c>
       <c r="I17" s="1">
         <f>J17-H17</f>
-        <v>42.8399999999999</v>
+        <v>28.8</v>
       </c>
       <c r="J17" s="1">
-        <v>1109.52</v>
+        <v>1037.08</v>
       </c>
       <c r="K17" s="1">
         <f>L17-J17</f>
-        <v>36.46</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L17" s="1">
-        <v>1145.98</v>
+        <v>1077.18</v>
       </c>
       <c r="M17" s="1">
         <f>N17-L17</f>
-        <v>37.49</v>
+        <v>26.03</v>
       </c>
       <c r="N17" s="1">
-        <v>1183.47</v>
+        <v>1103.21</v>
       </c>
       <c r="O17" s="1">
         <f>P17-N17</f>
-        <v>33.3699999999999</v>
+        <v>28.3499999999999</v>
       </c>
       <c r="P17" s="1">
-        <v>1216.84</v>
+        <v>1131.56</v>
       </c>
       <c r="Q17" s="1">
         <f>R17-P17</f>
-        <v>24.8900000000001</v>
+        <v>50.1900000000001</v>
       </c>
       <c r="R17" s="1">
-        <v>1241.73</v>
+        <v>1181.75</v>
       </c>
       <c r="S17" s="1">
         <f>T17-R17</f>
-        <v>42.3099999999999</v>
+        <v>26.8699999999999</v>
       </c>
       <c r="T17" s="1">
-        <v>1284.04</v>
+        <v>1208.62</v>
       </c>
       <c r="U17" s="1">
         <f>T17-D17</f>
-        <v>330.26</v>
+        <v>300.68</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="W17" s="1">
-        <v>455.12</v>
+        <v>403.82</v>
       </c>
       <c r="X17" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Y17" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="14">
-        <v>105419</v>
-      </c>
-      <c r="AA17" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>65285</v>
+      </c>
+      <c r="AA17" s="13">
         <f>T17*10000/Z17/164.158</f>
-        <v>0.741989241844566</v>
+        <v>1.1277538433989</v>
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="1">
-        <v>950.09</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="A18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3">
+        <v>363.88</v>
+      </c>
+      <c r="E18" s="3">
         <f>F18-D18</f>
-        <v>42.4</v>
-      </c>
-      <c r="F18" s="1">
-        <v>992.49</v>
-      </c>
-      <c r="G18" s="1">
+        <v>14.21</v>
+      </c>
+      <c r="F18" s="3">
+        <v>378.09</v>
+      </c>
+      <c r="G18" s="3">
         <f>H18-F18</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1031.08</v>
-      </c>
-      <c r="I18" s="1">
+        <v>11.22</v>
+      </c>
+      <c r="H18" s="3">
+        <v>389.31</v>
+      </c>
+      <c r="I18" s="3">
         <f>J18-H18</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1053.68</v>
-      </c>
-      <c r="K18" s="1">
+        <v>13.62</v>
+      </c>
+      <c r="J18" s="3">
+        <v>402.93</v>
+      </c>
+      <c r="K18" s="3">
         <f>L18-J18</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L18" s="1">
-        <v>1064.61</v>
-      </c>
-      <c r="M18" s="1">
+        <v>11.13</v>
+      </c>
+      <c r="L18" s="3">
+        <v>414.06</v>
+      </c>
+      <c r="M18" s="3">
         <f>N18-L18</f>
-        <v>16.1800000000001</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1080.79</v>
-      </c>
-      <c r="O18" s="1">
+        <v>17.39</v>
+      </c>
+      <c r="N18" s="3">
+        <v>431.45</v>
+      </c>
+      <c r="O18" s="3">
         <f>P18-N18</f>
-        <v>13.6700000000001</v>
-      </c>
-      <c r="P18" s="1">
-        <v>1094.46</v>
-      </c>
-      <c r="Q18" s="1">
+        <v>6.32999999999998</v>
+      </c>
+      <c r="P18" s="3">
+        <v>437.78</v>
+      </c>
+      <c r="Q18" s="3">
         <f>R18-P18</f>
-        <v>56.26</v>
-      </c>
-      <c r="R18" s="1">
-        <v>1150.72</v>
-      </c>
-      <c r="S18" s="1">
+        <v>53.01</v>
+      </c>
+      <c r="R18" s="3">
+        <v>490.79</v>
+      </c>
+      <c r="S18" s="3">
         <f>T18-R18</f>
-        <v>41.27</v>
-      </c>
-      <c r="T18" s="1">
-        <v>1191.99</v>
-      </c>
-      <c r="U18" s="1">
+        <v>11.82</v>
+      </c>
+      <c r="T18" s="3">
+        <v>502.61</v>
+      </c>
+      <c r="U18" s="3">
         <f>T18-D18</f>
-        <v>241.9</v>
-      </c>
-      <c r="V18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="W18" s="1">
-        <v>457.32</v>
-      </c>
-      <c r="X18" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>2.2</v>
-      </c>
-      <c r="Z18" s="14">
-        <v>86194</v>
-      </c>
-      <c r="AA18" s="15">
+        <v>138.73</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18" s="3">
+        <v>139.29</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>47256</v>
+      </c>
+      <c r="AA18" s="14">
         <f>T18*10000/Z18/164.158</f>
-        <v>0.842429418076795</v>
+        <v>0.647906168874828</v>
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1446.65</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="A19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2533.85</v>
+      </c>
+      <c r="E19" s="5">
         <f>F19-D19</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1474.83</v>
-      </c>
-      <c r="G19" s="1">
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2583.9</v>
+      </c>
+      <c r="G19" s="5">
         <f>H19-F19</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1538.65</v>
-      </c>
-      <c r="I19" s="1">
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2669.66</v>
+      </c>
+      <c r="I19" s="5">
         <f>J19-H19</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1561.57</v>
-      </c>
-      <c r="K19" s="1">
+        <v>81.79</v>
+      </c>
+      <c r="J19" s="5">
+        <v>2751.45</v>
+      </c>
+      <c r="K19" s="5">
         <f>L19-J19</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1632.43</v>
-      </c>
-      <c r="M19" s="1">
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2834.62</v>
+      </c>
+      <c r="M19" s="5">
         <f>N19-L19</f>
-        <v>37.4099999999999</v>
-      </c>
-      <c r="N19" s="1">
-        <v>1669.84</v>
-      </c>
-      <c r="O19" s="1">
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N19" s="5">
+        <v>2891.61</v>
+      </c>
+      <c r="O19" s="5">
         <f>P19-N19</f>
-        <v>32.8300000000002</v>
-      </c>
-      <c r="P19" s="1">
-        <v>1702.67</v>
-      </c>
-      <c r="Q19" s="1">
+        <v>103.98</v>
+      </c>
+      <c r="P19" s="5">
+        <v>2995.59</v>
+      </c>
+      <c r="Q19" s="5">
         <f>R19-P19</f>
-        <v>51.9499999999998</v>
-      </c>
-      <c r="R19" s="1">
-        <v>1754.62</v>
-      </c>
-      <c r="S19" s="1">
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R19" s="5">
+        <v>3064.44</v>
+      </c>
+      <c r="S19" s="5">
         <f>T19-R19</f>
-        <v>40.1200000000001</v>
-      </c>
-      <c r="T19" s="1">
-        <v>1794.74</v>
-      </c>
-      <c r="U19" s="1">
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T19" s="5">
+        <v>3112.05</v>
+      </c>
+      <c r="U19" s="5">
         <f>T19-D19</f>
-        <v>348.09</v>
-      </c>
-      <c r="V19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="W19" s="1">
-        <v>687.67</v>
-      </c>
-      <c r="X19" s="1">
-        <v>65</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" s="14">
-        <v>109333</v>
-      </c>
-      <c r="AA19" s="15">
+        <v>578.2</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="W19" s="5">
+        <v>647.97</v>
+      </c>
+      <c r="X19" s="5">
+        <v>200</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>172501</v>
+      </c>
+      <c r="AA19" s="16">
         <f>T19*10000/Z19/164.158</f>
-        <v>0.999972887392791</v>
+        <v>1.09898786419624</v>
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1576.18</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="A20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="3">
+        <v>552.79</v>
+      </c>
+      <c r="E20" s="3">
         <f>F20-D20</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1615.02</v>
-      </c>
-      <c r="G20" s="1">
+        <v>15.9400000000001</v>
+      </c>
+      <c r="F20" s="3">
+        <v>568.73</v>
+      </c>
+      <c r="G20" s="3">
         <f>H20-F20</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1650.62</v>
-      </c>
-      <c r="I20" s="1">
+        <v>1.61000000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <v>570.34</v>
+      </c>
+      <c r="I20" s="3">
         <f>J20-H20</f>
-        <v>37.47</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1688.09</v>
-      </c>
-      <c r="K20" s="1">
+        <v>7.13999999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>577.48</v>
+      </c>
+      <c r="K20" s="3">
         <f>L20-J20</f>
-        <v>21.49</v>
-      </c>
-      <c r="L20" s="1">
-        <v>1709.58</v>
-      </c>
-      <c r="M20" s="1">
+        <v>2.88999999999999</v>
+      </c>
+      <c r="L20" s="3">
+        <v>580.37</v>
+      </c>
+      <c r="M20" s="3">
         <f>N20-L20</f>
-        <v>24.53</v>
-      </c>
-      <c r="N20" s="1">
-        <v>1734.11</v>
-      </c>
-      <c r="O20" s="1">
+        <v>2.55999999999995</v>
+      </c>
+      <c r="N20" s="3">
+        <v>582.93</v>
+      </c>
+      <c r="O20" s="3">
         <f>P20-N20</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P20" s="1">
-        <v>1753.64</v>
-      </c>
-      <c r="Q20" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="P20" s="3">
+        <v>607.92</v>
+      </c>
+      <c r="Q20" s="3">
         <f>R20-P20</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R20" s="1">
-        <v>1818.75</v>
-      </c>
-      <c r="S20" s="1">
+        <v>0.330000000000041</v>
+      </c>
+      <c r="R20" s="3">
+        <v>608.25</v>
+      </c>
+      <c r="S20" s="3">
         <f>T20-R20</f>
-        <v>34.3699999999999</v>
-      </c>
-      <c r="T20" s="1">
-        <v>1853.12</v>
-      </c>
-      <c r="U20" s="1">
+        <v>1.80999999999995</v>
+      </c>
+      <c r="T20" s="3">
+        <v>610.06</v>
+      </c>
+      <c r="U20" s="3">
         <f>T20-D20</f>
-        <v>276.94</v>
-      </c>
-      <c r="V20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="W20" s="1">
-        <v>374.52</v>
-      </c>
-      <c r="X20" s="1">
+        <v>57.27</v>
+      </c>
+      <c r="V20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W20" s="3">
+        <v>131.95</v>
+      </c>
+      <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="14">
-        <v>127369</v>
-      </c>
-      <c r="AA20" s="15">
+      <c r="Y20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>49654</v>
+      </c>
+      <c r="AA20" s="14">
         <f>T20*10000/Z20/164.158</f>
-        <v>0.886293882927787</v>
+        <v>0.74843873870761</v>
       </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
-        <v>907.94</v>
+        <v>953.78</v>
       </c>
       <c r="E21" s="1">
         <f>F21-D21</f>
-        <v>64.0799999999999</v>
+        <v>28.97</v>
       </c>
       <c r="F21" s="1">
-        <v>972.02</v>
+        <v>982.75</v>
       </c>
       <c r="G21" s="1">
         <f>H21-F21</f>
-        <v>36.26</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>1008.28</v>
+        <v>1066.68</v>
       </c>
       <c r="I21" s="1">
         <f>J21-H21</f>
-        <v>28.8</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J21" s="1">
-        <v>1037.08</v>
+        <v>1109.52</v>
       </c>
       <c r="K21" s="1">
         <f>L21-J21</f>
-        <v>40.1000000000001</v>
+        <v>36.46</v>
       </c>
       <c r="L21" s="1">
-        <v>1077.18</v>
+        <v>1145.98</v>
       </c>
       <c r="M21" s="1">
         <f>N21-L21</f>
-        <v>26.03</v>
+        <v>37.49</v>
       </c>
       <c r="N21" s="1">
-        <v>1103.21</v>
+        <v>1183.47</v>
       </c>
       <c r="O21" s="1">
         <f>P21-N21</f>
-        <v>28.3499999999999</v>
+        <v>33.3699999999999</v>
       </c>
       <c r="P21" s="1">
-        <v>1131.56</v>
+        <v>1216.84</v>
       </c>
       <c r="Q21" s="1">
         <f>R21-P21</f>
-        <v>50.1900000000001</v>
+        <v>24.8900000000001</v>
       </c>
       <c r="R21" s="1">
-        <v>1181.75</v>
+        <v>1241.73</v>
       </c>
       <c r="S21" s="1">
         <f>T21-R21</f>
-        <v>26.8699999999999</v>
+        <v>42.3099999999999</v>
       </c>
       <c r="T21" s="1">
-        <v>1208.62</v>
+        <v>1284.04</v>
       </c>
       <c r="U21" s="1">
         <f>T21-D21</f>
-        <v>300.68</v>
+        <v>330.26</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="W21" s="1">
-        <v>403.82</v>
+        <v>455.12</v>
       </c>
       <c r="X21" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Y21" s="1">
-        <v>8.2</v>
-      </c>
-      <c r="Z21" s="14">
-        <v>65285</v>
-      </c>
-      <c r="AA21" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>105419</v>
+      </c>
+      <c r="AA21" s="13">
         <f>T21*10000/Z21/164.158</f>
-        <v>1.1277538433989</v>
+        <v>0.741989241844566</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1">
-        <v>848.93</v>
+        <v>927.15</v>
       </c>
       <c r="E22" s="1">
         <f>F22-D22</f>
-        <v>34.5600000000001</v>
+        <v>17.9300000000001</v>
       </c>
       <c r="F22" s="1">
-        <v>883.49</v>
+        <v>945.08</v>
       </c>
       <c r="G22" s="1">
         <f>H22-F22</f>
-        <v>46.08</v>
+        <v>24.04</v>
       </c>
       <c r="H22" s="1">
-        <v>929.57</v>
+        <v>969.12</v>
       </c>
       <c r="I22" s="1">
         <f>J22-H22</f>
-        <v>27.7399999999999</v>
+        <v>26.96</v>
       </c>
       <c r="J22" s="1">
-        <v>957.31</v>
+        <v>996.08</v>
       </c>
       <c r="K22" s="1">
         <f>L22-J22</f>
-        <v>47.36</v>
+        <v>23.3499999999999</v>
       </c>
       <c r="L22" s="1">
-        <v>1004.67</v>
+        <v>1019.43</v>
       </c>
       <c r="M22" s="1">
         <f>N22-L22</f>
-        <v>25.9399999999999</v>
+        <v>23.7400000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>1030.61</v>
+        <v>1043.17</v>
       </c>
       <c r="O22" s="1">
         <f>P22-N22</f>
-        <v>37.71</v>
+        <v>24.99</v>
       </c>
       <c r="P22" s="1">
-        <v>1068.32</v>
+        <v>1068.16</v>
       </c>
       <c r="Q22" s="1">
         <f>R22-P22</f>
-        <v>18.3800000000001</v>
+        <v>25.3499999999999</v>
       </c>
       <c r="R22" s="1">
-        <v>1086.7</v>
+        <v>1093.51</v>
       </c>
       <c r="S22" s="1">
         <f>T22-R22</f>
-        <v>21.04</v>
+        <v>46.8499999999999</v>
       </c>
       <c r="T22" s="1">
-        <v>1107.74</v>
+        <v>1140.36</v>
       </c>
       <c r="U22" s="1">
         <f>T22-D22</f>
-        <v>258.81</v>
+        <v>213.21</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="W22" s="1">
-        <v>378.87</v>
+        <v>323.37</v>
       </c>
       <c r="X22" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="Z22" s="14">
-        <v>78989</v>
-      </c>
-      <c r="AA22" s="15">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>80664</v>
+      </c>
+      <c r="AA22" s="13">
         <f>T22*10000/Z22/164.158</f>
-        <v>0.854297568333938</v>
+        <v>0.86119236096077</v>
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="A23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="3">
         <v>262.39</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="3">
         <f>F23-D23</f>
         <v>11.5</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="3">
         <v>273.89</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="3">
         <f>H23-F23</f>
         <v>13.97</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="3">
         <v>287.86</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <f>J23-H23</f>
         <v>16.24</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="3">
         <v>304.1</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="3">
         <f>L23-J23</f>
         <v>12.65</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="3">
         <v>316.75</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="3">
         <f>N23-L23</f>
         <v>9.99000000000001</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="3">
         <v>326.74</v>
       </c>
-      <c r="O23" s="5">
+      <c r="O23" s="3">
         <f>P23-N23</f>
         <v>6.31999999999999</v>
       </c>
-      <c r="P23" s="5">
+      <c r="P23" s="3">
         <v>333.06</v>
       </c>
-      <c r="Q23" s="5">
+      <c r="Q23" s="3">
         <f>R23-P23</f>
         <v>21.13</v>
       </c>
-      <c r="R23" s="5">
+      <c r="R23" s="3">
         <v>354.19</v>
       </c>
-      <c r="S23" s="5">
+      <c r="S23" s="3">
         <f>T23-R23</f>
         <v>17.68</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="3">
         <v>371.87</v>
       </c>
-      <c r="U23" s="5">
+      <c r="U23" s="3">
         <f>T23-D23</f>
         <v>109.48</v>
       </c>
-      <c r="V23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="W23" s="5">
+      <c r="V23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W23" s="3">
         <v>130.16</v>
       </c>
-      <c r="X23" s="5">
+      <c r="X23" s="3">
         <v>0</v>
       </c>
-      <c r="Y23" s="5">
+      <c r="Y23" s="3">
         <v>1</v>
       </c>
-      <c r="Z23" s="20">
+      <c r="Z23" s="3">
         <v>36684</v>
       </c>
-      <c r="AA23" s="21">
+      <c r="AA23" s="14">
         <f>T23*10000/Z23/164.158</f>
         <v>0.617521960503705</v>
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5">
-        <v>407.35</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1735.94</v>
+      </c>
+      <c r="E24" s="2">
         <f>F24-D24</f>
-        <v>13.86</v>
-      </c>
-      <c r="F24" s="5">
-        <v>421.21</v>
-      </c>
-      <c r="G24" s="5">
+        <v>48.5999999999999</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1784.54</v>
+      </c>
+      <c r="G24" s="2">
         <f>H24-F24</f>
-        <v>16.43</v>
-      </c>
-      <c r="H24" s="5">
-        <v>437.64</v>
-      </c>
-      <c r="I24" s="5">
+        <v>74.1600000000001</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1858.7</v>
+      </c>
+      <c r="I24" s="2">
         <f>J24-H24</f>
-        <v>13.64</v>
-      </c>
-      <c r="J24" s="5">
-        <v>451.28</v>
-      </c>
-      <c r="K24" s="5">
+        <v>65.55</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1924.25</v>
+      </c>
+      <c r="K24" s="2">
         <f>L24-J24</f>
-        <v>11.6</v>
-      </c>
-      <c r="L24" s="5">
-        <v>462.88</v>
-      </c>
-      <c r="M24" s="5">
+        <v>35.73</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1959.98</v>
+      </c>
+      <c r="M24" s="2">
         <f>N24-L24</f>
-        <v>47.68</v>
-      </c>
-      <c r="N24" s="5">
-        <v>510.56</v>
-      </c>
-      <c r="O24" s="5">
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N24" s="2">
+        <v>2001.86</v>
+      </c>
+      <c r="O24" s="2">
         <f>P24-N24</f>
-        <v>20.51</v>
-      </c>
-      <c r="P24" s="5">
-        <v>531.07</v>
-      </c>
-      <c r="Q24" s="5">
+        <v>74.6600000000001</v>
+      </c>
+      <c r="P24" s="2">
+        <v>2076.52</v>
+      </c>
+      <c r="Q24" s="2">
         <f>R24-P24</f>
-        <v>18.6099999999999</v>
-      </c>
-      <c r="R24" s="5">
-        <v>549.68</v>
-      </c>
-      <c r="S24" s="5">
+        <v>48.71</v>
+      </c>
+      <c r="R24" s="2">
+        <v>2125.23</v>
+      </c>
+      <c r="S24" s="2">
         <f>T24-R24</f>
-        <v>11.9400000000001</v>
-      </c>
-      <c r="T24" s="5">
-        <v>561.62</v>
-      </c>
-      <c r="U24" s="5">
+        <v>57.4200000000001</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2182.65</v>
+      </c>
+      <c r="U24" s="2">
         <f>T24-D24</f>
-        <v>154.27</v>
-      </c>
-      <c r="V24" s="11" t="s">
+        <v>446.71</v>
+      </c>
+      <c r="V24" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="W24" s="5">
-        <v>237.66</v>
-      </c>
-      <c r="X24" s="5">
-        <v>30</v>
-      </c>
-      <c r="Y24" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="Z24" s="20">
-        <v>43895</v>
-      </c>
-      <c r="AA24" s="21">
+      <c r="W24" s="2">
+        <v>515.22</v>
+      </c>
+      <c r="X24" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>150192</v>
+      </c>
+      <c r="AA24" s="12">
         <f>T24*10000/Z24/164.158</f>
-        <v>0.779409077439543</v>
+        <v>0.885268980487198</v>
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="5">
-        <v>363.88</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1446.65</v>
+      </c>
+      <c r="E25" s="1">
         <f>F25-D25</f>
-        <v>14.21</v>
-      </c>
-      <c r="F25" s="5">
-        <v>378.09</v>
-      </c>
-      <c r="G25" s="5">
+        <v>28.1799999999998</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1474.83</v>
+      </c>
+      <c r="G25" s="1">
         <f>H25-F25</f>
-        <v>11.22</v>
-      </c>
-      <c r="H25" s="5">
-        <v>389.31</v>
-      </c>
-      <c r="I25" s="5">
+        <v>63.8200000000002</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1538.65</v>
+      </c>
+      <c r="I25" s="1">
         <f>J25-H25</f>
-        <v>13.62</v>
-      </c>
-      <c r="J25" s="5">
-        <v>402.93</v>
-      </c>
-      <c r="K25" s="5">
+        <v>22.9199999999998</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1561.57</v>
+      </c>
+      <c r="K25" s="1">
         <f>L25-J25</f>
-        <v>11.13</v>
-      </c>
-      <c r="L25" s="5">
-        <v>414.06</v>
-      </c>
-      <c r="M25" s="5">
+        <v>70.8600000000001</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1632.43</v>
+      </c>
+      <c r="M25" s="1">
         <f>N25-L25</f>
-        <v>17.39</v>
-      </c>
-      <c r="N25" s="5">
-        <v>431.45</v>
-      </c>
-      <c r="O25" s="5">
+        <v>37.4099999999999</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1669.84</v>
+      </c>
+      <c r="O25" s="1">
         <f>P25-N25</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P25" s="5">
-        <v>437.78</v>
-      </c>
-      <c r="Q25" s="5">
+        <v>32.8300000000002</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1702.67</v>
+      </c>
+      <c r="Q25" s="1">
         <f>R25-P25</f>
-        <v>53.01</v>
-      </c>
-      <c r="R25" s="5">
-        <v>490.79</v>
-      </c>
-      <c r="S25" s="5">
+        <v>51.9499999999998</v>
+      </c>
+      <c r="R25" s="1">
+        <v>1754.62</v>
+      </c>
+      <c r="S25" s="1">
         <f>T25-R25</f>
-        <v>11.82</v>
-      </c>
-      <c r="T25" s="5">
-        <v>502.61</v>
-      </c>
-      <c r="U25" s="5">
+        <v>40.1200000000001</v>
+      </c>
+      <c r="T25" s="1">
+        <v>1794.74</v>
+      </c>
+      <c r="U25" s="1">
         <f>T25-D25</f>
-        <v>138.73</v>
-      </c>
-      <c r="V25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="W25" s="5">
-        <v>139.29</v>
-      </c>
-      <c r="X25" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="20">
-        <v>47256</v>
-      </c>
-      <c r="AA25" s="21">
+        <v>348.09</v>
+      </c>
+      <c r="V25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W25" s="1">
+        <v>687.67</v>
+      </c>
+      <c r="X25" s="1">
+        <v>65</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>109333</v>
+      </c>
+      <c r="AA25" s="13">
         <f>T25*10000/Z25/164.158</f>
-        <v>0.647906168874828</v>
+        <v>0.999972887392791</v>
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="A26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="3">
         <v>305.29</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="3">
         <f>F26-D26</f>
         <v>17.97</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="3">
         <v>323.26</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="3">
         <f>H26-F26</f>
         <v>10.82</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="3">
         <v>334.08</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="3">
         <f>J26-H26</f>
         <v>16.2</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="3">
         <v>350.28</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="3">
         <f>L26-J26</f>
         <v>10.8</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="3">
         <v>361.08</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="3">
         <f>N26-L26</f>
         <v>9.98000000000002</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="3">
         <v>371.06</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="3">
         <f>P26-N26</f>
         <v>10.17</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="3">
         <v>381.23</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q26" s="3">
         <f>R26-P26</f>
         <v>20.97</v>
       </c>
-      <c r="R26" s="5">
+      <c r="R26" s="3">
         <v>402.2</v>
       </c>
-      <c r="S26" s="5">
+      <c r="S26" s="3">
         <f>T26-R26</f>
         <v>5.68000000000001</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="3">
         <v>407.88</v>
       </c>
-      <c r="U26" s="5">
+      <c r="U26" s="3">
         <f>T26-D26</f>
         <v>102.59</v>
       </c>
-      <c r="V26" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="W26" s="5">
+      <c r="V26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W26" s="3">
         <v>114.59</v>
       </c>
-      <c r="X26" s="5">
+      <c r="X26" s="3">
         <v>0</v>
       </c>
-      <c r="Y26" s="5">
+      <c r="Y26" s="3">
         <v>1</v>
       </c>
-      <c r="Z26" s="20">
+      <c r="Z26" s="3">
         <v>28066</v>
       </c>
-      <c r="AA26" s="21">
+      <c r="AA26" s="14">
         <f>T26*10000/Z26/164.158</f>
         <v>0.885298722383714</v>
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="5">
-        <v>552.79</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="C27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="1">
+        <v>950.09</v>
+      </c>
+      <c r="E27" s="1">
         <f>F27-D27</f>
-        <v>15.9400000000001</v>
-      </c>
-      <c r="F27" s="5">
-        <v>568.73</v>
-      </c>
-      <c r="G27" s="5">
+        <v>42.4</v>
+      </c>
+      <c r="F27" s="1">
+        <v>992.49</v>
+      </c>
+      <c r="G27" s="1">
         <f>H27-F27</f>
-        <v>1.61000000000001</v>
-      </c>
-      <c r="H27" s="5">
-        <v>570.34</v>
-      </c>
-      <c r="I27" s="5">
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1031.08</v>
+      </c>
+      <c r="I27" s="1">
         <f>J27-H27</f>
-        <v>7.13999999999999</v>
-      </c>
-      <c r="J27" s="5">
-        <v>577.48</v>
-      </c>
-      <c r="K27" s="5">
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1053.68</v>
+      </c>
+      <c r="K27" s="1">
         <f>L27-J27</f>
-        <v>2.88999999999999</v>
-      </c>
-      <c r="L27" s="5">
-        <v>580.37</v>
-      </c>
-      <c r="M27" s="5">
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1064.61</v>
+      </c>
+      <c r="M27" s="1">
         <f>N27-L27</f>
-        <v>2.55999999999995</v>
-      </c>
-      <c r="N27" s="5">
-        <v>582.93</v>
-      </c>
-      <c r="O27" s="5">
+        <v>16.1800000000001</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1080.79</v>
+      </c>
+      <c r="O27" s="1">
         <f>P27-N27</f>
-        <v>24.99</v>
-      </c>
-      <c r="P27" s="5">
-        <v>607.92</v>
-      </c>
-      <c r="Q27" s="5">
+        <v>13.6700000000001</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1094.46</v>
+      </c>
+      <c r="Q27" s="1">
         <f>R27-P27</f>
-        <v>0.330000000000041</v>
-      </c>
-      <c r="R27" s="5">
-        <v>608.25</v>
-      </c>
-      <c r="S27" s="5">
+        <v>56.26</v>
+      </c>
+      <c r="R27" s="1">
+        <v>1150.72</v>
+      </c>
+      <c r="S27" s="1">
         <f>T27-R27</f>
-        <v>1.80999999999995</v>
-      </c>
-      <c r="T27" s="5">
-        <v>610.06</v>
-      </c>
-      <c r="U27" s="5">
+        <v>41.27</v>
+      </c>
+      <c r="T27" s="1">
+        <v>1191.99</v>
+      </c>
+      <c r="U27" s="1">
         <f>T27-D27</f>
-        <v>57.27</v>
-      </c>
-      <c r="V27" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="W27" s="5">
-        <v>131.95</v>
-      </c>
-      <c r="X27" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="Z27" s="20">
-        <v>49654</v>
-      </c>
-      <c r="AA27" s="21">
+        <v>241.9</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="W27" s="1">
+        <v>457.32</v>
+      </c>
+      <c r="X27" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>86194</v>
+      </c>
+      <c r="AA27" s="13">
         <f>T27*10000/Z27/164.158</f>
-        <v>0.74843873870761</v>
+        <v>0.842429418076795</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="30" spans="1:23">
+      <c r="A30" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1317.56</v>
-      </c>
-      <c r="E28" s="1">
-        <f>F28-D28</f>
-        <v>15.77</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1333.33</v>
-      </c>
-      <c r="G28" s="1">
-        <f>H28-F28</f>
-        <v>15.1700000000001</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1348.5</v>
-      </c>
-      <c r="I28" s="1">
-        <f>J28-H28</f>
-        <v>28.9300000000001</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1377.43</v>
-      </c>
-      <c r="K28" s="1">
-        <f>L28-J28</f>
-        <v>9.14999999999986</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1386.58</v>
-      </c>
-      <c r="M28" s="1">
-        <f>N28-L28</f>
-        <v>29.4100000000001</v>
-      </c>
-      <c r="N28" s="1">
-        <v>1415.99</v>
-      </c>
-      <c r="O28" s="1">
-        <f>P28-N28</f>
-        <v>8.81999999999994</v>
-      </c>
-      <c r="P28" s="1">
-        <v>1424.81</v>
-      </c>
-      <c r="Q28" s="1">
-        <f>R28-P28</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>1424.81</v>
-      </c>
-      <c r="S28" s="1">
-        <f>T28-R28</f>
-        <v>0</v>
-      </c>
-      <c r="T28" s="1">
-        <v>1424.81</v>
-      </c>
-      <c r="U28" s="1">
-        <f>T28-D28</f>
-        <v>107.25</v>
-      </c>
-      <c r="V28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="W28" s="1">
-        <v>271.82</v>
-      </c>
-      <c r="X28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="14">
-        <v>136029</v>
-      </c>
-      <c r="AA28" s="15">
-        <f>T28*10000/Z28/164.158</f>
-        <v>0.638062758131816</v>
-      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
+      <c r="P31" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
@@ -3985,67 +3892,57 @@
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="P32" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>78</v>
       </c>
+      <c r="C33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
         <v>81</v>
@@ -4053,7 +3950,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>82</v>
@@ -4069,35 +3966,27 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
         <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AA28">
-    <sortCondition ref="S2" descending="1"/>
+  <sortState ref="A2:AA27">
+    <sortCondition ref="A2"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="P32:X32"/>
-    <mergeCell ref="C34:V34"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="C33:V33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4109,7 +3998,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4121,7 +4010,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="104">
   <si>
     <t>区服</t>
   </si>
@@ -76,6 +76,9 @@
     <t>战力（2025.5.28）</t>
   </si>
   <si>
+    <t>战力（2025.6.4）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -94,166 +97,166 @@
     <t>抽卡数</t>
   </si>
   <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>白处尊（养神）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>狐狸（快攻）</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
     <t>KB</t>
   </si>
   <si>
-    <t>大氪</t>
-  </si>
-  <si>
     <t>圣母（杂糅）</t>
   </si>
   <si>
-    <t>148区</t>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>秋雨</t>
   </si>
   <si>
     <t>大核桃</t>
   </si>
   <si>
-    <t>中大氪</t>
-  </si>
-  <si>
     <t>眼镜妹（跳费）</t>
   </si>
   <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>瓦斯兰（快攻）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
     <t>水煮肉片</t>
   </si>
   <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>白处尊（养神）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
     <t>桃太郎</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -992,7 +995,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1011,29 +1014,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1351,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB39"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1372,19 +1390,18 @@
     <col min="16" max="16" width="16.3583333333333" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="16.9916666666667" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="17.8666666666667" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="18.0166666666667" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="18.0166666666667" customWidth="1"/>
-    <col min="21" max="21" width="16.625" customWidth="1"/>
+    <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="17.3916666666667" customWidth="1"/>
-    <col min="23" max="23" width="18.0166666666667" customWidth="1"/>
-    <col min="24" max="24" width="18.8916666666667" customWidth="1"/>
-    <col min="25" max="25" width="14.5416666666667" customWidth="1"/>
-    <col min="26" max="26" width="11.625" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="25" width="18.0166666666667" customWidth="1"/>
+    <col min="26" max="26" width="18.8916666666667" customWidth="1"/>
+    <col min="27" max="27" width="14.5416666666667" customWidth="1"/>
+    <col min="28" max="28" width="11.625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1452,697 +1469,752 @@
         <v>13</v>
       </c>
       <c r="W1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:28">
-      <c r="A2" s="6" t="s">
+      <c r="AD1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:30">
+      <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="6">
-        <v>4105.48</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1754.54</v>
+      </c>
+      <c r="E2" s="2">
         <f>F2-D2</f>
-        <v>181.21</v>
-      </c>
-      <c r="F2" s="6">
-        <v>4286.69</v>
-      </c>
-      <c r="G2" s="6">
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1807.91</v>
+      </c>
+      <c r="G2" s="2">
         <f>H2-F2</f>
-        <v>139.09</v>
-      </c>
-      <c r="H2" s="6">
-        <v>4425.78</v>
-      </c>
-      <c r="I2" s="6">
+        <v>90.24</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1898.15</v>
+      </c>
+      <c r="I2" s="2">
         <f>J2-H2</f>
-        <v>54.8800000000001</v>
-      </c>
-      <c r="J2" s="6">
-        <v>4480.66</v>
-      </c>
-      <c r="K2" s="6">
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1988.53</v>
+      </c>
+      <c r="K2" s="2">
         <f>L2-J2</f>
-        <v>104.900000000001</v>
-      </c>
-      <c r="L2" s="6">
-        <v>4585.56</v>
-      </c>
-      <c r="M2" s="6">
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2048.24</v>
+      </c>
+      <c r="M2" s="2">
         <f>N2-L2</f>
-        <v>70.29</v>
-      </c>
-      <c r="N2" s="6">
-        <v>4655.85</v>
-      </c>
-      <c r="O2" s="6">
+        <v>153.99</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2202.23</v>
+      </c>
+      <c r="O2" s="2">
         <f>P2-N2</f>
-        <v>49.1700000000001</v>
-      </c>
-      <c r="P2" s="6">
-        <v>4705.02</v>
-      </c>
-      <c r="Q2" s="6">
+        <v>64.21</v>
+      </c>
+      <c r="P2" s="2">
+        <v>2266.44</v>
+      </c>
+      <c r="Q2" s="2">
         <f>R2-P2</f>
-        <v>38.2199999999993</v>
-      </c>
-      <c r="R2" s="6">
-        <v>4743.24</v>
-      </c>
-      <c r="S2" s="6">
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2314</v>
+      </c>
+      <c r="S2" s="2">
         <f>T2-R2</f>
-        <v>45.6199999999999</v>
-      </c>
-      <c r="T2" s="6">
-        <v>4788.86</v>
-      </c>
-      <c r="U2" s="6">
+        <v>59.6500000000001</v>
+      </c>
+      <c r="T2" s="2">
+        <v>2373.65</v>
+      </c>
+      <c r="U2" s="2">
         <f>V2-T2</f>
-        <v>27.5900000000001</v>
-      </c>
-      <c r="V2" s="6">
-        <v>4816.45</v>
-      </c>
-      <c r="W2" s="6">
-        <f>V2-D2</f>
-        <v>710.97</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>1376.82</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>400</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>186759</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
-      <c r="A3" s="1" t="s">
+        <v>70.6399999999999</v>
+      </c>
+      <c r="V2" s="8">
+        <v>2444.29</v>
+      </c>
+      <c r="W2" s="2">
+        <f>X2-V2</f>
+        <v>95.9299999999998</v>
+      </c>
+      <c r="X2" s="8">
+        <v>2540.22</v>
+      </c>
+      <c r="Y2" s="2">
+        <f>X2-D2</f>
+        <v>785.68</v>
+      </c>
+      <c r="Z2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="AA2" s="2">
+        <v>477.92</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>300</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>132783</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="1">
-        <v>2714.1</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="2">
+        <v>1726.42</v>
+      </c>
+      <c r="E3" s="2">
         <f>F3-D3</f>
-        <v>123.29</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2837.39</v>
-      </c>
-      <c r="G3" s="1">
+        <v>56.28</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1782.7</v>
+      </c>
+      <c r="G3" s="2">
         <f>H3-F3</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2933.24</v>
-      </c>
-      <c r="I3" s="1">
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1853.62</v>
+      </c>
+      <c r="I3" s="2">
         <f>J3-H3</f>
-        <v>92.46</v>
-      </c>
-      <c r="J3" s="1">
-        <v>3025.7</v>
-      </c>
-      <c r="K3" s="1">
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1903.2</v>
+      </c>
+      <c r="K3" s="2">
         <f>L3-J3</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L3" s="1">
-        <v>3116.11</v>
-      </c>
-      <c r="M3" s="1">
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1943.61</v>
+      </c>
+      <c r="M3" s="2">
         <f>N3-L3</f>
-        <v>103.54</v>
-      </c>
-      <c r="N3" s="1">
-        <v>3219.65</v>
-      </c>
-      <c r="O3" s="1">
+        <v>30.01</v>
+      </c>
+      <c r="N3" s="2">
+        <v>1973.62</v>
+      </c>
+      <c r="O3" s="2">
         <f>P3-N3</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P3" s="1">
-        <v>3295.31</v>
-      </c>
-      <c r="Q3" s="1">
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P3" s="2">
+        <v>2056.9</v>
+      </c>
+      <c r="Q3" s="2">
         <f>R3-P3</f>
-        <v>88.98</v>
-      </c>
-      <c r="R3" s="1">
-        <v>3384.29</v>
-      </c>
-      <c r="S3" s="1">
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2082.54</v>
+      </c>
+      <c r="S3" s="2">
         <f>T3-R3</f>
-        <v>102.46</v>
-      </c>
-      <c r="T3" s="1">
-        <v>3486.75</v>
-      </c>
-      <c r="U3" s="1">
+        <v>66.46</v>
+      </c>
+      <c r="T3" s="2">
+        <v>2149</v>
+      </c>
+      <c r="U3" s="2">
         <f>V3-T3</f>
-        <v>69.23</v>
-      </c>
-      <c r="V3" s="1">
-        <v>3555.98</v>
-      </c>
-      <c r="W3" s="1">
-        <f>V3-D3</f>
-        <v>841.88</v>
-      </c>
-      <c r="X3" s="9" t="s">
+        <v>43.5599999999999</v>
+      </c>
+      <c r="V3" s="8">
+        <v>2192.56</v>
+      </c>
+      <c r="W3" s="2">
+        <f>X3-V3</f>
+        <v>46.3200000000002</v>
+      </c>
+      <c r="X3" s="8">
+        <v>2238.88</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>X3-D3</f>
+        <v>512.46</v>
+      </c>
+      <c r="Z3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="1">
-        <v>755.92</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>500</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>191519</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
-      <c r="A4" s="1" t="s">
+      <c r="AA3" s="2">
+        <v>544.12</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>50</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>124763</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
+      <c r="A4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2533.85</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1156.57</v>
+      </c>
+      <c r="E4" s="5">
         <f>F4-D4</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2583.9</v>
-      </c>
-      <c r="G4" s="1">
+        <v>40.4400000000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1197.01</v>
+      </c>
+      <c r="G4" s="5">
         <f>H4-F4</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2669.66</v>
-      </c>
-      <c r="I4" s="1">
+        <v>46.97</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1243.98</v>
+      </c>
+      <c r="I4" s="5">
         <f>J4-H4</f>
-        <v>81.79</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2751.45</v>
-      </c>
-      <c r="K4" s="1">
+        <v>58.49</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1302.47</v>
+      </c>
+      <c r="K4" s="5">
         <f>L4-J4</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L4" s="1">
-        <v>2834.62</v>
-      </c>
-      <c r="M4" s="1">
+        <v>36.6399999999999</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1339.11</v>
+      </c>
+      <c r="M4" s="5">
         <f>N4-L4</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2891.61</v>
-      </c>
-      <c r="O4" s="1">
+        <v>33.99</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1373.1</v>
+      </c>
+      <c r="O4" s="5">
         <f>P4-N4</f>
-        <v>103.98</v>
-      </c>
-      <c r="P4" s="1">
-        <v>2995.59</v>
-      </c>
-      <c r="Q4" s="1">
+        <v>30.0600000000002</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1403.16</v>
+      </c>
+      <c r="Q4" s="5">
         <f>R4-P4</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R4" s="1">
-        <v>3064.44</v>
-      </c>
-      <c r="S4" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1450.46</v>
+      </c>
+      <c r="S4" s="5">
         <f>T4-R4</f>
-        <v>47.6100000000001</v>
-      </c>
-      <c r="T4" s="1">
-        <v>3112.05</v>
-      </c>
-      <c r="U4" s="1">
+        <v>46.8299999999999</v>
+      </c>
+      <c r="T4" s="5">
+        <v>1497.29</v>
+      </c>
+      <c r="U4" s="5">
         <f>V4-T4</f>
-        <v>38.1599999999999</v>
-      </c>
-      <c r="V4" s="1">
-        <v>3150.21</v>
-      </c>
-      <c r="W4" s="1">
-        <f>V4-D4</f>
-        <v>616.36</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>625.42</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>200</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>172501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
+        <v>58.6500000000001</v>
+      </c>
+      <c r="V4" s="9">
+        <v>1555.94</v>
+      </c>
+      <c r="W4" s="5">
+        <f>X4-V4</f>
+        <v>70.3099999999999</v>
+      </c>
+      <c r="X4" s="9">
+        <v>1626.25</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>X4-D4</f>
+        <v>469.68</v>
+      </c>
+      <c r="Z4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>433.42</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>100457</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2">
-        <v>2136.24</v>
+        <v>1425.22</v>
       </c>
       <c r="E5" s="2">
         <f>F5-D5</f>
-        <v>40.8200000000002</v>
+        <v>64.8599999999999</v>
       </c>
       <c r="F5" s="2">
-        <v>2177.06</v>
+        <v>1490.08</v>
       </c>
       <c r="G5" s="2">
         <f>H5-F5</f>
-        <v>62.5999999999999</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2">
-        <v>2239.66</v>
+        <v>1536.08</v>
       </c>
       <c r="I5" s="2">
         <f>J5-H5</f>
-        <v>47.0700000000002</v>
+        <v>50.8500000000001</v>
       </c>
       <c r="J5" s="2">
-        <v>2286.73</v>
+        <v>1586.93</v>
       </c>
       <c r="K5" s="2">
         <f>L5-J5</f>
-        <v>25.52</v>
+        <v>86.5599999999999</v>
       </c>
       <c r="L5" s="2">
-        <v>2312.25</v>
+        <v>1673.49</v>
       </c>
       <c r="M5" s="2">
         <f>N5-L5</f>
-        <v>36.7800000000002</v>
+        <v>38.5599999999999</v>
       </c>
       <c r="N5" s="2">
-        <v>2349.03</v>
+        <v>1712.05</v>
       </c>
       <c r="O5" s="2">
         <f>P5-N5</f>
-        <v>-18.02</v>
+        <v>57.0900000000001</v>
       </c>
       <c r="P5" s="2">
-        <v>2331.01</v>
+        <v>1769.14</v>
       </c>
       <c r="Q5" s="2">
         <f>R5-P5</f>
-        <v>62.7599999999998</v>
+        <v>50.8699999999999</v>
       </c>
       <c r="R5" s="2">
-        <v>2393.77</v>
+        <v>1820.01</v>
       </c>
       <c r="S5" s="2">
         <f>T5-R5</f>
-        <v>55.5599999999999</v>
+        <v>94.4300000000001</v>
       </c>
       <c r="T5" s="2">
-        <v>2449.33</v>
+        <v>1914.44</v>
       </c>
       <c r="U5" s="2">
         <f>V5-T5</f>
-        <v>31.96</v>
-      </c>
-      <c r="V5" s="2">
-        <v>2481.29</v>
+        <v>31.51</v>
+      </c>
+      <c r="V5" s="8">
+        <v>1945.95</v>
       </c>
       <c r="W5" s="2">
-        <f>V5-D5</f>
-        <v>345.05</v>
-      </c>
-      <c r="X5" s="10" t="s">
+        <f>X5-V5</f>
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X5" s="8">
+        <v>2038.54</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>X5-D5</f>
+        <v>613.32</v>
+      </c>
+      <c r="Z5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Y5" s="2">
-        <v>724.52</v>
-      </c>
-      <c r="Z5" s="2">
+      <c r="AA5" s="2">
+        <v>498.7</v>
+      </c>
+      <c r="AB5" s="5">
         <v>20</v>
       </c>
-      <c r="AA5" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="2" t="s">
+      <c r="AC5" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1576.18</v>
+      </c>
+      <c r="E6" s="5">
+        <f>F6-D6</f>
+        <v>38.8399999999999</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1615.02</v>
+      </c>
+      <c r="G6" s="5">
+        <f>H6-F6</f>
+        <v>35.5999999999999</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1650.62</v>
+      </c>
+      <c r="I6" s="5">
+        <f>J6-H6</f>
+        <v>37.47</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1688.09</v>
+      </c>
+      <c r="K6" s="5">
+        <f>L6-J6</f>
+        <v>21.49</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1709.58</v>
+      </c>
+      <c r="M6" s="5">
+        <f>N6-L6</f>
+        <v>24.53</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1734.11</v>
+      </c>
+      <c r="O6" s="5">
+        <f>P6-N6</f>
+        <v>19.5300000000002</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1753.64</v>
+      </c>
+      <c r="Q6" s="5">
+        <f>R6-P6</f>
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1818.75</v>
+      </c>
+      <c r="S6" s="5">
+        <f>T6-R6</f>
+        <v>34.3699999999999</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1853.12</v>
+      </c>
+      <c r="U6" s="5">
+        <f>V6-T6</f>
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V6" s="9">
+        <v>1893.96</v>
+      </c>
+      <c r="W6" s="5">
+        <f>X6-V6</f>
+        <v>40.96</v>
+      </c>
+      <c r="X6" s="9">
+        <v>1934.92</v>
+      </c>
+      <c r="Y6" s="5">
+        <f>X6-D6</f>
+        <v>358.74</v>
+      </c>
+      <c r="Z6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>407.07</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1349.35</v>
+      </c>
+      <c r="E7" s="5">
+        <f>F7-D7</f>
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1398.97</v>
+      </c>
+      <c r="G7" s="5">
+        <f>H7-F7</f>
+        <v>27.79</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1426.76</v>
+      </c>
+      <c r="I7" s="5">
+        <f>J7-H7</f>
+        <v>29.02</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1455.78</v>
+      </c>
+      <c r="K7" s="5">
+        <f>L7-J7</f>
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1553.66</v>
+      </c>
+      <c r="M7" s="5">
+        <f>N7-L7</f>
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1596.02</v>
+      </c>
+      <c r="O7" s="5">
+        <f>P7-N7</f>
+        <v>54.22</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1650.24</v>
+      </c>
+      <c r="Q7" s="5">
+        <f>R7-P7</f>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1685.83</v>
+      </c>
+      <c r="S7" s="5">
+        <f>T7-R7</f>
+        <v>68.1300000000001</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1753.96</v>
+      </c>
+      <c r="U7" s="5">
+        <f>V7-T7</f>
+        <v>58.5599999999999</v>
+      </c>
+      <c r="V7" s="9">
+        <v>1812.52</v>
+      </c>
+      <c r="W7" s="5">
+        <f>X7-V7</f>
+        <v>67.21</v>
+      </c>
+      <c r="X7" s="9">
+        <v>1879.73</v>
+      </c>
+      <c r="Y7" s="5">
+        <f>X7-D7</f>
+        <v>530.38</v>
+      </c>
+      <c r="Z7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>451.2</v>
+      </c>
+      <c r="AB7" s="5">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1966.62</v>
-      </c>
-      <c r="E6" s="2">
-        <f>F6-D6</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2015.64</v>
-      </c>
-      <c r="G6" s="2">
-        <f>H6-F6</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2049.8</v>
-      </c>
-      <c r="I6" s="2">
-        <f>J6-H6</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2139.9</v>
-      </c>
-      <c r="K6" s="2">
-        <f>L6-J6</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2193.07</v>
-      </c>
-      <c r="M6" s="2">
-        <f>N6-L6</f>
-        <v>63.9099999999999</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2256.98</v>
-      </c>
-      <c r="O6" s="2">
-        <f>P6-N6</f>
-        <v>45.71</v>
-      </c>
-      <c r="P6" s="2">
-        <v>2302.69</v>
-      </c>
-      <c r="Q6" s="2">
-        <f>R6-P6</f>
-        <v>37.2199999999998</v>
-      </c>
-      <c r="R6" s="2">
-        <v>2339.91</v>
-      </c>
-      <c r="S6" s="2">
-        <f>T6-R6</f>
-        <v>47.3099999999999</v>
-      </c>
-      <c r="T6" s="2">
-        <v>2387.22</v>
-      </c>
-      <c r="U6" s="2">
-        <f>V6-T6</f>
-        <v>88.2600000000002</v>
-      </c>
-      <c r="V6" s="2">
-        <v>2475.48</v>
-      </c>
-      <c r="W6" s="2">
-        <f>V6-D6</f>
-        <v>508.86</v>
-      </c>
-      <c r="X6" s="10" t="s">
+      <c r="AC7" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>109106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1060.77</v>
+      </c>
+      <c r="E8" s="5">
+        <f>F8-D8</f>
+        <v>63.24</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1124.01</v>
+      </c>
+      <c r="G8" s="5">
+        <f>H8-F8</f>
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1143.68</v>
+      </c>
+      <c r="I8" s="5">
+        <f>J8-H8</f>
+        <v>47.76</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1191.44</v>
+      </c>
+      <c r="K8" s="5">
+        <f>L8-J8</f>
+        <v>40.22</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1231.66</v>
+      </c>
+      <c r="M8" s="5">
+        <f>N8-L8</f>
+        <v>44.8</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1276.46</v>
+      </c>
+      <c r="O8" s="5">
+        <f>P8-N8</f>
+        <v>28.03</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1304.49</v>
+      </c>
+      <c r="Q8" s="5">
+        <f>R8-P8</f>
+        <v>31.78</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1336.27</v>
+      </c>
+      <c r="S8" s="5">
+        <f>T8-R8</f>
+        <v>44.9000000000001</v>
+      </c>
+      <c r="T8" s="5">
+        <v>1381.17</v>
+      </c>
+      <c r="U8" s="5">
+        <f>V8-T8</f>
+        <v>53.1499999999999</v>
+      </c>
+      <c r="V8" s="9">
+        <v>1434.32</v>
+      </c>
+      <c r="W8" s="5">
+        <f>X8-V8</f>
+        <v>41.46</v>
+      </c>
+      <c r="X8" s="9">
+        <v>1475.78</v>
+      </c>
+      <c r="Y8" s="5">
+        <f>X8-D8</f>
+        <v>415.01</v>
+      </c>
+      <c r="Z8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="Y6" s="2">
-        <v>848.87</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>65</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>130589</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2183.01</v>
-      </c>
-      <c r="E7" s="2">
-        <f>F7-D7</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2207.13</v>
-      </c>
-      <c r="G7" s="2">
-        <f>H7-F7</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2229.99</v>
-      </c>
-      <c r="I7" s="2">
-        <f>J7-H7</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J7" s="2">
-        <v>2241.77</v>
-      </c>
-      <c r="K7" s="2">
-        <f>L7-J7</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2254.78</v>
-      </c>
-      <c r="M7" s="2">
-        <f>N7-L7</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N7" s="2">
-        <v>2317.42</v>
-      </c>
-      <c r="O7" s="2">
-        <f>P7-N7</f>
-        <v>16.27</v>
-      </c>
-      <c r="P7" s="2">
-        <v>2333.69</v>
-      </c>
-      <c r="Q7" s="2">
-        <f>R7-P7</f>
-        <v>36.5</v>
-      </c>
-      <c r="R7" s="2">
-        <v>2370.19</v>
-      </c>
-      <c r="S7" s="2">
-        <f>T7-R7</f>
-        <v>65.1900000000001</v>
-      </c>
-      <c r="T7" s="2">
-        <v>2435.38</v>
-      </c>
-      <c r="U7" s="2">
-        <f>V7-T7</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V7" s="2">
-        <v>2467.14</v>
-      </c>
-      <c r="W7" s="2">
-        <f>V7-D7</f>
-        <v>284.13</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>605.47</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1754.54</v>
-      </c>
-      <c r="E8" s="2">
-        <f>F8-D8</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1807.91</v>
-      </c>
-      <c r="G8" s="2">
-        <f>H8-F8</f>
-        <v>90.24</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1898.15</v>
-      </c>
-      <c r="I8" s="2">
-        <f>J8-H8</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1988.53</v>
-      </c>
-      <c r="K8" s="2">
-        <f>L8-J8</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L8" s="2">
-        <v>2048.24</v>
-      </c>
-      <c r="M8" s="2">
-        <f>N8-L8</f>
-        <v>153.99</v>
-      </c>
-      <c r="N8" s="2">
-        <v>2202.23</v>
-      </c>
-      <c r="O8" s="2">
-        <f>P8-N8</f>
-        <v>64.21</v>
-      </c>
-      <c r="P8" s="2">
-        <v>2266.44</v>
-      </c>
-      <c r="Q8" s="2">
-        <f>R8-P8</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R8" s="2">
-        <v>2314</v>
-      </c>
-      <c r="S8" s="2">
-        <f>T8-R8</f>
-        <v>59.6500000000001</v>
-      </c>
-      <c r="T8" s="2">
-        <v>2373.65</v>
-      </c>
-      <c r="U8" s="2">
-        <f>V8-T8</f>
-        <v>70.6399999999999</v>
-      </c>
-      <c r="V8" s="2">
-        <v>2444.29</v>
-      </c>
-      <c r="W8" s="2">
-        <f>V8-D8</f>
-        <v>689.75</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>442.65</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>132783</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
+      <c r="AA8" s="5">
+        <v>277.72</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>71153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -2150,7 +2222,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2">
         <v>1735.94</v>
@@ -2215,230 +2287,251 @@
         <f>V9-T9</f>
         <v>68.9400000000001</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9" s="8">
         <v>2251.59</v>
       </c>
       <c r="W9" s="2">
-        <f>V9-D9</f>
-        <v>515.65</v>
-      </c>
-      <c r="X9" s="10" t="s">
+        <f>X9-V9</f>
+        <v>72.0299999999997</v>
+      </c>
+      <c r="X9" s="8">
+        <v>2323.62</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>X9-D9</f>
+        <v>587.68</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>538.92</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>150192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
+      <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Y9" s="2">
-        <v>549.37</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>150192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1726.42</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="C10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2533.85</v>
+      </c>
+      <c r="E10" s="1">
         <f>F10-D10</f>
-        <v>56.28</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1782.7</v>
-      </c>
-      <c r="G10" s="2">
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2583.9</v>
+      </c>
+      <c r="G10" s="1">
         <f>H10-F10</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1853.62</v>
-      </c>
-      <c r="I10" s="2">
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2669.66</v>
+      </c>
+      <c r="I10" s="1">
         <f>J10-H10</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1903.2</v>
-      </c>
-      <c r="K10" s="2">
+        <v>81.79</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2751.45</v>
+      </c>
+      <c r="K10" s="1">
         <f>L10-J10</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1943.61</v>
-      </c>
-      <c r="M10" s="2">
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2834.62</v>
+      </c>
+      <c r="M10" s="1">
         <f>N10-L10</f>
-        <v>30.01</v>
-      </c>
-      <c r="N10" s="2">
-        <v>1973.62</v>
-      </c>
-      <c r="O10" s="2">
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2891.61</v>
+      </c>
+      <c r="O10" s="1">
         <f>P10-N10</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P10" s="2">
-        <v>2056.9</v>
-      </c>
-      <c r="Q10" s="2">
+        <v>103.98</v>
+      </c>
+      <c r="P10" s="1">
+        <v>2995.59</v>
+      </c>
+      <c r="Q10" s="1">
         <f>R10-P10</f>
-        <v>25.6399999999999</v>
-      </c>
-      <c r="R10" s="2">
-        <v>2082.54</v>
-      </c>
-      <c r="S10" s="2">
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R10" s="1">
+        <v>3064.44</v>
+      </c>
+      <c r="S10" s="1">
         <f>T10-R10</f>
-        <v>66.46</v>
-      </c>
-      <c r="T10" s="2">
-        <v>2149</v>
-      </c>
-      <c r="U10" s="2">
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T10" s="1">
+        <v>3112.05</v>
+      </c>
+      <c r="U10" s="1">
         <f>V10-T10</f>
-        <v>43.5599999999999</v>
-      </c>
-      <c r="V10" s="2">
-        <v>2192.56</v>
-      </c>
-      <c r="W10" s="2">
-        <f>V10-D10</f>
-        <v>466.14</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>519.82</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>50</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>124763</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+        <v>38.1599999999999</v>
+      </c>
+      <c r="V10" s="10">
+        <v>3150.21</v>
+      </c>
+      <c r="W10" s="1">
+        <f>X10-V10</f>
+        <v>146.1</v>
+      </c>
+      <c r="X10" s="10">
+        <v>3296.31</v>
+      </c>
+      <c r="Y10" s="1">
+        <f>X10-D10</f>
+        <v>762.46</v>
+      </c>
+      <c r="Z10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>662.22</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>200</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>172501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5">
-        <v>1425.22</v>
+        <v>1446.65</v>
       </c>
       <c r="E11" s="5">
         <f>F11-D11</f>
-        <v>64.8599999999999</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F11" s="5">
-        <v>1490.08</v>
+        <v>1474.83</v>
       </c>
       <c r="G11" s="5">
         <f>H11-F11</f>
-        <v>46</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H11" s="5">
-        <v>1536.08</v>
+        <v>1538.65</v>
       </c>
       <c r="I11" s="5">
         <f>J11-H11</f>
-        <v>50.8500000000001</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J11" s="5">
-        <v>1586.93</v>
+        <v>1561.57</v>
       </c>
       <c r="K11" s="5">
         <f>L11-J11</f>
-        <v>86.5599999999999</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L11" s="5">
-        <v>1673.49</v>
+        <v>1632.43</v>
       </c>
       <c r="M11" s="5">
         <f>N11-L11</f>
-        <v>38.5599999999999</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N11" s="5">
-        <v>1712.05</v>
+        <v>1669.84</v>
       </c>
       <c r="O11" s="5">
         <f>P11-N11</f>
-        <v>57.0900000000001</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P11" s="5">
-        <v>1769.14</v>
+        <v>1702.67</v>
       </c>
       <c r="Q11" s="5">
         <f>R11-P11</f>
-        <v>50.8699999999999</v>
+        <v>51.9499999999998</v>
       </c>
       <c r="R11" s="5">
-        <v>1820.01</v>
+        <v>1754.62</v>
       </c>
       <c r="S11" s="5">
         <f>T11-R11</f>
-        <v>94.4300000000001</v>
+        <v>40.1200000000001</v>
       </c>
       <c r="T11" s="5">
-        <v>1914.44</v>
+        <v>1794.74</v>
       </c>
       <c r="U11" s="5">
         <f>V11-T11</f>
-        <v>31.51</v>
-      </c>
-      <c r="V11" s="5">
-        <v>1945.95</v>
+        <v>77.5</v>
+      </c>
+      <c r="V11" s="9">
+        <v>1872.24</v>
       </c>
       <c r="W11" s="5">
-        <f>V11-D11</f>
-        <v>520.73</v>
-      </c>
-      <c r="X11" s="11" t="s">
+        <f>X11-V11</f>
+        <v>79.5899999999999</v>
+      </c>
+      <c r="X11" s="9">
+        <v>1951.83</v>
+      </c>
+      <c r="Y11" s="5">
+        <f>X11-D11</f>
+        <v>505.18</v>
+      </c>
+      <c r="Z11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="Y11" s="5">
-        <v>472.8</v>
-      </c>
-      <c r="Z11" s="5">
-        <v>20</v>
-      </c>
       <c r="AA11" s="5">
-        <v>1.1</v>
+        <v>767.57</v>
       </c>
       <c r="AB11" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+        <v>65</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>109333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D12" s="5">
         <v>1350.52</v>
@@ -2503,806 +2596,869 @@
         <f>V12-T12</f>
         <v>66.5899999999999</v>
       </c>
-      <c r="V12" s="5">
+      <c r="V12" s="9">
         <v>1898.56</v>
       </c>
       <c r="W12" s="5">
-        <f>V12-D12</f>
-        <v>548.04</v>
-      </c>
-      <c r="X12" s="11" t="s">
+        <f>X12-V12</f>
+        <v>48.77</v>
+      </c>
+      <c r="X12" s="9">
+        <v>1947.33</v>
+      </c>
+      <c r="Y12" s="5">
+        <f>X12-D12</f>
+        <v>596.81</v>
+      </c>
+      <c r="Z12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>590.12</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>65</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>127603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="A13" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="Y12" s="5">
-        <v>573.17</v>
-      </c>
-      <c r="Z12" s="5">
-        <v>65</v>
-      </c>
-      <c r="AA12" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="AB12" s="5">
-        <v>127603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5">
-        <v>1576.18</v>
+        <v>953.78</v>
       </c>
       <c r="E13" s="5">
         <f>F13-D13</f>
-        <v>38.8399999999999</v>
+        <v>28.97</v>
       </c>
       <c r="F13" s="5">
-        <v>1615.02</v>
+        <v>982.75</v>
       </c>
       <c r="G13" s="5">
         <f>H13-F13</f>
-        <v>35.5999999999999</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H13" s="5">
-        <v>1650.62</v>
+        <v>1066.68</v>
       </c>
       <c r="I13" s="5">
         <f>J13-H13</f>
-        <v>37.47</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J13" s="5">
-        <v>1688.09</v>
+        <v>1109.52</v>
       </c>
       <c r="K13" s="5">
         <f>L13-J13</f>
-        <v>21.49</v>
+        <v>36.46</v>
       </c>
       <c r="L13" s="5">
-        <v>1709.58</v>
+        <v>1145.98</v>
       </c>
       <c r="M13" s="5">
         <f>N13-L13</f>
-        <v>24.53</v>
+        <v>37.49</v>
       </c>
       <c r="N13" s="5">
-        <v>1734.11</v>
+        <v>1183.47</v>
       </c>
       <c r="O13" s="5">
         <f>P13-N13</f>
-        <v>19.5300000000002</v>
+        <v>33.3699999999999</v>
       </c>
       <c r="P13" s="5">
-        <v>1753.64</v>
+        <v>1216.84</v>
       </c>
       <c r="Q13" s="5">
         <f>R13-P13</f>
-        <v>65.1099999999999</v>
+        <v>24.8900000000001</v>
       </c>
       <c r="R13" s="5">
-        <v>1818.75</v>
+        <v>1241.73</v>
       </c>
       <c r="S13" s="5">
         <f>T13-R13</f>
-        <v>34.3699999999999</v>
+        <v>42.3099999999999</v>
       </c>
       <c r="T13" s="5">
-        <v>1853.12</v>
+        <v>1284.04</v>
       </c>
       <c r="U13" s="5">
         <f>V13-T13</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V13" s="5">
-        <v>1893.96</v>
+        <v>44.8400000000001</v>
+      </c>
+      <c r="V13" s="9">
+        <v>1328.88</v>
       </c>
       <c r="W13" s="5">
-        <f>V13-D13</f>
-        <v>317.78</v>
-      </c>
-      <c r="X13" s="11" t="s">
+        <f>X13-V13</f>
+        <v>45.9499999999998</v>
+      </c>
+      <c r="X13" s="9">
+        <v>1374.83</v>
+      </c>
+      <c r="Y13" s="5">
+        <f>X13-D13</f>
+        <v>421.05</v>
+      </c>
+      <c r="Z13" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>485.97</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>30</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>105419</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Y13" s="5">
-        <v>399.22</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="C14" s="5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>1446.65</v>
+        <v>848.93</v>
       </c>
       <c r="E14" s="5">
         <f>F14-D14</f>
-        <v>28.1799999999998</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F14" s="5">
-        <v>1474.83</v>
+        <v>883.49</v>
       </c>
       <c r="G14" s="5">
         <f>H14-F14</f>
-        <v>63.8200000000002</v>
+        <v>46.08</v>
       </c>
       <c r="H14" s="5">
-        <v>1538.65</v>
+        <v>929.57</v>
       </c>
       <c r="I14" s="5">
         <f>J14-H14</f>
-        <v>22.9199999999998</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J14" s="5">
-        <v>1561.57</v>
+        <v>957.31</v>
       </c>
       <c r="K14" s="5">
         <f>L14-J14</f>
-        <v>70.8600000000001</v>
+        <v>47.36</v>
       </c>
       <c r="L14" s="5">
-        <v>1632.43</v>
+        <v>1004.67</v>
       </c>
       <c r="M14" s="5">
         <f>N14-L14</f>
-        <v>37.4099999999999</v>
+        <v>25.9399999999999</v>
       </c>
       <c r="N14" s="5">
-        <v>1669.84</v>
+        <v>1030.61</v>
       </c>
       <c r="O14" s="5">
         <f>P14-N14</f>
-        <v>32.8300000000002</v>
+        <v>37.71</v>
       </c>
       <c r="P14" s="5">
-        <v>1702.67</v>
+        <v>1068.32</v>
       </c>
       <c r="Q14" s="5">
         <f>R14-P14</f>
-        <v>51.9499999999998</v>
+        <v>18.3800000000001</v>
       </c>
       <c r="R14" s="5">
-        <v>1754.62</v>
+        <v>1086.7</v>
       </c>
       <c r="S14" s="5">
         <f>T14-R14</f>
-        <v>40.1200000000001</v>
+        <v>21.04</v>
       </c>
       <c r="T14" s="5">
-        <v>1794.74</v>
+        <v>1107.74</v>
       </c>
       <c r="U14" s="5">
         <f>V14-T14</f>
-        <v>77.5</v>
-      </c>
-      <c r="V14" s="5">
-        <v>1872.24</v>
+        <v>32.7</v>
+      </c>
+      <c r="V14" s="9">
+        <v>1140.44</v>
       </c>
       <c r="W14" s="5">
-        <f>V14-D14</f>
-        <v>425.59</v>
-      </c>
-      <c r="X14" s="11" t="s">
+        <f>X14-V14</f>
+        <v>26.9299999999998</v>
+      </c>
+      <c r="X14" s="9">
+        <v>1167.37</v>
+      </c>
+      <c r="Y14" s="5">
+        <f>X14-D14</f>
+        <v>318.44</v>
+      </c>
+      <c r="Z14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA14" s="5">
+        <v>411.37</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>30</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>78989</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
+      <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Y14" s="5">
-        <v>734.17</v>
-      </c>
-      <c r="Z14" s="5">
-        <v>65</v>
-      </c>
-      <c r="AA14" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="AB14" s="5">
-        <v>109333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="A15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1349.35</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="3">
+        <v>262.39</v>
+      </c>
+      <c r="E15" s="3">
         <f>F15-D15</f>
-        <v>49.6200000000001</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1398.97</v>
-      </c>
-      <c r="G15" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>273.89</v>
+      </c>
+      <c r="G15" s="3">
         <f>H15-F15</f>
-        <v>27.79</v>
-      </c>
-      <c r="H15" s="5">
-        <v>1426.76</v>
-      </c>
-      <c r="I15" s="5">
+        <v>13.97</v>
+      </c>
+      <c r="H15" s="3">
+        <v>287.86</v>
+      </c>
+      <c r="I15" s="3">
         <f>J15-H15</f>
-        <v>29.02</v>
-      </c>
-      <c r="J15" s="5">
-        <v>1455.78</v>
-      </c>
-      <c r="K15" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="J15" s="3">
+        <v>304.1</v>
+      </c>
+      <c r="K15" s="3">
         <f>L15-J15</f>
-        <v>97.8800000000001</v>
-      </c>
-      <c r="L15" s="5">
-        <v>1553.66</v>
-      </c>
-      <c r="M15" s="5">
+        <v>12.65</v>
+      </c>
+      <c r="L15" s="3">
+        <v>316.75</v>
+      </c>
+      <c r="M15" s="3">
         <f>N15-L15</f>
-        <v>42.3599999999999</v>
-      </c>
-      <c r="N15" s="5">
-        <v>1596.02</v>
-      </c>
-      <c r="O15" s="5">
+        <v>9.99000000000001</v>
+      </c>
+      <c r="N15" s="3">
+        <v>326.74</v>
+      </c>
+      <c r="O15" s="3">
         <f>P15-N15</f>
-        <v>54.22</v>
-      </c>
-      <c r="P15" s="5">
-        <v>1650.24</v>
-      </c>
-      <c r="Q15" s="5">
+        <v>6.31999999999999</v>
+      </c>
+      <c r="P15" s="3">
+        <v>333.06</v>
+      </c>
+      <c r="Q15" s="3">
         <f>R15-P15</f>
-        <v>35.5899999999999</v>
-      </c>
-      <c r="R15" s="5">
-        <v>1685.83</v>
-      </c>
-      <c r="S15" s="5">
+        <v>21.13</v>
+      </c>
+      <c r="R15" s="3">
+        <v>354.19</v>
+      </c>
+      <c r="S15" s="3">
         <f>T15-R15</f>
-        <v>68.1300000000001</v>
-      </c>
-      <c r="T15" s="5">
-        <v>1753.96</v>
-      </c>
-      <c r="U15" s="5">
+        <v>17.68</v>
+      </c>
+      <c r="T15" s="3">
+        <v>371.87</v>
+      </c>
+      <c r="U15" s="3">
         <f>V15-T15</f>
-        <v>58.5599999999999</v>
-      </c>
-      <c r="V15" s="5">
-        <v>1812.52</v>
-      </c>
-      <c r="W15" s="5">
-        <f>V15-D15</f>
-        <v>463.17</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>438.4</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>20</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>109106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="A16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="5" t="s">
+        <v>11.66</v>
+      </c>
+      <c r="V15" s="11">
+        <v>383.53</v>
+      </c>
+      <c r="W15" s="3">
+        <f>X15-V15</f>
+        <v>20.5700000000001</v>
+      </c>
+      <c r="X15" s="11">
+        <v>404.1</v>
+      </c>
+      <c r="Y15" s="3">
+        <f>X15-D15</f>
+        <v>141.71</v>
+      </c>
+      <c r="Z15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1156.57</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="AA15" s="3">
+        <v>140.92</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>36684</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3">
+        <v>407.35</v>
+      </c>
+      <c r="E16" s="3">
         <f>F16-D16</f>
-        <v>40.4400000000001</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1197.01</v>
-      </c>
-      <c r="G16" s="5">
+        <v>13.86</v>
+      </c>
+      <c r="F16" s="3">
+        <v>421.21</v>
+      </c>
+      <c r="G16" s="3">
         <f>H16-F16</f>
-        <v>46.97</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1243.98</v>
-      </c>
-      <c r="I16" s="5">
+        <v>16.43</v>
+      </c>
+      <c r="H16" s="3">
+        <v>437.64</v>
+      </c>
+      <c r="I16" s="3">
         <f>J16-H16</f>
-        <v>58.49</v>
-      </c>
-      <c r="J16" s="5">
-        <v>1302.47</v>
-      </c>
-      <c r="K16" s="5">
+        <v>13.64</v>
+      </c>
+      <c r="J16" s="3">
+        <v>451.28</v>
+      </c>
+      <c r="K16" s="3">
         <f>L16-J16</f>
-        <v>36.6399999999999</v>
-      </c>
-      <c r="L16" s="5">
-        <v>1339.11</v>
-      </c>
-      <c r="M16" s="5">
+        <v>11.6</v>
+      </c>
+      <c r="L16" s="3">
+        <v>462.88</v>
+      </c>
+      <c r="M16" s="3">
         <f>N16-L16</f>
-        <v>33.99</v>
-      </c>
-      <c r="N16" s="5">
-        <v>1373.1</v>
-      </c>
-      <c r="O16" s="5">
+        <v>47.68</v>
+      </c>
+      <c r="N16" s="3">
+        <v>510.56</v>
+      </c>
+      <c r="O16" s="3">
         <f>P16-N16</f>
-        <v>30.0600000000002</v>
-      </c>
-      <c r="P16" s="5">
-        <v>1403.16</v>
-      </c>
-      <c r="Q16" s="5">
+        <v>20.51</v>
+      </c>
+      <c r="P16" s="3">
+        <v>531.07</v>
+      </c>
+      <c r="Q16" s="3">
         <f>R16-P16</f>
-        <v>47.3</v>
-      </c>
-      <c r="R16" s="5">
-        <v>1450.46</v>
-      </c>
-      <c r="S16" s="5">
+        <v>18.6099999999999</v>
+      </c>
+      <c r="R16" s="3">
+        <v>549.68</v>
+      </c>
+      <c r="S16" s="3">
         <f>T16-R16</f>
-        <v>46.8299999999999</v>
-      </c>
-      <c r="T16" s="5">
-        <v>1497.29</v>
-      </c>
-      <c r="U16" s="5">
+        <v>11.9400000000001</v>
+      </c>
+      <c r="T16" s="3">
+        <v>561.62</v>
+      </c>
+      <c r="U16" s="3">
         <f>V16-T16</f>
-        <v>58.6500000000001</v>
-      </c>
-      <c r="V16" s="5">
-        <v>1555.94</v>
-      </c>
-      <c r="W16" s="5">
-        <f>V16-D16</f>
-        <v>399.37</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y16" s="5">
-        <v>386.42</v>
-      </c>
-      <c r="Z16" s="5">
-        <v>25</v>
-      </c>
-      <c r="AA16" s="5">
-        <v>3</v>
-      </c>
-      <c r="AB16" s="5">
-        <v>100457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
+        <v>16.23</v>
+      </c>
+      <c r="V16" s="11">
+        <v>577.85</v>
+      </c>
+      <c r="W16" s="3">
+        <f>X16-V16</f>
+        <v>15.28</v>
+      </c>
+      <c r="X16" s="11">
+        <v>593.13</v>
+      </c>
+      <c r="Y16" s="3">
+        <f>X16-D16</f>
+        <v>185.78</v>
+      </c>
+      <c r="Z16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>262.06</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>30</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D17" s="5">
-        <v>1060.77</v>
+        <v>950.09</v>
       </c>
       <c r="E17" s="5">
         <f>F17-D17</f>
-        <v>63.24</v>
+        <v>42.4</v>
       </c>
       <c r="F17" s="5">
-        <v>1124.01</v>
+        <v>992.49</v>
       </c>
       <c r="G17" s="5">
         <f>H17-F17</f>
-        <v>19.6700000000001</v>
+        <v>38.5899999999999</v>
       </c>
       <c r="H17" s="5">
-        <v>1143.68</v>
+        <v>1031.08</v>
       </c>
       <c r="I17" s="5">
         <f>J17-H17</f>
-        <v>47.76</v>
+        <v>22.6000000000001</v>
       </c>
       <c r="J17" s="5">
-        <v>1191.44</v>
+        <v>1053.68</v>
       </c>
       <c r="K17" s="5">
         <f>L17-J17</f>
-        <v>40.22</v>
+        <v>10.9299999999998</v>
       </c>
       <c r="L17" s="5">
-        <v>1231.66</v>
+        <v>1064.61</v>
       </c>
       <c r="M17" s="5">
         <f>N17-L17</f>
-        <v>44.8</v>
+        <v>16.1800000000001</v>
       </c>
       <c r="N17" s="5">
-        <v>1276.46</v>
+        <v>1080.79</v>
       </c>
       <c r="O17" s="5">
         <f>P17-N17</f>
-        <v>28.03</v>
+        <v>13.6700000000001</v>
       </c>
       <c r="P17" s="5">
-        <v>1304.49</v>
+        <v>1094.46</v>
       </c>
       <c r="Q17" s="5">
         <f>R17-P17</f>
-        <v>31.78</v>
+        <v>56.26</v>
       </c>
       <c r="R17" s="5">
-        <v>1336.27</v>
+        <v>1150.72</v>
       </c>
       <c r="S17" s="5">
         <f>T17-R17</f>
-        <v>44.9000000000001</v>
+        <v>41.27</v>
       </c>
       <c r="T17" s="5">
-        <v>1381.17</v>
+        <v>1191.99</v>
       </c>
       <c r="U17" s="5">
         <f>V17-T17</f>
-        <v>53.1499999999999</v>
-      </c>
-      <c r="V17" s="5">
-        <v>1434.32</v>
+        <v>35.21</v>
+      </c>
+      <c r="V17" s="9">
+        <v>1227.2</v>
       </c>
       <c r="W17" s="5">
-        <f>V17-D17</f>
-        <v>373.55</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>51</v>
+        <f>X17-V17</f>
+        <v>33.3599999999999</v>
+      </c>
+      <c r="X17" s="9">
+        <v>1260.56</v>
       </c>
       <c r="Y17" s="5">
-        <v>271.42</v>
-      </c>
-      <c r="Z17" s="5">
+        <f>X17-D17</f>
+        <v>310.47</v>
+      </c>
+      <c r="Z17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA17" s="5">
+        <v>483.62</v>
+      </c>
+      <c r="AB17" s="5">
         <v>10</v>
       </c>
-      <c r="AA17" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="AB17" s="5">
-        <v>71153</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
-      <c r="A18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="5">
-        <v>953.78</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="AC17" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>86194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
+      <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2136.24</v>
+      </c>
+      <c r="E18" s="2">
         <f>F18-D18</f>
-        <v>28.97</v>
-      </c>
-      <c r="F18" s="5">
-        <v>982.75</v>
-      </c>
-      <c r="G18" s="5">
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2177.06</v>
+      </c>
+      <c r="G18" s="2">
         <f>H18-F18</f>
-        <v>83.9300000000001</v>
-      </c>
-      <c r="H18" s="5">
-        <v>1066.68</v>
-      </c>
-      <c r="I18" s="5">
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2239.66</v>
+      </c>
+      <c r="I18" s="2">
         <f>J18-H18</f>
-        <v>42.8399999999999</v>
-      </c>
-      <c r="J18" s="5">
-        <v>1109.52</v>
-      </c>
-      <c r="K18" s="5">
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2286.73</v>
+      </c>
+      <c r="K18" s="2">
         <f>L18-J18</f>
-        <v>36.46</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1145.98</v>
-      </c>
-      <c r="M18" s="5">
+        <v>25.52</v>
+      </c>
+      <c r="L18" s="2">
+        <v>2312.25</v>
+      </c>
+      <c r="M18" s="2">
         <f>N18-L18</f>
-        <v>37.49</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1183.47</v>
-      </c>
-      <c r="O18" s="5">
+        <v>36.7800000000002</v>
+      </c>
+      <c r="N18" s="2">
+        <v>2349.03</v>
+      </c>
+      <c r="O18" s="2">
         <f>P18-N18</f>
-        <v>33.3699999999999</v>
-      </c>
-      <c r="P18" s="5">
-        <v>1216.84</v>
-      </c>
-      <c r="Q18" s="5">
+        <v>-18.02</v>
+      </c>
+      <c r="P18" s="2">
+        <v>2331.01</v>
+      </c>
+      <c r="Q18" s="2">
         <f>R18-P18</f>
-        <v>24.8900000000001</v>
-      </c>
-      <c r="R18" s="5">
-        <v>1241.73</v>
-      </c>
-      <c r="S18" s="5">
+        <v>62.7599999999998</v>
+      </c>
+      <c r="R18" s="2">
+        <v>2393.77</v>
+      </c>
+      <c r="S18" s="2">
         <f>T18-R18</f>
-        <v>42.3099999999999</v>
-      </c>
-      <c r="T18" s="5">
-        <v>1284.04</v>
-      </c>
-      <c r="U18" s="5">
+        <v>55.5599999999999</v>
+      </c>
+      <c r="T18" s="2">
+        <v>2449.33</v>
+      </c>
+      <c r="U18" s="2">
         <f>V18-T18</f>
-        <v>44.8400000000001</v>
-      </c>
-      <c r="V18" s="5">
-        <v>1328.88</v>
-      </c>
-      <c r="W18" s="5">
-        <f>V18-D18</f>
-        <v>375.1</v>
-      </c>
-      <c r="X18" s="11" t="s">
+        <v>31.96</v>
+      </c>
+      <c r="V18" s="8">
+        <v>2481.29</v>
+      </c>
+      <c r="W18" s="2">
+        <f>X18-V18</f>
+        <v>109.47</v>
+      </c>
+      <c r="X18" s="8">
+        <v>2590.76</v>
+      </c>
+      <c r="Y18" s="2">
+        <f>X18-D18</f>
+        <v>454.52</v>
+      </c>
+      <c r="Z18" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>814.82</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1966.62</v>
+      </c>
+      <c r="E19" s="2">
+        <f>F19-D19</f>
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2015.64</v>
+      </c>
+      <c r="G19" s="2">
+        <f>H19-F19</f>
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2049.8</v>
+      </c>
+      <c r="I19" s="2">
+        <f>J19-H19</f>
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2139.9</v>
+      </c>
+      <c r="K19" s="2">
+        <f>L19-J19</f>
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L19" s="2">
+        <v>2193.07</v>
+      </c>
+      <c r="M19" s="2">
+        <f>N19-L19</f>
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N19" s="2">
+        <v>2256.98</v>
+      </c>
+      <c r="O19" s="2">
+        <f>P19-N19</f>
+        <v>45.71</v>
+      </c>
+      <c r="P19" s="2">
+        <v>2302.69</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>R19-P19</f>
+        <v>37.2199999999998</v>
+      </c>
+      <c r="R19" s="2">
+        <v>2339.91</v>
+      </c>
+      <c r="S19" s="2">
+        <f>T19-R19</f>
+        <v>47.3099999999999</v>
+      </c>
+      <c r="T19" s="2">
+        <v>2387.22</v>
+      </c>
+      <c r="U19" s="2">
+        <f>V19-T19</f>
+        <v>88.2600000000002</v>
+      </c>
+      <c r="V19" s="8">
+        <v>2475.48</v>
+      </c>
+      <c r="W19" s="2">
+        <f>X19-V19</f>
+        <v>67.5900000000001</v>
+      </c>
+      <c r="X19" s="8">
+        <v>2543.07</v>
+      </c>
+      <c r="Y19" s="2">
+        <f>X19-D19</f>
+        <v>576.45</v>
+      </c>
+      <c r="Z19" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>815.12</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>65</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AD19" s="2">
+        <v>130589</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="6">
+        <v>4105.48</v>
+      </c>
+      <c r="E20" s="6">
+        <f>F20-D20</f>
+        <v>181.21</v>
+      </c>
+      <c r="F20" s="6">
+        <v>4286.69</v>
+      </c>
+      <c r="G20" s="6">
+        <f>H20-F20</f>
+        <v>139.09</v>
+      </c>
+      <c r="H20" s="6">
+        <v>4425.78</v>
+      </c>
+      <c r="I20" s="6">
+        <f>J20-H20</f>
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J20" s="6">
+        <v>4480.66</v>
+      </c>
+      <c r="K20" s="6">
+        <f>L20-J20</f>
+        <v>104.900000000001</v>
+      </c>
+      <c r="L20" s="6">
+        <v>4585.56</v>
+      </c>
+      <c r="M20" s="6">
+        <f>N20-L20</f>
+        <v>70.29</v>
+      </c>
+      <c r="N20" s="6">
+        <v>4655.85</v>
+      </c>
+      <c r="O20" s="6">
+        <f>P20-N20</f>
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P20" s="6">
+        <v>4705.02</v>
+      </c>
+      <c r="Q20" s="6">
+        <f>R20-P20</f>
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R20" s="6">
+        <v>4743.24</v>
+      </c>
+      <c r="S20" s="6">
+        <f>T20-R20</f>
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T20" s="6">
+        <v>4788.86</v>
+      </c>
+      <c r="U20" s="6">
+        <f>V20-T20</f>
+        <v>27.5900000000001</v>
+      </c>
+      <c r="V20" s="12">
+        <v>4816.45</v>
+      </c>
+      <c r="W20" s="6">
+        <f>X20-V20</f>
+        <v>158.22</v>
+      </c>
+      <c r="X20" s="12">
+        <v>4974.67</v>
+      </c>
+      <c r="Y20" s="6">
+        <f>X20-D20</f>
+        <v>869.190000000001</v>
+      </c>
+      <c r="Z20" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>1376.92</v>
+      </c>
+      <c r="AB20" s="18">
+        <v>400</v>
+      </c>
+      <c r="AC20" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="AD20" s="18">
+        <v>186759</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
+      <c r="A21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Y18" s="5">
-        <v>475.87</v>
-      </c>
-      <c r="Z18" s="5">
-        <v>30</v>
-      </c>
-      <c r="AA18" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="5">
-        <v>105419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="5">
-        <v>907.94</v>
-      </c>
-      <c r="E19" s="5">
-        <f>F19-D19</f>
-        <v>64.0799999999999</v>
-      </c>
-      <c r="F19" s="5">
-        <v>972.02</v>
-      </c>
-      <c r="G19" s="5">
-        <f>H19-F19</f>
-        <v>36.26</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1008.28</v>
-      </c>
-      <c r="I19" s="5">
-        <f>J19-H19</f>
-        <v>28.8</v>
-      </c>
-      <c r="J19" s="5">
-        <v>1037.08</v>
-      </c>
-      <c r="K19" s="5">
-        <f>L19-J19</f>
-        <v>40.1000000000001</v>
-      </c>
-      <c r="L19" s="5">
-        <v>1077.18</v>
-      </c>
-      <c r="M19" s="5">
-        <f>N19-L19</f>
-        <v>26.03</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1103.21</v>
-      </c>
-      <c r="O19" s="5">
-        <f>P19-N19</f>
-        <v>28.3499999999999</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1131.56</v>
-      </c>
-      <c r="Q19" s="5">
-        <f>R19-P19</f>
-        <v>50.1900000000001</v>
-      </c>
-      <c r="R19" s="5">
-        <v>1181.75</v>
-      </c>
-      <c r="S19" s="5">
-        <f>T19-R19</f>
-        <v>26.8699999999999</v>
-      </c>
-      <c r="T19" s="5">
-        <v>1208.62</v>
-      </c>
-      <c r="U19" s="5">
-        <f>V19-T19</f>
-        <v>58.3000000000002</v>
-      </c>
-      <c r="V19" s="5">
-        <v>1266.92</v>
-      </c>
-      <c r="W19" s="5">
-        <f>V19-D19</f>
-        <v>358.98</v>
-      </c>
-      <c r="X19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="5">
-        <v>436.17</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA19" s="5">
-        <v>8.2</v>
-      </c>
-      <c r="AB19" s="5">
-        <v>65285</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28">
-      <c r="A20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="5">
-        <v>950.09</v>
-      </c>
-      <c r="E20" s="5">
-        <f>F20-D20</f>
-        <v>42.4</v>
-      </c>
-      <c r="F20" s="5">
-        <v>992.49</v>
-      </c>
-      <c r="G20" s="5">
-        <f>H20-F20</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1031.08</v>
-      </c>
-      <c r="I20" s="5">
-        <f>J20-H20</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J20" s="5">
-        <v>1053.68</v>
-      </c>
-      <c r="K20" s="5">
-        <f>L20-J20</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1064.61</v>
-      </c>
-      <c r="M20" s="5">
-        <f>N20-L20</f>
-        <v>16.1800000000001</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1080.79</v>
-      </c>
-      <c r="O20" s="5">
-        <f>P20-N20</f>
-        <v>13.6700000000001</v>
-      </c>
-      <c r="P20" s="5">
-        <v>1094.46</v>
-      </c>
-      <c r="Q20" s="5">
-        <f>R20-P20</f>
-        <v>56.26</v>
-      </c>
-      <c r="R20" s="5">
-        <v>1150.72</v>
-      </c>
-      <c r="S20" s="5">
-        <f>T20-R20</f>
-        <v>41.27</v>
-      </c>
-      <c r="T20" s="5">
-        <v>1191.99</v>
-      </c>
-      <c r="U20" s="5">
-        <f>V20-T20</f>
-        <v>35.21</v>
-      </c>
-      <c r="V20" s="12">
-        <v>1227.2</v>
-      </c>
-      <c r="W20" s="5">
-        <f>V20-D20</f>
-        <v>277.11</v>
-      </c>
-      <c r="X20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y20" s="5">
-        <v>468.37</v>
-      </c>
-      <c r="Z20" s="5">
-        <v>10</v>
-      </c>
-      <c r="AA20" s="5">
-        <v>2.2</v>
-      </c>
-      <c r="AB20" s="5">
-        <v>86194</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28">
-      <c r="A21" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="B21" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5">
         <v>927.15</v>
@@ -3367,611 +3523,660 @@
         <f>V21-T21</f>
         <v>28.76</v>
       </c>
-      <c r="V21" s="5">
+      <c r="V21" s="9">
         <v>1169.12</v>
       </c>
       <c r="W21" s="5">
-        <f>V21-D21</f>
-        <v>241.97</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>47</v>
+        <f>X21-V21</f>
+        <v>32.7600000000002</v>
+      </c>
+      <c r="X21" s="9">
+        <v>1201.88</v>
       </c>
       <c r="Y21" s="5">
-        <v>332.32</v>
-      </c>
-      <c r="Z21" s="5">
+        <f>X21-D21</f>
+        <v>274.73</v>
+      </c>
+      <c r="Z21" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA21" s="5">
+        <v>331.42</v>
+      </c>
+      <c r="AB21" s="5">
         <v>10</v>
       </c>
-      <c r="AA21" s="5">
+      <c r="AC21" s="5">
         <v>1.1</v>
       </c>
-      <c r="AB21" s="5">
+      <c r="AD21" s="5">
         <v>80664</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
-      <c r="A22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="5">
-        <v>848.93</v>
-      </c>
-      <c r="E22" s="5">
+    <row r="22" spans="1:30">
+      <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3">
+        <v>552.79</v>
+      </c>
+      <c r="E22" s="3">
         <f>F22-D22</f>
-        <v>34.5600000000001</v>
-      </c>
-      <c r="F22" s="5">
-        <v>883.49</v>
-      </c>
-      <c r="G22" s="5">
+        <v>15.9400000000001</v>
+      </c>
+      <c r="F22" s="3">
+        <v>568.73</v>
+      </c>
+      <c r="G22" s="3">
         <f>H22-F22</f>
-        <v>46.08</v>
-      </c>
-      <c r="H22" s="5">
-        <v>929.57</v>
-      </c>
-      <c r="I22" s="5">
+        <v>1.61000000000001</v>
+      </c>
+      <c r="H22" s="3">
+        <v>570.34</v>
+      </c>
+      <c r="I22" s="3">
         <f>J22-H22</f>
-        <v>27.7399999999999</v>
-      </c>
-      <c r="J22" s="5">
-        <v>957.31</v>
-      </c>
-      <c r="K22" s="5">
+        <v>7.13999999999999</v>
+      </c>
+      <c r="J22" s="3">
+        <v>577.48</v>
+      </c>
+      <c r="K22" s="3">
         <f>L22-J22</f>
-        <v>47.36</v>
-      </c>
-      <c r="L22" s="5">
-        <v>1004.67</v>
-      </c>
-      <c r="M22" s="5">
+        <v>2.88999999999999</v>
+      </c>
+      <c r="L22" s="3">
+        <v>580.37</v>
+      </c>
+      <c r="M22" s="3">
         <f>N22-L22</f>
-        <v>25.9399999999999</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1030.61</v>
-      </c>
-      <c r="O22" s="5">
+        <v>2.55999999999995</v>
+      </c>
+      <c r="N22" s="3">
+        <v>582.93</v>
+      </c>
+      <c r="O22" s="3">
         <f>P22-N22</f>
-        <v>37.71</v>
-      </c>
-      <c r="P22" s="5">
-        <v>1068.32</v>
-      </c>
-      <c r="Q22" s="5">
+        <v>24.99</v>
+      </c>
+      <c r="P22" s="3">
+        <v>607.92</v>
+      </c>
+      <c r="Q22" s="3">
         <f>R22-P22</f>
-        <v>18.3800000000001</v>
-      </c>
-      <c r="R22" s="5">
-        <v>1086.7</v>
-      </c>
-      <c r="S22" s="5">
+        <v>0.330000000000041</v>
+      </c>
+      <c r="R22" s="3">
+        <v>608.25</v>
+      </c>
+      <c r="S22" s="3">
         <f>T22-R22</f>
-        <v>21.04</v>
-      </c>
-      <c r="T22" s="5">
-        <v>1107.74</v>
-      </c>
-      <c r="U22" s="5">
+        <v>1.80999999999995</v>
+      </c>
+      <c r="T22" s="3">
+        <v>610.06</v>
+      </c>
+      <c r="U22" s="3">
         <f>V22-T22</f>
-        <v>32.7</v>
-      </c>
-      <c r="V22" s="5">
-        <v>1140.44</v>
-      </c>
-      <c r="W22" s="5">
-        <f>V22-D22</f>
-        <v>291.51</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y22" s="5">
-        <v>405.07</v>
-      </c>
-      <c r="Z22" s="5">
-        <v>30</v>
-      </c>
-      <c r="AA22" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AB22" s="5">
-        <v>78989</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+        <v>0.560000000000059</v>
+      </c>
+      <c r="V22" s="11">
+        <v>610.62</v>
+      </c>
+      <c r="W22" s="3">
+        <f>X22-V22</f>
+        <v>3.83000000000004</v>
+      </c>
+      <c r="X22" s="11">
+        <v>614.45</v>
+      </c>
+      <c r="Y22" s="3">
+        <f>X22-D22</f>
+        <v>61.6600000000001</v>
+      </c>
+      <c r="Z22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>133.25</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>49654</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D23" s="3">
-        <v>552.79</v>
+        <v>363.88</v>
       </c>
       <c r="E23" s="3">
         <f>F23-D23</f>
-        <v>15.9400000000001</v>
+        <v>14.21</v>
       </c>
       <c r="F23" s="3">
-        <v>568.73</v>
+        <v>378.09</v>
       </c>
       <c r="G23" s="3">
         <f>H23-F23</f>
-        <v>1.61000000000001</v>
+        <v>11.22</v>
       </c>
       <c r="H23" s="3">
-        <v>570.34</v>
+        <v>389.31</v>
       </c>
       <c r="I23" s="3">
         <f>J23-H23</f>
-        <v>7.13999999999999</v>
+        <v>13.62</v>
       </c>
       <c r="J23" s="3">
-        <v>577.48</v>
+        <v>402.93</v>
       </c>
       <c r="K23" s="3">
         <f>L23-J23</f>
-        <v>2.88999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="L23" s="3">
-        <v>580.37</v>
+        <v>414.06</v>
       </c>
       <c r="M23" s="3">
         <f>N23-L23</f>
-        <v>2.55999999999995</v>
+        <v>17.39</v>
       </c>
       <c r="N23" s="3">
-        <v>582.93</v>
+        <v>431.45</v>
       </c>
       <c r="O23" s="3">
         <f>P23-N23</f>
-        <v>24.99</v>
+        <v>6.32999999999998</v>
       </c>
       <c r="P23" s="3">
-        <v>607.92</v>
+        <v>437.78</v>
       </c>
       <c r="Q23" s="3">
         <f>R23-P23</f>
-        <v>0.330000000000041</v>
+        <v>53.01</v>
       </c>
       <c r="R23" s="3">
-        <v>608.25</v>
+        <v>490.79</v>
       </c>
       <c r="S23" s="3">
         <f>T23-R23</f>
-        <v>1.80999999999995</v>
+        <v>11.82</v>
       </c>
       <c r="T23" s="3">
-        <v>610.06</v>
+        <v>502.61</v>
       </c>
       <c r="U23" s="3">
         <f>V23-T23</f>
-        <v>0.560000000000059</v>
-      </c>
-      <c r="V23" s="3">
-        <v>610.62</v>
+        <v>19.3099999999999</v>
+      </c>
+      <c r="V23" s="11">
+        <v>521.92</v>
       </c>
       <c r="W23" s="3">
-        <f>V23-D23</f>
-        <v>57.83</v>
-      </c>
-      <c r="X23" s="13" t="s">
-        <v>47</v>
+        <f>X23-V23</f>
+        <v>29.5400000000001</v>
+      </c>
+      <c r="X23" s="11">
+        <v>551.46</v>
       </c>
       <c r="Y23" s="3">
-        <v>132.05</v>
-      </c>
-      <c r="Z23" s="3">
+        <f>X23-D23</f>
+        <v>187.58</v>
+      </c>
+      <c r="Z23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>150.79</v>
+      </c>
+      <c r="AB23" s="3">
         <v>0</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>49654</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28">
+      <c r="AC23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3">
-        <v>407.35</v>
+        <v>305.29</v>
       </c>
       <c r="E24" s="3">
         <f>F24-D24</f>
-        <v>13.86</v>
+        <v>17.97</v>
       </c>
       <c r="F24" s="3">
-        <v>421.21</v>
+        <v>323.26</v>
       </c>
       <c r="G24" s="3">
         <f>H24-F24</f>
-        <v>16.43</v>
+        <v>10.82</v>
       </c>
       <c r="H24" s="3">
-        <v>437.64</v>
+        <v>334.08</v>
       </c>
       <c r="I24" s="3">
         <f>J24-H24</f>
-        <v>13.64</v>
+        <v>16.2</v>
       </c>
       <c r="J24" s="3">
-        <v>451.28</v>
+        <v>350.28</v>
       </c>
       <c r="K24" s="3">
         <f>L24-J24</f>
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="L24" s="3">
-        <v>462.88</v>
+        <v>361.08</v>
       </c>
       <c r="M24" s="3">
         <f>N24-L24</f>
-        <v>47.68</v>
+        <v>9.98000000000002</v>
       </c>
       <c r="N24" s="3">
-        <v>510.56</v>
+        <v>371.06</v>
       </c>
       <c r="O24" s="3">
         <f>P24-N24</f>
-        <v>20.51</v>
+        <v>10.17</v>
       </c>
       <c r="P24" s="3">
-        <v>531.07</v>
+        <v>381.23</v>
       </c>
       <c r="Q24" s="3">
         <f>R24-P24</f>
-        <v>18.6099999999999</v>
+        <v>20.97</v>
       </c>
       <c r="R24" s="3">
-        <v>549.68</v>
+        <v>402.2</v>
       </c>
       <c r="S24" s="3">
         <f>T24-R24</f>
-        <v>11.9400000000001</v>
+        <v>5.68000000000001</v>
       </c>
       <c r="T24" s="3">
-        <v>561.62</v>
+        <v>407.88</v>
       </c>
       <c r="U24" s="3">
         <f>V24-T24</f>
-        <v>16.23</v>
-      </c>
-      <c r="V24" s="3">
-        <v>577.85</v>
+        <v>25.13</v>
+      </c>
+      <c r="V24" s="11">
+        <v>433.01</v>
       </c>
       <c r="W24" s="3">
-        <f>V24-D24</f>
-        <v>170.5</v>
-      </c>
-      <c r="X24" s="13" t="s">
-        <v>68</v>
+        <f>X24-V24</f>
+        <v>37.15</v>
+      </c>
+      <c r="X24" s="11">
+        <v>470.16</v>
       </c>
       <c r="Y24" s="3">
-        <v>252.01</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>30</v>
+        <f>X24-D24</f>
+        <v>164.87</v>
+      </c>
+      <c r="Z24" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="AA24" s="3">
-        <v>2.4</v>
+        <v>143.89</v>
       </c>
       <c r="AB24" s="3">
-        <v>43895</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28">
-      <c r="A25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="3">
-        <v>363.88</v>
-      </c>
-      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>28066</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2714.1</v>
+      </c>
+      <c r="E25" s="1">
         <f>F25-D25</f>
-        <v>14.21</v>
-      </c>
-      <c r="F25" s="3">
-        <v>378.09</v>
-      </c>
-      <c r="G25" s="3">
+        <v>123.29</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2837.39</v>
+      </c>
+      <c r="G25" s="1">
         <f>H25-F25</f>
-        <v>11.22</v>
-      </c>
-      <c r="H25" s="3">
-        <v>389.31</v>
-      </c>
-      <c r="I25" s="3">
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2933.24</v>
+      </c>
+      <c r="I25" s="1">
         <f>J25-H25</f>
-        <v>13.62</v>
-      </c>
-      <c r="J25" s="3">
-        <v>402.93</v>
-      </c>
-      <c r="K25" s="3">
+        <v>92.46</v>
+      </c>
+      <c r="J25" s="1">
+        <v>3025.7</v>
+      </c>
+      <c r="K25" s="1">
         <f>L25-J25</f>
-        <v>11.13</v>
-      </c>
-      <c r="L25" s="3">
-        <v>414.06</v>
-      </c>
-      <c r="M25" s="3">
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L25" s="1">
+        <v>3116.11</v>
+      </c>
+      <c r="M25" s="1">
         <f>N25-L25</f>
-        <v>17.39</v>
-      </c>
-      <c r="N25" s="3">
-        <v>431.45</v>
-      </c>
-      <c r="O25" s="3">
+        <v>103.54</v>
+      </c>
+      <c r="N25" s="1">
+        <v>3219.65</v>
+      </c>
+      <c r="O25" s="1">
         <f>P25-N25</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P25" s="3">
-        <v>437.78</v>
-      </c>
-      <c r="Q25" s="3">
+        <v>75.6599999999999</v>
+      </c>
+      <c r="P25" s="1">
+        <v>3295.31</v>
+      </c>
+      <c r="Q25" s="1">
         <f>R25-P25</f>
-        <v>53.01</v>
-      </c>
-      <c r="R25" s="3">
-        <v>490.79</v>
-      </c>
-      <c r="S25" s="3">
+        <v>88.98</v>
+      </c>
+      <c r="R25" s="1">
+        <v>3384.29</v>
+      </c>
+      <c r="S25" s="1">
         <f>T25-R25</f>
-        <v>11.82</v>
-      </c>
-      <c r="T25" s="3">
-        <v>502.61</v>
-      </c>
-      <c r="U25" s="3">
+        <v>102.46</v>
+      </c>
+      <c r="T25" s="1">
+        <v>3486.75</v>
+      </c>
+      <c r="U25" s="1">
         <f>V25-T25</f>
-        <v>19.3099999999999</v>
-      </c>
-      <c r="V25" s="3">
-        <v>521.92</v>
-      </c>
-      <c r="W25" s="3">
-        <f>V25-D25</f>
-        <v>158.04</v>
-      </c>
-      <c r="X25" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>135.38</v>
-      </c>
-      <c r="Z25" s="3">
+        <v>69.23</v>
+      </c>
+      <c r="V25" s="10">
+        <v>3555.98</v>
+      </c>
+      <c r="W25" s="1">
+        <f>X25-V25</f>
+        <v>133.46</v>
+      </c>
+      <c r="X25" s="10">
+        <v>3689.44</v>
+      </c>
+      <c r="Y25" s="1">
+        <f>X25-D25</f>
+        <v>975.34</v>
+      </c>
+      <c r="Z25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>785.72</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>191519</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E26" s="2">
+        <f>F26-D26</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G26" s="2">
+        <f>H26-F26</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I26" s="2">
+        <f>J26-H26</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K26" s="2">
+        <f>L26-J26</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L26" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M26" s="2">
+        <f>N26-L26</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N26" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O26" s="2">
+        <f>P26-N26</f>
+        <v>16.27</v>
+      </c>
+      <c r="P26" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>R26-P26</f>
+        <v>36.5</v>
+      </c>
+      <c r="R26" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S26" s="2">
+        <f>T26-R26</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T26" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U26" s="2">
+        <f>V26-T26</f>
+        <v>31.7599999999998</v>
+      </c>
+      <c r="V26" s="8">
+        <v>2467.14</v>
+      </c>
+      <c r="W26" s="2">
+        <f>X26-V26</f>
+        <v>53.75</v>
+      </c>
+      <c r="X26" s="8">
+        <v>2520.89</v>
+      </c>
+      <c r="Y26" s="2">
+        <f>X26-D26</f>
+        <v>337.88</v>
+      </c>
+      <c r="Z26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>616.57</v>
+      </c>
+      <c r="AB26" s="2">
         <v>0</v>
       </c>
-      <c r="AA25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="3">
-        <v>47256</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="3">
-        <v>305.29</v>
-      </c>
-      <c r="E26" s="3">
-        <f>F26-D26</f>
-        <v>17.97</v>
-      </c>
-      <c r="F26" s="3">
-        <v>323.26</v>
-      </c>
-      <c r="G26" s="3">
-        <f>H26-F26</f>
-        <v>10.82</v>
-      </c>
-      <c r="H26" s="3">
-        <v>334.08</v>
-      </c>
-      <c r="I26" s="3">
-        <f>J26-H26</f>
-        <v>16.2</v>
-      </c>
-      <c r="J26" s="3">
-        <v>350.28</v>
-      </c>
-      <c r="K26" s="3">
-        <f>L26-J26</f>
-        <v>10.8</v>
-      </c>
-      <c r="L26" s="3">
-        <v>361.08</v>
-      </c>
-      <c r="M26" s="3">
-        <f>N26-L26</f>
-        <v>9.98000000000002</v>
-      </c>
-      <c r="N26" s="3">
-        <v>371.06</v>
-      </c>
-      <c r="O26" s="3">
-        <f>P26-N26</f>
-        <v>10.17</v>
-      </c>
-      <c r="P26" s="3">
-        <v>381.23</v>
-      </c>
-      <c r="Q26" s="3">
-        <f>R26-P26</f>
-        <v>20.97</v>
-      </c>
-      <c r="R26" s="3">
-        <v>402.2</v>
-      </c>
-      <c r="S26" s="3">
-        <f>T26-R26</f>
-        <v>5.68000000000001</v>
-      </c>
-      <c r="T26" s="3">
-        <v>407.88</v>
-      </c>
-      <c r="U26" s="3">
-        <f>V26-T26</f>
-        <v>25.13</v>
-      </c>
-      <c r="V26" s="3">
-        <v>433.01</v>
-      </c>
-      <c r="W26" s="3">
-        <f>V26-D26</f>
-        <v>127.72</v>
-      </c>
-      <c r="X26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>126.95</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="2">
         <v>0</v>
       </c>
-      <c r="AA26" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>28066</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="AD26" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
+      <c r="A27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="5">
+        <v>907.94</v>
+      </c>
+      <c r="E27" s="5">
+        <f>F27-D27</f>
+        <v>64.0799999999999</v>
+      </c>
+      <c r="F27" s="5">
+        <v>972.02</v>
+      </c>
+      <c r="G27" s="5">
+        <f>H27-F27</f>
+        <v>36.26</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1008.28</v>
+      </c>
+      <c r="I27" s="5">
+        <f>J27-H27</f>
+        <v>28.8</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1037.08</v>
+      </c>
+      <c r="K27" s="5">
+        <f>L27-J27</f>
+        <v>40.1000000000001</v>
+      </c>
+      <c r="L27" s="5">
+        <v>1077.18</v>
+      </c>
+      <c r="M27" s="5">
+        <f>N27-L27</f>
+        <v>26.03</v>
+      </c>
+      <c r="N27" s="5">
+        <v>1103.21</v>
+      </c>
+      <c r="O27" s="5">
+        <f>P27-N27</f>
+        <v>28.3499999999999</v>
+      </c>
+      <c r="P27" s="5">
+        <v>1131.56</v>
+      </c>
+      <c r="Q27" s="5">
+        <f>R27-P27</f>
+        <v>50.1900000000001</v>
+      </c>
+      <c r="R27" s="5">
+        <v>1181.75</v>
+      </c>
+      <c r="S27" s="5">
+        <f>T27-R27</f>
+        <v>26.8699999999999</v>
+      </c>
+      <c r="T27" s="5">
+        <v>1208.62</v>
+      </c>
+      <c r="U27" s="5">
+        <f>V27-T27</f>
+        <v>58.3000000000002</v>
+      </c>
+      <c r="V27" s="9">
+        <v>1266.92</v>
+      </c>
+      <c r="W27" s="5">
+        <f>X27-V27</f>
+        <v>41.0599999999999</v>
+      </c>
+      <c r="X27" s="9">
+        <v>1307.98</v>
+      </c>
+      <c r="Y27" s="5">
+        <f>X27-D27</f>
+        <v>400.04</v>
+      </c>
+      <c r="Z27" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="3">
-        <v>262.39</v>
-      </c>
-      <c r="E27" s="3">
-        <f>F27-D27</f>
-        <v>11.5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>273.89</v>
-      </c>
-      <c r="G27" s="3">
-        <f>H27-F27</f>
-        <v>13.97</v>
-      </c>
-      <c r="H27" s="3">
-        <v>287.86</v>
-      </c>
-      <c r="I27" s="3">
-        <f>J27-H27</f>
-        <v>16.24</v>
-      </c>
-      <c r="J27" s="3">
-        <v>304.1</v>
-      </c>
-      <c r="K27" s="3">
-        <f>L27-J27</f>
-        <v>12.65</v>
-      </c>
-      <c r="L27" s="3">
-        <v>316.75</v>
-      </c>
-      <c r="M27" s="3">
-        <f>N27-L27</f>
-        <v>9.99000000000001</v>
-      </c>
-      <c r="N27" s="3">
-        <v>326.74</v>
-      </c>
-      <c r="O27" s="3">
-        <f>P27-N27</f>
-        <v>6.31999999999999</v>
-      </c>
-      <c r="P27" s="3">
-        <v>333.06</v>
-      </c>
-      <c r="Q27" s="3">
-        <f>R27-P27</f>
-        <v>21.13</v>
-      </c>
-      <c r="R27" s="3">
-        <v>354.19</v>
-      </c>
-      <c r="S27" s="3">
-        <f>T27-R27</f>
-        <v>17.68</v>
-      </c>
-      <c r="T27" s="3">
-        <v>371.87</v>
-      </c>
-      <c r="U27" s="3">
-        <f>V27-T27</f>
-        <v>11.66</v>
-      </c>
-      <c r="V27" s="3">
-        <v>383.53</v>
-      </c>
-      <c r="W27" s="3">
-        <f>V27-D27</f>
-        <v>121.14</v>
-      </c>
-      <c r="X27" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>131.21</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>36684</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+      <c r="AA27" s="5">
+        <v>447.17</v>
+      </c>
+      <c r="AB27" s="5">
+        <v>35</v>
+      </c>
+      <c r="AC27" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>65285</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3996,13 +4201,15 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="7"/>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -4015,21 +4222,23 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
+      <c r="AA31" s="7"/>
+      <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4053,58 +4262,60 @@
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AB27">
-    <sortCondition ref="V2" descending="1"/>
+  <sortState ref="A2:AD27">
+    <sortCondition ref="Z4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4141,40 +4352,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4515,7 +4726,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -4569,7 +4780,7 @@
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -4878,10 +5089,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -5425,7 +5636,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
+    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="105">
   <si>
     <t>区服</t>
   </si>
@@ -79,6 +79,9 @@
     <t>战力（2025.6.4）</t>
   </si>
   <si>
+    <t>战力（2025.6.11）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -97,6 +100,39 @@
     <t>抽卡数</t>
   </si>
   <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>狐狸（快攻）</t>
+  </si>
+  <si>
     <t>145区</t>
   </si>
   <si>
@@ -109,16 +145,55 @@
     <t>白处尊（养神）</t>
   </si>
   <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>洞察妹（洞察）</t>
+  </si>
+  <si>
     <t>杜佳捷</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
     <t>白处尊（杂糅）</t>
   </si>
   <si>
-    <t>148区</t>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>小黑</t>
   </si>
   <si>
     <t>12345。</t>
@@ -130,133 +205,61 @@
     <t>冰男（浦冰）</t>
   </si>
   <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>大氪</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>146区</t>
-  </si>
-  <si>
     <t>谢之求学者</t>
   </si>
   <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>狐狸（快攻）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
     <t>150区</t>
   </si>
   <si>
     <t>开飞机的贝塔</t>
   </si>
   <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
     <t>[永恒]</t>
   </si>
   <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
+    <t>秋雨</t>
+  </si>
+  <si>
     <t>糊涂阳</t>
   </si>
   <si>
-    <t>微氪</t>
-  </si>
-  <si>
     <t>丽娅（杂糅）</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>圣母（杂糅）</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -1020,20 +1023,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1041,17 +1053,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1369,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD39"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1392,16 +1395,17 @@
     <col min="18" max="18" width="17.8666666666667" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="17.3916666666667" customWidth="1"/>
-    <col min="23" max="25" width="18.0166666666667" customWidth="1"/>
-    <col min="26" max="26" width="18.8916666666667" customWidth="1"/>
-    <col min="27" max="27" width="14.5416666666667" customWidth="1"/>
-    <col min="28" max="28" width="11.625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="17.3916666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="24" max="27" width="18.0166666666667" customWidth="1"/>
+    <col min="28" max="28" width="18.8916666666667" customWidth="1"/>
+    <col min="29" max="29" width="14.5416666666667" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="11.625" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1475,754 +1479,809 @@
         <v>14</v>
       </c>
       <c r="Y1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:30">
-      <c r="A2" s="2" t="s">
+      <c r="AF1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:32">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6">
+        <v>4105.48</v>
+      </c>
+      <c r="E2" s="6">
+        <f>F2-D2</f>
+        <v>181.21</v>
+      </c>
+      <c r="F2" s="6">
+        <v>4286.69</v>
+      </c>
+      <c r="G2" s="6">
+        <f>H2-F2</f>
+        <v>139.09</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4425.78</v>
+      </c>
+      <c r="I2" s="6">
+        <f>J2-H2</f>
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J2" s="6">
+        <v>4480.66</v>
+      </c>
+      <c r="K2" s="6">
+        <f>L2-J2</f>
+        <v>104.900000000001</v>
+      </c>
+      <c r="L2" s="6">
+        <v>4585.56</v>
+      </c>
+      <c r="M2" s="6">
+        <f>N2-L2</f>
+        <v>70.29</v>
+      </c>
+      <c r="N2" s="6">
+        <v>4655.85</v>
+      </c>
+      <c r="O2" s="6">
+        <f>P2-N2</f>
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P2" s="6">
+        <v>4705.02</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>R2-P2</f>
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R2" s="6">
+        <v>4743.24</v>
+      </c>
+      <c r="S2" s="6">
+        <f>T2-R2</f>
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T2" s="6">
+        <v>4788.86</v>
+      </c>
+      <c r="U2" s="6">
+        <f>V2-T2</f>
+        <v>27.5900000000001</v>
+      </c>
+      <c r="V2" s="8">
+        <v>4816.45</v>
+      </c>
+      <c r="W2" s="6">
+        <f>X2-V2</f>
+        <v>158.22</v>
+      </c>
+      <c r="X2" s="8">
+        <v>4974.67</v>
+      </c>
+      <c r="Y2" s="6">
+        <f>Z2-X2</f>
+        <v>32.8999999999996</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>5007.57</v>
+      </c>
+      <c r="AA2" s="6">
+        <f>Z2-D2</f>
+        <v>902.09</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC2" s="6">
+        <v>1376.92</v>
+      </c>
+      <c r="AD2" s="14">
+        <v>400</v>
+      </c>
+      <c r="AE2" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="AF2" s="14">
+        <v>186759</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2714.1</v>
+      </c>
+      <c r="E3" s="1">
+        <f>F3-D3</f>
+        <v>123.29</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2837.39</v>
+      </c>
+      <c r="G3" s="1">
+        <f>H3-F3</f>
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2933.24</v>
+      </c>
+      <c r="I3" s="1">
+        <f>J3-H3</f>
+        <v>92.46</v>
+      </c>
+      <c r="J3" s="1">
+        <v>3025.7</v>
+      </c>
+      <c r="K3" s="1">
+        <f>L3-J3</f>
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L3" s="1">
+        <v>3116.11</v>
+      </c>
+      <c r="M3" s="1">
+        <f>N3-L3</f>
+        <v>103.54</v>
+      </c>
+      <c r="N3" s="1">
+        <v>3219.65</v>
+      </c>
+      <c r="O3" s="1">
+        <f>P3-N3</f>
+        <v>75.6599999999999</v>
+      </c>
+      <c r="P3" s="1">
+        <v>3295.31</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>R3-P3</f>
+        <v>88.98</v>
+      </c>
+      <c r="R3" s="1">
+        <v>3384.29</v>
+      </c>
+      <c r="S3" s="1">
+        <f>T3-R3</f>
+        <v>102.46</v>
+      </c>
+      <c r="T3" s="1">
+        <v>3486.75</v>
+      </c>
+      <c r="U3" s="1">
+        <f>V3-T3</f>
+        <v>69.23</v>
+      </c>
+      <c r="V3" s="9">
+        <v>3555.98</v>
+      </c>
+      <c r="W3" s="1">
+        <f>X3-V3</f>
+        <v>133.46</v>
+      </c>
+      <c r="X3" s="9">
+        <v>3689.44</v>
+      </c>
+      <c r="Y3" s="1">
+        <f>Z3-X3</f>
+        <v>10.5999999999999</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>3700.04</v>
+      </c>
+      <c r="AA3" s="1">
+        <f>Z3-D3</f>
+        <v>985.94</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>785.72</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>500</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>191519</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2533.85</v>
+      </c>
+      <c r="E4" s="1">
+        <f>F4-D4</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2583.9</v>
+      </c>
+      <c r="G4" s="1">
+        <f>H4-F4</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2669.66</v>
+      </c>
+      <c r="I4" s="1">
+        <f>J4-H4</f>
+        <v>81.79</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2751.45</v>
+      </c>
+      <c r="K4" s="1">
+        <f>L4-J4</f>
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2834.62</v>
+      </c>
+      <c r="M4" s="1">
+        <f>N4-L4</f>
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2891.61</v>
+      </c>
+      <c r="O4" s="1">
+        <f>P4-N4</f>
+        <v>103.98</v>
+      </c>
+      <c r="P4" s="1">
+        <v>2995.59</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>R4-P4</f>
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R4" s="1">
+        <v>3064.44</v>
+      </c>
+      <c r="S4" s="1">
+        <f>T4-R4</f>
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T4" s="1">
+        <v>3112.05</v>
+      </c>
+      <c r="U4" s="1">
+        <f>V4-T4</f>
+        <v>38.1599999999999</v>
+      </c>
+      <c r="V4" s="9">
+        <v>3150.21</v>
+      </c>
+      <c r="W4" s="1">
+        <f>X4-V4</f>
+        <v>146.1</v>
+      </c>
+      <c r="X4" s="9">
+        <v>3296.31</v>
+      </c>
+      <c r="Y4" s="1">
+        <f>Z4-X4</f>
+        <v>31.9400000000001</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>3328.25</v>
+      </c>
+      <c r="AA4" s="1">
+        <f>Z4-D4</f>
+        <v>794.4</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>662.22</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>200</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>172501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
         <v>1754.54</v>
-      </c>
-      <c r="E2" s="2">
-        <f>F2-D2</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1807.91</v>
-      </c>
-      <c r="G2" s="2">
-        <f>H2-F2</f>
-        <v>90.24</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1898.15</v>
-      </c>
-      <c r="I2" s="2">
-        <f>J2-H2</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1988.53</v>
-      </c>
-      <c r="K2" s="2">
-        <f>L2-J2</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L2" s="2">
-        <v>2048.24</v>
-      </c>
-      <c r="M2" s="2">
-        <f>N2-L2</f>
-        <v>153.99</v>
-      </c>
-      <c r="N2" s="2">
-        <v>2202.23</v>
-      </c>
-      <c r="O2" s="2">
-        <f>P2-N2</f>
-        <v>64.21</v>
-      </c>
-      <c r="P2" s="2">
-        <v>2266.44</v>
-      </c>
-      <c r="Q2" s="2">
-        <f>R2-P2</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R2" s="2">
-        <v>2314</v>
-      </c>
-      <c r="S2" s="2">
-        <f>T2-R2</f>
-        <v>59.6500000000001</v>
-      </c>
-      <c r="T2" s="2">
-        <v>2373.65</v>
-      </c>
-      <c r="U2" s="2">
-        <f>V2-T2</f>
-        <v>70.6399999999999</v>
-      </c>
-      <c r="V2" s="8">
-        <v>2444.29</v>
-      </c>
-      <c r="W2" s="2">
-        <f>X2-V2</f>
-        <v>95.9299999999998</v>
-      </c>
-      <c r="X2" s="8">
-        <v>2540.22</v>
-      </c>
-      <c r="Y2" s="2">
-        <f>X2-D2</f>
-        <v>785.68</v>
-      </c>
-      <c r="Z2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>477.92</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>300</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>132783</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1726.42</v>
-      </c>
-      <c r="E3" s="2">
-        <f>F3-D3</f>
-        <v>56.28</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1782.7</v>
-      </c>
-      <c r="G3" s="2">
-        <f>H3-F3</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1853.62</v>
-      </c>
-      <c r="I3" s="2">
-        <f>J3-H3</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1903.2</v>
-      </c>
-      <c r="K3" s="2">
-        <f>L3-J3</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1943.61</v>
-      </c>
-      <c r="M3" s="2">
-        <f>N3-L3</f>
-        <v>30.01</v>
-      </c>
-      <c r="N3" s="2">
-        <v>1973.62</v>
-      </c>
-      <c r="O3" s="2">
-        <f>P3-N3</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P3" s="2">
-        <v>2056.9</v>
-      </c>
-      <c r="Q3" s="2">
-        <f>R3-P3</f>
-        <v>25.6399999999999</v>
-      </c>
-      <c r="R3" s="2">
-        <v>2082.54</v>
-      </c>
-      <c r="S3" s="2">
-        <f>T3-R3</f>
-        <v>66.46</v>
-      </c>
-      <c r="T3" s="2">
-        <v>2149</v>
-      </c>
-      <c r="U3" s="2">
-        <f>V3-T3</f>
-        <v>43.5599999999999</v>
-      </c>
-      <c r="V3" s="8">
-        <v>2192.56</v>
-      </c>
-      <c r="W3" s="2">
-        <f>X3-V3</f>
-        <v>46.3200000000002</v>
-      </c>
-      <c r="X3" s="8">
-        <v>2238.88</v>
-      </c>
-      <c r="Y3" s="2">
-        <f>X3-D3</f>
-        <v>512.46</v>
-      </c>
-      <c r="Z3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>544.12</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>50</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>124763</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
-      <c r="A4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1156.57</v>
-      </c>
-      <c r="E4" s="5">
-        <f>F4-D4</f>
-        <v>40.4400000000001</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1197.01</v>
-      </c>
-      <c r="G4" s="5">
-        <f>H4-F4</f>
-        <v>46.97</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1243.98</v>
-      </c>
-      <c r="I4" s="5">
-        <f>J4-H4</f>
-        <v>58.49</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1302.47</v>
-      </c>
-      <c r="K4" s="5">
-        <f>L4-J4</f>
-        <v>36.6399999999999</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1339.11</v>
-      </c>
-      <c r="M4" s="5">
-        <f>N4-L4</f>
-        <v>33.99</v>
-      </c>
-      <c r="N4" s="5">
-        <v>1373.1</v>
-      </c>
-      <c r="O4" s="5">
-        <f>P4-N4</f>
-        <v>30.0600000000002</v>
-      </c>
-      <c r="P4" s="5">
-        <v>1403.16</v>
-      </c>
-      <c r="Q4" s="5">
-        <f>R4-P4</f>
-        <v>47.3</v>
-      </c>
-      <c r="R4" s="5">
-        <v>1450.46</v>
-      </c>
-      <c r="S4" s="5">
-        <f>T4-R4</f>
-        <v>46.8299999999999</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1497.29</v>
-      </c>
-      <c r="U4" s="5">
-        <f>V4-T4</f>
-        <v>58.6500000000001</v>
-      </c>
-      <c r="V4" s="9">
-        <v>1555.94</v>
-      </c>
-      <c r="W4" s="5">
-        <f>X4-V4</f>
-        <v>70.3099999999999</v>
-      </c>
-      <c r="X4" s="9">
-        <v>1626.25</v>
-      </c>
-      <c r="Y4" s="5">
-        <f>X4-D4</f>
-        <v>469.68</v>
-      </c>
-      <c r="Z4" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA4" s="5">
-        <v>433.42</v>
-      </c>
-      <c r="AB4" s="5">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="5">
-        <v>3</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>100457</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1425.22</v>
       </c>
       <c r="E5" s="2">
         <f>F5-D5</f>
-        <v>64.8599999999999</v>
+        <v>53.3700000000001</v>
       </c>
       <c r="F5" s="2">
-        <v>1490.08</v>
+        <v>1807.91</v>
       </c>
       <c r="G5" s="2">
         <f>H5-F5</f>
-        <v>46</v>
+        <v>90.24</v>
       </c>
       <c r="H5" s="2">
-        <v>1536.08</v>
+        <v>1898.15</v>
       </c>
       <c r="I5" s="2">
         <f>J5-H5</f>
-        <v>50.8500000000001</v>
+        <v>90.3799999999999</v>
       </c>
       <c r="J5" s="2">
-        <v>1586.93</v>
+        <v>1988.53</v>
       </c>
       <c r="K5" s="2">
         <f>L5-J5</f>
-        <v>86.5599999999999</v>
+        <v>59.7099999999998</v>
       </c>
       <c r="L5" s="2">
-        <v>1673.49</v>
+        <v>2048.24</v>
       </c>
       <c r="M5" s="2">
         <f>N5-L5</f>
-        <v>38.5599999999999</v>
+        <v>153.99</v>
       </c>
       <c r="N5" s="2">
-        <v>1712.05</v>
+        <v>2202.23</v>
       </c>
       <c r="O5" s="2">
         <f>P5-N5</f>
-        <v>57.0900000000001</v>
+        <v>64.21</v>
       </c>
       <c r="P5" s="2">
-        <v>1769.14</v>
+        <v>2266.44</v>
       </c>
       <c r="Q5" s="2">
         <f>R5-P5</f>
-        <v>50.8699999999999</v>
+        <v>47.5599999999999</v>
       </c>
       <c r="R5" s="2">
-        <v>1820.01</v>
+        <v>2314</v>
       </c>
       <c r="S5" s="2">
         <f>T5-R5</f>
-        <v>94.4300000000001</v>
+        <v>59.6500000000001</v>
       </c>
       <c r="T5" s="2">
-        <v>1914.44</v>
+        <v>2373.65</v>
       </c>
       <c r="U5" s="2">
         <f>V5-T5</f>
-        <v>31.51</v>
-      </c>
-      <c r="V5" s="8">
-        <v>1945.95</v>
+        <v>70.6399999999999</v>
+      </c>
+      <c r="V5" s="10">
+        <v>2444.29</v>
       </c>
       <c r="W5" s="2">
         <f>X5-V5</f>
-        <v>92.5899999999999</v>
-      </c>
-      <c r="X5" s="8">
-        <v>2038.54</v>
+        <v>95.9299999999998</v>
+      </c>
+      <c r="X5" s="10">
+        <v>2540.22</v>
       </c>
       <c r="Y5" s="2">
-        <f>X5-D5</f>
-        <v>613.32</v>
-      </c>
-      <c r="Z5" s="13" t="s">
+        <f>Z5-X5</f>
+        <v>90.3200000000002</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>2630.54</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>Z5-D5</f>
+        <v>876</v>
+      </c>
+      <c r="AB5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>477.92</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>300</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>132783</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA5" s="2">
-        <v>498.7</v>
-      </c>
-      <c r="AB5" s="5">
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2136.24</v>
+      </c>
+      <c r="E6" s="2">
+        <f>F6-D6</f>
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2177.06</v>
+      </c>
+      <c r="G6" s="2">
+        <f>H6-F6</f>
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2239.66</v>
+      </c>
+      <c r="I6" s="2">
+        <f>J6-H6</f>
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2286.73</v>
+      </c>
+      <c r="K6" s="2">
+        <f>L6-J6</f>
+        <v>25.52</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2312.25</v>
+      </c>
+      <c r="M6" s="2">
+        <f>N6-L6</f>
+        <v>36.7800000000002</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2349.03</v>
+      </c>
+      <c r="O6" s="2">
+        <f>P6-N6</f>
+        <v>-18.02</v>
+      </c>
+      <c r="P6" s="2">
+        <v>2331.01</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>R6-P6</f>
+        <v>62.7599999999998</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2393.77</v>
+      </c>
+      <c r="S6" s="2">
+        <f>T6-R6</f>
+        <v>55.5599999999999</v>
+      </c>
+      <c r="T6" s="2">
+        <v>2449.33</v>
+      </c>
+      <c r="U6" s="2">
+        <f>V6-T6</f>
+        <v>31.96</v>
+      </c>
+      <c r="V6" s="10">
+        <v>2481.29</v>
+      </c>
+      <c r="W6" s="2">
+        <f>X6-V6</f>
+        <v>109.47</v>
+      </c>
+      <c r="X6" s="10">
+        <v>2590.76</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>Z6-X6</f>
+        <v>20.4299999999998</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>2611.19</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>Z6-D6</f>
+        <v>474.95</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>814.82</v>
+      </c>
+      <c r="AD6" s="2">
         <v>20</v>
       </c>
-      <c r="AC5" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AD5" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
-      <c r="A6" s="5" t="s">
+      <c r="AE6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D7" s="2">
+        <v>1966.62</v>
+      </c>
+      <c r="E7" s="2">
+        <f>F7-D7</f>
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2015.64</v>
+      </c>
+      <c r="G7" s="2">
+        <f>H7-F7</f>
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2049.8</v>
+      </c>
+      <c r="I7" s="2">
+        <f>J7-H7</f>
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2139.9</v>
+      </c>
+      <c r="K7" s="2">
+        <f>L7-J7</f>
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2193.07</v>
+      </c>
+      <c r="M7" s="2">
+        <f>N7-L7</f>
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2256.98</v>
+      </c>
+      <c r="O7" s="2">
+        <f>P7-N7</f>
+        <v>45.71</v>
+      </c>
+      <c r="P7" s="2">
+        <v>2302.69</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>R7-P7</f>
+        <v>37.2199999999998</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2339.91</v>
+      </c>
+      <c r="S7" s="2">
+        <f>T7-R7</f>
+        <v>47.3099999999999</v>
+      </c>
+      <c r="T7" s="2">
+        <v>2387.22</v>
+      </c>
+      <c r="U7" s="2">
+        <f>V7-T7</f>
+        <v>88.2600000000002</v>
+      </c>
+      <c r="V7" s="10">
+        <v>2475.48</v>
+      </c>
+      <c r="W7" s="2">
+        <f>X7-V7</f>
+        <v>67.5900000000001</v>
+      </c>
+      <c r="X7" s="10">
+        <v>2543.07</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>Z7-X7</f>
+        <v>22.73</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>2565.8</v>
+      </c>
+      <c r="AA7" s="2">
+        <f>Z7-D7</f>
+        <v>599.18</v>
+      </c>
+      <c r="AB7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>815.12</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>65</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>130589</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="5">
-        <v>1576.18</v>
-      </c>
-      <c r="E6" s="5">
-        <f>F6-D6</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1615.02</v>
-      </c>
-      <c r="G6" s="5">
-        <f>H6-F6</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1650.62</v>
-      </c>
-      <c r="I6" s="5">
-        <f>J6-H6</f>
-        <v>37.47</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1688.09</v>
-      </c>
-      <c r="K6" s="5">
-        <f>L6-J6</f>
-        <v>21.49</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1709.58</v>
-      </c>
-      <c r="M6" s="5">
-        <f>N6-L6</f>
-        <v>24.53</v>
-      </c>
-      <c r="N6" s="5">
-        <v>1734.11</v>
-      </c>
-      <c r="O6" s="5">
-        <f>P6-N6</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P6" s="5">
-        <v>1753.64</v>
-      </c>
-      <c r="Q6" s="5">
-        <f>R6-P6</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R6" s="5">
-        <v>1818.75</v>
-      </c>
-      <c r="S6" s="5">
-        <f>T6-R6</f>
-        <v>34.3699999999999</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1853.12</v>
-      </c>
-      <c r="U6" s="5">
-        <f>V6-T6</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V6" s="9">
-        <v>1893.96</v>
-      </c>
-      <c r="W6" s="5">
-        <f>X6-V6</f>
-        <v>40.96</v>
-      </c>
-      <c r="X6" s="9">
-        <v>1934.92</v>
-      </c>
-      <c r="Y6" s="5">
-        <f>X6-D6</f>
-        <v>358.74</v>
-      </c>
-      <c r="Z6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA6" s="5">
-        <v>407.07</v>
-      </c>
-      <c r="AB6" s="5">
+      <c r="D8" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E8" s="2">
+        <f>F8-D8</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G8" s="2">
+        <f>H8-F8</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I8" s="2">
+        <f>J8-H8</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K8" s="2">
+        <f>L8-J8</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M8" s="2">
+        <f>N8-L8</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O8" s="2">
+        <f>P8-N8</f>
+        <v>16.27</v>
+      </c>
+      <c r="P8" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>R8-P8</f>
+        <v>36.5</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S8" s="2">
+        <f>T8-R8</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U8" s="2">
+        <f>V8-T8</f>
+        <v>31.7599999999998</v>
+      </c>
+      <c r="V8" s="10">
+        <v>2467.14</v>
+      </c>
+      <c r="W8" s="2">
+        <f>X8-V8</f>
+        <v>53.75</v>
+      </c>
+      <c r="X8" s="10">
+        <v>2520.89</v>
+      </c>
+      <c r="Y8" s="2">
+        <f>Z8-X8</f>
+        <v>24.3299999999999</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>2545.22</v>
+      </c>
+      <c r="AA8" s="2">
+        <f>Z8-D8</f>
+        <v>362.21</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>616.57</v>
+      </c>
+      <c r="AD8" s="2">
         <v>0</v>
       </c>
-      <c r="AC6" s="5">
+      <c r="AE8" s="2">
         <v>0</v>
       </c>
-      <c r="AD6" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1349.35</v>
-      </c>
-      <c r="E7" s="5">
-        <f>F7-D7</f>
-        <v>49.6200000000001</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1398.97</v>
-      </c>
-      <c r="G7" s="5">
-        <f>H7-F7</f>
-        <v>27.79</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1426.76</v>
-      </c>
-      <c r="I7" s="5">
-        <f>J7-H7</f>
-        <v>29.02</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1455.78</v>
-      </c>
-      <c r="K7" s="5">
-        <f>L7-J7</f>
-        <v>97.8800000000001</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1553.66</v>
-      </c>
-      <c r="M7" s="5">
-        <f>N7-L7</f>
-        <v>42.3599999999999</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1596.02</v>
-      </c>
-      <c r="O7" s="5">
-        <f>P7-N7</f>
-        <v>54.22</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1650.24</v>
-      </c>
-      <c r="Q7" s="5">
-        <f>R7-P7</f>
-        <v>35.5899999999999</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1685.83</v>
-      </c>
-      <c r="S7" s="5">
-        <f>T7-R7</f>
-        <v>68.1300000000001</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1753.96</v>
-      </c>
-      <c r="U7" s="5">
-        <f>V7-T7</f>
-        <v>58.5599999999999</v>
-      </c>
-      <c r="V7" s="9">
-        <v>1812.52</v>
-      </c>
-      <c r="W7" s="5">
-        <f>X7-V7</f>
-        <v>67.21</v>
-      </c>
-      <c r="X7" s="9">
-        <v>1879.73</v>
-      </c>
-      <c r="Y7" s="5">
-        <f>X7-D7</f>
-        <v>530.38</v>
-      </c>
-      <c r="Z7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA7" s="5">
-        <v>451.2</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>20</v>
-      </c>
-      <c r="AC7" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AD7" s="5">
-        <v>109106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1060.77</v>
-      </c>
-      <c r="E8" s="5">
-        <f>F8-D8</f>
-        <v>63.24</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1124.01</v>
-      </c>
-      <c r="G8" s="5">
-        <f>H8-F8</f>
-        <v>19.6700000000001</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1143.68</v>
-      </c>
-      <c r="I8" s="5">
-        <f>J8-H8</f>
-        <v>47.76</v>
-      </c>
-      <c r="J8" s="5">
-        <v>1191.44</v>
-      </c>
-      <c r="K8" s="5">
-        <f>L8-J8</f>
-        <v>40.22</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1231.66</v>
-      </c>
-      <c r="M8" s="5">
-        <f>N8-L8</f>
-        <v>44.8</v>
-      </c>
-      <c r="N8" s="5">
-        <v>1276.46</v>
-      </c>
-      <c r="O8" s="5">
-        <f>P8-N8</f>
-        <v>28.03</v>
-      </c>
-      <c r="P8" s="5">
-        <v>1304.49</v>
-      </c>
-      <c r="Q8" s="5">
-        <f>R8-P8</f>
-        <v>31.78</v>
-      </c>
-      <c r="R8" s="5">
-        <v>1336.27</v>
-      </c>
-      <c r="S8" s="5">
-        <f>T8-R8</f>
-        <v>44.9000000000001</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1381.17</v>
-      </c>
-      <c r="U8" s="5">
-        <f>V8-T8</f>
-        <v>53.1499999999999</v>
-      </c>
-      <c r="V8" s="9">
-        <v>1434.32</v>
-      </c>
-      <c r="W8" s="5">
-        <f>X8-V8</f>
-        <v>41.46</v>
-      </c>
-      <c r="X8" s="9">
-        <v>1475.78</v>
-      </c>
-      <c r="Y8" s="5">
-        <f>X8-D8</f>
-        <v>415.01</v>
-      </c>
-      <c r="Z8" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA8" s="5">
-        <v>277.72</v>
-      </c>
-      <c r="AB8" s="5">
-        <v>10</v>
-      </c>
-      <c r="AC8" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="AD8" s="5">
-        <v>71153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30">
+      <c r="AF8" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2">
         <v>1735.94</v>
@@ -2287,251 +2346,272 @@
         <f>V9-T9</f>
         <v>68.9400000000001</v>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="10">
         <v>2251.59</v>
       </c>
       <c r="W9" s="2">
         <f>X9-V9</f>
         <v>72.0299999999997</v>
       </c>
-      <c r="X9" s="8">
+      <c r="X9" s="10">
         <v>2323.62</v>
       </c>
       <c r="Y9" s="2">
-        <f>X9-D9</f>
-        <v>587.68</v>
-      </c>
-      <c r="Z9" s="13" t="s">
-        <v>41</v>
+        <f>Z9-X9</f>
+        <v>23.6300000000001</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>2347.25</v>
       </c>
       <c r="AA9" s="2">
+        <f>Z9-D9</f>
+        <v>611.31</v>
+      </c>
+      <c r="AB9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC9" s="2">
         <v>538.92</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AD9" s="2">
         <v>80</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AE9" s="2">
         <v>7.2</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AF9" s="2">
         <v>150192</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="1:32">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2533.85</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="2">
+        <v>1726.42</v>
+      </c>
+      <c r="E10" s="2">
         <f>F10-D10</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2583.9</v>
-      </c>
-      <c r="G10" s="1">
+        <v>56.28</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1782.7</v>
+      </c>
+      <c r="G10" s="2">
         <f>H10-F10</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H10" s="1">
-        <v>2669.66</v>
-      </c>
-      <c r="I10" s="1">
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1853.62</v>
+      </c>
+      <c r="I10" s="2">
         <f>J10-H10</f>
-        <v>81.79</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2751.45</v>
-      </c>
-      <c r="K10" s="1">
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1903.2</v>
+      </c>
+      <c r="K10" s="2">
         <f>L10-J10</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L10" s="1">
-        <v>2834.62</v>
-      </c>
-      <c r="M10" s="1">
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1943.61</v>
+      </c>
+      <c r="M10" s="2">
         <f>N10-L10</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N10" s="1">
-        <v>2891.61</v>
-      </c>
-      <c r="O10" s="1">
+        <v>30.01</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1973.62</v>
+      </c>
+      <c r="O10" s="2">
         <f>P10-N10</f>
-        <v>103.98</v>
-      </c>
-      <c r="P10" s="1">
-        <v>2995.59</v>
-      </c>
-      <c r="Q10" s="1">
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2056.9</v>
+      </c>
+      <c r="Q10" s="2">
         <f>R10-P10</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R10" s="1">
-        <v>3064.44</v>
-      </c>
-      <c r="S10" s="1">
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2082.54</v>
+      </c>
+      <c r="S10" s="2">
         <f>T10-R10</f>
-        <v>47.6100000000001</v>
-      </c>
-      <c r="T10" s="1">
-        <v>3112.05</v>
-      </c>
-      <c r="U10" s="1">
+        <v>66.46</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2149</v>
+      </c>
+      <c r="U10" s="2">
         <f>V10-T10</f>
-        <v>38.1599999999999</v>
+        <v>43.5599999999999</v>
       </c>
       <c r="V10" s="10">
-        <v>3150.21</v>
-      </c>
-      <c r="W10" s="1">
+        <v>2192.56</v>
+      </c>
+      <c r="W10" s="2">
         <f>X10-V10</f>
-        <v>146.1</v>
+        <v>46.3200000000002</v>
       </c>
       <c r="X10" s="10">
-        <v>3296.31</v>
-      </c>
-      <c r="Y10" s="1">
-        <f>X10-D10</f>
-        <v>762.46</v>
-      </c>
-      <c r="Z10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>662.22</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>200</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>172501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
+        <v>2238.88</v>
+      </c>
+      <c r="Y10" s="2">
+        <f>Z10-X10</f>
+        <v>17.23</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>2256.11</v>
+      </c>
+      <c r="AA10" s="2">
+        <f>Z10-D10</f>
+        <v>529.69</v>
+      </c>
+      <c r="AB10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="AC10" s="2">
+        <v>544.12</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>50</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>124763</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1425.22</v>
+      </c>
+      <c r="E11" s="2">
+        <f>F11-D11</f>
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1490.08</v>
+      </c>
+      <c r="G11" s="2">
+        <f>H11-F11</f>
+        <v>46</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1536.08</v>
+      </c>
+      <c r="I11" s="2">
+        <f>J11-H11</f>
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1586.93</v>
+      </c>
+      <c r="K11" s="2">
+        <f>L11-J11</f>
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1673.49</v>
+      </c>
+      <c r="M11" s="2">
+        <f>N11-L11</f>
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1712.05</v>
+      </c>
+      <c r="O11" s="2">
+        <f>P11-N11</f>
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P11" s="2">
+        <v>1769.14</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>R11-P11</f>
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1820.01</v>
+      </c>
+      <c r="S11" s="2">
+        <f>T11-R11</f>
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1914.44</v>
+      </c>
+      <c r="U11" s="2">
+        <f>V11-T11</f>
+        <v>31.51</v>
+      </c>
+      <c r="V11" s="10">
+        <v>1945.95</v>
+      </c>
+      <c r="W11" s="2">
+        <f>X11-V11</f>
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X11" s="10">
+        <v>2038.54</v>
+      </c>
+      <c r="Y11" s="2">
+        <f>Z11-X11</f>
+        <v>48.1399999999999</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>2086.68</v>
+      </c>
+      <c r="AA11" s="2">
+        <f>Z11-D11</f>
+        <v>661.46</v>
+      </c>
+      <c r="AB11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>498.7</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5">
-        <v>1446.65</v>
-      </c>
-      <c r="E11" s="5">
-        <f>F11-D11</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1474.83</v>
-      </c>
-      <c r="G11" s="5">
-        <f>H11-F11</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1538.65</v>
-      </c>
-      <c r="I11" s="5">
-        <f>J11-H11</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J11" s="5">
-        <v>1561.57</v>
-      </c>
-      <c r="K11" s="5">
-        <f>L11-J11</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1632.43</v>
-      </c>
-      <c r="M11" s="5">
-        <f>N11-L11</f>
-        <v>37.4099999999999</v>
-      </c>
-      <c r="N11" s="5">
-        <v>1669.84</v>
-      </c>
-      <c r="O11" s="5">
-        <f>P11-N11</f>
-        <v>32.8300000000002</v>
-      </c>
-      <c r="P11" s="5">
-        <v>1702.67</v>
-      </c>
-      <c r="Q11" s="5">
-        <f>R11-P11</f>
-        <v>51.9499999999998</v>
-      </c>
-      <c r="R11" s="5">
-        <v>1754.62</v>
-      </c>
-      <c r="S11" s="5">
-        <f>T11-R11</f>
-        <v>40.1200000000001</v>
-      </c>
-      <c r="T11" s="5">
-        <v>1794.74</v>
-      </c>
-      <c r="U11" s="5">
-        <f>V11-T11</f>
-        <v>77.5</v>
-      </c>
-      <c r="V11" s="9">
-        <v>1872.24</v>
-      </c>
-      <c r="W11" s="5">
-        <f>X11-V11</f>
-        <v>79.5899999999999</v>
-      </c>
-      <c r="X11" s="9">
-        <v>1951.83</v>
-      </c>
-      <c r="Y11" s="5">
-        <f>X11-D11</f>
-        <v>505.18</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA11" s="5">
-        <v>767.57</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>65</v>
-      </c>
-      <c r="AC11" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>109333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D12" s="5">
         <v>1350.52</v>
@@ -2596,869 +2676,932 @@
         <f>V12-T12</f>
         <v>66.5899999999999</v>
       </c>
-      <c r="V12" s="9">
+      <c r="V12" s="11">
         <v>1898.56</v>
       </c>
       <c r="W12" s="5">
         <f>X12-V12</f>
         <v>48.77</v>
       </c>
-      <c r="X12" s="9">
+      <c r="X12" s="11">
         <v>1947.33</v>
       </c>
       <c r="Y12" s="5">
-        <f>X12-D12</f>
-        <v>596.81</v>
-      </c>
-      <c r="Z12" s="14" t="s">
-        <v>47</v>
+        <f>Z12-X12</f>
+        <v>59.47</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>2006.8</v>
       </c>
       <c r="AA12" s="5">
+        <f>Z12-D12</f>
+        <v>656.28</v>
+      </c>
+      <c r="AB12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC12" s="5">
         <v>590.12</v>
       </c>
-      <c r="AB12" s="5">
+      <c r="AD12" s="5">
         <v>65</v>
       </c>
-      <c r="AC12" s="5">
+      <c r="AE12" s="5">
         <v>1.4</v>
       </c>
-      <c r="AD12" s="5">
+      <c r="AF12" s="5">
         <v>127603</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:32">
       <c r="A13" s="5" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5">
-        <v>953.78</v>
+        <v>1576.18</v>
       </c>
       <c r="E13" s="5">
         <f>F13-D13</f>
-        <v>28.97</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F13" s="5">
-        <v>982.75</v>
+        <v>1615.02</v>
       </c>
       <c r="G13" s="5">
         <f>H13-F13</f>
-        <v>83.9300000000001</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H13" s="5">
-        <v>1066.68</v>
+        <v>1650.62</v>
       </c>
       <c r="I13" s="5">
         <f>J13-H13</f>
-        <v>42.8399999999999</v>
+        <v>37.47</v>
       </c>
       <c r="J13" s="5">
-        <v>1109.52</v>
+        <v>1688.09</v>
       </c>
       <c r="K13" s="5">
         <f>L13-J13</f>
-        <v>36.46</v>
+        <v>21.49</v>
       </c>
       <c r="L13" s="5">
-        <v>1145.98</v>
+        <v>1709.58</v>
       </c>
       <c r="M13" s="5">
         <f>N13-L13</f>
-        <v>37.49</v>
+        <v>24.53</v>
       </c>
       <c r="N13" s="5">
-        <v>1183.47</v>
+        <v>1734.11</v>
       </c>
       <c r="O13" s="5">
         <f>P13-N13</f>
-        <v>33.3699999999999</v>
+        <v>19.5300000000002</v>
       </c>
       <c r="P13" s="5">
-        <v>1216.84</v>
+        <v>1753.64</v>
       </c>
       <c r="Q13" s="5">
         <f>R13-P13</f>
-        <v>24.8900000000001</v>
+        <v>65.1099999999999</v>
       </c>
       <c r="R13" s="5">
-        <v>1241.73</v>
+        <v>1818.75</v>
       </c>
       <c r="S13" s="5">
         <f>T13-R13</f>
-        <v>42.3099999999999</v>
+        <v>34.3699999999999</v>
       </c>
       <c r="T13" s="5">
-        <v>1284.04</v>
+        <v>1853.12</v>
       </c>
       <c r="U13" s="5">
         <f>V13-T13</f>
-        <v>44.8400000000001</v>
-      </c>
-      <c r="V13" s="9">
-        <v>1328.88</v>
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V13" s="11">
+        <v>1893.96</v>
       </c>
       <c r="W13" s="5">
         <f>X13-V13</f>
-        <v>45.9499999999998</v>
-      </c>
-      <c r="X13" s="9">
-        <v>1374.83</v>
+        <v>40.96</v>
+      </c>
+      <c r="X13" s="11">
+        <v>1934.92</v>
       </c>
       <c r="Y13" s="5">
-        <f>X13-D13</f>
-        <v>421.05</v>
-      </c>
-      <c r="Z13" s="14" t="s">
-        <v>47</v>
+        <f>Z13-X13</f>
+        <v>59.05</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>1993.97</v>
       </c>
       <c r="AA13" s="5">
-        <v>485.97</v>
-      </c>
-      <c r="AB13" s="5">
-        <v>30</v>
+        <f>Z13-D13</f>
+        <v>417.79</v>
+      </c>
+      <c r="AB13" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="AC13" s="5">
-        <v>1</v>
+        <v>407.07</v>
       </c>
       <c r="AD13" s="5">
-        <v>105419</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D14" s="5">
-        <v>848.93</v>
+        <v>1446.65</v>
       </c>
       <c r="E14" s="5">
         <f>F14-D14</f>
-        <v>34.5600000000001</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F14" s="5">
-        <v>883.49</v>
+        <v>1474.83</v>
       </c>
       <c r="G14" s="5">
         <f>H14-F14</f>
-        <v>46.08</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H14" s="5">
-        <v>929.57</v>
+        <v>1538.65</v>
       </c>
       <c r="I14" s="5">
         <f>J14-H14</f>
-        <v>27.7399999999999</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J14" s="5">
-        <v>957.31</v>
+        <v>1561.57</v>
       </c>
       <c r="K14" s="5">
         <f>L14-J14</f>
-        <v>47.36</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L14" s="5">
-        <v>1004.67</v>
+        <v>1632.43</v>
       </c>
       <c r="M14" s="5">
         <f>N14-L14</f>
-        <v>25.9399999999999</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N14" s="5">
-        <v>1030.61</v>
+        <v>1669.84</v>
       </c>
       <c r="O14" s="5">
         <f>P14-N14</f>
-        <v>37.71</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P14" s="5">
-        <v>1068.32</v>
+        <v>1702.67</v>
       </c>
       <c r="Q14" s="5">
         <f>R14-P14</f>
-        <v>18.3800000000001</v>
+        <v>51.9499999999998</v>
       </c>
       <c r="R14" s="5">
-        <v>1086.7</v>
+        <v>1754.62</v>
       </c>
       <c r="S14" s="5">
         <f>T14-R14</f>
-        <v>21.04</v>
+        <v>40.1200000000001</v>
       </c>
       <c r="T14" s="5">
-        <v>1107.74</v>
+        <v>1794.74</v>
       </c>
       <c r="U14" s="5">
         <f>V14-T14</f>
-        <v>32.7</v>
-      </c>
-      <c r="V14" s="9">
-        <v>1140.44</v>
+        <v>77.5</v>
+      </c>
+      <c r="V14" s="11">
+        <v>1872.24</v>
       </c>
       <c r="W14" s="5">
         <f>X14-V14</f>
-        <v>26.9299999999998</v>
-      </c>
-      <c r="X14" s="9">
-        <v>1167.37</v>
+        <v>79.5899999999999</v>
+      </c>
+      <c r="X14" s="11">
+        <v>1951.83</v>
       </c>
       <c r="Y14" s="5">
-        <f>X14-D14</f>
-        <v>318.44</v>
-      </c>
-      <c r="Z14" s="14" t="s">
-        <v>47</v>
+        <f>Z14-X14</f>
+        <v>9.01999999999998</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>1960.85</v>
       </c>
       <c r="AA14" s="5">
-        <v>411.37</v>
-      </c>
-      <c r="AB14" s="5">
-        <v>30</v>
+        <f>Z14-D14</f>
+        <v>514.2</v>
+      </c>
+      <c r="AB14" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="AC14" s="5">
+        <v>767.57</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>65</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>109333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1349.35</v>
+      </c>
+      <c r="E15" s="5">
+        <f>F15-D15</f>
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1398.97</v>
+      </c>
+      <c r="G15" s="5">
+        <f>H15-F15</f>
+        <v>27.79</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1426.76</v>
+      </c>
+      <c r="I15" s="5">
+        <f>J15-H15</f>
+        <v>29.02</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1455.78</v>
+      </c>
+      <c r="K15" s="5">
+        <f>L15-J15</f>
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1553.66</v>
+      </c>
+      <c r="M15" s="5">
+        <f>N15-L15</f>
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1596.02</v>
+      </c>
+      <c r="O15" s="5">
+        <f>P15-N15</f>
+        <v>54.22</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1650.24</v>
+      </c>
+      <c r="Q15" s="5">
+        <f>R15-P15</f>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R15" s="5">
+        <v>1685.83</v>
+      </c>
+      <c r="S15" s="5">
+        <f>T15-R15</f>
+        <v>68.1300000000001</v>
+      </c>
+      <c r="T15" s="5">
+        <v>1753.96</v>
+      </c>
+      <c r="U15" s="5">
+        <f>V15-T15</f>
+        <v>58.5599999999999</v>
+      </c>
+      <c r="V15" s="11">
+        <v>1812.52</v>
+      </c>
+      <c r="W15" s="5">
+        <f>X15-V15</f>
+        <v>67.21</v>
+      </c>
+      <c r="X15" s="11">
+        <v>1879.73</v>
+      </c>
+      <c r="Y15" s="5">
+        <f>Z15-X15</f>
+        <v>20.22</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>1899.95</v>
+      </c>
+      <c r="AA15" s="5">
+        <f>Z15-D15</f>
+        <v>550.6</v>
+      </c>
+      <c r="AB15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>451.2</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE15" s="5">
         <v>3.2</v>
       </c>
-      <c r="AD14" s="5">
-        <v>78989</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30">
-      <c r="A15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="3">
-        <v>262.39</v>
-      </c>
-      <c r="E15" s="3">
-        <f>F15-D15</f>
-        <v>11.5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>273.89</v>
-      </c>
-      <c r="G15" s="3">
-        <f>H15-F15</f>
-        <v>13.97</v>
-      </c>
-      <c r="H15" s="3">
-        <v>287.86</v>
-      </c>
-      <c r="I15" s="3">
-        <f>J15-H15</f>
-        <v>16.24</v>
-      </c>
-      <c r="J15" s="3">
-        <v>304.1</v>
-      </c>
-      <c r="K15" s="3">
-        <f>L15-J15</f>
-        <v>12.65</v>
-      </c>
-      <c r="L15" s="3">
-        <v>316.75</v>
-      </c>
-      <c r="M15" s="3">
-        <f>N15-L15</f>
-        <v>9.99000000000001</v>
-      </c>
-      <c r="N15" s="3">
-        <v>326.74</v>
-      </c>
-      <c r="O15" s="3">
-        <f>P15-N15</f>
-        <v>6.31999999999999</v>
-      </c>
-      <c r="P15" s="3">
-        <v>333.06</v>
-      </c>
-      <c r="Q15" s="3">
-        <f>R15-P15</f>
-        <v>21.13</v>
-      </c>
-      <c r="R15" s="3">
-        <v>354.19</v>
-      </c>
-      <c r="S15" s="3">
-        <f>T15-R15</f>
-        <v>17.68</v>
-      </c>
-      <c r="T15" s="3">
-        <v>371.87</v>
-      </c>
-      <c r="U15" s="3">
-        <f>V15-T15</f>
-        <v>11.66</v>
-      </c>
-      <c r="V15" s="11">
-        <v>383.53</v>
-      </c>
-      <c r="W15" s="3">
-        <f>X15-V15</f>
-        <v>20.5700000000001</v>
-      </c>
-      <c r="X15" s="11">
-        <v>404.1</v>
-      </c>
-      <c r="Y15" s="3">
-        <f>X15-D15</f>
-        <v>141.71</v>
-      </c>
-      <c r="Z15" s="16" t="s">
+      <c r="AF15" s="5">
+        <v>109106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AA15" s="3">
-        <v>140.92</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>36684</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="3">
-        <v>407.35</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="5">
+        <v>1156.57</v>
+      </c>
+      <c r="E16" s="5">
         <f>F16-D16</f>
-        <v>13.86</v>
-      </c>
-      <c r="F16" s="3">
-        <v>421.21</v>
-      </c>
-      <c r="G16" s="3">
+        <v>40.4400000000001</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1197.01</v>
+      </c>
+      <c r="G16" s="5">
         <f>H16-F16</f>
-        <v>16.43</v>
-      </c>
-      <c r="H16" s="3">
-        <v>437.64</v>
-      </c>
-      <c r="I16" s="3">
+        <v>46.97</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1243.98</v>
+      </c>
+      <c r="I16" s="5">
         <f>J16-H16</f>
-        <v>13.64</v>
-      </c>
-      <c r="J16" s="3">
-        <v>451.28</v>
-      </c>
-      <c r="K16" s="3">
+        <v>58.49</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1302.47</v>
+      </c>
+      <c r="K16" s="5">
         <f>L16-J16</f>
-        <v>11.6</v>
-      </c>
-      <c r="L16" s="3">
-        <v>462.88</v>
-      </c>
-      <c r="M16" s="3">
+        <v>36.6399999999999</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1339.11</v>
+      </c>
+      <c r="M16" s="5">
         <f>N16-L16</f>
-        <v>47.68</v>
-      </c>
-      <c r="N16" s="3">
-        <v>510.56</v>
-      </c>
-      <c r="O16" s="3">
+        <v>33.99</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1373.1</v>
+      </c>
+      <c r="O16" s="5">
         <f>P16-N16</f>
-        <v>20.51</v>
-      </c>
-      <c r="P16" s="3">
-        <v>531.07</v>
-      </c>
-      <c r="Q16" s="3">
+        <v>30.0600000000002</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1403.16</v>
+      </c>
+      <c r="Q16" s="5">
         <f>R16-P16</f>
-        <v>18.6099999999999</v>
-      </c>
-      <c r="R16" s="3">
-        <v>549.68</v>
-      </c>
-      <c r="S16" s="3">
+        <v>47.3</v>
+      </c>
+      <c r="R16" s="5">
+        <v>1450.46</v>
+      </c>
+      <c r="S16" s="5">
         <f>T16-R16</f>
-        <v>11.9400000000001</v>
-      </c>
-      <c r="T16" s="3">
-        <v>561.62</v>
-      </c>
-      <c r="U16" s="3">
+        <v>46.8299999999999</v>
+      </c>
+      <c r="T16" s="5">
+        <v>1497.29</v>
+      </c>
+      <c r="U16" s="5">
         <f>V16-T16</f>
-        <v>16.23</v>
+        <v>58.6500000000001</v>
       </c>
       <c r="V16" s="11">
-        <v>577.85</v>
-      </c>
-      <c r="W16" s="3">
+        <v>1555.94</v>
+      </c>
+      <c r="W16" s="5">
         <f>X16-V16</f>
-        <v>15.28</v>
+        <v>70.3099999999999</v>
       </c>
       <c r="X16" s="11">
-        <v>593.13</v>
-      </c>
-      <c r="Y16" s="3">
-        <f>X16-D16</f>
-        <v>185.78</v>
-      </c>
-      <c r="Z16" s="16" t="s">
+        <v>1626.25</v>
+      </c>
+      <c r="Y16" s="5">
+        <f>Z16-X16</f>
+        <v>31.49</v>
+      </c>
+      <c r="Z16" s="5">
+        <v>1657.74</v>
+      </c>
+      <c r="AA16" s="5">
+        <f>Z16-D16</f>
+        <v>501.17</v>
+      </c>
+      <c r="AB16" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="AA16" s="3">
-        <v>262.06</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>30</v>
-      </c>
-      <c r="AC16" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="AD16" s="3">
-        <v>43895</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30">
+      <c r="AC16" s="5">
+        <v>433.42</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>25</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>3</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>100457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D17" s="5">
-        <v>950.09</v>
+        <v>1060.77</v>
       </c>
       <c r="E17" s="5">
         <f>F17-D17</f>
-        <v>42.4</v>
+        <v>63.24</v>
       </c>
       <c r="F17" s="5">
-        <v>992.49</v>
+        <v>1124.01</v>
       </c>
       <c r="G17" s="5">
         <f>H17-F17</f>
-        <v>38.5899999999999</v>
+        <v>19.6700000000001</v>
       </c>
       <c r="H17" s="5">
-        <v>1031.08</v>
+        <v>1143.68</v>
       </c>
       <c r="I17" s="5">
         <f>J17-H17</f>
-        <v>22.6000000000001</v>
+        <v>47.76</v>
       </c>
       <c r="J17" s="5">
-        <v>1053.68</v>
+        <v>1191.44</v>
       </c>
       <c r="K17" s="5">
         <f>L17-J17</f>
-        <v>10.9299999999998</v>
+        <v>40.22</v>
       </c>
       <c r="L17" s="5">
-        <v>1064.61</v>
+        <v>1231.66</v>
       </c>
       <c r="M17" s="5">
         <f>N17-L17</f>
-        <v>16.1800000000001</v>
+        <v>44.8</v>
       </c>
       <c r="N17" s="5">
-        <v>1080.79</v>
+        <v>1276.46</v>
       </c>
       <c r="O17" s="5">
         <f>P17-N17</f>
-        <v>13.6700000000001</v>
+        <v>28.03</v>
       </c>
       <c r="P17" s="5">
-        <v>1094.46</v>
+        <v>1304.49</v>
       </c>
       <c r="Q17" s="5">
         <f>R17-P17</f>
-        <v>56.26</v>
+        <v>31.78</v>
       </c>
       <c r="R17" s="5">
-        <v>1150.72</v>
+        <v>1336.27</v>
       </c>
       <c r="S17" s="5">
         <f>T17-R17</f>
-        <v>41.27</v>
+        <v>44.9000000000001</v>
       </c>
       <c r="T17" s="5">
-        <v>1191.99</v>
+        <v>1381.17</v>
       </c>
       <c r="U17" s="5">
         <f>V17-T17</f>
-        <v>35.21</v>
-      </c>
-      <c r="V17" s="9">
-        <v>1227.2</v>
+        <v>53.1499999999999</v>
+      </c>
+      <c r="V17" s="11">
+        <v>1434.32</v>
       </c>
       <c r="W17" s="5">
         <f>X17-V17</f>
+        <v>41.46</v>
+      </c>
+      <c r="X17" s="11">
+        <v>1475.78</v>
+      </c>
+      <c r="Y17" s="5">
+        <f>Z17-X17</f>
+        <v>38.55</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>1514.33</v>
+      </c>
+      <c r="AA17" s="5">
+        <f>Z17-D17</f>
+        <v>453.56</v>
+      </c>
+      <c r="AB17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>277.72</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>10</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AF17" s="5">
+        <v>71153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="5">
+        <v>953.78</v>
+      </c>
+      <c r="E18" s="5">
+        <f>F18-D18</f>
+        <v>28.97</v>
+      </c>
+      <c r="F18" s="5">
+        <v>982.75</v>
+      </c>
+      <c r="G18" s="5">
+        <f>H18-F18</f>
+        <v>83.9300000000001</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1066.68</v>
+      </c>
+      <c r="I18" s="5">
+        <f>J18-H18</f>
+        <v>42.8399999999999</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1109.52</v>
+      </c>
+      <c r="K18" s="5">
+        <f>L18-J18</f>
+        <v>36.46</v>
+      </c>
+      <c r="L18" s="5">
+        <v>1145.98</v>
+      </c>
+      <c r="M18" s="5">
+        <f>N18-L18</f>
+        <v>37.49</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1183.47</v>
+      </c>
+      <c r="O18" s="5">
+        <f>P18-N18</f>
+        <v>33.3699999999999</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1216.84</v>
+      </c>
+      <c r="Q18" s="5">
+        <f>R18-P18</f>
+        <v>24.8900000000001</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1241.73</v>
+      </c>
+      <c r="S18" s="5">
+        <f>T18-R18</f>
+        <v>42.3099999999999</v>
+      </c>
+      <c r="T18" s="5">
+        <v>1284.04</v>
+      </c>
+      <c r="U18" s="5">
+        <f>V18-T18</f>
+        <v>44.8400000000001</v>
+      </c>
+      <c r="V18" s="11">
+        <v>1328.88</v>
+      </c>
+      <c r="W18" s="5">
+        <f>X18-V18</f>
+        <v>45.9499999999998</v>
+      </c>
+      <c r="X18" s="11">
+        <v>1374.83</v>
+      </c>
+      <c r="Y18" s="5">
+        <f>Z18-X18</f>
+        <v>16.4200000000001</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>1391.25</v>
+      </c>
+      <c r="AA18" s="5">
+        <f>Z18-D18</f>
+        <v>437.47</v>
+      </c>
+      <c r="AB18" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>485.97</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>30</v>
+      </c>
+      <c r="AE18" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="5">
+        <v>105419</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="5">
+        <v>907.94</v>
+      </c>
+      <c r="E19" s="5">
+        <f>F19-D19</f>
+        <v>64.0799999999999</v>
+      </c>
+      <c r="F19" s="5">
+        <v>972.02</v>
+      </c>
+      <c r="G19" s="5">
+        <f>H19-F19</f>
+        <v>36.26</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1008.28</v>
+      </c>
+      <c r="I19" s="5">
+        <f>J19-H19</f>
+        <v>28.8</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1037.08</v>
+      </c>
+      <c r="K19" s="5">
+        <f>L19-J19</f>
+        <v>40.1000000000001</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1077.18</v>
+      </c>
+      <c r="M19" s="5">
+        <f>N19-L19</f>
+        <v>26.03</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1103.21</v>
+      </c>
+      <c r="O19" s="5">
+        <f>P19-N19</f>
+        <v>28.3499999999999</v>
+      </c>
+      <c r="P19" s="5">
+        <v>1131.56</v>
+      </c>
+      <c r="Q19" s="5">
+        <f>R19-P19</f>
+        <v>50.1900000000001</v>
+      </c>
+      <c r="R19" s="5">
+        <v>1181.75</v>
+      </c>
+      <c r="S19" s="5">
+        <f>T19-R19</f>
+        <v>26.8699999999999</v>
+      </c>
+      <c r="T19" s="5">
+        <v>1208.62</v>
+      </c>
+      <c r="U19" s="5">
+        <f>V19-T19</f>
+        <v>58.3000000000002</v>
+      </c>
+      <c r="V19" s="11">
+        <v>1266.92</v>
+      </c>
+      <c r="W19" s="5">
+        <f>X19-V19</f>
+        <v>41.0599999999999</v>
+      </c>
+      <c r="X19" s="11">
+        <v>1307.98</v>
+      </c>
+      <c r="Y19" s="5">
+        <f>Z19-X19</f>
+        <v>31.49</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>1339.47</v>
+      </c>
+      <c r="AA19" s="5">
+        <f>Z19-D19</f>
+        <v>431.53</v>
+      </c>
+      <c r="AB19" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>447.17</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>35</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="AF19" s="5">
+        <v>65285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="5">
+        <v>950.09</v>
+      </c>
+      <c r="E20" s="5">
+        <f>F20-D20</f>
+        <v>42.4</v>
+      </c>
+      <c r="F20" s="5">
+        <v>992.49</v>
+      </c>
+      <c r="G20" s="5">
+        <f>H20-F20</f>
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1031.08</v>
+      </c>
+      <c r="I20" s="5">
+        <f>J20-H20</f>
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1053.68</v>
+      </c>
+      <c r="K20" s="5">
+        <f>L20-J20</f>
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1064.61</v>
+      </c>
+      <c r="M20" s="5">
+        <f>N20-L20</f>
+        <v>16.1800000000001</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1080.79</v>
+      </c>
+      <c r="O20" s="5">
+        <f>P20-N20</f>
+        <v>13.6700000000001</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1094.46</v>
+      </c>
+      <c r="Q20" s="5">
+        <f>R20-P20</f>
+        <v>56.26</v>
+      </c>
+      <c r="R20" s="5">
+        <v>1150.72</v>
+      </c>
+      <c r="S20" s="5">
+        <f>T20-R20</f>
+        <v>41.27</v>
+      </c>
+      <c r="T20" s="5">
+        <v>1191.99</v>
+      </c>
+      <c r="U20" s="5">
+        <f>V20-T20</f>
+        <v>35.21</v>
+      </c>
+      <c r="V20" s="11">
+        <v>1227.2</v>
+      </c>
+      <c r="W20" s="5">
+        <f>X20-V20</f>
         <v>33.3599999999999</v>
       </c>
-      <c r="X17" s="9">
+      <c r="X20" s="11">
         <v>1260.56</v>
       </c>
-      <c r="Y17" s="5">
-        <f>X17-D17</f>
-        <v>310.47</v>
-      </c>
-      <c r="Z17" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA17" s="5">
+      <c r="Y20" s="5">
+        <f>Z20-X20</f>
+        <v>46.0900000000001</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>1306.65</v>
+      </c>
+      <c r="AA20" s="5">
+        <f>Z20-D20</f>
+        <v>356.56</v>
+      </c>
+      <c r="AB20" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC20" s="5">
         <v>483.62</v>
       </c>
-      <c r="AB17" s="5">
+      <c r="AD20" s="5">
         <v>10</v>
       </c>
-      <c r="AC17" s="5">
+      <c r="AE20" s="5">
         <v>2.2</v>
       </c>
-      <c r="AD17" s="5">
+      <c r="AF20" s="5">
         <v>86194</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
-      <c r="A18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2136.24</v>
-      </c>
-      <c r="E18" s="2">
-        <f>F18-D18</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F18" s="2">
-        <v>2177.06</v>
-      </c>
-      <c r="G18" s="2">
-        <f>H18-F18</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H18" s="2">
-        <v>2239.66</v>
-      </c>
-      <c r="I18" s="2">
-        <f>J18-H18</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J18" s="2">
-        <v>2286.73</v>
-      </c>
-      <c r="K18" s="2">
-        <f>L18-J18</f>
-        <v>25.52</v>
-      </c>
-      <c r="L18" s="2">
-        <v>2312.25</v>
-      </c>
-      <c r="M18" s="2">
-        <f>N18-L18</f>
-        <v>36.7800000000002</v>
-      </c>
-      <c r="N18" s="2">
-        <v>2349.03</v>
-      </c>
-      <c r="O18" s="2">
-        <f>P18-N18</f>
-        <v>-18.02</v>
-      </c>
-      <c r="P18" s="2">
-        <v>2331.01</v>
-      </c>
-      <c r="Q18" s="2">
-        <f>R18-P18</f>
-        <v>62.7599999999998</v>
-      </c>
-      <c r="R18" s="2">
-        <v>2393.77</v>
-      </c>
-      <c r="S18" s="2">
-        <f>T18-R18</f>
-        <v>55.5599999999999</v>
-      </c>
-      <c r="T18" s="2">
-        <v>2449.33</v>
-      </c>
-      <c r="U18" s="2">
-        <f>V18-T18</f>
-        <v>31.96</v>
-      </c>
-      <c r="V18" s="8">
-        <v>2481.29</v>
-      </c>
-      <c r="W18" s="2">
-        <f>X18-V18</f>
-        <v>109.47</v>
-      </c>
-      <c r="X18" s="8">
-        <v>2590.76</v>
-      </c>
-      <c r="Y18" s="2">
-        <f>X18-D18</f>
-        <v>454.52</v>
-      </c>
-      <c r="Z18" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA18" s="2">
-        <v>814.82</v>
-      </c>
-      <c r="AB18" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1966.62</v>
-      </c>
-      <c r="E19" s="2">
-        <f>F19-D19</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F19" s="2">
-        <v>2015.64</v>
-      </c>
-      <c r="G19" s="2">
-        <f>H19-F19</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H19" s="2">
-        <v>2049.8</v>
-      </c>
-      <c r="I19" s="2">
-        <f>J19-H19</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J19" s="2">
-        <v>2139.9</v>
-      </c>
-      <c r="K19" s="2">
-        <f>L19-J19</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L19" s="2">
-        <v>2193.07</v>
-      </c>
-      <c r="M19" s="2">
-        <f>N19-L19</f>
-        <v>63.9099999999999</v>
-      </c>
-      <c r="N19" s="2">
-        <v>2256.98</v>
-      </c>
-      <c r="O19" s="2">
-        <f>P19-N19</f>
-        <v>45.71</v>
-      </c>
-      <c r="P19" s="2">
-        <v>2302.69</v>
-      </c>
-      <c r="Q19" s="2">
-        <f>R19-P19</f>
-        <v>37.2199999999998</v>
-      </c>
-      <c r="R19" s="2">
-        <v>2339.91</v>
-      </c>
-      <c r="S19" s="2">
-        <f>T19-R19</f>
-        <v>47.3099999999999</v>
-      </c>
-      <c r="T19" s="2">
-        <v>2387.22</v>
-      </c>
-      <c r="U19" s="2">
-        <f>V19-T19</f>
-        <v>88.2600000000002</v>
-      </c>
-      <c r="V19" s="8">
-        <v>2475.48</v>
-      </c>
-      <c r="W19" s="2">
-        <f>X19-V19</f>
-        <v>67.5900000000001</v>
-      </c>
-      <c r="X19" s="8">
-        <v>2543.07</v>
-      </c>
-      <c r="Y19" s="2">
-        <f>X19-D19</f>
-        <v>576.45</v>
-      </c>
-      <c r="Z19" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA19" s="2">
-        <v>815.12</v>
-      </c>
-      <c r="AB19" s="2">
+    <row r="21" spans="1:32">
+      <c r="A21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>130589</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30">
-      <c r="A20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="6">
-        <v>4105.48</v>
-      </c>
-      <c r="E20" s="6">
-        <f>F20-D20</f>
-        <v>181.21</v>
-      </c>
-      <c r="F20" s="6">
-        <v>4286.69</v>
-      </c>
-      <c r="G20" s="6">
-        <f>H20-F20</f>
-        <v>139.09</v>
-      </c>
-      <c r="H20" s="6">
-        <v>4425.78</v>
-      </c>
-      <c r="I20" s="6">
-        <f>J20-H20</f>
-        <v>54.8800000000001</v>
-      </c>
-      <c r="J20" s="6">
-        <v>4480.66</v>
-      </c>
-      <c r="K20" s="6">
-        <f>L20-J20</f>
-        <v>104.900000000001</v>
-      </c>
-      <c r="L20" s="6">
-        <v>4585.56</v>
-      </c>
-      <c r="M20" s="6">
-        <f>N20-L20</f>
-        <v>70.29</v>
-      </c>
-      <c r="N20" s="6">
-        <v>4655.85</v>
-      </c>
-      <c r="O20" s="6">
-        <f>P20-N20</f>
-        <v>49.1700000000001</v>
-      </c>
-      <c r="P20" s="6">
-        <v>4705.02</v>
-      </c>
-      <c r="Q20" s="6">
-        <f>R20-P20</f>
-        <v>38.2199999999993</v>
-      </c>
-      <c r="R20" s="6">
-        <v>4743.24</v>
-      </c>
-      <c r="S20" s="6">
-        <f>T20-R20</f>
-        <v>45.6199999999999</v>
-      </c>
-      <c r="T20" s="6">
-        <v>4788.86</v>
-      </c>
-      <c r="U20" s="6">
-        <f>V20-T20</f>
-        <v>27.5900000000001</v>
-      </c>
-      <c r="V20" s="12">
-        <v>4816.45</v>
-      </c>
-      <c r="W20" s="6">
-        <f>X20-V20</f>
-        <v>158.22</v>
-      </c>
-      <c r="X20" s="12">
-        <v>4974.67</v>
-      </c>
-      <c r="Y20" s="6">
-        <f>X20-D20</f>
-        <v>869.190000000001</v>
-      </c>
-      <c r="Z20" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA20" s="6">
-        <v>1376.92</v>
-      </c>
-      <c r="AB20" s="18">
-        <v>400</v>
-      </c>
-      <c r="AC20" s="18">
-        <v>1.2</v>
-      </c>
-      <c r="AD20" s="18">
-        <v>186759</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30">
-      <c r="A21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="D21" s="5">
         <v>927.15</v>
@@ -3523,660 +3666,709 @@
         <f>V21-T21</f>
         <v>28.76</v>
       </c>
-      <c r="V21" s="9">
+      <c r="V21" s="11">
         <v>1169.12</v>
       </c>
       <c r="W21" s="5">
         <f>X21-V21</f>
         <v>32.7600000000002</v>
       </c>
-      <c r="X21" s="9">
+      <c r="X21" s="11">
         <v>1201.88</v>
       </c>
       <c r="Y21" s="5">
-        <f>X21-D21</f>
-        <v>274.73</v>
-      </c>
-      <c r="Z21" s="14" t="s">
+        <f>Z21-X21</f>
+        <v>24.9599999999998</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>1226.84</v>
+      </c>
+      <c r="AA21" s="5">
+        <f>Z21-D21</f>
+        <v>299.69</v>
+      </c>
+      <c r="AB21" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="AA21" s="5">
+      <c r="AC21" s="5">
         <v>331.42</v>
       </c>
-      <c r="AB21" s="5">
+      <c r="AD21" s="5">
         <v>10</v>
       </c>
-      <c r="AC21" s="5">
+      <c r="AE21" s="5">
         <v>1.1</v>
       </c>
-      <c r="AD21" s="5">
+      <c r="AF21" s="5">
         <v>80664</v>
       </c>
     </row>
-    <row r="22" spans="1:30">
-      <c r="A22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="1:32">
+      <c r="A22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3">
-        <v>552.79</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="C22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="5">
+        <v>848.93</v>
+      </c>
+      <c r="E22" s="5">
         <f>F22-D22</f>
-        <v>15.9400000000001</v>
-      </c>
-      <c r="F22" s="3">
-        <v>568.73</v>
-      </c>
-      <c r="G22" s="3">
+        <v>34.5600000000001</v>
+      </c>
+      <c r="F22" s="5">
+        <v>883.49</v>
+      </c>
+      <c r="G22" s="5">
         <f>H22-F22</f>
-        <v>1.61000000000001</v>
-      </c>
-      <c r="H22" s="3">
-        <v>570.34</v>
-      </c>
-      <c r="I22" s="3">
+        <v>46.08</v>
+      </c>
+      <c r="H22" s="5">
+        <v>929.57</v>
+      </c>
+      <c r="I22" s="5">
         <f>J22-H22</f>
-        <v>7.13999999999999</v>
-      </c>
-      <c r="J22" s="3">
-        <v>577.48</v>
-      </c>
-      <c r="K22" s="3">
+        <v>27.7399999999999</v>
+      </c>
+      <c r="J22" s="5">
+        <v>957.31</v>
+      </c>
+      <c r="K22" s="5">
         <f>L22-J22</f>
-        <v>2.88999999999999</v>
-      </c>
-      <c r="L22" s="3">
-        <v>580.37</v>
-      </c>
-      <c r="M22" s="3">
+        <v>47.36</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1004.67</v>
+      </c>
+      <c r="M22" s="5">
         <f>N22-L22</f>
-        <v>2.55999999999995</v>
-      </c>
-      <c r="N22" s="3">
-        <v>582.93</v>
-      </c>
-      <c r="O22" s="3">
+        <v>25.9399999999999</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1030.61</v>
+      </c>
+      <c r="O22" s="5">
         <f>P22-N22</f>
-        <v>24.99</v>
-      </c>
-      <c r="P22" s="3">
-        <v>607.92</v>
-      </c>
-      <c r="Q22" s="3">
+        <v>37.71</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1068.32</v>
+      </c>
+      <c r="Q22" s="5">
         <f>R22-P22</f>
-        <v>0.330000000000041</v>
-      </c>
-      <c r="R22" s="3">
-        <v>608.25</v>
-      </c>
-      <c r="S22" s="3">
+        <v>18.3800000000001</v>
+      </c>
+      <c r="R22" s="5">
+        <v>1086.7</v>
+      </c>
+      <c r="S22" s="5">
         <f>T22-R22</f>
-        <v>1.80999999999995</v>
-      </c>
-      <c r="T22" s="3">
-        <v>610.06</v>
-      </c>
-      <c r="U22" s="3">
+        <v>21.04</v>
+      </c>
+      <c r="T22" s="5">
+        <v>1107.74</v>
+      </c>
+      <c r="U22" s="5">
         <f>V22-T22</f>
-        <v>0.560000000000059</v>
+        <v>32.7</v>
       </c>
       <c r="V22" s="11">
-        <v>610.62</v>
-      </c>
-      <c r="W22" s="3">
+        <v>1140.44</v>
+      </c>
+      <c r="W22" s="5">
         <f>X22-V22</f>
-        <v>3.83000000000004</v>
+        <v>26.9299999999998</v>
       </c>
       <c r="X22" s="11">
-        <v>614.45</v>
-      </c>
-      <c r="Y22" s="3">
-        <f>X22-D22</f>
-        <v>61.6600000000001</v>
-      </c>
-      <c r="Z22" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>133.25</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>49654</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30">
+        <v>1167.37</v>
+      </c>
+      <c r="Y22" s="5">
+        <f>Z22-X22</f>
+        <v>37.0300000000002</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>1204.4</v>
+      </c>
+      <c r="AA22" s="5">
+        <f>Z22-D22</f>
+        <v>355.47</v>
+      </c>
+      <c r="AB22" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC22" s="5">
+        <v>411.37</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AF22" s="5">
+        <v>78989</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D23" s="3">
-        <v>363.88</v>
+        <v>407.35</v>
       </c>
       <c r="E23" s="3">
         <f>F23-D23</f>
-        <v>14.21</v>
+        <v>13.86</v>
       </c>
       <c r="F23" s="3">
-        <v>378.09</v>
+        <v>421.21</v>
       </c>
       <c r="G23" s="3">
         <f>H23-F23</f>
-        <v>11.22</v>
+        <v>16.43</v>
       </c>
       <c r="H23" s="3">
-        <v>389.31</v>
+        <v>437.64</v>
       </c>
       <c r="I23" s="3">
         <f>J23-H23</f>
-        <v>13.62</v>
+        <v>13.64</v>
       </c>
       <c r="J23" s="3">
-        <v>402.93</v>
+        <v>451.28</v>
       </c>
       <c r="K23" s="3">
         <f>L23-J23</f>
-        <v>11.13</v>
+        <v>11.6</v>
       </c>
       <c r="L23" s="3">
-        <v>414.06</v>
+        <v>462.88</v>
       </c>
       <c r="M23" s="3">
         <f>N23-L23</f>
-        <v>17.39</v>
+        <v>47.68</v>
       </c>
       <c r="N23" s="3">
-        <v>431.45</v>
+        <v>510.56</v>
       </c>
       <c r="O23" s="3">
         <f>P23-N23</f>
-        <v>6.32999999999998</v>
+        <v>20.51</v>
       </c>
       <c r="P23" s="3">
-        <v>437.78</v>
+        <v>531.07</v>
       </c>
       <c r="Q23" s="3">
         <f>R23-P23</f>
-        <v>53.01</v>
+        <v>18.6099999999999</v>
       </c>
       <c r="R23" s="3">
-        <v>490.79</v>
+        <v>549.68</v>
       </c>
       <c r="S23" s="3">
         <f>T23-R23</f>
-        <v>11.82</v>
+        <v>11.9400000000001</v>
       </c>
       <c r="T23" s="3">
-        <v>502.61</v>
+        <v>561.62</v>
       </c>
       <c r="U23" s="3">
         <f>V23-T23</f>
-        <v>19.3099999999999</v>
-      </c>
-      <c r="V23" s="11">
-        <v>521.92</v>
+        <v>16.23</v>
+      </c>
+      <c r="V23" s="12">
+        <v>577.85</v>
       </c>
       <c r="W23" s="3">
         <f>X23-V23</f>
-        <v>29.5400000000001</v>
-      </c>
-      <c r="X23" s="11">
-        <v>551.46</v>
+        <v>15.28</v>
+      </c>
+      <c r="X23" s="12">
+        <v>593.13</v>
       </c>
       <c r="Y23" s="3">
-        <f>X23-D23</f>
-        <v>187.58</v>
-      </c>
-      <c r="Z23" s="16" t="s">
-        <v>66</v>
+        <f>Z23-X23</f>
+        <v>33.2</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>626.33</v>
       </c>
       <c r="AA23" s="3">
-        <v>150.79</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>0</v>
+        <f>Z23-D23</f>
+        <v>218.98</v>
+      </c>
+      <c r="AB23" s="18" t="s">
+        <v>69</v>
       </c>
       <c r="AC23" s="3">
-        <v>1</v>
+        <v>262.06</v>
       </c>
       <c r="AD23" s="3">
-        <v>47256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30">
+        <v>30</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3">
-        <v>305.29</v>
+        <v>552.79</v>
       </c>
       <c r="E24" s="3">
         <f>F24-D24</f>
-        <v>17.97</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F24" s="3">
-        <v>323.26</v>
+        <v>568.73</v>
       </c>
       <c r="G24" s="3">
         <f>H24-F24</f>
-        <v>10.82</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H24" s="3">
-        <v>334.08</v>
+        <v>570.34</v>
       </c>
       <c r="I24" s="3">
         <f>J24-H24</f>
-        <v>16.2</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J24" s="3">
-        <v>350.28</v>
+        <v>577.48</v>
       </c>
       <c r="K24" s="3">
         <f>L24-J24</f>
-        <v>10.8</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L24" s="3">
-        <v>361.08</v>
+        <v>580.37</v>
       </c>
       <c r="M24" s="3">
         <f>N24-L24</f>
-        <v>9.98000000000002</v>
+        <v>2.55999999999995</v>
       </c>
       <c r="N24" s="3">
-        <v>371.06</v>
+        <v>582.93</v>
       </c>
       <c r="O24" s="3">
         <f>P24-N24</f>
-        <v>10.17</v>
+        <v>24.99</v>
       </c>
       <c r="P24" s="3">
-        <v>381.23</v>
+        <v>607.92</v>
       </c>
       <c r="Q24" s="3">
         <f>R24-P24</f>
-        <v>20.97</v>
+        <v>0.330000000000041</v>
       </c>
       <c r="R24" s="3">
-        <v>402.2</v>
+        <v>608.25</v>
       </c>
       <c r="S24" s="3">
         <f>T24-R24</f>
-        <v>5.68000000000001</v>
+        <v>1.80999999999995</v>
       </c>
       <c r="T24" s="3">
-        <v>407.88</v>
+        <v>610.06</v>
       </c>
       <c r="U24" s="3">
         <f>V24-T24</f>
-        <v>25.13</v>
-      </c>
-      <c r="V24" s="11">
-        <v>433.01</v>
+        <v>0.560000000000059</v>
+      </c>
+      <c r="V24" s="12">
+        <v>610.62</v>
       </c>
       <c r="W24" s="3">
         <f>X24-V24</f>
+        <v>3.83000000000004</v>
+      </c>
+      <c r="X24" s="12">
+        <v>614.45</v>
+      </c>
+      <c r="Y24" s="3">
+        <f>Z24-X24</f>
+        <v>0.189999999999941</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>614.64</v>
+      </c>
+      <c r="AA24" s="3">
+        <f>Z24-D24</f>
+        <v>61.85</v>
+      </c>
+      <c r="AB24" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>133.25</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>49654</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="3">
+        <v>363.88</v>
+      </c>
+      <c r="E25" s="3">
+        <f>F25-D25</f>
+        <v>14.21</v>
+      </c>
+      <c r="F25" s="3">
+        <v>378.09</v>
+      </c>
+      <c r="G25" s="3">
+        <f>H25-F25</f>
+        <v>11.22</v>
+      </c>
+      <c r="H25" s="3">
+        <v>389.31</v>
+      </c>
+      <c r="I25" s="3">
+        <f>J25-H25</f>
+        <v>13.62</v>
+      </c>
+      <c r="J25" s="3">
+        <v>402.93</v>
+      </c>
+      <c r="K25" s="3">
+        <f>L25-J25</f>
+        <v>11.13</v>
+      </c>
+      <c r="L25" s="3">
+        <v>414.06</v>
+      </c>
+      <c r="M25" s="3">
+        <f>N25-L25</f>
+        <v>17.39</v>
+      </c>
+      <c r="N25" s="3">
+        <v>431.45</v>
+      </c>
+      <c r="O25" s="3">
+        <f>P25-N25</f>
+        <v>6.32999999999998</v>
+      </c>
+      <c r="P25" s="3">
+        <v>437.78</v>
+      </c>
+      <c r="Q25" s="3">
+        <f>R25-P25</f>
+        <v>53.01</v>
+      </c>
+      <c r="R25" s="3">
+        <v>490.79</v>
+      </c>
+      <c r="S25" s="3">
+        <f>T25-R25</f>
+        <v>11.82</v>
+      </c>
+      <c r="T25" s="3">
+        <v>502.61</v>
+      </c>
+      <c r="U25" s="3">
+        <f>V25-T25</f>
+        <v>19.3099999999999</v>
+      </c>
+      <c r="V25" s="12">
+        <v>521.92</v>
+      </c>
+      <c r="W25" s="3">
+        <f>X25-V25</f>
+        <v>29.5400000000001</v>
+      </c>
+      <c r="X25" s="12">
+        <v>551.46</v>
+      </c>
+      <c r="Y25" s="3">
+        <f>Z25-X25</f>
+        <v>36.98</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>588.44</v>
+      </c>
+      <c r="AA25" s="3">
+        <f>Z25-D25</f>
+        <v>224.56</v>
+      </c>
+      <c r="AB25" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>150.79</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="3">
+        <v>305.29</v>
+      </c>
+      <c r="E26" s="3">
+        <f>F26-D26</f>
+        <v>17.97</v>
+      </c>
+      <c r="F26" s="3">
+        <v>323.26</v>
+      </c>
+      <c r="G26" s="3">
+        <f>H26-F26</f>
+        <v>10.82</v>
+      </c>
+      <c r="H26" s="3">
+        <v>334.08</v>
+      </c>
+      <c r="I26" s="3">
+        <f>J26-H26</f>
+        <v>16.2</v>
+      </c>
+      <c r="J26" s="3">
+        <v>350.28</v>
+      </c>
+      <c r="K26" s="3">
+        <f>L26-J26</f>
+        <v>10.8</v>
+      </c>
+      <c r="L26" s="3">
+        <v>361.08</v>
+      </c>
+      <c r="M26" s="3">
+        <f>N26-L26</f>
+        <v>9.98000000000002</v>
+      </c>
+      <c r="N26" s="3">
+        <v>371.06</v>
+      </c>
+      <c r="O26" s="3">
+        <f>P26-N26</f>
+        <v>10.17</v>
+      </c>
+      <c r="P26" s="3">
+        <v>381.23</v>
+      </c>
+      <c r="Q26" s="3">
+        <f>R26-P26</f>
+        <v>20.97</v>
+      </c>
+      <c r="R26" s="3">
+        <v>402.2</v>
+      </c>
+      <c r="S26" s="3">
+        <f>T26-R26</f>
+        <v>5.68000000000001</v>
+      </c>
+      <c r="T26" s="3">
+        <v>407.88</v>
+      </c>
+      <c r="U26" s="3">
+        <f>V26-T26</f>
+        <v>25.13</v>
+      </c>
+      <c r="V26" s="12">
+        <v>433.01</v>
+      </c>
+      <c r="W26" s="3">
+        <f>X26-V26</f>
         <v>37.15</v>
       </c>
-      <c r="X24" s="11">
+      <c r="X26" s="12">
         <v>470.16</v>
       </c>
-      <c r="Y24" s="3">
-        <f>X24-D24</f>
-        <v>164.87</v>
-      </c>
-      <c r="Z24" s="16" t="s">
+      <c r="Y26" s="3">
+        <f>Z26-X26</f>
+        <v>10.92</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>481.08</v>
+      </c>
+      <c r="AA26" s="3">
+        <f>Z26-D26</f>
+        <v>175.79</v>
+      </c>
+      <c r="AB26" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC26" s="3">
         <v>143.89</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD26" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE26" s="3">
         <v>1</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF26" s="3">
         <v>28066</v>
       </c>
     </row>
-    <row r="25" spans="1:30">
-      <c r="A25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2714.1</v>
-      </c>
-      <c r="E25" s="1">
-        <f>F25-D25</f>
-        <v>123.29</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2837.39</v>
-      </c>
-      <c r="G25" s="1">
-        <f>H25-F25</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H25" s="1">
-        <v>2933.24</v>
-      </c>
-      <c r="I25" s="1">
-        <f>J25-H25</f>
-        <v>92.46</v>
-      </c>
-      <c r="J25" s="1">
-        <v>3025.7</v>
-      </c>
-      <c r="K25" s="1">
-        <f>L25-J25</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L25" s="1">
-        <v>3116.11</v>
-      </c>
-      <c r="M25" s="1">
-        <f>N25-L25</f>
-        <v>103.54</v>
-      </c>
-      <c r="N25" s="1">
-        <v>3219.65</v>
-      </c>
-      <c r="O25" s="1">
-        <f>P25-N25</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P25" s="1">
-        <v>3295.31</v>
-      </c>
-      <c r="Q25" s="1">
-        <f>R25-P25</f>
-        <v>88.98</v>
-      </c>
-      <c r="R25" s="1">
-        <v>3384.29</v>
-      </c>
-      <c r="S25" s="1">
-        <f>T25-R25</f>
-        <v>102.46</v>
-      </c>
-      <c r="T25" s="1">
-        <v>3486.75</v>
-      </c>
-      <c r="U25" s="1">
-        <f>V25-T25</f>
-        <v>69.23</v>
-      </c>
-      <c r="V25" s="10">
-        <v>3555.98</v>
-      </c>
-      <c r="W25" s="1">
-        <f>X25-V25</f>
-        <v>133.46</v>
-      </c>
-      <c r="X25" s="10">
-        <v>3689.44</v>
-      </c>
-      <c r="Y25" s="1">
-        <f>X25-D25</f>
-        <v>975.34</v>
-      </c>
-      <c r="Z25" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>785.72</v>
-      </c>
-      <c r="AB25" s="1">
-        <v>500</v>
-      </c>
-      <c r="AC25" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="AD25" s="1">
-        <v>191519</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="2">
-        <v>2183.01</v>
-      </c>
-      <c r="E26" s="2">
-        <f>F26-D26</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F26" s="2">
-        <v>2207.13</v>
-      </c>
-      <c r="G26" s="2">
-        <f>H26-F26</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H26" s="2">
-        <v>2229.99</v>
-      </c>
-      <c r="I26" s="2">
-        <f>J26-H26</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J26" s="2">
-        <v>2241.77</v>
-      </c>
-      <c r="K26" s="2">
-        <f>L26-J26</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L26" s="2">
-        <v>2254.78</v>
-      </c>
-      <c r="M26" s="2">
-        <f>N26-L26</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N26" s="2">
-        <v>2317.42</v>
-      </c>
-      <c r="O26" s="2">
-        <f>P26-N26</f>
-        <v>16.27</v>
-      </c>
-      <c r="P26" s="2">
-        <v>2333.69</v>
-      </c>
-      <c r="Q26" s="2">
-        <f>R26-P26</f>
-        <v>36.5</v>
-      </c>
-      <c r="R26" s="2">
-        <v>2370.19</v>
-      </c>
-      <c r="S26" s="2">
-        <f>T26-R26</f>
-        <v>65.1900000000001</v>
-      </c>
-      <c r="T26" s="2">
-        <v>2435.38</v>
-      </c>
-      <c r="U26" s="2">
-        <f>V26-T26</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V26" s="8">
-        <v>2467.14</v>
-      </c>
-      <c r="W26" s="2">
-        <f>X26-V26</f>
-        <v>53.75</v>
-      </c>
-      <c r="X26" s="8">
-        <v>2520.89</v>
-      </c>
-      <c r="Y26" s="2">
-        <f>X26-D26</f>
-        <v>337.88</v>
-      </c>
-      <c r="Z26" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>616.57</v>
-      </c>
-      <c r="AB26" s="2">
+    <row r="27" spans="1:32">
+      <c r="A27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="3">
+        <v>262.39</v>
+      </c>
+      <c r="E27" s="3">
+        <f>F27-D27</f>
+        <v>11.5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>273.89</v>
+      </c>
+      <c r="G27" s="3">
+        <f>H27-F27</f>
+        <v>13.97</v>
+      </c>
+      <c r="H27" s="3">
+        <v>287.86</v>
+      </c>
+      <c r="I27" s="3">
+        <f>J27-H27</f>
+        <v>16.24</v>
+      </c>
+      <c r="J27" s="3">
+        <v>304.1</v>
+      </c>
+      <c r="K27" s="3">
+        <f>L27-J27</f>
+        <v>12.65</v>
+      </c>
+      <c r="L27" s="3">
+        <v>316.75</v>
+      </c>
+      <c r="M27" s="3">
+        <f>N27-L27</f>
+        <v>9.99000000000001</v>
+      </c>
+      <c r="N27" s="3">
+        <v>326.74</v>
+      </c>
+      <c r="O27" s="3">
+        <f>P27-N27</f>
+        <v>6.31999999999999</v>
+      </c>
+      <c r="P27" s="3">
+        <v>333.06</v>
+      </c>
+      <c r="Q27" s="3">
+        <f>R27-P27</f>
+        <v>21.13</v>
+      </c>
+      <c r="R27" s="3">
+        <v>354.19</v>
+      </c>
+      <c r="S27" s="3">
+        <f>T27-R27</f>
+        <v>17.68</v>
+      </c>
+      <c r="T27" s="3">
+        <v>371.87</v>
+      </c>
+      <c r="U27" s="3">
+        <f>V27-T27</f>
+        <v>11.66</v>
+      </c>
+      <c r="V27" s="12">
+        <v>383.53</v>
+      </c>
+      <c r="W27" s="3">
+        <f>X27-V27</f>
+        <v>20.5700000000001</v>
+      </c>
+      <c r="X27" s="12">
+        <v>404.1</v>
+      </c>
+      <c r="Y27" s="3">
+        <f>Z27-X27</f>
+        <v>33.33</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>437.43</v>
+      </c>
+      <c r="AA27" s="3">
+        <f>Z27-D27</f>
+        <v>175.04</v>
+      </c>
+      <c r="AB27" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>140.92</v>
+      </c>
+      <c r="AD27" s="3">
         <v>0</v>
       </c>
-      <c r="AC26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="5">
-        <v>907.94</v>
-      </c>
-      <c r="E27" s="5">
-        <f>F27-D27</f>
-        <v>64.0799999999999</v>
-      </c>
-      <c r="F27" s="5">
-        <v>972.02</v>
-      </c>
-      <c r="G27" s="5">
-        <f>H27-F27</f>
-        <v>36.26</v>
-      </c>
-      <c r="H27" s="5">
-        <v>1008.28</v>
-      </c>
-      <c r="I27" s="5">
-        <f>J27-H27</f>
-        <v>28.8</v>
-      </c>
-      <c r="J27" s="5">
-        <v>1037.08</v>
-      </c>
-      <c r="K27" s="5">
-        <f>L27-J27</f>
-        <v>40.1000000000001</v>
-      </c>
-      <c r="L27" s="5">
-        <v>1077.18</v>
-      </c>
-      <c r="M27" s="5">
-        <f>N27-L27</f>
-        <v>26.03</v>
-      </c>
-      <c r="N27" s="5">
-        <v>1103.21</v>
-      </c>
-      <c r="O27" s="5">
-        <f>P27-N27</f>
-        <v>28.3499999999999</v>
-      </c>
-      <c r="P27" s="5">
-        <v>1131.56</v>
-      </c>
-      <c r="Q27" s="5">
-        <f>R27-P27</f>
-        <v>50.1900000000001</v>
-      </c>
-      <c r="R27" s="5">
-        <v>1181.75</v>
-      </c>
-      <c r="S27" s="5">
-        <f>T27-R27</f>
-        <v>26.8699999999999</v>
-      </c>
-      <c r="T27" s="5">
-        <v>1208.62</v>
-      </c>
-      <c r="U27" s="5">
-        <f>V27-T27</f>
-        <v>58.3000000000002</v>
-      </c>
-      <c r="V27" s="9">
-        <v>1266.92</v>
-      </c>
-      <c r="W27" s="5">
-        <f>X27-V27</f>
-        <v>41.0599999999999</v>
-      </c>
-      <c r="X27" s="9">
-        <v>1307.98</v>
-      </c>
-      <c r="Y27" s="5">
-        <f>X27-D27</f>
-        <v>400.04</v>
-      </c>
-      <c r="Z27" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA27" s="5">
-        <v>447.17</v>
-      </c>
-      <c r="AB27" s="5">
-        <v>35</v>
-      </c>
-      <c r="AC27" s="5">
-        <v>8.2</v>
-      </c>
-      <c r="AD27" s="5">
-        <v>65285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="AE27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>36684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -4203,13 +4395,15 @@
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
-    </row>
-    <row r="31" spans="1:28">
+      <c r="AB30" s="7"/>
+      <c r="AC30" s="7"/>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -4224,21 +4418,23 @@
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4264,58 +4460,60 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AD27">
-    <sortCondition ref="Z4"/>
+  <sortState ref="A2:AF27">
+    <sortCondition ref="Z2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4352,40 +4550,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4726,7 +4924,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -4780,7 +4978,7 @@
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5089,10 +5287,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -5636,7 +5834,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
+    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="107">
   <si>
     <t>区服</t>
   </si>
@@ -82,6 +82,9 @@
     <t>战力（2025.6.11）</t>
   </si>
   <si>
+    <t>战力（2025.6.18）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -100,61 +103,145 @@
     <t>抽卡数</t>
   </si>
   <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>白处尊（养神）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>Mr.Go</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
     <t>KB</t>
   </si>
   <si>
-    <t>大氪</t>
-  </si>
-  <si>
     <t>圣母（杂糅）</t>
   </si>
   <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
     <t>148区</t>
   </si>
   <si>
     <t>大核桃</t>
   </si>
   <si>
-    <t>中大氪</t>
-  </si>
-  <si>
     <t>眼镜妹（跳费）</t>
   </si>
   <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>喵喵（跳费）</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
     <t>149区</t>
   </si>
   <si>
     <t>灰企鹅呆瓜</t>
   </si>
   <si>
-    <t>狐狸（快攻）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>白处尊（养神）</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
+    <t>沙琪玛（快攻）</t>
+  </si>
+  <si>
+    <t>桂林碧桂园</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>151区</t>
@@ -163,58 +250,13 @@
     <t>suola</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>洞察妹（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>玩玩</t>
+    <t>圣母（洞察）</t>
   </si>
   <si>
     <t>星空</t>
   </si>
   <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
+    <t>秋雨</t>
   </si>
   <si>
     <t>152区</t>
@@ -224,42 +266,6 @@
   </si>
   <si>
     <t>梅（养神）</t>
-  </si>
-  <si>
-    <t>朱</t>
-  </si>
-  <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -1023,20 +1029,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1045,15 +1060,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1372,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF39"/>
+  <dimension ref="A1:AH39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1396,16 +1402,16 @@
     <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="17.3916666666667" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="18.0166666666667" hidden="1" customWidth="1"/>
-    <col min="24" max="27" width="18.0166666666667" customWidth="1"/>
-    <col min="28" max="28" width="18.8916666666667" customWidth="1"/>
-    <col min="29" max="29" width="14.5416666666667" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="11.625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="25" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="26" max="29" width="18.0166666666667" customWidth="1"/>
+    <col min="30" max="30" width="18.8916666666667" customWidth="1"/>
+    <col min="31" max="31" width="14.5416666666667" customWidth="1"/>
+    <col min="32" max="32" width="11.625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1485,473 +1491,507 @@
         <v>15</v>
       </c>
       <c r="AA1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB1" t="s">
         <v>16</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>18</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>19</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:32">
-      <c r="A2" s="6" t="s">
+      <c r="AH1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:34">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="6">
-        <v>4105.48</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1754.54</v>
+      </c>
+      <c r="E2" s="2">
         <f>F2-D2</f>
-        <v>181.21</v>
-      </c>
-      <c r="F2" s="6">
-        <v>4286.69</v>
-      </c>
-      <c r="G2" s="6">
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1807.91</v>
+      </c>
+      <c r="G2" s="2">
         <f>H2-F2</f>
-        <v>139.09</v>
-      </c>
-      <c r="H2" s="6">
-        <v>4425.78</v>
-      </c>
-      <c r="I2" s="6">
+        <v>90.24</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1898.15</v>
+      </c>
+      <c r="I2" s="2">
         <f>J2-H2</f>
-        <v>54.8800000000001</v>
-      </c>
-      <c r="J2" s="6">
-        <v>4480.66</v>
-      </c>
-      <c r="K2" s="6">
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1988.53</v>
+      </c>
+      <c r="K2" s="2">
         <f>L2-J2</f>
-        <v>104.900000000001</v>
-      </c>
-      <c r="L2" s="6">
-        <v>4585.56</v>
-      </c>
-      <c r="M2" s="6">
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2048.24</v>
+      </c>
+      <c r="M2" s="2">
         <f>N2-L2</f>
-        <v>70.29</v>
-      </c>
-      <c r="N2" s="6">
-        <v>4655.85</v>
-      </c>
-      <c r="O2" s="6">
+        <v>153.99</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2202.23</v>
+      </c>
+      <c r="O2" s="2">
         <f>P2-N2</f>
-        <v>49.1700000000001</v>
-      </c>
-      <c r="P2" s="6">
-        <v>4705.02</v>
-      </c>
-      <c r="Q2" s="6">
+        <v>64.21</v>
+      </c>
+      <c r="P2" s="2">
+        <v>2266.44</v>
+      </c>
+      <c r="Q2" s="2">
         <f>R2-P2</f>
-        <v>38.2199999999993</v>
-      </c>
-      <c r="R2" s="6">
-        <v>4743.24</v>
-      </c>
-      <c r="S2" s="6">
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2314</v>
+      </c>
+      <c r="S2" s="2">
         <f>T2-R2</f>
-        <v>45.6199999999999</v>
-      </c>
-      <c r="T2" s="6">
-        <v>4788.86</v>
-      </c>
-      <c r="U2" s="6">
+        <v>59.6500000000001</v>
+      </c>
+      <c r="T2" s="2">
+        <v>2373.65</v>
+      </c>
+      <c r="U2" s="2">
         <f>V2-T2</f>
-        <v>27.5900000000001</v>
+        <v>70.6399999999999</v>
       </c>
       <c r="V2" s="8">
-        <v>4816.45</v>
-      </c>
-      <c r="W2" s="6">
+        <v>2444.29</v>
+      </c>
+      <c r="W2" s="2">
         <f>X2-V2</f>
-        <v>158.22</v>
+        <v>95.9299999999998</v>
       </c>
       <c r="X2" s="8">
-        <v>4974.67</v>
-      </c>
-      <c r="Y2" s="6">
+        <v>2540.22</v>
+      </c>
+      <c r="Y2" s="2">
         <f>Z2-X2</f>
-        <v>32.8999999999996</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>5007.57</v>
-      </c>
-      <c r="AA2" s="6">
-        <f>Z2-D2</f>
-        <v>902.09</v>
-      </c>
-      <c r="AB2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>1376.92</v>
-      </c>
-      <c r="AD2" s="14">
-        <v>400</v>
-      </c>
-      <c r="AE2" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="AF2" s="14">
-        <v>186759</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="1" t="s">
+        <v>90.3200000000002</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>2630.54</v>
+      </c>
+      <c r="AA2" s="2">
+        <f>AB2-Z2</f>
+        <v>69.7800000000002</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>2700.32</v>
+      </c>
+      <c r="AC2" s="2">
+        <f>AB2-D2</f>
+        <v>945.78</v>
+      </c>
+      <c r="AD2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="AE2" s="2">
+        <v>462.52</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>132783</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="1">
-        <v>2714.1</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="2">
+        <v>1425.22</v>
+      </c>
+      <c r="E3" s="2">
         <f>F3-D3</f>
-        <v>123.29</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2837.39</v>
-      </c>
-      <c r="G3" s="1">
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1490.08</v>
+      </c>
+      <c r="G3" s="2">
         <f>H3-F3</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2933.24</v>
-      </c>
-      <c r="I3" s="1">
+        <v>46</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1536.08</v>
+      </c>
+      <c r="I3" s="2">
         <f>J3-H3</f>
-        <v>92.46</v>
-      </c>
-      <c r="J3" s="1">
-        <v>3025.7</v>
-      </c>
-      <c r="K3" s="1">
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1586.93</v>
+      </c>
+      <c r="K3" s="2">
         <f>L3-J3</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L3" s="1">
-        <v>3116.11</v>
-      </c>
-      <c r="M3" s="1">
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1673.49</v>
+      </c>
+      <c r="M3" s="2">
         <f>N3-L3</f>
-        <v>103.54</v>
-      </c>
-      <c r="N3" s="1">
-        <v>3219.65</v>
-      </c>
-      <c r="O3" s="1">
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N3" s="2">
+        <v>1712.05</v>
+      </c>
+      <c r="O3" s="2">
         <f>P3-N3</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P3" s="1">
-        <v>3295.31</v>
-      </c>
-      <c r="Q3" s="1">
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1769.14</v>
+      </c>
+      <c r="Q3" s="2">
         <f>R3-P3</f>
-        <v>88.98</v>
-      </c>
-      <c r="R3" s="1">
-        <v>3384.29</v>
-      </c>
-      <c r="S3" s="1">
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R3" s="2">
+        <v>1820.01</v>
+      </c>
+      <c r="S3" s="2">
         <f>T3-R3</f>
-        <v>102.46</v>
-      </c>
-      <c r="T3" s="1">
-        <v>3486.75</v>
-      </c>
-      <c r="U3" s="1">
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T3" s="2">
+        <v>1914.44</v>
+      </c>
+      <c r="U3" s="2">
         <f>V3-T3</f>
-        <v>69.23</v>
-      </c>
-      <c r="V3" s="9">
-        <v>3555.98</v>
-      </c>
-      <c r="W3" s="1">
+        <v>31.51</v>
+      </c>
+      <c r="V3" s="8">
+        <v>1945.95</v>
+      </c>
+      <c r="W3" s="2">
         <f>X3-V3</f>
-        <v>133.46</v>
-      </c>
-      <c r="X3" s="9">
-        <v>3689.44</v>
-      </c>
-      <c r="Y3" s="1">
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X3" s="8">
+        <v>2038.54</v>
+      </c>
+      <c r="Y3" s="2">
         <f>Z3-X3</f>
-        <v>10.5999999999999</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>3700.04</v>
-      </c>
-      <c r="AA3" s="1">
-        <f>Z3-D3</f>
-        <v>985.94</v>
-      </c>
-      <c r="AB3" s="15" t="s">
+        <v>48.1399999999999</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>2086.68</v>
+      </c>
+      <c r="AA3" s="2">
+        <f>AB3-Z3</f>
+        <v>78.1300000000001</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>2164.81</v>
+      </c>
+      <c r="AC3" s="2">
+        <f>AB3-D3</f>
+        <v>739.59</v>
+      </c>
+      <c r="AD3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AC3" s="1">
-        <v>785.72</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>500</v>
-      </c>
-      <c r="AE3" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="AF3" s="1">
-        <v>191519</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="1" t="s">
+      <c r="AE3" s="2">
+        <v>511.98</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1726.42</v>
+      </c>
+      <c r="E4" s="2">
+        <f>F4-D4</f>
+        <v>56.28</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1782.7</v>
+      </c>
+      <c r="G4" s="2">
+        <f>H4-F4</f>
+        <v>70.9199999999998</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1853.62</v>
+      </c>
+      <c r="I4" s="2">
+        <f>J4-H4</f>
+        <v>49.5800000000002</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1903.2</v>
+      </c>
+      <c r="K4" s="2">
+        <f>L4-J4</f>
+        <v>40.4099999999999</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1943.61</v>
+      </c>
+      <c r="M4" s="2">
+        <f>N4-L4</f>
+        <v>30.01</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1973.62</v>
+      </c>
+      <c r="O4" s="2">
+        <f>P4-N4</f>
+        <v>83.2800000000002</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2056.9</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>R4-P4</f>
+        <v>25.6399999999999</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2082.54</v>
+      </c>
+      <c r="S4" s="2">
+        <f>T4-R4</f>
+        <v>66.46</v>
+      </c>
+      <c r="T4" s="2">
+        <v>2149</v>
+      </c>
+      <c r="U4" s="2">
+        <f>V4-T4</f>
+        <v>43.5599999999999</v>
+      </c>
+      <c r="V4" s="8">
+        <v>2192.56</v>
+      </c>
+      <c r="W4" s="2">
+        <f>X4-V4</f>
+        <v>46.3200000000002</v>
+      </c>
+      <c r="X4" s="8">
+        <v>2238.88</v>
+      </c>
+      <c r="Y4" s="2">
+        <f>Z4-X4</f>
+        <v>17.23</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>2256.11</v>
+      </c>
+      <c r="AA4" s="2">
+        <f>AB4-Z4</f>
+        <v>97.5799999999999</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>2353.69</v>
+      </c>
+      <c r="AC4" s="2">
+        <f>AB4-D4</f>
+        <v>627.27</v>
+      </c>
+      <c r="AD4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="AE4" s="2">
+        <v>545.4</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>50</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>124763</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1">
-        <v>2533.85</v>
-      </c>
-      <c r="E4" s="1">
-        <f>F4-D4</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2583.9</v>
-      </c>
-      <c r="G4" s="1">
-        <f>H4-F4</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2669.66</v>
-      </c>
-      <c r="I4" s="1">
-        <f>J4-H4</f>
-        <v>81.79</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2751.45</v>
-      </c>
-      <c r="K4" s="1">
-        <f>L4-J4</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L4" s="1">
-        <v>2834.62</v>
-      </c>
-      <c r="M4" s="1">
-        <f>N4-L4</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2891.61</v>
-      </c>
-      <c r="O4" s="1">
-        <f>P4-N4</f>
-        <v>103.98</v>
-      </c>
-      <c r="P4" s="1">
-        <v>2995.59</v>
-      </c>
-      <c r="Q4" s="1">
-        <f>R4-P4</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R4" s="1">
-        <v>3064.44</v>
-      </c>
-      <c r="S4" s="1">
-        <f>T4-R4</f>
-        <v>47.6100000000001</v>
-      </c>
-      <c r="T4" s="1">
-        <v>3112.05</v>
-      </c>
-      <c r="U4" s="1">
-        <f>V4-T4</f>
-        <v>38.1599999999999</v>
-      </c>
-      <c r="V4" s="9">
-        <v>3150.21</v>
-      </c>
-      <c r="W4" s="1">
-        <f>X4-V4</f>
-        <v>146.1</v>
-      </c>
-      <c r="X4" s="9">
-        <v>3296.31</v>
-      </c>
-      <c r="Y4" s="1">
-        <f>Z4-X4</f>
-        <v>31.9400000000001</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>3328.25</v>
-      </c>
-      <c r="AA4" s="1">
-        <f>Z4-D4</f>
-        <v>794.4</v>
-      </c>
-      <c r="AB4" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>662.22</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>200</v>
-      </c>
-      <c r="AE4" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AF4" s="1">
-        <v>172501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="5">
+        <v>1349.35</v>
+      </c>
+      <c r="E5" s="5">
+        <f>F5-D5</f>
+        <v>49.6200000000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1398.97</v>
+      </c>
+      <c r="G5" s="5">
+        <f>H5-F5</f>
+        <v>27.79</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1426.76</v>
+      </c>
+      <c r="I5" s="5">
+        <f>J5-H5</f>
+        <v>29.02</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1455.78</v>
+      </c>
+      <c r="K5" s="5">
+        <f>L5-J5</f>
+        <v>97.8800000000001</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1553.66</v>
+      </c>
+      <c r="M5" s="5">
+        <f>N5-L5</f>
+        <v>42.3599999999999</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1596.02</v>
+      </c>
+      <c r="O5" s="5">
+        <f>P5-N5</f>
+        <v>54.22</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1650.24</v>
+      </c>
+      <c r="Q5" s="5">
+        <f>R5-P5</f>
+        <v>35.5899999999999</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1685.83</v>
+      </c>
+      <c r="S5" s="5">
+        <f>T5-R5</f>
+        <v>68.1300000000001</v>
+      </c>
+      <c r="T5" s="5">
+        <v>1753.96</v>
+      </c>
+      <c r="U5" s="5">
+        <f>V5-T5</f>
+        <v>58.5599999999999</v>
+      </c>
+      <c r="V5" s="9">
+        <v>1812.52</v>
+      </c>
+      <c r="W5" s="5">
+        <f>X5-V5</f>
+        <v>67.21</v>
+      </c>
+      <c r="X5" s="9">
+        <v>1879.73</v>
+      </c>
+      <c r="Y5" s="5">
+        <f>Z5-X5</f>
+        <v>20.22</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>1899.95</v>
+      </c>
+      <c r="AA5" s="5">
+        <f>AB5-Z5</f>
+        <v>35.0999999999999</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>1935.05</v>
+      </c>
+      <c r="AC5" s="5">
+        <f>AB5-D5</f>
+        <v>585.7</v>
+      </c>
+      <c r="AD5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="AE5" s="5">
+        <v>468.76</v>
+      </c>
+      <c r="AF5" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG5" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>109106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1754.54</v>
-      </c>
-      <c r="E5" s="2">
-        <f>F5-D5</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1807.91</v>
-      </c>
-      <c r="G5" s="2">
-        <f>H5-F5</f>
-        <v>90.24</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1898.15</v>
-      </c>
-      <c r="I5" s="2">
-        <f>J5-H5</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1988.53</v>
-      </c>
-      <c r="K5" s="2">
-        <f>L5-J5</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2048.24</v>
-      </c>
-      <c r="M5" s="2">
-        <f>N5-L5</f>
-        <v>153.99</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2202.23</v>
-      </c>
-      <c r="O5" s="2">
-        <f>P5-N5</f>
-        <v>64.21</v>
-      </c>
-      <c r="P5" s="2">
-        <v>2266.44</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>R5-P5</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R5" s="2">
-        <v>2314</v>
-      </c>
-      <c r="S5" s="2">
-        <f>T5-R5</f>
-        <v>59.6500000000001</v>
-      </c>
-      <c r="T5" s="2">
-        <v>2373.65</v>
-      </c>
-      <c r="U5" s="2">
-        <f>V5-T5</f>
-        <v>70.6399999999999</v>
-      </c>
-      <c r="V5" s="10">
-        <v>2444.29</v>
-      </c>
-      <c r="W5" s="2">
-        <f>X5-V5</f>
-        <v>95.9299999999998</v>
-      </c>
-      <c r="X5" s="10">
-        <v>2540.22</v>
-      </c>
-      <c r="Y5" s="2">
-        <f>Z5-X5</f>
-        <v>90.3200000000002</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>2630.54</v>
-      </c>
-      <c r="AA5" s="2">
-        <f>Z5-D5</f>
-        <v>876</v>
-      </c>
-      <c r="AB5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>477.92</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>300</v>
-      </c>
-      <c r="AE5" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" s="2">
-        <v>132783</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="2">
         <v>2136.24</v>
@@ -2016,14 +2056,14 @@
         <f>V6-T6</f>
         <v>31.96</v>
       </c>
-      <c r="V6" s="10">
+      <c r="V6" s="8">
         <v>2481.29</v>
       </c>
       <c r="W6" s="2">
         <f>X6-V6</f>
         <v>109.47</v>
       </c>
-      <c r="X6" s="10">
+      <c r="X6" s="8">
         <v>2590.76</v>
       </c>
       <c r="Y6" s="2">
@@ -2034,2124 +2074,2264 @@
         <v>2611.19</v>
       </c>
       <c r="AA6" s="2">
-        <f>Z6-D6</f>
-        <v>474.95</v>
-      </c>
-      <c r="AB6" s="16" t="s">
+        <f>AB6-Z6</f>
+        <v>32.9899999999998</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>2644.18</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>AB6-D6</f>
+        <v>507.94</v>
+      </c>
+      <c r="AD6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>846.38</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AC6" s="2">
-        <v>814.82</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" s="2">
+      <c r="D7" s="5">
+        <v>848.93</v>
+      </c>
+      <c r="E7" s="5">
+        <f>F7-D7</f>
+        <v>34.5600000000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>883.49</v>
+      </c>
+      <c r="G7" s="5">
+        <f>H7-F7</f>
+        <v>46.08</v>
+      </c>
+      <c r="H7" s="5">
+        <v>929.57</v>
+      </c>
+      <c r="I7" s="5">
+        <f>J7-H7</f>
+        <v>27.7399999999999</v>
+      </c>
+      <c r="J7" s="5">
+        <v>957.31</v>
+      </c>
+      <c r="K7" s="5">
+        <f>L7-J7</f>
+        <v>47.36</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1004.67</v>
+      </c>
+      <c r="M7" s="5">
+        <f>N7-L7</f>
+        <v>25.9399999999999</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1030.61</v>
+      </c>
+      <c r="O7" s="5">
+        <f>P7-N7</f>
+        <v>37.71</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1068.32</v>
+      </c>
+      <c r="Q7" s="5">
+        <f>R7-P7</f>
+        <v>18.3800000000001</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1086.7</v>
+      </c>
+      <c r="S7" s="5">
+        <f>T7-R7</f>
+        <v>21.04</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1107.74</v>
+      </c>
+      <c r="U7" s="5">
+        <f>V7-T7</f>
+        <v>32.7</v>
+      </c>
+      <c r="V7" s="9">
+        <v>1140.44</v>
+      </c>
+      <c r="W7" s="5">
+        <f>X7-V7</f>
+        <v>26.9299999999998</v>
+      </c>
+      <c r="X7" s="9">
+        <v>1167.37</v>
+      </c>
+      <c r="Y7" s="5">
+        <f>Z7-X7</f>
+        <v>37.0300000000002</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>1204.4</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>AB7-Z7</f>
+        <v>33.6199999999999</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>1238.02</v>
+      </c>
+      <c r="AC7" s="5">
+        <f>AB7-D7</f>
+        <v>389.09</v>
+      </c>
+      <c r="AD7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>456.07</v>
+      </c>
+      <c r="AF7" s="5">
+        <v>30</v>
+      </c>
+      <c r="AG7" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AH7" s="5">
+        <v>78989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3">
+        <v>407.35</v>
+      </c>
+      <c r="E8" s="3">
+        <f>F8-D8</f>
+        <v>13.86</v>
+      </c>
+      <c r="F8" s="3">
+        <v>421.21</v>
+      </c>
+      <c r="G8" s="3">
+        <f>H8-F8</f>
+        <v>16.43</v>
+      </c>
+      <c r="H8" s="3">
+        <v>437.64</v>
+      </c>
+      <c r="I8" s="3">
+        <f>J8-H8</f>
+        <v>13.64</v>
+      </c>
+      <c r="J8" s="3">
+        <v>451.28</v>
+      </c>
+      <c r="K8" s="3">
+        <f>L8-J8</f>
+        <v>11.6</v>
+      </c>
+      <c r="L8" s="3">
+        <v>462.88</v>
+      </c>
+      <c r="M8" s="3">
+        <f>N8-L8</f>
+        <v>47.68</v>
+      </c>
+      <c r="N8" s="3">
+        <v>510.56</v>
+      </c>
+      <c r="O8" s="3">
+        <f>P8-N8</f>
+        <v>20.51</v>
+      </c>
+      <c r="P8" s="3">
+        <v>531.07</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>R8-P8</f>
+        <v>18.6099999999999</v>
+      </c>
+      <c r="R8" s="3">
+        <v>549.68</v>
+      </c>
+      <c r="S8" s="3">
+        <f>T8-R8</f>
+        <v>11.9400000000001</v>
+      </c>
+      <c r="T8" s="3">
+        <v>561.62</v>
+      </c>
+      <c r="U8" s="3">
+        <f>V8-T8</f>
+        <v>16.23</v>
+      </c>
+      <c r="V8" s="10">
+        <v>577.85</v>
+      </c>
+      <c r="W8" s="3">
+        <f>X8-V8</f>
+        <v>15.28</v>
+      </c>
+      <c r="X8" s="10">
+        <v>593.13</v>
+      </c>
+      <c r="Y8" s="3">
+        <f>Z8-X8</f>
+        <v>33.2</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>626.33</v>
+      </c>
+      <c r="AA8" s="3">
+        <f>AB8-Z8</f>
+        <v>16.7199999999999</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>643.05</v>
+      </c>
+      <c r="AC8" s="3">
+        <f>AB8-D8</f>
+        <v>235.7</v>
+      </c>
+      <c r="AD8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>286.65</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4105.48</v>
+      </c>
+      <c r="E9" s="6">
+        <f>F9-D9</f>
+        <v>181.21</v>
+      </c>
+      <c r="F9" s="6">
+        <v>4286.69</v>
+      </c>
+      <c r="G9" s="6">
+        <f>H9-F9</f>
+        <v>139.09</v>
+      </c>
+      <c r="H9" s="6">
+        <v>4425.78</v>
+      </c>
+      <c r="I9" s="6">
+        <f>J9-H9</f>
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J9" s="6">
+        <v>4480.66</v>
+      </c>
+      <c r="K9" s="6">
+        <f>L9-J9</f>
+        <v>104.900000000001</v>
+      </c>
+      <c r="L9" s="6">
+        <v>4585.56</v>
+      </c>
+      <c r="M9" s="6">
+        <f>N9-L9</f>
+        <v>70.29</v>
+      </c>
+      <c r="N9" s="6">
+        <v>4655.85</v>
+      </c>
+      <c r="O9" s="6">
+        <f>P9-N9</f>
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P9" s="6">
+        <v>4705.02</v>
+      </c>
+      <c r="Q9" s="6">
+        <f>R9-P9</f>
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R9" s="6">
+        <v>4743.24</v>
+      </c>
+      <c r="S9" s="6">
+        <f>T9-R9</f>
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T9" s="6">
+        <v>4788.86</v>
+      </c>
+      <c r="U9" s="6">
+        <f>V9-T9</f>
+        <v>27.5900000000001</v>
+      </c>
+      <c r="V9" s="11">
+        <v>4816.45</v>
+      </c>
+      <c r="W9" s="6">
+        <f>X9-V9</f>
+        <v>158.22</v>
+      </c>
+      <c r="X9" s="11">
+        <v>4974.67</v>
+      </c>
+      <c r="Y9" s="6">
+        <f>Z9-X9</f>
+        <v>32.8999999999996</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>5007.57</v>
+      </c>
+      <c r="AA9" s="6">
+        <f>AB9-Z9</f>
+        <v>19.5700000000006</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>5027.14</v>
+      </c>
+      <c r="AC9" s="6">
+        <f>AB9-D9</f>
+        <v>921.660000000001</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>1374.75</v>
+      </c>
+      <c r="AF9" s="17">
+        <v>400</v>
+      </c>
+      <c r="AG9" s="17">
         <v>1.2</v>
       </c>
-      <c r="AF6" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1966.62</v>
-      </c>
-      <c r="E7" s="2">
-        <f>F7-D7</f>
-        <v>49.0200000000002</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2015.64</v>
-      </c>
-      <c r="G7" s="2">
-        <f>H7-F7</f>
-        <v>34.1600000000001</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2049.8</v>
-      </c>
-      <c r="I7" s="2">
-        <f>J7-H7</f>
-        <v>90.0999999999999</v>
-      </c>
-      <c r="J7" s="2">
-        <v>2139.9</v>
-      </c>
-      <c r="K7" s="2">
-        <f>L7-J7</f>
-        <v>53.1700000000001</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2193.07</v>
-      </c>
-      <c r="M7" s="2">
-        <f>N7-L7</f>
-        <v>63.9099999999999</v>
-      </c>
-      <c r="N7" s="2">
-        <v>2256.98</v>
-      </c>
-      <c r="O7" s="2">
-        <f>P7-N7</f>
-        <v>45.71</v>
-      </c>
-      <c r="P7" s="2">
-        <v>2302.69</v>
-      </c>
-      <c r="Q7" s="2">
-        <f>R7-P7</f>
-        <v>37.2199999999998</v>
-      </c>
-      <c r="R7" s="2">
-        <v>2339.91</v>
-      </c>
-      <c r="S7" s="2">
-        <f>T7-R7</f>
-        <v>47.3099999999999</v>
-      </c>
-      <c r="T7" s="2">
-        <v>2387.22</v>
-      </c>
-      <c r="U7" s="2">
-        <f>V7-T7</f>
-        <v>88.2600000000002</v>
-      </c>
-      <c r="V7" s="10">
-        <v>2475.48</v>
-      </c>
-      <c r="W7" s="2">
-        <f>X7-V7</f>
-        <v>67.5900000000001</v>
-      </c>
-      <c r="X7" s="10">
-        <v>2543.07</v>
-      </c>
-      <c r="Y7" s="2">
-        <f>Z7-X7</f>
-        <v>22.73</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>2565.8</v>
-      </c>
-      <c r="AA7" s="2">
-        <f>Z7-D7</f>
-        <v>599.18</v>
-      </c>
-      <c r="AB7" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>815.12</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>65</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>130589</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2183.01</v>
-      </c>
-      <c r="E8" s="2">
-        <f>F8-D8</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2207.13</v>
-      </c>
-      <c r="G8" s="2">
-        <f>H8-F8</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2229.99</v>
-      </c>
-      <c r="I8" s="2">
-        <f>J8-H8</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J8" s="2">
-        <v>2241.77</v>
-      </c>
-      <c r="K8" s="2">
-        <f>L8-J8</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L8" s="2">
-        <v>2254.78</v>
-      </c>
-      <c r="M8" s="2">
-        <f>N8-L8</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N8" s="2">
-        <v>2317.42</v>
-      </c>
-      <c r="O8" s="2">
-        <f>P8-N8</f>
-        <v>16.27</v>
-      </c>
-      <c r="P8" s="2">
-        <v>2333.69</v>
-      </c>
-      <c r="Q8" s="2">
-        <f>R8-P8</f>
-        <v>36.5</v>
-      </c>
-      <c r="R8" s="2">
-        <v>2370.19</v>
-      </c>
-      <c r="S8" s="2">
-        <f>T8-R8</f>
-        <v>65.1900000000001</v>
-      </c>
-      <c r="T8" s="2">
-        <v>2435.38</v>
-      </c>
-      <c r="U8" s="2">
-        <f>V8-T8</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V8" s="10">
-        <v>2467.14</v>
-      </c>
-      <c r="W8" s="2">
-        <f>X8-V8</f>
-        <v>53.75</v>
-      </c>
-      <c r="X8" s="10">
-        <v>2520.89</v>
-      </c>
-      <c r="Y8" s="2">
-        <f>Z8-X8</f>
-        <v>24.3299999999999</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>2545.22</v>
-      </c>
-      <c r="AA8" s="2">
-        <f>Z8-D8</f>
-        <v>362.21</v>
-      </c>
-      <c r="AB8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>616.57</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="AH9" s="17">
+        <v>186759</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1735.94</v>
-      </c>
-      <c r="E9" s="2">
-        <f>F9-D9</f>
-        <v>48.5999999999999</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1784.54</v>
-      </c>
-      <c r="G9" s="2">
-        <f>H9-F9</f>
-        <v>74.1600000000001</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1858.7</v>
-      </c>
-      <c r="I9" s="2">
-        <f>J9-H9</f>
-        <v>65.55</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1924.25</v>
-      </c>
-      <c r="K9" s="2">
-        <f>L9-J9</f>
-        <v>35.73</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1959.98</v>
-      </c>
-      <c r="M9" s="2">
-        <f>N9-L9</f>
-        <v>41.8799999999999</v>
-      </c>
-      <c r="N9" s="2">
-        <v>2001.86</v>
-      </c>
-      <c r="O9" s="2">
-        <f>P9-N9</f>
-        <v>74.6600000000001</v>
-      </c>
-      <c r="P9" s="2">
-        <v>2076.52</v>
-      </c>
-      <c r="Q9" s="2">
-        <f>R9-P9</f>
-        <v>48.71</v>
-      </c>
-      <c r="R9" s="2">
-        <v>2125.23</v>
-      </c>
-      <c r="S9" s="2">
-        <f>T9-R9</f>
-        <v>57.4200000000001</v>
-      </c>
-      <c r="T9" s="2">
-        <v>2182.65</v>
-      </c>
-      <c r="U9" s="2">
-        <f>V9-T9</f>
-        <v>68.9400000000001</v>
-      </c>
-      <c r="V9" s="10">
-        <v>2251.59</v>
-      </c>
-      <c r="W9" s="2">
-        <f>X9-V9</f>
-        <v>72.0299999999997</v>
-      </c>
-      <c r="X9" s="10">
-        <v>2323.62</v>
-      </c>
-      <c r="Y9" s="2">
-        <f>Z9-X9</f>
-        <v>23.6300000000001</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>2347.25</v>
-      </c>
-      <c r="AA9" s="2">
-        <f>Z9-D9</f>
-        <v>611.31</v>
-      </c>
-      <c r="AB9" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>538.92</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE9" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="AF9" s="2">
-        <v>150192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2">
-        <v>1726.42</v>
+        <v>1966.62</v>
       </c>
       <c r="E10" s="2">
         <f>F10-D10</f>
-        <v>56.28</v>
+        <v>49.0200000000002</v>
       </c>
       <c r="F10" s="2">
-        <v>1782.7</v>
+        <v>2015.64</v>
       </c>
       <c r="G10" s="2">
         <f>H10-F10</f>
-        <v>70.9199999999998</v>
+        <v>34.1600000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>1853.62</v>
+        <v>2049.8</v>
       </c>
       <c r="I10" s="2">
         <f>J10-H10</f>
-        <v>49.5800000000002</v>
+        <v>90.0999999999999</v>
       </c>
       <c r="J10" s="2">
-        <v>1903.2</v>
+        <v>2139.9</v>
       </c>
       <c r="K10" s="2">
         <f>L10-J10</f>
-        <v>40.4099999999999</v>
+        <v>53.1700000000001</v>
       </c>
       <c r="L10" s="2">
-        <v>1943.61</v>
+        <v>2193.07</v>
       </c>
       <c r="M10" s="2">
         <f>N10-L10</f>
-        <v>30.01</v>
+        <v>63.9099999999999</v>
       </c>
       <c r="N10" s="2">
-        <v>1973.62</v>
+        <v>2256.98</v>
       </c>
       <c r="O10" s="2">
         <f>P10-N10</f>
-        <v>83.2800000000002</v>
+        <v>45.71</v>
       </c>
       <c r="P10" s="2">
-        <v>2056.9</v>
+        <v>2302.69</v>
       </c>
       <c r="Q10" s="2">
         <f>R10-P10</f>
-        <v>25.6399999999999</v>
+        <v>37.2199999999998</v>
       </c>
       <c r="R10" s="2">
-        <v>2082.54</v>
+        <v>2339.91</v>
       </c>
       <c r="S10" s="2">
         <f>T10-R10</f>
-        <v>66.46</v>
+        <v>47.3099999999999</v>
       </c>
       <c r="T10" s="2">
-        <v>2149</v>
+        <v>2387.22</v>
       </c>
       <c r="U10" s="2">
         <f>V10-T10</f>
-        <v>43.5599999999999</v>
-      </c>
-      <c r="V10" s="10">
-        <v>2192.56</v>
+        <v>88.2600000000002</v>
+      </c>
+      <c r="V10" s="8">
+        <v>2475.48</v>
       </c>
       <c r="W10" s="2">
         <f>X10-V10</f>
-        <v>46.3200000000002</v>
-      </c>
-      <c r="X10" s="10">
-        <v>2238.88</v>
+        <v>67.5900000000001</v>
+      </c>
+      <c r="X10" s="8">
+        <v>2543.07</v>
       </c>
       <c r="Y10" s="2">
         <f>Z10-X10</f>
-        <v>17.23</v>
+        <v>22.73</v>
       </c>
       <c r="Z10" s="2">
-        <v>2256.11</v>
+        <v>2565.8</v>
       </c>
       <c r="AA10" s="2">
-        <f>Z10-D10</f>
-        <v>529.69</v>
-      </c>
-      <c r="AB10" s="16" t="s">
+        <f>AB10-Z10</f>
+        <v>140.25</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>2706.05</v>
+      </c>
+      <c r="AC10" s="2">
+        <f>AB10-D10</f>
+        <v>739.43</v>
+      </c>
+      <c r="AD10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>969.35</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>65</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>130589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1060.77</v>
+      </c>
+      <c r="E11" s="5">
+        <f>F11-D11</f>
+        <v>63.24</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1124.01</v>
+      </c>
+      <c r="G11" s="5">
+        <f>H11-F11</f>
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1143.68</v>
+      </c>
+      <c r="I11" s="5">
+        <f>J11-H11</f>
+        <v>47.76</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1191.44</v>
+      </c>
+      <c r="K11" s="5">
+        <f>L11-J11</f>
+        <v>40.22</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1231.66</v>
+      </c>
+      <c r="M11" s="5">
+        <f>N11-L11</f>
+        <v>44.8</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1276.46</v>
+      </c>
+      <c r="O11" s="5">
+        <f>P11-N11</f>
+        <v>28.03</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1304.49</v>
+      </c>
+      <c r="Q11" s="5">
+        <f>R11-P11</f>
+        <v>31.78</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1336.27</v>
+      </c>
+      <c r="S11" s="5">
+        <f>T11-R11</f>
+        <v>44.9000000000001</v>
+      </c>
+      <c r="T11" s="5">
+        <v>1381.17</v>
+      </c>
+      <c r="U11" s="5">
+        <f>V11-T11</f>
+        <v>53.1499999999999</v>
+      </c>
+      <c r="V11" s="9">
+        <v>1434.32</v>
+      </c>
+      <c r="W11" s="5">
+        <f>X11-V11</f>
+        <v>41.46</v>
+      </c>
+      <c r="X11" s="9">
+        <v>1475.78</v>
+      </c>
+      <c r="Y11" s="5">
+        <f>Z11-X11</f>
+        <v>38.55</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>1514.33</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>AB11-Z11</f>
+        <v>85.23</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>1599.56</v>
+      </c>
+      <c r="AC11" s="5">
+        <f>AB11-D11</f>
+        <v>538.79</v>
+      </c>
+      <c r="AD11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>283.72</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>10</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>71153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AC10" s="2">
-        <v>544.12</v>
-      </c>
-      <c r="AD10" s="2">
+      <c r="D12" s="1">
+        <v>2714.1</v>
+      </c>
+      <c r="E12" s="1">
+        <f>F12-D12</f>
+        <v>123.29</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2837.39</v>
+      </c>
+      <c r="G12" s="1">
+        <f>H12-F12</f>
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2933.24</v>
+      </c>
+      <c r="I12" s="1">
+        <f>J12-H12</f>
+        <v>92.46</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3025.7</v>
+      </c>
+      <c r="K12" s="1">
+        <f>L12-J12</f>
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L12" s="1">
+        <v>3116.11</v>
+      </c>
+      <c r="M12" s="1">
+        <f>N12-L12</f>
+        <v>103.54</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3219.65</v>
+      </c>
+      <c r="O12" s="1">
+        <f>P12-N12</f>
+        <v>75.6599999999999</v>
+      </c>
+      <c r="P12" s="1">
+        <v>3295.31</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>R12-P12</f>
+        <v>88.98</v>
+      </c>
+      <c r="R12" s="1">
+        <v>3384.29</v>
+      </c>
+      <c r="S12" s="1">
+        <f>T12-R12</f>
+        <v>102.46</v>
+      </c>
+      <c r="T12" s="1">
+        <v>3486.75</v>
+      </c>
+      <c r="U12" s="1">
+        <f>V12-T12</f>
+        <v>69.23</v>
+      </c>
+      <c r="V12" s="12">
+        <v>3555.98</v>
+      </c>
+      <c r="W12" s="1">
+        <f>X12-V12</f>
+        <v>133.46</v>
+      </c>
+      <c r="X12" s="12">
+        <v>3689.44</v>
+      </c>
+      <c r="Y12" s="1">
+        <f>Z12-X12</f>
+        <v>10.5999999999999</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>3700.04</v>
+      </c>
+      <c r="AA12" s="1">
+        <f>AB12-Z12</f>
+        <v>145.58</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>3845.62</v>
+      </c>
+      <c r="AC12" s="1">
+        <f>AB12-D12</f>
+        <v>1131.52</v>
+      </c>
+      <c r="AD12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="AE10" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>124763</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1425.22</v>
-      </c>
-      <c r="E11" s="2">
-        <f>F11-D11</f>
-        <v>64.8599999999999</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1490.08</v>
-      </c>
-      <c r="G11" s="2">
-        <f>H11-F11</f>
-        <v>46</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1536.08</v>
-      </c>
-      <c r="I11" s="2">
-        <f>J11-H11</f>
-        <v>50.8500000000001</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1586.93</v>
-      </c>
-      <c r="K11" s="2">
-        <f>L11-J11</f>
-        <v>86.5599999999999</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1673.49</v>
-      </c>
-      <c r="M11" s="2">
-        <f>N11-L11</f>
-        <v>38.5599999999999</v>
-      </c>
-      <c r="N11" s="2">
-        <v>1712.05</v>
-      </c>
-      <c r="O11" s="2">
-        <f>P11-N11</f>
-        <v>57.0900000000001</v>
-      </c>
-      <c r="P11" s="2">
-        <v>1769.14</v>
-      </c>
-      <c r="Q11" s="2">
-        <f>R11-P11</f>
-        <v>50.8699999999999</v>
-      </c>
-      <c r="R11" s="2">
-        <v>1820.01</v>
-      </c>
-      <c r="S11" s="2">
-        <f>T11-R11</f>
-        <v>94.4300000000001</v>
-      </c>
-      <c r="T11" s="2">
-        <v>1914.44</v>
-      </c>
-      <c r="U11" s="2">
-        <f>V11-T11</f>
-        <v>31.51</v>
-      </c>
-      <c r="V11" s="10">
-        <v>1945.95</v>
-      </c>
-      <c r="W11" s="2">
-        <f>X11-V11</f>
-        <v>92.5899999999999</v>
-      </c>
-      <c r="X11" s="10">
-        <v>2038.54</v>
-      </c>
-      <c r="Y11" s="2">
-        <f>Z11-X11</f>
-        <v>48.1399999999999</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>2086.68</v>
-      </c>
-      <c r="AA11" s="2">
-        <f>Z11-D11</f>
-        <v>661.46</v>
-      </c>
-      <c r="AB11" s="16" t="s">
+      <c r="AE12" s="1">
+        <v>838.25</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>500</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>191519</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="2">
-        <v>498.7</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>20</v>
-      </c>
-      <c r="AE11" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32">
-      <c r="A12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2">
         <v>1350.52</v>
       </c>
-      <c r="E12" s="5">
-        <f>F12-D12</f>
+      <c r="E13" s="2">
+        <f>F13-D13</f>
         <v>52.6800000000001</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="2">
         <v>1403.2</v>
       </c>
-      <c r="G12" s="5">
-        <f>H12-F12</f>
+      <c r="G13" s="2">
+        <f>H13-F13</f>
         <v>55.3199999999999</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H13" s="2">
         <v>1458.52</v>
       </c>
-      <c r="I12" s="5">
-        <f>J12-H12</f>
+      <c r="I13" s="2">
+        <f>J13-H13</f>
         <v>32.6800000000001</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="2">
         <v>1491.2</v>
       </c>
-      <c r="K12" s="5">
-        <f>L12-J12</f>
+      <c r="K13" s="2">
+        <f>L13-J13</f>
         <v>54.96</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L13" s="2">
         <v>1546.16</v>
       </c>
-      <c r="M12" s="5">
-        <f>N12-L12</f>
+      <c r="M13" s="2">
+        <f>N13-L13</f>
         <v>92.1299999999999</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N13" s="2">
         <v>1638.29</v>
       </c>
-      <c r="O12" s="5">
-        <f>P12-N12</f>
+      <c r="O13" s="2">
+        <f>P13-N13</f>
         <v>59.4400000000001</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P13" s="2">
         <v>1697.73</v>
       </c>
-      <c r="Q12" s="5">
-        <f>R12-P12</f>
+      <c r="Q13" s="2">
+        <f>R13-P13</f>
         <v>71.3399999999999</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R13" s="2">
         <v>1769.07</v>
       </c>
-      <c r="S12" s="5">
-        <f>T12-R12</f>
+      <c r="S13" s="2">
+        <f>T13-R13</f>
         <v>62.9000000000001</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T13" s="2">
         <v>1831.97</v>
       </c>
-      <c r="U12" s="5">
-        <f>V12-T12</f>
+      <c r="U13" s="2">
+        <f>V13-T13</f>
         <v>66.5899999999999</v>
       </c>
-      <c r="V12" s="11">
+      <c r="V13" s="8">
         <v>1898.56</v>
       </c>
-      <c r="W12" s="5">
-        <f>X12-V12</f>
+      <c r="W13" s="2">
+        <f>X13-V13</f>
         <v>48.77</v>
       </c>
-      <c r="X12" s="11">
+      <c r="X13" s="8">
         <v>1947.33</v>
       </c>
-      <c r="Y12" s="5">
-        <f>Z12-X12</f>
+      <c r="Y13" s="2">
+        <f>Z13-X13</f>
         <v>59.47</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z13" s="2">
         <v>2006.8</v>
       </c>
-      <c r="AA12" s="5">
-        <f>Z12-D12</f>
-        <v>656.28</v>
-      </c>
-      <c r="AB12" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>590.12</v>
-      </c>
-      <c r="AD12" s="5">
+      <c r="AA13" s="2">
+        <f>AB13-Z13</f>
+        <v>82.3900000000001</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>2089.19</v>
+      </c>
+      <c r="AC13" s="2">
+        <f>AB13-D13</f>
+        <v>738.67</v>
+      </c>
+      <c r="AD13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>659.37</v>
+      </c>
+      <c r="AF13" s="5">
         <v>65</v>
       </c>
-      <c r="AE12" s="5">
+      <c r="AG13" s="5">
         <v>1.4</v>
       </c>
-      <c r="AF12" s="5">
+      <c r="AH13" s="5">
         <v>127603</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1576.18</v>
-      </c>
-      <c r="E13" s="5">
-        <f>F13-D13</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1615.02</v>
-      </c>
-      <c r="G13" s="5">
-        <f>H13-F13</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1650.62</v>
-      </c>
-      <c r="I13" s="5">
-        <f>J13-H13</f>
-        <v>37.47</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1688.09</v>
-      </c>
-      <c r="K13" s="5">
-        <f>L13-J13</f>
-        <v>21.49</v>
-      </c>
-      <c r="L13" s="5">
-        <v>1709.58</v>
-      </c>
-      <c r="M13" s="5">
-        <f>N13-L13</f>
-        <v>24.53</v>
-      </c>
-      <c r="N13" s="5">
-        <v>1734.11</v>
-      </c>
-      <c r="O13" s="5">
-        <f>P13-N13</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P13" s="5">
-        <v>1753.64</v>
-      </c>
-      <c r="Q13" s="5">
-        <f>R13-P13</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R13" s="5">
-        <v>1818.75</v>
-      </c>
-      <c r="S13" s="5">
-        <f>T13-R13</f>
-        <v>34.3699999999999</v>
-      </c>
-      <c r="T13" s="5">
-        <v>1853.12</v>
-      </c>
-      <c r="U13" s="5">
-        <f>V13-T13</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V13" s="11">
-        <v>1893.96</v>
-      </c>
-      <c r="W13" s="5">
-        <f>X13-V13</f>
-        <v>40.96</v>
-      </c>
-      <c r="X13" s="11">
-        <v>1934.92</v>
-      </c>
-      <c r="Y13" s="5">
-        <f>Z13-X13</f>
-        <v>59.05</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>1993.97</v>
-      </c>
-      <c r="AA13" s="5">
-        <f>Z13-D13</f>
-        <v>417.79</v>
-      </c>
-      <c r="AB13" s="17" t="s">
+    <row r="14" spans="1:34">
+      <c r="A14" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="AC13" s="5">
-        <v>407.07</v>
-      </c>
-      <c r="AD13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="A14" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5">
-        <v>1446.65</v>
+        <v>1156.57</v>
       </c>
       <c r="E14" s="5">
         <f>F14-D14</f>
-        <v>28.1799999999998</v>
+        <v>40.4400000000001</v>
       </c>
       <c r="F14" s="5">
-        <v>1474.83</v>
+        <v>1197.01</v>
       </c>
       <c r="G14" s="5">
         <f>H14-F14</f>
-        <v>63.8200000000002</v>
+        <v>46.97</v>
       </c>
       <c r="H14" s="5">
-        <v>1538.65</v>
+        <v>1243.98</v>
       </c>
       <c r="I14" s="5">
         <f>J14-H14</f>
-        <v>22.9199999999998</v>
+        <v>58.49</v>
       </c>
       <c r="J14" s="5">
-        <v>1561.57</v>
+        <v>1302.47</v>
       </c>
       <c r="K14" s="5">
         <f>L14-J14</f>
-        <v>70.8600000000001</v>
+        <v>36.6399999999999</v>
       </c>
       <c r="L14" s="5">
-        <v>1632.43</v>
+        <v>1339.11</v>
       </c>
       <c r="M14" s="5">
         <f>N14-L14</f>
-        <v>37.4099999999999</v>
+        <v>33.99</v>
       </c>
       <c r="N14" s="5">
-        <v>1669.84</v>
+        <v>1373.1</v>
       </c>
       <c r="O14" s="5">
         <f>P14-N14</f>
-        <v>32.8300000000002</v>
+        <v>30.0600000000002</v>
       </c>
       <c r="P14" s="5">
-        <v>1702.67</v>
+        <v>1403.16</v>
       </c>
       <c r="Q14" s="5">
         <f>R14-P14</f>
-        <v>51.9499999999998</v>
+        <v>47.3</v>
       </c>
       <c r="R14" s="5">
-        <v>1754.62</v>
+        <v>1450.46</v>
       </c>
       <c r="S14" s="5">
         <f>T14-R14</f>
-        <v>40.1200000000001</v>
+        <v>46.8299999999999</v>
       </c>
       <c r="T14" s="5">
-        <v>1794.74</v>
+        <v>1497.29</v>
       </c>
       <c r="U14" s="5">
         <f>V14-T14</f>
-        <v>77.5</v>
-      </c>
-      <c r="V14" s="11">
-        <v>1872.24</v>
+        <v>58.6500000000001</v>
+      </c>
+      <c r="V14" s="9">
+        <v>1555.94</v>
       </c>
       <c r="W14" s="5">
         <f>X14-V14</f>
-        <v>79.5899999999999</v>
-      </c>
-      <c r="X14" s="11">
-        <v>1951.83</v>
+        <v>70.3099999999999</v>
+      </c>
+      <c r="X14" s="9">
+        <v>1626.25</v>
       </c>
       <c r="Y14" s="5">
         <f>Z14-X14</f>
-        <v>9.01999999999998</v>
+        <v>31.49</v>
       </c>
       <c r="Z14" s="5">
-        <v>1960.85</v>
+        <v>1657.74</v>
       </c>
       <c r="AA14" s="5">
-        <f>Z14-D14</f>
-        <v>514.2</v>
-      </c>
-      <c r="AB14" s="17" t="s">
-        <v>50</v>
+        <f>AB14-Z14</f>
+        <v>59.21</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>1716.95</v>
       </c>
       <c r="AC14" s="5">
-        <v>767.57</v>
-      </c>
-      <c r="AD14" s="5">
-        <v>65</v>
+        <f>AB14-D14</f>
+        <v>560.38</v>
+      </c>
+      <c r="AD14" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="AE14" s="5">
-        <v>1.4</v>
+        <v>458.27</v>
       </c>
       <c r="AF14" s="5">
-        <v>109333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32">
+        <v>25</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="5">
+        <v>100457</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D15" s="5">
-        <v>1349.35</v>
+        <v>907.94</v>
       </c>
       <c r="E15" s="5">
         <f>F15-D15</f>
-        <v>49.6200000000001</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F15" s="5">
-        <v>1398.97</v>
+        <v>972.02</v>
       </c>
       <c r="G15" s="5">
         <f>H15-F15</f>
-        <v>27.79</v>
+        <v>36.26</v>
       </c>
       <c r="H15" s="5">
-        <v>1426.76</v>
+        <v>1008.28</v>
       </c>
       <c r="I15" s="5">
         <f>J15-H15</f>
-        <v>29.02</v>
+        <v>28.8</v>
       </c>
       <c r="J15" s="5">
-        <v>1455.78</v>
+        <v>1037.08</v>
       </c>
       <c r="K15" s="5">
         <f>L15-J15</f>
-        <v>97.8800000000001</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L15" s="5">
-        <v>1553.66</v>
+        <v>1077.18</v>
       </c>
       <c r="M15" s="5">
         <f>N15-L15</f>
-        <v>42.3599999999999</v>
+        <v>26.03</v>
       </c>
       <c r="N15" s="5">
-        <v>1596.02</v>
+        <v>1103.21</v>
       </c>
       <c r="O15" s="5">
         <f>P15-N15</f>
-        <v>54.22</v>
+        <v>28.3499999999999</v>
       </c>
       <c r="P15" s="5">
-        <v>1650.24</v>
+        <v>1131.56</v>
       </c>
       <c r="Q15" s="5">
         <f>R15-P15</f>
-        <v>35.5899999999999</v>
+        <v>50.1900000000001</v>
       </c>
       <c r="R15" s="5">
-        <v>1685.83</v>
+        <v>1181.75</v>
       </c>
       <c r="S15" s="5">
         <f>T15-R15</f>
-        <v>68.1300000000001</v>
+        <v>26.8699999999999</v>
       </c>
       <c r="T15" s="5">
-        <v>1753.96</v>
+        <v>1208.62</v>
       </c>
       <c r="U15" s="5">
         <f>V15-T15</f>
-        <v>58.5599999999999</v>
-      </c>
-      <c r="V15" s="11">
-        <v>1812.52</v>
+        <v>58.3000000000002</v>
+      </c>
+      <c r="V15" s="9">
+        <v>1266.92</v>
       </c>
       <c r="W15" s="5">
         <f>X15-V15</f>
-        <v>67.21</v>
-      </c>
-      <c r="X15" s="11">
-        <v>1879.73</v>
+        <v>41.0599999999999</v>
+      </c>
+      <c r="X15" s="9">
+        <v>1307.98</v>
       </c>
       <c r="Y15" s="5">
         <f>Z15-X15</f>
-        <v>20.22</v>
+        <v>31.49</v>
       </c>
       <c r="Z15" s="5">
-        <v>1899.95</v>
+        <v>1339.47</v>
       </c>
       <c r="AA15" s="5">
-        <f>Z15-D15</f>
-        <v>550.6</v>
-      </c>
-      <c r="AB15" s="17" t="s">
+        <f>AB15-Z15</f>
+        <v>50.5899999999999</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>1390.06</v>
+      </c>
+      <c r="AC15" s="5">
+        <f>AB15-D15</f>
+        <v>482.12</v>
+      </c>
+      <c r="AD15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>473.77</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>35</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="AH15" s="5">
+        <v>65285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC15" s="5">
-        <v>451.2</v>
-      </c>
-      <c r="AD15" s="5">
-        <v>20</v>
-      </c>
-      <c r="AE15" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AF15" s="5">
-        <v>109106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32">
-      <c r="A16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="5">
-        <v>1156.57</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="C16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1576.18</v>
+      </c>
+      <c r="E16" s="2">
         <f>F16-D16</f>
-        <v>40.4400000000001</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1197.01</v>
-      </c>
-      <c r="G16" s="5">
+        <v>38.8399999999999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1615.02</v>
+      </c>
+      <c r="G16" s="2">
         <f>H16-F16</f>
-        <v>46.97</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1243.98</v>
-      </c>
-      <c r="I16" s="5">
+        <v>35.5999999999999</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1650.62</v>
+      </c>
+      <c r="I16" s="2">
         <f>J16-H16</f>
-        <v>58.49</v>
-      </c>
-      <c r="J16" s="5">
-        <v>1302.47</v>
-      </c>
-      <c r="K16" s="5">
+        <v>37.47</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1688.09</v>
+      </c>
+      <c r="K16" s="2">
         <f>L16-J16</f>
-        <v>36.6399999999999</v>
-      </c>
-      <c r="L16" s="5">
-        <v>1339.11</v>
-      </c>
-      <c r="M16" s="5">
+        <v>21.49</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1709.58</v>
+      </c>
+      <c r="M16" s="2">
         <f>N16-L16</f>
-        <v>33.99</v>
-      </c>
-      <c r="N16" s="5">
-        <v>1373.1</v>
-      </c>
-      <c r="O16" s="5">
+        <v>24.53</v>
+      </c>
+      <c r="N16" s="2">
+        <v>1734.11</v>
+      </c>
+      <c r="O16" s="2">
         <f>P16-N16</f>
-        <v>30.0600000000002</v>
-      </c>
-      <c r="P16" s="5">
-        <v>1403.16</v>
-      </c>
-      <c r="Q16" s="5">
+        <v>19.5300000000002</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1753.64</v>
+      </c>
+      <c r="Q16" s="2">
         <f>R16-P16</f>
-        <v>47.3</v>
-      </c>
-      <c r="R16" s="5">
-        <v>1450.46</v>
-      </c>
-      <c r="S16" s="5">
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1818.75</v>
+      </c>
+      <c r="S16" s="2">
         <f>T16-R16</f>
-        <v>46.8299999999999</v>
-      </c>
-      <c r="T16" s="5">
-        <v>1497.29</v>
-      </c>
-      <c r="U16" s="5">
+        <v>34.3699999999999</v>
+      </c>
+      <c r="T16" s="2">
+        <v>1853.12</v>
+      </c>
+      <c r="U16" s="2">
         <f>V16-T16</f>
-        <v>58.6500000000001</v>
-      </c>
-      <c r="V16" s="11">
-        <v>1555.94</v>
-      </c>
-      <c r="W16" s="5">
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V16" s="8">
+        <v>1893.96</v>
+      </c>
+      <c r="W16" s="2">
         <f>X16-V16</f>
-        <v>70.3099999999999</v>
-      </c>
-      <c r="X16" s="11">
-        <v>1626.25</v>
-      </c>
-      <c r="Y16" s="5">
+        <v>40.96</v>
+      </c>
+      <c r="X16" s="8">
+        <v>1934.92</v>
+      </c>
+      <c r="Y16" s="2">
         <f>Z16-X16</f>
-        <v>31.49</v>
-      </c>
-      <c r="Z16" s="5">
-        <v>1657.74</v>
-      </c>
-      <c r="AA16" s="5">
-        <f>Z16-D16</f>
-        <v>501.17</v>
-      </c>
-      <c r="AB16" s="17" t="s">
+        <v>59.05</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>1993.97</v>
+      </c>
+      <c r="AA16" s="2">
+        <f>AB16-Z16</f>
+        <v>58.4799999999998</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>2052.45</v>
+      </c>
+      <c r="AC16" s="2">
+        <f>AB16-D16</f>
+        <v>476.27</v>
+      </c>
+      <c r="AD16" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>505.86</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AC16" s="5">
-        <v>433.42</v>
-      </c>
-      <c r="AD16" s="5">
+      <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AE16" s="5">
-        <v>3</v>
-      </c>
-      <c r="AF16" s="5">
-        <v>100457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32">
-      <c r="A17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="D17" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E17" s="2">
+        <f>F17-D17</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G17" s="2">
+        <f>H17-F17</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H17" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I17" s="2">
+        <f>J17-H17</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K17" s="2">
+        <f>L17-J17</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M17" s="2">
+        <f>N17-L17</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N17" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O17" s="2">
+        <f>P17-N17</f>
+        <v>16.27</v>
+      </c>
+      <c r="P17" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>R17-P17</f>
+        <v>36.5</v>
+      </c>
+      <c r="R17" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S17" s="2">
+        <f>T17-R17</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T17" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U17" s="2">
+        <f>V17-T17</f>
+        <v>31.7599999999998</v>
+      </c>
+      <c r="V17" s="8">
+        <v>2467.14</v>
+      </c>
+      <c r="W17" s="2">
+        <f>X17-V17</f>
+        <v>53.75</v>
+      </c>
+      <c r="X17" s="8">
+        <v>2520.89</v>
+      </c>
+      <c r="Y17" s="2">
+        <f>Z17-X17</f>
+        <v>24.3299999999999</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>2545.22</v>
+      </c>
+      <c r="AA17" s="2">
+        <f>AB17-Z17</f>
+        <v>59.3900000000003</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>2604.61</v>
+      </c>
+      <c r="AC17" s="2">
+        <f>AB17-D17</f>
+        <v>421.6</v>
+      </c>
+      <c r="AD17" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1060.77</v>
-      </c>
-      <c r="E17" s="5">
-        <f>F17-D17</f>
-        <v>63.24</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1124.01</v>
-      </c>
-      <c r="G17" s="5">
-        <f>H17-F17</f>
-        <v>19.6700000000001</v>
-      </c>
-      <c r="H17" s="5">
-        <v>1143.68</v>
-      </c>
-      <c r="I17" s="5">
-        <f>J17-H17</f>
-        <v>47.76</v>
-      </c>
-      <c r="J17" s="5">
-        <v>1191.44</v>
-      </c>
-      <c r="K17" s="5">
-        <f>L17-J17</f>
-        <v>40.22</v>
-      </c>
-      <c r="L17" s="5">
-        <v>1231.66</v>
-      </c>
-      <c r="M17" s="5">
-        <f>N17-L17</f>
-        <v>44.8</v>
-      </c>
-      <c r="N17" s="5">
-        <v>1276.46</v>
-      </c>
-      <c r="O17" s="5">
-        <f>P17-N17</f>
-        <v>28.03</v>
-      </c>
-      <c r="P17" s="5">
-        <v>1304.49</v>
-      </c>
-      <c r="Q17" s="5">
-        <f>R17-P17</f>
-        <v>31.78</v>
-      </c>
-      <c r="R17" s="5">
-        <v>1336.27</v>
-      </c>
-      <c r="S17" s="5">
-        <f>T17-R17</f>
-        <v>44.9000000000001</v>
-      </c>
-      <c r="T17" s="5">
-        <v>1381.17</v>
-      </c>
-      <c r="U17" s="5">
-        <f>V17-T17</f>
-        <v>53.1499999999999</v>
-      </c>
-      <c r="V17" s="11">
-        <v>1434.32</v>
-      </c>
-      <c r="W17" s="5">
-        <f>X17-V17</f>
-        <v>41.46</v>
-      </c>
-      <c r="X17" s="11">
-        <v>1475.78</v>
-      </c>
-      <c r="Y17" s="5">
-        <f>Z17-X17</f>
-        <v>38.55</v>
-      </c>
-      <c r="Z17" s="5">
-        <v>1514.33</v>
-      </c>
-      <c r="AA17" s="5">
-        <f>Z17-D17</f>
-        <v>453.56</v>
-      </c>
-      <c r="AB17" s="17" t="s">
+      <c r="AE17" s="2">
+        <v>607.91</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AC17" s="5">
-        <v>277.72</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>10</v>
-      </c>
-      <c r="AE17" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="AF17" s="5">
-        <v>71153</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32">
-      <c r="A18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
+        <v>363.88</v>
+      </c>
+      <c r="E18" s="3">
+        <f>F18-D18</f>
+        <v>14.21</v>
+      </c>
+      <c r="F18" s="3">
+        <v>378.09</v>
+      </c>
+      <c r="G18" s="3">
+        <f>H18-F18</f>
+        <v>11.22</v>
+      </c>
+      <c r="H18" s="3">
+        <v>389.31</v>
+      </c>
+      <c r="I18" s="3">
+        <f>J18-H18</f>
+        <v>13.62</v>
+      </c>
+      <c r="J18" s="3">
+        <v>402.93</v>
+      </c>
+      <c r="K18" s="3">
+        <f>L18-J18</f>
+        <v>11.13</v>
+      </c>
+      <c r="L18" s="3">
+        <v>414.06</v>
+      </c>
+      <c r="M18" s="3">
+        <f>N18-L18</f>
+        <v>17.39</v>
+      </c>
+      <c r="N18" s="3">
+        <v>431.45</v>
+      </c>
+      <c r="O18" s="3">
+        <f>P18-N18</f>
+        <v>6.32999999999998</v>
+      </c>
+      <c r="P18" s="3">
+        <v>437.78</v>
+      </c>
+      <c r="Q18" s="3">
+        <f>R18-P18</f>
+        <v>53.01</v>
+      </c>
+      <c r="R18" s="3">
+        <v>490.79</v>
+      </c>
+      <c r="S18" s="3">
+        <f>T18-R18</f>
+        <v>11.82</v>
+      </c>
+      <c r="T18" s="3">
+        <v>502.61</v>
+      </c>
+      <c r="U18" s="3">
+        <f>V18-T18</f>
+        <v>19.3099999999999</v>
+      </c>
+      <c r="V18" s="10">
+        <v>521.92</v>
+      </c>
+      <c r="W18" s="3">
+        <f>X18-V18</f>
+        <v>29.5400000000001</v>
+      </c>
+      <c r="X18" s="10">
+        <v>551.46</v>
+      </c>
+      <c r="Y18" s="3">
+        <f>Z18-X18</f>
+        <v>36.98</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>588.44</v>
+      </c>
+      <c r="AA18" s="3">
+        <f>AB18-Z18</f>
+        <v>21.17</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>609.61</v>
+      </c>
+      <c r="AC18" s="3">
+        <f>AB18-D18</f>
+        <v>245.73</v>
+      </c>
+      <c r="AD18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>161.31</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34">
+      <c r="A19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2533.85</v>
+      </c>
+      <c r="E19" s="1">
+        <f>F19-D19</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2583.9</v>
+      </c>
+      <c r="G19" s="1">
+        <f>H19-F19</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2669.66</v>
+      </c>
+      <c r="I19" s="1">
+        <f>J19-H19</f>
+        <v>81.79</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2751.45</v>
+      </c>
+      <c r="K19" s="1">
+        <f>L19-J19</f>
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2834.62</v>
+      </c>
+      <c r="M19" s="1">
+        <f>N19-L19</f>
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2891.61</v>
+      </c>
+      <c r="O19" s="1">
+        <f>P19-N19</f>
+        <v>103.98</v>
+      </c>
+      <c r="P19" s="1">
+        <v>2995.59</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>R19-P19</f>
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R19" s="1">
+        <v>3064.44</v>
+      </c>
+      <c r="S19" s="1">
+        <f>T19-R19</f>
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T19" s="1">
+        <v>3112.05</v>
+      </c>
+      <c r="U19" s="1">
+        <f>V19-T19</f>
+        <v>38.1599999999999</v>
+      </c>
+      <c r="V19" s="12">
+        <v>3150.21</v>
+      </c>
+      <c r="W19" s="1">
+        <f>X19-V19</f>
+        <v>146.1</v>
+      </c>
+      <c r="X19" s="12">
+        <v>3296.31</v>
+      </c>
+      <c r="Y19" s="1">
+        <f>Z19-X19</f>
+        <v>31.9400000000001</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>3328.25</v>
+      </c>
+      <c r="AA19" s="1">
+        <f>AB19-Z19</f>
+        <v>79.8800000000001</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>3408.13</v>
+      </c>
+      <c r="AC19" s="1">
+        <f>AB19-D19</f>
+        <v>874.28</v>
+      </c>
+      <c r="AD19" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>680.92</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>200</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>172501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34">
+      <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="3">
+        <v>552.79</v>
+      </c>
+      <c r="E20" s="3">
+        <f>F20-D20</f>
+        <v>15.9400000000001</v>
+      </c>
+      <c r="F20" s="3">
+        <v>568.73</v>
+      </c>
+      <c r="G20" s="3">
+        <f>H20-F20</f>
+        <v>1.61000000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <v>570.34</v>
+      </c>
+      <c r="I20" s="3">
+        <f>J20-H20</f>
+        <v>7.13999999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>577.48</v>
+      </c>
+      <c r="K20" s="3">
+        <f>L20-J20</f>
+        <v>2.88999999999999</v>
+      </c>
+      <c r="L20" s="3">
+        <v>580.37</v>
+      </c>
+      <c r="M20" s="3">
+        <f>N20-L20</f>
+        <v>2.55999999999995</v>
+      </c>
+      <c r="N20" s="3">
+        <v>582.93</v>
+      </c>
+      <c r="O20" s="3">
+        <f>P20-N20</f>
+        <v>24.99</v>
+      </c>
+      <c r="P20" s="3">
+        <v>607.92</v>
+      </c>
+      <c r="Q20" s="3">
+        <f>R20-P20</f>
+        <v>0.330000000000041</v>
+      </c>
+      <c r="R20" s="3">
+        <v>608.25</v>
+      </c>
+      <c r="S20" s="3">
+        <f>T20-R20</f>
+        <v>1.80999999999995</v>
+      </c>
+      <c r="T20" s="3">
+        <v>610.06</v>
+      </c>
+      <c r="U20" s="3">
+        <f>V20-T20</f>
+        <v>0.560000000000059</v>
+      </c>
+      <c r="V20" s="10">
+        <v>610.62</v>
+      </c>
+      <c r="W20" s="3">
+        <f>X20-V20</f>
+        <v>3.83000000000004</v>
+      </c>
+      <c r="X20" s="10">
+        <v>614.45</v>
+      </c>
+      <c r="Y20" s="3">
+        <f>Z20-X20</f>
+        <v>0.189999999999941</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>614.64</v>
+      </c>
+      <c r="AA20" s="3">
+        <f>AB20-Z20</f>
+        <v>0.690000000000055</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>615.33</v>
+      </c>
+      <c r="AC20" s="3">
+        <f>AB20-D20</f>
+        <v>62.5400000000001</v>
+      </c>
+      <c r="AD20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>133.35</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>49654</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34">
+      <c r="A21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="5">
         <v>953.78</v>
-      </c>
-      <c r="E18" s="5">
-        <f>F18-D18</f>
-        <v>28.97</v>
-      </c>
-      <c r="F18" s="5">
-        <v>982.75</v>
-      </c>
-      <c r="G18" s="5">
-        <f>H18-F18</f>
-        <v>83.9300000000001</v>
-      </c>
-      <c r="H18" s="5">
-        <v>1066.68</v>
-      </c>
-      <c r="I18" s="5">
-        <f>J18-H18</f>
-        <v>42.8399999999999</v>
-      </c>
-      <c r="J18" s="5">
-        <v>1109.52</v>
-      </c>
-      <c r="K18" s="5">
-        <f>L18-J18</f>
-        <v>36.46</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1145.98</v>
-      </c>
-      <c r="M18" s="5">
-        <f>N18-L18</f>
-        <v>37.49</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1183.47</v>
-      </c>
-      <c r="O18" s="5">
-        <f>P18-N18</f>
-        <v>33.3699999999999</v>
-      </c>
-      <c r="P18" s="5">
-        <v>1216.84</v>
-      </c>
-      <c r="Q18" s="5">
-        <f>R18-P18</f>
-        <v>24.8900000000001</v>
-      </c>
-      <c r="R18" s="5">
-        <v>1241.73</v>
-      </c>
-      <c r="S18" s="5">
-        <f>T18-R18</f>
-        <v>42.3099999999999</v>
-      </c>
-      <c r="T18" s="5">
-        <v>1284.04</v>
-      </c>
-      <c r="U18" s="5">
-        <f>V18-T18</f>
-        <v>44.8400000000001</v>
-      </c>
-      <c r="V18" s="11">
-        <v>1328.88</v>
-      </c>
-      <c r="W18" s="5">
-        <f>X18-V18</f>
-        <v>45.9499999999998</v>
-      </c>
-      <c r="X18" s="11">
-        <v>1374.83</v>
-      </c>
-      <c r="Y18" s="5">
-        <f>Z18-X18</f>
-        <v>16.4200000000001</v>
-      </c>
-      <c r="Z18" s="5">
-        <v>1391.25</v>
-      </c>
-      <c r="AA18" s="5">
-        <f>Z18-D18</f>
-        <v>437.47</v>
-      </c>
-      <c r="AB18" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC18" s="5">
-        <v>485.97</v>
-      </c>
-      <c r="AD18" s="5">
-        <v>30</v>
-      </c>
-      <c r="AE18" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="5">
-        <v>105419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="5">
-        <v>907.94</v>
-      </c>
-      <c r="E19" s="5">
-        <f>F19-D19</f>
-        <v>64.0799999999999</v>
-      </c>
-      <c r="F19" s="5">
-        <v>972.02</v>
-      </c>
-      <c r="G19" s="5">
-        <f>H19-F19</f>
-        <v>36.26</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1008.28</v>
-      </c>
-      <c r="I19" s="5">
-        <f>J19-H19</f>
-        <v>28.8</v>
-      </c>
-      <c r="J19" s="5">
-        <v>1037.08</v>
-      </c>
-      <c r="K19" s="5">
-        <f>L19-J19</f>
-        <v>40.1000000000001</v>
-      </c>
-      <c r="L19" s="5">
-        <v>1077.18</v>
-      </c>
-      <c r="M19" s="5">
-        <f>N19-L19</f>
-        <v>26.03</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1103.21</v>
-      </c>
-      <c r="O19" s="5">
-        <f>P19-N19</f>
-        <v>28.3499999999999</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1131.56</v>
-      </c>
-      <c r="Q19" s="5">
-        <f>R19-P19</f>
-        <v>50.1900000000001</v>
-      </c>
-      <c r="R19" s="5">
-        <v>1181.75</v>
-      </c>
-      <c r="S19" s="5">
-        <f>T19-R19</f>
-        <v>26.8699999999999</v>
-      </c>
-      <c r="T19" s="5">
-        <v>1208.62</v>
-      </c>
-      <c r="U19" s="5">
-        <f>V19-T19</f>
-        <v>58.3000000000002</v>
-      </c>
-      <c r="V19" s="11">
-        <v>1266.92</v>
-      </c>
-      <c r="W19" s="5">
-        <f>X19-V19</f>
-        <v>41.0599999999999</v>
-      </c>
-      <c r="X19" s="11">
-        <v>1307.98</v>
-      </c>
-      <c r="Y19" s="5">
-        <f>Z19-X19</f>
-        <v>31.49</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>1339.47</v>
-      </c>
-      <c r="AA19" s="5">
-        <f>Z19-D19</f>
-        <v>431.53</v>
-      </c>
-      <c r="AB19" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC19" s="5">
-        <v>447.17</v>
-      </c>
-      <c r="AD19" s="5">
-        <v>35</v>
-      </c>
-      <c r="AE19" s="5">
-        <v>8.2</v>
-      </c>
-      <c r="AF19" s="5">
-        <v>65285</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32">
-      <c r="A20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="5">
-        <v>950.09</v>
-      </c>
-      <c r="E20" s="5">
-        <f>F20-D20</f>
-        <v>42.4</v>
-      </c>
-      <c r="F20" s="5">
-        <v>992.49</v>
-      </c>
-      <c r="G20" s="5">
-        <f>H20-F20</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1031.08</v>
-      </c>
-      <c r="I20" s="5">
-        <f>J20-H20</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J20" s="5">
-        <v>1053.68</v>
-      </c>
-      <c r="K20" s="5">
-        <f>L20-J20</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1064.61</v>
-      </c>
-      <c r="M20" s="5">
-        <f>N20-L20</f>
-        <v>16.1800000000001</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1080.79</v>
-      </c>
-      <c r="O20" s="5">
-        <f>P20-N20</f>
-        <v>13.6700000000001</v>
-      </c>
-      <c r="P20" s="5">
-        <v>1094.46</v>
-      </c>
-      <c r="Q20" s="5">
-        <f>R20-P20</f>
-        <v>56.26</v>
-      </c>
-      <c r="R20" s="5">
-        <v>1150.72</v>
-      </c>
-      <c r="S20" s="5">
-        <f>T20-R20</f>
-        <v>41.27</v>
-      </c>
-      <c r="T20" s="5">
-        <v>1191.99</v>
-      </c>
-      <c r="U20" s="5">
-        <f>V20-T20</f>
-        <v>35.21</v>
-      </c>
-      <c r="V20" s="11">
-        <v>1227.2</v>
-      </c>
-      <c r="W20" s="5">
-        <f>X20-V20</f>
-        <v>33.3599999999999</v>
-      </c>
-      <c r="X20" s="11">
-        <v>1260.56</v>
-      </c>
-      <c r="Y20" s="5">
-        <f>Z20-X20</f>
-        <v>46.0900000000001</v>
-      </c>
-      <c r="Z20" s="5">
-        <v>1306.65</v>
-      </c>
-      <c r="AA20" s="5">
-        <f>Z20-D20</f>
-        <v>356.56</v>
-      </c>
-      <c r="AB20" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>483.62</v>
-      </c>
-      <c r="AD20" s="5">
-        <v>10</v>
-      </c>
-      <c r="AE20" s="5">
-        <v>2.2</v>
-      </c>
-      <c r="AF20" s="5">
-        <v>86194</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="5">
-        <v>927.15</v>
       </c>
       <c r="E21" s="5">
         <f>F21-D21</f>
-        <v>17.9300000000001</v>
+        <v>28.97</v>
       </c>
       <c r="F21" s="5">
-        <v>945.08</v>
+        <v>982.75</v>
       </c>
       <c r="G21" s="5">
         <f>H21-F21</f>
-        <v>24.04</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H21" s="5">
-        <v>969.12</v>
+        <v>1066.68</v>
       </c>
       <c r="I21" s="5">
         <f>J21-H21</f>
-        <v>26.96</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J21" s="5">
-        <v>996.08</v>
+        <v>1109.52</v>
       </c>
       <c r="K21" s="5">
         <f>L21-J21</f>
-        <v>23.3499999999999</v>
+        <v>36.46</v>
       </c>
       <c r="L21" s="5">
-        <v>1019.43</v>
+        <v>1145.98</v>
       </c>
       <c r="M21" s="5">
         <f>N21-L21</f>
-        <v>23.7400000000001</v>
+        <v>37.49</v>
       </c>
       <c r="N21" s="5">
-        <v>1043.17</v>
+        <v>1183.47</v>
       </c>
       <c r="O21" s="5">
         <f>P21-N21</f>
-        <v>24.99</v>
+        <v>33.3699999999999</v>
       </c>
       <c r="P21" s="5">
-        <v>1068.16</v>
+        <v>1216.84</v>
       </c>
       <c r="Q21" s="5">
         <f>R21-P21</f>
-        <v>25.3499999999999</v>
+        <v>24.8900000000001</v>
       </c>
       <c r="R21" s="5">
-        <v>1093.51</v>
+        <v>1241.73</v>
       </c>
       <c r="S21" s="5">
         <f>T21-R21</f>
-        <v>46.8499999999999</v>
+        <v>42.3099999999999</v>
       </c>
       <c r="T21" s="5">
-        <v>1140.36</v>
+        <v>1284.04</v>
       </c>
       <c r="U21" s="5">
         <f>V21-T21</f>
-        <v>28.76</v>
-      </c>
-      <c r="V21" s="11">
-        <v>1169.12</v>
+        <v>44.8400000000001</v>
+      </c>
+      <c r="V21" s="9">
+        <v>1328.88</v>
       </c>
       <c r="W21" s="5">
         <f>X21-V21</f>
-        <v>32.7600000000002</v>
-      </c>
-      <c r="X21" s="11">
-        <v>1201.88</v>
+        <v>45.9499999999998</v>
+      </c>
+      <c r="X21" s="9">
+        <v>1374.83</v>
       </c>
       <c r="Y21" s="5">
         <f>Z21-X21</f>
-        <v>24.9599999999998</v>
+        <v>16.4200000000001</v>
       </c>
       <c r="Z21" s="5">
-        <v>1226.84</v>
+        <v>1391.25</v>
       </c>
       <c r="AA21" s="5">
-        <f>Z21-D21</f>
-        <v>299.69</v>
-      </c>
-      <c r="AB21" s="17" t="s">
-        <v>66</v>
+        <f>AB21-Z21</f>
+        <v>22.0699999999999</v>
+      </c>
+      <c r="AB21" s="5">
+        <v>1413.32</v>
       </c>
       <c r="AC21" s="5">
-        <v>331.42</v>
-      </c>
-      <c r="AD21" s="5">
-        <v>10</v>
+        <f>AB21-D21</f>
+        <v>459.54</v>
+      </c>
+      <c r="AD21" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="AE21" s="5">
-        <v>1.1</v>
+        <v>492.07</v>
       </c>
       <c r="AF21" s="5">
-        <v>80664</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32">
+        <v>30</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>105419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D22" s="5">
-        <v>848.93</v>
+        <v>927.15</v>
       </c>
       <c r="E22" s="5">
         <f>F22-D22</f>
-        <v>34.5600000000001</v>
+        <v>17.9300000000001</v>
       </c>
       <c r="F22" s="5">
-        <v>883.49</v>
+        <v>945.08</v>
       </c>
       <c r="G22" s="5">
         <f>H22-F22</f>
-        <v>46.08</v>
+        <v>24.04</v>
       </c>
       <c r="H22" s="5">
-        <v>929.57</v>
+        <v>969.12</v>
       </c>
       <c r="I22" s="5">
         <f>J22-H22</f>
-        <v>27.7399999999999</v>
+        <v>26.96</v>
       </c>
       <c r="J22" s="5">
-        <v>957.31</v>
+        <v>996.08</v>
       </c>
       <c r="K22" s="5">
         <f>L22-J22</f>
-        <v>47.36</v>
+        <v>23.3499999999999</v>
       </c>
       <c r="L22" s="5">
-        <v>1004.67</v>
+        <v>1019.43</v>
       </c>
       <c r="M22" s="5">
         <f>N22-L22</f>
-        <v>25.9399999999999</v>
+        <v>23.7400000000001</v>
       </c>
       <c r="N22" s="5">
-        <v>1030.61</v>
+        <v>1043.17</v>
       </c>
       <c r="O22" s="5">
         <f>P22-N22</f>
-        <v>37.71</v>
+        <v>24.99</v>
       </c>
       <c r="P22" s="5">
-        <v>1068.32</v>
+        <v>1068.16</v>
       </c>
       <c r="Q22" s="5">
         <f>R22-P22</f>
-        <v>18.3800000000001</v>
+        <v>25.3499999999999</v>
       </c>
       <c r="R22" s="5">
-        <v>1086.7</v>
+        <v>1093.51</v>
       </c>
       <c r="S22" s="5">
         <f>T22-R22</f>
-        <v>21.04</v>
+        <v>46.8499999999999</v>
       </c>
       <c r="T22" s="5">
-        <v>1107.74</v>
+        <v>1140.36</v>
       </c>
       <c r="U22" s="5">
         <f>V22-T22</f>
-        <v>32.7</v>
-      </c>
-      <c r="V22" s="11">
-        <v>1140.44</v>
+        <v>28.76</v>
+      </c>
+      <c r="V22" s="9">
+        <v>1169.12</v>
       </c>
       <c r="W22" s="5">
         <f>X22-V22</f>
-        <v>26.9299999999998</v>
-      </c>
-      <c r="X22" s="11">
-        <v>1167.37</v>
+        <v>32.7600000000002</v>
+      </c>
+      <c r="X22" s="9">
+        <v>1201.88</v>
       </c>
       <c r="Y22" s="5">
         <f>Z22-X22</f>
-        <v>37.0300000000002</v>
+        <v>24.9599999999998</v>
       </c>
       <c r="Z22" s="5">
-        <v>1204.4</v>
+        <v>1226.84</v>
       </c>
       <c r="AA22" s="5">
-        <f>Z22-D22</f>
-        <v>355.47</v>
-      </c>
-      <c r="AB22" s="17" t="s">
-        <v>50</v>
+        <f>AB22-Z22</f>
+        <v>27.6900000000001</v>
+      </c>
+      <c r="AB22" s="5">
+        <v>1254.53</v>
       </c>
       <c r="AC22" s="5">
-        <v>411.37</v>
-      </c>
-      <c r="AD22" s="5">
-        <v>30</v>
+        <f>AB22-D22</f>
+        <v>327.38</v>
+      </c>
+      <c r="AD22" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="AE22" s="5">
-        <v>3.2</v>
+        <v>350.61</v>
       </c>
       <c r="AF22" s="5">
-        <v>78989</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32">
+        <v>10</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AH22" s="5">
+        <v>80664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23" s="3" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3">
-        <v>407.35</v>
+        <v>262.39</v>
       </c>
       <c r="E23" s="3">
         <f>F23-D23</f>
-        <v>13.86</v>
+        <v>11.5</v>
       </c>
       <c r="F23" s="3">
-        <v>421.21</v>
+        <v>273.89</v>
       </c>
       <c r="G23" s="3">
         <f>H23-F23</f>
-        <v>16.43</v>
+        <v>13.97</v>
       </c>
       <c r="H23" s="3">
-        <v>437.64</v>
+        <v>287.86</v>
       </c>
       <c r="I23" s="3">
         <f>J23-H23</f>
-        <v>13.64</v>
+        <v>16.24</v>
       </c>
       <c r="J23" s="3">
-        <v>451.28</v>
+        <v>304.1</v>
       </c>
       <c r="K23" s="3">
         <f>L23-J23</f>
-        <v>11.6</v>
+        <v>12.65</v>
       </c>
       <c r="L23" s="3">
-        <v>462.88</v>
+        <v>316.75</v>
       </c>
       <c r="M23" s="3">
         <f>N23-L23</f>
-        <v>47.68</v>
+        <v>9.99000000000001</v>
       </c>
       <c r="N23" s="3">
-        <v>510.56</v>
+        <v>326.74</v>
       </c>
       <c r="O23" s="3">
         <f>P23-N23</f>
-        <v>20.51</v>
+        <v>6.31999999999999</v>
       </c>
       <c r="P23" s="3">
-        <v>531.07</v>
+        <v>333.06</v>
       </c>
       <c r="Q23" s="3">
         <f>R23-P23</f>
-        <v>18.6099999999999</v>
+        <v>21.13</v>
       </c>
       <c r="R23" s="3">
-        <v>549.68</v>
+        <v>354.19</v>
       </c>
       <c r="S23" s="3">
         <f>T23-R23</f>
-        <v>11.9400000000001</v>
+        <v>17.68</v>
       </c>
       <c r="T23" s="3">
-        <v>561.62</v>
+        <v>371.87</v>
       </c>
       <c r="U23" s="3">
         <f>V23-T23</f>
-        <v>16.23</v>
-      </c>
-      <c r="V23" s="12">
-        <v>577.85</v>
+        <v>11.66</v>
+      </c>
+      <c r="V23" s="10">
+        <v>383.53</v>
       </c>
       <c r="W23" s="3">
         <f>X23-V23</f>
-        <v>15.28</v>
-      </c>
-      <c r="X23" s="12">
-        <v>593.13</v>
+        <v>20.5700000000001</v>
+      </c>
+      <c r="X23" s="10">
+        <v>404.1</v>
       </c>
       <c r="Y23" s="3">
         <f>Z23-X23</f>
-        <v>33.2</v>
+        <v>33.33</v>
       </c>
       <c r="Z23" s="3">
-        <v>626.33</v>
+        <v>437.43</v>
       </c>
       <c r="AA23" s="3">
-        <f>Z23-D23</f>
-        <v>218.98</v>
-      </c>
-      <c r="AB23" s="18" t="s">
+        <f>AB23-Z23</f>
+        <v>27.72</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>465.15</v>
+      </c>
+      <c r="AC23" s="3">
+        <f>AB23-D23</f>
+        <v>202.76</v>
+      </c>
+      <c r="AD23" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="AC23" s="3">
-        <v>262.06</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>30</v>
-      </c>
       <c r="AE23" s="3">
-        <v>2.4</v>
+        <v>161.56</v>
       </c>
       <c r="AF23" s="3">
-        <v>43895</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="A24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>36684</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34">
+      <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1735.94</v>
+      </c>
+      <c r="E24" s="2">
+        <f>F24-D24</f>
+        <v>48.5999999999999</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1784.54</v>
+      </c>
+      <c r="G24" s="2">
+        <f>H24-F24</f>
+        <v>74.1600000000001</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1858.7</v>
+      </c>
+      <c r="I24" s="2">
+        <f>J24-H24</f>
+        <v>65.55</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1924.25</v>
+      </c>
+      <c r="K24" s="2">
+        <f>L24-J24</f>
+        <v>35.73</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1959.98</v>
+      </c>
+      <c r="M24" s="2">
+        <f>N24-L24</f>
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N24" s="2">
+        <v>2001.86</v>
+      </c>
+      <c r="O24" s="2">
+        <f>P24-N24</f>
+        <v>74.6600000000001</v>
+      </c>
+      <c r="P24" s="2">
+        <v>2076.52</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>R24-P24</f>
+        <v>48.71</v>
+      </c>
+      <c r="R24" s="2">
+        <v>2125.23</v>
+      </c>
+      <c r="S24" s="2">
+        <f>T24-R24</f>
+        <v>57.4200000000001</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2182.65</v>
+      </c>
+      <c r="U24" s="2">
+        <f>V24-T24</f>
+        <v>68.9400000000001</v>
+      </c>
+      <c r="V24" s="8">
+        <v>2251.59</v>
+      </c>
+      <c r="W24" s="2">
+        <f>X24-V24</f>
+        <v>72.0299999999997</v>
+      </c>
+      <c r="X24" s="8">
+        <v>2323.62</v>
+      </c>
+      <c r="Y24" s="2">
+        <f>Z24-X24</f>
+        <v>23.6300000000001</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>2347.25</v>
+      </c>
+      <c r="AA24" s="2">
+        <f>AB24-Z24</f>
+        <v>64.5300000000002</v>
+      </c>
+      <c r="AB24" s="2">
+        <v>2411.78</v>
+      </c>
+      <c r="AC24" s="2">
+        <f>AB24-D24</f>
+        <v>675.84</v>
+      </c>
+      <c r="AD24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE24" s="2">
+        <v>608.32</v>
+      </c>
+      <c r="AF24" s="2">
+        <v>80</v>
+      </c>
+      <c r="AG24" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="AH24" s="2">
+        <v>150192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34">
+      <c r="A25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1446.65</v>
+      </c>
+      <c r="E25" s="2">
+        <f>F25-D25</f>
+        <v>28.1799999999998</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1474.83</v>
+      </c>
+      <c r="G25" s="2">
+        <f>H25-F25</f>
+        <v>63.8200000000002</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1538.65</v>
+      </c>
+      <c r="I25" s="2">
+        <f>J25-H25</f>
+        <v>22.9199999999998</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1561.57</v>
+      </c>
+      <c r="K25" s="2">
+        <f>L25-J25</f>
+        <v>70.8600000000001</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1632.43</v>
+      </c>
+      <c r="M25" s="2">
+        <f>N25-L25</f>
+        <v>37.4099999999999</v>
+      </c>
+      <c r="N25" s="2">
+        <v>1669.84</v>
+      </c>
+      <c r="O25" s="2">
+        <f>P25-N25</f>
+        <v>32.8300000000002</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1702.67</v>
+      </c>
+      <c r="Q25" s="2">
+        <f>R25-P25</f>
+        <v>51.9499999999998</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1754.62</v>
+      </c>
+      <c r="S25" s="2">
+        <f>T25-R25</f>
+        <v>40.1200000000001</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1794.74</v>
+      </c>
+      <c r="U25" s="2">
+        <f>V25-T25</f>
+        <v>77.5</v>
+      </c>
+      <c r="V25" s="8">
+        <v>1872.24</v>
+      </c>
+      <c r="W25" s="2">
+        <f>X25-V25</f>
+        <v>79.5899999999999</v>
+      </c>
+      <c r="X25" s="8">
+        <v>1951.83</v>
+      </c>
+      <c r="Y25" s="2">
+        <f>Z25-X25</f>
+        <v>9.01999999999998</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>1960.85</v>
+      </c>
+      <c r="AA25" s="2">
+        <f>AB25-Z25</f>
+        <v>74</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>2034.85</v>
+      </c>
+      <c r="AC25" s="2">
+        <f>AB25-D25</f>
+        <v>588.2</v>
+      </c>
+      <c r="AD25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE25" s="2">
+        <v>770.53</v>
+      </c>
+      <c r="AF25" s="5">
         <v>65</v>
       </c>
-      <c r="D24" s="3">
-        <v>552.79</v>
-      </c>
-      <c r="E24" s="3">
-        <f>F24-D24</f>
-        <v>15.9400000000001</v>
-      </c>
-      <c r="F24" s="3">
-        <v>568.73</v>
-      </c>
-      <c r="G24" s="3">
-        <f>H24-F24</f>
-        <v>1.61000000000001</v>
-      </c>
-      <c r="H24" s="3">
-        <v>570.34</v>
-      </c>
-      <c r="I24" s="3">
-        <f>J24-H24</f>
-        <v>7.13999999999999</v>
-      </c>
-      <c r="J24" s="3">
-        <v>577.48</v>
-      </c>
-      <c r="K24" s="3">
-        <f>L24-J24</f>
-        <v>2.88999999999999</v>
-      </c>
-      <c r="L24" s="3">
-        <v>580.37</v>
-      </c>
-      <c r="M24" s="3">
-        <f>N24-L24</f>
-        <v>2.55999999999995</v>
-      </c>
-      <c r="N24" s="3">
-        <v>582.93</v>
-      </c>
-      <c r="O24" s="3">
-        <f>P24-N24</f>
-        <v>24.99</v>
-      </c>
-      <c r="P24" s="3">
-        <v>607.92</v>
-      </c>
-      <c r="Q24" s="3">
-        <f>R24-P24</f>
-        <v>0.330000000000041</v>
-      </c>
-      <c r="R24" s="3">
-        <v>608.25</v>
-      </c>
-      <c r="S24" s="3">
-        <f>T24-R24</f>
-        <v>1.80999999999995</v>
-      </c>
-      <c r="T24" s="3">
-        <v>610.06</v>
-      </c>
-      <c r="U24" s="3">
-        <f>V24-T24</f>
-        <v>0.560000000000059</v>
-      </c>
-      <c r="V24" s="12">
-        <v>610.62</v>
-      </c>
-      <c r="W24" s="3">
-        <f>X24-V24</f>
-        <v>3.83000000000004</v>
-      </c>
-      <c r="X24" s="12">
-        <v>614.45</v>
-      </c>
-      <c r="Y24" s="3">
-        <f>Z24-X24</f>
-        <v>0.189999999999941</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>614.64</v>
-      </c>
-      <c r="AA24" s="3">
-        <f>Z24-D24</f>
-        <v>61.85</v>
-      </c>
-      <c r="AB24" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>133.25</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>49654</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="A25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="3">
-        <v>363.88</v>
-      </c>
-      <c r="E25" s="3">
-        <f>F25-D25</f>
-        <v>14.21</v>
-      </c>
-      <c r="F25" s="3">
-        <v>378.09</v>
-      </c>
-      <c r="G25" s="3">
-        <f>H25-F25</f>
-        <v>11.22</v>
-      </c>
-      <c r="H25" s="3">
-        <v>389.31</v>
-      </c>
-      <c r="I25" s="3">
-        <f>J25-H25</f>
-        <v>13.62</v>
-      </c>
-      <c r="J25" s="3">
-        <v>402.93</v>
-      </c>
-      <c r="K25" s="3">
-        <f>L25-J25</f>
-        <v>11.13</v>
-      </c>
-      <c r="L25" s="3">
-        <v>414.06</v>
-      </c>
-      <c r="M25" s="3">
-        <f>N25-L25</f>
-        <v>17.39</v>
-      </c>
-      <c r="N25" s="3">
-        <v>431.45</v>
-      </c>
-      <c r="O25" s="3">
-        <f>P25-N25</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P25" s="3">
-        <v>437.78</v>
-      </c>
-      <c r="Q25" s="3">
-        <f>R25-P25</f>
-        <v>53.01</v>
-      </c>
-      <c r="R25" s="3">
-        <v>490.79</v>
-      </c>
-      <c r="S25" s="3">
-        <f>T25-R25</f>
-        <v>11.82</v>
-      </c>
-      <c r="T25" s="3">
-        <v>502.61</v>
-      </c>
-      <c r="U25" s="3">
-        <f>V25-T25</f>
-        <v>19.3099999999999</v>
-      </c>
-      <c r="V25" s="12">
-        <v>521.92</v>
-      </c>
-      <c r="W25" s="3">
-        <f>X25-V25</f>
-        <v>29.5400000000001</v>
-      </c>
-      <c r="X25" s="12">
-        <v>551.46</v>
-      </c>
-      <c r="Y25" s="3">
-        <f>Z25-X25</f>
-        <v>36.98</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>588.44</v>
-      </c>
-      <c r="AA25" s="3">
-        <f>Z25-D25</f>
-        <v>224.56</v>
-      </c>
-      <c r="AB25" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC25" s="3">
-        <v>150.79</v>
-      </c>
-      <c r="AD25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="3">
-        <v>47256</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32">
+      <c r="AG25" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AH25" s="5">
+        <v>109333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D26" s="3">
         <v>305.29</v>
@@ -4216,14 +4396,14 @@
         <f>V26-T26</f>
         <v>25.13</v>
       </c>
-      <c r="V26" s="12">
+      <c r="V26" s="10">
         <v>433.01</v>
       </c>
       <c r="W26" s="3">
         <f>X26-V26</f>
         <v>37.15</v>
       </c>
-      <c r="X26" s="12">
+      <c r="X26" s="10">
         <v>470.16</v>
       </c>
       <c r="Y26" s="3">
@@ -4234,141 +4414,155 @@
         <v>481.08</v>
       </c>
       <c r="AA26" s="3">
-        <f>Z26-D26</f>
-        <v>175.79</v>
-      </c>
-      <c r="AB26" s="18" t="s">
-        <v>66</v>
+        <f>AB26-Z26</f>
+        <v>13.68</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>494.76</v>
       </c>
       <c r="AC26" s="3">
-        <v>143.89</v>
-      </c>
-      <c r="AD26" s="3">
+        <f>AB26-D26</f>
+        <v>189.47</v>
+      </c>
+      <c r="AD26" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>156.1</v>
+      </c>
+      <c r="AF26" s="3">
         <v>0</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>28066</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
-      <c r="A27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="3">
-        <v>262.39</v>
-      </c>
-      <c r="E27" s="3">
+    <row r="27" spans="1:34">
+      <c r="A27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="5">
+        <v>950.09</v>
+      </c>
+      <c r="E27" s="5">
         <f>F27-D27</f>
-        <v>11.5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>273.89</v>
-      </c>
-      <c r="G27" s="3">
+        <v>42.4</v>
+      </c>
+      <c r="F27" s="5">
+        <v>992.49</v>
+      </c>
+      <c r="G27" s="5">
         <f>H27-F27</f>
-        <v>13.97</v>
-      </c>
-      <c r="H27" s="3">
-        <v>287.86</v>
-      </c>
-      <c r="I27" s="3">
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1031.08</v>
+      </c>
+      <c r="I27" s="5">
         <f>J27-H27</f>
-        <v>16.24</v>
-      </c>
-      <c r="J27" s="3">
-        <v>304.1</v>
-      </c>
-      <c r="K27" s="3">
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1053.68</v>
+      </c>
+      <c r="K27" s="5">
         <f>L27-J27</f>
-        <v>12.65</v>
-      </c>
-      <c r="L27" s="3">
-        <v>316.75</v>
-      </c>
-      <c r="M27" s="3">
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L27" s="5">
+        <v>1064.61</v>
+      </c>
+      <c r="M27" s="5">
         <f>N27-L27</f>
-        <v>9.99000000000001</v>
-      </c>
-      <c r="N27" s="3">
-        <v>326.74</v>
-      </c>
-      <c r="O27" s="3">
+        <v>16.1800000000001</v>
+      </c>
+      <c r="N27" s="5">
+        <v>1080.79</v>
+      </c>
+      <c r="O27" s="5">
         <f>P27-N27</f>
-        <v>6.31999999999999</v>
-      </c>
-      <c r="P27" s="3">
-        <v>333.06</v>
-      </c>
-      <c r="Q27" s="3">
+        <v>13.6700000000001</v>
+      </c>
+      <c r="P27" s="5">
+        <v>1094.46</v>
+      </c>
+      <c r="Q27" s="5">
         <f>R27-P27</f>
-        <v>21.13</v>
-      </c>
-      <c r="R27" s="3">
-        <v>354.19</v>
-      </c>
-      <c r="S27" s="3">
+        <v>56.26</v>
+      </c>
+      <c r="R27" s="5">
+        <v>1150.72</v>
+      </c>
+      <c r="S27" s="5">
         <f>T27-R27</f>
-        <v>17.68</v>
-      </c>
-      <c r="T27" s="3">
-        <v>371.87</v>
-      </c>
-      <c r="U27" s="3">
+        <v>41.27</v>
+      </c>
+      <c r="T27" s="5">
+        <v>1191.99</v>
+      </c>
+      <c r="U27" s="5">
         <f>V27-T27</f>
-        <v>11.66</v>
-      </c>
-      <c r="V27" s="12">
-        <v>383.53</v>
-      </c>
-      <c r="W27" s="3">
+        <v>35.21</v>
+      </c>
+      <c r="V27" s="9">
+        <v>1227.2</v>
+      </c>
+      <c r="W27" s="5">
         <f>X27-V27</f>
-        <v>20.5700000000001</v>
-      </c>
-      <c r="X27" s="12">
-        <v>404.1</v>
-      </c>
-      <c r="Y27" s="3">
+        <v>33.3599999999999</v>
+      </c>
+      <c r="X27" s="9">
+        <v>1260.56</v>
+      </c>
+      <c r="Y27" s="5">
         <f>Z27-X27</f>
-        <v>33.33</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>437.43</v>
-      </c>
-      <c r="AA27" s="3">
-        <f>Z27-D27</f>
-        <v>175.04</v>
-      </c>
-      <c r="AB27" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>140.92</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>36684</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>46.0900000000001</v>
+      </c>
+      <c r="Z27" s="5">
+        <v>1306.65</v>
+      </c>
+      <c r="AA27" s="5">
+        <f>AB27-Z27</f>
+        <v>31.1699999999998</v>
+      </c>
+      <c r="AB27" s="5">
+        <v>1337.82</v>
+      </c>
+      <c r="AC27" s="5">
+        <f>AB27-D27</f>
+        <v>387.73</v>
+      </c>
+      <c r="AD27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE27" s="5">
+        <v>501.92</v>
+      </c>
+      <c r="AF27" s="5">
+        <v>10</v>
+      </c>
+      <c r="AG27" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="AH27" s="5">
+        <v>86194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -4397,13 +4591,15 @@
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
       <c r="AC30" s="7"/>
-    </row>
-    <row r="31" spans="1:30">
+      <c r="AD30" s="7"/>
+      <c r="AE30" s="7"/>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -4420,21 +4616,23 @@
       <c r="AB31" s="7"/>
       <c r="AC31" s="7"/>
       <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4462,58 +4660,60 @@
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AF27">
-    <sortCondition ref="Z2" descending="1"/>
+  <sortState ref="A2:AH27">
+    <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4550,40 +4750,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4924,7 +5124,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -4978,7 +5178,7 @@
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5287,10 +5487,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -5834,7 +6034,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
+    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="109">
   <si>
     <t>区服</t>
   </si>
@@ -85,6 +85,9 @@
     <t>战力（2025.6.18）</t>
   </si>
   <si>
+    <t>战力（2025.6.25）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -115,103 +118,106 @@
     <t>白处尊（养神）</t>
   </si>
   <si>
+    <t>古希腊掌管贫穷的神</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
     <t>1。</t>
   </si>
   <si>
-    <t>中低氪</t>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>[永恒]</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>清风</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>格洛（快攻）</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>眼睛妹（跳费）</t>
+  </si>
+  <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
   </si>
   <si>
     <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>Mr.Go</t>
-  </si>
-  <si>
-    <t>大氪</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
-  </si>
-  <si>
-    <t>[永恒]</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>清风</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>146区</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>圣母（杂糅）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>喵喵（跳费）</t>
-  </si>
-  <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
   </si>
   <si>
     <t>149区</t>
@@ -1023,7 +1029,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1038,7 +1044,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1053,10 +1059,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1378,11 +1384,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH39"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.5833333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.4666666666667" customWidth="1"/>
     <col min="3" max="3" width="10.6416666666667" customWidth="1"/>
     <col min="4" max="4" width="13.2583333333333" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" hidden="1" customWidth="1"/>
@@ -1402,16 +1408,16 @@
     <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="17.3916666666667" hidden="1" customWidth="1"/>
-    <col min="23" max="25" width="18.0166666666667" hidden="1" customWidth="1"/>
-    <col min="26" max="29" width="18.0166666666667" customWidth="1"/>
-    <col min="30" max="30" width="18.8916666666667" customWidth="1"/>
-    <col min="31" max="31" width="14.5416666666667" customWidth="1"/>
-    <col min="32" max="32" width="11.625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="27" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="28" max="31" width="18.0166666666667" customWidth="1"/>
+    <col min="32" max="32" width="18.8916666666667" customWidth="1"/>
+    <col min="33" max="33" width="14.5416666666667" customWidth="1"/>
+    <col min="34" max="34" width="11.625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1497,33 +1503,39 @@
         <v>16</v>
       </c>
       <c r="AC1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" t="s">
         <v>17</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>18</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>19</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>21</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:34">
+      <c r="AJ1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:36">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2">
         <v>1754.54</v>
@@ -1613,151 +1625,165 @@
         <v>2700.32</v>
       </c>
       <c r="AC2" s="2">
-        <f>AB2-D2</f>
-        <v>945.78</v>
-      </c>
-      <c r="AD2" s="13" t="s">
-        <v>26</v>
+        <f>AD2-AB2</f>
+        <v>57.52</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>2757.84</v>
       </c>
       <c r="AE2" s="2">
-        <v>462.52</v>
-      </c>
-      <c r="AF2" s="2">
+        <f>AD2-D2</f>
+        <v>1003.3</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>468.18</v>
+      </c>
+      <c r="AH2" s="2">
         <v>300</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="AI2" s="2">
         <v>2.2</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AJ2" s="2">
         <v>132783</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:36">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2">
-        <v>1425.22</v>
+        <v>2136.24</v>
       </c>
       <c r="E3" s="2">
         <f>F3-D3</f>
-        <v>64.8599999999999</v>
+        <v>40.8200000000002</v>
       </c>
       <c r="F3" s="2">
-        <v>1490.08</v>
+        <v>2177.06</v>
       </c>
       <c r="G3" s="2">
         <f>H3-F3</f>
-        <v>46</v>
+        <v>62.5999999999999</v>
       </c>
       <c r="H3" s="2">
-        <v>1536.08</v>
+        <v>2239.66</v>
       </c>
       <c r="I3" s="2">
         <f>J3-H3</f>
-        <v>50.8500000000001</v>
+        <v>47.0700000000002</v>
       </c>
       <c r="J3" s="2">
-        <v>1586.93</v>
+        <v>2286.73</v>
       </c>
       <c r="K3" s="2">
         <f>L3-J3</f>
-        <v>86.5599999999999</v>
+        <v>25.52</v>
       </c>
       <c r="L3" s="2">
-        <v>1673.49</v>
+        <v>2312.25</v>
       </c>
       <c r="M3" s="2">
         <f>N3-L3</f>
-        <v>38.5599999999999</v>
+        <v>36.7800000000002</v>
       </c>
       <c r="N3" s="2">
-        <v>1712.05</v>
+        <v>2349.03</v>
       </c>
       <c r="O3" s="2">
         <f>P3-N3</f>
-        <v>57.0900000000001</v>
+        <v>-18.02</v>
       </c>
       <c r="P3" s="2">
-        <v>1769.14</v>
+        <v>2331.01</v>
       </c>
       <c r="Q3" s="2">
         <f>R3-P3</f>
-        <v>50.8699999999999</v>
+        <v>62.7599999999998</v>
       </c>
       <c r="R3" s="2">
-        <v>1820.01</v>
+        <v>2393.77</v>
       </c>
       <c r="S3" s="2">
         <f>T3-R3</f>
-        <v>94.4300000000001</v>
+        <v>55.5599999999999</v>
       </c>
       <c r="T3" s="2">
-        <v>1914.44</v>
+        <v>2449.33</v>
       </c>
       <c r="U3" s="2">
         <f>V3-T3</f>
-        <v>31.51</v>
+        <v>31.96</v>
       </c>
       <c r="V3" s="8">
-        <v>1945.95</v>
+        <v>2481.29</v>
       </c>
       <c r="W3" s="2">
         <f>X3-V3</f>
-        <v>92.5899999999999</v>
+        <v>109.47</v>
       </c>
       <c r="X3" s="8">
-        <v>2038.54</v>
+        <v>2590.76</v>
       </c>
       <c r="Y3" s="2">
         <f>Z3-X3</f>
-        <v>48.1399999999999</v>
+        <v>20.4299999999998</v>
       </c>
       <c r="Z3" s="2">
-        <v>2086.68</v>
+        <v>2611.19</v>
       </c>
       <c r="AA3" s="2">
         <f>AB3-Z3</f>
-        <v>78.1300000000001</v>
+        <v>32.9899999999998</v>
       </c>
       <c r="AB3" s="2">
-        <v>2164.81</v>
+        <v>2644.18</v>
       </c>
       <c r="AC3" s="2">
-        <f>AB3-D3</f>
-        <v>739.59</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>29</v>
+        <f>AD3-AB3</f>
+        <v>45.9000000000001</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>2690.08</v>
       </c>
       <c r="AE3" s="2">
-        <v>511.98</v>
-      </c>
-      <c r="AF3" s="5">
+        <f>AD3-D3</f>
+        <v>553.84</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>885.76</v>
+      </c>
+      <c r="AH3" s="2">
         <v>20</v>
       </c>
-      <c r="AG3" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AH3" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34">
+      <c r="AI3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AJ3" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2">
         <v>1726.42</v>
@@ -1847,262 +1873,283 @@
         <v>2353.69</v>
       </c>
       <c r="AC4" s="2">
-        <f>AB4-D4</f>
-        <v>627.27</v>
-      </c>
-      <c r="AD4" s="13" t="s">
-        <v>31</v>
+        <f>AD4-AB4</f>
+        <v>58.8600000000001</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>2412.55</v>
       </c>
       <c r="AE4" s="2">
-        <v>545.4</v>
-      </c>
-      <c r="AF4" s="2">
+        <f>AD4-D4</f>
+        <v>686.13</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>588.34</v>
+      </c>
+      <c r="AH4" s="2">
         <v>50</v>
       </c>
-      <c r="AG4" s="2">
+      <c r="AI4" s="2">
         <v>1.3</v>
       </c>
-      <c r="AH4" s="2">
+      <c r="AJ4" s="2">
         <v>124763</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
-      <c r="A5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:36">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
+        <v>1425.22</v>
+      </c>
+      <c r="E5" s="2">
+        <f>F5-D5</f>
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1490.08</v>
+      </c>
+      <c r="G5" s="2">
+        <f>H5-F5</f>
+        <v>46</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1536.08</v>
+      </c>
+      <c r="I5" s="2">
+        <f>J5-H5</f>
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1586.93</v>
+      </c>
+      <c r="K5" s="2">
+        <f>L5-J5</f>
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1673.49</v>
+      </c>
+      <c r="M5" s="2">
+        <f>N5-L5</f>
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1712.05</v>
+      </c>
+      <c r="O5" s="2">
+        <f>P5-N5</f>
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P5" s="2">
+        <v>1769.14</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>R5-P5</f>
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1820.01</v>
+      </c>
+      <c r="S5" s="2">
+        <f>T5-R5</f>
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T5" s="2">
+        <v>1914.44</v>
+      </c>
+      <c r="U5" s="2">
+        <f>V5-T5</f>
+        <v>31.51</v>
+      </c>
+      <c r="V5" s="8">
+        <v>1945.95</v>
+      </c>
+      <c r="W5" s="2">
+        <f>X5-V5</f>
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X5" s="8">
+        <v>2038.54</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>Z5-X5</f>
+        <v>48.1399999999999</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>2086.68</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>AB5-Z5</f>
+        <v>78.1300000000001</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>2164.81</v>
+      </c>
+      <c r="AC5" s="2">
+        <f>AD5-AB5</f>
+        <v>39.8400000000001</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>2204.65</v>
+      </c>
+      <c r="AE5" s="2">
+        <f>AD5-D5</f>
+        <v>779.43</v>
+      </c>
+      <c r="AF5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>533.09</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>20</v>
+      </c>
+      <c r="AI5" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AJ5" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36">
+      <c r="A6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5">
         <v>1349.35</v>
       </c>
-      <c r="E5" s="5">
-        <f>F5-D5</f>
+      <c r="E6" s="5">
+        <f>F6-D6</f>
         <v>49.6200000000001</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F6" s="5">
         <v>1398.97</v>
       </c>
-      <c r="G5" s="5">
-        <f>H5-F5</f>
+      <c r="G6" s="5">
+        <f>H6-F6</f>
         <v>27.79</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
         <v>1426.76</v>
       </c>
-      <c r="I5" s="5">
-        <f>J5-H5</f>
+      <c r="I6" s="5">
+        <f>J6-H6</f>
         <v>29.02</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J6" s="5">
         <v>1455.78</v>
       </c>
-      <c r="K5" s="5">
-        <f>L5-J5</f>
+      <c r="K6" s="5">
+        <f>L6-J6</f>
         <v>97.8800000000001</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L6" s="5">
         <v>1553.66</v>
       </c>
-      <c r="M5" s="5">
-        <f>N5-L5</f>
+      <c r="M6" s="5">
+        <f>N6-L6</f>
         <v>42.3599999999999</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N6" s="5">
         <v>1596.02</v>
       </c>
-      <c r="O5" s="5">
-        <f>P5-N5</f>
+      <c r="O6" s="5">
+        <f>P6-N6</f>
         <v>54.22</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P6" s="5">
         <v>1650.24</v>
       </c>
-      <c r="Q5" s="5">
-        <f>R5-P5</f>
+      <c r="Q6" s="5">
+        <f>R6-P6</f>
         <v>35.5899999999999</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R6" s="5">
         <v>1685.83</v>
       </c>
-      <c r="S5" s="5">
-        <f>T5-R5</f>
+      <c r="S6" s="5">
+        <f>T6-R6</f>
         <v>68.1300000000001</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T6" s="5">
         <v>1753.96</v>
       </c>
-      <c r="U5" s="5">
-        <f>V5-T5</f>
+      <c r="U6" s="5">
+        <f>V6-T6</f>
         <v>58.5599999999999</v>
       </c>
-      <c r="V5" s="9">
+      <c r="V6" s="9">
         <v>1812.52</v>
       </c>
-      <c r="W5" s="5">
-        <f>X5-V5</f>
+      <c r="W6" s="5">
+        <f>X6-V6</f>
         <v>67.21</v>
       </c>
-      <c r="X5" s="9">
+      <c r="X6" s="9">
         <v>1879.73</v>
       </c>
-      <c r="Y5" s="5">
-        <f>Z5-X5</f>
+      <c r="Y6" s="5">
+        <f>Z6-X6</f>
         <v>20.22</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z6" s="5">
         <v>1899.95</v>
       </c>
-      <c r="AA5" s="5">
-        <f>AB5-Z5</f>
+      <c r="AA6" s="5">
+        <f>AB6-Z6</f>
         <v>35.0999999999999</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AB6" s="5">
         <v>1935.05</v>
       </c>
-      <c r="AC5" s="5">
-        <f>AB5-D5</f>
-        <v>585.7</v>
-      </c>
-      <c r="AD5" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE5" s="5">
-        <v>468.76</v>
-      </c>
-      <c r="AF5" s="5">
+      <c r="AC6" s="5">
+        <f>AD6-AB6</f>
+        <v>44.73</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>1979.78</v>
+      </c>
+      <c r="AE6" s="5">
+        <f>AD6-D6</f>
+        <v>630.43</v>
+      </c>
+      <c r="AF6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG6" s="5">
+        <v>488.53</v>
+      </c>
+      <c r="AH6" s="5">
         <v>20</v>
       </c>
-      <c r="AG5" s="5">
+      <c r="AI6" s="5">
         <v>3.2</v>
       </c>
-      <c r="AH5" s="5">
+      <c r="AJ6" s="5">
         <v>109106</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2136.24</v>
-      </c>
-      <c r="E6" s="2">
-        <f>F6-D6</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2177.06</v>
-      </c>
-      <c r="G6" s="2">
-        <f>H6-F6</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2239.66</v>
-      </c>
-      <c r="I6" s="2">
-        <f>J6-H6</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2286.73</v>
-      </c>
-      <c r="K6" s="2">
-        <f>L6-J6</f>
-        <v>25.52</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2312.25</v>
-      </c>
-      <c r="M6" s="2">
-        <f>N6-L6</f>
-        <v>36.7800000000002</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2349.03</v>
-      </c>
-      <c r="O6" s="2">
-        <f>P6-N6</f>
-        <v>-18.02</v>
-      </c>
-      <c r="P6" s="2">
-        <v>2331.01</v>
-      </c>
-      <c r="Q6" s="2">
-        <f>R6-P6</f>
-        <v>62.7599999999998</v>
-      </c>
-      <c r="R6" s="2">
-        <v>2393.77</v>
-      </c>
-      <c r="S6" s="2">
-        <f>T6-R6</f>
-        <v>55.5599999999999</v>
-      </c>
-      <c r="T6" s="2">
-        <v>2449.33</v>
-      </c>
-      <c r="U6" s="2">
-        <f>V6-T6</f>
-        <v>31.96</v>
-      </c>
-      <c r="V6" s="8">
-        <v>2481.29</v>
-      </c>
-      <c r="W6" s="2">
-        <f>X6-V6</f>
-        <v>109.47</v>
-      </c>
-      <c r="X6" s="8">
-        <v>2590.76</v>
-      </c>
-      <c r="Y6" s="2">
-        <f>Z6-X6</f>
-        <v>20.4299999999998</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>2611.19</v>
-      </c>
-      <c r="AA6" s="2">
-        <f>AB6-Z6</f>
-        <v>32.9899999999998</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>2644.18</v>
-      </c>
-      <c r="AC6" s="2">
-        <f>AB6-D6</f>
-        <v>507.94</v>
-      </c>
-      <c r="AD6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE6" s="2">
-        <v>846.38</v>
-      </c>
-      <c r="AF6" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AH6" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:36">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>37</v>
@@ -2198,28 +2245,35 @@
         <v>1238.02</v>
       </c>
       <c r="AC7" s="5">
-        <f>AB7-D7</f>
-        <v>389.09</v>
-      </c>
-      <c r="AD7" s="14" t="s">
+        <f>AD7-AB7</f>
+        <v>53.73</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1291.75</v>
+      </c>
+      <c r="AE7" s="5">
+        <f>AD7-D7</f>
+        <v>442.82</v>
+      </c>
+      <c r="AF7" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="5">
-        <v>456.07</v>
-      </c>
-      <c r="AF7" s="5">
+      <c r="AG7" s="5">
+        <v>471.97</v>
+      </c>
+      <c r="AH7" s="5">
         <v>30</v>
       </c>
-      <c r="AG7" s="5">
+      <c r="AI7" s="5">
         <v>3.2</v>
       </c>
-      <c r="AH7" s="5">
+      <c r="AJ7" s="5">
         <v>78989</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:36">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>40</v>
@@ -2315,26 +2369,33 @@
         <v>643.05</v>
       </c>
       <c r="AC8" s="3">
-        <f>AB8-D8</f>
-        <v>235.7</v>
-      </c>
-      <c r="AD8" s="15" t="s">
+        <f>AD8-AB8</f>
+        <v>11.9300000000001</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>654.98</v>
+      </c>
+      <c r="AE8" s="3">
+        <f>AD8-D8</f>
+        <v>247.63</v>
+      </c>
+      <c r="AF8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="AE8" s="3">
-        <v>286.65</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
+        <v>294.1</v>
+      </c>
+      <c r="AH8" s="3">
         <v>30</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2.4</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>43895</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:36">
       <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
@@ -2342,7 +2403,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D9" s="6">
         <v>4105.48</v>
@@ -2432,26 +2493,33 @@
         <v>5027.14</v>
       </c>
       <c r="AC9" s="6">
-        <f>AB9-D9</f>
-        <v>921.660000000001</v>
-      </c>
-      <c r="AD9" s="16" t="s">
+        <f>AD9-AB9</f>
+        <v>77.6899999999996</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>5104.83</v>
+      </c>
+      <c r="AE9" s="6">
+        <f>AD9-D9</f>
+        <v>999.35</v>
+      </c>
+      <c r="AF9" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AE9" s="6">
-        <v>1374.75</v>
-      </c>
-      <c r="AF9" s="17">
+      <c r="AG9" s="6">
+        <v>1361.06</v>
+      </c>
+      <c r="AH9" s="6">
         <v>400</v>
       </c>
-      <c r="AG9" s="17">
+      <c r="AI9" s="6">
         <v>1.2</v>
       </c>
-      <c r="AH9" s="17">
+      <c r="AJ9" s="6">
         <v>186759</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:36">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -2549,31 +2617,38 @@
         <v>2706.05</v>
       </c>
       <c r="AC10" s="2">
-        <f>AB10-D10</f>
-        <v>739.43</v>
-      </c>
-      <c r="AD10" s="13" t="s">
-        <v>36</v>
+        <f>AD10-AB10</f>
+        <v>57.1099999999997</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>2763.16</v>
       </c>
       <c r="AE10" s="2">
-        <v>969.35</v>
-      </c>
-      <c r="AF10" s="2">
+        <f>AD10-D10</f>
+        <v>796.54</v>
+      </c>
+      <c r="AF10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>1044.09</v>
+      </c>
+      <c r="AH10" s="2">
         <v>65</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AI10" s="2">
         <v>1.2</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AJ10" s="2">
         <v>130589</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:36">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>38</v>
@@ -2666,31 +2741,38 @@
         <v>1599.56</v>
       </c>
       <c r="AC11" s="5">
-        <f>AB11-D11</f>
-        <v>538.79</v>
-      </c>
-      <c r="AD11" s="14" t="s">
-        <v>29</v>
+        <f>AD11-AB11</f>
+        <v>73.21</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>1672.77</v>
       </c>
       <c r="AE11" s="5">
-        <v>283.72</v>
-      </c>
-      <c r="AF11" s="5">
+        <f>AD11-D11</f>
+        <v>612</v>
+      </c>
+      <c r="AF11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>323.34</v>
+      </c>
+      <c r="AH11" s="5">
         <v>10</v>
       </c>
-      <c r="AG11" s="5">
+      <c r="AI11" s="5">
         <v>1.3</v>
       </c>
-      <c r="AH11" s="5">
+      <c r="AJ11" s="5">
         <v>71153</v>
       </c>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:36">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
@@ -2783,619 +2865,661 @@
         <v>3845.62</v>
       </c>
       <c r="AC12" s="1">
-        <f>AB12-D12</f>
-        <v>1131.52</v>
-      </c>
-      <c r="AD12" s="18" t="s">
-        <v>50</v>
+        <f>AD12-AB12</f>
+        <v>64.1800000000003</v>
+      </c>
+      <c r="AD12" s="17">
+        <v>3909.8</v>
       </c>
       <c r="AE12" s="1">
-        <v>838.25</v>
-      </c>
-      <c r="AF12" s="1">
+        <f>AD12-D12</f>
+        <v>1195.7</v>
+      </c>
+      <c r="AF12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>871.5</v>
+      </c>
+      <c r="AH12" s="1">
         <v>500</v>
       </c>
-      <c r="AG12" s="1">
+      <c r="AI12" s="1">
         <v>8.6</v>
       </c>
-      <c r="AH12" s="1">
+      <c r="AJ12" s="1">
         <v>191519</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:36">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2">
-        <v>1350.52</v>
+        <v>2183.01</v>
       </c>
       <c r="E13" s="2">
         <f>F13-D13</f>
-        <v>52.6800000000001</v>
+        <v>24.1199999999999</v>
       </c>
       <c r="F13" s="2">
-        <v>1403.2</v>
+        <v>2207.13</v>
       </c>
       <c r="G13" s="2">
         <f>H13-F13</f>
-        <v>55.3199999999999</v>
+        <v>22.8599999999997</v>
       </c>
       <c r="H13" s="2">
-        <v>1458.52</v>
+        <v>2229.99</v>
       </c>
       <c r="I13" s="2">
         <f>J13-H13</f>
-        <v>32.6800000000001</v>
+        <v>11.7800000000002</v>
       </c>
       <c r="J13" s="2">
-        <v>1491.2</v>
+        <v>2241.77</v>
       </c>
       <c r="K13" s="2">
         <f>L13-J13</f>
-        <v>54.96</v>
+        <v>13.0100000000002</v>
       </c>
       <c r="L13" s="2">
-        <v>1546.16</v>
+        <v>2254.78</v>
       </c>
       <c r="M13" s="2">
         <f>N13-L13</f>
-        <v>92.1299999999999</v>
+        <v>62.6399999999999</v>
       </c>
       <c r="N13" s="2">
-        <v>1638.29</v>
+        <v>2317.42</v>
       </c>
       <c r="O13" s="2">
         <f>P13-N13</f>
-        <v>59.4400000000001</v>
+        <v>16.27</v>
       </c>
       <c r="P13" s="2">
-        <v>1697.73</v>
+        <v>2333.69</v>
       </c>
       <c r="Q13" s="2">
         <f>R13-P13</f>
-        <v>71.3399999999999</v>
+        <v>36.5</v>
       </c>
       <c r="R13" s="2">
-        <v>1769.07</v>
+        <v>2370.19</v>
       </c>
       <c r="S13" s="2">
         <f>T13-R13</f>
-        <v>62.9000000000001</v>
+        <v>65.1900000000001</v>
       </c>
       <c r="T13" s="2">
-        <v>1831.97</v>
+        <v>2435.38</v>
       </c>
       <c r="U13" s="2">
         <f>V13-T13</f>
-        <v>66.5899999999999</v>
+        <v>31.7599999999998</v>
       </c>
       <c r="V13" s="8">
-        <v>1898.56</v>
+        <v>2467.14</v>
       </c>
       <c r="W13" s="2">
         <f>X13-V13</f>
-        <v>48.77</v>
+        <v>53.75</v>
       </c>
       <c r="X13" s="8">
-        <v>1947.33</v>
+        <v>2520.89</v>
       </c>
       <c r="Y13" s="2">
         <f>Z13-X13</f>
-        <v>59.47</v>
+        <v>24.3299999999999</v>
       </c>
       <c r="Z13" s="2">
-        <v>2006.8</v>
+        <v>2545.22</v>
       </c>
       <c r="AA13" s="2">
         <f>AB13-Z13</f>
+        <v>59.3900000000003</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>2604.61</v>
+      </c>
+      <c r="AC13" s="2">
+        <f>AD13-AB13</f>
+        <v>34.0499999999997</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>2638.66</v>
+      </c>
+      <c r="AE13" s="2">
+        <f>AD13-D13</f>
+        <v>455.65</v>
+      </c>
+      <c r="AF13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG13" s="2">
+        <v>642.41</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1350.52</v>
+      </c>
+      <c r="E14" s="2">
+        <f>F14-D14</f>
+        <v>52.6800000000001</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1403.2</v>
+      </c>
+      <c r="G14" s="2">
+        <f>H14-F14</f>
+        <v>55.3199999999999</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1458.52</v>
+      </c>
+      <c r="I14" s="2">
+        <f>J14-H14</f>
+        <v>32.6800000000001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1491.2</v>
+      </c>
+      <c r="K14" s="2">
+        <f>L14-J14</f>
+        <v>54.96</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1546.16</v>
+      </c>
+      <c r="M14" s="2">
+        <f>N14-L14</f>
+        <v>92.1299999999999</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1638.29</v>
+      </c>
+      <c r="O14" s="2">
+        <f>P14-N14</f>
+        <v>59.4400000000001</v>
+      </c>
+      <c r="P14" s="2">
+        <v>1697.73</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>R14-P14</f>
+        <v>71.3399999999999</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1769.07</v>
+      </c>
+      <c r="S14" s="2">
+        <f>T14-R14</f>
+        <v>62.9000000000001</v>
+      </c>
+      <c r="T14" s="2">
+        <v>1831.97</v>
+      </c>
+      <c r="U14" s="2">
+        <f>V14-T14</f>
+        <v>66.5899999999999</v>
+      </c>
+      <c r="V14" s="8">
+        <v>1898.56</v>
+      </c>
+      <c r="W14" s="2">
+        <f>X14-V14</f>
+        <v>48.77</v>
+      </c>
+      <c r="X14" s="8">
+        <v>1947.33</v>
+      </c>
+      <c r="Y14" s="2">
+        <f>Z14-X14</f>
+        <v>59.47</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>2006.8</v>
+      </c>
+      <c r="AA14" s="2">
+        <f>AB14-Z14</f>
         <v>82.3900000000001</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AB14" s="2">
         <v>2089.19</v>
       </c>
-      <c r="AC13" s="2">
-        <f>AB13-D13</f>
-        <v>738.67</v>
-      </c>
-      <c r="AD13" s="13" t="s">
+      <c r="AC14" s="2">
+        <f>AD14-AB14</f>
+        <v>98.8200000000002</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>2188.01</v>
+      </c>
+      <c r="AE14" s="2">
+        <f>AD14-D14</f>
+        <v>837.49</v>
+      </c>
+      <c r="AF14" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AE13" s="2">
-        <v>659.37</v>
-      </c>
-      <c r="AF13" s="5">
+      <c r="AG14" s="2">
+        <v>679.12</v>
+      </c>
+      <c r="AH14" s="5">
         <v>65</v>
       </c>
-      <c r="AG13" s="5">
+      <c r="AI14" s="5">
         <v>1.4</v>
       </c>
-      <c r="AH13" s="5">
+      <c r="AJ14" s="5">
         <v>127603</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
-      <c r="A14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    <row r="15" spans="1:36">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1576.18</v>
+      </c>
+      <c r="E15" s="2">
+        <f>F15-D15</f>
+        <v>38.8399999999999</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1615.02</v>
+      </c>
+      <c r="G15" s="2">
+        <f>H15-F15</f>
+        <v>35.5999999999999</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1650.62</v>
+      </c>
+      <c r="I15" s="2">
+        <f>J15-H15</f>
+        <v>37.47</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1688.09</v>
+      </c>
+      <c r="K15" s="2">
+        <f>L15-J15</f>
+        <v>21.49</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1709.58</v>
+      </c>
+      <c r="M15" s="2">
+        <f>N15-L15</f>
+        <v>24.53</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1734.11</v>
+      </c>
+      <c r="O15" s="2">
+        <f>P15-N15</f>
+        <v>19.5300000000002</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1753.64</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>R15-P15</f>
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1818.75</v>
+      </c>
+      <c r="S15" s="2">
+        <f>T15-R15</f>
+        <v>34.3699999999999</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1853.12</v>
+      </c>
+      <c r="U15" s="2">
+        <f>V15-T15</f>
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V15" s="8">
+        <v>1893.96</v>
+      </c>
+      <c r="W15" s="2">
+        <f>X15-V15</f>
+        <v>40.96</v>
+      </c>
+      <c r="X15" s="8">
+        <v>1934.92</v>
+      </c>
+      <c r="Y15" s="2">
+        <f>Z15-X15</f>
+        <v>59.05</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>1993.97</v>
+      </c>
+      <c r="AA15" s="2">
+        <f>AB15-Z15</f>
+        <v>58.4799999999998</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>2052.45</v>
+      </c>
+      <c r="AC15" s="2">
+        <f>AD15-AB15</f>
+        <v>26.7400000000002</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>2079.19</v>
+      </c>
+      <c r="AE15" s="2">
+        <f>AD15-D15</f>
+        <v>503.01</v>
+      </c>
+      <c r="AF15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>509.96</v>
+      </c>
+      <c r="AH15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="A16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D16" s="5">
         <v>1156.57</v>
       </c>
-      <c r="E14" s="5">
-        <f>F14-D14</f>
+      <c r="E16" s="5">
+        <f>F16-D16</f>
         <v>40.4400000000001</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F16" s="5">
         <v>1197.01</v>
       </c>
-      <c r="G14" s="5">
-        <f>H14-F14</f>
+      <c r="G16" s="5">
+        <f>H16-F16</f>
         <v>46.97</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H16" s="5">
         <v>1243.98</v>
       </c>
-      <c r="I14" s="5">
-        <f>J14-H14</f>
+      <c r="I16" s="5">
+        <f>J16-H16</f>
         <v>58.49</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J16" s="5">
         <v>1302.47</v>
       </c>
-      <c r="K14" s="5">
-        <f>L14-J14</f>
+      <c r="K16" s="5">
+        <f>L16-J16</f>
         <v>36.6399999999999</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L16" s="5">
         <v>1339.11</v>
       </c>
-      <c r="M14" s="5">
-        <f>N14-L14</f>
+      <c r="M16" s="5">
+        <f>N16-L16</f>
         <v>33.99</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N16" s="5">
         <v>1373.1</v>
       </c>
-      <c r="O14" s="5">
-        <f>P14-N14</f>
+      <c r="O16" s="5">
+        <f>P16-N16</f>
         <v>30.0600000000002</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P16" s="5">
         <v>1403.16</v>
       </c>
-      <c r="Q14" s="5">
-        <f>R14-P14</f>
+      <c r="Q16" s="5">
+        <f>R16-P16</f>
         <v>47.3</v>
       </c>
-      <c r="R14" s="5">
+      <c r="R16" s="5">
         <v>1450.46</v>
       </c>
-      <c r="S14" s="5">
-        <f>T14-R14</f>
+      <c r="S16" s="5">
+        <f>T16-R16</f>
         <v>46.8299999999999</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T16" s="5">
         <v>1497.29</v>
       </c>
-      <c r="U14" s="5">
-        <f>V14-T14</f>
+      <c r="U16" s="5">
+        <f>V16-T16</f>
         <v>58.6500000000001</v>
       </c>
-      <c r="V14" s="9">
+      <c r="V16" s="9">
         <v>1555.94</v>
       </c>
-      <c r="W14" s="5">
-        <f>X14-V14</f>
+      <c r="W16" s="5">
+        <f>X16-V16</f>
         <v>70.3099999999999</v>
       </c>
-      <c r="X14" s="9">
+      <c r="X16" s="9">
         <v>1626.25</v>
       </c>
-      <c r="Y14" s="5">
-        <f>Z14-X14</f>
+      <c r="Y16" s="5">
+        <f>Z16-X16</f>
         <v>31.49</v>
       </c>
-      <c r="Z14" s="5">
+      <c r="Z16" s="5">
         <v>1657.74</v>
       </c>
-      <c r="AA14" s="5">
-        <f>AB14-Z14</f>
+      <c r="AA16" s="5">
+        <f>AB16-Z16</f>
         <v>59.21</v>
       </c>
-      <c r="AB14" s="5">
+      <c r="AB16" s="5">
         <v>1716.95</v>
       </c>
-      <c r="AC14" s="5">
-        <f>AB14-D14</f>
-        <v>560.38</v>
-      </c>
-      <c r="AD14" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE14" s="5">
-        <v>458.27</v>
-      </c>
-      <c r="AF14" s="5">
+      <c r="AC16" s="5">
+        <f>AD16-AB16</f>
+        <v>31.99</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>1748.94</v>
+      </c>
+      <c r="AE16" s="5">
+        <f>AD16-D16</f>
+        <v>592.37</v>
+      </c>
+      <c r="AF16" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>470.82</v>
+      </c>
+      <c r="AH16" s="5">
         <v>25</v>
       </c>
-      <c r="AG14" s="5">
+      <c r="AI16" s="5">
         <v>3</v>
       </c>
-      <c r="AH14" s="5">
+      <c r="AJ16" s="5">
         <v>100457</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
-      <c r="A15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="5">
+    <row r="17" spans="1:36">
+      <c r="A17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5">
         <v>907.94</v>
       </c>
-      <c r="E15" s="5">
-        <f>F15-D15</f>
+      <c r="E17" s="5">
+        <f>F17-D17</f>
         <v>64.0799999999999</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F17" s="5">
         <v>972.02</v>
       </c>
-      <c r="G15" s="5">
-        <f>H15-F15</f>
+      <c r="G17" s="5">
+        <f>H17-F17</f>
         <v>36.26</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H17" s="5">
         <v>1008.28</v>
       </c>
-      <c r="I15" s="5">
-        <f>J15-H15</f>
+      <c r="I17" s="5">
+        <f>J17-H17</f>
         <v>28.8</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J17" s="5">
         <v>1037.08</v>
       </c>
-      <c r="K15" s="5">
-        <f>L15-J15</f>
+      <c r="K17" s="5">
+        <f>L17-J17</f>
         <v>40.1000000000001</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L17" s="5">
         <v>1077.18</v>
       </c>
-      <c r="M15" s="5">
-        <f>N15-L15</f>
+      <c r="M17" s="5">
+        <f>N17-L17</f>
         <v>26.03</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N17" s="5">
         <v>1103.21</v>
       </c>
-      <c r="O15" s="5">
-        <f>P15-N15</f>
+      <c r="O17" s="5">
+        <f>P17-N17</f>
         <v>28.3499999999999</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P17" s="5">
         <v>1131.56</v>
       </c>
-      <c r="Q15" s="5">
-        <f>R15-P15</f>
+      <c r="Q17" s="5">
+        <f>R17-P17</f>
         <v>50.1900000000001</v>
       </c>
-      <c r="R15" s="5">
+      <c r="R17" s="5">
         <v>1181.75</v>
       </c>
-      <c r="S15" s="5">
-        <f>T15-R15</f>
+      <c r="S17" s="5">
+        <f>T17-R17</f>
         <v>26.8699999999999</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T17" s="5">
         <v>1208.62</v>
       </c>
-      <c r="U15" s="5">
-        <f>V15-T15</f>
+      <c r="U17" s="5">
+        <f>V17-T17</f>
         <v>58.3000000000002</v>
       </c>
-      <c r="V15" s="9">
+      <c r="V17" s="9">
         <v>1266.92</v>
       </c>
-      <c r="W15" s="5">
-        <f>X15-V15</f>
+      <c r="W17" s="5">
+        <f>X17-V17</f>
         <v>41.0599999999999</v>
       </c>
-      <c r="X15" s="9">
+      <c r="X17" s="9">
         <v>1307.98</v>
       </c>
-      <c r="Y15" s="5">
-        <f>Z15-X15</f>
+      <c r="Y17" s="5">
+        <f>Z17-X17</f>
         <v>31.49</v>
       </c>
-      <c r="Z15" s="5">
+      <c r="Z17" s="5">
         <v>1339.47</v>
       </c>
-      <c r="AA15" s="5">
-        <f>AB15-Z15</f>
+      <c r="AA17" s="5">
+        <f>AB17-Z17</f>
         <v>50.5899999999999</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="AB17" s="5">
         <v>1390.06</v>
       </c>
-      <c r="AC15" s="5">
-        <f>AB15-D15</f>
-        <v>482.12</v>
-      </c>
-      <c r="AD15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE15" s="5">
-        <v>473.77</v>
-      </c>
-      <c r="AF15" s="5">
+      <c r="AC17" s="5">
+        <f>AD17-AB17</f>
+        <v>35.8099999999999</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>1425.87</v>
+      </c>
+      <c r="AE17" s="5">
+        <f>AD17-D17</f>
+        <v>517.93</v>
+      </c>
+      <c r="AF17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG17" s="5">
+        <v>489.27</v>
+      </c>
+      <c r="AH17" s="5">
         <v>35</v>
       </c>
-      <c r="AG15" s="5">
+      <c r="AI17" s="5">
         <v>8.2</v>
       </c>
-      <c r="AH15" s="5">
+      <c r="AJ17" s="5">
         <v>65285</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
-      <c r="A16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1576.18</v>
-      </c>
-      <c r="E16" s="2">
-        <f>F16-D16</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1615.02</v>
-      </c>
-      <c r="G16" s="2">
-        <f>H16-F16</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1650.62</v>
-      </c>
-      <c r="I16" s="2">
-        <f>J16-H16</f>
-        <v>37.47</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1688.09</v>
-      </c>
-      <c r="K16" s="2">
-        <f>L16-J16</f>
-        <v>21.49</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1709.58</v>
-      </c>
-      <c r="M16" s="2">
-        <f>N16-L16</f>
-        <v>24.53</v>
-      </c>
-      <c r="N16" s="2">
-        <v>1734.11</v>
-      </c>
-      <c r="O16" s="2">
-        <f>P16-N16</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P16" s="2">
-        <v>1753.64</v>
-      </c>
-      <c r="Q16" s="2">
-        <f>R16-P16</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R16" s="2">
-        <v>1818.75</v>
-      </c>
-      <c r="S16" s="2">
-        <f>T16-R16</f>
-        <v>34.3699999999999</v>
-      </c>
-      <c r="T16" s="2">
-        <v>1853.12</v>
-      </c>
-      <c r="U16" s="2">
-        <f>V16-T16</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V16" s="8">
-        <v>1893.96</v>
-      </c>
-      <c r="W16" s="2">
-        <f>X16-V16</f>
-        <v>40.96</v>
-      </c>
-      <c r="X16" s="8">
-        <v>1934.92</v>
-      </c>
-      <c r="Y16" s="2">
-        <f>Z16-X16</f>
-        <v>59.05</v>
-      </c>
-      <c r="Z16" s="2">
-        <v>1993.97</v>
-      </c>
-      <c r="AA16" s="2">
-        <f>AB16-Z16</f>
-        <v>58.4799999999998</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>2052.45</v>
-      </c>
-      <c r="AC16" s="2">
-        <f>AB16-D16</f>
-        <v>476.27</v>
-      </c>
-      <c r="AD16" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE16" s="2">
-        <v>505.86</v>
-      </c>
-      <c r="AF16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2">
-        <v>2183.01</v>
-      </c>
-      <c r="E17" s="2">
-        <f>F17-D17</f>
-        <v>24.1199999999999</v>
-      </c>
-      <c r="F17" s="2">
-        <v>2207.13</v>
-      </c>
-      <c r="G17" s="2">
-        <f>H17-F17</f>
-        <v>22.8599999999997</v>
-      </c>
-      <c r="H17" s="2">
-        <v>2229.99</v>
-      </c>
-      <c r="I17" s="2">
-        <f>J17-H17</f>
-        <v>11.7800000000002</v>
-      </c>
-      <c r="J17" s="2">
-        <v>2241.77</v>
-      </c>
-      <c r="K17" s="2">
-        <f>L17-J17</f>
-        <v>13.0100000000002</v>
-      </c>
-      <c r="L17" s="2">
-        <v>2254.78</v>
-      </c>
-      <c r="M17" s="2">
-        <f>N17-L17</f>
-        <v>62.6399999999999</v>
-      </c>
-      <c r="N17" s="2">
-        <v>2317.42</v>
-      </c>
-      <c r="O17" s="2">
-        <f>P17-N17</f>
-        <v>16.27</v>
-      </c>
-      <c r="P17" s="2">
-        <v>2333.69</v>
-      </c>
-      <c r="Q17" s="2">
-        <f>R17-P17</f>
-        <v>36.5</v>
-      </c>
-      <c r="R17" s="2">
-        <v>2370.19</v>
-      </c>
-      <c r="S17" s="2">
-        <f>T17-R17</f>
-        <v>65.1900000000001</v>
-      </c>
-      <c r="T17" s="2">
-        <v>2435.38</v>
-      </c>
-      <c r="U17" s="2">
-        <f>V17-T17</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V17" s="8">
-        <v>2467.14</v>
-      </c>
-      <c r="W17" s="2">
-        <f>X17-V17</f>
-        <v>53.75</v>
-      </c>
-      <c r="X17" s="8">
-        <v>2520.89</v>
-      </c>
-      <c r="Y17" s="2">
-        <f>Z17-X17</f>
-        <v>24.3299999999999</v>
-      </c>
-      <c r="Z17" s="2">
-        <v>2545.22</v>
-      </c>
-      <c r="AA17" s="2">
-        <f>AB17-Z17</f>
-        <v>59.3900000000003</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>2604.61</v>
-      </c>
-      <c r="AC17" s="2">
-        <f>AB17-D17</f>
-        <v>421.6</v>
-      </c>
-      <c r="AD17" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE17" s="2">
-        <v>607.91</v>
-      </c>
-      <c r="AF17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:36">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3">
         <v>363.88</v>
@@ -3485,31 +3609,38 @@
         <v>609.61</v>
       </c>
       <c r="AC18" s="3">
-        <f>AB18-D18</f>
-        <v>245.73</v>
-      </c>
-      <c r="AD18" s="15" t="s">
-        <v>29</v>
+        <f>AD18-AB18</f>
+        <v>17.4399999999999</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>627.05</v>
       </c>
       <c r="AE18" s="3">
-        <v>161.31</v>
-      </c>
-      <c r="AF18" s="3">
+        <f>AD18-D18</f>
+        <v>263.17</v>
+      </c>
+      <c r="AF18" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>183.87</v>
+      </c>
+      <c r="AH18" s="3">
         <v>0</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>47256</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:36">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>46</v>
@@ -3602,34 +3733,41 @@
         <v>3408.13</v>
       </c>
       <c r="AC19" s="1">
-        <f>AB19-D19</f>
-        <v>874.28</v>
-      </c>
-      <c r="AD19" s="18" t="s">
+        <f>AD19-AB19</f>
+        <v>68.9099999999999</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>3477.04</v>
+      </c>
+      <c r="AE19" s="1">
+        <f>AD19-D19</f>
+        <v>943.19</v>
+      </c>
+      <c r="AF19" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>689.92</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>200</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>172501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36">
+      <c r="A20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AE19" s="1">
-        <v>680.92</v>
-      </c>
-      <c r="AF19" s="1">
-        <v>200</v>
-      </c>
-      <c r="AG19" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AH19" s="1">
-        <v>172501</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34">
-      <c r="A20" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D20" s="3">
         <v>552.79</v>
@@ -3719,34 +3857,41 @@
         <v>615.33</v>
       </c>
       <c r="AC20" s="3">
-        <f>AB20-D20</f>
-        <v>62.5400000000001</v>
-      </c>
-      <c r="AD20" s="15" t="s">
-        <v>29</v>
+        <f>AD20-AB20</f>
+        <v>6.64999999999998</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>621.98</v>
       </c>
       <c r="AE20" s="3">
-        <v>133.35</v>
-      </c>
-      <c r="AF20" s="3">
+        <f>AD20-D20</f>
+        <v>69.1900000000001</v>
+      </c>
+      <c r="AF20" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>126.77</v>
+      </c>
+      <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>0.5</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>49654</v>
       </c>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:36">
       <c r="A21" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5">
         <v>953.78</v>
@@ -3836,34 +3981,41 @@
         <v>1413.32</v>
       </c>
       <c r="AC21" s="5">
-        <f>AB21-D21</f>
-        <v>459.54</v>
-      </c>
-      <c r="AD21" s="14" t="s">
+        <f>AD21-AB21</f>
+        <v>73.72</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>1487.04</v>
+      </c>
+      <c r="AE21" s="5">
+        <f>AD21-D21</f>
+        <v>533.26</v>
+      </c>
+      <c r="AF21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AE21" s="5">
-        <v>492.07</v>
-      </c>
-      <c r="AF21" s="5">
+      <c r="AG21" s="5">
+        <v>539.88</v>
+      </c>
+      <c r="AH21" s="5">
         <v>30</v>
       </c>
-      <c r="AG21" s="5">
+      <c r="AI21" s="5">
         <v>1</v>
       </c>
-      <c r="AH21" s="5">
+      <c r="AJ21" s="5">
         <v>105419</v>
       </c>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:36">
       <c r="A22" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="5">
         <v>927.15</v>
@@ -3953,34 +4105,41 @@
         <v>1254.53</v>
       </c>
       <c r="AC22" s="5">
-        <f>AB22-D22</f>
-        <v>327.38</v>
-      </c>
-      <c r="AD22" s="14" t="s">
-        <v>29</v>
+        <f>AD22-AB22</f>
+        <v>18.8900000000001</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>1273.42</v>
       </c>
       <c r="AE22" s="5">
-        <v>350.61</v>
-      </c>
-      <c r="AF22" s="5">
+        <f>AD22-D22</f>
+        <v>346.27</v>
+      </c>
+      <c r="AF22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>354.06</v>
+      </c>
+      <c r="AH22" s="5">
         <v>10</v>
       </c>
-      <c r="AG22" s="5">
+      <c r="AI22" s="5">
         <v>1.1</v>
       </c>
-      <c r="AH22" s="5">
+      <c r="AJ22" s="5">
         <v>80664</v>
       </c>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:36">
       <c r="A23" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3">
         <v>262.39</v>
@@ -4070,34 +4229,41 @@
         <v>465.15</v>
       </c>
       <c r="AC23" s="3">
-        <f>AB23-D23</f>
-        <v>202.76</v>
-      </c>
-      <c r="AD23" s="15" t="s">
-        <v>69</v>
+        <f>AD23-AB23</f>
+        <v>9.79000000000002</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>474.94</v>
       </c>
       <c r="AE23" s="3">
-        <v>161.56</v>
-      </c>
-      <c r="AF23" s="3">
+        <f>AD23-D23</f>
+        <v>212.55</v>
+      </c>
+      <c r="AF23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>162.06</v>
+      </c>
+      <c r="AH23" s="3">
         <v>0</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>36684</v>
       </c>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:36">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2">
         <v>1735.94</v>
@@ -4187,34 +4353,41 @@
         <v>2411.78</v>
       </c>
       <c r="AC24" s="2">
-        <f>AB24-D24</f>
-        <v>675.84</v>
-      </c>
-      <c r="AD24" s="13" t="s">
+        <f>AD24-AB24</f>
+        <v>30.2599999999998</v>
+      </c>
+      <c r="AD24" s="2">
+        <v>2442.04</v>
+      </c>
+      <c r="AE24" s="2">
+        <f>AD24-D24</f>
+        <v>706.1</v>
+      </c>
+      <c r="AF24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG24" s="2">
+        <v>631.57</v>
+      </c>
+      <c r="AH24" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI24" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="AJ24" s="2">
+        <v>150192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36">
+      <c r="A25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AE24" s="2">
-        <v>608.32</v>
-      </c>
-      <c r="AF24" s="2">
-        <v>80</v>
-      </c>
-      <c r="AG24" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="AH24" s="2">
-        <v>150192</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34">
-      <c r="A25" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2">
         <v>1446.65</v>
@@ -4304,34 +4477,41 @@
         <v>2034.85</v>
       </c>
       <c r="AC25" s="2">
-        <f>AB25-D25</f>
-        <v>588.2</v>
-      </c>
-      <c r="AD25" s="13" t="s">
+        <f>AD25-AB25</f>
+        <v>31.8000000000002</v>
+      </c>
+      <c r="AD25" s="2">
+        <v>2066.65</v>
+      </c>
+      <c r="AE25" s="2">
+        <f>AD25-D25</f>
+        <v>620</v>
+      </c>
+      <c r="AF25" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AE25" s="2">
-        <v>770.53</v>
-      </c>
-      <c r="AF25" s="5">
+      <c r="AG25" s="2">
+        <v>794.88</v>
+      </c>
+      <c r="AH25" s="5">
         <v>65</v>
       </c>
-      <c r="AG25" s="5">
+      <c r="AI25" s="5">
         <v>1.4</v>
       </c>
-      <c r="AH25" s="5">
+      <c r="AJ25" s="5">
         <v>109333</v>
       </c>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:36">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="3">
         <v>305.29</v>
@@ -4421,31 +4601,38 @@
         <v>494.76</v>
       </c>
       <c r="AC26" s="3">
-        <f>AB26-D26</f>
-        <v>189.47</v>
-      </c>
-      <c r="AD26" s="15" t="s">
-        <v>29</v>
+        <f>AD26-AB26</f>
+        <v>12.69</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>507.45</v>
       </c>
       <c r="AE26" s="3">
-        <v>156.1</v>
-      </c>
-      <c r="AF26" s="3">
+        <f>AD26-D26</f>
+        <v>202.16</v>
+      </c>
+      <c r="AF26" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>121.84</v>
+      </c>
+      <c r="AH26" s="3">
         <v>0</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>28066</v>
       </c>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:36">
       <c r="A27" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>38</v>
@@ -4538,31 +4725,38 @@
         <v>1337.82</v>
       </c>
       <c r="AC27" s="5">
-        <f>AB27-D27</f>
-        <v>387.73</v>
-      </c>
-      <c r="AD27" s="14" t="s">
-        <v>77</v>
+        <f>AD27-AB27</f>
+        <v>18.79</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>1356.61</v>
       </c>
       <c r="AE27" s="5">
-        <v>501.92</v>
-      </c>
-      <c r="AF27" s="5">
+        <f>AD27-D27</f>
+        <v>406.52</v>
+      </c>
+      <c r="AF27" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG27" s="5">
+        <v>514.42</v>
+      </c>
+      <c r="AH27" s="5">
         <v>10</v>
       </c>
-      <c r="AG27" s="5">
+      <c r="AI27" s="5">
         <v>2.2</v>
       </c>
-      <c r="AH27" s="5">
+      <c r="AJ27" s="5">
         <v>86194</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" spans="1:33">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -4593,13 +4787,15 @@
       <c r="AC30" s="7"/>
       <c r="AD30" s="7"/>
       <c r="AE30" s="7"/>
-    </row>
-    <row r="31" spans="1:32">
+      <c r="AF30" s="7"/>
+      <c r="AG30" s="7"/>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -4618,21 +4814,23 @@
       <c r="AD31" s="7"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
+      <c r="AG31" s="7"/>
+      <c r="AH31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4662,21 +4860,23 @@
       <c r="AB33" s="7"/>
       <c r="AC33" s="7"/>
       <c r="AD33" s="7"/>
+      <c r="AE33" s="7"/>
+      <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4684,35 +4884,35 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AH27">
+  <sortState ref="A2:AJ27">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4750,40 +4950,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5124,7 +5324,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -5178,7 +5378,7 @@
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5487,10 +5687,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -6034,7 +6234,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
+    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="109">
   <si>
     <t>区服</t>
   </si>
@@ -88,6 +88,9 @@
     <t>战力（2025.6.25）</t>
   </si>
   <si>
+    <t>战力（2025.7.2）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -106,6 +109,39 @@
     <t>抽卡数</t>
   </si>
   <si>
+    <t>146区</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>大氪</t>
+  </si>
+  <si>
+    <t>圣母（杂糅）</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>沙琪玛（快攻）</t>
+  </si>
+  <si>
     <t>145区</t>
   </si>
   <si>
@@ -118,21 +154,36 @@
     <t>白处尊（养神）</t>
   </si>
   <si>
+    <t>江南</t>
+  </si>
+  <si>
+    <t>魔尊（快攻）</t>
+  </si>
+  <si>
     <t>古希腊掌管贫穷的神</t>
   </si>
   <si>
-    <t>大氪</t>
-  </si>
-  <si>
-    <t>魔尊（快攻）</t>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>眼睛妹（跳费）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>洞察女（洞察）</t>
   </si>
   <si>
     <t>杜佳捷</t>
   </si>
   <si>
-    <t>中低氪</t>
-  </si>
-  <si>
     <t>白处尊（杂糅）</t>
   </si>
   <si>
@@ -142,16 +193,61 @@
     <t>查查（养神）</t>
   </si>
   <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>玩玩</t>
+  </si>
+  <si>
     <t>小黑</t>
   </si>
   <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
+    <t>152区</t>
+  </si>
+  <si>
+    <t>养乐多</t>
+  </si>
+  <si>
+    <t>梅（养神）</t>
+  </si>
+  <si>
     <t>[永恒]</t>
   </si>
   <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
+    <t>朱</t>
+  </si>
+  <si>
+    <t>微氪</t>
+  </si>
+  <si>
+    <t>讯（养神）</t>
   </si>
   <si>
     <t>清风</t>
@@ -160,118 +256,22 @@
     <t>冽（传承）</t>
   </si>
   <si>
-    <t>146区</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>圣母（杂糅）</t>
-  </si>
-  <si>
-    <t>江南</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>格洛（快攻）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>眼睛妹（跳费）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>玩玩</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
     <t>白夜</t>
   </si>
   <si>
     <t>零氪</t>
   </si>
   <si>
-    <t>讯（养神）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>沙琪玛（快攻）</t>
-  </si>
-  <si>
     <t>桂林碧桂园</t>
   </si>
   <si>
-    <t>微氪</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>朱</t>
+    <t>秋雨</t>
   </si>
   <si>
     <t>糊涂阳</t>
   </si>
   <si>
     <t>丽娅（杂糅）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>圣母（洞察）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>152区</t>
-  </si>
-  <si>
-    <t>养乐多</t>
-  </si>
-  <si>
-    <t>梅（养神）</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -1010,7 +1010,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1035,6 +1035,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1044,11 +1050,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1057,15 +1078,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1384,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1408,16 +1420,16 @@
     <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="17.3916666666667" hidden="1" customWidth="1"/>
-    <col min="23" max="27" width="18.0166666666667" hidden="1" customWidth="1"/>
-    <col min="28" max="31" width="18.0166666666667" customWidth="1"/>
-    <col min="32" max="32" width="18.8916666666667" customWidth="1"/>
-    <col min="33" max="33" width="14.5416666666667" customWidth="1"/>
-    <col min="34" max="34" width="11.625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="29" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="30" max="33" width="18.0166666666667" customWidth="1"/>
+    <col min="34" max="34" width="18.8916666666667" customWidth="1"/>
+    <col min="35" max="35" width="14.5416666666667" customWidth="1"/>
+    <col min="36" max="36" width="11.625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:38">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1508,1770 +1520,1874 @@
       <c r="AD1" t="s">
         <v>17</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF1" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>20</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>21</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>22</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:36">
-      <c r="A2" s="2" t="s">
+      <c r="AL1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:38">
+      <c r="A2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="6">
+        <v>4105.48</v>
+      </c>
+      <c r="E2" s="6">
+        <f>F2-D2</f>
+        <v>181.21</v>
+      </c>
+      <c r="F2" s="6">
+        <v>4286.69</v>
+      </c>
+      <c r="G2" s="6">
+        <f>H2-F2</f>
+        <v>139.09</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4425.78</v>
+      </c>
+      <c r="I2" s="6">
+        <f>J2-H2</f>
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J2" s="6">
+        <v>4480.66</v>
+      </c>
+      <c r="K2" s="6">
+        <f>L2-J2</f>
+        <v>104.900000000001</v>
+      </c>
+      <c r="L2" s="6">
+        <v>4585.56</v>
+      </c>
+      <c r="M2" s="6">
+        <f>N2-L2</f>
+        <v>70.29</v>
+      </c>
+      <c r="N2" s="6">
+        <v>4655.85</v>
+      </c>
+      <c r="O2" s="6">
+        <f>P2-N2</f>
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P2" s="6">
+        <v>4705.02</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>R2-P2</f>
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R2" s="6">
+        <v>4743.24</v>
+      </c>
+      <c r="S2" s="6">
+        <f>T2-R2</f>
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T2" s="6">
+        <v>4788.86</v>
+      </c>
+      <c r="U2" s="6">
+        <f>V2-T2</f>
+        <v>27.5900000000001</v>
+      </c>
+      <c r="V2" s="8">
+        <v>4816.45</v>
+      </c>
+      <c r="W2" s="6">
+        <f>X2-V2</f>
+        <v>158.22</v>
+      </c>
+      <c r="X2" s="8">
+        <v>4974.67</v>
+      </c>
+      <c r="Y2" s="6">
+        <f>Z2-X2</f>
+        <v>32.8999999999996</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>5007.57</v>
+      </c>
+      <c r="AA2" s="6">
+        <f>AB2-Z2</f>
+        <v>19.5700000000006</v>
+      </c>
+      <c r="AB2" s="6">
+        <v>5027.14</v>
+      </c>
+      <c r="AC2" s="6">
+        <f>AD2-AB2</f>
+        <v>77.6899999999996</v>
+      </c>
+      <c r="AD2" s="6">
+        <v>5104.83</v>
+      </c>
+      <c r="AE2" s="13">
+        <f>AF2-AD2</f>
+        <v>27.4499999999998</v>
+      </c>
+      <c r="AF2" s="13">
+        <v>5132.28</v>
+      </c>
+      <c r="AG2" s="13">
+        <f>AF2-D2</f>
+        <v>1026.8</v>
+      </c>
+      <c r="AH2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI2" s="13">
+        <v>1493.67</v>
+      </c>
+      <c r="AJ2" s="6">
+        <v>400</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>186759</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38">
+      <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2714.1</v>
+      </c>
+      <c r="E3" s="6">
+        <f>F3-D3</f>
+        <v>123.29</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2837.39</v>
+      </c>
+      <c r="G3" s="6">
+        <f>H3-F3</f>
+        <v>95.8499999999999</v>
+      </c>
+      <c r="H3" s="6">
+        <v>2933.24</v>
+      </c>
+      <c r="I3" s="6">
+        <f>J3-H3</f>
+        <v>92.46</v>
+      </c>
+      <c r="J3" s="6">
+        <v>3025.7</v>
+      </c>
+      <c r="K3" s="6">
+        <f>L3-J3</f>
+        <v>90.4100000000003</v>
+      </c>
+      <c r="L3" s="6">
+        <v>3116.11</v>
+      </c>
+      <c r="M3" s="6">
+        <f>N3-L3</f>
+        <v>103.54</v>
+      </c>
+      <c r="N3" s="6">
+        <v>3219.65</v>
+      </c>
+      <c r="O3" s="6">
+        <f>P3-N3</f>
+        <v>75.6599999999999</v>
+      </c>
+      <c r="P3" s="6">
+        <v>3295.31</v>
+      </c>
+      <c r="Q3" s="6">
+        <f>R3-P3</f>
+        <v>88.98</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3384.29</v>
+      </c>
+      <c r="S3" s="6">
+        <f>T3-R3</f>
+        <v>102.46</v>
+      </c>
+      <c r="T3" s="6">
+        <v>3486.75</v>
+      </c>
+      <c r="U3" s="6">
+        <f>V3-T3</f>
+        <v>69.23</v>
+      </c>
+      <c r="V3" s="8">
+        <v>3555.98</v>
+      </c>
+      <c r="W3" s="6">
+        <f>X3-V3</f>
+        <v>133.46</v>
+      </c>
+      <c r="X3" s="8">
+        <v>3689.44</v>
+      </c>
+      <c r="Y3" s="6">
+        <f>Z3-X3</f>
+        <v>10.5999999999999</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>3700.04</v>
+      </c>
+      <c r="AA3" s="6">
+        <f>AB3-Z3</f>
+        <v>145.58</v>
+      </c>
+      <c r="AB3" s="6">
+        <v>3845.62</v>
+      </c>
+      <c r="AC3" s="6">
+        <f>AD3-AB3</f>
+        <v>64.1800000000003</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>3909.8</v>
+      </c>
+      <c r="AE3" s="13">
+        <f>AF3-AD3</f>
+        <v>98.8399999999997</v>
+      </c>
+      <c r="AF3" s="13">
+        <v>4008.64</v>
+      </c>
+      <c r="AG3" s="13">
+        <f>AF3-D3</f>
+        <v>1294.54</v>
+      </c>
+      <c r="AH3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI3" s="13">
+        <v>862.62</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>500</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>191519</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2533.85</v>
+      </c>
+      <c r="E4" s="1">
+        <f>F4-D4</f>
+        <v>50.0500000000002</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2583.9</v>
+      </c>
+      <c r="G4" s="1">
+        <f>H4-F4</f>
+        <v>85.7599999999998</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2669.66</v>
+      </c>
+      <c r="I4" s="1">
+        <f>J4-H4</f>
+        <v>81.79</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2751.45</v>
+      </c>
+      <c r="K4" s="1">
+        <f>L4-J4</f>
+        <v>83.1700000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2834.62</v>
+      </c>
+      <c r="M4" s="1">
+        <f>N4-L4</f>
+        <v>56.9900000000002</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2891.61</v>
+      </c>
+      <c r="O4" s="1">
+        <f>P4-N4</f>
+        <v>103.98</v>
+      </c>
+      <c r="P4" s="1">
+        <v>2995.59</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>R4-P4</f>
+        <v>68.8499999999999</v>
+      </c>
+      <c r="R4" s="1">
+        <v>3064.44</v>
+      </c>
+      <c r="S4" s="1">
+        <f>T4-R4</f>
+        <v>47.6100000000001</v>
+      </c>
+      <c r="T4" s="1">
+        <v>3112.05</v>
+      </c>
+      <c r="U4" s="1">
+        <f>V4-T4</f>
+        <v>38.1599999999999</v>
+      </c>
+      <c r="V4" s="9">
+        <v>3150.21</v>
+      </c>
+      <c r="W4" s="1">
+        <f>X4-V4</f>
+        <v>146.1</v>
+      </c>
+      <c r="X4" s="9">
+        <v>3296.31</v>
+      </c>
+      <c r="Y4" s="1">
+        <f>Z4-X4</f>
+        <v>31.9400000000001</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>3328.25</v>
+      </c>
+      <c r="AA4" s="1">
+        <f>AB4-Z4</f>
+        <v>79.8800000000001</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>3408.13</v>
+      </c>
+      <c r="AC4" s="1">
+        <f>AD4-AB4</f>
+        <v>68.9099999999999</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>3477.04</v>
+      </c>
+      <c r="AE4" s="14">
+        <f>AF4-AD4</f>
+        <v>143.74</v>
+      </c>
+      <c r="AF4" s="14">
+        <v>3620.78</v>
+      </c>
+      <c r="AG4" s="14">
+        <f>AF4-D4</f>
+        <v>1086.93</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="14">
+        <v>780.42</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>200</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>172501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2">
         <v>1754.54</v>
-      </c>
-      <c r="E2" s="2">
-        <f>F2-D2</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1807.91</v>
-      </c>
-      <c r="G2" s="2">
-        <f>H2-F2</f>
-        <v>90.24</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1898.15</v>
-      </c>
-      <c r="I2" s="2">
-        <f>J2-H2</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1988.53</v>
-      </c>
-      <c r="K2" s="2">
-        <f>L2-J2</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L2" s="2">
-        <v>2048.24</v>
-      </c>
-      <c r="M2" s="2">
-        <f>N2-L2</f>
-        <v>153.99</v>
-      </c>
-      <c r="N2" s="2">
-        <v>2202.23</v>
-      </c>
-      <c r="O2" s="2">
-        <f>P2-N2</f>
-        <v>64.21</v>
-      </c>
-      <c r="P2" s="2">
-        <v>2266.44</v>
-      </c>
-      <c r="Q2" s="2">
-        <f>R2-P2</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R2" s="2">
-        <v>2314</v>
-      </c>
-      <c r="S2" s="2">
-        <f>T2-R2</f>
-        <v>59.6500000000001</v>
-      </c>
-      <c r="T2" s="2">
-        <v>2373.65</v>
-      </c>
-      <c r="U2" s="2">
-        <f>V2-T2</f>
-        <v>70.6399999999999</v>
-      </c>
-      <c r="V2" s="8">
-        <v>2444.29</v>
-      </c>
-      <c r="W2" s="2">
-        <f>X2-V2</f>
-        <v>95.9299999999998</v>
-      </c>
-      <c r="X2" s="8">
-        <v>2540.22</v>
-      </c>
-      <c r="Y2" s="2">
-        <f>Z2-X2</f>
-        <v>90.3200000000002</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>2630.54</v>
-      </c>
-      <c r="AA2" s="2">
-        <f>AB2-Z2</f>
-        <v>69.7800000000002</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>2700.32</v>
-      </c>
-      <c r="AC2" s="2">
-        <f>AD2-AB2</f>
-        <v>57.52</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>2757.84</v>
-      </c>
-      <c r="AE2" s="2">
-        <f>AD2-D2</f>
-        <v>1003.3</v>
-      </c>
-      <c r="AF2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>468.18</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>300</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>132783</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2136.24</v>
-      </c>
-      <c r="E3" s="2">
-        <f>F3-D3</f>
-        <v>40.8200000000002</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2177.06</v>
-      </c>
-      <c r="G3" s="2">
-        <f>H3-F3</f>
-        <v>62.5999999999999</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2239.66</v>
-      </c>
-      <c r="I3" s="2">
-        <f>J3-H3</f>
-        <v>47.0700000000002</v>
-      </c>
-      <c r="J3" s="2">
-        <v>2286.73</v>
-      </c>
-      <c r="K3" s="2">
-        <f>L3-J3</f>
-        <v>25.52</v>
-      </c>
-      <c r="L3" s="2">
-        <v>2312.25</v>
-      </c>
-      <c r="M3" s="2">
-        <f>N3-L3</f>
-        <v>36.7800000000002</v>
-      </c>
-      <c r="N3" s="2">
-        <v>2349.03</v>
-      </c>
-      <c r="O3" s="2">
-        <f>P3-N3</f>
-        <v>-18.02</v>
-      </c>
-      <c r="P3" s="2">
-        <v>2331.01</v>
-      </c>
-      <c r="Q3" s="2">
-        <f>R3-P3</f>
-        <v>62.7599999999998</v>
-      </c>
-      <c r="R3" s="2">
-        <v>2393.77</v>
-      </c>
-      <c r="S3" s="2">
-        <f>T3-R3</f>
-        <v>55.5599999999999</v>
-      </c>
-      <c r="T3" s="2">
-        <v>2449.33</v>
-      </c>
-      <c r="U3" s="2">
-        <f>V3-T3</f>
-        <v>31.96</v>
-      </c>
-      <c r="V3" s="8">
-        <v>2481.29</v>
-      </c>
-      <c r="W3" s="2">
-        <f>X3-V3</f>
-        <v>109.47</v>
-      </c>
-      <c r="X3" s="8">
-        <v>2590.76</v>
-      </c>
-      <c r="Y3" s="2">
-        <f>Z3-X3</f>
-        <v>20.4299999999998</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>2611.19</v>
-      </c>
-      <c r="AA3" s="2">
-        <f>AB3-Z3</f>
-        <v>32.9899999999998</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>2644.18</v>
-      </c>
-      <c r="AC3" s="2">
-        <f>AD3-AB3</f>
-        <v>45.9000000000001</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>2690.08</v>
-      </c>
-      <c r="AE3" s="2">
-        <f>AD3-D3</f>
-        <v>553.84</v>
-      </c>
-      <c r="AF3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG3" s="2">
-        <v>885.76</v>
-      </c>
-      <c r="AH3" s="2">
-        <v>20</v>
-      </c>
-      <c r="AI3" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AJ3" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1726.42</v>
-      </c>
-      <c r="E4" s="2">
-        <f>F4-D4</f>
-        <v>56.28</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1782.7</v>
-      </c>
-      <c r="G4" s="2">
-        <f>H4-F4</f>
-        <v>70.9199999999998</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1853.62</v>
-      </c>
-      <c r="I4" s="2">
-        <f>J4-H4</f>
-        <v>49.5800000000002</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1903.2</v>
-      </c>
-      <c r="K4" s="2">
-        <f>L4-J4</f>
-        <v>40.4099999999999</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1943.61</v>
-      </c>
-      <c r="M4" s="2">
-        <f>N4-L4</f>
-        <v>30.01</v>
-      </c>
-      <c r="N4" s="2">
-        <v>1973.62</v>
-      </c>
-      <c r="O4" s="2">
-        <f>P4-N4</f>
-        <v>83.2800000000002</v>
-      </c>
-      <c r="P4" s="2">
-        <v>2056.9</v>
-      </c>
-      <c r="Q4" s="2">
-        <f>R4-P4</f>
-        <v>25.6399999999999</v>
-      </c>
-      <c r="R4" s="2">
-        <v>2082.54</v>
-      </c>
-      <c r="S4" s="2">
-        <f>T4-R4</f>
-        <v>66.46</v>
-      </c>
-      <c r="T4" s="2">
-        <v>2149</v>
-      </c>
-      <c r="U4" s="2">
-        <f>V4-T4</f>
-        <v>43.5599999999999</v>
-      </c>
-      <c r="V4" s="8">
-        <v>2192.56</v>
-      </c>
-      <c r="W4" s="2">
-        <f>X4-V4</f>
-        <v>46.3200000000002</v>
-      </c>
-      <c r="X4" s="8">
-        <v>2238.88</v>
-      </c>
-      <c r="Y4" s="2">
-        <f>Z4-X4</f>
-        <v>17.23</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>2256.11</v>
-      </c>
-      <c r="AA4" s="2">
-        <f>AB4-Z4</f>
-        <v>97.5799999999999</v>
-      </c>
-      <c r="AB4" s="2">
-        <v>2353.69</v>
-      </c>
-      <c r="AC4" s="2">
-        <f>AD4-AB4</f>
-        <v>58.8600000000001</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>2412.55</v>
-      </c>
-      <c r="AE4" s="2">
-        <f>AD4-D4</f>
-        <v>686.13</v>
-      </c>
-      <c r="AF4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>588.34</v>
-      </c>
-      <c r="AH4" s="2">
-        <v>50</v>
-      </c>
-      <c r="AI4" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>124763</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1425.22</v>
       </c>
       <c r="E5" s="2">
         <f>F5-D5</f>
-        <v>64.8599999999999</v>
+        <v>53.3700000000001</v>
       </c>
       <c r="F5" s="2">
-        <v>1490.08</v>
+        <v>1807.91</v>
       </c>
       <c r="G5" s="2">
         <f>H5-F5</f>
-        <v>46</v>
+        <v>90.24</v>
       </c>
       <c r="H5" s="2">
-        <v>1536.08</v>
+        <v>1898.15</v>
       </c>
       <c r="I5" s="2">
         <f>J5-H5</f>
-        <v>50.8500000000001</v>
+        <v>90.3799999999999</v>
       </c>
       <c r="J5" s="2">
-        <v>1586.93</v>
+        <v>1988.53</v>
       </c>
       <c r="K5" s="2">
         <f>L5-J5</f>
-        <v>86.5599999999999</v>
+        <v>59.7099999999998</v>
       </c>
       <c r="L5" s="2">
-        <v>1673.49</v>
+        <v>2048.24</v>
       </c>
       <c r="M5" s="2">
         <f>N5-L5</f>
-        <v>38.5599999999999</v>
+        <v>153.99</v>
       </c>
       <c r="N5" s="2">
-        <v>1712.05</v>
+        <v>2202.23</v>
       </c>
       <c r="O5" s="2">
         <f>P5-N5</f>
-        <v>57.0900000000001</v>
+        <v>64.21</v>
       </c>
       <c r="P5" s="2">
-        <v>1769.14</v>
+        <v>2266.44</v>
       </c>
       <c r="Q5" s="2">
         <f>R5-P5</f>
-        <v>50.8699999999999</v>
+        <v>47.5599999999999</v>
       </c>
       <c r="R5" s="2">
-        <v>1820.01</v>
+        <v>2314</v>
       </c>
       <c r="S5" s="2">
         <f>T5-R5</f>
-        <v>94.4300000000001</v>
+        <v>59.6500000000001</v>
       </c>
       <c r="T5" s="2">
-        <v>1914.44</v>
+        <v>2373.65</v>
       </c>
       <c r="U5" s="2">
         <f>V5-T5</f>
-        <v>31.51</v>
-      </c>
-      <c r="V5" s="8">
-        <v>1945.95</v>
+        <v>70.6399999999999</v>
+      </c>
+      <c r="V5" s="10">
+        <v>2444.29</v>
       </c>
       <c r="W5" s="2">
         <f>X5-V5</f>
-        <v>92.5899999999999</v>
-      </c>
-      <c r="X5" s="8">
-        <v>2038.54</v>
+        <v>95.9299999999998</v>
+      </c>
+      <c r="X5" s="10">
+        <v>2540.22</v>
       </c>
       <c r="Y5" s="2">
         <f>Z5-X5</f>
-        <v>48.1399999999999</v>
+        <v>90.3200000000002</v>
       </c>
       <c r="Z5" s="2">
-        <v>2086.68</v>
+        <v>2630.54</v>
       </c>
       <c r="AA5" s="2">
         <f>AB5-Z5</f>
-        <v>78.1300000000001</v>
+        <v>69.7800000000002</v>
       </c>
       <c r="AB5" s="2">
-        <v>2164.81</v>
+        <v>2700.32</v>
       </c>
       <c r="AC5" s="2">
         <f>AD5-AB5</f>
-        <v>39.8400000000001</v>
+        <v>57.52</v>
       </c>
       <c r="AD5" s="2">
-        <v>2204.65</v>
-      </c>
-      <c r="AE5" s="2">
-        <f>AD5-D5</f>
-        <v>779.43</v>
-      </c>
-      <c r="AF5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG5" s="2">
-        <v>533.09</v>
-      </c>
-      <c r="AH5" s="5">
+        <v>2757.84</v>
+      </c>
+      <c r="AE5" s="15">
+        <f>AF5-AD5</f>
+        <v>217.06</v>
+      </c>
+      <c r="AF5" s="15">
+        <v>2974.9</v>
+      </c>
+      <c r="AG5" s="15">
+        <f>AF5-D5</f>
+        <v>1220.36</v>
+      </c>
+      <c r="AH5" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI5" s="15">
+        <v>540.87</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>300</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="AL5" s="2">
+        <v>132783</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1966.62</v>
+      </c>
+      <c r="E6" s="2">
+        <f>F6-D6</f>
+        <v>49.0200000000002</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2015.64</v>
+      </c>
+      <c r="G6" s="2">
+        <f>H6-F6</f>
+        <v>34.1600000000001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2049.8</v>
+      </c>
+      <c r="I6" s="2">
+        <f>J6-H6</f>
+        <v>90.0999999999999</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2139.9</v>
+      </c>
+      <c r="K6" s="2">
+        <f>L6-J6</f>
+        <v>53.1700000000001</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2193.07</v>
+      </c>
+      <c r="M6" s="2">
+        <f>N6-L6</f>
+        <v>63.9099999999999</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2256.98</v>
+      </c>
+      <c r="O6" s="2">
+        <f>P6-N6</f>
+        <v>45.71</v>
+      </c>
+      <c r="P6" s="2">
+        <v>2302.69</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>R6-P6</f>
+        <v>37.2199999999998</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2339.91</v>
+      </c>
+      <c r="S6" s="2">
+        <f>T6-R6</f>
+        <v>47.3099999999999</v>
+      </c>
+      <c r="T6" s="2">
+        <v>2387.22</v>
+      </c>
+      <c r="U6" s="2">
+        <f>V6-T6</f>
+        <v>88.2600000000002</v>
+      </c>
+      <c r="V6" s="10">
+        <v>2475.48</v>
+      </c>
+      <c r="W6" s="2">
+        <f>X6-V6</f>
+        <v>67.5900000000001</v>
+      </c>
+      <c r="X6" s="10">
+        <v>2543.07</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>Z6-X6</f>
+        <v>22.73</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>2565.8</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>AB6-Z6</f>
+        <v>140.25</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>2706.05</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>AD6-AB6</f>
+        <v>57.1099999999997</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>2763.16</v>
+      </c>
+      <c r="AE6" s="15">
+        <f>AF6-AD6</f>
+        <v>70.9100000000003</v>
+      </c>
+      <c r="AF6" s="15">
+        <v>2834.07</v>
+      </c>
+      <c r="AG6" s="15">
+        <f>AF6-D6</f>
+        <v>867.45</v>
+      </c>
+      <c r="AH6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI6" s="15">
+        <v>1115.27</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>65</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>130589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2136.24</v>
+      </c>
+      <c r="E7" s="2">
+        <f>F7-D7</f>
+        <v>40.8200000000002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2177.06</v>
+      </c>
+      <c r="G7" s="2">
+        <f>H7-F7</f>
+        <v>62.5999999999999</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2239.66</v>
+      </c>
+      <c r="I7" s="2">
+        <f>J7-H7</f>
+        <v>47.0700000000002</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2286.73</v>
+      </c>
+      <c r="K7" s="2">
+        <f>L7-J7</f>
+        <v>25.52</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2312.25</v>
+      </c>
+      <c r="M7" s="2">
+        <f>N7-L7</f>
+        <v>36.7800000000002</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2349.03</v>
+      </c>
+      <c r="O7" s="2">
+        <f>P7-N7</f>
+        <v>-18.02</v>
+      </c>
+      <c r="P7" s="2">
+        <v>2331.01</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>R7-P7</f>
+        <v>62.7599999999998</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2393.77</v>
+      </c>
+      <c r="S7" s="2">
+        <f>T7-R7</f>
+        <v>55.5599999999999</v>
+      </c>
+      <c r="T7" s="2">
+        <v>2449.33</v>
+      </c>
+      <c r="U7" s="2">
+        <f>V7-T7</f>
+        <v>31.96</v>
+      </c>
+      <c r="V7" s="10">
+        <v>2481.29</v>
+      </c>
+      <c r="W7" s="2">
+        <f>X7-V7</f>
+        <v>109.47</v>
+      </c>
+      <c r="X7" s="10">
+        <v>2590.76</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>Z7-X7</f>
+        <v>20.4299999999998</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>2611.19</v>
+      </c>
+      <c r="AA7" s="2">
+        <f>AB7-Z7</f>
+        <v>32.9899999999998</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>2644.18</v>
+      </c>
+      <c r="AC7" s="2">
+        <f>AD7-AB7</f>
+        <v>45.9000000000001</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>2690.08</v>
+      </c>
+      <c r="AE7" s="15">
+        <f>AF7-AD7</f>
+        <v>62.79</v>
+      </c>
+      <c r="AF7" s="15">
+        <v>2752.87</v>
+      </c>
+      <c r="AG7" s="15">
+        <f>AF7-D7</f>
+        <v>616.63</v>
+      </c>
+      <c r="AH7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI7" s="15">
+        <v>945.47</v>
+      </c>
+      <c r="AJ7" s="2">
         <v>20</v>
       </c>
-      <c r="AI5" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AJ5" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="AK7" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E8" s="2">
+        <f>F8-D8</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G8" s="2">
+        <f>H8-F8</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I8" s="2">
+        <f>J8-H8</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K8" s="2">
+        <f>L8-J8</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M8" s="2">
+        <f>N8-L8</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O8" s="2">
+        <f>P8-N8</f>
+        <v>16.27</v>
+      </c>
+      <c r="P8" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>R8-P8</f>
+        <v>36.5</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S8" s="2">
+        <f>T8-R8</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U8" s="2">
+        <f>V8-T8</f>
+        <v>31.7599999999998</v>
+      </c>
+      <c r="V8" s="10">
+        <v>2467.14</v>
+      </c>
+      <c r="W8" s="2">
+        <f>X8-V8</f>
+        <v>53.75</v>
+      </c>
+      <c r="X8" s="10">
+        <v>2520.89</v>
+      </c>
+      <c r="Y8" s="2">
+        <f>Z8-X8</f>
+        <v>24.3299999999999</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>2545.22</v>
+      </c>
+      <c r="AA8" s="2">
+        <f>AB8-Z8</f>
+        <v>59.3900000000003</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>2604.61</v>
+      </c>
+      <c r="AC8" s="2">
+        <f>AD8-AB8</f>
+        <v>34.0499999999997</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>2638.66</v>
+      </c>
+      <c r="AE8" s="15">
+        <f>AF8-AD8</f>
+        <v>63.75</v>
+      </c>
+      <c r="AF8" s="15">
+        <v>2702.41</v>
+      </c>
+      <c r="AG8" s="15">
+        <f>AF8-D8</f>
+        <v>519.4</v>
+      </c>
+      <c r="AH8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI8" s="15">
+        <v>681.42</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1735.94</v>
+      </c>
+      <c r="E9" s="2">
+        <f>F9-D9</f>
+        <v>48.5999999999999</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1784.54</v>
+      </c>
+      <c r="G9" s="2">
+        <f>H9-F9</f>
+        <v>74.1600000000001</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1858.7</v>
+      </c>
+      <c r="I9" s="2">
+        <f>J9-H9</f>
+        <v>65.55</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1924.25</v>
+      </c>
+      <c r="K9" s="2">
+        <f>L9-J9</f>
+        <v>35.73</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1959.98</v>
+      </c>
+      <c r="M9" s="2">
+        <f>N9-L9</f>
+        <v>41.8799999999999</v>
+      </c>
+      <c r="N9" s="2">
+        <v>2001.86</v>
+      </c>
+      <c r="O9" s="2">
+        <f>P9-N9</f>
+        <v>74.6600000000001</v>
+      </c>
+      <c r="P9" s="2">
+        <v>2076.52</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>R9-P9</f>
+        <v>48.71</v>
+      </c>
+      <c r="R9" s="2">
+        <v>2125.23</v>
+      </c>
+      <c r="S9" s="2">
+        <f>T9-R9</f>
+        <v>57.4200000000001</v>
+      </c>
+      <c r="T9" s="2">
+        <v>2182.65</v>
+      </c>
+      <c r="U9" s="2">
+        <f>V9-T9</f>
+        <v>68.9400000000001</v>
+      </c>
+      <c r="V9" s="10">
+        <v>2251.59</v>
+      </c>
+      <c r="W9" s="2">
+        <f>X9-V9</f>
+        <v>72.0299999999997</v>
+      </c>
+      <c r="X9" s="10">
+        <v>2323.62</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>Z9-X9</f>
+        <v>23.6300000000001</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>2347.25</v>
+      </c>
+      <c r="AA9" s="2">
+        <f>AB9-Z9</f>
+        <v>64.5300000000002</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>2411.78</v>
+      </c>
+      <c r="AC9" s="2">
+        <f>AD9-AB9</f>
+        <v>30.2599999999998</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>2442.04</v>
+      </c>
+      <c r="AE9" s="15">
+        <f>AF9-AD9</f>
+        <v>104.94</v>
+      </c>
+      <c r="AF9" s="15">
+        <v>2546.98</v>
+      </c>
+      <c r="AG9" s="15">
+        <f>AF9-D9</f>
+        <v>811.04</v>
+      </c>
+      <c r="AH9" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI9" s="15">
+        <v>641.67</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="AL9" s="2">
+        <v>150192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1349.35</v>
-      </c>
-      <c r="E6" s="5">
-        <f>F6-D6</f>
-        <v>49.6200000000001</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1398.97</v>
-      </c>
-      <c r="G6" s="5">
-        <f>H6-F6</f>
-        <v>27.79</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1426.76</v>
-      </c>
-      <c r="I6" s="5">
-        <f>J6-H6</f>
-        <v>29.02</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1455.78</v>
-      </c>
-      <c r="K6" s="5">
-        <f>L6-J6</f>
-        <v>97.8800000000001</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1553.66</v>
-      </c>
-      <c r="M6" s="5">
-        <f>N6-L6</f>
-        <v>42.3599999999999</v>
-      </c>
-      <c r="N6" s="5">
-        <v>1596.02</v>
-      </c>
-      <c r="O6" s="5">
-        <f>P6-N6</f>
-        <v>54.22</v>
-      </c>
-      <c r="P6" s="5">
-        <v>1650.24</v>
-      </c>
-      <c r="Q6" s="5">
-        <f>R6-P6</f>
-        <v>35.5899999999999</v>
-      </c>
-      <c r="R6" s="5">
-        <v>1685.83</v>
-      </c>
-      <c r="S6" s="5">
-        <f>T6-R6</f>
-        <v>68.1300000000001</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1753.96</v>
-      </c>
-      <c r="U6" s="5">
-        <f>V6-T6</f>
-        <v>58.5599999999999</v>
-      </c>
-      <c r="V6" s="9">
-        <v>1812.52</v>
-      </c>
-      <c r="W6" s="5">
-        <f>X6-V6</f>
-        <v>67.21</v>
-      </c>
-      <c r="X6" s="9">
-        <v>1879.73</v>
-      </c>
-      <c r="Y6" s="5">
-        <f>Z6-X6</f>
-        <v>20.22</v>
-      </c>
-      <c r="Z6" s="5">
-        <v>1899.95</v>
-      </c>
-      <c r="AA6" s="5">
-        <f>AB6-Z6</f>
-        <v>35.0999999999999</v>
-      </c>
-      <c r="AB6" s="5">
-        <v>1935.05</v>
-      </c>
-      <c r="AC6" s="5">
-        <f>AD6-AB6</f>
-        <v>44.73</v>
-      </c>
-      <c r="AD6" s="5">
-        <v>1979.78</v>
-      </c>
-      <c r="AE6" s="5">
-        <f>AD6-D6</f>
-        <v>630.43</v>
-      </c>
-      <c r="AF6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG6" s="5">
-        <v>488.53</v>
-      </c>
-      <c r="AH6" s="5">
-        <v>20</v>
-      </c>
-      <c r="AI6" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AJ6" s="5">
-        <v>109106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="5">
-        <v>848.93</v>
-      </c>
-      <c r="E7" s="5">
-        <f>F7-D7</f>
-        <v>34.5600000000001</v>
-      </c>
-      <c r="F7" s="5">
-        <v>883.49</v>
-      </c>
-      <c r="G7" s="5">
-        <f>H7-F7</f>
-        <v>46.08</v>
-      </c>
-      <c r="H7" s="5">
-        <v>929.57</v>
-      </c>
-      <c r="I7" s="5">
-        <f>J7-H7</f>
-        <v>27.7399999999999</v>
-      </c>
-      <c r="J7" s="5">
-        <v>957.31</v>
-      </c>
-      <c r="K7" s="5">
-        <f>L7-J7</f>
-        <v>47.36</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1004.67</v>
-      </c>
-      <c r="M7" s="5">
-        <f>N7-L7</f>
-        <v>25.9399999999999</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1030.61</v>
-      </c>
-      <c r="O7" s="5">
-        <f>P7-N7</f>
-        <v>37.71</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1068.32</v>
-      </c>
-      <c r="Q7" s="5">
-        <f>R7-P7</f>
-        <v>18.3800000000001</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1086.7</v>
-      </c>
-      <c r="S7" s="5">
-        <f>T7-R7</f>
-        <v>21.04</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1107.74</v>
-      </c>
-      <c r="U7" s="5">
-        <f>V7-T7</f>
-        <v>32.7</v>
-      </c>
-      <c r="V7" s="9">
-        <v>1140.44</v>
-      </c>
-      <c r="W7" s="5">
-        <f>X7-V7</f>
-        <v>26.9299999999998</v>
-      </c>
-      <c r="X7" s="9">
-        <v>1167.37</v>
-      </c>
-      <c r="Y7" s="5">
-        <f>Z7-X7</f>
-        <v>37.0300000000002</v>
-      </c>
-      <c r="Z7" s="5">
-        <v>1204.4</v>
-      </c>
-      <c r="AA7" s="5">
-        <f>AB7-Z7</f>
-        <v>33.6199999999999</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>1238.02</v>
-      </c>
-      <c r="AC7" s="5">
-        <f>AD7-AB7</f>
-        <v>53.73</v>
-      </c>
-      <c r="AD7" s="5">
-        <v>1291.75</v>
-      </c>
-      <c r="AE7" s="5">
-        <f>AD7-D7</f>
-        <v>442.82</v>
-      </c>
-      <c r="AF7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG7" s="5">
-        <v>471.97</v>
-      </c>
-      <c r="AH7" s="5">
-        <v>30</v>
-      </c>
-      <c r="AI7" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AJ7" s="5">
-        <v>78989</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3">
-        <v>407.35</v>
-      </c>
-      <c r="E8" s="3">
-        <f>F8-D8</f>
-        <v>13.86</v>
-      </c>
-      <c r="F8" s="3">
-        <v>421.21</v>
-      </c>
-      <c r="G8" s="3">
-        <f>H8-F8</f>
-        <v>16.43</v>
-      </c>
-      <c r="H8" s="3">
-        <v>437.64</v>
-      </c>
-      <c r="I8" s="3">
-        <f>J8-H8</f>
-        <v>13.64</v>
-      </c>
-      <c r="J8" s="3">
-        <v>451.28</v>
-      </c>
-      <c r="K8" s="3">
-        <f>L8-J8</f>
-        <v>11.6</v>
-      </c>
-      <c r="L8" s="3">
-        <v>462.88</v>
-      </c>
-      <c r="M8" s="3">
-        <f>N8-L8</f>
-        <v>47.68</v>
-      </c>
-      <c r="N8" s="3">
-        <v>510.56</v>
-      </c>
-      <c r="O8" s="3">
-        <f>P8-N8</f>
-        <v>20.51</v>
-      </c>
-      <c r="P8" s="3">
-        <v>531.07</v>
-      </c>
-      <c r="Q8" s="3">
-        <f>R8-P8</f>
-        <v>18.6099999999999</v>
-      </c>
-      <c r="R8" s="3">
-        <v>549.68</v>
-      </c>
-      <c r="S8" s="3">
-        <f>T8-R8</f>
-        <v>11.9400000000001</v>
-      </c>
-      <c r="T8" s="3">
-        <v>561.62</v>
-      </c>
-      <c r="U8" s="3">
-        <f>V8-T8</f>
-        <v>16.23</v>
-      </c>
-      <c r="V8" s="10">
-        <v>577.85</v>
-      </c>
-      <c r="W8" s="3">
-        <f>X8-V8</f>
-        <v>15.28</v>
-      </c>
-      <c r="X8" s="10">
-        <v>593.13</v>
-      </c>
-      <c r="Y8" s="3">
-        <f>Z8-X8</f>
-        <v>33.2</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>626.33</v>
-      </c>
-      <c r="AA8" s="3">
-        <f>AB8-Z8</f>
-        <v>16.7199999999999</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>643.05</v>
-      </c>
-      <c r="AC8" s="3">
-        <f>AD8-AB8</f>
-        <v>11.9300000000001</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>654.98</v>
-      </c>
-      <c r="AE8" s="3">
-        <f>AD8-D8</f>
-        <v>247.63</v>
-      </c>
-      <c r="AF8" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>294.1</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>30</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>43895</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36">
-      <c r="A9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6">
-        <v>4105.48</v>
-      </c>
-      <c r="E9" s="6">
-        <f>F9-D9</f>
-        <v>181.21</v>
-      </c>
-      <c r="F9" s="6">
-        <v>4286.69</v>
-      </c>
-      <c r="G9" s="6">
-        <f>H9-F9</f>
-        <v>139.09</v>
-      </c>
-      <c r="H9" s="6">
-        <v>4425.78</v>
-      </c>
-      <c r="I9" s="6">
-        <f>J9-H9</f>
-        <v>54.8800000000001</v>
-      </c>
-      <c r="J9" s="6">
-        <v>4480.66</v>
-      </c>
-      <c r="K9" s="6">
-        <f>L9-J9</f>
-        <v>104.900000000001</v>
-      </c>
-      <c r="L9" s="6">
-        <v>4585.56</v>
-      </c>
-      <c r="M9" s="6">
-        <f>N9-L9</f>
-        <v>70.29</v>
-      </c>
-      <c r="N9" s="6">
-        <v>4655.85</v>
-      </c>
-      <c r="O9" s="6">
-        <f>P9-N9</f>
-        <v>49.1700000000001</v>
-      </c>
-      <c r="P9" s="6">
-        <v>4705.02</v>
-      </c>
-      <c r="Q9" s="6">
-        <f>R9-P9</f>
-        <v>38.2199999999993</v>
-      </c>
-      <c r="R9" s="6">
-        <v>4743.24</v>
-      </c>
-      <c r="S9" s="6">
-        <f>T9-R9</f>
-        <v>45.6199999999999</v>
-      </c>
-      <c r="T9" s="6">
-        <v>4788.86</v>
-      </c>
-      <c r="U9" s="6">
-        <f>V9-T9</f>
-        <v>27.5900000000001</v>
-      </c>
-      <c r="V9" s="11">
-        <v>4816.45</v>
-      </c>
-      <c r="W9" s="6">
-        <f>X9-V9</f>
-        <v>158.22</v>
-      </c>
-      <c r="X9" s="11">
-        <v>4974.67</v>
-      </c>
-      <c r="Y9" s="6">
-        <f>Z9-X9</f>
-        <v>32.8999999999996</v>
-      </c>
-      <c r="Z9" s="6">
-        <v>5007.57</v>
-      </c>
-      <c r="AA9" s="6">
-        <f>AB9-Z9</f>
-        <v>19.5700000000006</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>5027.14</v>
-      </c>
-      <c r="AC9" s="6">
-        <f>AD9-AB9</f>
-        <v>77.6899999999996</v>
-      </c>
-      <c r="AD9" s="6">
-        <v>5104.83</v>
-      </c>
-      <c r="AE9" s="6">
-        <f>AD9-D9</f>
-        <v>999.35</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG9" s="6">
-        <v>1361.06</v>
-      </c>
-      <c r="AH9" s="6">
-        <v>400</v>
-      </c>
-      <c r="AI9" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="AJ9" s="6">
-        <v>186759</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="2">
-        <v>1966.62</v>
+        <v>1726.42</v>
       </c>
       <c r="E10" s="2">
         <f>F10-D10</f>
-        <v>49.0200000000002</v>
+        <v>56.28</v>
       </c>
       <c r="F10" s="2">
-        <v>2015.64</v>
+        <v>1782.7</v>
       </c>
       <c r="G10" s="2">
         <f>H10-F10</f>
-        <v>34.1600000000001</v>
+        <v>70.9199999999998</v>
       </c>
       <c r="H10" s="2">
-        <v>2049.8</v>
+        <v>1853.62</v>
       </c>
       <c r="I10" s="2">
         <f>J10-H10</f>
-        <v>90.0999999999999</v>
+        <v>49.5800000000002</v>
       </c>
       <c r="J10" s="2">
-        <v>2139.9</v>
+        <v>1903.2</v>
       </c>
       <c r="K10" s="2">
         <f>L10-J10</f>
-        <v>53.1700000000001</v>
+        <v>40.4099999999999</v>
       </c>
       <c r="L10" s="2">
-        <v>2193.07</v>
+        <v>1943.61</v>
       </c>
       <c r="M10" s="2">
         <f>N10-L10</f>
-        <v>63.9099999999999</v>
+        <v>30.01</v>
       </c>
       <c r="N10" s="2">
-        <v>2256.98</v>
+        <v>1973.62</v>
       </c>
       <c r="O10" s="2">
         <f>P10-N10</f>
-        <v>45.71</v>
+        <v>83.2800000000002</v>
       </c>
       <c r="P10" s="2">
-        <v>2302.69</v>
+        <v>2056.9</v>
       </c>
       <c r="Q10" s="2">
         <f>R10-P10</f>
-        <v>37.2199999999998</v>
+        <v>25.6399999999999</v>
       </c>
       <c r="R10" s="2">
-        <v>2339.91</v>
+        <v>2082.54</v>
       </c>
       <c r="S10" s="2">
         <f>T10-R10</f>
-        <v>47.3099999999999</v>
+        <v>66.46</v>
       </c>
       <c r="T10" s="2">
-        <v>2387.22</v>
+        <v>2149</v>
       </c>
       <c r="U10" s="2">
         <f>V10-T10</f>
-        <v>88.2600000000002</v>
-      </c>
-      <c r="V10" s="8">
-        <v>2475.48</v>
+        <v>43.5599999999999</v>
+      </c>
+      <c r="V10" s="10">
+        <v>2192.56</v>
       </c>
       <c r="W10" s="2">
         <f>X10-V10</f>
-        <v>67.5900000000001</v>
-      </c>
-      <c r="X10" s="8">
-        <v>2543.07</v>
+        <v>46.3200000000002</v>
+      </c>
+      <c r="X10" s="10">
+        <v>2238.88</v>
       </c>
       <c r="Y10" s="2">
         <f>Z10-X10</f>
-        <v>22.73</v>
+        <v>17.23</v>
       </c>
       <c r="Z10" s="2">
-        <v>2565.8</v>
+        <v>2256.11</v>
       </c>
       <c r="AA10" s="2">
         <f>AB10-Z10</f>
-        <v>140.25</v>
+        <v>97.5799999999999</v>
       </c>
       <c r="AB10" s="2">
-        <v>2706.05</v>
+        <v>2353.69</v>
       </c>
       <c r="AC10" s="2">
         <f>AD10-AB10</f>
-        <v>57.1099999999997</v>
+        <v>58.8600000000001</v>
       </c>
       <c r="AD10" s="2">
-        <v>2763.16</v>
-      </c>
-      <c r="AE10" s="2">
-        <f>AD10-D10</f>
-        <v>796.54</v>
-      </c>
-      <c r="AF10" s="13" t="s">
+        <v>2412.55</v>
+      </c>
+      <c r="AE10" s="15">
+        <f>AF10-AD10</f>
+        <v>33.52</v>
+      </c>
+      <c r="AF10" s="15">
+        <v>2446.07</v>
+      </c>
+      <c r="AG10" s="15">
+        <f>AF10-D10</f>
+        <v>719.65</v>
+      </c>
+      <c r="AH10" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI10" s="15">
+        <v>603.17</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>124763</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AG10" s="2">
-        <v>1044.09</v>
-      </c>
-      <c r="AH10" s="2">
+      <c r="D11" s="2">
+        <v>1425.22</v>
+      </c>
+      <c r="E11" s="2">
+        <f>F11-D11</f>
+        <v>64.8599999999999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1490.08</v>
+      </c>
+      <c r="G11" s="2">
+        <f>H11-F11</f>
+        <v>46</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1536.08</v>
+      </c>
+      <c r="I11" s="2">
+        <f>J11-H11</f>
+        <v>50.8500000000001</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1586.93</v>
+      </c>
+      <c r="K11" s="2">
+        <f>L11-J11</f>
+        <v>86.5599999999999</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1673.49</v>
+      </c>
+      <c r="M11" s="2">
+        <f>N11-L11</f>
+        <v>38.5599999999999</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1712.05</v>
+      </c>
+      <c r="O11" s="2">
+        <f>P11-N11</f>
+        <v>57.0900000000001</v>
+      </c>
+      <c r="P11" s="2">
+        <v>1769.14</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>R11-P11</f>
+        <v>50.8699999999999</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1820.01</v>
+      </c>
+      <c r="S11" s="2">
+        <f>T11-R11</f>
+        <v>94.4300000000001</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1914.44</v>
+      </c>
+      <c r="U11" s="2">
+        <f>V11-T11</f>
+        <v>31.51</v>
+      </c>
+      <c r="V11" s="10">
+        <v>1945.95</v>
+      </c>
+      <c r="W11" s="2">
+        <f>X11-V11</f>
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X11" s="10">
+        <v>2038.54</v>
+      </c>
+      <c r="Y11" s="2">
+        <f>Z11-X11</f>
+        <v>48.1399999999999</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>2086.68</v>
+      </c>
+      <c r="AA11" s="2">
+        <f>AB11-Z11</f>
+        <v>78.1300000000001</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>2164.81</v>
+      </c>
+      <c r="AC11" s="2">
+        <f>AD11-AB11</f>
+        <v>39.8400000000001</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>2204.65</v>
+      </c>
+      <c r="AE11" s="15">
+        <f>AF11-AD11</f>
+        <v>79.98</v>
+      </c>
+      <c r="AF11" s="15">
+        <v>2284.63</v>
+      </c>
+      <c r="AG11" s="15">
+        <f>AF11-D11</f>
+        <v>859.41</v>
+      </c>
+      <c r="AH11" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI11" s="15">
+        <v>544.87</v>
+      </c>
+      <c r="AJ11" s="5">
+        <v>20</v>
+      </c>
+      <c r="AK11" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AL11" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1350.52</v>
+      </c>
+      <c r="E12" s="2">
+        <f>F12-D12</f>
+        <v>52.6800000000001</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1403.2</v>
+      </c>
+      <c r="G12" s="2">
+        <f>H12-F12</f>
+        <v>55.3199999999999</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1458.52</v>
+      </c>
+      <c r="I12" s="2">
+        <f>J12-H12</f>
+        <v>32.6800000000001</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1491.2</v>
+      </c>
+      <c r="K12" s="2">
+        <f>L12-J12</f>
+        <v>54.96</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1546.16</v>
+      </c>
+      <c r="M12" s="2">
+        <f>N12-L12</f>
+        <v>92.1299999999999</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1638.29</v>
+      </c>
+      <c r="O12" s="2">
+        <f>P12-N12</f>
+        <v>59.4400000000001</v>
+      </c>
+      <c r="P12" s="2">
+        <v>1697.73</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>R12-P12</f>
+        <v>71.3399999999999</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1769.07</v>
+      </c>
+      <c r="S12" s="2">
+        <f>T12-R12</f>
+        <v>62.9000000000001</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1831.97</v>
+      </c>
+      <c r="U12" s="2">
+        <f>V12-T12</f>
+        <v>66.5899999999999</v>
+      </c>
+      <c r="V12" s="10">
+        <v>1898.56</v>
+      </c>
+      <c r="W12" s="2">
+        <f>X12-V12</f>
+        <v>48.77</v>
+      </c>
+      <c r="X12" s="10">
+        <v>1947.33</v>
+      </c>
+      <c r="Y12" s="2">
+        <f>Z12-X12</f>
+        <v>59.47</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>2006.8</v>
+      </c>
+      <c r="AA12" s="2">
+        <f>AB12-Z12</f>
+        <v>82.3900000000001</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>2089.19</v>
+      </c>
+      <c r="AC12" s="2">
+        <f>AD12-AB12</f>
+        <v>98.8200000000002</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>2188.01</v>
+      </c>
+      <c r="AE12" s="15">
+        <f>AF12-AD12</f>
+        <v>16.2299999999996</v>
+      </c>
+      <c r="AF12" s="15">
+        <v>2204.24</v>
+      </c>
+      <c r="AG12" s="15">
+        <f>AF12-D12</f>
+        <v>853.72</v>
+      </c>
+      <c r="AH12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI12" s="15">
+        <v>678.17</v>
+      </c>
+      <c r="AJ12" s="5">
         <v>65</v>
       </c>
-      <c r="AI10" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AJ10" s="2">
-        <v>130589</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36">
-      <c r="A11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1060.77</v>
-      </c>
-      <c r="E11" s="5">
-        <f>F11-D11</f>
-        <v>63.24</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1124.01</v>
-      </c>
-      <c r="G11" s="5">
-        <f>H11-F11</f>
-        <v>19.6700000000001</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1143.68</v>
-      </c>
-      <c r="I11" s="5">
-        <f>J11-H11</f>
-        <v>47.76</v>
-      </c>
-      <c r="J11" s="5">
-        <v>1191.44</v>
-      </c>
-      <c r="K11" s="5">
-        <f>L11-J11</f>
-        <v>40.22</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1231.66</v>
-      </c>
-      <c r="M11" s="5">
-        <f>N11-L11</f>
-        <v>44.8</v>
-      </c>
-      <c r="N11" s="5">
-        <v>1276.46</v>
-      </c>
-      <c r="O11" s="5">
-        <f>P11-N11</f>
-        <v>28.03</v>
-      </c>
-      <c r="P11" s="5">
-        <v>1304.49</v>
-      </c>
-      <c r="Q11" s="5">
-        <f>R11-P11</f>
-        <v>31.78</v>
-      </c>
-      <c r="R11" s="5">
-        <v>1336.27</v>
-      </c>
-      <c r="S11" s="5">
-        <f>T11-R11</f>
-        <v>44.9000000000001</v>
-      </c>
-      <c r="T11" s="5">
-        <v>1381.17</v>
-      </c>
-      <c r="U11" s="5">
-        <f>V11-T11</f>
-        <v>53.1499999999999</v>
-      </c>
-      <c r="V11" s="9">
-        <v>1434.32</v>
-      </c>
-      <c r="W11" s="5">
-        <f>X11-V11</f>
-        <v>41.46</v>
-      </c>
-      <c r="X11" s="9">
-        <v>1475.78</v>
-      </c>
-      <c r="Y11" s="5">
-        <f>Z11-X11</f>
-        <v>38.55</v>
-      </c>
-      <c r="Z11" s="5">
-        <v>1514.33</v>
-      </c>
-      <c r="AA11" s="5">
-        <f>AB11-Z11</f>
-        <v>85.23</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>1599.56</v>
-      </c>
-      <c r="AC11" s="5">
-        <f>AD11-AB11</f>
-        <v>73.21</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>1672.77</v>
-      </c>
-      <c r="AE11" s="5">
-        <f>AD11-D11</f>
-        <v>612</v>
-      </c>
-      <c r="AF11" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG11" s="5">
-        <v>323.34</v>
-      </c>
-      <c r="AH11" s="5">
-        <v>10</v>
-      </c>
-      <c r="AI11" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="AJ11" s="5">
-        <v>71153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2714.1</v>
-      </c>
-      <c r="E12" s="1">
-        <f>F12-D12</f>
-        <v>123.29</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2837.39</v>
-      </c>
-      <c r="G12" s="1">
-        <f>H12-F12</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2933.24</v>
-      </c>
-      <c r="I12" s="1">
-        <f>J12-H12</f>
-        <v>92.46</v>
-      </c>
-      <c r="J12" s="1">
-        <v>3025.7</v>
-      </c>
-      <c r="K12" s="1">
-        <f>L12-J12</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L12" s="1">
-        <v>3116.11</v>
-      </c>
-      <c r="M12" s="1">
-        <f>N12-L12</f>
-        <v>103.54</v>
-      </c>
-      <c r="N12" s="1">
-        <v>3219.65</v>
-      </c>
-      <c r="O12" s="1">
-        <f>P12-N12</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P12" s="1">
-        <v>3295.31</v>
-      </c>
-      <c r="Q12" s="1">
-        <f>R12-P12</f>
-        <v>88.98</v>
-      </c>
-      <c r="R12" s="1">
-        <v>3384.29</v>
-      </c>
-      <c r="S12" s="1">
-        <f>T12-R12</f>
-        <v>102.46</v>
-      </c>
-      <c r="T12" s="1">
-        <v>3486.75</v>
-      </c>
-      <c r="U12" s="1">
-        <f>V12-T12</f>
-        <v>69.23</v>
-      </c>
-      <c r="V12" s="12">
-        <v>3555.98</v>
-      </c>
-      <c r="W12" s="1">
-        <f>X12-V12</f>
-        <v>133.46</v>
-      </c>
-      <c r="X12" s="12">
-        <v>3689.44</v>
-      </c>
-      <c r="Y12" s="1">
-        <f>Z12-X12</f>
-        <v>10.5999999999999</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>3700.04</v>
-      </c>
-      <c r="AA12" s="1">
-        <f>AB12-Z12</f>
-        <v>145.58</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>3845.62</v>
-      </c>
-      <c r="AC12" s="1">
-        <f>AD12-AB12</f>
-        <v>64.1800000000003</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>3909.8</v>
-      </c>
-      <c r="AE12" s="1">
-        <f>AD12-D12</f>
-        <v>1195.7</v>
-      </c>
-      <c r="AF12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>871.5</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>500</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>191519</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36">
+      <c r="AK12" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AL12" s="5">
+        <v>127603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2">
-        <v>2183.01</v>
+        <v>1446.65</v>
       </c>
       <c r="E13" s="2">
         <f>F13-D13</f>
-        <v>24.1199999999999</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F13" s="2">
-        <v>2207.13</v>
+        <v>1474.83</v>
       </c>
       <c r="G13" s="2">
         <f>H13-F13</f>
-        <v>22.8599999999997</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H13" s="2">
-        <v>2229.99</v>
+        <v>1538.65</v>
       </c>
       <c r="I13" s="2">
         <f>J13-H13</f>
-        <v>11.7800000000002</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J13" s="2">
-        <v>2241.77</v>
+        <v>1561.57</v>
       </c>
       <c r="K13" s="2">
         <f>L13-J13</f>
-        <v>13.0100000000002</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L13" s="2">
-        <v>2254.78</v>
+        <v>1632.43</v>
       </c>
       <c r="M13" s="2">
         <f>N13-L13</f>
-        <v>62.6399999999999</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N13" s="2">
-        <v>2317.42</v>
+        <v>1669.84</v>
       </c>
       <c r="O13" s="2">
         <f>P13-N13</f>
-        <v>16.27</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P13" s="2">
-        <v>2333.69</v>
+        <v>1702.67</v>
       </c>
       <c r="Q13" s="2">
         <f>R13-P13</f>
-        <v>36.5</v>
+        <v>51.9499999999998</v>
       </c>
       <c r="R13" s="2">
-        <v>2370.19</v>
+        <v>1754.62</v>
       </c>
       <c r="S13" s="2">
         <f>T13-R13</f>
-        <v>65.1900000000001</v>
+        <v>40.1200000000001</v>
       </c>
       <c r="T13" s="2">
-        <v>2435.38</v>
+        <v>1794.74</v>
       </c>
       <c r="U13" s="2">
         <f>V13-T13</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V13" s="8">
-        <v>2467.14</v>
+        <v>77.5</v>
+      </c>
+      <c r="V13" s="10">
+        <v>1872.24</v>
       </c>
       <c r="W13" s="2">
         <f>X13-V13</f>
-        <v>53.75</v>
-      </c>
-      <c r="X13" s="8">
-        <v>2520.89</v>
+        <v>79.5899999999999</v>
+      </c>
+      <c r="X13" s="10">
+        <v>1951.83</v>
       </c>
       <c r="Y13" s="2">
         <f>Z13-X13</f>
-        <v>24.3299999999999</v>
+        <v>9.01999999999998</v>
       </c>
       <c r="Z13" s="2">
-        <v>2545.22</v>
+        <v>1960.85</v>
       </c>
       <c r="AA13" s="2">
         <f>AB13-Z13</f>
-        <v>59.3900000000003</v>
+        <v>74</v>
       </c>
       <c r="AB13" s="2">
-        <v>2604.61</v>
+        <v>2034.85</v>
       </c>
       <c r="AC13" s="2">
         <f>AD13-AB13</f>
-        <v>34.0499999999997</v>
+        <v>31.8000000000002</v>
       </c>
       <c r="AD13" s="2">
-        <v>2638.66</v>
-      </c>
-      <c r="AE13" s="2">
-        <f>AD13-D13</f>
-        <v>455.65</v>
-      </c>
-      <c r="AF13" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG13" s="2">
-        <v>642.41</v>
-      </c>
-      <c r="AH13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36">
+        <v>2066.65</v>
+      </c>
+      <c r="AE13" s="15">
+        <f>AF13-AD13</f>
+        <v>107.43</v>
+      </c>
+      <c r="AF13" s="15">
+        <v>2174.08</v>
+      </c>
+      <c r="AG13" s="15">
+        <f>AF13-D13</f>
+        <v>727.43</v>
+      </c>
+      <c r="AH13" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI13" s="15">
+        <v>834.42</v>
+      </c>
+      <c r="AJ13" s="5">
+        <v>65</v>
+      </c>
+      <c r="AK13" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AL13" s="5">
+        <v>109333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
-        <v>1350.52</v>
+        <v>1576.18</v>
       </c>
       <c r="E14" s="2">
         <f>F14-D14</f>
-        <v>52.6800000000001</v>
+        <v>38.8399999999999</v>
       </c>
       <c r="F14" s="2">
-        <v>1403.2</v>
+        <v>1615.02</v>
       </c>
       <c r="G14" s="2">
         <f>H14-F14</f>
-        <v>55.3199999999999</v>
+        <v>35.5999999999999</v>
       </c>
       <c r="H14" s="2">
-        <v>1458.52</v>
+        <v>1650.62</v>
       </c>
       <c r="I14" s="2">
         <f>J14-H14</f>
-        <v>32.6800000000001</v>
+        <v>37.47</v>
       </c>
       <c r="J14" s="2">
-        <v>1491.2</v>
+        <v>1688.09</v>
       </c>
       <c r="K14" s="2">
         <f>L14-J14</f>
-        <v>54.96</v>
+        <v>21.49</v>
       </c>
       <c r="L14" s="2">
-        <v>1546.16</v>
+        <v>1709.58</v>
       </c>
       <c r="M14" s="2">
         <f>N14-L14</f>
-        <v>92.1299999999999</v>
+        <v>24.53</v>
       </c>
       <c r="N14" s="2">
-        <v>1638.29</v>
+        <v>1734.11</v>
       </c>
       <c r="O14" s="2">
         <f>P14-N14</f>
-        <v>59.4400000000001</v>
+        <v>19.5300000000002</v>
       </c>
       <c r="P14" s="2">
-        <v>1697.73</v>
+        <v>1753.64</v>
       </c>
       <c r="Q14" s="2">
         <f>R14-P14</f>
-        <v>71.3399999999999</v>
+        <v>65.1099999999999</v>
       </c>
       <c r="R14" s="2">
-        <v>1769.07</v>
+        <v>1818.75</v>
       </c>
       <c r="S14" s="2">
         <f>T14-R14</f>
-        <v>62.9000000000001</v>
+        <v>34.3699999999999</v>
       </c>
       <c r="T14" s="2">
-        <v>1831.97</v>
+        <v>1853.12</v>
       </c>
       <c r="U14" s="2">
         <f>V14-T14</f>
-        <v>66.5899999999999</v>
-      </c>
-      <c r="V14" s="8">
-        <v>1898.56</v>
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V14" s="10">
+        <v>1893.96</v>
       </c>
       <c r="W14" s="2">
         <f>X14-V14</f>
-        <v>48.77</v>
-      </c>
-      <c r="X14" s="8">
-        <v>1947.33</v>
+        <v>40.96</v>
+      </c>
+      <c r="X14" s="10">
+        <v>1934.92</v>
       </c>
       <c r="Y14" s="2">
         <f>Z14-X14</f>
-        <v>59.47</v>
+        <v>59.05</v>
       </c>
       <c r="Z14" s="2">
-        <v>2006.8</v>
+        <v>1993.97</v>
       </c>
       <c r="AA14" s="2">
         <f>AB14-Z14</f>
-        <v>82.3900000000001</v>
+        <v>58.4799999999998</v>
       </c>
       <c r="AB14" s="2">
-        <v>2089.19</v>
+        <v>2052.45</v>
       </c>
       <c r="AC14" s="2">
         <f>AD14-AB14</f>
-        <v>98.8200000000002</v>
+        <v>26.7400000000002</v>
       </c>
       <c r="AD14" s="2">
-        <v>2188.01</v>
-      </c>
-      <c r="AE14" s="2">
-        <f>AD14-D14</f>
-        <v>837.49</v>
-      </c>
-      <c r="AF14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG14" s="2">
-        <v>679.12</v>
-      </c>
-      <c r="AH14" s="5">
-        <v>65</v>
-      </c>
-      <c r="AI14" s="5">
-        <v>1.4</v>
+        <v>2079.19</v>
+      </c>
+      <c r="AE14" s="15">
+        <f>AF14-AD14</f>
+        <v>34.79</v>
+      </c>
+      <c r="AF14" s="15">
+        <v>2113.98</v>
+      </c>
+      <c r="AG14" s="15">
+        <f>AF14-D14</f>
+        <v>537.8</v>
+      </c>
+      <c r="AH14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI14" s="15">
+        <v>528.52</v>
       </c>
       <c r="AJ14" s="5">
-        <v>127603</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2">
-        <v>1576.18</v>
+        <v>1349.35</v>
       </c>
       <c r="E15" s="2">
         <f>F15-D15</f>
-        <v>38.8399999999999</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F15" s="2">
-        <v>1615.02</v>
+        <v>1398.97</v>
       </c>
       <c r="G15" s="2">
         <f>H15-F15</f>
-        <v>35.5999999999999</v>
+        <v>27.79</v>
       </c>
       <c r="H15" s="2">
-        <v>1650.62</v>
+        <v>1426.76</v>
       </c>
       <c r="I15" s="2">
         <f>J15-H15</f>
-        <v>37.47</v>
+        <v>29.02</v>
       </c>
       <c r="J15" s="2">
-        <v>1688.09</v>
+        <v>1455.78</v>
       </c>
       <c r="K15" s="2">
         <f>L15-J15</f>
-        <v>21.49</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L15" s="2">
-        <v>1709.58</v>
+        <v>1553.66</v>
       </c>
       <c r="M15" s="2">
         <f>N15-L15</f>
-        <v>24.53</v>
+        <v>42.3599999999999</v>
       </c>
       <c r="N15" s="2">
-        <v>1734.11</v>
+        <v>1596.02</v>
       </c>
       <c r="O15" s="2">
         <f>P15-N15</f>
-        <v>19.5300000000002</v>
+        <v>54.22</v>
       </c>
       <c r="P15" s="2">
-        <v>1753.64</v>
+        <v>1650.24</v>
       </c>
       <c r="Q15" s="2">
         <f>R15-P15</f>
-        <v>65.1099999999999</v>
+        <v>35.5899999999999</v>
       </c>
       <c r="R15" s="2">
-        <v>1818.75</v>
+        <v>1685.83</v>
       </c>
       <c r="S15" s="2">
         <f>T15-R15</f>
-        <v>34.3699999999999</v>
+        <v>68.1300000000001</v>
       </c>
       <c r="T15" s="2">
-        <v>1853.12</v>
+        <v>1753.96</v>
       </c>
       <c r="U15" s="2">
         <f>V15-T15</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V15" s="8">
-        <v>1893.96</v>
+        <v>58.5599999999999</v>
+      </c>
+      <c r="V15" s="10">
+        <v>1812.52</v>
       </c>
       <c r="W15" s="2">
         <f>X15-V15</f>
-        <v>40.96</v>
-      </c>
-      <c r="X15" s="8">
-        <v>1934.92</v>
+        <v>67.21</v>
+      </c>
+      <c r="X15" s="10">
+        <v>1879.73</v>
       </c>
       <c r="Y15" s="2">
         <f>Z15-X15</f>
-        <v>59.05</v>
+        <v>20.22</v>
       </c>
       <c r="Z15" s="2">
-        <v>1993.97</v>
+        <v>1899.95</v>
       </c>
       <c r="AA15" s="2">
         <f>AB15-Z15</f>
-        <v>58.4799999999998</v>
+        <v>35.0999999999999</v>
       </c>
       <c r="AB15" s="2">
-        <v>2052.45</v>
+        <v>1935.05</v>
       </c>
       <c r="AC15" s="2">
         <f>AD15-AB15</f>
-        <v>26.7400000000002</v>
+        <v>44.73</v>
       </c>
       <c r="AD15" s="2">
-        <v>2079.19</v>
-      </c>
-      <c r="AE15" s="2">
-        <f>AD15-D15</f>
-        <v>503.01</v>
-      </c>
-      <c r="AF15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG15" s="2">
-        <v>509.96</v>
-      </c>
-      <c r="AH15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="5">
-        <v>0</v>
+        <v>1979.78</v>
+      </c>
+      <c r="AE15" s="15">
+        <f>AF15-AD15</f>
+        <v>31.1700000000001</v>
+      </c>
+      <c r="AF15" s="15">
+        <v>2010.95</v>
+      </c>
+      <c r="AG15" s="15">
+        <f>AF15-D15</f>
+        <v>661.6</v>
+      </c>
+      <c r="AH15" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI15" s="15">
+        <v>498.5</v>
       </c>
       <c r="AJ15" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36">
+        <v>20</v>
+      </c>
+      <c r="AK15" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AL15" s="5">
+        <v>109106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D16" s="5">
         <v>1156.57</v>
@@ -3336,14 +3452,14 @@
         <f>V16-T16</f>
         <v>58.6500000000001</v>
       </c>
-      <c r="V16" s="9">
+      <c r="V16" s="11">
         <v>1555.94</v>
       </c>
       <c r="W16" s="5">
         <f>X16-V16</f>
         <v>70.3099999999999</v>
       </c>
-      <c r="X16" s="9">
+      <c r="X16" s="11">
         <v>1626.25</v>
       </c>
       <c r="Y16" s="5">
@@ -3367,655 +3483,697 @@
       <c r="AD16" s="5">
         <v>1748.94</v>
       </c>
-      <c r="AE16" s="5">
-        <f>AD16-D16</f>
-        <v>592.37</v>
-      </c>
-      <c r="AF16" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG16" s="5">
-        <v>470.82</v>
-      </c>
-      <c r="AH16" s="5">
+      <c r="AE16" s="16">
+        <f>AF16-AD16</f>
+        <v>52.0999999999999</v>
+      </c>
+      <c r="AF16" s="16">
+        <v>1801.04</v>
+      </c>
+      <c r="AG16" s="16">
+        <f>AF16-D16</f>
+        <v>644.47</v>
+      </c>
+      <c r="AH16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI16" s="16">
+        <v>484.52</v>
+      </c>
+      <c r="AJ16" s="5">
         <v>25</v>
       </c>
-      <c r="AI16" s="5">
+      <c r="AK16" s="5">
         <v>3</v>
       </c>
-      <c r="AJ16" s="5">
+      <c r="AL16" s="5">
         <v>100457</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:38">
       <c r="A17" s="5" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5">
-        <v>907.94</v>
+        <v>1060.77</v>
       </c>
       <c r="E17" s="5">
         <f>F17-D17</f>
-        <v>64.0799999999999</v>
+        <v>63.24</v>
       </c>
       <c r="F17" s="5">
-        <v>972.02</v>
+        <v>1124.01</v>
       </c>
       <c r="G17" s="5">
         <f>H17-F17</f>
-        <v>36.26</v>
+        <v>19.6700000000001</v>
       </c>
       <c r="H17" s="5">
-        <v>1008.28</v>
+        <v>1143.68</v>
       </c>
       <c r="I17" s="5">
         <f>J17-H17</f>
-        <v>28.8</v>
+        <v>47.76</v>
       </c>
       <c r="J17" s="5">
-        <v>1037.08</v>
+        <v>1191.44</v>
       </c>
       <c r="K17" s="5">
         <f>L17-J17</f>
-        <v>40.1000000000001</v>
+        <v>40.22</v>
       </c>
       <c r="L17" s="5">
-        <v>1077.18</v>
+        <v>1231.66</v>
       </c>
       <c r="M17" s="5">
         <f>N17-L17</f>
-        <v>26.03</v>
+        <v>44.8</v>
       </c>
       <c r="N17" s="5">
-        <v>1103.21</v>
+        <v>1276.46</v>
       </c>
       <c r="O17" s="5">
         <f>P17-N17</f>
-        <v>28.3499999999999</v>
+        <v>28.03</v>
       </c>
       <c r="P17" s="5">
-        <v>1131.56</v>
+        <v>1304.49</v>
       </c>
       <c r="Q17" s="5">
         <f>R17-P17</f>
-        <v>50.1900000000001</v>
+        <v>31.78</v>
       </c>
       <c r="R17" s="5">
-        <v>1181.75</v>
+        <v>1336.27</v>
       </c>
       <c r="S17" s="5">
         <f>T17-R17</f>
-        <v>26.8699999999999</v>
+        <v>44.9000000000001</v>
       </c>
       <c r="T17" s="5">
-        <v>1208.62</v>
+        <v>1381.17</v>
       </c>
       <c r="U17" s="5">
         <f>V17-T17</f>
-        <v>58.3000000000002</v>
-      </c>
-      <c r="V17" s="9">
-        <v>1266.92</v>
+        <v>53.1499999999999</v>
+      </c>
+      <c r="V17" s="11">
+        <v>1434.32</v>
       </c>
       <c r="W17" s="5">
         <f>X17-V17</f>
-        <v>41.0599999999999</v>
-      </c>
-      <c r="X17" s="9">
-        <v>1307.98</v>
+        <v>41.46</v>
+      </c>
+      <c r="X17" s="11">
+        <v>1475.78</v>
       </c>
       <c r="Y17" s="5">
         <f>Z17-X17</f>
-        <v>31.49</v>
+        <v>38.55</v>
       </c>
       <c r="Z17" s="5">
-        <v>1339.47</v>
+        <v>1514.33</v>
       </c>
       <c r="AA17" s="5">
         <f>AB17-Z17</f>
-        <v>50.5899999999999</v>
+        <v>85.23</v>
       </c>
       <c r="AB17" s="5">
-        <v>1390.06</v>
+        <v>1599.56</v>
       </c>
       <c r="AC17" s="5">
         <f>AD17-AB17</f>
+        <v>73.21</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>1672.77</v>
+      </c>
+      <c r="AE17" s="16">
+        <f>AF17-AD17</f>
+        <v>43.3600000000001</v>
+      </c>
+      <c r="AF17" s="16">
+        <v>1716.13</v>
+      </c>
+      <c r="AG17" s="16">
+        <f>AF17-D17</f>
+        <v>655.36</v>
+      </c>
+      <c r="AH17" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI17" s="16">
+        <v>344.56</v>
+      </c>
+      <c r="AJ17" s="5">
+        <v>10</v>
+      </c>
+      <c r="AK17" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AL17" s="5">
+        <v>71153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5">
+        <v>953.78</v>
+      </c>
+      <c r="E18" s="5">
+        <f>F18-D18</f>
+        <v>28.97</v>
+      </c>
+      <c r="F18" s="5">
+        <v>982.75</v>
+      </c>
+      <c r="G18" s="5">
+        <f>H18-F18</f>
+        <v>83.9300000000001</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1066.68</v>
+      </c>
+      <c r="I18" s="5">
+        <f>J18-H18</f>
+        <v>42.8399999999999</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1109.52</v>
+      </c>
+      <c r="K18" s="5">
+        <f>L18-J18</f>
+        <v>36.46</v>
+      </c>
+      <c r="L18" s="5">
+        <v>1145.98</v>
+      </c>
+      <c r="M18" s="5">
+        <f>N18-L18</f>
+        <v>37.49</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1183.47</v>
+      </c>
+      <c r="O18" s="5">
+        <f>P18-N18</f>
+        <v>33.3699999999999</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1216.84</v>
+      </c>
+      <c r="Q18" s="5">
+        <f>R18-P18</f>
+        <v>24.8900000000001</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1241.73</v>
+      </c>
+      <c r="S18" s="5">
+        <f>T18-R18</f>
+        <v>42.3099999999999</v>
+      </c>
+      <c r="T18" s="5">
+        <v>1284.04</v>
+      </c>
+      <c r="U18" s="5">
+        <f>V18-T18</f>
+        <v>44.8400000000001</v>
+      </c>
+      <c r="V18" s="11">
+        <v>1328.88</v>
+      </c>
+      <c r="W18" s="5">
+        <f>X18-V18</f>
+        <v>45.9499999999998</v>
+      </c>
+      <c r="X18" s="11">
+        <v>1374.83</v>
+      </c>
+      <c r="Y18" s="5">
+        <f>Z18-X18</f>
+        <v>16.4200000000001</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>1391.25</v>
+      </c>
+      <c r="AA18" s="5">
+        <f>AB18-Z18</f>
+        <v>22.0699999999999</v>
+      </c>
+      <c r="AB18" s="5">
+        <v>1413.32</v>
+      </c>
+      <c r="AC18" s="5">
+        <f>AD18-AB18</f>
+        <v>73.72</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>1487.04</v>
+      </c>
+      <c r="AE18" s="16">
+        <f>AF18-AD18</f>
+        <v>48.22</v>
+      </c>
+      <c r="AF18" s="16">
+        <v>1535.26</v>
+      </c>
+      <c r="AG18" s="16">
+        <f>AF18-D18</f>
+        <v>581.48</v>
+      </c>
+      <c r="AH18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI18" s="16">
+        <v>591.02</v>
+      </c>
+      <c r="AJ18" s="5">
+        <v>30</v>
+      </c>
+      <c r="AK18" s="5">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="5">
+        <v>105419</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5">
+        <v>907.94</v>
+      </c>
+      <c r="E19" s="5">
+        <f>F19-D19</f>
+        <v>64.0799999999999</v>
+      </c>
+      <c r="F19" s="5">
+        <v>972.02</v>
+      </c>
+      <c r="G19" s="5">
+        <f>H19-F19</f>
+        <v>36.26</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1008.28</v>
+      </c>
+      <c r="I19" s="5">
+        <f>J19-H19</f>
+        <v>28.8</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1037.08</v>
+      </c>
+      <c r="K19" s="5">
+        <f>L19-J19</f>
+        <v>40.1000000000001</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1077.18</v>
+      </c>
+      <c r="M19" s="5">
+        <f>N19-L19</f>
+        <v>26.03</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1103.21</v>
+      </c>
+      <c r="O19" s="5">
+        <f>P19-N19</f>
+        <v>28.3499999999999</v>
+      </c>
+      <c r="P19" s="5">
+        <v>1131.56</v>
+      </c>
+      <c r="Q19" s="5">
+        <f>R19-P19</f>
+        <v>50.1900000000001</v>
+      </c>
+      <c r="R19" s="5">
+        <v>1181.75</v>
+      </c>
+      <c r="S19" s="5">
+        <f>T19-R19</f>
+        <v>26.8699999999999</v>
+      </c>
+      <c r="T19" s="5">
+        <v>1208.62</v>
+      </c>
+      <c r="U19" s="5">
+        <f>V19-T19</f>
+        <v>58.3000000000002</v>
+      </c>
+      <c r="V19" s="11">
+        <v>1266.92</v>
+      </c>
+      <c r="W19" s="5">
+        <f>X19-V19</f>
+        <v>41.0599999999999</v>
+      </c>
+      <c r="X19" s="11">
+        <v>1307.98</v>
+      </c>
+      <c r="Y19" s="5">
+        <f>Z19-X19</f>
+        <v>31.49</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>1339.47</v>
+      </c>
+      <c r="AA19" s="5">
+        <f>AB19-Z19</f>
+        <v>50.5899999999999</v>
+      </c>
+      <c r="AB19" s="5">
+        <v>1390.06</v>
+      </c>
+      <c r="AC19" s="5">
+        <f>AD19-AB19</f>
         <v>35.8099999999999</v>
       </c>
-      <c r="AD17" s="5">
+      <c r="AD19" s="5">
         <v>1425.87</v>
       </c>
-      <c r="AE17" s="5">
-        <f>AD17-D17</f>
-        <v>517.93</v>
-      </c>
-      <c r="AF17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG17" s="5">
-        <v>489.27</v>
-      </c>
-      <c r="AH17" s="5">
+      <c r="AE19" s="16">
+        <f>AF19-AD19</f>
+        <v>62.6300000000001</v>
+      </c>
+      <c r="AF19" s="16">
+        <v>1488.5</v>
+      </c>
+      <c r="AG19" s="16">
+        <f>AF19-D19</f>
+        <v>580.56</v>
+      </c>
+      <c r="AH19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI19" s="16">
+        <v>514.72</v>
+      </c>
+      <c r="AJ19" s="5">
         <v>35</v>
       </c>
-      <c r="AI17" s="5">
+      <c r="AK19" s="5">
         <v>8.2</v>
       </c>
-      <c r="AJ17" s="5">
+      <c r="AL19" s="5">
         <v>65285</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
-      <c r="A18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="20" spans="1:38">
+      <c r="A20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="3">
-        <v>363.88</v>
-      </c>
-      <c r="E18" s="3">
-        <f>F18-D18</f>
-        <v>14.21</v>
-      </c>
-      <c r="F18" s="3">
-        <v>378.09</v>
-      </c>
-      <c r="G18" s="3">
-        <f>H18-F18</f>
-        <v>11.22</v>
-      </c>
-      <c r="H18" s="3">
-        <v>389.31</v>
-      </c>
-      <c r="I18" s="3">
-        <f>J18-H18</f>
-        <v>13.62</v>
-      </c>
-      <c r="J18" s="3">
-        <v>402.93</v>
-      </c>
-      <c r="K18" s="3">
-        <f>L18-J18</f>
-        <v>11.13</v>
-      </c>
-      <c r="L18" s="3">
-        <v>414.06</v>
-      </c>
-      <c r="M18" s="3">
-        <f>N18-L18</f>
-        <v>17.39</v>
-      </c>
-      <c r="N18" s="3">
-        <v>431.45</v>
-      </c>
-      <c r="O18" s="3">
-        <f>P18-N18</f>
-        <v>6.32999999999998</v>
-      </c>
-      <c r="P18" s="3">
-        <v>437.78</v>
-      </c>
-      <c r="Q18" s="3">
-        <f>R18-P18</f>
-        <v>53.01</v>
-      </c>
-      <c r="R18" s="3">
-        <v>490.79</v>
-      </c>
-      <c r="S18" s="3">
-        <f>T18-R18</f>
-        <v>11.82</v>
-      </c>
-      <c r="T18" s="3">
-        <v>502.61</v>
-      </c>
-      <c r="U18" s="3">
-        <f>V18-T18</f>
-        <v>19.3099999999999</v>
-      </c>
-      <c r="V18" s="10">
-        <v>521.92</v>
-      </c>
-      <c r="W18" s="3">
-        <f>X18-V18</f>
-        <v>29.5400000000001</v>
-      </c>
-      <c r="X18" s="10">
-        <v>551.46</v>
-      </c>
-      <c r="Y18" s="3">
-        <f>Z18-X18</f>
-        <v>36.98</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>588.44</v>
-      </c>
-      <c r="AA18" s="3">
-        <f>AB18-Z18</f>
-        <v>21.17</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>609.61</v>
-      </c>
-      <c r="AC18" s="3">
-        <f>AD18-AB18</f>
-        <v>17.4399999999999</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>627.05</v>
-      </c>
-      <c r="AE18" s="3">
-        <f>AD18-D18</f>
-        <v>263.17</v>
-      </c>
-      <c r="AF18" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>183.87</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>47256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:36">
-      <c r="A19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2533.85</v>
-      </c>
-      <c r="E19" s="1">
-        <f>F19-D19</f>
-        <v>50.0500000000002</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2583.9</v>
-      </c>
-      <c r="G19" s="1">
-        <f>H19-F19</f>
-        <v>85.7599999999998</v>
-      </c>
-      <c r="H19" s="1">
-        <v>2669.66</v>
-      </c>
-      <c r="I19" s="1">
-        <f>J19-H19</f>
-        <v>81.79</v>
-      </c>
-      <c r="J19" s="1">
-        <v>2751.45</v>
-      </c>
-      <c r="K19" s="1">
-        <f>L19-J19</f>
-        <v>83.1700000000001</v>
-      </c>
-      <c r="L19" s="1">
-        <v>2834.62</v>
-      </c>
-      <c r="M19" s="1">
-        <f>N19-L19</f>
-        <v>56.9900000000002</v>
-      </c>
-      <c r="N19" s="1">
-        <v>2891.61</v>
-      </c>
-      <c r="O19" s="1">
-        <f>P19-N19</f>
-        <v>103.98</v>
-      </c>
-      <c r="P19" s="1">
-        <v>2995.59</v>
-      </c>
-      <c r="Q19" s="1">
-        <f>R19-P19</f>
-        <v>68.8499999999999</v>
-      </c>
-      <c r="R19" s="1">
-        <v>3064.44</v>
-      </c>
-      <c r="S19" s="1">
-        <f>T19-R19</f>
-        <v>47.6100000000001</v>
-      </c>
-      <c r="T19" s="1">
-        <v>3112.05</v>
-      </c>
-      <c r="U19" s="1">
-        <f>V19-T19</f>
-        <v>38.1599999999999</v>
-      </c>
-      <c r="V19" s="12">
-        <v>3150.21</v>
-      </c>
-      <c r="W19" s="1">
-        <f>X19-V19</f>
-        <v>146.1</v>
-      </c>
-      <c r="X19" s="12">
-        <v>3296.31</v>
-      </c>
-      <c r="Y19" s="1">
-        <f>Z19-X19</f>
-        <v>31.9400000000001</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>3328.25</v>
-      </c>
-      <c r="AA19" s="1">
-        <f>AB19-Z19</f>
-        <v>79.8800000000001</v>
-      </c>
-      <c r="AB19" s="1">
-        <v>3408.13</v>
-      </c>
-      <c r="AC19" s="1">
-        <f>AD19-AB19</f>
-        <v>68.9099999999999</v>
-      </c>
-      <c r="AD19" s="1">
-        <v>3477.04</v>
-      </c>
-      <c r="AE19" s="1">
-        <f>AD19-D19</f>
-        <v>943.19</v>
-      </c>
-      <c r="AF19" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG19" s="1">
-        <v>689.92</v>
-      </c>
-      <c r="AH19" s="1">
-        <v>200</v>
-      </c>
-      <c r="AI19" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AJ19" s="1">
-        <v>172501</v>
-      </c>
-    </row>
-    <row r="20" spans="1:36">
-      <c r="A20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="3">
-        <v>552.79</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="5">
+        <v>950.09</v>
+      </c>
+      <c r="E20" s="5">
         <f>F20-D20</f>
-        <v>15.9400000000001</v>
-      </c>
-      <c r="F20" s="3">
-        <v>568.73</v>
-      </c>
-      <c r="G20" s="3">
+        <v>42.4</v>
+      </c>
+      <c r="F20" s="5">
+        <v>992.49</v>
+      </c>
+      <c r="G20" s="5">
         <f>H20-F20</f>
-        <v>1.61000000000001</v>
-      </c>
-      <c r="H20" s="3">
-        <v>570.34</v>
-      </c>
-      <c r="I20" s="3">
+        <v>38.5899999999999</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1031.08</v>
+      </c>
+      <c r="I20" s="5">
         <f>J20-H20</f>
-        <v>7.13999999999999</v>
-      </c>
-      <c r="J20" s="3">
-        <v>577.48</v>
-      </c>
-      <c r="K20" s="3">
+        <v>22.6000000000001</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1053.68</v>
+      </c>
+      <c r="K20" s="5">
         <f>L20-J20</f>
-        <v>2.88999999999999</v>
-      </c>
-      <c r="L20" s="3">
-        <v>580.37</v>
-      </c>
-      <c r="M20" s="3">
+        <v>10.9299999999998</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1064.61</v>
+      </c>
+      <c r="M20" s="5">
         <f>N20-L20</f>
-        <v>2.55999999999995</v>
-      </c>
-      <c r="N20" s="3">
-        <v>582.93</v>
-      </c>
-      <c r="O20" s="3">
+        <v>16.1800000000001</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1080.79</v>
+      </c>
+      <c r="O20" s="5">
         <f>P20-N20</f>
-        <v>24.99</v>
-      </c>
-      <c r="P20" s="3">
-        <v>607.92</v>
-      </c>
-      <c r="Q20" s="3">
+        <v>13.6700000000001</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1094.46</v>
+      </c>
+      <c r="Q20" s="5">
         <f>R20-P20</f>
-        <v>0.330000000000041</v>
-      </c>
-      <c r="R20" s="3">
-        <v>608.25</v>
-      </c>
-      <c r="S20" s="3">
+        <v>56.26</v>
+      </c>
+      <c r="R20" s="5">
+        <v>1150.72</v>
+      </c>
+      <c r="S20" s="5">
         <f>T20-R20</f>
-        <v>1.80999999999995</v>
-      </c>
-      <c r="T20" s="3">
-        <v>610.06</v>
-      </c>
-      <c r="U20" s="3">
+        <v>41.27</v>
+      </c>
+      <c r="T20" s="5">
+        <v>1191.99</v>
+      </c>
+      <c r="U20" s="5">
         <f>V20-T20</f>
-        <v>0.560000000000059</v>
-      </c>
-      <c r="V20" s="10">
-        <v>610.62</v>
-      </c>
-      <c r="W20" s="3">
+        <v>35.21</v>
+      </c>
+      <c r="V20" s="11">
+        <v>1227.2</v>
+      </c>
+      <c r="W20" s="5">
         <f>X20-V20</f>
-        <v>3.83000000000004</v>
-      </c>
-      <c r="X20" s="10">
-        <v>614.45</v>
-      </c>
-      <c r="Y20" s="3">
+        <v>33.3599999999999</v>
+      </c>
+      <c r="X20" s="11">
+        <v>1260.56</v>
+      </c>
+      <c r="Y20" s="5">
         <f>Z20-X20</f>
-        <v>0.189999999999941</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>614.64</v>
-      </c>
-      <c r="AA20" s="3">
+        <v>46.0900000000001</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>1306.65</v>
+      </c>
+      <c r="AA20" s="5">
         <f>AB20-Z20</f>
-        <v>0.690000000000055</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>615.33</v>
-      </c>
-      <c r="AC20" s="3">
+        <v>31.1699999999998</v>
+      </c>
+      <c r="AB20" s="5">
+        <v>1337.82</v>
+      </c>
+      <c r="AC20" s="5">
         <f>AD20-AB20</f>
-        <v>6.64999999999998</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>621.98</v>
-      </c>
-      <c r="AE20" s="3">
-        <f>AD20-D20</f>
-        <v>69.1900000000001</v>
-      </c>
-      <c r="AF20" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>126.77</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>49654</v>
-      </c>
-    </row>
-    <row r="21" spans="1:36">
+        <v>18.79</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>1356.61</v>
+      </c>
+      <c r="AE20" s="16">
+        <f>AF20-AD20</f>
+        <v>31.5900000000001</v>
+      </c>
+      <c r="AF20" s="16">
+        <v>1388.2</v>
+      </c>
+      <c r="AG20" s="16">
+        <f>AF20-D20</f>
+        <v>438.11</v>
+      </c>
+      <c r="AH20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI20" s="16">
+        <v>519.72</v>
+      </c>
+      <c r="AJ20" s="5">
+        <v>10</v>
+      </c>
+      <c r="AK20" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" s="5">
+        <v>86194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38">
       <c r="A21" s="5" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D21" s="5">
-        <v>953.78</v>
+        <v>848.93</v>
       </c>
       <c r="E21" s="5">
         <f>F21-D21</f>
-        <v>28.97</v>
+        <v>34.5600000000001</v>
       </c>
       <c r="F21" s="5">
-        <v>982.75</v>
+        <v>883.49</v>
       </c>
       <c r="G21" s="5">
         <f>H21-F21</f>
-        <v>83.9300000000001</v>
+        <v>46.08</v>
       </c>
       <c r="H21" s="5">
-        <v>1066.68</v>
+        <v>929.57</v>
       </c>
       <c r="I21" s="5">
         <f>J21-H21</f>
-        <v>42.8399999999999</v>
+        <v>27.7399999999999</v>
       </c>
       <c r="J21" s="5">
-        <v>1109.52</v>
+        <v>957.31</v>
       </c>
       <c r="K21" s="5">
         <f>L21-J21</f>
-        <v>36.46</v>
+        <v>47.36</v>
       </c>
       <c r="L21" s="5">
-        <v>1145.98</v>
+        <v>1004.67</v>
       </c>
       <c r="M21" s="5">
         <f>N21-L21</f>
-        <v>37.49</v>
+        <v>25.9399999999999</v>
       </c>
       <c r="N21" s="5">
-        <v>1183.47</v>
+        <v>1030.61</v>
       </c>
       <c r="O21" s="5">
         <f>P21-N21</f>
-        <v>33.3699999999999</v>
+        <v>37.71</v>
       </c>
       <c r="P21" s="5">
-        <v>1216.84</v>
+        <v>1068.32</v>
       </c>
       <c r="Q21" s="5">
         <f>R21-P21</f>
-        <v>24.8900000000001</v>
+        <v>18.3800000000001</v>
       </c>
       <c r="R21" s="5">
-        <v>1241.73</v>
+        <v>1086.7</v>
       </c>
       <c r="S21" s="5">
         <f>T21-R21</f>
-        <v>42.3099999999999</v>
+        <v>21.04</v>
       </c>
       <c r="T21" s="5">
-        <v>1284.04</v>
+        <v>1107.74</v>
       </c>
       <c r="U21" s="5">
         <f>V21-T21</f>
-        <v>44.8400000000001</v>
-      </c>
-      <c r="V21" s="9">
-        <v>1328.88</v>
+        <v>32.7</v>
+      </c>
+      <c r="V21" s="11">
+        <v>1140.44</v>
       </c>
       <c r="W21" s="5">
         <f>X21-V21</f>
-        <v>45.9499999999998</v>
-      </c>
-      <c r="X21" s="9">
-        <v>1374.83</v>
+        <v>26.9299999999998</v>
+      </c>
+      <c r="X21" s="11">
+        <v>1167.37</v>
       </c>
       <c r="Y21" s="5">
         <f>Z21-X21</f>
-        <v>16.4200000000001</v>
+        <v>37.0300000000002</v>
       </c>
       <c r="Z21" s="5">
-        <v>1391.25</v>
+        <v>1204.4</v>
       </c>
       <c r="AA21" s="5">
         <f>AB21-Z21</f>
-        <v>22.0699999999999</v>
+        <v>33.6199999999999</v>
       </c>
       <c r="AB21" s="5">
-        <v>1413.32</v>
+        <v>1238.02</v>
       </c>
       <c r="AC21" s="5">
         <f>AD21-AB21</f>
-        <v>73.72</v>
+        <v>53.73</v>
       </c>
       <c r="AD21" s="5">
-        <v>1487.04</v>
-      </c>
-      <c r="AE21" s="5">
-        <f>AD21-D21</f>
-        <v>533.26</v>
-      </c>
-      <c r="AF21" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG21" s="5">
-        <v>539.88</v>
-      </c>
-      <c r="AH21" s="5">
+        <v>1291.75</v>
+      </c>
+      <c r="AE21" s="16">
+        <f>AF21-AD21</f>
+        <v>23.99</v>
+      </c>
+      <c r="AF21" s="16">
+        <v>1315.74</v>
+      </c>
+      <c r="AG21" s="16">
+        <f>AF21-D21</f>
+        <v>466.81</v>
+      </c>
+      <c r="AH21" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI21" s="16">
+        <v>481.17</v>
+      </c>
+      <c r="AJ21" s="5">
         <v>30</v>
       </c>
-      <c r="AI21" s="5">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="5">
-        <v>105419</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36">
+      <c r="AK21" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AL21" s="5">
+        <v>78989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38">
       <c r="A22" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D22" s="5">
         <v>927.15</v>
@@ -4080,14 +4238,14 @@
         <f>V22-T22</f>
         <v>28.76</v>
       </c>
-      <c r="V22" s="9">
+      <c r="V22" s="11">
         <v>1169.12</v>
       </c>
       <c r="W22" s="5">
         <f>X22-V22</f>
         <v>32.7600000000002</v>
       </c>
-      <c r="X22" s="9">
+      <c r="X22" s="11">
         <v>1201.88</v>
       </c>
       <c r="Y22" s="5">
@@ -4111,407 +4269,435 @@
       <c r="AD22" s="5">
         <v>1273.42</v>
       </c>
-      <c r="AE22" s="5">
-        <f>AD22-D22</f>
-        <v>346.27</v>
-      </c>
-      <c r="AF22" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG22" s="5">
-        <v>354.06</v>
-      </c>
-      <c r="AH22" s="5">
+      <c r="AE22" s="16">
+        <f>AF22-AD22</f>
+        <v>34.0999999999999</v>
+      </c>
+      <c r="AF22" s="16">
+        <v>1307.52</v>
+      </c>
+      <c r="AG22" s="16">
+        <f>AF22-D22</f>
+        <v>380.37</v>
+      </c>
+      <c r="AH22" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI22" s="16">
+        <v>363.97</v>
+      </c>
+      <c r="AJ22" s="5">
         <v>10</v>
       </c>
-      <c r="AI22" s="5">
+      <c r="AK22" s="5">
         <v>1.1</v>
       </c>
-      <c r="AJ22" s="5">
+      <c r="AL22" s="5">
         <v>80664</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:38">
       <c r="A23" s="3" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3">
-        <v>262.39</v>
+        <v>407.35</v>
       </c>
       <c r="E23" s="3">
         <f>F23-D23</f>
-        <v>11.5</v>
+        <v>13.86</v>
       </c>
       <c r="F23" s="3">
-        <v>273.89</v>
+        <v>421.21</v>
       </c>
       <c r="G23" s="3">
         <f>H23-F23</f>
-        <v>13.97</v>
+        <v>16.43</v>
       </c>
       <c r="H23" s="3">
-        <v>287.86</v>
+        <v>437.64</v>
       </c>
       <c r="I23" s="3">
         <f>J23-H23</f>
-        <v>16.24</v>
+        <v>13.64</v>
       </c>
       <c r="J23" s="3">
-        <v>304.1</v>
+        <v>451.28</v>
       </c>
       <c r="K23" s="3">
         <f>L23-J23</f>
-        <v>12.65</v>
+        <v>11.6</v>
       </c>
       <c r="L23" s="3">
-        <v>316.75</v>
+        <v>462.88</v>
       </c>
       <c r="M23" s="3">
         <f>N23-L23</f>
-        <v>9.99000000000001</v>
+        <v>47.68</v>
       </c>
       <c r="N23" s="3">
-        <v>326.74</v>
+        <v>510.56</v>
       </c>
       <c r="O23" s="3">
         <f>P23-N23</f>
-        <v>6.31999999999999</v>
+        <v>20.51</v>
       </c>
       <c r="P23" s="3">
-        <v>333.06</v>
+        <v>531.07</v>
       </c>
       <c r="Q23" s="3">
         <f>R23-P23</f>
-        <v>21.13</v>
+        <v>18.6099999999999</v>
       </c>
       <c r="R23" s="3">
-        <v>354.19</v>
+        <v>549.68</v>
       </c>
       <c r="S23" s="3">
         <f>T23-R23</f>
-        <v>17.68</v>
+        <v>11.9400000000001</v>
       </c>
       <c r="T23" s="3">
-        <v>371.87</v>
+        <v>561.62</v>
       </c>
       <c r="U23" s="3">
         <f>V23-T23</f>
-        <v>11.66</v>
-      </c>
-      <c r="V23" s="10">
-        <v>383.53</v>
+        <v>16.23</v>
+      </c>
+      <c r="V23" s="12">
+        <v>577.85</v>
       </c>
       <c r="W23" s="3">
         <f>X23-V23</f>
-        <v>20.5700000000001</v>
-      </c>
-      <c r="X23" s="10">
-        <v>404.1</v>
+        <v>15.28</v>
+      </c>
+      <c r="X23" s="12">
+        <v>593.13</v>
       </c>
       <c r="Y23" s="3">
         <f>Z23-X23</f>
-        <v>33.33</v>
+        <v>33.2</v>
       </c>
       <c r="Z23" s="3">
-        <v>437.43</v>
+        <v>626.33</v>
       </c>
       <c r="AA23" s="3">
         <f>AB23-Z23</f>
-        <v>27.72</v>
+        <v>16.7199999999999</v>
       </c>
       <c r="AB23" s="3">
-        <v>465.15</v>
+        <v>643.05</v>
       </c>
       <c r="AC23" s="3">
         <f>AD23-AB23</f>
-        <v>9.79000000000002</v>
+        <v>11.9300000000001</v>
       </c>
       <c r="AD23" s="3">
-        <v>474.94</v>
-      </c>
-      <c r="AE23" s="3">
-        <f>AD23-D23</f>
-        <v>212.55</v>
-      </c>
-      <c r="AF23" s="15" t="s">
+        <v>654.98</v>
+      </c>
+      <c r="AE23" s="17">
+        <f>AF23-AD23</f>
+        <v>9.16999999999996</v>
+      </c>
+      <c r="AF23" s="17">
+        <v>664.15</v>
+      </c>
+      <c r="AG23" s="17">
+        <f>AF23-D23</f>
+        <v>256.8</v>
+      </c>
+      <c r="AH23" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI23" s="17">
+        <v>297.3</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>30</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38">
+      <c r="A24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3">
+        <v>363.88</v>
+      </c>
+      <c r="E24" s="3">
+        <f>F24-D24</f>
+        <v>14.21</v>
+      </c>
+      <c r="F24" s="3">
+        <v>378.09</v>
+      </c>
+      <c r="G24" s="3">
+        <f>H24-F24</f>
+        <v>11.22</v>
+      </c>
+      <c r="H24" s="3">
+        <v>389.31</v>
+      </c>
+      <c r="I24" s="3">
+        <f>J24-H24</f>
+        <v>13.62</v>
+      </c>
+      <c r="J24" s="3">
+        <v>402.93</v>
+      </c>
+      <c r="K24" s="3">
+        <f>L24-J24</f>
+        <v>11.13</v>
+      </c>
+      <c r="L24" s="3">
+        <v>414.06</v>
+      </c>
+      <c r="M24" s="3">
+        <f>N24-L24</f>
+        <v>17.39</v>
+      </c>
+      <c r="N24" s="3">
+        <v>431.45</v>
+      </c>
+      <c r="O24" s="3">
+        <f>P24-N24</f>
+        <v>6.32999999999998</v>
+      </c>
+      <c r="P24" s="3">
+        <v>437.78</v>
+      </c>
+      <c r="Q24" s="3">
+        <f>R24-P24</f>
+        <v>53.01</v>
+      </c>
+      <c r="R24" s="3">
+        <v>490.79</v>
+      </c>
+      <c r="S24" s="3">
+        <f>T24-R24</f>
+        <v>11.82</v>
+      </c>
+      <c r="T24" s="3">
+        <v>502.61</v>
+      </c>
+      <c r="U24" s="3">
+        <f>V24-T24</f>
+        <v>19.3099999999999</v>
+      </c>
+      <c r="V24" s="12">
+        <v>521.92</v>
+      </c>
+      <c r="W24" s="3">
+        <f>X24-V24</f>
+        <v>29.5400000000001</v>
+      </c>
+      <c r="X24" s="12">
+        <v>551.46</v>
+      </c>
+      <c r="Y24" s="3">
+        <f>Z24-X24</f>
+        <v>36.98</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>588.44</v>
+      </c>
+      <c r="AA24" s="3">
+        <f>AB24-Z24</f>
+        <v>21.17</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>609.61</v>
+      </c>
+      <c r="AC24" s="3">
+        <f>AD24-AB24</f>
+        <v>17.4399999999999</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>627.05</v>
+      </c>
+      <c r="AE24" s="17">
+        <f>AF24-AD24</f>
+        <v>21.0500000000001</v>
+      </c>
+      <c r="AF24" s="17">
+        <v>648.1</v>
+      </c>
+      <c r="AG24" s="17">
+        <f>AF24-D24</f>
+        <v>284.22</v>
+      </c>
+      <c r="AH24" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AG23" s="3">
-        <v>162.06</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI24" s="17">
+        <v>192.49</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>0</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK24" s="3">
         <v>1</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>36684</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36">
-      <c r="A24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1735.94</v>
-      </c>
-      <c r="E24" s="2">
-        <f>F24-D24</f>
-        <v>48.5999999999999</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1784.54</v>
-      </c>
-      <c r="G24" s="2">
-        <f>H24-F24</f>
-        <v>74.1600000000001</v>
-      </c>
-      <c r="H24" s="2">
-        <v>1858.7</v>
-      </c>
-      <c r="I24" s="2">
-        <f>J24-H24</f>
-        <v>65.55</v>
-      </c>
-      <c r="J24" s="2">
-        <v>1924.25</v>
-      </c>
-      <c r="K24" s="2">
-        <f>L24-J24</f>
-        <v>35.73</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1959.98</v>
-      </c>
-      <c r="M24" s="2">
-        <f>N24-L24</f>
-        <v>41.8799999999999</v>
-      </c>
-      <c r="N24" s="2">
-        <v>2001.86</v>
-      </c>
-      <c r="O24" s="2">
-        <f>P24-N24</f>
-        <v>74.6600000000001</v>
-      </c>
-      <c r="P24" s="2">
-        <v>2076.52</v>
-      </c>
-      <c r="Q24" s="2">
-        <f>R24-P24</f>
-        <v>48.71</v>
-      </c>
-      <c r="R24" s="2">
-        <v>2125.23</v>
-      </c>
-      <c r="S24" s="2">
-        <f>T24-R24</f>
-        <v>57.4200000000001</v>
-      </c>
-      <c r="T24" s="2">
-        <v>2182.65</v>
-      </c>
-      <c r="U24" s="2">
-        <f>V24-T24</f>
-        <v>68.9400000000001</v>
-      </c>
-      <c r="V24" s="8">
-        <v>2251.59</v>
-      </c>
-      <c r="W24" s="2">
-        <f>X24-V24</f>
-        <v>72.0299999999997</v>
-      </c>
-      <c r="X24" s="8">
-        <v>2323.62</v>
-      </c>
-      <c r="Y24" s="2">
-        <f>Z24-X24</f>
-        <v>23.6300000000001</v>
-      </c>
-      <c r="Z24" s="2">
-        <v>2347.25</v>
-      </c>
-      <c r="AA24" s="2">
-        <f>AB24-Z24</f>
-        <v>64.5300000000002</v>
-      </c>
-      <c r="AB24" s="2">
-        <v>2411.78</v>
-      </c>
-      <c r="AC24" s="2">
-        <f>AD24-AB24</f>
-        <v>30.2599999999998</v>
-      </c>
-      <c r="AD24" s="2">
-        <v>2442.04</v>
-      </c>
-      <c r="AE24" s="2">
-        <f>AD24-D24</f>
-        <v>706.1</v>
-      </c>
-      <c r="AF24" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG24" s="2">
-        <v>631.57</v>
-      </c>
-      <c r="AH24" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI24" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="AJ24" s="2">
-        <v>150192</v>
-      </c>
-    </row>
-    <row r="25" spans="1:36">
-      <c r="A25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1446.65</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="AL24" s="3">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38">
+      <c r="A25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="3">
+        <v>552.79</v>
+      </c>
+      <c r="E25" s="3">
         <f>F25-D25</f>
-        <v>28.1799999999998</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1474.83</v>
-      </c>
-      <c r="G25" s="2">
+        <v>15.9400000000001</v>
+      </c>
+      <c r="F25" s="3">
+        <v>568.73</v>
+      </c>
+      <c r="G25" s="3">
         <f>H25-F25</f>
-        <v>63.8200000000002</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1538.65</v>
-      </c>
-      <c r="I25" s="2">
+        <v>1.61000000000001</v>
+      </c>
+      <c r="H25" s="3">
+        <v>570.34</v>
+      </c>
+      <c r="I25" s="3">
         <f>J25-H25</f>
-        <v>22.9199999999998</v>
-      </c>
-      <c r="J25" s="2">
-        <v>1561.57</v>
-      </c>
-      <c r="K25" s="2">
+        <v>7.13999999999999</v>
+      </c>
+      <c r="J25" s="3">
+        <v>577.48</v>
+      </c>
+      <c r="K25" s="3">
         <f>L25-J25</f>
-        <v>70.8600000000001</v>
-      </c>
-      <c r="L25" s="2">
-        <v>1632.43</v>
-      </c>
-      <c r="M25" s="2">
+        <v>2.88999999999999</v>
+      </c>
+      <c r="L25" s="3">
+        <v>580.37</v>
+      </c>
+      <c r="M25" s="3">
         <f>N25-L25</f>
-        <v>37.4099999999999</v>
-      </c>
-      <c r="N25" s="2">
-        <v>1669.84</v>
-      </c>
-      <c r="O25" s="2">
+        <v>2.55999999999995</v>
+      </c>
+      <c r="N25" s="3">
+        <v>582.93</v>
+      </c>
+      <c r="O25" s="3">
         <f>P25-N25</f>
-        <v>32.8300000000002</v>
-      </c>
-      <c r="P25" s="2">
-        <v>1702.67</v>
-      </c>
-      <c r="Q25" s="2">
+        <v>24.99</v>
+      </c>
+      <c r="P25" s="3">
+        <v>607.92</v>
+      </c>
+      <c r="Q25" s="3">
         <f>R25-P25</f>
-        <v>51.9499999999998</v>
-      </c>
-      <c r="R25" s="2">
-        <v>1754.62</v>
-      </c>
-      <c r="S25" s="2">
+        <v>0.330000000000041</v>
+      </c>
+      <c r="R25" s="3">
+        <v>608.25</v>
+      </c>
+      <c r="S25" s="3">
         <f>T25-R25</f>
-        <v>40.1200000000001</v>
-      </c>
-      <c r="T25" s="2">
-        <v>1794.74</v>
-      </c>
-      <c r="U25" s="2">
+        <v>1.80999999999995</v>
+      </c>
+      <c r="T25" s="3">
+        <v>610.06</v>
+      </c>
+      <c r="U25" s="3">
         <f>V25-T25</f>
-        <v>77.5</v>
-      </c>
-      <c r="V25" s="8">
-        <v>1872.24</v>
-      </c>
-      <c r="W25" s="2">
+        <v>0.560000000000059</v>
+      </c>
+      <c r="V25" s="12">
+        <v>610.62</v>
+      </c>
+      <c r="W25" s="3">
         <f>X25-V25</f>
-        <v>79.5899999999999</v>
-      </c>
-      <c r="X25" s="8">
-        <v>1951.83</v>
-      </c>
-      <c r="Y25" s="2">
+        <v>3.83000000000004</v>
+      </c>
+      <c r="X25" s="12">
+        <v>614.45</v>
+      </c>
+      <c r="Y25" s="3">
         <f>Z25-X25</f>
-        <v>9.01999999999998</v>
-      </c>
-      <c r="Z25" s="2">
-        <v>1960.85</v>
-      </c>
-      <c r="AA25" s="2">
+        <v>0.189999999999941</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>614.64</v>
+      </c>
+      <c r="AA25" s="3">
         <f>AB25-Z25</f>
-        <v>74</v>
-      </c>
-      <c r="AB25" s="2">
-        <v>2034.85</v>
-      </c>
-      <c r="AC25" s="2">
+        <v>0.690000000000055</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>615.33</v>
+      </c>
+      <c r="AC25" s="3">
         <f>AD25-AB25</f>
-        <v>31.8000000000002</v>
-      </c>
-      <c r="AD25" s="2">
-        <v>2066.65</v>
-      </c>
-      <c r="AE25" s="2">
-        <f>AD25-D25</f>
-        <v>620</v>
-      </c>
-      <c r="AF25" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG25" s="2">
-        <v>794.88</v>
-      </c>
-      <c r="AH25" s="5">
-        <v>65</v>
-      </c>
-      <c r="AI25" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="AJ25" s="5">
-        <v>109333</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36">
+        <v>6.64999999999998</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>621.98</v>
+      </c>
+      <c r="AE25" s="17">
+        <f>AF25-AD25</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="17">
+        <v>621.98</v>
+      </c>
+      <c r="AG25" s="17">
+        <f>AF25-D25</f>
+        <v>69.1900000000001</v>
+      </c>
+      <c r="AH25" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI25" s="17">
+        <v>137</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>49654</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3">
         <v>305.29</v>
@@ -4576,14 +4762,14 @@
         <f>V26-T26</f>
         <v>25.13</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="12">
         <v>433.01</v>
       </c>
       <c r="W26" s="3">
         <f>X26-V26</f>
         <v>37.15</v>
       </c>
-      <c r="X26" s="10">
+      <c r="X26" s="12">
         <v>470.16</v>
       </c>
       <c r="Y26" s="3">
@@ -4607,151 +4793,165 @@
       <c r="AD26" s="3">
         <v>507.45</v>
       </c>
-      <c r="AE26" s="3">
-        <f>AD26-D26</f>
-        <v>202.16</v>
-      </c>
-      <c r="AF26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>121.84</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AE26" s="17">
+        <f>AF26-AD26</f>
+        <v>42.97</v>
+      </c>
+      <c r="AF26" s="17">
+        <v>550.42</v>
+      </c>
+      <c r="AG26" s="17">
+        <f>AF26-D26</f>
+        <v>245.13</v>
+      </c>
+      <c r="AH26" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI26" s="17">
+        <v>174.01</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>0</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>28066</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
-      <c r="A27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="1:38">
+      <c r="A27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="5">
-        <v>950.09</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="C27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="3">
+        <v>262.39</v>
+      </c>
+      <c r="E27" s="3">
         <f>F27-D27</f>
-        <v>42.4</v>
-      </c>
-      <c r="F27" s="5">
-        <v>992.49</v>
-      </c>
-      <c r="G27" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>273.89</v>
+      </c>
+      <c r="G27" s="3">
         <f>H27-F27</f>
-        <v>38.5899999999999</v>
-      </c>
-      <c r="H27" s="5">
-        <v>1031.08</v>
-      </c>
-      <c r="I27" s="5">
+        <v>13.97</v>
+      </c>
+      <c r="H27" s="3">
+        <v>287.86</v>
+      </c>
+      <c r="I27" s="3">
         <f>J27-H27</f>
-        <v>22.6000000000001</v>
-      </c>
-      <c r="J27" s="5">
-        <v>1053.68</v>
-      </c>
-      <c r="K27" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="J27" s="3">
+        <v>304.1</v>
+      </c>
+      <c r="K27" s="3">
         <f>L27-J27</f>
-        <v>10.9299999999998</v>
-      </c>
-      <c r="L27" s="5">
-        <v>1064.61</v>
-      </c>
-      <c r="M27" s="5">
+        <v>12.65</v>
+      </c>
+      <c r="L27" s="3">
+        <v>316.75</v>
+      </c>
+      <c r="M27" s="3">
         <f>N27-L27</f>
-        <v>16.1800000000001</v>
-      </c>
-      <c r="N27" s="5">
-        <v>1080.79</v>
-      </c>
-      <c r="O27" s="5">
+        <v>9.99000000000001</v>
+      </c>
+      <c r="N27" s="3">
+        <v>326.74</v>
+      </c>
+      <c r="O27" s="3">
         <f>P27-N27</f>
-        <v>13.6700000000001</v>
-      </c>
-      <c r="P27" s="5">
-        <v>1094.46</v>
-      </c>
-      <c r="Q27" s="5">
+        <v>6.31999999999999</v>
+      </c>
+      <c r="P27" s="3">
+        <v>333.06</v>
+      </c>
+      <c r="Q27" s="3">
         <f>R27-P27</f>
-        <v>56.26</v>
-      </c>
-      <c r="R27" s="5">
-        <v>1150.72</v>
-      </c>
-      <c r="S27" s="5">
+        <v>21.13</v>
+      </c>
+      <c r="R27" s="3">
+        <v>354.19</v>
+      </c>
+      <c r="S27" s="3">
         <f>T27-R27</f>
-        <v>41.27</v>
-      </c>
-      <c r="T27" s="5">
-        <v>1191.99</v>
-      </c>
-      <c r="U27" s="5">
+        <v>17.68</v>
+      </c>
+      <c r="T27" s="3">
+        <v>371.87</v>
+      </c>
+      <c r="U27" s="3">
         <f>V27-T27</f>
-        <v>35.21</v>
-      </c>
-      <c r="V27" s="9">
-        <v>1227.2</v>
-      </c>
-      <c r="W27" s="5">
+        <v>11.66</v>
+      </c>
+      <c r="V27" s="12">
+        <v>383.53</v>
+      </c>
+      <c r="W27" s="3">
         <f>X27-V27</f>
-        <v>33.3599999999999</v>
-      </c>
-      <c r="X27" s="9">
-        <v>1260.56</v>
-      </c>
-      <c r="Y27" s="5">
+        <v>20.5700000000001</v>
+      </c>
+      <c r="X27" s="12">
+        <v>404.1</v>
+      </c>
+      <c r="Y27" s="3">
         <f>Z27-X27</f>
-        <v>46.0900000000001</v>
-      </c>
-      <c r="Z27" s="5">
-        <v>1306.65</v>
-      </c>
-      <c r="AA27" s="5">
+        <v>33.33</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>437.43</v>
+      </c>
+      <c r="AA27" s="3">
         <f>AB27-Z27</f>
-        <v>31.1699999999998</v>
-      </c>
-      <c r="AB27" s="5">
-        <v>1337.82</v>
-      </c>
-      <c r="AC27" s="5">
+        <v>27.72</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>465.15</v>
+      </c>
+      <c r="AC27" s="3">
         <f>AD27-AB27</f>
-        <v>18.79</v>
-      </c>
-      <c r="AD27" s="5">
-        <v>1356.61</v>
-      </c>
-      <c r="AE27" s="5">
-        <f>AD27-D27</f>
-        <v>406.52</v>
-      </c>
-      <c r="AF27" s="14" t="s">
+        <v>9.79000000000002</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>474.94</v>
+      </c>
+      <c r="AE27" s="17">
+        <f>AF27-AD27</f>
+        <v>13.05</v>
+      </c>
+      <c r="AF27" s="17">
+        <v>487.99</v>
+      </c>
+      <c r="AG27" s="17">
+        <f>AF27-D27</f>
+        <v>225.6</v>
+      </c>
+      <c r="AH27" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AG27" s="5">
-        <v>514.42</v>
-      </c>
-      <c r="AH27" s="5">
-        <v>10</v>
-      </c>
-      <c r="AI27" s="5">
-        <v>2.2</v>
-      </c>
-      <c r="AJ27" s="5">
-        <v>86194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="AI27" s="17">
+        <v>164.76</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="3">
+        <v>36684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -4789,10 +4989,12 @@
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="AG30" s="7"/>
-    </row>
-    <row r="31" spans="1:34">
+      <c r="AH30" s="7"/>
+      <c r="AI30" s="7"/>
+    </row>
+    <row r="31" spans="1:36">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
         <v>82</v>
@@ -4816,18 +5018,20 @@
       <c r="AF31" s="7"/>
       <c r="AG31" s="7"/>
       <c r="AH31" s="7"/>
+      <c r="AI31" s="7"/>
+      <c r="AJ31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>84</v>
@@ -4862,10 +5066,12 @@
       <c r="AD33" s="7"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
+      <c r="AG33" s="7"/>
+      <c r="AH33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>85</v>
@@ -4873,7 +5079,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>86</v>
@@ -4881,7 +5087,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
         <v>87</v>
@@ -4889,7 +5095,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
@@ -4912,8 +5118,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AJ27">
-    <sortCondition ref="A2"/>
+  <sortState ref="A2:AL27">
+    <sortCondition ref="AF2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6234,7 +6440,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
+    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="19星域战力标" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="110">
   <si>
     <t>区服</t>
   </si>
@@ -91,6 +91,9 @@
     <t>战力（2025.7.2）</t>
   </si>
   <si>
+    <t>战力（2025.7.9）</t>
+  </si>
+  <si>
     <t>累计提升</t>
   </si>
   <si>
@@ -109,6 +112,39 @@
     <t>抽卡数</t>
   </si>
   <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>眼镜妹（跳费）</t>
+  </si>
+  <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
+    <t>白处尊（养神）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>沙琪玛（快攻）</t>
+  </si>
+  <si>
     <t>146区</t>
   </si>
   <si>
@@ -121,114 +157,81 @@
     <t>圣母（杂糅）</t>
   </si>
   <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>眼镜妹（跳费）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>沙琪玛（快攻）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>白处尊（养神）</t>
-  </si>
-  <si>
     <t>江南</t>
   </si>
   <si>
     <t>魔尊（快攻）</t>
   </si>
   <si>
+    <t>请叫我阿奎</t>
+  </si>
+  <si>
+    <t>中低氪</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>1。</t>
+  </si>
+  <si>
+    <t>查查（养神）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>洞察女（洞察）</t>
+  </si>
+  <si>
+    <t>杜佳捷</t>
+  </si>
+  <si>
+    <t>白处尊（杂糅）</t>
+  </si>
+  <si>
+    <t>星空</t>
+  </si>
+  <si>
+    <t>12345。</t>
+  </si>
+  <si>
+    <t>低氪</t>
+  </si>
+  <si>
+    <t>冰男（浦冰）</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>谢之求学者</t>
+  </si>
+  <si>
     <t>古希腊掌管贫穷的神</t>
   </si>
   <si>
+    <t>150区</t>
+  </si>
+  <si>
+    <t>开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>桃太郎</t>
+  </si>
+  <si>
     <t>水煮肉片</t>
   </si>
   <si>
     <t>眼睛妹（跳费）</t>
   </si>
   <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>中低氪</t>
-  </si>
-  <si>
-    <t>洞察女（洞察）</t>
-  </si>
-  <si>
-    <t>杜佳捷</t>
-  </si>
-  <si>
-    <t>白处尊（杂糅）</t>
-  </si>
-  <si>
-    <t>1。</t>
-  </si>
-  <si>
-    <t>查查（养神）</t>
-  </si>
-  <si>
-    <t>请叫我阿奎</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>星空</t>
-  </si>
-  <si>
     <t>玩玩</t>
   </si>
   <si>
-    <t>小黑</t>
-  </si>
-  <si>
-    <t>12345。</t>
-  </si>
-  <si>
-    <t>低氪</t>
-  </si>
-  <si>
-    <t>冰男（浦冰）</t>
-  </si>
-  <si>
-    <t>谢之求学者</t>
-  </si>
-  <si>
-    <t>150区</t>
-  </si>
-  <si>
-    <t>开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>桃太郎</t>
-  </si>
-  <si>
     <t>152区</t>
   </si>
   <si>
@@ -250,28 +253,28 @@
     <t>讯（养神）</t>
   </si>
   <si>
+    <t>白夜</t>
+  </si>
+  <si>
+    <t>零氪</t>
+  </si>
+  <si>
     <t>清风</t>
   </si>
   <si>
     <t>冽（传承）</t>
   </si>
   <si>
-    <t>白夜</t>
-  </si>
-  <si>
-    <t>零氪</t>
+    <t>秋雨</t>
+  </si>
+  <si>
+    <t>糊涂阳</t>
+  </si>
+  <si>
+    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>桂林碧桂园</t>
-  </si>
-  <si>
-    <t>秋雨</t>
-  </si>
-  <si>
-    <t>糊涂阳</t>
-  </si>
-  <si>
-    <t>丽娅（杂糅）</t>
   </si>
   <si>
     <t>氪度表：</t>
@@ -1038,12 +1041,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1053,12 +1056,12 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1068,10 +1071,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1396,7 +1399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1420,16 +1423,16 @@
     <col min="19" max="20" width="18.0166666666667" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="16.625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="17.3916666666667" hidden="1" customWidth="1"/>
-    <col min="23" max="29" width="18.0166666666667" hidden="1" customWidth="1"/>
-    <col min="30" max="33" width="18.0166666666667" customWidth="1"/>
-    <col min="34" max="34" width="18.8916666666667" customWidth="1"/>
-    <col min="35" max="35" width="14.5416666666667" customWidth="1"/>
-    <col min="36" max="36" width="11.625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="23" max="31" width="18.0166666666667" hidden="1" customWidth="1"/>
+    <col min="32" max="35" width="18.0166666666667" customWidth="1"/>
+    <col min="36" max="36" width="18.8916666666667" customWidth="1"/>
+    <col min="37" max="37" width="14.5416666666667" customWidth="1"/>
+    <col min="38" max="38" width="11.625" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="15.0166666666667" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1527,295 +1530,315 @@
         <v>18</v>
       </c>
       <c r="AG1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH1" t="s">
         <v>19</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>20</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>21</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>22</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>23</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:38">
+      <c r="AN1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:40">
       <c r="A2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="6">
-        <v>4105.48</v>
+        <v>2714.1</v>
       </c>
       <c r="E2" s="6">
         <f>F2-D2</f>
-        <v>181.21</v>
+        <v>123.29</v>
       </c>
       <c r="F2" s="6">
-        <v>4286.69</v>
+        <v>2837.39</v>
       </c>
       <c r="G2" s="6">
         <f>H2-F2</f>
-        <v>139.09</v>
+        <v>95.8499999999999</v>
       </c>
       <c r="H2" s="6">
-        <v>4425.78</v>
+        <v>2933.24</v>
       </c>
       <c r="I2" s="6">
         <f>J2-H2</f>
-        <v>54.8800000000001</v>
+        <v>92.46</v>
       </c>
       <c r="J2" s="6">
-        <v>4480.66</v>
+        <v>3025.7</v>
       </c>
       <c r="K2" s="6">
         <f>L2-J2</f>
-        <v>104.900000000001</v>
+        <v>90.4100000000003</v>
       </c>
       <c r="L2" s="6">
-        <v>4585.56</v>
+        <v>3116.11</v>
       </c>
       <c r="M2" s="6">
         <f>N2-L2</f>
-        <v>70.29</v>
+        <v>103.54</v>
       </c>
       <c r="N2" s="6">
-        <v>4655.85</v>
+        <v>3219.65</v>
       </c>
       <c r="O2" s="6">
         <f>P2-N2</f>
-        <v>49.1700000000001</v>
+        <v>75.6599999999999</v>
       </c>
       <c r="P2" s="6">
-        <v>4705.02</v>
+        <v>3295.31</v>
       </c>
       <c r="Q2" s="6">
         <f>R2-P2</f>
-        <v>38.2199999999993</v>
+        <v>88.98</v>
       </c>
       <c r="R2" s="6">
-        <v>4743.24</v>
+        <v>3384.29</v>
       </c>
       <c r="S2" s="6">
         <f>T2-R2</f>
-        <v>45.6199999999999</v>
+        <v>102.46</v>
       </c>
       <c r="T2" s="6">
-        <v>4788.86</v>
+        <v>3486.75</v>
       </c>
       <c r="U2" s="6">
         <f>V2-T2</f>
-        <v>27.5900000000001</v>
+        <v>69.23</v>
       </c>
       <c r="V2" s="8">
-        <v>4816.45</v>
+        <v>3555.98</v>
       </c>
       <c r="W2" s="6">
         <f>X2-V2</f>
-        <v>158.22</v>
+        <v>133.46</v>
       </c>
       <c r="X2" s="8">
-        <v>4974.67</v>
+        <v>3689.44</v>
       </c>
       <c r="Y2" s="6">
         <f>Z2-X2</f>
-        <v>32.8999999999996</v>
+        <v>10.5999999999999</v>
       </c>
       <c r="Z2" s="6">
-        <v>5007.57</v>
+        <v>3700.04</v>
       </c>
       <c r="AA2" s="6">
         <f>AB2-Z2</f>
-        <v>19.5700000000006</v>
+        <v>145.58</v>
       </c>
       <c r="AB2" s="6">
-        <v>5027.14</v>
+        <v>3845.62</v>
       </c>
       <c r="AC2" s="6">
         <f>AD2-AB2</f>
-        <v>77.6899999999996</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>5104.83</v>
+        <v>64.1800000000003</v>
+      </c>
+      <c r="AD2" s="13">
+        <v>3909.8</v>
       </c>
       <c r="AE2" s="13">
         <f>AF2-AD2</f>
-        <v>27.4499999999998</v>
+        <v>98.8399999999997</v>
       </c>
       <c r="AF2" s="13">
-        <v>5132.28</v>
+        <v>4008.64</v>
       </c>
       <c r="AG2" s="13">
-        <f>AF2-D2</f>
-        <v>1026.8</v>
-      </c>
-      <c r="AH2" s="18" t="s">
+        <f>AH2-AF2</f>
+        <v>157.920000000001</v>
+      </c>
+      <c r="AH2" s="13">
+        <v>4166.56</v>
+      </c>
+      <c r="AI2" s="13">
+        <f>AH2-D2</f>
+        <v>1452.46</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK2" s="13">
+        <v>922.52</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>500</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>191519</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1754.54</v>
+      </c>
+      <c r="E3" s="2">
+        <f>F3-D3</f>
+        <v>53.3700000000001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1807.91</v>
+      </c>
+      <c r="G3" s="2">
+        <f>H3-F3</f>
+        <v>90.24</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1898.15</v>
+      </c>
+      <c r="I3" s="2">
+        <f>J3-H3</f>
+        <v>90.3799999999999</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1988.53</v>
+      </c>
+      <c r="K3" s="2">
+        <f>L3-J3</f>
+        <v>59.7099999999998</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2048.24</v>
+      </c>
+      <c r="M3" s="2">
+        <f>N3-L3</f>
+        <v>153.99</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2202.23</v>
+      </c>
+      <c r="O3" s="2">
+        <f>P3-N3</f>
+        <v>64.21</v>
+      </c>
+      <c r="P3" s="2">
+        <v>2266.44</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>R3-P3</f>
+        <v>47.5599999999999</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2314</v>
+      </c>
+      <c r="S3" s="2">
+        <f>T3-R3</f>
+        <v>59.6500000000001</v>
+      </c>
+      <c r="T3" s="2">
+        <v>2373.65</v>
+      </c>
+      <c r="U3" s="2">
+        <f>V3-T3</f>
+        <v>70.6399999999999</v>
+      </c>
+      <c r="V3" s="9">
+        <v>2444.29</v>
+      </c>
+      <c r="W3" s="2">
+        <f>X3-V3</f>
+        <v>95.9299999999998</v>
+      </c>
+      <c r="X3" s="9">
+        <v>2540.22</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>Z3-X3</f>
+        <v>90.3200000000002</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>2630.54</v>
+      </c>
+      <c r="AA3" s="2">
+        <f>AB3-Z3</f>
+        <v>69.7800000000002</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>2700.32</v>
+      </c>
+      <c r="AC3" s="2">
+        <f>AD3-AB3</f>
+        <v>57.52</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>2757.84</v>
+      </c>
+      <c r="AE3" s="14">
+        <f>AF3-AD3</f>
+        <v>217.06</v>
+      </c>
+      <c r="AF3" s="14">
+        <v>2974.9</v>
+      </c>
+      <c r="AG3" s="14">
+        <f>AH3-AF3</f>
+        <v>18.4400000000001</v>
+      </c>
+      <c r="AH3" s="14">
+        <v>2993.34</v>
+      </c>
+      <c r="AI3" s="14">
+        <f>AH3-D3</f>
+        <v>1238.8</v>
+      </c>
+      <c r="AJ3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK3" s="14">
+        <v>515.07</v>
+      </c>
+      <c r="AL3" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM3" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="AN3" s="2">
+        <v>132783</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="AI2" s="13">
-        <v>1493.67</v>
-      </c>
-      <c r="AJ2" s="6">
-        <v>400</v>
-      </c>
-      <c r="AK2" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="AL2" s="6">
-        <v>186759</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6">
-        <v>2714.1</v>
-      </c>
-      <c r="E3" s="6">
-        <f>F3-D3</f>
-        <v>123.29</v>
-      </c>
-      <c r="F3" s="6">
-        <v>2837.39</v>
-      </c>
-      <c r="G3" s="6">
-        <f>H3-F3</f>
-        <v>95.8499999999999</v>
-      </c>
-      <c r="H3" s="6">
-        <v>2933.24</v>
-      </c>
-      <c r="I3" s="6">
-        <f>J3-H3</f>
-        <v>92.46</v>
-      </c>
-      <c r="J3" s="6">
-        <v>3025.7</v>
-      </c>
-      <c r="K3" s="6">
-        <f>L3-J3</f>
-        <v>90.4100000000003</v>
-      </c>
-      <c r="L3" s="6">
-        <v>3116.11</v>
-      </c>
-      <c r="M3" s="6">
-        <f>N3-L3</f>
-        <v>103.54</v>
-      </c>
-      <c r="N3" s="6">
-        <v>3219.65</v>
-      </c>
-      <c r="O3" s="6">
-        <f>P3-N3</f>
-        <v>75.6599999999999</v>
-      </c>
-      <c r="P3" s="6">
-        <v>3295.31</v>
-      </c>
-      <c r="Q3" s="6">
-        <f>R3-P3</f>
-        <v>88.98</v>
-      </c>
-      <c r="R3" s="6">
-        <v>3384.29</v>
-      </c>
-      <c r="S3" s="6">
-        <f>T3-R3</f>
-        <v>102.46</v>
-      </c>
-      <c r="T3" s="6">
-        <v>3486.75</v>
-      </c>
-      <c r="U3" s="6">
-        <f>V3-T3</f>
-        <v>69.23</v>
-      </c>
-      <c r="V3" s="8">
-        <v>3555.98</v>
-      </c>
-      <c r="W3" s="6">
-        <f>X3-V3</f>
-        <v>133.46</v>
-      </c>
-      <c r="X3" s="8">
-        <v>3689.44</v>
-      </c>
-      <c r="Y3" s="6">
-        <f>Z3-X3</f>
-        <v>10.5999999999999</v>
-      </c>
-      <c r="Z3" s="6">
-        <v>3700.04</v>
-      </c>
-      <c r="AA3" s="6">
-        <f>AB3-Z3</f>
-        <v>145.58</v>
-      </c>
-      <c r="AB3" s="6">
-        <v>3845.62</v>
-      </c>
-      <c r="AC3" s="6">
-        <f>AD3-AB3</f>
-        <v>64.1800000000003</v>
-      </c>
-      <c r="AD3" s="13">
-        <v>3909.8</v>
-      </c>
-      <c r="AE3" s="13">
-        <f>AF3-AD3</f>
-        <v>98.8399999999997</v>
-      </c>
-      <c r="AF3" s="13">
-        <v>4008.64</v>
-      </c>
-      <c r="AG3" s="13">
-        <f>AF3-D3</f>
-        <v>1294.54</v>
-      </c>
-      <c r="AH3" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI3" s="13">
-        <v>862.62</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>500</v>
-      </c>
-      <c r="AK3" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="AL3" s="1">
-        <v>191519</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D4" s="1">
         <v>2533.85</v>
@@ -1880,14 +1903,14 @@
         <f>V4-T4</f>
         <v>38.1599999999999</v>
       </c>
-      <c r="V4" s="9">
+      <c r="V4" s="10">
         <v>3150.21</v>
       </c>
       <c r="W4" s="1">
         <f>X4-V4</f>
         <v>146.1</v>
       </c>
-      <c r="X4" s="9">
+      <c r="X4" s="10">
         <v>3296.31</v>
       </c>
       <c r="Y4" s="1">
@@ -1911,173 +1934,187 @@
       <c r="AD4" s="1">
         <v>3477.04</v>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="15">
         <f>AF4-AD4</f>
         <v>143.74</v>
       </c>
-      <c r="AF4" s="14">
+      <c r="AF4" s="15">
         <v>3620.78</v>
       </c>
-      <c r="AG4" s="14">
-        <f>AF4-D4</f>
-        <v>1086.93</v>
-      </c>
-      <c r="AH4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI4" s="14">
-        <v>780.42</v>
-      </c>
-      <c r="AJ4" s="1">
+      <c r="AG4" s="15">
+        <f>AH4-AF4</f>
+        <v>82.0999999999999</v>
+      </c>
+      <c r="AH4" s="15">
+        <v>3702.88</v>
+      </c>
+      <c r="AI4" s="15">
+        <f>AH4-D4</f>
+        <v>1169.03</v>
+      </c>
+      <c r="AJ4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK4" s="15">
+        <v>787.92</v>
+      </c>
+      <c r="AL4" s="1">
         <v>200</v>
       </c>
-      <c r="AK4" s="1">
+      <c r="AM4" s="1">
         <v>1.6</v>
       </c>
-      <c r="AL4" s="1">
+      <c r="AN4" s="1">
         <v>172501</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
-      <c r="A5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:40">
+      <c r="A5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2">
-        <v>1754.54</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="C5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4105.48</v>
+      </c>
+      <c r="E5" s="6">
         <f>F5-D5</f>
-        <v>53.3700000000001</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1807.91</v>
-      </c>
-      <c r="G5" s="2">
+        <v>181.21</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4286.69</v>
+      </c>
+      <c r="G5" s="6">
         <f>H5-F5</f>
-        <v>90.24</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1898.15</v>
-      </c>
-      <c r="I5" s="2">
+        <v>139.09</v>
+      </c>
+      <c r="H5" s="6">
+        <v>4425.78</v>
+      </c>
+      <c r="I5" s="6">
         <f>J5-H5</f>
-        <v>90.3799999999999</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1988.53</v>
-      </c>
-      <c r="K5" s="2">
+        <v>54.8800000000001</v>
+      </c>
+      <c r="J5" s="6">
+        <v>4480.66</v>
+      </c>
+      <c r="K5" s="6">
         <f>L5-J5</f>
-        <v>59.7099999999998</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2048.24</v>
-      </c>
-      <c r="M5" s="2">
+        <v>104.900000000001</v>
+      </c>
+      <c r="L5" s="6">
+        <v>4585.56</v>
+      </c>
+      <c r="M5" s="6">
         <f>N5-L5</f>
-        <v>153.99</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2202.23</v>
-      </c>
-      <c r="O5" s="2">
+        <v>70.29</v>
+      </c>
+      <c r="N5" s="6">
+        <v>4655.85</v>
+      </c>
+      <c r="O5" s="6">
         <f>P5-N5</f>
-        <v>64.21</v>
-      </c>
-      <c r="P5" s="2">
-        <v>2266.44</v>
-      </c>
-      <c r="Q5" s="2">
+        <v>49.1700000000001</v>
+      </c>
+      <c r="P5" s="6">
+        <v>4705.02</v>
+      </c>
+      <c r="Q5" s="6">
         <f>R5-P5</f>
-        <v>47.5599999999999</v>
-      </c>
-      <c r="R5" s="2">
-        <v>2314</v>
-      </c>
-      <c r="S5" s="2">
+        <v>38.2199999999993</v>
+      </c>
+      <c r="R5" s="6">
+        <v>4743.24</v>
+      </c>
+      <c r="S5" s="6">
         <f>T5-R5</f>
-        <v>59.6500000000001</v>
-      </c>
-      <c r="T5" s="2">
-        <v>2373.65</v>
-      </c>
-      <c r="U5" s="2">
+        <v>45.6199999999999</v>
+      </c>
+      <c r="T5" s="6">
+        <v>4788.86</v>
+      </c>
+      <c r="U5" s="6">
         <f>V5-T5</f>
-        <v>70.6399999999999</v>
-      </c>
-      <c r="V5" s="10">
-        <v>2444.29</v>
-      </c>
-      <c r="W5" s="2">
+        <v>27.5900000000001</v>
+      </c>
+      <c r="V5" s="8">
+        <v>4816.45</v>
+      </c>
+      <c r="W5" s="6">
         <f>X5-V5</f>
-        <v>95.9299999999998</v>
-      </c>
-      <c r="X5" s="10">
-        <v>2540.22</v>
-      </c>
-      <c r="Y5" s="2">
+        <v>158.22</v>
+      </c>
+      <c r="X5" s="8">
+        <v>4974.67</v>
+      </c>
+      <c r="Y5" s="6">
         <f>Z5-X5</f>
-        <v>90.3200000000002</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>2630.54</v>
-      </c>
-      <c r="AA5" s="2">
+        <v>32.8999999999996</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>5007.57</v>
+      </c>
+      <c r="AA5" s="6">
         <f>AB5-Z5</f>
-        <v>69.7800000000002</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>2700.32</v>
-      </c>
-      <c r="AC5" s="2">
+        <v>19.5700000000006</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>5027.14</v>
+      </c>
+      <c r="AC5" s="6">
         <f>AD5-AB5</f>
-        <v>57.52</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>2757.84</v>
-      </c>
-      <c r="AE5" s="15">
+        <v>77.6899999999996</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>5104.83</v>
+      </c>
+      <c r="AE5" s="13">
         <f>AF5-AD5</f>
-        <v>217.06</v>
-      </c>
-      <c r="AF5" s="15">
-        <v>2974.9</v>
-      </c>
-      <c r="AG5" s="15">
-        <f>AF5-D5</f>
-        <v>1220.36</v>
-      </c>
-      <c r="AH5" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI5" s="15">
-        <v>540.87</v>
-      </c>
-      <c r="AJ5" s="2">
-        <v>300</v>
-      </c>
-      <c r="AK5" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="AL5" s="2">
-        <v>132783</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38">
+        <v>27.4499999999998</v>
+      </c>
+      <c r="AF5" s="13">
+        <v>5132.28</v>
+      </c>
+      <c r="AG5" s="13">
+        <f>AH5-AF5</f>
+        <v>129.35</v>
+      </c>
+      <c r="AH5" s="13">
+        <v>5261.63</v>
+      </c>
+      <c r="AI5" s="13">
+        <f>AH5-D5</f>
+        <v>1156.15</v>
+      </c>
+      <c r="AJ5" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK5" s="13">
+        <v>1601.02</v>
+      </c>
+      <c r="AL5" s="6">
+        <v>400</v>
+      </c>
+      <c r="AM5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="AN5" s="6">
+        <v>186759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2">
         <v>1966.62</v>
@@ -2142,14 +2179,14 @@
         <f>V6-T6</f>
         <v>88.2600000000002</v>
       </c>
-      <c r="V6" s="10">
+      <c r="V6" s="9">
         <v>2475.48</v>
       </c>
       <c r="W6" s="2">
         <f>X6-V6</f>
         <v>67.5900000000001</v>
       </c>
-      <c r="X6" s="10">
+      <c r="X6" s="9">
         <v>2543.07</v>
       </c>
       <c r="Y6" s="2">
@@ -2173,304 +2210,325 @@
       <c r="AD6" s="2">
         <v>2763.16</v>
       </c>
-      <c r="AE6" s="15">
+      <c r="AE6" s="14">
         <f>AF6-AD6</f>
         <v>70.9100000000003</v>
       </c>
-      <c r="AF6" s="15">
+      <c r="AF6" s="14">
         <v>2834.07</v>
       </c>
-      <c r="AG6" s="15">
-        <f>AF6-D6</f>
-        <v>867.45</v>
-      </c>
-      <c r="AH6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI6" s="15">
-        <v>1115.27</v>
-      </c>
-      <c r="AJ6" s="2">
+      <c r="AG6" s="14">
+        <f>AH6-AF6</f>
+        <v>94.4299999999998</v>
+      </c>
+      <c r="AH6" s="14">
+        <v>2928.5</v>
+      </c>
+      <c r="AI6" s="14">
+        <f>AH6-D6</f>
+        <v>961.88</v>
+      </c>
+      <c r="AJ6" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK6" s="14">
+        <v>1112.22</v>
+      </c>
+      <c r="AL6" s="2">
         <v>65</v>
       </c>
-      <c r="AK6" s="2">
+      <c r="AM6" s="2">
         <v>1.2</v>
       </c>
-      <c r="AL6" s="2">
+      <c r="AN6" s="2">
         <v>130589</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2">
-        <v>2136.24</v>
+        <v>1350.52</v>
       </c>
       <c r="E7" s="2">
         <f>F7-D7</f>
-        <v>40.8200000000002</v>
+        <v>52.6800000000001</v>
       </c>
       <c r="F7" s="2">
-        <v>2177.06</v>
+        <v>1403.2</v>
       </c>
       <c r="G7" s="2">
         <f>H7-F7</f>
-        <v>62.5999999999999</v>
+        <v>55.3199999999999</v>
       </c>
       <c r="H7" s="2">
-        <v>2239.66</v>
+        <v>1458.52</v>
       </c>
       <c r="I7" s="2">
         <f>J7-H7</f>
-        <v>47.0700000000002</v>
+        <v>32.6800000000001</v>
       </c>
       <c r="J7" s="2">
-        <v>2286.73</v>
+        <v>1491.2</v>
       </c>
       <c r="K7" s="2">
         <f>L7-J7</f>
-        <v>25.52</v>
+        <v>54.96</v>
       </c>
       <c r="L7" s="2">
-        <v>2312.25</v>
+        <v>1546.16</v>
       </c>
       <c r="M7" s="2">
         <f>N7-L7</f>
-        <v>36.7800000000002</v>
+        <v>92.1299999999999</v>
       </c>
       <c r="N7" s="2">
-        <v>2349.03</v>
+        <v>1638.29</v>
       </c>
       <c r="O7" s="2">
         <f>P7-N7</f>
-        <v>-18.02</v>
+        <v>59.4400000000001</v>
       </c>
       <c r="P7" s="2">
-        <v>2331.01</v>
+        <v>1697.73</v>
       </c>
       <c r="Q7" s="2">
         <f>R7-P7</f>
-        <v>62.7599999999998</v>
+        <v>71.3399999999999</v>
       </c>
       <c r="R7" s="2">
-        <v>2393.77</v>
+        <v>1769.07</v>
       </c>
       <c r="S7" s="2">
         <f>T7-R7</f>
-        <v>55.5599999999999</v>
+        <v>62.9000000000001</v>
       </c>
       <c r="T7" s="2">
-        <v>2449.33</v>
+        <v>1831.97</v>
       </c>
       <c r="U7" s="2">
         <f>V7-T7</f>
-        <v>31.96</v>
-      </c>
-      <c r="V7" s="10">
-        <v>2481.29</v>
+        <v>66.5899999999999</v>
+      </c>
+      <c r="V7" s="9">
+        <v>1898.56</v>
       </c>
       <c r="W7" s="2">
         <f>X7-V7</f>
-        <v>109.47</v>
-      </c>
-      <c r="X7" s="10">
-        <v>2590.76</v>
+        <v>48.77</v>
+      </c>
+      <c r="X7" s="9">
+        <v>1947.33</v>
       </c>
       <c r="Y7" s="2">
         <f>Z7-X7</f>
-        <v>20.4299999999998</v>
+        <v>59.47</v>
       </c>
       <c r="Z7" s="2">
-        <v>2611.19</v>
+        <v>2006.8</v>
       </c>
       <c r="AA7" s="2">
         <f>AB7-Z7</f>
-        <v>32.9899999999998</v>
+        <v>82.3900000000001</v>
       </c>
       <c r="AB7" s="2">
-        <v>2644.18</v>
+        <v>2089.19</v>
       </c>
       <c r="AC7" s="2">
         <f>AD7-AB7</f>
-        <v>45.9000000000001</v>
+        <v>98.8200000000002</v>
       </c>
       <c r="AD7" s="2">
-        <v>2690.08</v>
-      </c>
-      <c r="AE7" s="15">
+        <v>2188.01</v>
+      </c>
+      <c r="AE7" s="14">
         <f>AF7-AD7</f>
-        <v>62.79</v>
-      </c>
-      <c r="AF7" s="15">
-        <v>2752.87</v>
-      </c>
-      <c r="AG7" s="15">
-        <f>AF7-D7</f>
-        <v>616.63</v>
-      </c>
-      <c r="AH7" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI7" s="15">
-        <v>945.47</v>
-      </c>
-      <c r="AJ7" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="AL7" s="2">
-        <v>153852</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38">
+        <v>16.2299999999996</v>
+      </c>
+      <c r="AF7" s="14">
+        <v>2204.24</v>
+      </c>
+      <c r="AG7" s="14">
+        <f>AH7-AF7</f>
+        <v>95.3900000000003</v>
+      </c>
+      <c r="AH7" s="14">
+        <v>2299.63</v>
+      </c>
+      <c r="AI7" s="14">
+        <f>AH7-D7</f>
+        <v>949.11</v>
+      </c>
+      <c r="AJ7" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK7" s="14">
+        <v>698.67</v>
+      </c>
+      <c r="AL7" s="5">
+        <v>65</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AN7" s="5">
+        <v>127603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2">
-        <v>2183.01</v>
+        <v>1425.22</v>
       </c>
       <c r="E8" s="2">
         <f>F8-D8</f>
-        <v>24.1199999999999</v>
+        <v>64.8599999999999</v>
       </c>
       <c r="F8" s="2">
-        <v>2207.13</v>
+        <v>1490.08</v>
       </c>
       <c r="G8" s="2">
         <f>H8-F8</f>
-        <v>22.8599999999997</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2">
-        <v>2229.99</v>
+        <v>1536.08</v>
       </c>
       <c r="I8" s="2">
         <f>J8-H8</f>
-        <v>11.7800000000002</v>
+        <v>50.8500000000001</v>
       </c>
       <c r="J8" s="2">
-        <v>2241.77</v>
+        <v>1586.93</v>
       </c>
       <c r="K8" s="2">
         <f>L8-J8</f>
-        <v>13.0100000000002</v>
+        <v>86.5599999999999</v>
       </c>
       <c r="L8" s="2">
-        <v>2254.78</v>
+        <v>1673.49</v>
       </c>
       <c r="M8" s="2">
         <f>N8-L8</f>
-        <v>62.6399999999999</v>
+        <v>38.5599999999999</v>
       </c>
       <c r="N8" s="2">
-        <v>2317.42</v>
+        <v>1712.05</v>
       </c>
       <c r="O8" s="2">
         <f>P8-N8</f>
-        <v>16.27</v>
+        <v>57.0900000000001</v>
       </c>
       <c r="P8" s="2">
-        <v>2333.69</v>
+        <v>1769.14</v>
       </c>
       <c r="Q8" s="2">
         <f>R8-P8</f>
-        <v>36.5</v>
+        <v>50.8699999999999</v>
       </c>
       <c r="R8" s="2">
-        <v>2370.19</v>
+        <v>1820.01</v>
       </c>
       <c r="S8" s="2">
         <f>T8-R8</f>
-        <v>65.1900000000001</v>
+        <v>94.4300000000001</v>
       </c>
       <c r="T8" s="2">
-        <v>2435.38</v>
+        <v>1914.44</v>
       </c>
       <c r="U8" s="2">
         <f>V8-T8</f>
-        <v>31.7599999999998</v>
-      </c>
-      <c r="V8" s="10">
-        <v>2467.14</v>
+        <v>31.51</v>
+      </c>
+      <c r="V8" s="9">
+        <v>1945.95</v>
       </c>
       <c r="W8" s="2">
         <f>X8-V8</f>
-        <v>53.75</v>
-      </c>
-      <c r="X8" s="10">
-        <v>2520.89</v>
+        <v>92.5899999999999</v>
+      </c>
+      <c r="X8" s="9">
+        <v>2038.54</v>
       </c>
       <c r="Y8" s="2">
         <f>Z8-X8</f>
-        <v>24.3299999999999</v>
+        <v>48.1399999999999</v>
       </c>
       <c r="Z8" s="2">
-        <v>2545.22</v>
+        <v>2086.68</v>
       </c>
       <c r="AA8" s="2">
         <f>AB8-Z8</f>
-        <v>59.3900000000003</v>
+        <v>78.1300000000001</v>
       </c>
       <c r="AB8" s="2">
-        <v>2604.61</v>
+        <v>2164.81</v>
       </c>
       <c r="AC8" s="2">
         <f>AD8-AB8</f>
-        <v>34.0499999999997</v>
+        <v>39.8400000000001</v>
       </c>
       <c r="AD8" s="2">
-        <v>2638.66</v>
-      </c>
-      <c r="AE8" s="15">
+        <v>2204.65</v>
+      </c>
+      <c r="AE8" s="14">
         <f>AF8-AD8</f>
-        <v>63.75</v>
-      </c>
-      <c r="AF8" s="15">
-        <v>2702.41</v>
-      </c>
-      <c r="AG8" s="15">
-        <f>AF8-D8</f>
-        <v>519.4</v>
-      </c>
-      <c r="AH8" s="20" t="s">
+        <v>79.98</v>
+      </c>
+      <c r="AF8" s="14">
+        <v>2284.63</v>
+      </c>
+      <c r="AG8" s="14">
+        <f>AH8-AF8</f>
+        <v>35.54</v>
+      </c>
+      <c r="AH8" s="14">
+        <v>2320.17</v>
+      </c>
+      <c r="AI8" s="14">
+        <f>AH8-D8</f>
+        <v>894.95</v>
+      </c>
+      <c r="AJ8" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK8" s="14">
+        <v>589.03</v>
+      </c>
+      <c r="AL8" s="5">
+        <v>20</v>
+      </c>
+      <c r="AM8" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="AN8" s="5">
+        <v>106867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="AI8" s="15">
-        <v>681.42</v>
-      </c>
-      <c r="AJ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="2">
-        <v>133781</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38">
-      <c r="A9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D9" s="2">
         <v>1735.94</v>
@@ -2535,14 +2593,14 @@
         <f>V9-T9</f>
         <v>68.9400000000001</v>
       </c>
-      <c r="V9" s="10">
+      <c r="V9" s="9">
         <v>2251.59</v>
       </c>
       <c r="W9" s="2">
         <f>X9-V9</f>
         <v>72.0299999999997</v>
       </c>
-      <c r="X9" s="10">
+      <c r="X9" s="9">
         <v>2323.62</v>
       </c>
       <c r="Y9" s="2">
@@ -2566,42 +2624,49 @@
       <c r="AD9" s="2">
         <v>2442.04</v>
       </c>
-      <c r="AE9" s="15">
+      <c r="AE9" s="14">
         <f>AF9-AD9</f>
         <v>104.94</v>
       </c>
-      <c r="AF9" s="15">
+      <c r="AF9" s="14">
         <v>2546.98</v>
       </c>
-      <c r="AG9" s="15">
-        <f>AF9-D9</f>
-        <v>811.04</v>
-      </c>
-      <c r="AH9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI9" s="15">
-        <v>641.67</v>
-      </c>
-      <c r="AJ9" s="2">
+      <c r="AG9" s="14">
+        <f>AH9-AF9</f>
+        <v>38.04</v>
+      </c>
+      <c r="AH9" s="14">
+        <v>2585.02</v>
+      </c>
+      <c r="AI9" s="14">
+        <f>AH9-D9</f>
+        <v>849.08</v>
+      </c>
+      <c r="AJ9" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK9" s="14">
+        <v>674.67</v>
+      </c>
+      <c r="AL9" s="2">
         <v>80</v>
       </c>
-      <c r="AK9" s="2">
+      <c r="AM9" s="2">
         <v>7.2</v>
       </c>
-      <c r="AL9" s="2">
+      <c r="AN9" s="2">
         <v>150192</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:40">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2">
         <v>1726.42</v>
@@ -2666,14 +2731,14 @@
         <f>V10-T10</f>
         <v>43.5599999999999</v>
       </c>
-      <c r="V10" s="10">
+      <c r="V10" s="9">
         <v>2192.56</v>
       </c>
       <c r="W10" s="2">
         <f>X10-V10</f>
         <v>46.3200000000002</v>
       </c>
-      <c r="X10" s="10">
+      <c r="X10" s="9">
         <v>2238.88</v>
       </c>
       <c r="Y10" s="2">
@@ -2697,1221 +2762,1291 @@
       <c r="AD10" s="2">
         <v>2412.55</v>
       </c>
-      <c r="AE10" s="15">
+      <c r="AE10" s="14">
         <f>AF10-AD10</f>
         <v>33.52</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AF10" s="14">
         <v>2446.07</v>
       </c>
-      <c r="AG10" s="15">
-        <f>AF10-D10</f>
-        <v>719.65</v>
-      </c>
-      <c r="AH10" s="20" t="s">
+      <c r="AG10" s="14">
+        <f>AH10-AF10</f>
+        <v>77.4199999999996</v>
+      </c>
+      <c r="AH10" s="14">
+        <v>2523.49</v>
+      </c>
+      <c r="AI10" s="14">
+        <f>AH10-D10</f>
+        <v>797.07</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK10" s="14">
+        <v>632.92</v>
+      </c>
+      <c r="AL10" s="2">
         <v>50</v>
       </c>
-      <c r="AI10" s="15">
-        <v>603.17</v>
-      </c>
-      <c r="AJ10" s="2">
-        <v>50</v>
-      </c>
-      <c r="AK10" s="2">
+      <c r="AM10" s="2">
         <v>1.3</v>
       </c>
-      <c r="AL10" s="2">
+      <c r="AN10" s="2">
         <v>124763</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:40">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2">
-        <v>1425.22</v>
+        <v>1446.65</v>
       </c>
       <c r="E11" s="2">
         <f>F11-D11</f>
-        <v>64.8599999999999</v>
+        <v>28.1799999999998</v>
       </c>
       <c r="F11" s="2">
-        <v>1490.08</v>
+        <v>1474.83</v>
       </c>
       <c r="G11" s="2">
         <f>H11-F11</f>
-        <v>46</v>
+        <v>63.8200000000002</v>
       </c>
       <c r="H11" s="2">
-        <v>1536.08</v>
+        <v>1538.65</v>
       </c>
       <c r="I11" s="2">
         <f>J11-H11</f>
-        <v>50.8500000000001</v>
+        <v>22.9199999999998</v>
       </c>
       <c r="J11" s="2">
-        <v>1586.93</v>
+        <v>1561.57</v>
       </c>
       <c r="K11" s="2">
         <f>L11-J11</f>
-        <v>86.5599999999999</v>
+        <v>70.8600000000001</v>
       </c>
       <c r="L11" s="2">
-        <v>1673.49</v>
+        <v>1632.43</v>
       </c>
       <c r="M11" s="2">
         <f>N11-L11</f>
-        <v>38.5599999999999</v>
+        <v>37.4099999999999</v>
       </c>
       <c r="N11" s="2">
-        <v>1712.05</v>
+        <v>1669.84</v>
       </c>
       <c r="O11" s="2">
         <f>P11-N11</f>
-        <v>57.0900000000001</v>
+        <v>32.8300000000002</v>
       </c>
       <c r="P11" s="2">
-        <v>1769.14</v>
+        <v>1702.67</v>
       </c>
       <c r="Q11" s="2">
         <f>R11-P11</f>
-        <v>50.8699999999999</v>
+        <v>51.9499999999998</v>
       </c>
       <c r="R11" s="2">
-        <v>1820.01</v>
+        <v>1754.62</v>
       </c>
       <c r="S11" s="2">
         <f>T11-R11</f>
-        <v>94.4300000000001</v>
+        <v>40.1200000000001</v>
       </c>
       <c r="T11" s="2">
-        <v>1914.44</v>
+        <v>1794.74</v>
       </c>
       <c r="U11" s="2">
         <f>V11-T11</f>
-        <v>31.51</v>
-      </c>
-      <c r="V11" s="10">
-        <v>1945.95</v>
+        <v>77.5</v>
+      </c>
+      <c r="V11" s="9">
+        <v>1872.24</v>
       </c>
       <c r="W11" s="2">
         <f>X11-V11</f>
-        <v>92.5899999999999</v>
-      </c>
-      <c r="X11" s="10">
-        <v>2038.54</v>
+        <v>79.5899999999999</v>
+      </c>
+      <c r="X11" s="9">
+        <v>1951.83</v>
       </c>
       <c r="Y11" s="2">
         <f>Z11-X11</f>
-        <v>48.1399999999999</v>
+        <v>9.01999999999998</v>
       </c>
       <c r="Z11" s="2">
-        <v>2086.68</v>
+        <v>1960.85</v>
       </c>
       <c r="AA11" s="2">
         <f>AB11-Z11</f>
-        <v>78.1300000000001</v>
+        <v>74</v>
       </c>
       <c r="AB11" s="2">
-        <v>2164.81</v>
+        <v>2034.85</v>
       </c>
       <c r="AC11" s="2">
         <f>AD11-AB11</f>
-        <v>39.8400000000001</v>
+        <v>31.8000000000002</v>
       </c>
       <c r="AD11" s="2">
-        <v>2204.65</v>
-      </c>
-      <c r="AE11" s="15">
+        <v>2066.65</v>
+      </c>
+      <c r="AE11" s="14">
         <f>AF11-AD11</f>
-        <v>79.98</v>
-      </c>
-      <c r="AF11" s="15">
-        <v>2284.63</v>
-      </c>
-      <c r="AG11" s="15">
-        <f>AF11-D11</f>
-        <v>859.41</v>
-      </c>
-      <c r="AH11" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI11" s="15">
-        <v>544.87</v>
-      </c>
-      <c r="AJ11" s="5">
-        <v>20</v>
-      </c>
-      <c r="AK11" s="5">
-        <v>1.1</v>
+        <v>107.43</v>
+      </c>
+      <c r="AF11" s="14">
+        <v>2174.08</v>
+      </c>
+      <c r="AG11" s="14">
+        <f>AH11-AF11</f>
+        <v>53.3499999999999</v>
+      </c>
+      <c r="AH11" s="14">
+        <v>2227.43</v>
+      </c>
+      <c r="AI11" s="14">
+        <f>AH11-D11</f>
+        <v>780.78</v>
+      </c>
+      <c r="AJ11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK11" s="14">
+        <v>864.97</v>
       </c>
       <c r="AL11" s="5">
-        <v>106867</v>
-      </c>
-    </row>
-    <row r="12" spans="1:38">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1350.52</v>
-      </c>
-      <c r="E12" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM11" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="AN11" s="5">
+        <v>109333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1156.57</v>
+      </c>
+      <c r="E12" s="5">
         <f>F12-D12</f>
-        <v>52.6800000000001</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1403.2</v>
-      </c>
-      <c r="G12" s="2">
+        <v>40.4400000000001</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1197.01</v>
+      </c>
+      <c r="G12" s="5">
         <f>H12-F12</f>
-        <v>55.3199999999999</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1458.52</v>
-      </c>
-      <c r="I12" s="2">
+        <v>46.97</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1243.98</v>
+      </c>
+      <c r="I12" s="5">
         <f>J12-H12</f>
-        <v>32.6800000000001</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1491.2</v>
-      </c>
-      <c r="K12" s="2">
+        <v>58.49</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1302.47</v>
+      </c>
+      <c r="K12" s="5">
         <f>L12-J12</f>
-        <v>54.96</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1546.16</v>
-      </c>
-      <c r="M12" s="2">
+        <v>36.6399999999999</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1339.11</v>
+      </c>
+      <c r="M12" s="5">
         <f>N12-L12</f>
-        <v>92.1299999999999</v>
-      </c>
-      <c r="N12" s="2">
-        <v>1638.29</v>
-      </c>
-      <c r="O12" s="2">
+        <v>33.99</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1373.1</v>
+      </c>
+      <c r="O12" s="5">
         <f>P12-N12</f>
-        <v>59.4400000000001</v>
-      </c>
-      <c r="P12" s="2">
-        <v>1697.73</v>
-      </c>
-      <c r="Q12" s="2">
+        <v>30.0600000000002</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1403.16</v>
+      </c>
+      <c r="Q12" s="5">
         <f>R12-P12</f>
-        <v>71.3399999999999</v>
-      </c>
-      <c r="R12" s="2">
-        <v>1769.07</v>
-      </c>
-      <c r="S12" s="2">
+        <v>47.3</v>
+      </c>
+      <c r="R12" s="5">
+        <v>1450.46</v>
+      </c>
+      <c r="S12" s="5">
         <f>T12-R12</f>
-        <v>62.9000000000001</v>
-      </c>
-      <c r="T12" s="2">
-        <v>1831.97</v>
-      </c>
-      <c r="U12" s="2">
+        <v>46.8299999999999</v>
+      </c>
+      <c r="T12" s="5">
+        <v>1497.29</v>
+      </c>
+      <c r="U12" s="5">
         <f>V12-T12</f>
-        <v>66.5899999999999</v>
-      </c>
-      <c r="V12" s="10">
-        <v>1898.56</v>
-      </c>
-      <c r="W12" s="2">
+        <v>58.6500000000001</v>
+      </c>
+      <c r="V12" s="11">
+        <v>1555.94</v>
+      </c>
+      <c r="W12" s="5">
         <f>X12-V12</f>
-        <v>48.77</v>
-      </c>
-      <c r="X12" s="10">
-        <v>1947.33</v>
-      </c>
-      <c r="Y12" s="2">
+        <v>70.3099999999999</v>
+      </c>
+      <c r="X12" s="11">
+        <v>1626.25</v>
+      </c>
+      <c r="Y12" s="5">
         <f>Z12-X12</f>
-        <v>59.47</v>
-      </c>
-      <c r="Z12" s="2">
-        <v>2006.8</v>
-      </c>
-      <c r="AA12" s="2">
+        <v>31.49</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>1657.74</v>
+      </c>
+      <c r="AA12" s="5">
         <f>AB12-Z12</f>
-        <v>82.3900000000001</v>
-      </c>
-      <c r="AB12" s="2">
-        <v>2089.19</v>
-      </c>
-      <c r="AC12" s="2">
+        <v>59.21</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>1716.95</v>
+      </c>
+      <c r="AC12" s="5">
         <f>AD12-AB12</f>
-        <v>98.8200000000002</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>2188.01</v>
-      </c>
-      <c r="AE12" s="15">
+        <v>31.99</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>1748.94</v>
+      </c>
+      <c r="AE12" s="16">
         <f>AF12-AD12</f>
-        <v>16.2299999999996</v>
-      </c>
-      <c r="AF12" s="15">
-        <v>2204.24</v>
-      </c>
-      <c r="AG12" s="15">
-        <f>AF12-D12</f>
-        <v>853.72</v>
-      </c>
-      <c r="AH12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI12" s="15">
-        <v>678.17</v>
-      </c>
-      <c r="AJ12" s="5">
-        <v>65</v>
-      </c>
-      <c r="AK12" s="5">
-        <v>1.4</v>
+        <v>52.0999999999999</v>
+      </c>
+      <c r="AF12" s="16">
+        <v>1801.04</v>
+      </c>
+      <c r="AG12" s="16">
+        <f>AH12-AF12</f>
+        <v>74.74</v>
+      </c>
+      <c r="AH12" s="16">
+        <v>1875.78</v>
+      </c>
+      <c r="AI12" s="16">
+        <f>AH12-D12</f>
+        <v>719.21</v>
+      </c>
+      <c r="AJ12" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK12" s="16">
+        <v>508.72</v>
       </c>
       <c r="AL12" s="5">
-        <v>127603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:38">
+        <v>25</v>
+      </c>
+      <c r="AM12" s="5">
+        <v>3</v>
+      </c>
+      <c r="AN12" s="5">
+        <v>100457</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2">
-        <v>1446.65</v>
+        <v>1349.35</v>
       </c>
       <c r="E13" s="2">
         <f>F13-D13</f>
-        <v>28.1799999999998</v>
+        <v>49.6200000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>1474.83</v>
+        <v>1398.97</v>
       </c>
       <c r="G13" s="2">
         <f>H13-F13</f>
-        <v>63.8200000000002</v>
+        <v>27.79</v>
       </c>
       <c r="H13" s="2">
-        <v>1538.65</v>
+        <v>1426.76</v>
       </c>
       <c r="I13" s="2">
         <f>J13-H13</f>
-        <v>22.9199999999998</v>
+        <v>29.02</v>
       </c>
       <c r="J13" s="2">
-        <v>1561.57</v>
+        <v>1455.78</v>
       </c>
       <c r="K13" s="2">
         <f>L13-J13</f>
-        <v>70.8600000000001</v>
+        <v>97.8800000000001</v>
       </c>
       <c r="L13" s="2">
-        <v>1632.43</v>
+        <v>1553.66</v>
       </c>
       <c r="M13" s="2">
         <f>N13-L13</f>
-        <v>37.4099999999999</v>
+        <v>42.3599999999999</v>
       </c>
       <c r="N13" s="2">
-        <v>1669.84</v>
+        <v>1596.02</v>
       </c>
       <c r="O13" s="2">
         <f>P13-N13</f>
-        <v>32.8300000000002</v>
+        <v>54.22</v>
       </c>
       <c r="P13" s="2">
-        <v>1702.67</v>
+        <v>1650.24</v>
       </c>
       <c r="Q13" s="2">
         <f>R13-P13</f>
-        <v>51.9499999999998</v>
+        <v>35.5899999999999</v>
       </c>
       <c r="R13" s="2">
-        <v>1754.62</v>
+        <v>1685.83</v>
       </c>
       <c r="S13" s="2">
         <f>T13-R13</f>
-        <v>40.1200000000001</v>
+        <v>68.1300000000001</v>
       </c>
       <c r="T13" s="2">
-        <v>1794.74</v>
+        <v>1753.96</v>
       </c>
       <c r="U13" s="2">
         <f>V13-T13</f>
-        <v>77.5</v>
-      </c>
-      <c r="V13" s="10">
-        <v>1872.24</v>
+        <v>58.5599999999999</v>
+      </c>
+      <c r="V13" s="9">
+        <v>1812.52</v>
       </c>
       <c r="W13" s="2">
         <f>X13-V13</f>
-        <v>79.5899999999999</v>
-      </c>
-      <c r="X13" s="10">
-        <v>1951.83</v>
+        <v>67.21</v>
+      </c>
+      <c r="X13" s="9">
+        <v>1879.73</v>
       </c>
       <c r="Y13" s="2">
         <f>Z13-X13</f>
-        <v>9.01999999999998</v>
+        <v>20.22</v>
       </c>
       <c r="Z13" s="2">
-        <v>1960.85</v>
+        <v>1899.95</v>
       </c>
       <c r="AA13" s="2">
         <f>AB13-Z13</f>
-        <v>74</v>
+        <v>35.0999999999999</v>
       </c>
       <c r="AB13" s="2">
-        <v>2034.85</v>
+        <v>1935.05</v>
       </c>
       <c r="AC13" s="2">
         <f>AD13-AB13</f>
-        <v>31.8000000000002</v>
+        <v>44.73</v>
       </c>
       <c r="AD13" s="2">
-        <v>2066.65</v>
-      </c>
-      <c r="AE13" s="15">
+        <v>1979.78</v>
+      </c>
+      <c r="AE13" s="14">
         <f>AF13-AD13</f>
-        <v>107.43</v>
-      </c>
-      <c r="AF13" s="15">
-        <v>2174.08</v>
-      </c>
-      <c r="AG13" s="15">
-        <f>AF13-D13</f>
-        <v>727.43</v>
-      </c>
-      <c r="AH13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI13" s="15">
-        <v>834.42</v>
-      </c>
-      <c r="AJ13" s="5">
-        <v>65</v>
-      </c>
-      <c r="AK13" s="5">
-        <v>1.4</v>
+        <v>31.1700000000001</v>
+      </c>
+      <c r="AF13" s="14">
+        <v>2010.95</v>
+      </c>
+      <c r="AG13" s="14">
+        <f>AH13-AF13</f>
+        <v>51.4100000000001</v>
+      </c>
+      <c r="AH13" s="14">
+        <v>2062.36</v>
+      </c>
+      <c r="AI13" s="14">
+        <f>AH13-D13</f>
+        <v>713.01</v>
+      </c>
+      <c r="AJ13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK13" s="14">
+        <v>498.45</v>
       </c>
       <c r="AL13" s="5">
-        <v>109333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38">
-      <c r="A14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1576.18</v>
-      </c>
-      <c r="E14" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM13" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AN13" s="5">
+        <v>109106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1060.77</v>
+      </c>
+      <c r="E14" s="5">
         <f>F14-D14</f>
-        <v>38.8399999999999</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1615.02</v>
-      </c>
-      <c r="G14" s="2">
+        <v>63.24</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1124.01</v>
+      </c>
+      <c r="G14" s="5">
         <f>H14-F14</f>
-        <v>35.5999999999999</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1650.62</v>
-      </c>
-      <c r="I14" s="2">
+        <v>19.6700000000001</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1143.68</v>
+      </c>
+      <c r="I14" s="5">
         <f>J14-H14</f>
-        <v>37.47</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1688.09</v>
-      </c>
-      <c r="K14" s="2">
+        <v>47.76</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1191.44</v>
+      </c>
+      <c r="K14" s="5">
         <f>L14-J14</f>
-        <v>21.49</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1709.58</v>
-      </c>
-      <c r="M14" s="2">
+        <v>40.22</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1231.66</v>
+      </c>
+      <c r="M14" s="5">
         <f>N14-L14</f>
-        <v>24.53</v>
-      </c>
-      <c r="N14" s="2">
-        <v>1734.11</v>
-      </c>
-      <c r="O14" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1276.46</v>
+      </c>
+      <c r="O14" s="5">
         <f>P14-N14</f>
-        <v>19.5300000000002</v>
-      </c>
-      <c r="P14" s="2">
-        <v>1753.64</v>
-      </c>
-      <c r="Q14" s="2">
+        <v>28.03</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1304.49</v>
+      </c>
+      <c r="Q14" s="5">
         <f>R14-P14</f>
-        <v>65.1099999999999</v>
-      </c>
-      <c r="R14" s="2">
-        <v>1818.75</v>
-      </c>
-      <c r="S14" s="2">
+        <v>31.78</v>
+      </c>
+      <c r="R14" s="5">
+        <v>1336.27</v>
+      </c>
+      <c r="S14" s="5">
         <f>T14-R14</f>
-        <v>34.3699999999999</v>
-      </c>
-      <c r="T14" s="2">
-        <v>1853.12</v>
-      </c>
-      <c r="U14" s="2">
+        <v>44.9000000000001</v>
+      </c>
+      <c r="T14" s="5">
+        <v>1381.17</v>
+      </c>
+      <c r="U14" s="5">
         <f>V14-T14</f>
-        <v>40.8400000000001</v>
-      </c>
-      <c r="V14" s="10">
-        <v>1893.96</v>
-      </c>
-      <c r="W14" s="2">
+        <v>53.1499999999999</v>
+      </c>
+      <c r="V14" s="11">
+        <v>1434.32</v>
+      </c>
+      <c r="W14" s="5">
         <f>X14-V14</f>
-        <v>40.96</v>
-      </c>
-      <c r="X14" s="10">
-        <v>1934.92</v>
-      </c>
-      <c r="Y14" s="2">
+        <v>41.46</v>
+      </c>
+      <c r="X14" s="11">
+        <v>1475.78</v>
+      </c>
+      <c r="Y14" s="5">
         <f>Z14-X14</f>
-        <v>59.05</v>
-      </c>
-      <c r="Z14" s="2">
-        <v>1993.97</v>
-      </c>
-      <c r="AA14" s="2">
+        <v>38.55</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>1514.33</v>
+      </c>
+      <c r="AA14" s="5">
         <f>AB14-Z14</f>
-        <v>58.4799999999998</v>
-      </c>
-      <c r="AB14" s="2">
-        <v>2052.45</v>
-      </c>
-      <c r="AC14" s="2">
+        <v>85.23</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>1599.56</v>
+      </c>
+      <c r="AC14" s="5">
         <f>AD14-AB14</f>
-        <v>26.7400000000002</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>2079.19</v>
-      </c>
-      <c r="AE14" s="15">
+        <v>73.21</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>1672.77</v>
+      </c>
+      <c r="AE14" s="16">
         <f>AF14-AD14</f>
-        <v>34.79</v>
-      </c>
-      <c r="AF14" s="15">
-        <v>2113.98</v>
-      </c>
-      <c r="AG14" s="15">
-        <f>AF14-D14</f>
-        <v>537.8</v>
-      </c>
-      <c r="AH14" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI14" s="15">
-        <v>528.52</v>
-      </c>
-      <c r="AJ14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="5">
-        <v>0</v>
+        <v>43.3600000000001</v>
+      </c>
+      <c r="AF14" s="16">
+        <v>1716.13</v>
+      </c>
+      <c r="AG14" s="16">
+        <f>AH14-AF14</f>
+        <v>52.6399999999999</v>
+      </c>
+      <c r="AH14" s="16">
+        <v>1768.77</v>
+      </c>
+      <c r="AI14" s="16">
+        <f>AH14-D14</f>
+        <v>708</v>
+      </c>
+      <c r="AJ14" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK14" s="16">
+        <v>345.63</v>
       </c>
       <c r="AL14" s="5">
-        <v>127369</v>
-      </c>
-    </row>
-    <row r="15" spans="1:38">
+        <v>10</v>
+      </c>
+      <c r="AM14" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" s="5">
+        <v>71153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2">
-        <v>1349.35</v>
+        <v>2136.24</v>
       </c>
       <c r="E15" s="2">
         <f>F15-D15</f>
-        <v>49.6200000000001</v>
+        <v>40.8200000000002</v>
       </c>
       <c r="F15" s="2">
-        <v>1398.97</v>
+        <v>2177.06</v>
       </c>
       <c r="G15" s="2">
         <f>H15-F15</f>
-        <v>27.79</v>
+        <v>62.5999999999999</v>
       </c>
       <c r="H15" s="2">
-        <v>1426.76</v>
+        <v>2239.66</v>
       </c>
       <c r="I15" s="2">
         <f>J15-H15</f>
-        <v>29.02</v>
+        <v>47.0700000000002</v>
       </c>
       <c r="J15" s="2">
-        <v>1455.78</v>
+        <v>2286.73</v>
       </c>
       <c r="K15" s="2">
         <f>L15-J15</f>
-        <v>97.8800000000001</v>
+        <v>25.52</v>
       </c>
       <c r="L15" s="2">
-        <v>1553.66</v>
+        <v>2312.25</v>
       </c>
       <c r="M15" s="2">
         <f>N15-L15</f>
-        <v>42.3599999999999</v>
+        <v>36.7800000000002</v>
       </c>
       <c r="N15" s="2">
-        <v>1596.02</v>
+        <v>2349.03</v>
       </c>
       <c r="O15" s="2">
         <f>P15-N15</f>
-        <v>54.22</v>
+        <v>-18.02</v>
       </c>
       <c r="P15" s="2">
-        <v>1650.24</v>
+        <v>2331.01</v>
       </c>
       <c r="Q15" s="2">
         <f>R15-P15</f>
-        <v>35.5899999999999</v>
+        <v>62.7599999999998</v>
       </c>
       <c r="R15" s="2">
-        <v>1685.83</v>
+        <v>2393.77</v>
       </c>
       <c r="S15" s="2">
         <f>T15-R15</f>
-        <v>68.1300000000001</v>
+        <v>55.5599999999999</v>
       </c>
       <c r="T15" s="2">
-        <v>1753.96</v>
+        <v>2449.33</v>
       </c>
       <c r="U15" s="2">
         <f>V15-T15</f>
-        <v>58.5599999999999</v>
-      </c>
-      <c r="V15" s="10">
-        <v>1812.52</v>
+        <v>31.96</v>
+      </c>
+      <c r="V15" s="9">
+        <v>2481.29</v>
       </c>
       <c r="W15" s="2">
         <f>X15-V15</f>
-        <v>67.21</v>
-      </c>
-      <c r="X15" s="10">
-        <v>1879.73</v>
+        <v>109.47</v>
+      </c>
+      <c r="X15" s="9">
+        <v>2590.76</v>
       </c>
       <c r="Y15" s="2">
         <f>Z15-X15</f>
-        <v>20.22</v>
+        <v>20.4299999999998</v>
       </c>
       <c r="Z15" s="2">
-        <v>1899.95</v>
+        <v>2611.19</v>
       </c>
       <c r="AA15" s="2">
         <f>AB15-Z15</f>
-        <v>35.0999999999999</v>
+        <v>32.9899999999998</v>
       </c>
       <c r="AB15" s="2">
-        <v>1935.05</v>
+        <v>2644.18</v>
       </c>
       <c r="AC15" s="2">
         <f>AD15-AB15</f>
-        <v>44.73</v>
+        <v>45.9000000000001</v>
       </c>
       <c r="AD15" s="2">
-        <v>1979.78</v>
-      </c>
-      <c r="AE15" s="15">
+        <v>2690.08</v>
+      </c>
+      <c r="AE15" s="14">
         <f>AF15-AD15</f>
-        <v>31.1700000000001</v>
-      </c>
-      <c r="AF15" s="15">
-        <v>2010.95</v>
-      </c>
-      <c r="AG15" s="15">
-        <f>AF15-D15</f>
-        <v>661.6</v>
-      </c>
-      <c r="AH15" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI15" s="15">
-        <v>498.5</v>
-      </c>
-      <c r="AJ15" s="5">
+        <v>62.79</v>
+      </c>
+      <c r="AF15" s="14">
+        <v>2752.87</v>
+      </c>
+      <c r="AG15" s="14">
+        <f>AH15-AF15</f>
+        <v>72.2800000000002</v>
+      </c>
+      <c r="AH15" s="14">
+        <v>2825.15</v>
+      </c>
+      <c r="AI15" s="14">
+        <f>AH15-D15</f>
+        <v>688.91</v>
+      </c>
+      <c r="AJ15" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK15" s="14">
+        <v>1005.62</v>
+      </c>
+      <c r="AL15" s="2">
         <v>20</v>
       </c>
-      <c r="AK15" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="AL15" s="5">
-        <v>109106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:38">
+      <c r="AM15" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" s="2">
+        <v>153852</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
       <c r="A16" s="5" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D16" s="5">
-        <v>1156.57</v>
+        <v>953.78</v>
       </c>
       <c r="E16" s="5">
         <f>F16-D16</f>
-        <v>40.4400000000001</v>
+        <v>28.97</v>
       </c>
       <c r="F16" s="5">
-        <v>1197.01</v>
+        <v>982.75</v>
       </c>
       <c r="G16" s="5">
         <f>H16-F16</f>
-        <v>46.97</v>
+        <v>83.9300000000001</v>
       </c>
       <c r="H16" s="5">
-        <v>1243.98</v>
+        <v>1066.68</v>
       </c>
       <c r="I16" s="5">
         <f>J16-H16</f>
-        <v>58.49</v>
+        <v>42.8399999999999</v>
       </c>
       <c r="J16" s="5">
-        <v>1302.47</v>
+        <v>1109.52</v>
       </c>
       <c r="K16" s="5">
         <f>L16-J16</f>
-        <v>36.6399999999999</v>
+        <v>36.46</v>
       </c>
       <c r="L16" s="5">
-        <v>1339.11</v>
+        <v>1145.98</v>
       </c>
       <c r="M16" s="5">
         <f>N16-L16</f>
-        <v>33.99</v>
+        <v>37.49</v>
       </c>
       <c r="N16" s="5">
-        <v>1373.1</v>
+        <v>1183.47</v>
       </c>
       <c r="O16" s="5">
         <f>P16-N16</f>
-        <v>30.0600000000002</v>
+        <v>33.3699999999999</v>
       </c>
       <c r="P16" s="5">
-        <v>1403.16</v>
+        <v>1216.84</v>
       </c>
       <c r="Q16" s="5">
         <f>R16-P16</f>
-        <v>47.3</v>
+        <v>24.8900000000001</v>
       </c>
       <c r="R16" s="5">
-        <v>1450.46</v>
+        <v>1241.73</v>
       </c>
       <c r="S16" s="5">
         <f>T16-R16</f>
-        <v>46.8299999999999</v>
+        <v>42.3099999999999</v>
       </c>
       <c r="T16" s="5">
-        <v>1497.29</v>
+        <v>1284.04</v>
       </c>
       <c r="U16" s="5">
         <f>V16-T16</f>
-        <v>58.6500000000001</v>
+        <v>44.8400000000001</v>
       </c>
       <c r="V16" s="11">
-        <v>1555.94</v>
+        <v>1328.88</v>
       </c>
       <c r="W16" s="5">
         <f>X16-V16</f>
-        <v>70.3099999999999</v>
+        <v>45.9499999999998</v>
       </c>
       <c r="X16" s="11">
-        <v>1626.25</v>
+        <v>1374.83</v>
       </c>
       <c r="Y16" s="5">
         <f>Z16-X16</f>
-        <v>31.49</v>
+        <v>16.4200000000001</v>
       </c>
       <c r="Z16" s="5">
-        <v>1657.74</v>
+        <v>1391.25</v>
       </c>
       <c r="AA16" s="5">
         <f>AB16-Z16</f>
-        <v>59.21</v>
+        <v>22.0699999999999</v>
       </c>
       <c r="AB16" s="5">
-        <v>1716.95</v>
+        <v>1413.32</v>
       </c>
       <c r="AC16" s="5">
         <f>AD16-AB16</f>
-        <v>31.99</v>
+        <v>73.72</v>
       </c>
       <c r="AD16" s="5">
-        <v>1748.94</v>
+        <v>1487.04</v>
       </c>
       <c r="AE16" s="16">
         <f>AF16-AD16</f>
-        <v>52.0999999999999</v>
+        <v>48.22</v>
       </c>
       <c r="AF16" s="16">
-        <v>1801.04</v>
+        <v>1535.26</v>
       </c>
       <c r="AG16" s="16">
-        <f>AF16-D16</f>
-        <v>644.47</v>
-      </c>
-      <c r="AH16" s="21" t="s">
-        <v>60</v>
+        <f>AH16-AF16</f>
+        <v>71.02</v>
+      </c>
+      <c r="AH16" s="16">
+        <v>1606.28</v>
       </c>
       <c r="AI16" s="16">
-        <v>484.52</v>
-      </c>
-      <c r="AJ16" s="5">
-        <v>25</v>
-      </c>
-      <c r="AK16" s="5">
-        <v>3</v>
+        <f>AH16-D16</f>
+        <v>652.5</v>
+      </c>
+      <c r="AJ16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK16" s="16">
+        <v>620.97</v>
       </c>
       <c r="AL16" s="5">
-        <v>100457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:38">
+        <v>30</v>
+      </c>
+      <c r="AM16" s="5">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="5">
+        <v>105419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5">
-        <v>1060.77</v>
+        <v>907.94</v>
       </c>
       <c r="E17" s="5">
         <f>F17-D17</f>
-        <v>63.24</v>
+        <v>64.0799999999999</v>
       </c>
       <c r="F17" s="5">
-        <v>1124.01</v>
+        <v>972.02</v>
       </c>
       <c r="G17" s="5">
         <f>H17-F17</f>
-        <v>19.6700000000001</v>
+        <v>36.26</v>
       </c>
       <c r="H17" s="5">
-        <v>1143.68</v>
+        <v>1008.28</v>
       </c>
       <c r="I17" s="5">
         <f>J17-H17</f>
-        <v>47.76</v>
+        <v>28.8</v>
       </c>
       <c r="J17" s="5">
-        <v>1191.44</v>
+        <v>1037.08</v>
       </c>
       <c r="K17" s="5">
         <f>L17-J17</f>
-        <v>40.22</v>
+        <v>40.1000000000001</v>
       </c>
       <c r="L17" s="5">
-        <v>1231.66</v>
+        <v>1077.18</v>
       </c>
       <c r="M17" s="5">
         <f>N17-L17</f>
-        <v>44.8</v>
+        <v>26.03</v>
       </c>
       <c r="N17" s="5">
-        <v>1276.46</v>
+        <v>1103.21</v>
       </c>
       <c r="O17" s="5">
         <f>P17-N17</f>
-        <v>28.03</v>
+        <v>28.3499999999999</v>
       </c>
       <c r="P17" s="5">
-        <v>1304.49</v>
+        <v>1131.56</v>
       </c>
       <c r="Q17" s="5">
         <f>R17-P17</f>
-        <v>31.78</v>
+        <v>50.1900000000001</v>
       </c>
       <c r="R17" s="5">
-        <v>1336.27</v>
+        <v>1181.75</v>
       </c>
       <c r="S17" s="5">
         <f>T17-R17</f>
-        <v>44.9000000000001</v>
+        <v>26.8699999999999</v>
       </c>
       <c r="T17" s="5">
-        <v>1381.17</v>
+        <v>1208.62</v>
       </c>
       <c r="U17" s="5">
         <f>V17-T17</f>
-        <v>53.1499999999999</v>
+        <v>58.3000000000002</v>
       </c>
       <c r="V17" s="11">
-        <v>1434.32</v>
+        <v>1266.92</v>
       </c>
       <c r="W17" s="5">
         <f>X17-V17</f>
-        <v>41.46</v>
+        <v>41.0599999999999</v>
       </c>
       <c r="X17" s="11">
-        <v>1475.78</v>
+        <v>1307.98</v>
       </c>
       <c r="Y17" s="5">
         <f>Z17-X17</f>
-        <v>38.55</v>
+        <v>31.49</v>
       </c>
       <c r="Z17" s="5">
-        <v>1514.33</v>
+        <v>1339.47</v>
       </c>
       <c r="AA17" s="5">
         <f>AB17-Z17</f>
-        <v>85.23</v>
+        <v>50.5899999999999</v>
       </c>
       <c r="AB17" s="5">
-        <v>1599.56</v>
+        <v>1390.06</v>
       </c>
       <c r="AC17" s="5">
         <f>AD17-AB17</f>
-        <v>73.21</v>
+        <v>35.8099999999999</v>
       </c>
       <c r="AD17" s="5">
-        <v>1672.77</v>
+        <v>1425.87</v>
       </c>
       <c r="AE17" s="16">
         <f>AF17-AD17</f>
-        <v>43.3600000000001</v>
+        <v>62.6300000000001</v>
       </c>
       <c r="AF17" s="16">
-        <v>1716.13</v>
+        <v>1488.5</v>
       </c>
       <c r="AG17" s="16">
-        <f>AF17-D17</f>
-        <v>655.36</v>
-      </c>
-      <c r="AH17" s="21" t="s">
-        <v>52</v>
+        <f>AH17-AF17</f>
+        <v>53.9200000000001</v>
+      </c>
+      <c r="AH17" s="16">
+        <v>1542.42</v>
       </c>
       <c r="AI17" s="16">
-        <v>344.56</v>
-      </c>
-      <c r="AJ17" s="5">
-        <v>10</v>
-      </c>
-      <c r="AK17" s="5">
-        <v>1.3</v>
+        <f>AH17-D17</f>
+        <v>634.48</v>
+      </c>
+      <c r="AJ17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK17" s="16">
+        <v>518.97</v>
       </c>
       <c r="AL17" s="5">
-        <v>71153</v>
-      </c>
-    </row>
-    <row r="18" spans="1:38">
-      <c r="A18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM17" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="AN17" s="5">
+        <v>65285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40">
+      <c r="A18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2183.01</v>
+      </c>
+      <c r="E18" s="2">
+        <f>F18-D18</f>
+        <v>24.1199999999999</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2207.13</v>
+      </c>
+      <c r="G18" s="2">
+        <f>H18-F18</f>
+        <v>22.8599999999997</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2229.99</v>
+      </c>
+      <c r="I18" s="2">
+        <f>J18-H18</f>
+        <v>11.7800000000002</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2241.77</v>
+      </c>
+      <c r="K18" s="2">
+        <f>L18-J18</f>
+        <v>13.0100000000002</v>
+      </c>
+      <c r="L18" s="2">
+        <v>2254.78</v>
+      </c>
+      <c r="M18" s="2">
+        <f>N18-L18</f>
+        <v>62.6399999999999</v>
+      </c>
+      <c r="N18" s="2">
+        <v>2317.42</v>
+      </c>
+      <c r="O18" s="2">
+        <f>P18-N18</f>
+        <v>16.27</v>
+      </c>
+      <c r="P18" s="2">
+        <v>2333.69</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>R18-P18</f>
+        <v>36.5</v>
+      </c>
+      <c r="R18" s="2">
+        <v>2370.19</v>
+      </c>
+      <c r="S18" s="2">
+        <f>T18-R18</f>
+        <v>65.1900000000001</v>
+      </c>
+      <c r="T18" s="2">
+        <v>2435.38</v>
+      </c>
+      <c r="U18" s="2">
+        <f>V18-T18</f>
+        <v>31.7599999999998</v>
+      </c>
+      <c r="V18" s="9">
+        <v>2467.14</v>
+      </c>
+      <c r="W18" s="2">
+        <f>X18-V18</f>
+        <v>53.75</v>
+      </c>
+      <c r="X18" s="9">
+        <v>2520.89</v>
+      </c>
+      <c r="Y18" s="2">
+        <f>Z18-X18</f>
+        <v>24.3299999999999</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>2545.22</v>
+      </c>
+      <c r="AA18" s="2">
+        <f>AB18-Z18</f>
+        <v>59.3900000000003</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>2604.61</v>
+      </c>
+      <c r="AC18" s="2">
+        <f>AD18-AB18</f>
+        <v>34.0499999999997</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>2638.66</v>
+      </c>
+      <c r="AE18" s="14">
+        <f>AF18-AD18</f>
+        <v>63.75</v>
+      </c>
+      <c r="AF18" s="14">
+        <v>2702.41</v>
+      </c>
+      <c r="AG18" s="14">
+        <f>AH18-AF18</f>
+        <v>98.3600000000001</v>
+      </c>
+      <c r="AH18" s="14">
+        <v>2800.77</v>
+      </c>
+      <c r="AI18" s="14">
+        <f>AH18-D18</f>
+        <v>617.76</v>
+      </c>
+      <c r="AJ18" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK18" s="14">
+        <v>680.87</v>
+      </c>
+      <c r="AL18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="2">
+        <v>133781</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40">
+      <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1576.18</v>
+      </c>
+      <c r="E19" s="2">
+        <f>F19-D19</f>
+        <v>38.8399999999999</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1615.02</v>
+      </c>
+      <c r="G19" s="2">
+        <f>H19-F19</f>
+        <v>35.5999999999999</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1650.62</v>
+      </c>
+      <c r="I19" s="2">
+        <f>J19-H19</f>
+        <v>37.47</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1688.09</v>
+      </c>
+      <c r="K19" s="2">
+        <f>L19-J19</f>
+        <v>21.49</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1709.58</v>
+      </c>
+      <c r="M19" s="2">
+        <f>N19-L19</f>
+        <v>24.53</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1734.11</v>
+      </c>
+      <c r="O19" s="2">
+        <f>P19-N19</f>
+        <v>19.5300000000002</v>
+      </c>
+      <c r="P19" s="2">
+        <v>1753.64</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>R19-P19</f>
+        <v>65.1099999999999</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1818.75</v>
+      </c>
+      <c r="S19" s="2">
+        <f>T19-R19</f>
+        <v>34.3699999999999</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1853.12</v>
+      </c>
+      <c r="U19" s="2">
+        <f>V19-T19</f>
+        <v>40.8400000000001</v>
+      </c>
+      <c r="V19" s="9">
+        <v>1893.96</v>
+      </c>
+      <c r="W19" s="2">
+        <f>X19-V19</f>
+        <v>40.96</v>
+      </c>
+      <c r="X19" s="9">
+        <v>1934.92</v>
+      </c>
+      <c r="Y19" s="2">
+        <f>Z19-X19</f>
+        <v>59.05</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>1993.97</v>
+      </c>
+      <c r="AA19" s="2">
+        <f>AB19-Z19</f>
+        <v>58.4799999999998</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>2052.45</v>
+      </c>
+      <c r="AC19" s="2">
+        <f>AD19-AB19</f>
+        <v>26.7400000000002</v>
+      </c>
+      <c r="AD19" s="2">
+        <v>2079.19</v>
+      </c>
+      <c r="AE19" s="14">
+        <f>AF19-AD19</f>
+        <v>34.79</v>
+      </c>
+      <c r="AF19" s="14">
+        <v>2113.98</v>
+      </c>
+      <c r="AG19" s="14">
+        <f>AH19-AF19</f>
+        <v>17.4400000000001</v>
+      </c>
+      <c r="AH19" s="14">
+        <v>2131.42</v>
+      </c>
+      <c r="AI19" s="14">
+        <f>AH19-D19</f>
+        <v>555.24</v>
+      </c>
+      <c r="AJ19" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="5">
-        <v>953.78</v>
-      </c>
-      <c r="E18" s="5">
-        <f>F18-D18</f>
-        <v>28.97</v>
-      </c>
-      <c r="F18" s="5">
-        <v>982.75</v>
-      </c>
-      <c r="G18" s="5">
-        <f>H18-F18</f>
-        <v>83.9300000000001</v>
-      </c>
-      <c r="H18" s="5">
-        <v>1066.68</v>
-      </c>
-      <c r="I18" s="5">
-        <f>J18-H18</f>
-        <v>42.8399999999999</v>
-      </c>
-      <c r="J18" s="5">
-        <v>1109.52</v>
-      </c>
-      <c r="K18" s="5">
-        <f>L18-J18</f>
-        <v>36.46</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1145.98</v>
-      </c>
-      <c r="M18" s="5">
-        <f>N18-L18</f>
-        <v>37.49</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1183.47</v>
-      </c>
-      <c r="O18" s="5">
-        <f>P18-N18</f>
-        <v>33.3699999999999</v>
-      </c>
-      <c r="P18" s="5">
-        <v>1216.84</v>
-      </c>
-      <c r="Q18" s="5">
-        <f>R18-P18</f>
-        <v>24.8900000000001</v>
-      </c>
-      <c r="R18" s="5">
-        <v>1241.73</v>
-      </c>
-      <c r="S18" s="5">
-        <f>T18-R18</f>
-        <v>42.3099999999999</v>
-      </c>
-      <c r="T18" s="5">
-        <v>1284.04</v>
-      </c>
-      <c r="U18" s="5">
-        <f>V18-T18</f>
-        <v>44.8400000000001</v>
-      </c>
-      <c r="V18" s="11">
-        <v>1328.88</v>
-      </c>
-      <c r="W18" s="5">
-        <f>X18-V18</f>
-        <v>45.9499999999998</v>
-      </c>
-      <c r="X18" s="11">
-        <v>1374.83</v>
-      </c>
-      <c r="Y18" s="5">
-        <f>Z18-X18</f>
-        <v>16.4200000000001</v>
-      </c>
-      <c r="Z18" s="5">
-        <v>1391.25</v>
-      </c>
-      <c r="AA18" s="5">
-        <f>AB18-Z18</f>
-        <v>22.0699999999999</v>
-      </c>
-      <c r="AB18" s="5">
-        <v>1413.32</v>
-      </c>
-      <c r="AC18" s="5">
-        <f>AD18-AB18</f>
-        <v>73.72</v>
-      </c>
-      <c r="AD18" s="5">
-        <v>1487.04</v>
-      </c>
-      <c r="AE18" s="16">
-        <f>AF18-AD18</f>
-        <v>48.22</v>
-      </c>
-      <c r="AF18" s="16">
-        <v>1535.26</v>
-      </c>
-      <c r="AG18" s="16">
-        <f>AF18-D18</f>
-        <v>581.48</v>
-      </c>
-      <c r="AH18" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI18" s="16">
-        <v>591.02</v>
-      </c>
-      <c r="AJ18" s="5">
-        <v>30</v>
-      </c>
-      <c r="AK18" s="5">
-        <v>1</v>
-      </c>
-      <c r="AL18" s="5">
-        <v>105419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:38">
-      <c r="A19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="5">
-        <v>907.94</v>
-      </c>
-      <c r="E19" s="5">
-        <f>F19-D19</f>
-        <v>64.0799999999999</v>
-      </c>
-      <c r="F19" s="5">
-        <v>972.02</v>
-      </c>
-      <c r="G19" s="5">
-        <f>H19-F19</f>
-        <v>36.26</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1008.28</v>
-      </c>
-      <c r="I19" s="5">
-        <f>J19-H19</f>
-        <v>28.8</v>
-      </c>
-      <c r="J19" s="5">
-        <v>1037.08</v>
-      </c>
-      <c r="K19" s="5">
-        <f>L19-J19</f>
-        <v>40.1000000000001</v>
-      </c>
-      <c r="L19" s="5">
-        <v>1077.18</v>
-      </c>
-      <c r="M19" s="5">
-        <f>N19-L19</f>
-        <v>26.03</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1103.21</v>
-      </c>
-      <c r="O19" s="5">
-        <f>P19-N19</f>
-        <v>28.3499999999999</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1131.56</v>
-      </c>
-      <c r="Q19" s="5">
-        <f>R19-P19</f>
-        <v>50.1900000000001</v>
-      </c>
-      <c r="R19" s="5">
-        <v>1181.75</v>
-      </c>
-      <c r="S19" s="5">
-        <f>T19-R19</f>
-        <v>26.8699999999999</v>
-      </c>
-      <c r="T19" s="5">
-        <v>1208.62</v>
-      </c>
-      <c r="U19" s="5">
-        <f>V19-T19</f>
-        <v>58.3000000000002</v>
-      </c>
-      <c r="V19" s="11">
-        <v>1266.92</v>
-      </c>
-      <c r="W19" s="5">
-        <f>X19-V19</f>
-        <v>41.0599999999999</v>
-      </c>
-      <c r="X19" s="11">
-        <v>1307.98</v>
-      </c>
-      <c r="Y19" s="5">
-        <f>Z19-X19</f>
-        <v>31.49</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>1339.47</v>
-      </c>
-      <c r="AA19" s="5">
-        <f>AB19-Z19</f>
-        <v>50.5899999999999</v>
-      </c>
-      <c r="AB19" s="5">
-        <v>1390.06</v>
-      </c>
-      <c r="AC19" s="5">
-        <f>AD19-AB19</f>
-        <v>35.8099999999999</v>
-      </c>
-      <c r="AD19" s="5">
-        <v>1425.87</v>
-      </c>
-      <c r="AE19" s="16">
-        <f>AF19-AD19</f>
-        <v>62.6300000000001</v>
-      </c>
-      <c r="AF19" s="16">
-        <v>1488.5</v>
-      </c>
-      <c r="AG19" s="16">
-        <f>AF19-D19</f>
-        <v>580.56</v>
-      </c>
-      <c r="AH19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI19" s="16">
-        <v>514.72</v>
-      </c>
-      <c r="AJ19" s="5">
-        <v>35</v>
-      </c>
-      <c r="AK19" s="5">
-        <v>8.2</v>
+      <c r="AK19" s="14">
+        <v>482.78</v>
       </c>
       <c r="AL19" s="5">
-        <v>65285</v>
-      </c>
-    </row>
-    <row r="20" spans="1:38">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="5">
+        <v>127369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40">
       <c r="A20" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5">
         <v>950.09</v>
@@ -4015,34 +4150,41 @@
         <v>1388.2</v>
       </c>
       <c r="AG20" s="16">
-        <f>AF20-D20</f>
-        <v>438.11</v>
-      </c>
-      <c r="AH20" s="21" t="s">
-        <v>67</v>
+        <f>AH20-AF20</f>
+        <v>61.74</v>
+      </c>
+      <c r="AH20" s="16">
+        <v>1449.94</v>
       </c>
       <c r="AI20" s="16">
-        <v>519.72</v>
-      </c>
-      <c r="AJ20" s="5">
+        <f>AH20-D20</f>
+        <v>499.85</v>
+      </c>
+      <c r="AJ20" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK20" s="16">
+        <v>538.42</v>
+      </c>
+      <c r="AL20" s="5">
         <v>10</v>
       </c>
-      <c r="AK20" s="5">
+      <c r="AM20" s="5">
         <v>2.2</v>
       </c>
-      <c r="AL20" s="5">
+      <c r="AN20" s="5">
         <v>86194</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:40">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5">
         <v>848.93</v>
@@ -4146,34 +4288,41 @@
         <v>1315.74</v>
       </c>
       <c r="AG21" s="16">
-        <f>AF21-D21</f>
-        <v>466.81</v>
-      </c>
-      <c r="AH21" s="21" t="s">
-        <v>54</v>
+        <f>AH21-AF21</f>
+        <v>29.53</v>
+      </c>
+      <c r="AH21" s="16">
+        <v>1345.27</v>
       </c>
       <c r="AI21" s="16">
-        <v>481.17</v>
-      </c>
-      <c r="AJ21" s="5">
+        <f>AH21-D21</f>
+        <v>496.34</v>
+      </c>
+      <c r="AJ21" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK21" s="16">
+        <v>500.37</v>
+      </c>
+      <c r="AL21" s="5">
         <v>30</v>
       </c>
-      <c r="AK21" s="5">
+      <c r="AM21" s="5">
         <v>3.2</v>
       </c>
-      <c r="AL21" s="5">
+      <c r="AN21" s="5">
         <v>78989</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:40">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D22" s="5">
         <v>927.15</v>
@@ -4277,686 +4426,728 @@
         <v>1307.52</v>
       </c>
       <c r="AG22" s="16">
-        <f>AF22-D22</f>
-        <v>380.37</v>
-      </c>
-      <c r="AH22" s="21" t="s">
-        <v>71</v>
+        <f>AH22-AF22</f>
+        <v>40.6600000000001</v>
+      </c>
+      <c r="AH22" s="16">
+        <v>1348.18</v>
       </c>
       <c r="AI22" s="16">
-        <v>363.97</v>
-      </c>
-      <c r="AJ22" s="5">
+        <f>AH22-D22</f>
+        <v>421.03</v>
+      </c>
+      <c r="AJ22" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK22" s="16">
+        <v>375.47</v>
+      </c>
+      <c r="AL22" s="5">
         <v>10</v>
       </c>
-      <c r="AK22" s="5">
+      <c r="AM22" s="5">
         <v>1.1</v>
       </c>
-      <c r="AL22" s="5">
+      <c r="AN22" s="5">
         <v>80664</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:40">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3">
-        <v>407.35</v>
+        <v>363.88</v>
       </c>
       <c r="E23" s="3">
         <f>F23-D23</f>
-        <v>13.86</v>
+        <v>14.21</v>
       </c>
       <c r="F23" s="3">
-        <v>421.21</v>
+        <v>378.09</v>
       </c>
       <c r="G23" s="3">
         <f>H23-F23</f>
-        <v>16.43</v>
+        <v>11.22</v>
       </c>
       <c r="H23" s="3">
-        <v>437.64</v>
+        <v>389.31</v>
       </c>
       <c r="I23" s="3">
         <f>J23-H23</f>
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
       <c r="J23" s="3">
-        <v>451.28</v>
+        <v>402.93</v>
       </c>
       <c r="K23" s="3">
         <f>L23-J23</f>
-        <v>11.6</v>
+        <v>11.13</v>
       </c>
       <c r="L23" s="3">
-        <v>462.88</v>
+        <v>414.06</v>
       </c>
       <c r="M23" s="3">
         <f>N23-L23</f>
-        <v>47.68</v>
+        <v>17.39</v>
       </c>
       <c r="N23" s="3">
-        <v>510.56</v>
+        <v>431.45</v>
       </c>
       <c r="O23" s="3">
         <f>P23-N23</f>
-        <v>20.51</v>
+        <v>6.32999999999998</v>
       </c>
       <c r="P23" s="3">
-        <v>531.07</v>
+        <v>437.78</v>
       </c>
       <c r="Q23" s="3">
         <f>R23-P23</f>
-        <v>18.6099999999999</v>
+        <v>53.01</v>
       </c>
       <c r="R23" s="3">
-        <v>549.68</v>
+        <v>490.79</v>
       </c>
       <c r="S23" s="3">
         <f>T23-R23</f>
-        <v>11.9400000000001</v>
+        <v>11.82</v>
       </c>
       <c r="T23" s="3">
-        <v>561.62</v>
+        <v>502.61</v>
       </c>
       <c r="U23" s="3">
         <f>V23-T23</f>
-        <v>16.23</v>
+        <v>19.3099999999999</v>
       </c>
       <c r="V23" s="12">
-        <v>577.85</v>
+        <v>521.92</v>
       </c>
       <c r="W23" s="3">
         <f>X23-V23</f>
-        <v>15.28</v>
+        <v>29.5400000000001</v>
       </c>
       <c r="X23" s="12">
-        <v>593.13</v>
+        <v>551.46</v>
       </c>
       <c r="Y23" s="3">
         <f>Z23-X23</f>
-        <v>33.2</v>
+        <v>36.98</v>
       </c>
       <c r="Z23" s="3">
-        <v>626.33</v>
+        <v>588.44</v>
       </c>
       <c r="AA23" s="3">
         <f>AB23-Z23</f>
-        <v>16.7199999999999</v>
+        <v>21.17</v>
       </c>
       <c r="AB23" s="3">
-        <v>643.05</v>
+        <v>609.61</v>
       </c>
       <c r="AC23" s="3">
         <f>AD23-AB23</f>
-        <v>11.9300000000001</v>
+        <v>17.4399999999999</v>
       </c>
       <c r="AD23" s="3">
-        <v>654.98</v>
+        <v>627.05</v>
       </c>
       <c r="AE23" s="17">
         <f>AF23-AD23</f>
-        <v>9.16999999999996</v>
+        <v>21.0500000000001</v>
       </c>
       <c r="AF23" s="17">
-        <v>664.15</v>
+        <v>648.1</v>
       </c>
       <c r="AG23" s="17">
-        <f>AF23-D23</f>
-        <v>256.8</v>
-      </c>
-      <c r="AH23" s="22" t="s">
-        <v>73</v>
+        <f>AH23-AF23</f>
+        <v>37.27</v>
+      </c>
+      <c r="AH23" s="17">
+        <v>685.37</v>
       </c>
       <c r="AI23" s="17">
-        <v>297.3</v>
-      </c>
-      <c r="AJ23" s="3">
+        <f>AH23-D23</f>
+        <v>321.49</v>
+      </c>
+      <c r="AJ23" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK23" s="17">
+        <v>227.07</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="3">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40">
+      <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AK23" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="AL23" s="3">
-        <v>43895</v>
-      </c>
-    </row>
-    <row r="24" spans="1:38">
-      <c r="A24" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="B24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D24" s="3">
-        <v>363.88</v>
+        <v>407.35</v>
       </c>
       <c r="E24" s="3">
         <f>F24-D24</f>
-        <v>14.21</v>
+        <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>378.09</v>
+        <v>421.21</v>
       </c>
       <c r="G24" s="3">
         <f>H24-F24</f>
-        <v>11.22</v>
+        <v>16.43</v>
       </c>
       <c r="H24" s="3">
-        <v>389.31</v>
+        <v>437.64</v>
       </c>
       <c r="I24" s="3">
         <f>J24-H24</f>
-        <v>13.62</v>
+        <v>13.64</v>
       </c>
       <c r="J24" s="3">
-        <v>402.93</v>
+        <v>451.28</v>
       </c>
       <c r="K24" s="3">
         <f>L24-J24</f>
-        <v>11.13</v>
+        <v>11.6</v>
       </c>
       <c r="L24" s="3">
-        <v>414.06</v>
+        <v>462.88</v>
       </c>
       <c r="M24" s="3">
         <f>N24-L24</f>
-        <v>17.39</v>
+        <v>47.68</v>
       </c>
       <c r="N24" s="3">
-        <v>431.45</v>
+        <v>510.56</v>
       </c>
       <c r="O24" s="3">
         <f>P24-N24</f>
-        <v>6.32999999999998</v>
+        <v>20.51</v>
       </c>
       <c r="P24" s="3">
-        <v>437.78</v>
+        <v>531.07</v>
       </c>
       <c r="Q24" s="3">
         <f>R24-P24</f>
-        <v>53.01</v>
+        <v>18.6099999999999</v>
       </c>
       <c r="R24" s="3">
-        <v>490.79</v>
+        <v>549.68</v>
       </c>
       <c r="S24" s="3">
         <f>T24-R24</f>
-        <v>11.82</v>
+        <v>11.9400000000001</v>
       </c>
       <c r="T24" s="3">
-        <v>502.61</v>
+        <v>561.62</v>
       </c>
       <c r="U24" s="3">
         <f>V24-T24</f>
-        <v>19.3099999999999</v>
+        <v>16.23</v>
       </c>
       <c r="V24" s="12">
-        <v>521.92</v>
+        <v>577.85</v>
       </c>
       <c r="W24" s="3">
         <f>X24-V24</f>
-        <v>29.5400000000001</v>
+        <v>15.28</v>
       </c>
       <c r="X24" s="12">
-        <v>551.46</v>
+        <v>593.13</v>
       </c>
       <c r="Y24" s="3">
         <f>Z24-X24</f>
-        <v>36.98</v>
+        <v>33.2</v>
       </c>
       <c r="Z24" s="3">
-        <v>588.44</v>
+        <v>626.33</v>
       </c>
       <c r="AA24" s="3">
         <f>AB24-Z24</f>
-        <v>21.17</v>
+        <v>16.7199999999999</v>
       </c>
       <c r="AB24" s="3">
-        <v>609.61</v>
+        <v>643.05</v>
       </c>
       <c r="AC24" s="3">
         <f>AD24-AB24</f>
-        <v>17.4399999999999</v>
+        <v>11.9300000000001</v>
       </c>
       <c r="AD24" s="3">
-        <v>627.05</v>
+        <v>654.98</v>
       </c>
       <c r="AE24" s="17">
         <f>AF24-AD24</f>
-        <v>21.0500000000001</v>
+        <v>9.16999999999996</v>
       </c>
       <c r="AF24" s="17">
-        <v>648.1</v>
+        <v>664.15</v>
       </c>
       <c r="AG24" s="17">
-        <f>AF24-D24</f>
-        <v>284.22</v>
-      </c>
-      <c r="AH24" s="22" t="s">
+        <f>AH24-AF24</f>
+        <v>25.0500000000001</v>
+      </c>
+      <c r="AH24" s="17">
+        <v>689.2</v>
+      </c>
+      <c r="AI24" s="17">
+        <f>AH24-D24</f>
+        <v>281.85</v>
+      </c>
+      <c r="AJ24" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK24" s="17">
+        <v>308.25</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>30</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40">
+      <c r="A25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AI24" s="17">
-        <v>192.49</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL24" s="3">
-        <v>47256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:38">
-      <c r="A25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D25" s="3">
-        <v>552.79</v>
+        <v>305.29</v>
       </c>
       <c r="E25" s="3">
         <f>F25-D25</f>
-        <v>15.9400000000001</v>
+        <v>17.97</v>
       </c>
       <c r="F25" s="3">
-        <v>568.73</v>
+        <v>323.26</v>
       </c>
       <c r="G25" s="3">
         <f>H25-F25</f>
-        <v>1.61000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="H25" s="3">
-        <v>570.34</v>
+        <v>334.08</v>
       </c>
       <c r="I25" s="3">
         <f>J25-H25</f>
-        <v>7.13999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="J25" s="3">
-        <v>577.48</v>
+        <v>350.28</v>
       </c>
       <c r="K25" s="3">
         <f>L25-J25</f>
-        <v>2.88999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="L25" s="3">
-        <v>580.37</v>
+        <v>361.08</v>
       </c>
       <c r="M25" s="3">
         <f>N25-L25</f>
-        <v>2.55999999999995</v>
+        <v>9.98000000000002</v>
       </c>
       <c r="N25" s="3">
-        <v>582.93</v>
+        <v>371.06</v>
       </c>
       <c r="O25" s="3">
         <f>P25-N25</f>
-        <v>24.99</v>
+        <v>10.17</v>
       </c>
       <c r="P25" s="3">
-        <v>607.92</v>
+        <v>381.23</v>
       </c>
       <c r="Q25" s="3">
         <f>R25-P25</f>
-        <v>0.330000000000041</v>
+        <v>20.97</v>
       </c>
       <c r="R25" s="3">
-        <v>608.25</v>
+        <v>402.2</v>
       </c>
       <c r="S25" s="3">
         <f>T25-R25</f>
-        <v>1.80999999999995</v>
+        <v>5.68000000000001</v>
       </c>
       <c r="T25" s="3">
-        <v>610.06</v>
+        <v>407.88</v>
       </c>
       <c r="U25" s="3">
         <f>V25-T25</f>
-        <v>0.560000000000059</v>
+        <v>25.13</v>
       </c>
       <c r="V25" s="12">
-        <v>610.62</v>
+        <v>433.01</v>
       </c>
       <c r="W25" s="3">
         <f>X25-V25</f>
-        <v>3.83000000000004</v>
+        <v>37.15</v>
       </c>
       <c r="X25" s="12">
-        <v>614.45</v>
+        <v>470.16</v>
       </c>
       <c r="Y25" s="3">
         <f>Z25-X25</f>
-        <v>0.189999999999941</v>
+        <v>10.92</v>
       </c>
       <c r="Z25" s="3">
-        <v>614.64</v>
+        <v>481.08</v>
       </c>
       <c r="AA25" s="3">
         <f>AB25-Z25</f>
-        <v>0.690000000000055</v>
+        <v>13.68</v>
       </c>
       <c r="AB25" s="3">
-        <v>615.33</v>
+        <v>494.76</v>
       </c>
       <c r="AC25" s="3">
         <f>AD25-AB25</f>
-        <v>6.64999999999998</v>
+        <v>12.69</v>
       </c>
       <c r="AD25" s="3">
-        <v>621.98</v>
+        <v>507.45</v>
       </c>
       <c r="AE25" s="17">
         <f>AF25-AD25</f>
+        <v>42.97</v>
+      </c>
+      <c r="AF25" s="17">
+        <v>550.42</v>
+      </c>
+      <c r="AG25" s="17">
+        <f>AH25-AF25</f>
+        <v>13</v>
+      </c>
+      <c r="AH25" s="17">
+        <v>563.42</v>
+      </c>
+      <c r="AI25" s="17">
+        <f>AH25-D25</f>
+        <v>258.13</v>
+      </c>
+      <c r="AJ25" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK25" s="17">
+        <v>171.21</v>
+      </c>
+      <c r="AL25" s="3">
         <v>0</v>
       </c>
-      <c r="AF25" s="17">
-        <v>621.98</v>
-      </c>
-      <c r="AG25" s="17">
-        <f>AF25-D25</f>
-        <v>69.1900000000001</v>
-      </c>
-      <c r="AH25" s="22" t="s">
+      <c r="AM25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>28066</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40">
+      <c r="A26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AI25" s="17">
-        <v>137</v>
-      </c>
-      <c r="AJ25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AL25" s="3">
-        <v>49654</v>
-      </c>
-    </row>
-    <row r="26" spans="1:38">
-      <c r="A26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D26" s="3">
-        <v>305.29</v>
+        <v>262.39</v>
       </c>
       <c r="E26" s="3">
         <f>F26-D26</f>
-        <v>17.97</v>
+        <v>11.5</v>
       </c>
       <c r="F26" s="3">
-        <v>323.26</v>
+        <v>273.89</v>
       </c>
       <c r="G26" s="3">
         <f>H26-F26</f>
-        <v>10.82</v>
+        <v>13.97</v>
       </c>
       <c r="H26" s="3">
-        <v>334.08</v>
+        <v>287.86</v>
       </c>
       <c r="I26" s="3">
         <f>J26-H26</f>
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="J26" s="3">
-        <v>350.28</v>
+        <v>304.1</v>
       </c>
       <c r="K26" s="3">
         <f>L26-J26</f>
-        <v>10.8</v>
+        <v>12.65</v>
       </c>
       <c r="L26" s="3">
-        <v>361.08</v>
+        <v>316.75</v>
       </c>
       <c r="M26" s="3">
         <f>N26-L26</f>
-        <v>9.98000000000002</v>
+        <v>9.99000000000001</v>
       </c>
       <c r="N26" s="3">
-        <v>371.06</v>
+        <v>326.74</v>
       </c>
       <c r="O26" s="3">
         <f>P26-N26</f>
-        <v>10.17</v>
+        <v>6.31999999999999</v>
       </c>
       <c r="P26" s="3">
-        <v>381.23</v>
+        <v>333.06</v>
       </c>
       <c r="Q26" s="3">
         <f>R26-P26</f>
-        <v>20.97</v>
+        <v>21.13</v>
       </c>
       <c r="R26" s="3">
-        <v>402.2</v>
+        <v>354.19</v>
       </c>
       <c r="S26" s="3">
         <f>T26-R26</f>
-        <v>5.68000000000001</v>
+        <v>17.68</v>
       </c>
       <c r="T26" s="3">
-        <v>407.88</v>
+        <v>371.87</v>
       </c>
       <c r="U26" s="3">
         <f>V26-T26</f>
-        <v>25.13</v>
+        <v>11.66</v>
       </c>
       <c r="V26" s="12">
-        <v>433.01</v>
+        <v>383.53</v>
       </c>
       <c r="W26" s="3">
         <f>X26-V26</f>
-        <v>37.15</v>
+        <v>20.5700000000001</v>
       </c>
       <c r="X26" s="12">
-        <v>470.16</v>
+        <v>404.1</v>
       </c>
       <c r="Y26" s="3">
         <f>Z26-X26</f>
-        <v>10.92</v>
+        <v>33.33</v>
       </c>
       <c r="Z26" s="3">
-        <v>481.08</v>
+        <v>437.43</v>
       </c>
       <c r="AA26" s="3">
         <f>AB26-Z26</f>
-        <v>13.68</v>
+        <v>27.72</v>
       </c>
       <c r="AB26" s="3">
-        <v>494.76</v>
+        <v>465.15</v>
       </c>
       <c r="AC26" s="3">
         <f>AD26-AB26</f>
-        <v>12.69</v>
+        <v>9.79000000000002</v>
       </c>
       <c r="AD26" s="3">
-        <v>507.45</v>
+        <v>474.94</v>
       </c>
       <c r="AE26" s="17">
         <f>AF26-AD26</f>
-        <v>42.97</v>
+        <v>13.05</v>
       </c>
       <c r="AF26" s="17">
-        <v>550.42</v>
+        <v>487.99</v>
       </c>
       <c r="AG26" s="17">
-        <f>AF26-D26</f>
-        <v>245.13</v>
-      </c>
-      <c r="AH26" s="22" t="s">
+        <f>AH26-AF26</f>
+        <v>19.13</v>
+      </c>
+      <c r="AH26" s="17">
+        <v>507.12</v>
+      </c>
+      <c r="AI26" s="17">
+        <f>AH26-D26</f>
+        <v>244.73</v>
+      </c>
+      <c r="AJ26" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK26" s="17">
+        <v>165.96</v>
+      </c>
+      <c r="AL26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="3">
+        <v>36684</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40">
+      <c r="A27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AI26" s="17">
-        <v>174.01</v>
-      </c>
-      <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="3">
-        <v>28066</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38">
-      <c r="A27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D27" s="3">
-        <v>262.39</v>
+        <v>552.79</v>
       </c>
       <c r="E27" s="3">
         <f>F27-D27</f>
-        <v>11.5</v>
+        <v>15.9400000000001</v>
       </c>
       <c r="F27" s="3">
-        <v>273.89</v>
+        <v>568.73</v>
       </c>
       <c r="G27" s="3">
         <f>H27-F27</f>
-        <v>13.97</v>
+        <v>1.61000000000001</v>
       </c>
       <c r="H27" s="3">
-        <v>287.86</v>
+        <v>570.34</v>
       </c>
       <c r="I27" s="3">
         <f>J27-H27</f>
-        <v>16.24</v>
+        <v>7.13999999999999</v>
       </c>
       <c r="J27" s="3">
-        <v>304.1</v>
+        <v>577.48</v>
       </c>
       <c r="K27" s="3">
         <f>L27-J27</f>
-        <v>12.65</v>
+        <v>2.88999999999999</v>
       </c>
       <c r="L27" s="3">
-        <v>316.75</v>
+        <v>580.37</v>
       </c>
       <c r="M27" s="3">
         <f>N27-L27</f>
-        <v>9.99000000000001</v>
+        <v>2.55999999999995</v>
       </c>
       <c r="N27" s="3">
-        <v>326.74</v>
+        <v>582.93</v>
       </c>
       <c r="O27" s="3">
         <f>P27-N27</f>
-        <v>6.31999999999999</v>
+        <v>24.99</v>
       </c>
       <c r="P27" s="3">
-        <v>333.06</v>
+        <v>607.92</v>
       </c>
       <c r="Q27" s="3">
         <f>R27-P27</f>
-        <v>21.13</v>
+        <v>0.330000000000041</v>
       </c>
       <c r="R27" s="3">
-        <v>354.19</v>
+        <v>608.25</v>
       </c>
       <c r="S27" s="3">
         <f>T27-R27</f>
-        <v>17.68</v>
+        <v>1.80999999999995</v>
       </c>
       <c r="T27" s="3">
-        <v>371.87</v>
+        <v>610.06</v>
       </c>
       <c r="U27" s="3">
         <f>V27-T27</f>
-        <v>11.66</v>
+        <v>0.560000000000059</v>
       </c>
       <c r="V27" s="12">
-        <v>383.53</v>
+        <v>610.62</v>
       </c>
       <c r="W27" s="3">
         <f>X27-V27</f>
-        <v>20.5700000000001</v>
+        <v>3.83000000000004</v>
       </c>
       <c r="X27" s="12">
-        <v>404.1</v>
+        <v>614.45</v>
       </c>
       <c r="Y27" s="3">
         <f>Z27-X27</f>
-        <v>33.33</v>
+        <v>0.189999999999941</v>
       </c>
       <c r="Z27" s="3">
-        <v>437.43</v>
+        <v>614.64</v>
       </c>
       <c r="AA27" s="3">
         <f>AB27-Z27</f>
-        <v>27.72</v>
+        <v>0.690000000000055</v>
       </c>
       <c r="AB27" s="3">
-        <v>465.15</v>
+        <v>615.33</v>
       </c>
       <c r="AC27" s="3">
         <f>AD27-AB27</f>
-        <v>9.79000000000002</v>
+        <v>6.64999999999998</v>
       </c>
       <c r="AD27" s="3">
-        <v>474.94</v>
+        <v>621.98</v>
       </c>
       <c r="AE27" s="17">
         <f>AF27-AD27</f>
-        <v>13.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="17">
-        <v>487.99</v>
+        <v>621.98</v>
       </c>
       <c r="AG27" s="17">
-        <f>AF27-D27</f>
-        <v>225.6</v>
-      </c>
-      <c r="AH27" s="22" t="s">
-        <v>79</v>
+        <f>AH27-AF27</f>
+        <v>13.62</v>
+      </c>
+      <c r="AH27" s="17">
+        <v>635.6</v>
       </c>
       <c r="AI27" s="17">
-        <v>164.76</v>
-      </c>
-      <c r="AJ27" s="3">
+        <f>AH27-D27</f>
+        <v>82.8100000000001</v>
+      </c>
+      <c r="AJ27" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK27" s="17">
+        <v>148.52</v>
+      </c>
+      <c r="AL27" s="3">
         <v>0</v>
       </c>
-      <c r="AK27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL27" s="3">
-        <v>36684</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35">
+      <c r="AM27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AN27" s="3">
+        <v>49654</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -4991,13 +5182,15 @@
       <c r="AG30" s="7"/>
       <c r="AH30" s="7"/>
       <c r="AI30" s="7"/>
-    </row>
-    <row r="31" spans="1:36">
+      <c r="AJ30" s="7"/>
+      <c r="AK30" s="7"/>
+    </row>
+    <row r="31" spans="1:38">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
@@ -5020,21 +5213,23 @@
       <c r="AH31" s="7"/>
       <c r="AI31" s="7"/>
       <c r="AJ31" s="7"/>
+      <c r="AK31" s="7"/>
+      <c r="AL31" s="7"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:34">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -5068,58 +5263,60 @@
       <c r="AF33" s="7"/>
       <c r="AG33" s="7"/>
       <c r="AH33" s="7"/>
+      <c r="AI33" s="7"/>
+      <c r="AJ33" s="7"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AL27">
-    <sortCondition ref="AF2" descending="1"/>
+  <sortState ref="A2:AN27">
+    <sortCondition ref="AI2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5156,40 +5353,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5530,7 +5727,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -5584,7 +5781,7 @@
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5893,10 +6090,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -6440,7 +6637,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C46:L46 C44:L44 C42:L42 C40:L40 C38:L38 C36:L36 C34:L34 C32:L32" formulaRange="1"/>
+    <ignoredError sqref="C32:L32 C34:L34 C36:L36 C38:L38 C40:L40 C42:L42 C44:L44 C46:L46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
+++ b/src/utils/sxsyzlzq/zzz_xingyuzhanli.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="220">
   <si>
     <t>区服</t>
   </si>
@@ -278,6 +278,9 @@
     <t>战力（2026.08.26）</t>
   </si>
   <si>
+    <t>战力（2026.09.03）</t>
+  </si>
+  <si>
     <t>首席（流派）</t>
   </si>
   <si>
@@ -314,58 +317,58 @@
     <t>大氪</t>
   </si>
   <si>
+    <t>盲女（洞察）</t>
+  </si>
+  <si>
+    <t>洞察女（橙卡）</t>
+  </si>
+  <si>
+    <t>149区</t>
+  </si>
+  <si>
+    <t>灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>丽娅（人海）</t>
+  </si>
+  <si>
+    <t>148区</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
+    <t>眼镜妹（橙卡）</t>
+  </si>
+  <si>
+    <t>喵喵（橙卡）</t>
+  </si>
+  <si>
+    <t>145区</t>
+  </si>
+  <si>
+    <t>古月星辰</t>
+  </si>
+  <si>
+    <t>中大氪</t>
+  </si>
+  <si>
+    <t>冽（传承）</t>
+  </si>
+  <si>
+    <t>梅养（养神）</t>
+  </si>
+  <si>
+    <t>151区</t>
+  </si>
+  <si>
+    <t>suola</t>
+  </si>
+  <si>
+    <t>中氪</t>
+  </si>
+  <si>
     <t>圣母（洞察）</t>
-  </si>
-  <si>
-    <t>洞察女（橙卡）</t>
-  </si>
-  <si>
-    <t>148区</t>
-  </si>
-  <si>
-    <t>大核桃</t>
-  </si>
-  <si>
-    <t>眼镜妹（橙卡）</t>
-  </si>
-  <si>
-    <t>喵喵（橙卡）</t>
-  </si>
-  <si>
-    <t>149区</t>
-  </si>
-  <si>
-    <t>灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>丽娅（人海）</t>
-  </si>
-  <si>
-    <t>145区</t>
-  </si>
-  <si>
-    <t>古月星辰</t>
-  </si>
-  <si>
-    <t>中大氪</t>
-  </si>
-  <si>
-    <t>冽（传承）</t>
-  </si>
-  <si>
-    <t>梅养（养神）</t>
-  </si>
-  <si>
-    <t>151区</t>
-  </si>
-  <si>
-    <t>suola</t>
-  </si>
-  <si>
-    <t>中氪</t>
-  </si>
-  <si>
-    <t>盲女（洞察）</t>
   </si>
   <si>
     <t>请叫我阿奎</t>
@@ -1421,6 +1424,9 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1429,9 +1435,6 @@
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1767,7 +1770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FM39"/>
+  <dimension ref="A1:FO39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.3666666666667" customWidth="1"/>
@@ -1811,19 +1814,19 @@
     <col min="90" max="90" width="17.9333333333333" hidden="1" customWidth="1"/>
     <col min="91" max="119" width="17.2833333333333" hidden="1" customWidth="1"/>
     <col min="120" max="120" width="18.8" hidden="1" customWidth="1"/>
-    <col min="121" max="147" width="17.2833333333333" hidden="1" customWidth="1"/>
-    <col min="148" max="151" width="17.2833333333333" customWidth="1"/>
-    <col min="152" max="152" width="14.5416666666667" customWidth="1"/>
-    <col min="153" max="153" width="15.1833333333333" hidden="1" customWidth="1"/>
-    <col min="154" max="154" width="13.2583333333333" hidden="1" customWidth="1"/>
-    <col min="155" max="155" width="11.625" hidden="1" customWidth="1"/>
-    <col min="156" max="156" width="12.6083333333333" hidden="1" customWidth="1"/>
-    <col min="157" max="157" width="15.0166666666667" hidden="1" customWidth="1"/>
-    <col min="158" max="158" width="12.625"/>
-    <col min="159" max="159" width="11.4083333333333" hidden="1" customWidth="1"/>
+    <col min="121" max="149" width="17.2833333333333" hidden="1" customWidth="1"/>
+    <col min="150" max="153" width="17.2833333333333" customWidth="1"/>
+    <col min="154" max="154" width="14.5416666666667" customWidth="1"/>
+    <col min="155" max="155" width="15.1833333333333" hidden="1" customWidth="1"/>
+    <col min="156" max="156" width="13.2583333333333" hidden="1" customWidth="1"/>
+    <col min="157" max="157" width="11.625" hidden="1" customWidth="1"/>
+    <col min="158" max="158" width="12.6083333333333" hidden="1" customWidth="1"/>
+    <col min="159" max="159" width="15.0166666666667" hidden="1" customWidth="1"/>
+    <col min="160" max="160" width="12.625"/>
+    <col min="161" max="161" width="11.4083333333333" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:169">
+    <row r="1" spans="1:171">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2275,42 +2278,48 @@
         <v>79</v>
       </c>
       <c r="EU1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="EV1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="EV1" s="5" t="s">
+      <c r="EW1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EX1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="EY1" t="s">
         <v>83</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="EZ1" t="s">
         <v>84</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FA1" t="s">
         <v>85</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FB1" t="s">
         <v>86</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FC1" t="s">
         <v>87</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FD1" t="s">
         <v>88</v>
       </c>
+      <c r="FE1" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:169">
+    <row r="2" s="8" customFormat="1" spans="1:171">
       <c r="A2" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5">
         <v>4105.48</v>
@@ -2826,591 +2835,605 @@
       <c r="ET2" s="12">
         <v>11480.64</v>
       </c>
-      <c r="EU2" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="EV2" s="9">
-        <v>2820.22</v>
-      </c>
-      <c r="EW2" s="9" t="s">
+      <c r="EU2" s="12">
+        <f>EV2-ET2</f>
+        <v>229.08</v>
+      </c>
+      <c r="EV2" s="12">
+        <v>11709.72</v>
+      </c>
+      <c r="EW2" s="11" t="s">
         <v>93</v>
       </c>
       <c r="EX2" s="9">
+        <v>2973.52</v>
+      </c>
+      <c r="EY2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="EZ2" s="9">
         <v>1267.77</v>
       </c>
-      <c r="EY2" s="5">
+      <c r="FA2" s="5">
         <v>400</v>
       </c>
-      <c r="EZ2" s="5">
+      <c r="FB2" s="5">
         <v>1.2</v>
       </c>
-      <c r="FA2" s="5">
+      <c r="FC2" s="5">
         <v>186759</v>
       </c>
-      <c r="FB2" s="9">
-        <f>2.41/(ET2/EV2)</f>
-        <v>0.592016664576191</v>
-      </c>
-      <c r="FC2" s="9">
+      <c r="FD2" s="9">
+        <f>2.79/(EV2/EX2)</f>
+        <v>0.70848156915793</v>
+      </c>
+      <c r="FE2" s="9">
         <f>BP2-D2</f>
         <v>2684.95</v>
       </c>
     </row>
-    <row r="3" spans="1:169">
+    <row r="3" spans="1:171">
       <c r="A3" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" s="5">
-        <v>2714.1</v>
+        <v>2533.85</v>
       </c>
       <c r="E3" s="5">
         <f>F3-D3</f>
-        <v>123.29</v>
+        <v>50.0500000000002</v>
       </c>
       <c r="F3" s="5">
-        <v>2837.39</v>
+        <v>2583.9</v>
       </c>
       <c r="G3" s="5">
         <f>H3-F3</f>
-        <v>95.8499999999999</v>
+        <v>85.7599999999998</v>
       </c>
       <c r="H3" s="5">
-        <v>2933.24</v>
+        <v>2669.66</v>
       </c>
       <c r="I3" s="5">
         <f>J3-H3</f>
-        <v>92.46</v>
+        <v>81.79</v>
       </c>
       <c r="J3" s="5">
-        <v>3025.7</v>
+        <v>2751.45</v>
       </c>
       <c r="K3" s="5">
         <f>L3-J3</f>
-        <v>90.4100000000003</v>
+        <v>83.1700000000001</v>
       </c>
       <c r="L3" s="5">
-        <v>3116.11</v>
+        <v>2834.62</v>
       </c>
       <c r="M3" s="5">
         <f>N3-L3</f>
-        <v>103.54</v>
+        <v>56.9900000000002</v>
       </c>
       <c r="N3" s="5">
-        <v>3219.65</v>
+        <v>2891.61</v>
       </c>
       <c r="O3" s="5">
         <f>P3-N3</f>
-        <v>75.6599999999999</v>
+        <v>103.98</v>
       </c>
       <c r="P3" s="5">
-        <v>3295.31</v>
+        <v>2995.59</v>
       </c>
       <c r="Q3" s="5">
         <f>R3-P3</f>
-        <v>88.98</v>
+        <v>68.8499999999999</v>
       </c>
       <c r="R3" s="5">
-        <v>3384.29</v>
+        <v>3064.44</v>
       </c>
       <c r="S3" s="5">
         <f>T3-R3</f>
-        <v>102.46</v>
+        <v>47.6100000000001</v>
       </c>
       <c r="T3" s="5">
-        <v>3486.75</v>
+        <v>3112.05</v>
       </c>
       <c r="U3" s="5">
         <f>V3-T3</f>
-        <v>69.23</v>
+        <v>38.1599999999999</v>
       </c>
       <c r="V3" s="10">
-        <v>3555.98</v>
+        <v>3150.21</v>
       </c>
       <c r="W3" s="5">
         <f>X3-V3</f>
-        <v>133.46</v>
+        <v>146.1</v>
       </c>
       <c r="X3" s="10">
-        <v>3689.44</v>
+        <v>3296.31</v>
       </c>
       <c r="Y3" s="5">
         <f>Z3-X3</f>
-        <v>10.5999999999999</v>
+        <v>31.9400000000001</v>
       </c>
       <c r="Z3" s="5">
-        <v>3700.04</v>
+        <v>3328.25</v>
       </c>
       <c r="AA3" s="5">
         <f>AB3-Z3</f>
-        <v>145.58</v>
+        <v>79.8800000000001</v>
       </c>
       <c r="AB3" s="5">
-        <v>3845.62</v>
+        <v>3408.13</v>
       </c>
       <c r="AC3" s="5">
         <f>AD3-AB3</f>
-        <v>64.1800000000003</v>
-      </c>
-      <c r="AD3" s="9">
-        <v>3909.8</v>
+        <v>68.9099999999999</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>3477.04</v>
       </c>
       <c r="AE3" s="9">
         <f>AF3-AD3</f>
-        <v>98.8399999999997</v>
+        <v>143.74</v>
       </c>
       <c r="AF3" s="9">
-        <v>4008.64</v>
+        <v>3620.78</v>
       </c>
       <c r="AG3" s="9">
         <f>AH3-AF3</f>
-        <v>157.920000000001</v>
+        <v>82.0999999999999</v>
       </c>
       <c r="AH3" s="9">
-        <v>4166.56</v>
+        <v>3702.88</v>
       </c>
       <c r="AI3" s="9">
         <f>AJ3-AH3</f>
-        <v>103.339999999999</v>
+        <v>111.1</v>
       </c>
       <c r="AJ3" s="9">
-        <v>4269.9</v>
+        <v>3813.98</v>
       </c>
       <c r="AK3" s="9">
         <f>AL3-AJ3</f>
-        <v>66.25</v>
+        <v>119.59</v>
       </c>
       <c r="AL3" s="9">
-        <v>4336.15</v>
+        <v>3933.57</v>
       </c>
       <c r="AM3" s="9">
         <f>AN3-AL3</f>
-        <v>138.700000000001</v>
+        <v>39.71</v>
       </c>
       <c r="AN3" s="9">
-        <v>4474.85</v>
+        <v>3973.28</v>
       </c>
       <c r="AO3" s="9">
         <f>AP3-AN3</f>
-        <v>78.4499999999998</v>
+        <v>94.1399999999999</v>
       </c>
       <c r="AP3" s="9">
-        <v>4553.3</v>
+        <v>4067.42</v>
       </c>
       <c r="AQ3" s="9">
         <f>AR3-AP3</f>
-        <v>56.7699999999995</v>
+        <v>51.1800000000003</v>
       </c>
       <c r="AR3" s="9">
-        <v>4610.07</v>
+        <v>4118.6</v>
       </c>
       <c r="AS3" s="9">
         <f>AT3-AR3</f>
-        <v>32.3699999999999</v>
+        <v>33.4499999999998</v>
       </c>
       <c r="AT3" s="9">
-        <v>4642.44</v>
+        <v>4152.05</v>
       </c>
       <c r="AU3" s="11">
         <f>AV3-AT3</f>
-        <v>77.6300000000001</v>
+        <v>31.5199999999995</v>
       </c>
       <c r="AV3" s="11">
-        <v>4720.07</v>
+        <v>4183.57</v>
       </c>
       <c r="AW3" s="12">
         <f>AX3-AV3</f>
-        <v>121.33</v>
+        <v>33.7400000000007</v>
       </c>
       <c r="AX3" s="12">
-        <v>4841.4</v>
+        <v>4217.31</v>
       </c>
       <c r="AY3" s="12">
         <f>AZ3-AX3</f>
-        <v>61.2400000000007</v>
+        <v>64.8499999999995</v>
       </c>
       <c r="AZ3" s="12">
-        <v>4902.64</v>
+        <v>4282.16</v>
       </c>
       <c r="BA3" s="12">
         <f>BB3-AZ3</f>
-        <v>64.3099999999995</v>
+        <v>25.75</v>
       </c>
       <c r="BB3" s="12">
-        <v>4966.95</v>
+        <v>4307.91</v>
       </c>
       <c r="BC3" s="12">
         <f>BD3-BB3</f>
-        <v>87.1000000000004</v>
+        <v>42.4400000000005</v>
       </c>
       <c r="BD3" s="12">
-        <v>5054.05</v>
+        <v>4350.35</v>
       </c>
       <c r="BE3" s="11">
         <f>BF3-BD3</f>
-        <v>154.29</v>
+        <v>98.5899999999992</v>
       </c>
       <c r="BF3" s="12">
-        <v>5208.34</v>
+        <v>4448.94</v>
       </c>
       <c r="BG3" s="12">
         <f>BH3-BF3</f>
-        <v>181.45</v>
+        <v>93.3700000000008</v>
       </c>
       <c r="BH3" s="12">
-        <v>5389.79</v>
+        <v>4542.31</v>
       </c>
       <c r="BI3" s="12">
         <f>BJ3-BH3</f>
-        <v>99</v>
+        <v>105.799999999999</v>
       </c>
       <c r="BJ3" s="12">
-        <v>5488.79</v>
+        <v>4648.11</v>
       </c>
       <c r="BK3" s="12">
         <f>BL3-BJ3</f>
-        <v>53.9499999999998</v>
+        <v>49.4700000000003</v>
       </c>
       <c r="BL3" s="12">
-        <v>5542.74</v>
+        <v>4697.58</v>
       </c>
       <c r="BM3" s="12">
         <f>BN3-BL3</f>
-        <v>72.0300000000007</v>
+        <v>57.8599999999997</v>
       </c>
       <c r="BN3" s="12">
-        <v>5614.77</v>
+        <v>4755.44</v>
       </c>
       <c r="BO3" s="12">
         <f>BP3-BN3</f>
-        <v>122.11</v>
+        <v>55.5500000000002</v>
       </c>
       <c r="BP3" s="12">
-        <v>5736.88</v>
+        <v>4810.99</v>
       </c>
       <c r="BQ3" s="12">
         <f>BR3-BP3</f>
-        <v>22.0799999999999</v>
+        <v>63.8900000000003</v>
       </c>
       <c r="BR3" s="12">
-        <v>5758.96</v>
+        <v>4874.88</v>
       </c>
       <c r="BS3" s="12">
         <f>BT3-BR3</f>
-        <v>108.57</v>
+        <v>54.25</v>
       </c>
       <c r="BT3" s="12">
-        <v>5867.53</v>
+        <v>4929.13</v>
       </c>
       <c r="BU3" s="12">
         <f>BV3-BT3</f>
-        <v>81.8900000000003</v>
+        <v>68.8800000000001</v>
       </c>
       <c r="BV3" s="12">
-        <v>5949.42</v>
+        <v>4998.01</v>
       </c>
       <c r="BW3" s="12">
         <f>BX3-BV3</f>
-        <v>63.9799999999996</v>
+        <v>72.1899999999996</v>
       </c>
       <c r="BX3" s="12">
-        <v>6013.4</v>
+        <v>5070.2</v>
       </c>
       <c r="BY3" s="12">
         <f>BZ3-BX3</f>
-        <v>64.9900000000007</v>
+        <v>38.8299999999999</v>
       </c>
       <c r="BZ3" s="12">
-        <v>6078.39</v>
+        <v>5109.03</v>
       </c>
       <c r="CA3" s="12">
         <f>CB3-BZ3</f>
-        <v>86.1399999999994</v>
+        <v>102.610000000001</v>
       </c>
       <c r="CB3" s="12">
-        <v>6164.53</v>
+        <v>5211.64</v>
       </c>
       <c r="CC3" s="12">
         <f>CD3-CB3</f>
-        <v>29.3400000000001</v>
+        <v>59.3199999999997</v>
       </c>
       <c r="CD3" s="12">
-        <v>6193.87</v>
+        <v>5270.96</v>
       </c>
       <c r="CE3" s="12">
         <f>CF3-CD3</f>
-        <v>82.7200000000003</v>
+        <v>63.2200000000003</v>
       </c>
       <c r="CF3" s="12">
-        <v>6276.59</v>
+        <v>5334.18</v>
       </c>
       <c r="CG3" s="12">
         <f>CH3-CF3</f>
-        <v>160.44</v>
+        <v>272.25</v>
       </c>
       <c r="CH3" s="12">
-        <v>6437.03</v>
+        <v>5606.43</v>
       </c>
       <c r="CI3" s="12">
         <f>CJ3-CH3</f>
-        <v>40.8900000000003</v>
+        <v>78.3599999999997</v>
       </c>
       <c r="CJ3" s="12">
-        <v>6477.92</v>
+        <v>5684.79</v>
       </c>
       <c r="CK3" s="12">
         <f>CL3-CJ3</f>
-        <v>102.59</v>
+        <v>116.21</v>
       </c>
       <c r="CL3" s="12">
-        <v>6580.51</v>
+        <v>5801</v>
       </c>
       <c r="CM3" s="12">
         <f>CN3-CL3</f>
-        <v>95.1399999999994</v>
+        <v>62.1700000000001</v>
       </c>
       <c r="CN3" s="12">
-        <v>6675.65</v>
+        <v>5863.17</v>
       </c>
       <c r="CO3" s="12">
         <f>CP3-CN3</f>
-        <v>149.110000000001</v>
+        <v>27.79</v>
       </c>
       <c r="CP3" s="12">
-        <v>6824.76</v>
+        <v>5890.96</v>
       </c>
       <c r="CQ3" s="12">
         <f>CR3-CP3</f>
-        <v>76.1799999999994</v>
+        <v>135.12</v>
       </c>
       <c r="CR3" s="12">
-        <v>6900.94</v>
+        <v>6026.08</v>
       </c>
       <c r="CS3" s="12">
         <f>CT3-CR3</f>
-        <v>144.77</v>
+        <v>252.66</v>
       </c>
       <c r="CT3" s="12">
-        <v>7045.71</v>
+        <v>6278.74</v>
       </c>
       <c r="CU3" s="12">
         <f>CV3-CT3</f>
-        <v>135.99</v>
+        <v>96.1400000000003</v>
       </c>
       <c r="CV3" s="12">
-        <v>7181.7</v>
+        <v>6374.88</v>
       </c>
       <c r="CW3" s="11">
         <f>CX3-CV3</f>
-        <v>80.0600000000004</v>
+        <v>85.71</v>
       </c>
       <c r="CX3" s="12">
-        <v>7261.76</v>
+        <v>6460.59</v>
       </c>
       <c r="CY3" s="12">
         <f>CZ3-CX3</f>
-        <v>137.86</v>
+        <v>74.0699999999997</v>
       </c>
       <c r="CZ3" s="12">
-        <v>7399.62</v>
+        <v>6534.66</v>
       </c>
       <c r="DA3" s="12">
         <f>DB3-CZ3</f>
-        <v>22.5600000000004</v>
+        <v>110.27</v>
       </c>
       <c r="DB3" s="12">
-        <v>7422.18</v>
+        <v>6644.93</v>
       </c>
       <c r="DC3" s="12">
         <f>DD3-DB3</f>
-        <v>88.3299999999999</v>
+        <v>95.1599999999999</v>
       </c>
       <c r="DD3" s="12">
-        <v>7510.51</v>
+        <v>6740.09</v>
       </c>
       <c r="DE3" s="12">
         <f>DF3-DD3</f>
-        <v>133.13</v>
+        <v>134.67</v>
       </c>
       <c r="DF3" s="12">
-        <v>7643.64</v>
+        <v>6874.76</v>
       </c>
       <c r="DG3" s="12">
         <f>DH3-DF3</f>
-        <v>64.6899999999996</v>
+        <v>-37.1199999999999</v>
       </c>
       <c r="DH3" s="12">
-        <v>7708.33</v>
+        <v>6837.64</v>
       </c>
       <c r="DI3" s="12">
         <f>DJ3-DH3</f>
-        <v>63.2200000000003</v>
+        <v>169.32</v>
       </c>
       <c r="DJ3" s="12">
-        <v>7771.55</v>
+        <v>7006.96</v>
       </c>
       <c r="DK3" s="12">
         <f>DL3-DJ3</f>
-        <v>150.59</v>
+        <v>120.26</v>
       </c>
       <c r="DL3" s="12">
-        <v>7922.14</v>
+        <v>7127.22</v>
       </c>
       <c r="DM3" s="12">
         <f>DN3-DL3</f>
-        <v>84.6300000000001</v>
+        <v>239.96</v>
       </c>
       <c r="DN3" s="12">
-        <v>8006.77</v>
+        <v>7367.18</v>
       </c>
       <c r="DO3" s="11">
         <f>DP3-DN3</f>
-        <v>102.36</v>
+        <v>-0.0900000000001455</v>
       </c>
       <c r="DP3" s="12">
-        <v>8109.13</v>
+        <v>7367.09</v>
       </c>
       <c r="DQ3" s="12">
         <f>DR3-DP3</f>
-        <v>26.6899999999996</v>
+        <v>94.3099999999995</v>
       </c>
       <c r="DR3" s="12">
-        <v>8135.82</v>
+        <v>7461.4</v>
       </c>
       <c r="DS3" s="12">
         <f>DT3-DR3</f>
-        <v>115.76</v>
+        <v>129.72</v>
       </c>
       <c r="DT3" s="12">
-        <v>8251.58</v>
+        <v>7591.12</v>
       </c>
       <c r="DU3" s="12">
         <f>DV3-DT3</f>
-        <v>71.8099999999995</v>
+        <v>53.5200000000004</v>
       </c>
       <c r="DV3" s="12">
-        <v>8323.39</v>
+        <v>7644.64</v>
       </c>
       <c r="DW3" s="12">
         <f>DX3-DV3</f>
-        <v>-46.9099999999999</v>
+        <v>22.3299999999999</v>
       </c>
       <c r="DX3" s="12">
-        <v>8276.48</v>
+        <v>7666.97</v>
       </c>
       <c r="DY3" s="12">
         <f>DZ3-DX3</f>
-        <v>119</v>
+        <v>63.7199999999993</v>
       </c>
       <c r="DZ3" s="12">
-        <v>8395.48</v>
+        <v>7730.69</v>
       </c>
       <c r="EA3" s="12">
         <f>EB3-DZ3</f>
-        <v>136.75</v>
+        <v>107.67</v>
       </c>
       <c r="EB3" s="12">
-        <v>8532.23</v>
+        <v>7838.36</v>
       </c>
       <c r="EC3" s="12">
         <f>ED3-EB3</f>
-        <v>109.560000000001</v>
+        <v>63.3299999999999</v>
       </c>
       <c r="ED3" s="12">
-        <v>8641.79</v>
+        <v>7901.69</v>
       </c>
       <c r="EE3" s="12">
         <f>EF3-ED3</f>
-        <v>53.1899999999987</v>
+        <v>98.8900000000003</v>
       </c>
       <c r="EF3" s="12">
-        <v>8694.98</v>
+        <v>8000.58</v>
       </c>
       <c r="EG3" s="12">
         <f>EH3-EF3</f>
-        <v>69.5</v>
+        <v>134.14</v>
       </c>
       <c r="EH3" s="12">
-        <v>8764.48</v>
+        <v>8134.72</v>
       </c>
       <c r="EI3" s="12">
         <f>EJ3-EH3</f>
-        <v>37.1499999999996</v>
+        <v>87.2499999999991</v>
       </c>
       <c r="EJ3" s="12">
-        <v>8801.63</v>
+        <v>8221.97</v>
       </c>
       <c r="EK3" s="12">
         <f>EL3-EJ3</f>
-        <v>188.300000000001</v>
+        <v>306.200000000001</v>
       </c>
       <c r="EL3" s="12">
-        <v>8989.93</v>
+        <v>8528.17</v>
       </c>
       <c r="EM3" s="12">
         <f>EN3-EL3</f>
-        <v>139.709999999999</v>
+        <v>200.549999999999</v>
       </c>
       <c r="EN3" s="12">
-        <v>9129.64</v>
+        <v>8728.72</v>
       </c>
       <c r="EO3" s="12">
         <f>EP3-EN3</f>
-        <v>78.25</v>
+        <v>68.0400000000009</v>
       </c>
       <c r="EP3" s="12">
-        <v>9207.89</v>
+        <v>8796.76</v>
       </c>
       <c r="EQ3" s="12">
         <f>ER3-EP3</f>
-        <v>54.5799999999999</v>
+        <v>202.039999999999</v>
       </c>
       <c r="ER3" s="12">
-        <v>9262.47</v>
+        <v>8998.8</v>
       </c>
       <c r="ES3" s="12">
         <f>ET3-ER3</f>
-        <v>137.59</v>
+        <v>202.59</v>
       </c>
       <c r="ET3" s="12">
-        <v>9400.06</v>
-      </c>
-      <c r="EU3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="EV3" s="9">
-        <v>2426.02</v>
-      </c>
-      <c r="EW3" s="9" t="s">
+        <v>9201.39</v>
+      </c>
+      <c r="EU3" s="12">
+        <f>EV3-ET3</f>
+        <v>264.52</v>
+      </c>
+      <c r="EV3" s="12">
+        <v>9465.91</v>
+      </c>
+      <c r="EW3" s="11" t="s">
         <v>97</v>
       </c>
       <c r="EX3" s="9">
-        <v>1327.12</v>
-      </c>
-      <c r="EY3" s="5">
-        <v>500</v>
-      </c>
-      <c r="EZ3" s="5">
-        <v>8.6</v>
+        <v>2242.07</v>
+      </c>
+      <c r="EY3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="EZ3" s="9">
+        <v>1010.07</v>
       </c>
       <c r="FA3" s="5">
-        <v>191519</v>
-      </c>
-      <c r="FB3" s="9">
-        <f>2.41/(ET3/EV3)</f>
-        <v>0.621986263917464</v>
-      </c>
-      <c r="FC3" s="9">
+        <v>200</v>
+      </c>
+      <c r="FB3" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="FC3" s="5">
+        <v>172501</v>
+      </c>
+      <c r="FD3" s="9">
+        <f>2.79/(EV3/EX3)</f>
+        <v>0.660831901000538</v>
+      </c>
+      <c r="FE3" s="9">
         <f>BP3-D3</f>
-        <v>3022.78</v>
+        <v>2277.14</v>
       </c>
     </row>
-    <row r="4" spans="1:169">
+    <row r="4" spans="1:171">
       <c r="A4" s="5" t="s">
         <v>98</v>
       </c>
@@ -3418,561 +3441,568 @@
         <v>99</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5">
-        <v>2533.85</v>
+        <v>2714.1</v>
       </c>
       <c r="E4" s="5">
         <f>F4-D4</f>
-        <v>50.0500000000002</v>
+        <v>123.29</v>
       </c>
       <c r="F4" s="5">
-        <v>2583.9</v>
+        <v>2837.39</v>
       </c>
       <c r="G4" s="5">
         <f>H4-F4</f>
-        <v>85.7599999999998</v>
+        <v>95.8499999999999</v>
       </c>
       <c r="H4" s="5">
-        <v>2669.66</v>
+        <v>2933.24</v>
       </c>
       <c r="I4" s="5">
         <f>J4-H4</f>
-        <v>81.79</v>
+        <v>92.46</v>
       </c>
       <c r="J4" s="5">
-        <v>2751.45</v>
+        <v>3025.7</v>
       </c>
       <c r="K4" s="5">
         <f>L4-J4</f>
-        <v>83.1700000000001</v>
+        <v>90.4100000000003</v>
       </c>
       <c r="L4" s="5">
-        <v>2834.62</v>
+        <v>3116.11</v>
       </c>
       <c r="M4" s="5">
         <f>N4-L4</f>
-        <v>56.9900000000002</v>
+        <v>103.54</v>
       </c>
       <c r="N4" s="5">
-        <v>2891.61</v>
+        <v>3219.65</v>
       </c>
       <c r="O4" s="5">
         <f>P4-N4</f>
-        <v>103.98</v>
+        <v>75.6599999999999</v>
       </c>
       <c r="P4" s="5">
-        <v>2995.59</v>
+        <v>3295.31</v>
       </c>
       <c r="Q4" s="5">
         <f>R4-P4</f>
-        <v>68.8499999999999</v>
+        <v>88.98</v>
       </c>
       <c r="R4" s="5">
-        <v>3064.44</v>
+        <v>3384.29</v>
       </c>
       <c r="S4" s="5">
         <f>T4-R4</f>
-        <v>47.6100000000001</v>
+        <v>102.46</v>
       </c>
       <c r="T4" s="5">
-        <v>3112.05</v>
+        <v>3486.75</v>
       </c>
       <c r="U4" s="5">
         <f>V4-T4</f>
-        <v>38.1599999999999</v>
+        <v>69.23</v>
       </c>
       <c r="V4" s="10">
-        <v>3150.21</v>
+        <v>3555.98</v>
       </c>
       <c r="W4" s="5">
         <f>X4-V4</f>
-        <v>146.1</v>
+        <v>133.46</v>
       </c>
       <c r="X4" s="10">
-        <v>3296.31</v>
+        <v>3689.44</v>
       </c>
       <c r="Y4" s="5">
         <f>Z4-X4</f>
-        <v>31.9400000000001</v>
+        <v>10.5999999999999</v>
       </c>
       <c r="Z4" s="5">
-        <v>3328.25</v>
+        <v>3700.04</v>
       </c>
       <c r="AA4" s="5">
         <f>AB4-Z4</f>
-        <v>79.8800000000001</v>
+        <v>145.58</v>
       </c>
       <c r="AB4" s="5">
-        <v>3408.13</v>
+        <v>3845.62</v>
       </c>
       <c r="AC4" s="5">
         <f>AD4-AB4</f>
-        <v>68.9099999999999</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>3477.04</v>
+        <v>64.1800000000003</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>3909.8</v>
       </c>
       <c r="AE4" s="9">
         <f>AF4-AD4</f>
-        <v>143.74</v>
+        <v>98.8399999999997</v>
       </c>
       <c r="AF4" s="9">
-        <v>3620.78</v>
+        <v>4008.64</v>
       </c>
       <c r="AG4" s="9">
         <f>AH4-AF4</f>
-        <v>82.0999999999999</v>
+        <v>157.920000000001</v>
       </c>
       <c r="AH4" s="9">
-        <v>3702.88</v>
+        <v>4166.56</v>
       </c>
       <c r="AI4" s="9">
         <f>AJ4-AH4</f>
-        <v>111.1</v>
+        <v>103.339999999999</v>
       </c>
       <c r="AJ4" s="9">
-        <v>3813.98</v>
+        <v>4269.9</v>
       </c>
       <c r="AK4" s="9">
         <f>AL4-AJ4</f>
-        <v>119.59</v>
+        <v>66.25</v>
       </c>
       <c r="AL4" s="9">
-        <v>3933.57</v>
+        <v>4336.15</v>
       </c>
       <c r="AM4" s="9">
         <f>AN4-AL4</f>
-        <v>39.71</v>
+        <v>138.700000000001</v>
       </c>
       <c r="AN4" s="9">
-        <v>3973.28</v>
+        <v>4474.85</v>
       </c>
       <c r="AO4" s="9">
         <f>AP4-AN4</f>
-        <v>94.1399999999999</v>
+        <v>78.4499999999998</v>
       </c>
       <c r="AP4" s="9">
-        <v>4067.42</v>
+        <v>4553.3</v>
       </c>
       <c r="AQ4" s="9">
         <f>AR4-AP4</f>
-        <v>51.1800000000003</v>
+        <v>56.7699999999995</v>
       </c>
       <c r="AR4" s="9">
-        <v>4118.6</v>
+        <v>4610.07</v>
       </c>
       <c r="AS4" s="9">
         <f>AT4-AR4</f>
-        <v>33.4499999999998</v>
+        <v>32.3699999999999</v>
       </c>
       <c r="AT4" s="9">
-        <v>4152.05</v>
+        <v>4642.44</v>
       </c>
       <c r="AU4" s="11">
         <f>AV4-AT4</f>
-        <v>31.5199999999995</v>
+        <v>77.6300000000001</v>
       </c>
       <c r="AV4" s="11">
-        <v>4183.57</v>
+        <v>4720.07</v>
       </c>
       <c r="AW4" s="12">
         <f>AX4-AV4</f>
-        <v>33.7400000000007</v>
+        <v>121.33</v>
       </c>
       <c r="AX4" s="12">
-        <v>4217.31</v>
+        <v>4841.4</v>
       </c>
       <c r="AY4" s="12">
         <f>AZ4-AX4</f>
-        <v>64.8499999999995</v>
+        <v>61.2400000000007</v>
       </c>
       <c r="AZ4" s="12">
-        <v>4282.16</v>
+        <v>4902.64</v>
       </c>
       <c r="BA4" s="12">
         <f>BB4-AZ4</f>
-        <v>25.75</v>
+        <v>64.3099999999995</v>
       </c>
       <c r="BB4" s="12">
-        <v>4307.91</v>
+        <v>4966.95</v>
       </c>
       <c r="BC4" s="12">
         <f>BD4-BB4</f>
-        <v>42.4400000000005</v>
+        <v>87.1000000000004</v>
       </c>
       <c r="BD4" s="12">
-        <v>4350.35</v>
+        <v>5054.05</v>
       </c>
       <c r="BE4" s="11">
         <f>BF4-BD4</f>
-        <v>98.5899999999992</v>
+        <v>154.29</v>
       </c>
       <c r="BF4" s="12">
-        <v>4448.94</v>
+        <v>5208.34</v>
       </c>
       <c r="BG4" s="12">
         <f>BH4-BF4</f>
-        <v>93.3700000000008</v>
+        <v>181.45</v>
       </c>
       <c r="BH4" s="12">
-        <v>4542.31</v>
+        <v>5389.79</v>
       </c>
       <c r="BI4" s="12">
         <f>BJ4-BH4</f>
-        <v>105.799999999999</v>
+        <v>99</v>
       </c>
       <c r="BJ4" s="12">
-        <v>4648.11</v>
+        <v>5488.79</v>
       </c>
       <c r="BK4" s="12">
         <f>BL4-BJ4</f>
-        <v>49.4700000000003</v>
+        <v>53.9499999999998</v>
       </c>
       <c r="BL4" s="12">
-        <v>4697.58</v>
+        <v>5542.74</v>
       </c>
       <c r="BM4" s="12">
         <f>BN4-BL4</f>
-        <v>57.8599999999997</v>
+        <v>72.0300000000007</v>
       </c>
       <c r="BN4" s="12">
-        <v>4755.44</v>
+        <v>5614.77</v>
       </c>
       <c r="BO4" s="12">
         <f>BP4-BN4</f>
-        <v>55.5500000000002</v>
+        <v>122.11</v>
       </c>
       <c r="BP4" s="12">
-        <v>4810.99</v>
+        <v>5736.88</v>
       </c>
       <c r="BQ4" s="12">
         <f>BR4-BP4</f>
-        <v>63.8900000000003</v>
+        <v>22.0799999999999</v>
       </c>
       <c r="BR4" s="12">
-        <v>4874.88</v>
+        <v>5758.96</v>
       </c>
       <c r="BS4" s="12">
         <f>BT4-BR4</f>
-        <v>54.25</v>
+        <v>108.57</v>
       </c>
       <c r="BT4" s="12">
-        <v>4929.13</v>
+        <v>5867.53</v>
       </c>
       <c r="BU4" s="12">
         <f>BV4-BT4</f>
-        <v>68.8800000000001</v>
+        <v>81.8900000000003</v>
       </c>
       <c r="BV4" s="12">
-        <v>4998.01</v>
+        <v>5949.42</v>
       </c>
       <c r="BW4" s="12">
         <f>BX4-BV4</f>
-        <v>72.1899999999996</v>
+        <v>63.9799999999996</v>
       </c>
       <c r="BX4" s="12">
-        <v>5070.2</v>
+        <v>6013.4</v>
       </c>
       <c r="BY4" s="12">
         <f>BZ4-BX4</f>
-        <v>38.8299999999999</v>
+        <v>64.9900000000007</v>
       </c>
       <c r="BZ4" s="12">
-        <v>5109.03</v>
+        <v>6078.39</v>
       </c>
       <c r="CA4" s="12">
         <f>CB4-BZ4</f>
-        <v>102.610000000001</v>
+        <v>86.1399999999994</v>
       </c>
       <c r="CB4" s="12">
-        <v>5211.64</v>
+        <v>6164.53</v>
       </c>
       <c r="CC4" s="12">
         <f>CD4-CB4</f>
-        <v>59.3199999999997</v>
+        <v>29.3400000000001</v>
       </c>
       <c r="CD4" s="12">
-        <v>5270.96</v>
+        <v>6193.87</v>
       </c>
       <c r="CE4" s="12">
         <f>CF4-CD4</f>
-        <v>63.2200000000003</v>
+        <v>82.7200000000003</v>
       </c>
       <c r="CF4" s="12">
-        <v>5334.18</v>
+        <v>6276.59</v>
       </c>
       <c r="CG4" s="12">
         <f>CH4-CF4</f>
-        <v>272.25</v>
+        <v>160.44</v>
       </c>
       <c r="CH4" s="12">
-        <v>5606.43</v>
+        <v>6437.03</v>
       </c>
       <c r="CI4" s="12">
         <f>CJ4-CH4</f>
-        <v>78.3599999999997</v>
+        <v>40.8900000000003</v>
       </c>
       <c r="CJ4" s="12">
-        <v>5684.79</v>
+        <v>6477.92</v>
       </c>
       <c r="CK4" s="12">
         <f>CL4-CJ4</f>
-        <v>116.21</v>
+        <v>102.59</v>
       </c>
       <c r="CL4" s="12">
-        <v>5801</v>
+        <v>6580.51</v>
       </c>
       <c r="CM4" s="12">
         <f>CN4-CL4</f>
-        <v>62.1700000000001</v>
+        <v>95.1399999999994</v>
       </c>
       <c r="CN4" s="12">
-        <v>5863.17</v>
+        <v>6675.65</v>
       </c>
       <c r="CO4" s="12">
         <f>CP4-CN4</f>
-        <v>27.79</v>
+        <v>149.110000000001</v>
       </c>
       <c r="CP4" s="12">
-        <v>5890.96</v>
+        <v>6824.76</v>
       </c>
       <c r="CQ4" s="12">
         <f>CR4-CP4</f>
-        <v>135.12</v>
+        <v>76.1799999999994</v>
       </c>
       <c r="CR4" s="12">
-        <v>6026.08</v>
+        <v>6900.94</v>
       </c>
       <c r="CS4" s="12">
         <f>CT4-CR4</f>
-        <v>252.66</v>
+        <v>144.77</v>
       </c>
       <c r="CT4" s="12">
-        <v>6278.74</v>
+        <v>7045.71</v>
       </c>
       <c r="CU4" s="12">
         <f>CV4-CT4</f>
-        <v>96.1400000000003</v>
+        <v>135.99</v>
       </c>
       <c r="CV4" s="12">
-        <v>6374.88</v>
+        <v>7181.7</v>
       </c>
       <c r="CW4" s="11">
         <f>CX4-CV4</f>
-        <v>85.71</v>
+        <v>80.0600000000004</v>
       </c>
       <c r="CX4" s="12">
-        <v>6460.59</v>
+        <v>7261.76</v>
       </c>
       <c r="CY4" s="12">
         <f>CZ4-CX4</f>
-        <v>74.0699999999997</v>
+        <v>137.86</v>
       </c>
       <c r="CZ4" s="12">
-        <v>6534.66</v>
+        <v>7399.62</v>
       </c>
       <c r="DA4" s="12">
         <f>DB4-CZ4</f>
-        <v>110.27</v>
+        <v>22.5600000000004</v>
       </c>
       <c r="DB4" s="12">
-        <v>6644.93</v>
+        <v>7422.18</v>
       </c>
       <c r="DC4" s="12">
         <f>DD4-DB4</f>
-        <v>95.1599999999999</v>
+        <v>88.3299999999999</v>
       </c>
       <c r="DD4" s="12">
-        <v>6740.09</v>
+        <v>7510.51</v>
       </c>
       <c r="DE4" s="12">
         <f>DF4-DD4</f>
-        <v>134.67</v>
+        <v>133.13</v>
       </c>
       <c r="DF4" s="12">
-        <v>6874.76</v>
+        <v>7643.64</v>
       </c>
       <c r="DG4" s="12">
         <f>DH4-DF4</f>
-        <v>-37.1199999999999</v>
+        <v>64.6899999999996</v>
       </c>
       <c r="DH4" s="12">
-        <v>6837.64</v>
+        <v>7708.33</v>
       </c>
       <c r="DI4" s="12">
         <f>DJ4-DH4</f>
-        <v>169.32</v>
+        <v>63.2200000000003</v>
       </c>
       <c r="DJ4" s="12">
-        <v>7006.96</v>
+        <v>7771.55</v>
       </c>
       <c r="DK4" s="12">
         <f>DL4-DJ4</f>
-        <v>120.26</v>
+        <v>150.59</v>
       </c>
       <c r="DL4" s="12">
-        <v>7127.22</v>
+        <v>7922.14</v>
       </c>
       <c r="DM4" s="12">
         <f>DN4-DL4</f>
-        <v>239.96</v>
+        <v>84.6300000000001</v>
       </c>
       <c r="DN4" s="12">
-        <v>7367.18</v>
+        <v>8006.77</v>
       </c>
       <c r="DO4" s="11">
         <f>DP4-DN4</f>
-        <v>-0.0900000000001455</v>
+        <v>102.36</v>
       </c>
       <c r="DP4" s="12">
-        <v>7367.09</v>
+        <v>8109.13</v>
       </c>
       <c r="DQ4" s="12">
         <f>DR4-DP4</f>
-        <v>94.3099999999995</v>
+        <v>26.6899999999996</v>
       </c>
       <c r="DR4" s="12">
-        <v>7461.4</v>
+        <v>8135.82</v>
       </c>
       <c r="DS4" s="12">
         <f>DT4-DR4</f>
-        <v>129.72</v>
+        <v>115.76</v>
       </c>
       <c r="DT4" s="12">
-        <v>7591.12</v>
+        <v>8251.58</v>
       </c>
       <c r="DU4" s="12">
         <f>DV4-DT4</f>
-        <v>53.5200000000004</v>
+        <v>71.8099999999995</v>
       </c>
       <c r="DV4" s="12">
-        <v>7644.64</v>
+        <v>8323.39</v>
       </c>
       <c r="DW4" s="12">
         <f>DX4-DV4</f>
-        <v>22.3299999999999</v>
+        <v>-46.9099999999999</v>
       </c>
       <c r="DX4" s="12">
-        <v>7666.97</v>
+        <v>8276.48</v>
       </c>
       <c r="DY4" s="12">
         <f>DZ4-DX4</f>
-        <v>63.7199999999993</v>
+        <v>119</v>
       </c>
       <c r="DZ4" s="12">
-        <v>7730.69</v>
+        <v>8395.48</v>
       </c>
       <c r="EA4" s="12">
         <f>EB4-DZ4</f>
-        <v>107.67</v>
+        <v>136.75</v>
       </c>
       <c r="EB4" s="12">
-        <v>7838.36</v>
+        <v>8532.23</v>
       </c>
       <c r="EC4" s="12">
         <f>ED4-EB4</f>
-        <v>63.3299999999999</v>
+        <v>109.560000000001</v>
       </c>
       <c r="ED4" s="12">
-        <v>7901.69</v>
+        <v>8641.79</v>
       </c>
       <c r="EE4" s="12">
         <f>EF4-ED4</f>
-        <v>98.8900000000003</v>
+        <v>53.1899999999987</v>
       </c>
       <c r="EF4" s="12">
-        <v>8000.58</v>
+        <v>8694.98</v>
       </c>
       <c r="EG4" s="12">
         <f>EH4-EF4</f>
-        <v>134.14</v>
+        <v>69.5</v>
       </c>
       <c r="EH4" s="12">
-        <v>8134.72</v>
+        <v>8764.48</v>
       </c>
       <c r="EI4" s="12">
         <f>EJ4-EH4</f>
-        <v>87.2499999999991</v>
+        <v>37.1499999999996</v>
       </c>
       <c r="EJ4" s="12">
-        <v>8221.97</v>
+        <v>8801.63</v>
       </c>
       <c r="EK4" s="12">
         <f>EL4-EJ4</f>
-        <v>306.200000000001</v>
+        <v>188.300000000001</v>
       </c>
       <c r="EL4" s="12">
-        <v>8528.17</v>
+        <v>8989.93</v>
       </c>
       <c r="EM4" s="12">
         <f>EN4-EL4</f>
-        <v>200.549999999999</v>
+        <v>139.709999999999</v>
       </c>
       <c r="EN4" s="12">
-        <v>8728.72</v>
+        <v>9129.64</v>
       </c>
       <c r="EO4" s="12">
         <f>EP4-EN4</f>
-        <v>68.0400000000009</v>
+        <v>78.25</v>
       </c>
       <c r="EP4" s="12">
-        <v>8796.76</v>
+        <v>9207.89</v>
       </c>
       <c r="EQ4" s="12">
         <f>ER4-EP4</f>
-        <v>202.039999999999</v>
+        <v>54.5799999999999</v>
       </c>
       <c r="ER4" s="12">
-        <v>8998.8</v>
+        <v>9262.47</v>
       </c>
       <c r="ES4" s="12">
         <f>ET4-ER4</f>
-        <v>202.59</v>
+        <v>137.59</v>
       </c>
       <c r="ET4" s="12">
-        <v>9201.39</v>
-      </c>
-      <c r="EU4" s="11" t="s">
+        <v>9400.06</v>
+      </c>
+      <c r="EU4" s="12">
+        <f>EV4-ET4</f>
+        <v>-31.1899999999987</v>
+      </c>
+      <c r="EV4" s="12">
+        <v>9368.87</v>
+      </c>
+      <c r="EW4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="EV4" s="9">
-        <v>2216.77</v>
-      </c>
-      <c r="EW4" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="EX4" s="9">
-        <v>1010.07</v>
-      </c>
-      <c r="EY4" s="5">
-        <v>200</v>
-      </c>
-      <c r="EZ4" s="5">
-        <v>1.6</v>
+        <v>2652.52</v>
+      </c>
+      <c r="EY4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="EZ4" s="9">
+        <v>1327.12</v>
       </c>
       <c r="FA4" s="5">
-        <v>172501</v>
-      </c>
-      <c r="FB4" s="9">
-        <f>2.41/(ET4/EV4)</f>
-        <v>0.580609636152799</v>
-      </c>
-      <c r="FC4" s="9">
+        <v>500</v>
+      </c>
+      <c r="FB4" s="5">
+        <v>8.6</v>
+      </c>
+      <c r="FC4" s="5">
+        <v>191519</v>
+      </c>
+      <c r="FD4" s="9">
+        <f>2.79/(EV4/EX4)</f>
+        <v>0.789906445494494</v>
+      </c>
+      <c r="FE4" s="9">
         <f>BP4-D4</f>
-        <v>2277.14</v>
+        <v>3022.78</v>
       </c>
     </row>
-    <row r="5" spans="1:169">
+    <row r="5" spans="1:171">
       <c r="A5" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" s="5">
         <v>1754.54</v>
@@ -4488,48 +4518,55 @@
       <c r="ET5" s="12">
         <v>7532.22</v>
       </c>
-      <c r="EU5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="EV5" s="9">
-        <v>1641.31</v>
-      </c>
-      <c r="EW5" s="9" t="s">
+      <c r="EU5" s="12">
+        <f>EV5-ET5</f>
+        <v>53.1599999999999</v>
+      </c>
+      <c r="EV5" s="12">
+        <v>7585.38</v>
+      </c>
+      <c r="EW5" s="11" t="s">
         <v>105</v>
       </c>
       <c r="EX5" s="9">
+        <v>1591.14</v>
+      </c>
+      <c r="EY5" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="EZ5" s="9">
         <v>686.88</v>
       </c>
-      <c r="EY5" s="5">
+      <c r="FA5" s="5">
         <v>300</v>
       </c>
-      <c r="EZ5" s="5">
+      <c r="FB5" s="5">
         <v>2.2</v>
       </c>
-      <c r="FA5" s="5">
+      <c r="FC5" s="5">
         <v>132783</v>
       </c>
-      <c r="FB5" s="9">
-        <f>2.41/(ET5/EV5)</f>
-        <v>0.525151562222028</v>
-      </c>
-      <c r="FC5" s="9">
+      <c r="FD5" s="9">
+        <f>2.79/(EV5/EX5)</f>
+        <v>0.585241688616786</v>
+      </c>
+      <c r="FE5" s="9">
         <f>BP5-D5</f>
         <v>2267.65</v>
       </c>
-      <c r="FM5">
+      <c r="FO5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:169">
+    <row r="6" spans="1:171">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" s="1">
         <v>1735.94</v>
@@ -5045,45 +5082,52 @@
       <c r="ET6" s="16">
         <v>6413.72</v>
       </c>
-      <c r="EU6" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="EV6" s="14">
-        <v>2037.82</v>
-      </c>
-      <c r="EW6" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="EX6" s="9">
+      <c r="EU6" s="16">
+        <f>EV6-ET6</f>
+        <v>107.98</v>
+      </c>
+      <c r="EV6" s="16">
+        <v>6521.7</v>
+      </c>
+      <c r="EW6" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="EX6" s="14">
+        <v>2125.02</v>
+      </c>
+      <c r="EY6" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="EZ6" s="9">
         <v>824.67</v>
       </c>
-      <c r="EY6" s="5">
+      <c r="FA6" s="5">
         <v>80</v>
       </c>
-      <c r="EZ6" s="5">
+      <c r="FB6" s="5">
         <v>7.2</v>
       </c>
-      <c r="FA6" s="5">
+      <c r="FC6" s="5">
         <v>150192</v>
       </c>
-      <c r="FB6" s="9">
-        <f>2.41/(ET6/EV6)</f>
-        <v>0.765725070629837</v>
-      </c>
-      <c r="FC6" s="9">
+      <c r="FD6" s="9">
+        <f>2.79/(EV6/EX6)</f>
+        <v>0.909089010534063</v>
+      </c>
+      <c r="FE6" s="9">
         <f>BP6-D6</f>
         <v>1944.52</v>
       </c>
     </row>
-    <row r="7" spans="1:169">
+    <row r="7" spans="1:171">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" s="1">
         <v>1350.52</v>
@@ -5599,45 +5643,52 @@
       <c r="ET7" s="16">
         <v>6219.38</v>
       </c>
-      <c r="EU7" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="EV7" s="14">
-        <v>1911.17</v>
-      </c>
-      <c r="EW7" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="EX7" s="9">
+      <c r="EU7" s="16">
+        <f>EV7-ET7</f>
+        <v>111.59</v>
+      </c>
+      <c r="EV7" s="16">
+        <v>6330.97</v>
+      </c>
+      <c r="EW7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="EX7" s="14">
+        <v>1944.37</v>
+      </c>
+      <c r="EY7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="EZ7" s="9">
         <v>896.02</v>
       </c>
-      <c r="EY7" s="5">
+      <c r="FA7" s="5">
         <v>65</v>
       </c>
-      <c r="EZ7" s="5">
+      <c r="FB7" s="5">
         <v>1.4</v>
       </c>
-      <c r="FA7" s="5">
+      <c r="FC7" s="5">
         <v>127603</v>
       </c>
-      <c r="FB7" s="9">
-        <f>2.41/(ET7/EV7)</f>
-        <v>0.740575378896289</v>
-      </c>
-      <c r="FC7" s="9">
+      <c r="FD7" s="9">
+        <f>2.79/(EV7/EX7)</f>
+        <v>0.856865898906487</v>
+      </c>
+      <c r="FE7" s="9">
         <f>BP7-D7</f>
         <v>2104.56</v>
       </c>
     </row>
-    <row r="8" spans="1:169">
+    <row r="8" spans="1:171">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1">
         <v>2136.24</v>
@@ -6153,45 +6204,52 @@
       <c r="ET8" s="16">
         <v>5895.95</v>
       </c>
-      <c r="EU8" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="EV8" s="14">
-        <v>2128.77</v>
-      </c>
-      <c r="EW8" s="9" t="s">
+      <c r="EU8" s="16">
+        <f>EV8-ET8</f>
+        <v>121.04</v>
+      </c>
+      <c r="EV8" s="16">
+        <v>6016.99</v>
+      </c>
+      <c r="EW8" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="EX8" s="9">
+      <c r="EX8" s="14">
+        <v>2252.57</v>
+      </c>
+      <c r="EY8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="EZ8" s="9">
         <v>1211.82</v>
       </c>
-      <c r="EY8" s="5">
+      <c r="FA8" s="5">
         <v>20</v>
       </c>
-      <c r="EZ8" s="5">
+      <c r="FB8" s="5">
         <v>1.2</v>
       </c>
-      <c r="FA8" s="5">
+      <c r="FC8" s="5">
         <v>153852</v>
       </c>
-      <c r="FB8" s="9">
-        <f>2.41/(ET8/EV8)</f>
-        <v>0.870145727151689</v>
-      </c>
-      <c r="FC8" s="9">
+      <c r="FD8" s="9">
+        <f>2.79/(EV8/EX8)</f>
+        <v>1.04448740981787</v>
+      </c>
+      <c r="FE8" s="9">
         <f>BP8-D8</f>
         <v>1584.75</v>
       </c>
     </row>
-    <row r="9" spans="1:169">
+    <row r="9" spans="1:171">
       <c r="A9" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" s="1">
         <v>1726.42</v>
@@ -6707,45 +6765,52 @@
       <c r="ET9" s="16">
         <v>5716.33</v>
       </c>
-      <c r="EU9" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="EV9" s="14">
-        <v>1904.42</v>
-      </c>
-      <c r="EW9" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="EX9" s="9">
+      <c r="EU9" s="16">
+        <f>EV9-ET9</f>
+        <v>31.5900000000001</v>
+      </c>
+      <c r="EV9" s="16">
+        <v>5747.92</v>
+      </c>
+      <c r="EW9" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="EX9" s="14">
+        <v>1751.52</v>
+      </c>
+      <c r="EY9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="EZ9" s="9">
         <v>754.67</v>
       </c>
-      <c r="EY9" s="5">
+      <c r="FA9" s="5">
         <v>50</v>
       </c>
-      <c r="EZ9" s="5">
+      <c r="FB9" s="5">
         <v>1.3</v>
       </c>
-      <c r="FA9" s="5">
+      <c r="FC9" s="5">
         <v>124763</v>
       </c>
-      <c r="FB9" s="9">
-        <f>2.41/(ET9/EV9)</f>
-        <v>0.802901896846403</v>
-      </c>
-      <c r="FC9" s="9">
+      <c r="FD9" s="9">
+        <f>2.79/(EV9/EX9)</f>
+        <v>0.850175506965998</v>
+      </c>
+      <c r="FE9" s="9">
         <f>BP9-D9</f>
         <v>1654.23</v>
       </c>
     </row>
-    <row r="10" spans="1:169">
+    <row r="10" spans="1:171">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="1">
         <v>1446.65</v>
@@ -7261,599 +7326,613 @@
       <c r="ET10" s="16">
         <v>5337.14</v>
       </c>
-      <c r="EU10" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="EV10" s="14">
-        <v>2212.17</v>
-      </c>
-      <c r="EW10" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="EX10" s="9">
+      <c r="EU10" s="16">
+        <f>EV10-ET10</f>
+        <v>19.5799999999999</v>
+      </c>
+      <c r="EV10" s="16">
+        <v>5356.72</v>
+      </c>
+      <c r="EW10" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="EX10" s="14">
+        <v>1918.37</v>
+      </c>
+      <c r="EY10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="EZ10" s="9">
         <v>1048.57</v>
       </c>
-      <c r="EY10" s="5">
+      <c r="FA10" s="5">
         <v>65</v>
       </c>
-      <c r="EZ10" s="5">
+      <c r="FB10" s="5">
         <v>1.4</v>
       </c>
-      <c r="FA10" s="5">
+      <c r="FC10" s="5">
         <v>109333</v>
       </c>
-      <c r="FB10" s="9">
-        <f>2.41/(ET10/EV10)</f>
-        <v>0.998911345776952</v>
-      </c>
-      <c r="FC10" s="9">
+      <c r="FD10" s="9">
+        <f>2.79/(EV10/EX10)</f>
+        <v>0.999165963500052</v>
+      </c>
+      <c r="FE10" s="9">
         <f>BP10-D10</f>
         <v>1685.99</v>
       </c>
     </row>
-    <row r="11" spans="1:169">
-      <c r="A11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="2">
+    <row r="11" spans="1:171">
+      <c r="A11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="1">
         <v>1425.22</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <f>F11-D11</f>
         <v>64.8599999999999</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>1490.08</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <f>H11-F11</f>
         <v>46</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>1536.08</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <f>J11-H11</f>
         <v>50.8500000000001</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>1586.93</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <f>L11-J11</f>
         <v>86.5599999999999</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>1673.49</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <f>N11-L11</f>
         <v>38.5599999999999</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>1712.05</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
         <f>P11-N11</f>
         <v>57.0900000000001</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>1769.14</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <f>R11-P11</f>
         <v>50.8699999999999</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>1820.01</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <f>T11-R11</f>
         <v>94.4300000000001</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="1">
         <v>1914.44</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <f>V11-T11</f>
         <v>31.51</v>
       </c>
-      <c r="V11" s="17">
+      <c r="V11" s="13">
         <v>1945.95</v>
       </c>
-      <c r="W11" s="2">
+      <c r="W11" s="1">
         <f>X11-V11</f>
         <v>92.5899999999999</v>
       </c>
-      <c r="X11" s="17">
+      <c r="X11" s="13">
         <v>2038.54</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y11" s="1">
         <f>Z11-X11</f>
         <v>48.1399999999999</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="Z11" s="1">
         <v>2086.68</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AA11" s="1">
         <f>AB11-Z11</f>
         <v>78.1300000000001</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AB11" s="1">
         <v>2164.81</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AC11" s="1">
         <f>AD11-AB11</f>
         <v>39.8400000000001</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AD11" s="1">
         <v>2204.65</v>
       </c>
-      <c r="AE11" s="18">
+      <c r="AE11" s="14">
         <f>AF11-AD11</f>
         <v>79.98</v>
       </c>
-      <c r="AF11" s="18">
+      <c r="AF11" s="14">
         <v>2284.63</v>
       </c>
-      <c r="AG11" s="18">
+      <c r="AG11" s="14">
         <f>AH11-AF11</f>
         <v>35.54</v>
       </c>
-      <c r="AH11" s="18">
+      <c r="AH11" s="14">
         <v>2320.17</v>
       </c>
-      <c r="AI11" s="18">
+      <c r="AI11" s="14">
         <f>AJ11-AH11</f>
         <v>53.4000000000001</v>
       </c>
-      <c r="AJ11" s="18">
+      <c r="AJ11" s="14">
         <v>2373.57</v>
       </c>
-      <c r="AK11" s="18">
+      <c r="AK11" s="14">
         <f>AL11-AJ11</f>
         <v>36.6599999999999</v>
       </c>
-      <c r="AL11" s="18">
+      <c r="AL11" s="14">
         <v>2410.23</v>
       </c>
-      <c r="AM11" s="18">
+      <c r="AM11" s="14">
         <f>AN11-AL11</f>
         <v>51.25</v>
       </c>
-      <c r="AN11" s="18">
+      <c r="AN11" s="14">
         <v>2461.48</v>
       </c>
-      <c r="AO11" s="18">
+      <c r="AO11" s="14">
         <f>AP11-AN11</f>
         <v>66.4499999999998</v>
       </c>
-      <c r="AP11" s="18">
+      <c r="AP11" s="14">
         <v>2527.93</v>
       </c>
-      <c r="AQ11" s="18">
+      <c r="AQ11" s="14">
         <f>AR11-AP11</f>
         <v>47.4900000000002</v>
       </c>
-      <c r="AR11" s="18">
+      <c r="AR11" s="14">
         <v>2575.42</v>
       </c>
-      <c r="AS11" s="18">
+      <c r="AS11" s="14">
         <f>AT11-AR11</f>
         <v>40.75</v>
       </c>
-      <c r="AT11" s="18">
+      <c r="AT11" s="14">
         <v>2616.17</v>
       </c>
-      <c r="AU11" s="19">
+      <c r="AU11" s="15">
         <f>AV11-AT11</f>
         <v>48.8499999999999</v>
       </c>
-      <c r="AV11" s="19">
+      <c r="AV11" s="15">
         <v>2665.02</v>
       </c>
-      <c r="AW11" s="20">
+      <c r="AW11" s="16">
         <f>AX11-AV11</f>
         <v>41.5999999999999</v>
       </c>
-      <c r="AX11" s="20">
+      <c r="AX11" s="16">
         <v>2706.62</v>
       </c>
-      <c r="AY11" s="20">
+      <c r="AY11" s="16">
         <f>AZ11-AX11</f>
         <v>42.8900000000003</v>
       </c>
-      <c r="AZ11" s="20">
+      <c r="AZ11" s="16">
         <v>2749.51</v>
       </c>
-      <c r="BA11" s="20">
+      <c r="BA11" s="16">
         <f>BB11-AZ11</f>
         <v>35.6099999999997</v>
       </c>
-      <c r="BB11" s="20">
+      <c r="BB11" s="16">
         <v>2785.12</v>
       </c>
-      <c r="BC11" s="20">
+      <c r="BC11" s="16">
         <f>BD11-BB11</f>
         <v>30.4900000000002</v>
       </c>
-      <c r="BD11" s="20">
+      <c r="BD11" s="16">
         <v>2815.61</v>
       </c>
-      <c r="BE11" s="19">
+      <c r="BE11" s="15">
         <f>BF11-BD11</f>
         <v>72.29</v>
       </c>
-      <c r="BF11" s="20">
+      <c r="BF11" s="16">
         <v>2887.9</v>
       </c>
-      <c r="BG11" s="20">
+      <c r="BG11" s="16">
         <f>BH11-BF11</f>
         <v>44.9899999999998</v>
       </c>
-      <c r="BH11" s="20">
+      <c r="BH11" s="16">
         <v>2932.89</v>
       </c>
-      <c r="BI11" s="20">
+      <c r="BI11" s="16">
         <f>BJ11-BH11</f>
         <v>72.2400000000002</v>
       </c>
-      <c r="BJ11" s="20">
+      <c r="BJ11" s="16">
         <v>3005.13</v>
       </c>
-      <c r="BK11" s="20">
+      <c r="BK11" s="16">
         <f>BL11-BJ11</f>
         <v>54.4699999999998</v>
       </c>
-      <c r="BL11" s="20">
+      <c r="BL11" s="16">
         <v>3059.6</v>
       </c>
-      <c r="BM11" s="20">
+      <c r="BM11" s="16">
         <f>BN11-BL11</f>
         <v>16.6700000000001</v>
       </c>
-      <c r="BN11" s="20">
+      <c r="BN11" s="16">
         <v>3076.27</v>
       </c>
-      <c r="BO11" s="20">
+      <c r="BO11" s="16">
         <f>BP11-BN11</f>
         <v>64.46</v>
       </c>
-      <c r="BP11" s="20">
+      <c r="BP11" s="16">
         <v>3140.73</v>
       </c>
-      <c r="BQ11" s="20">
+      <c r="BQ11" s="16">
         <f>BR11-BP11</f>
         <v>68.6700000000001</v>
       </c>
-      <c r="BR11" s="20">
+      <c r="BR11" s="16">
         <v>3209.4</v>
       </c>
-      <c r="BS11" s="20">
+      <c r="BS11" s="16">
         <f>BT11-BR11</f>
         <v>59.4099999999999</v>
       </c>
-      <c r="BT11" s="20">
+      <c r="BT11" s="16">
         <v>3268.81</v>
       </c>
-      <c r="BU11" s="20">
+      <c r="BU11" s="16">
         <f>BV11-BT11</f>
         <v>44.3000000000002</v>
       </c>
-      <c r="BV11" s="20">
+      <c r="BV11" s="16">
         <v>3313.11</v>
       </c>
-      <c r="BW11" s="20">
+      <c r="BW11" s="16">
         <f>BX11-BV11</f>
         <v>32.3799999999997</v>
       </c>
-      <c r="BX11" s="20">
+      <c r="BX11" s="16">
         <v>3345.49</v>
       </c>
-      <c r="BY11" s="20">
+      <c r="BY11" s="16">
         <f>BZ11-BX11</f>
         <v>44.1300000000001</v>
       </c>
-      <c r="BZ11" s="20">
+      <c r="BZ11" s="16">
         <v>3389.62</v>
       </c>
-      <c r="CA11" s="20">
+      <c r="CA11" s="16">
         <f>CB11-BZ11</f>
         <v>44.1100000000001</v>
       </c>
-      <c r="CB11" s="20">
+      <c r="CB11" s="16">
         <v>3433.73</v>
       </c>
-      <c r="CC11" s="20">
+      <c r="CC11" s="16">
         <f>CD11-CB11</f>
         <v>32.5599999999999</v>
       </c>
-      <c r="CD11" s="20">
+      <c r="CD11" s="16">
         <v>3466.29</v>
       </c>
-      <c r="CE11" s="20">
+      <c r="CE11" s="16">
         <f>CF11-CD11</f>
         <v>42.1199999999999</v>
       </c>
-      <c r="CF11" s="20">
+      <c r="CF11" s="16">
         <v>3508.41</v>
       </c>
-      <c r="CG11" s="20">
+      <c r="CG11" s="16">
         <f>CH11-CF11</f>
         <v>83.3000000000002</v>
       </c>
-      <c r="CH11" s="20">
+      <c r="CH11" s="16">
         <v>3591.71</v>
       </c>
-      <c r="CI11" s="20">
+      <c r="CI11" s="16">
         <f>CJ11-CH11</f>
         <v>89.1700000000001</v>
       </c>
-      <c r="CJ11" s="20">
+      <c r="CJ11" s="16">
         <v>3680.88</v>
       </c>
-      <c r="CK11" s="20">
+      <c r="CK11" s="16">
         <f>CL11-CJ11</f>
         <v>43.0099999999998</v>
       </c>
-      <c r="CL11" s="20">
+      <c r="CL11" s="16">
         <v>3723.89</v>
       </c>
-      <c r="CM11" s="20">
+      <c r="CM11" s="16">
         <f>CN11-CL11</f>
         <v>35.3800000000001</v>
       </c>
-      <c r="CN11" s="20">
+      <c r="CN11" s="16">
         <v>3759.27</v>
       </c>
-      <c r="CO11" s="20">
+      <c r="CO11" s="16">
         <f>CP11-CN11</f>
         <v>49.6700000000001</v>
       </c>
-      <c r="CP11" s="20">
+      <c r="CP11" s="16">
         <v>3808.94</v>
       </c>
-      <c r="CQ11" s="20">
+      <c r="CQ11" s="16">
         <f>CR11-CP11</f>
         <v>60.2799999999997</v>
       </c>
-      <c r="CR11" s="20">
+      <c r="CR11" s="16">
         <v>3869.22</v>
       </c>
-      <c r="CS11" s="20">
+      <c r="CS11" s="16">
         <f>CT11-CR11</f>
         <v>104.95</v>
       </c>
-      <c r="CT11" s="20">
+      <c r="CT11" s="16">
         <v>3974.17</v>
       </c>
-      <c r="CU11" s="20">
+      <c r="CU11" s="16">
         <f>CV11-CT11</f>
         <v>50.29</v>
       </c>
-      <c r="CV11" s="20">
+      <c r="CV11" s="16">
         <v>4024.46</v>
       </c>
-      <c r="CW11" s="19">
+      <c r="CW11" s="15">
         <f>CX11-CV11</f>
         <v>41.1999999999998</v>
       </c>
-      <c r="CX11" s="20">
+      <c r="CX11" s="16">
         <v>4065.66</v>
       </c>
-      <c r="CY11" s="20">
+      <c r="CY11" s="16">
         <f>CZ11-CX11</f>
         <v>43.3400000000001</v>
       </c>
-      <c r="CZ11" s="20">
+      <c r="CZ11" s="16">
         <v>4109</v>
       </c>
-      <c r="DA11" s="20">
+      <c r="DA11" s="16">
         <f>DB11-CZ11</f>
         <v>40.9700000000003</v>
       </c>
-      <c r="DB11" s="20">
+      <c r="DB11" s="16">
         <v>4149.97</v>
       </c>
-      <c r="DC11" s="20">
+      <c r="DC11" s="16">
         <f>DD11-DB11</f>
         <v>60.8199999999997</v>
       </c>
-      <c r="DD11" s="20">
+      <c r="DD11" s="16">
         <v>4210.79</v>
       </c>
-      <c r="DE11" s="20">
+      <c r="DE11" s="16">
         <f>DF11-DD11</f>
         <v>57.8400000000001</v>
       </c>
-      <c r="DF11" s="20">
+      <c r="DF11" s="16">
         <v>4268.63</v>
       </c>
-      <c r="DG11" s="20">
+      <c r="DG11" s="16">
         <f>DH11-DF11</f>
         <v>36.7600000000002</v>
       </c>
-      <c r="DH11" s="20">
+      <c r="DH11" s="16">
         <v>4305.39</v>
       </c>
-      <c r="DI11" s="20">
+      <c r="DI11" s="16">
         <f>DJ11-DH11</f>
         <v>81.6199999999999</v>
       </c>
-      <c r="DJ11" s="20">
+      <c r="DJ11" s="16">
         <v>4387.01</v>
       </c>
-      <c r="DK11" s="20">
+      <c r="DK11" s="16">
         <f>DL11-DJ11</f>
         <v>31.0799999999999</v>
       </c>
-      <c r="DL11" s="20">
+      <c r="DL11" s="16">
         <v>4418.09</v>
       </c>
-      <c r="DM11" s="20">
+      <c r="DM11" s="16">
         <f>DN11-DL11</f>
         <v>91.9099999999999</v>
       </c>
-      <c r="DN11" s="20">
+      <c r="DN11" s="16">
         <v>4510</v>
       </c>
-      <c r="DO11" s="19">
+      <c r="DO11" s="15">
         <f>DP11-DN11</f>
         <v>28.9200000000001</v>
       </c>
-      <c r="DP11" s="20">
+      <c r="DP11" s="16">
         <v>4538.92</v>
       </c>
-      <c r="DQ11" s="20">
+      <c r="DQ11" s="16">
         <f>DR11-DP11</f>
         <v>23.96</v>
       </c>
-      <c r="DR11" s="20">
+      <c r="DR11" s="16">
         <v>4562.88</v>
       </c>
-      <c r="DS11" s="20">
+      <c r="DS11" s="16">
         <f>DT11-DR11</f>
         <v>26.8099999999995</v>
       </c>
-      <c r="DT11" s="20">
+      <c r="DT11" s="16">
         <v>4589.69</v>
       </c>
-      <c r="DU11" s="20">
+      <c r="DU11" s="16">
         <f>DV11-DT11</f>
         <v>29.9500000000007</v>
       </c>
-      <c r="DV11" s="20">
+      <c r="DV11" s="16">
         <v>4619.64</v>
       </c>
-      <c r="DW11" s="20">
+      <c r="DW11" s="16">
         <f>DX11-DV11</f>
         <v>30.0499999999993</v>
       </c>
-      <c r="DX11" s="20">
+      <c r="DX11" s="16">
         <v>4649.69</v>
       </c>
-      <c r="DY11" s="20">
+      <c r="DY11" s="16">
         <f>DZ11-DX11</f>
         <v>49.8200000000006</v>
       </c>
-      <c r="DZ11" s="20">
+      <c r="DZ11" s="16">
         <v>4699.51</v>
       </c>
-      <c r="EA11" s="20">
+      <c r="EA11" s="16">
         <f>EB11-DZ11</f>
         <v>35.1300000000001</v>
       </c>
-      <c r="EB11" s="20">
+      <c r="EB11" s="16">
         <v>4734.64</v>
       </c>
-      <c r="EC11" s="20">
+      <c r="EC11" s="16">
         <f>ED11-EB11</f>
         <v>40.4799999999996</v>
       </c>
-      <c r="ED11" s="20">
+      <c r="ED11" s="16">
         <v>4775.12</v>
       </c>
-      <c r="EE11" s="20">
+      <c r="EE11" s="16">
         <f>EF11-ED11</f>
         <v>28.3800000000001</v>
       </c>
-      <c r="EF11" s="20">
+      <c r="EF11" s="16">
         <v>4803.5</v>
       </c>
-      <c r="EG11" s="20">
+      <c r="EG11" s="16">
         <f>EH11-EF11</f>
         <v>83</v>
       </c>
-      <c r="EH11" s="20">
+      <c r="EH11" s="16">
         <v>4886.5</v>
       </c>
-      <c r="EI11" s="20">
+      <c r="EI11" s="16">
         <f>EJ11-EH11</f>
         <v>53.79</v>
       </c>
-      <c r="EJ11" s="20">
+      <c r="EJ11" s="16">
         <v>4940.29</v>
       </c>
-      <c r="EK11" s="20">
+      <c r="EK11" s="16">
         <f>EL11-EJ11</f>
         <v>12.96</v>
       </c>
-      <c r="EL11" s="20">
+      <c r="EL11" s="16">
         <v>4953.25</v>
       </c>
-      <c r="EM11" s="20">
+      <c r="EM11" s="16">
         <f>EN11-EL11</f>
         <v>1.01000000000022</v>
       </c>
-      <c r="EN11" s="20">
+      <c r="EN11" s="16">
         <v>4954.26</v>
       </c>
-      <c r="EO11" s="20">
+      <c r="EO11" s="16">
         <f>EP11-EN11</f>
         <v>3.27999999999975</v>
       </c>
-      <c r="EP11" s="20">
+      <c r="EP11" s="16">
         <v>4957.54</v>
       </c>
-      <c r="EQ11" s="20">
+      <c r="EQ11" s="16">
         <f>ER11-EP11</f>
         <v>25.8599999999997</v>
       </c>
-      <c r="ER11" s="20">
+      <c r="ER11" s="16">
         <v>4983.4</v>
       </c>
-      <c r="ES11" s="20">
+      <c r="ES11" s="16">
         <f>ET11-ER11</f>
         <v>26.3100000000004</v>
       </c>
-      <c r="ET11" s="20">
+      <c r="ET11" s="16">
         <v>5009.71</v>
       </c>
-      <c r="EU11" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="EV11" s="18">
+      <c r="EU11" s="16">
+        <f>EV11-ET11</f>
+        <v>15.4799999999996</v>
+      </c>
+      <c r="EV11" s="16">
+        <v>5025.19</v>
+      </c>
+      <c r="EW11" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="EX11" s="14">
         <v>1327.27</v>
       </c>
-      <c r="EW11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="EX11" s="14">
+      <c r="EY11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ11" s="14">
         <v>748.71</v>
       </c>
-      <c r="EY11" s="1">
+      <c r="FA11" s="1">
         <v>20</v>
       </c>
-      <c r="EZ11" s="1">
+      <c r="FB11" s="1">
         <v>1.1</v>
       </c>
-      <c r="FA11" s="1">
+      <c r="FC11" s="1">
         <v>106867</v>
       </c>
-      <c r="FB11" s="9">
-        <f>2.41/(ET11/EV11)</f>
-        <v>0.638504164911741</v>
-      </c>
-      <c r="FC11" s="9">
+      <c r="FD11" s="9">
+        <f>2.79/(EV11/EX11)</f>
+        <v>0.736904136958006</v>
+      </c>
+      <c r="FE11" s="9">
         <f>BP11-D11</f>
         <v>1715.51</v>
       </c>
     </row>
-    <row r="12" spans="1:169">
+    <row r="12" spans="1:171">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>1349.35</v>
@@ -8369,45 +8448,52 @@
       <c r="ET12" s="20">
         <v>4814.04</v>
       </c>
-      <c r="EU12" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="EV12" s="18">
-        <v>1563.72</v>
-      </c>
-      <c r="EW12" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="EX12" s="14">
+      <c r="EU12" s="20">
+        <f>EV12-ET12</f>
+        <v>25.8800000000001</v>
+      </c>
+      <c r="EV12" s="20">
+        <v>4839.92</v>
+      </c>
+      <c r="EW12" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="EX12" s="18">
+        <v>1571.92</v>
+      </c>
+      <c r="EY12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ12" s="14">
         <v>645.48</v>
       </c>
-      <c r="EY12" s="1">
+      <c r="FA12" s="1">
         <v>20</v>
       </c>
-      <c r="EZ12" s="1">
+      <c r="FB12" s="1">
         <v>3.2</v>
       </c>
-      <c r="FA12" s="1">
+      <c r="FC12" s="1">
         <v>109106</v>
       </c>
-      <c r="FB12" s="9">
-        <f>2.41/(ET12/EV12)</f>
-        <v>0.782827978163871</v>
-      </c>
-      <c r="FC12" s="9">
+      <c r="FD12" s="9">
+        <f>2.79/(EV12/EX12)</f>
+        <v>0.906142415577117</v>
+      </c>
+      <c r="FE12" s="9">
         <f>BP12-D12</f>
         <v>1368.34</v>
       </c>
     </row>
-    <row r="13" spans="1:169">
+    <row r="13" spans="1:171">
       <c r="A13" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2">
         <v>1156.57</v>
@@ -8923,45 +9009,52 @@
       <c r="ET13" s="20">
         <v>4808.68</v>
       </c>
-      <c r="EU13" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="EV13" s="18">
-        <v>1510.67</v>
-      </c>
-      <c r="EW13" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="EX13" s="14">
+      <c r="EU13" s="20">
+        <f>EV13-ET13</f>
+        <v>29.2599999999993</v>
+      </c>
+      <c r="EV13" s="20">
+        <v>4837.94</v>
+      </c>
+      <c r="EW13" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="EX13" s="18">
+        <v>1518.55</v>
+      </c>
+      <c r="EY13" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="EZ13" s="14">
         <v>614.12</v>
       </c>
-      <c r="EY13" s="1">
+      <c r="FA13" s="1">
         <v>25</v>
       </c>
-      <c r="EZ13" s="1">
+      <c r="FB13" s="1">
         <v>3</v>
       </c>
-      <c r="FA13" s="1">
+      <c r="FC13" s="1">
         <v>100457</v>
       </c>
-      <c r="FB13" s="9">
-        <f>2.41/(ET13/EV13)</f>
-        <v>0.757113116281391</v>
-      </c>
-      <c r="FC13" s="9">
+      <c r="FD13" s="9">
+        <f>2.79/(EV13/EX13)</f>
+        <v>0.875735230283964</v>
+      </c>
+      <c r="FE13" s="9">
         <f>BP13-D13</f>
         <v>1572.99</v>
       </c>
     </row>
-    <row r="14" spans="1:169">
+    <row r="14" spans="1:171">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D14" s="2">
         <v>907.94</v>
@@ -9477,45 +9570,52 @@
       <c r="ET14" s="20">
         <v>4244.73</v>
       </c>
-      <c r="EU14" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="EV14" s="18">
-        <v>1386.57</v>
-      </c>
-      <c r="EW14" s="18" t="s">
+      <c r="EU14" s="20">
+        <f>EV14-ET14</f>
+        <v>66.1000000000004</v>
+      </c>
+      <c r="EV14" s="20">
+        <v>4310.83</v>
+      </c>
+      <c r="EW14" s="19" t="s">
         <v>126</v>
       </c>
       <c r="EX14" s="18">
+        <v>1317.26</v>
+      </c>
+      <c r="EY14" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="EZ14" s="18">
         <v>628.67</v>
       </c>
-      <c r="EY14" s="2">
+      <c r="FA14" s="2">
         <v>35</v>
       </c>
-      <c r="EZ14" s="2">
+      <c r="FB14" s="2">
         <v>8.2</v>
       </c>
-      <c r="FA14" s="2">
+      <c r="FC14" s="2">
         <v>65285</v>
       </c>
-      <c r="FB14" s="9">
-        <f>2.41/(ET14/EV14)</f>
-        <v>0.787242934179559</v>
-      </c>
-      <c r="FC14" s="9">
+      <c r="FD14" s="9">
+        <f>2.79/(EV14/EX14)</f>
+        <v>0.85254009088737</v>
+      </c>
+      <c r="FE14" s="9">
         <f>BP14-D14</f>
         <v>1361.61</v>
       </c>
     </row>
-    <row r="15" spans="1:169">
+    <row r="15" spans="1:171">
       <c r="A15" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2">
         <v>953.78</v>
@@ -10031,45 +10131,52 @@
       <c r="ET15" s="20">
         <v>4100.56</v>
       </c>
-      <c r="EU15" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="EV15" s="18">
-        <v>1616.37</v>
-      </c>
-      <c r="EW15" s="18" t="s">
-        <v>111</v>
+      <c r="EU15" s="20">
+        <f>EV15-ET15</f>
+        <v>29.2999999999993</v>
+      </c>
+      <c r="EV15" s="20">
+        <v>4129.86</v>
+      </c>
+      <c r="EW15" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="EX15" s="18">
+        <v>1629.87</v>
+      </c>
+      <c r="EY15" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="EZ15" s="18">
         <v>758.25</v>
       </c>
-      <c r="EY15" s="2">
+      <c r="FA15" s="2">
         <v>30</v>
       </c>
-      <c r="EZ15" s="2">
+      <c r="FB15" s="2">
         <v>1</v>
       </c>
-      <c r="FA15" s="2">
+      <c r="FC15" s="2">
         <v>105419</v>
       </c>
-      <c r="FB15" s="9">
-        <f>2.41/(ET15/EV15)</f>
-        <v>0.949980417308855</v>
-      </c>
-      <c r="FC15" s="9">
+      <c r="FD15" s="9">
+        <f>2.79/(EV15/EX15)</f>
+        <v>1.10108751870523</v>
+      </c>
+      <c r="FE15" s="9">
         <f>BP15-D15</f>
         <v>1446.26</v>
       </c>
     </row>
-    <row r="16" spans="1:169">
+    <row r="16" spans="1:171">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2">
         <v>950.09</v>
@@ -10585,45 +10692,52 @@
       <c r="ET16" s="20">
         <v>3853.82</v>
       </c>
-      <c r="EU16" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="EV16" s="18">
-        <v>1503.01</v>
-      </c>
-      <c r="EW16" s="18" t="s">
+      <c r="EU16" s="20">
+        <f>EV16-ET16</f>
+        <v>90.6599999999999</v>
+      </c>
+      <c r="EV16" s="20">
+        <v>3944.48</v>
+      </c>
+      <c r="EW16" s="19" t="s">
         <v>133</v>
       </c>
       <c r="EX16" s="18">
+        <v>1556.36</v>
+      </c>
+      <c r="EY16" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="EZ16" s="18">
         <v>704.28</v>
       </c>
-      <c r="EY16" s="2">
+      <c r="FA16" s="2">
         <v>10</v>
       </c>
-      <c r="EZ16" s="2">
+      <c r="FB16" s="2">
         <v>2.2</v>
       </c>
-      <c r="FA16" s="2">
+      <c r="FC16" s="2">
         <v>86194</v>
       </c>
-      <c r="FB16" s="9">
-        <f>2.41/(ET16/EV16)</f>
-        <v>0.939912632141615</v>
-      </c>
-      <c r="FC16" s="9">
+      <c r="FD16" s="9">
+        <f>2.79/(EV16/EX16)</f>
+        <v>1.10084076988602</v>
+      </c>
+      <c r="FE16" s="9">
         <f>BP16-D16</f>
         <v>1143.19</v>
       </c>
     </row>
-    <row r="17" spans="1:159">
+    <row r="17" spans="1:161">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -11039,39 +11153,46 @@
       <c r="ET17" s="20">
         <v>3694.51</v>
       </c>
-      <c r="EU17" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="EV17" s="18">
-        <v>987.45</v>
-      </c>
-      <c r="EW17" s="18" t="s">
-        <v>133</v>
+      <c r="EU17" s="20">
+        <f>EV17-ET17</f>
+        <v>41.5299999999997</v>
+      </c>
+      <c r="EV17" s="20">
+        <v>3736.04</v>
+      </c>
+      <c r="EW17" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="EX17" s="18">
+        <v>1073.85</v>
+      </c>
+      <c r="EY17" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="EZ17" s="18">
         <v>304.12</v>
       </c>
-      <c r="EY17" s="2"/>
-      <c r="EZ17" s="2"/>
       <c r="FA17" s="2"/>
-      <c r="FB17" s="9">
-        <f>2.41/(ET17/EV17)</f>
-        <v>0.64413264546584</v>
-      </c>
-      <c r="FC17" s="9">
+      <c r="FB17" s="2"/>
+      <c r="FC17" s="2"/>
+      <c r="FD17" s="9">
+        <f>2.79/(EV17/EX17)</f>
+        <v>0.801929717026584</v>
+      </c>
+      <c r="FE17" s="9">
         <f>BP17-D17</f>
         <v>1776.78</v>
       </c>
     </row>
-    <row r="18" spans="1:159">
+    <row r="18" spans="1:161">
       <c r="A18" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -11487,487 +11608,501 @@
       <c r="ET18" s="20">
         <v>3651.17</v>
       </c>
-      <c r="EU18" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="EV18" s="18">
-        <v>856.52</v>
-      </c>
-      <c r="EW18" s="18" t="s">
-        <v>119</v>
+      <c r="EU18" s="20">
+        <f>EV18-ET18</f>
+        <v>40.1399999999999</v>
+      </c>
+      <c r="EV18" s="20">
+        <v>3691.31</v>
+      </c>
+      <c r="EW18" s="19" t="s">
+        <v>139</v>
       </c>
       <c r="EX18" s="18">
+        <v>884.52</v>
+      </c>
+      <c r="EY18" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ18" s="18">
         <v>490.62</v>
       </c>
-      <c r="EY18" s="2"/>
-      <c r="EZ18" s="2"/>
       <c r="FA18" s="2"/>
-      <c r="FB18" s="9">
-        <f>2.41/(ET18/EV18)</f>
-        <v>0.565356639104725</v>
-      </c>
-      <c r="FC18" s="9">
+      <c r="FB18" s="2"/>
+      <c r="FC18" s="2"/>
+      <c r="FD18" s="9">
+        <f>2.79/(EV18/EX18)</f>
+        <v>0.668546071719796</v>
+      </c>
+      <c r="FE18" s="9">
         <f>BP18-D18</f>
         <v>2634.73</v>
       </c>
     </row>
-    <row r="19" spans="1:159">
-      <c r="A19" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="8" t="s">
+    <row r="19" spans="1:161">
+      <c r="A19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="8"/>
-      <c r="AH19" s="8"/>
-      <c r="AI19" s="8"/>
-      <c r="AJ19" s="8"/>
-      <c r="AK19" s="8"/>
-      <c r="AL19" s="8"/>
-      <c r="AM19" s="8"/>
-      <c r="AN19" s="8"/>
-      <c r="AO19" s="8"/>
-      <c r="AP19" s="8"/>
-      <c r="AQ19" s="8"/>
-      <c r="AR19" s="21">
+      <c r="C19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="18">
         <v>1444.24</v>
       </c>
-      <c r="AS19" s="21">
+      <c r="AS19" s="18">
         <f>AT19-AR19</f>
         <v>0</v>
       </c>
-      <c r="AT19" s="21">
+      <c r="AT19" s="18">
         <v>1444.24</v>
       </c>
-      <c r="AU19" s="22">
+      <c r="AU19" s="19">
         <f>AV19-AT19</f>
         <v>35.5599999999999</v>
       </c>
-      <c r="AV19" s="23">
+      <c r="AV19" s="20">
         <v>1479.8</v>
       </c>
-      <c r="AW19" s="23">
+      <c r="AW19" s="20">
         <f>AX19-AV19</f>
         <v>30.3700000000001</v>
       </c>
-      <c r="AX19" s="23">
+      <c r="AX19" s="20">
         <v>1510.17</v>
       </c>
-      <c r="AY19" s="23">
+      <c r="AY19" s="20">
         <f>AZ19-AX19</f>
         <v>21.47</v>
       </c>
-      <c r="AZ19" s="23">
+      <c r="AZ19" s="20">
         <v>1531.64</v>
       </c>
-      <c r="BA19" s="23">
+      <c r="BA19" s="20">
         <f>BB19-AZ19</f>
         <v>41.3899999999999</v>
       </c>
-      <c r="BB19" s="23">
+      <c r="BB19" s="20">
         <v>1573.03</v>
       </c>
-      <c r="BC19" s="23">
+      <c r="BC19" s="20">
         <f>BD19-BB19</f>
         <v>24.21</v>
       </c>
-      <c r="BD19" s="23">
+      <c r="BD19" s="20">
         <v>1597.24</v>
       </c>
-      <c r="BE19" s="22">
+      <c r="BE19" s="19">
         <f>BF19-BD19</f>
         <v>19.22</v>
       </c>
-      <c r="BF19" s="23">
+      <c r="BF19" s="20">
         <v>1616.46</v>
       </c>
-      <c r="BG19" s="23">
+      <c r="BG19" s="20">
         <f>BH19-BF19</f>
         <v>35.5599999999999</v>
       </c>
-      <c r="BH19" s="23">
+      <c r="BH19" s="20">
         <v>1652.02</v>
       </c>
-      <c r="BI19" s="23">
+      <c r="BI19" s="20">
         <f>BJ19-BH19</f>
         <v>47.72</v>
       </c>
-      <c r="BJ19" s="23">
+      <c r="BJ19" s="20">
         <v>1699.74</v>
       </c>
-      <c r="BK19" s="23">
+      <c r="BK19" s="20">
         <f>BL19-BJ19</f>
         <v>34.0999999999999</v>
       </c>
-      <c r="BL19" s="23">
+      <c r="BL19" s="20">
         <v>1733.84</v>
       </c>
-      <c r="BM19" s="23">
+      <c r="BM19" s="20">
         <f>BN19-BL19</f>
         <v>41.5800000000002</v>
       </c>
-      <c r="BN19" s="23">
+      <c r="BN19" s="20">
         <v>1775.42</v>
       </c>
-      <c r="BO19" s="23">
+      <c r="BO19" s="20">
         <f>BP19-BN19</f>
         <v>41.6799999999998</v>
       </c>
-      <c r="BP19" s="23">
+      <c r="BP19" s="20">
         <v>1817.1</v>
       </c>
-      <c r="BQ19" s="23">
+      <c r="BQ19" s="20">
         <f>BR19-BP19</f>
         <v>28.2900000000002</v>
       </c>
-      <c r="BR19" s="23">
+      <c r="BR19" s="20">
         <v>1845.39</v>
       </c>
-      <c r="BS19" s="23">
+      <c r="BS19" s="20">
         <f>BT19-BR19</f>
         <v>31.1699999999998</v>
       </c>
-      <c r="BT19" s="23">
+      <c r="BT19" s="20">
         <v>1876.56</v>
       </c>
-      <c r="BU19" s="23">
+      <c r="BU19" s="20">
         <f>BV19-BT19</f>
         <v>31.27</v>
       </c>
-      <c r="BV19" s="23">
+      <c r="BV19" s="20">
         <v>1907.83</v>
       </c>
-      <c r="BW19" s="23">
+      <c r="BW19" s="20">
         <f>BX19-BV19</f>
         <v>38.53</v>
       </c>
-      <c r="BX19" s="23">
+      <c r="BX19" s="20">
         <v>1946.36</v>
       </c>
-      <c r="BY19" s="23">
+      <c r="BY19" s="20">
         <f>BZ19-BX19</f>
         <v>28.5400000000002</v>
       </c>
-      <c r="BZ19" s="23">
+      <c r="BZ19" s="20">
         <v>1974.9</v>
       </c>
-      <c r="CA19" s="23">
+      <c r="CA19" s="20">
         <f>CB19-BZ19</f>
         <v>15.3499999999999</v>
       </c>
-      <c r="CB19" s="23">
+      <c r="CB19" s="20">
         <v>1990.25</v>
       </c>
-      <c r="CC19" s="23">
+      <c r="CC19" s="20">
         <f>CD19-CB19</f>
         <v>65.8699999999999</v>
       </c>
-      <c r="CD19" s="23">
+      <c r="CD19" s="20">
         <v>2056.12</v>
       </c>
-      <c r="CE19" s="23">
+      <c r="CE19" s="20">
         <f>CF19-CD19</f>
         <v>22.29</v>
       </c>
-      <c r="CF19" s="23">
+      <c r="CF19" s="20">
         <v>2078.41</v>
       </c>
-      <c r="CG19" s="23">
+      <c r="CG19" s="20">
         <f>CH19-CF19</f>
         <v>42.4700000000003</v>
       </c>
-      <c r="CH19" s="23">
+      <c r="CH19" s="20">
         <v>2120.88</v>
       </c>
-      <c r="CI19" s="23">
+      <c r="CI19" s="20">
         <f>CJ19-CH19</f>
         <v>31.0099999999998</v>
       </c>
-      <c r="CJ19" s="23">
+      <c r="CJ19" s="20">
         <v>2151.89</v>
       </c>
-      <c r="CK19" s="23">
+      <c r="CK19" s="20">
         <f>CL19-CJ19</f>
         <v>75.6600000000003</v>
       </c>
-      <c r="CL19" s="23">
+      <c r="CL19" s="20">
         <v>2227.55</v>
       </c>
-      <c r="CM19" s="23">
+      <c r="CM19" s="20">
         <f>CN19-CL19</f>
         <v>9.57999999999993</v>
       </c>
-      <c r="CN19" s="23">
+      <c r="CN19" s="20">
         <v>2237.13</v>
       </c>
-      <c r="CO19" s="23">
+      <c r="CO19" s="20">
         <f>CP19-CN19</f>
         <v>44.8099999999999</v>
       </c>
-      <c r="CP19" s="23">
+      <c r="CP19" s="20">
         <v>2281.94</v>
       </c>
-      <c r="CQ19" s="23">
+      <c r="CQ19" s="20">
         <f>CR19-CP19</f>
         <v>35</v>
       </c>
-      <c r="CR19" s="23">
+      <c r="CR19" s="20">
         <v>2316.94</v>
       </c>
-      <c r="CS19" s="23">
+      <c r="CS19" s="20">
         <f>CT19-CR19</f>
         <v>59.8200000000002</v>
       </c>
-      <c r="CT19" s="23">
+      <c r="CT19" s="20">
         <v>2376.76</v>
       </c>
-      <c r="CU19" s="23">
+      <c r="CU19" s="20">
         <f>CV19-CT19</f>
         <v>42.6299999999997</v>
       </c>
-      <c r="CV19" s="23">
+      <c r="CV19" s="20">
         <v>2419.39</v>
       </c>
-      <c r="CW19" s="22">
+      <c r="CW19" s="19">
         <f>CX19-CV19</f>
         <v>47.4200000000001</v>
       </c>
-      <c r="CX19" s="23">
+      <c r="CX19" s="20">
         <v>2466.81</v>
       </c>
-      <c r="CY19" s="23">
+      <c r="CY19" s="20">
         <f>CZ19-CX19</f>
         <v>56.21</v>
       </c>
-      <c r="CZ19" s="23">
+      <c r="CZ19" s="20">
         <v>2523.02</v>
       </c>
-      <c r="DA19" s="23">
+      <c r="DA19" s="20">
         <f>DB19-CZ19</f>
         <v>17.04</v>
       </c>
-      <c r="DB19" s="23">
+      <c r="DB19" s="20">
         <v>2540.06</v>
       </c>
-      <c r="DC19" s="23">
+      <c r="DC19" s="20">
         <f>DD19-DB19</f>
         <v>46.29</v>
       </c>
-      <c r="DD19" s="23">
+      <c r="DD19" s="20">
         <v>2586.35</v>
       </c>
-      <c r="DE19" s="23">
+      <c r="DE19" s="20">
         <f>DF19-DD19</f>
         <v>53.6300000000001</v>
       </c>
-      <c r="DF19" s="23">
+      <c r="DF19" s="20">
         <v>2639.98</v>
       </c>
-      <c r="DG19" s="23">
+      <c r="DG19" s="20">
         <f>DH19-DF19</f>
         <v>36.5500000000002</v>
       </c>
-      <c r="DH19" s="23">
+      <c r="DH19" s="20">
         <v>2676.53</v>
       </c>
-      <c r="DI19" s="23">
+      <c r="DI19" s="20">
         <f>DJ19-DH19</f>
         <v>42.3599999999997</v>
       </c>
-      <c r="DJ19" s="23">
+      <c r="DJ19" s="20">
         <v>2718.89</v>
       </c>
-      <c r="DK19" s="23">
+      <c r="DK19" s="20">
         <f>DL19-DJ19</f>
         <v>33.8499999999999</v>
       </c>
-      <c r="DL19" s="23">
+      <c r="DL19" s="20">
         <v>2752.74</v>
       </c>
-      <c r="DM19" s="23">
+      <c r="DM19" s="20">
         <f>DN19-DL19</f>
         <v>30.1100000000001</v>
       </c>
-      <c r="DN19" s="23">
+      <c r="DN19" s="20">
         <v>2782.85</v>
       </c>
-      <c r="DO19" s="22">
+      <c r="DO19" s="19">
         <f>DP19-DN19</f>
         <v>27.9900000000002</v>
       </c>
-      <c r="DP19" s="23">
+      <c r="DP19" s="20">
         <v>2810.84</v>
       </c>
-      <c r="DQ19" s="23">
+      <c r="DQ19" s="20">
         <f>DR19-DP19</f>
         <v>39.1199999999999</v>
       </c>
-      <c r="DR19" s="23">
+      <c r="DR19" s="20">
         <v>2849.96</v>
       </c>
-      <c r="DS19" s="23">
+      <c r="DS19" s="20">
         <f>DT19-DR19</f>
         <v>32.6300000000001</v>
       </c>
-      <c r="DT19" s="23">
+      <c r="DT19" s="20">
         <v>2882.59</v>
       </c>
-      <c r="DU19" s="23">
+      <c r="DU19" s="20">
         <f>DV19-DT19</f>
         <v>41.8699999999999</v>
       </c>
-      <c r="DV19" s="23">
+      <c r="DV19" s="20">
         <v>2924.46</v>
       </c>
-      <c r="DW19" s="23">
+      <c r="DW19" s="20">
         <f>DX19-DV19</f>
         <v>31.9699999999998</v>
       </c>
-      <c r="DX19" s="23">
+      <c r="DX19" s="20">
         <v>2956.43</v>
       </c>
-      <c r="DY19" s="23">
+      <c r="DY19" s="20">
         <f>DZ19-DX19</f>
         <v>29.8200000000002</v>
       </c>
-      <c r="DZ19" s="23">
+      <c r="DZ19" s="20">
         <v>2986.25</v>
       </c>
-      <c r="EA19" s="23">
+      <c r="EA19" s="20">
         <f>EB19-DZ19</f>
         <v>21.0100000000002</v>
       </c>
-      <c r="EB19" s="23">
+      <c r="EB19" s="20">
         <v>3007.26</v>
       </c>
-      <c r="EC19" s="23">
+      <c r="EC19" s="20">
         <f>ED19-EB19</f>
         <v>56.2799999999997</v>
       </c>
-      <c r="ED19" s="23">
+      <c r="ED19" s="20">
         <v>3063.54</v>
       </c>
-      <c r="EE19" s="23">
+      <c r="EE19" s="20">
         <f>EF19-ED19</f>
         <v>23.4900000000002</v>
       </c>
-      <c r="EF19" s="23">
+      <c r="EF19" s="20">
         <v>3087.03</v>
       </c>
-      <c r="EG19" s="23">
+      <c r="EG19" s="20">
         <f>EH19-EF19</f>
         <v>77.02</v>
       </c>
-      <c r="EH19" s="23">
+      <c r="EH19" s="20">
         <v>3164.05</v>
       </c>
-      <c r="EI19" s="23">
+      <c r="EI19" s="20">
         <f>EJ19-EH19</f>
         <v>22.7999999999997</v>
       </c>
-      <c r="EJ19" s="23">
+      <c r="EJ19" s="20">
         <v>3186.85</v>
       </c>
-      <c r="EK19" s="23">
+      <c r="EK19" s="20">
         <f>EL19-EJ19</f>
         <v>52.3800000000001</v>
       </c>
-      <c r="EL19" s="23">
+      <c r="EL19" s="20">
         <v>3239.23</v>
       </c>
-      <c r="EM19" s="23">
+      <c r="EM19" s="20">
         <f>EN19-EL19</f>
         <v>64.3200000000002</v>
       </c>
-      <c r="EN19" s="23">
+      <c r="EN19" s="20">
         <v>3303.55</v>
       </c>
-      <c r="EO19" s="23">
+      <c r="EO19" s="20">
         <f>EP19-EN19</f>
         <v>13.5899999999997</v>
       </c>
-      <c r="EP19" s="23">
+      <c r="EP19" s="20">
         <v>3317.14</v>
       </c>
-      <c r="EQ19" s="23">
+      <c r="EQ19" s="20">
         <f>ER19-EP19</f>
         <v>65.5</v>
       </c>
-      <c r="ER19" s="23">
+      <c r="ER19" s="20">
         <v>3382.64</v>
       </c>
-      <c r="ES19" s="23">
+      <c r="ES19" s="20">
         <f>ET19-ER19</f>
         <v>78.1700000000001</v>
       </c>
-      <c r="ET19" s="23">
+      <c r="ET19" s="20">
         <v>3460.81</v>
       </c>
-      <c r="EU19" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="EV19" s="21">
+      <c r="EU19" s="20">
+        <f>EV19-ET19</f>
+        <v>40.2200000000003</v>
+      </c>
+      <c r="EV19" s="20">
+        <v>3501.03</v>
+      </c>
+      <c r="EW19" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="EX19" s="18">
         <v>573.21</v>
       </c>
-      <c r="EW19" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="EX19" s="18">
+      <c r="EY19" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ19" s="18">
         <v>303.44</v>
       </c>
-      <c r="EY19" s="2"/>
-      <c r="EZ19" s="2"/>
       <c r="FA19" s="2"/>
-      <c r="FB19" s="9">
-        <f>2.41/(ET19/EV19)</f>
-        <v>0.399165542170763</v>
-      </c>
-      <c r="FC19" s="9">
+      <c r="FB19" s="2"/>
+      <c r="FC19" s="2"/>
+      <c r="FD19" s="9">
+        <f>2.79/(EV19/EX19)</f>
+        <v>0.456795828656138</v>
+      </c>
+      <c r="FE19" s="9">
         <f>BP19-D19</f>
         <v>1817.1</v>
       </c>
     </row>
-    <row r="20" spans="1:159">
+    <row r="20" spans="1:161">
       <c r="A20" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -11987,435 +12122,442 @@
       <c r="S20" s="8"/>
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
-      <c r="V20" s="24"/>
+      <c r="V20" s="21"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="24"/>
+      <c r="X20" s="21"/>
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
       <c r="AC20" s="8"/>
       <c r="AD20" s="8"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="21"/>
-      <c r="AK20" s="21"/>
-      <c r="AL20" s="21"/>
-      <c r="AM20" s="21"/>
-      <c r="AN20" s="21"/>
-      <c r="AO20" s="21"/>
-      <c r="AP20" s="21"/>
-      <c r="AQ20" s="21"/>
-      <c r="AR20" s="21">
+      <c r="AE20" s="22"/>
+      <c r="AF20" s="22"/>
+      <c r="AG20" s="22"/>
+      <c r="AH20" s="22"/>
+      <c r="AI20" s="22"/>
+      <c r="AJ20" s="22"/>
+      <c r="AK20" s="22"/>
+      <c r="AL20" s="22"/>
+      <c r="AM20" s="22"/>
+      <c r="AN20" s="22"/>
+      <c r="AO20" s="22"/>
+      <c r="AP20" s="22"/>
+      <c r="AQ20" s="22"/>
+      <c r="AR20" s="22">
         <v>1644.57</v>
       </c>
-      <c r="AS20" s="21">
+      <c r="AS20" s="22">
         <f>AT20-AR20</f>
         <v>0</v>
       </c>
-      <c r="AT20" s="21">
+      <c r="AT20" s="22">
         <v>1644.57</v>
       </c>
-      <c r="AU20" s="22">
+      <c r="AU20" s="23">
         <f>AV20-AT20</f>
         <v>31.0700000000002</v>
       </c>
-      <c r="AV20" s="22">
+      <c r="AV20" s="23">
         <v>1675.64</v>
       </c>
-      <c r="AW20" s="23">
+      <c r="AW20" s="24">
         <f>AX20-AV20</f>
         <v>13.9599999999998</v>
       </c>
-      <c r="AX20" s="23">
+      <c r="AX20" s="24">
         <v>1689.6</v>
       </c>
-      <c r="AY20" s="23">
+      <c r="AY20" s="24">
         <f>AZ20-AX20</f>
         <v>44.99</v>
       </c>
-      <c r="AZ20" s="23">
+      <c r="AZ20" s="24">
         <v>1734.59</v>
       </c>
-      <c r="BA20" s="23">
+      <c r="BA20" s="24">
         <f>BB20-AZ20</f>
         <v>31.1600000000001</v>
       </c>
-      <c r="BB20" s="23">
+      <c r="BB20" s="24">
         <v>1765.75</v>
       </c>
-      <c r="BC20" s="23">
+      <c r="BC20" s="24">
         <f>BD20-BB20</f>
         <v>39.9200000000001</v>
       </c>
-      <c r="BD20" s="23">
+      <c r="BD20" s="24">
         <v>1805.67</v>
       </c>
-      <c r="BE20" s="22">
+      <c r="BE20" s="23">
         <f>BF20-BD20</f>
         <v>42.21</v>
       </c>
-      <c r="BF20" s="23">
+      <c r="BF20" s="24">
         <v>1847.88</v>
       </c>
-      <c r="BG20" s="23">
+      <c r="BG20" s="24">
         <f>BH20-BF20</f>
         <v>86</v>
       </c>
-      <c r="BH20" s="23">
+      <c r="BH20" s="24">
         <v>1933.88</v>
       </c>
-      <c r="BI20" s="23">
+      <c r="BI20" s="24">
         <f>BJ20-BH20</f>
         <v>21.8499999999999</v>
       </c>
-      <c r="BJ20" s="23">
+      <c r="BJ20" s="24">
         <v>1955.73</v>
       </c>
-      <c r="BK20" s="23">
+      <c r="BK20" s="24">
         <f>BL20-BJ20</f>
         <v>26.3099999999999</v>
       </c>
-      <c r="BL20" s="23">
+      <c r="BL20" s="24">
         <v>1982.04</v>
       </c>
-      <c r="BM20" s="23">
+      <c r="BM20" s="24">
         <f>BN20-BL20</f>
         <v>26.51</v>
       </c>
-      <c r="BN20" s="23">
+      <c r="BN20" s="24">
         <v>2008.55</v>
       </c>
-      <c r="BO20" s="23">
+      <c r="BO20" s="24">
         <f>BP20-BN20</f>
         <v>20.71</v>
       </c>
-      <c r="BP20" s="23">
+      <c r="BP20" s="24">
         <v>2029.26</v>
       </c>
-      <c r="BQ20" s="23">
+      <c r="BQ20" s="24">
         <f>BR20-BP20</f>
         <v>63.0800000000002</v>
       </c>
-      <c r="BR20" s="23">
+      <c r="BR20" s="24">
         <v>2092.34</v>
       </c>
-      <c r="BS20" s="23">
+      <c r="BS20" s="24">
         <f>BT20-BR20</f>
         <v>4.29999999999973</v>
       </c>
-      <c r="BT20" s="23">
+      <c r="BT20" s="24">
         <v>2096.64</v>
       </c>
-      <c r="BU20" s="23">
+      <c r="BU20" s="24">
         <f>BV20-BT20</f>
         <v>0.720000000000255</v>
       </c>
-      <c r="BV20" s="23">
+      <c r="BV20" s="24">
         <v>2097.36</v>
       </c>
-      <c r="BW20" s="23">
+      <c r="BW20" s="24">
         <f>BX20-BV20</f>
         <v>0</v>
       </c>
-      <c r="BX20" s="23">
+      <c r="BX20" s="24">
         <v>2097.36</v>
       </c>
-      <c r="BY20" s="23">
+      <c r="BY20" s="24">
         <f>BZ20-BX20</f>
         <v>0.0199999999999818</v>
       </c>
-      <c r="BZ20" s="23">
+      <c r="BZ20" s="24">
         <v>2097.38</v>
       </c>
-      <c r="CA20" s="23">
+      <c r="CA20" s="24">
         <f>CB20-BZ20</f>
         <v>30.5899999999997</v>
       </c>
-      <c r="CB20" s="23">
+      <c r="CB20" s="24">
         <v>2127.97</v>
       </c>
-      <c r="CC20" s="23">
+      <c r="CC20" s="24">
         <f>CD20-CB20</f>
         <v>62.5300000000002</v>
       </c>
-      <c r="CD20" s="23">
+      <c r="CD20" s="24">
         <v>2190.5</v>
       </c>
-      <c r="CE20" s="23">
+      <c r="CE20" s="24">
         <f>CF20-CD20</f>
         <v>49.0500000000002</v>
       </c>
-      <c r="CF20" s="23">
+      <c r="CF20" s="24">
         <v>2239.55</v>
       </c>
-      <c r="CG20" s="23">
+      <c r="CG20" s="24">
         <f>CH20-CF20</f>
         <v>52.2599999999998</v>
       </c>
-      <c r="CH20" s="23">
+      <c r="CH20" s="24">
         <v>2291.81</v>
       </c>
-      <c r="CI20" s="23">
+      <c r="CI20" s="24">
         <f>CJ20-CH20</f>
         <v>48.0300000000002</v>
       </c>
-      <c r="CJ20" s="23">
+      <c r="CJ20" s="24">
         <v>2339.84</v>
       </c>
-      <c r="CK20" s="23">
+      <c r="CK20" s="24">
         <f>CL20-CJ20</f>
         <v>56.8499999999999</v>
       </c>
-      <c r="CL20" s="23">
+      <c r="CL20" s="24">
         <v>2396.69</v>
       </c>
-      <c r="CM20" s="23">
+      <c r="CM20" s="24">
         <f>CN20-CL20</f>
         <v>35.73</v>
       </c>
-      <c r="CN20" s="23">
+      <c r="CN20" s="24">
         <v>2432.42</v>
       </c>
-      <c r="CO20" s="23">
+      <c r="CO20" s="24">
         <f>CP20-CN20</f>
         <v>31.79</v>
       </c>
-      <c r="CP20" s="23">
+      <c r="CP20" s="24">
         <v>2464.21</v>
       </c>
-      <c r="CQ20" s="23">
+      <c r="CQ20" s="24">
         <f>CR20-CP20</f>
         <v>28.4200000000001</v>
       </c>
-      <c r="CR20" s="23">
+      <c r="CR20" s="24">
         <v>2492.63</v>
       </c>
-      <c r="CS20" s="23">
+      <c r="CS20" s="24">
         <f>CT20-CR20</f>
         <v>84.6199999999999</v>
       </c>
-      <c r="CT20" s="23">
+      <c r="CT20" s="24">
         <v>2577.25</v>
       </c>
-      <c r="CU20" s="23">
+      <c r="CU20" s="24">
         <f>CV20-CT20</f>
         <v>29.0999999999999</v>
       </c>
-      <c r="CV20" s="23">
+      <c r="CV20" s="24">
         <v>2606.35</v>
       </c>
-      <c r="CW20" s="22">
+      <c r="CW20" s="23">
         <f>CX20-CV20</f>
         <v>33.1300000000001</v>
       </c>
-      <c r="CX20" s="23">
+      <c r="CX20" s="24">
         <v>2639.48</v>
       </c>
-      <c r="CY20" s="23">
+      <c r="CY20" s="24">
         <f>CZ20-CX20</f>
         <v>26.6199999999999</v>
       </c>
-      <c r="CZ20" s="23">
+      <c r="CZ20" s="24">
         <v>2666.1</v>
       </c>
-      <c r="DA20" s="23">
+      <c r="DA20" s="24">
         <f>DB20-CZ20</f>
         <v>34.8000000000002</v>
       </c>
-      <c r="DB20" s="23">
+      <c r="DB20" s="24">
         <v>2700.9</v>
       </c>
-      <c r="DC20" s="23">
+      <c r="DC20" s="24">
         <f>DD20-DB20</f>
         <v>51.6999999999998</v>
       </c>
-      <c r="DD20" s="23">
+      <c r="DD20" s="24">
         <v>2752.6</v>
       </c>
-      <c r="DE20" s="23">
+      <c r="DE20" s="24">
         <f>DF20-DD20</f>
         <v>32.4000000000001</v>
       </c>
-      <c r="DF20" s="23">
+      <c r="DF20" s="24">
         <v>2785</v>
       </c>
-      <c r="DG20" s="23">
+      <c r="DG20" s="24">
         <f>DH20-DF20</f>
         <v>12.6599999999999</v>
       </c>
-      <c r="DH20" s="23">
+      <c r="DH20" s="24">
         <v>2797.66</v>
       </c>
-      <c r="DI20" s="23">
+      <c r="DI20" s="24">
         <f>DJ20-DH20</f>
         <v>61.23</v>
       </c>
-      <c r="DJ20" s="23">
+      <c r="DJ20" s="24">
         <v>2858.89</v>
       </c>
-      <c r="DK20" s="23">
+      <c r="DK20" s="24">
         <f>DL20-DJ20</f>
         <v>32.0700000000002</v>
       </c>
-      <c r="DL20" s="23">
+      <c r="DL20" s="24">
         <v>2890.96</v>
       </c>
-      <c r="DM20" s="23">
+      <c r="DM20" s="24">
         <f>DN20-DL20</f>
         <v>56.8400000000001</v>
       </c>
-      <c r="DN20" s="23">
+      <c r="DN20" s="24">
         <v>2947.8</v>
       </c>
-      <c r="DO20" s="22">
+      <c r="DO20" s="23">
         <f>DP20-DN20</f>
         <v>12.0599999999999</v>
       </c>
-      <c r="DP20" s="23">
+      <c r="DP20" s="24">
         <v>2959.86</v>
       </c>
-      <c r="DQ20" s="23">
+      <c r="DQ20" s="24">
         <f>DR20-DP20</f>
         <v>19.8199999999997</v>
       </c>
-      <c r="DR20" s="23">
+      <c r="DR20" s="24">
         <v>2979.68</v>
       </c>
-      <c r="DS20" s="23">
+      <c r="DS20" s="24">
         <f>DT20-DR20</f>
         <v>24.1000000000004</v>
       </c>
-      <c r="DT20" s="23">
+      <c r="DT20" s="24">
         <v>3003.78</v>
       </c>
-      <c r="DU20" s="23">
+      <c r="DU20" s="24">
         <f>DV20-DT20</f>
         <v>34.7599999999998</v>
       </c>
-      <c r="DV20" s="23">
+      <c r="DV20" s="24">
         <v>3038.54</v>
       </c>
-      <c r="DW20" s="23">
+      <c r="DW20" s="24">
         <f>DX20-DV20</f>
         <v>33.0799999999999</v>
       </c>
-      <c r="DX20" s="23">
+      <c r="DX20" s="24">
         <v>3071.62</v>
       </c>
-      <c r="DY20" s="23">
+      <c r="DY20" s="24">
         <f>DZ20-DX20</f>
         <v>23.4200000000001</v>
       </c>
-      <c r="DZ20" s="23">
+      <c r="DZ20" s="24">
         <v>3095.04</v>
       </c>
-      <c r="EA20" s="23">
+      <c r="EA20" s="24">
         <f>EB20-DZ20</f>
         <v>43.3200000000002</v>
       </c>
-      <c r="EB20" s="23">
+      <c r="EB20" s="24">
         <v>3138.36</v>
       </c>
-      <c r="EC20" s="23">
+      <c r="EC20" s="24">
         <f>ED20-EB20</f>
         <v>18.71</v>
       </c>
-      <c r="ED20" s="23">
+      <c r="ED20" s="24">
         <v>3157.07</v>
       </c>
-      <c r="EE20" s="23">
+      <c r="EE20" s="24">
         <f>EF20-ED20</f>
         <v>16.0299999999997</v>
       </c>
-      <c r="EF20" s="23">
+      <c r="EF20" s="24">
         <v>3173.1</v>
       </c>
-      <c r="EG20" s="23">
+      <c r="EG20" s="24">
         <f>EH20-EF20</f>
         <v>31.71</v>
       </c>
-      <c r="EH20" s="23">
+      <c r="EH20" s="24">
         <v>3204.81</v>
       </c>
-      <c r="EI20" s="23">
+      <c r="EI20" s="24">
         <f>EJ20-EH20</f>
         <v>15.54</v>
       </c>
-      <c r="EJ20" s="23">
+      <c r="EJ20" s="24">
         <v>3220.35</v>
       </c>
-      <c r="EK20" s="23">
+      <c r="EK20" s="24">
         <f>EL20-EJ20</f>
         <v>19.9100000000003</v>
       </c>
-      <c r="EL20" s="23">
+      <c r="EL20" s="24">
         <v>3240.26</v>
       </c>
-      <c r="EM20" s="23">
+      <c r="EM20" s="24">
         <f>EN20-EL20</f>
         <v>0</v>
       </c>
-      <c r="EN20" s="23">
+      <c r="EN20" s="24">
         <v>3240.26</v>
       </c>
-      <c r="EO20" s="23">
+      <c r="EO20" s="24">
         <f>EP20-EN20</f>
         <v>0</v>
       </c>
-      <c r="EP20" s="23">
+      <c r="EP20" s="24">
         <v>3240.26</v>
       </c>
-      <c r="EQ20" s="23">
+      <c r="EQ20" s="24">
         <f>ER20-EP20</f>
         <v>0</v>
       </c>
-      <c r="ER20" s="23">
+      <c r="ER20" s="24">
         <v>3240.26</v>
       </c>
-      <c r="ES20" s="23">
+      <c r="ES20" s="24">
         <f>ET20-ER20</f>
         <v>0</v>
       </c>
-      <c r="ET20" s="23">
+      <c r="ET20" s="24">
         <v>3240.26</v>
       </c>
-      <c r="EU20" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="EV20" s="21">
+      <c r="EU20" s="24">
+        <f>EV20-ET20</f>
+        <v>0</v>
+      </c>
+      <c r="EV20" s="24">
+        <v>3240.26</v>
+      </c>
+      <c r="EW20" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="EX20" s="22">
         <v>668.48</v>
       </c>
-      <c r="EW20" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="EX20" s="18">
+      <c r="EY20" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ20" s="18">
         <v>367.24</v>
       </c>
-      <c r="EY20" s="2"/>
-      <c r="EZ20" s="2"/>
       <c r="FA20" s="2"/>
-      <c r="FB20" s="9">
-        <f>2.41/(ET20/EV20)</f>
-        <v>0.497193681988482</v>
-      </c>
-      <c r="FC20" s="9">
+      <c r="FB20" s="2"/>
+      <c r="FC20" s="2"/>
+      <c r="FD20" s="9">
+        <f>2.79/(EV20/EX20)</f>
+        <v>0.575589366285422</v>
+      </c>
+      <c r="FE20" s="9">
         <f>BP20-D20</f>
         <v>2029.26</v>
       </c>
     </row>
-    <row r="21" spans="1:159">
+    <row r="21" spans="1:161">
       <c r="A21" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -12435,253 +12577,260 @@
       <c r="S21" s="8"/>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
-      <c r="V21" s="24"/>
+      <c r="V21" s="21"/>
       <c r="W21" s="8"/>
-      <c r="X21" s="24"/>
+      <c r="X21" s="21"/>
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
-      <c r="AJ21" s="21"/>
-      <c r="AK21" s="21"/>
-      <c r="AL21" s="21"/>
-      <c r="AM21" s="21"/>
-      <c r="AN21" s="21"/>
-      <c r="AO21" s="21"/>
-      <c r="AP21" s="21"/>
-      <c r="AQ21" s="21"/>
-      <c r="AR21" s="21"/>
-      <c r="AS21" s="21"/>
-      <c r="AT21" s="21"/>
-      <c r="AU21" s="22"/>
-      <c r="AV21" s="22"/>
-      <c r="AW21" s="23"/>
-      <c r="AX21" s="23"/>
-      <c r="AY21" s="23"/>
-      <c r="AZ21" s="23"/>
-      <c r="BA21" s="23"/>
-      <c r="BB21" s="23"/>
-      <c r="BC21" s="23"/>
-      <c r="BD21" s="23"/>
-      <c r="BE21" s="22"/>
-      <c r="BF21" s="23"/>
-      <c r="BG21" s="23"/>
-      <c r="BH21" s="23"/>
-      <c r="BI21" s="23"/>
-      <c r="BJ21" s="23"/>
-      <c r="BK21" s="23"/>
-      <c r="BL21" s="23"/>
-      <c r="BM21" s="23"/>
-      <c r="BN21" s="23"/>
-      <c r="BO21" s="23"/>
-      <c r="BP21" s="23"/>
-      <c r="BQ21" s="23"/>
-      <c r="BR21" s="23"/>
-      <c r="BS21" s="23"/>
-      <c r="BT21" s="23"/>
-      <c r="BU21" s="23"/>
-      <c r="BV21" s="23"/>
-      <c r="BW21" s="23"/>
-      <c r="BX21" s="23"/>
-      <c r="BY21" s="23"/>
-      <c r="BZ21" s="23"/>
-      <c r="CA21" s="23"/>
-      <c r="CB21" s="23"/>
-      <c r="CC21" s="23"/>
-      <c r="CD21" s="23"/>
-      <c r="CE21" s="23"/>
-      <c r="CF21" s="23"/>
-      <c r="CG21" s="23"/>
-      <c r="CH21" s="23"/>
-      <c r="CI21" s="23"/>
-      <c r="CJ21" s="23"/>
-      <c r="CK21" s="23"/>
-      <c r="CL21" s="23"/>
-      <c r="CM21" s="23"/>
-      <c r="CN21" s="23"/>
-      <c r="CO21" s="23"/>
-      <c r="CP21" s="23"/>
-      <c r="CQ21" s="23"/>
-      <c r="CR21" s="23"/>
-      <c r="CS21" s="23"/>
-      <c r="CT21" s="23"/>
-      <c r="CU21" s="23"/>
-      <c r="CV21" s="23"/>
-      <c r="CW21" s="22"/>
-      <c r="CX21" s="23"/>
-      <c r="CY21" s="23"/>
-      <c r="CZ21" s="23"/>
-      <c r="DA21" s="23"/>
-      <c r="DB21" s="23"/>
-      <c r="DC21" s="23"/>
-      <c r="DD21" s="23"/>
-      <c r="DE21" s="23"/>
-      <c r="DF21" s="23"/>
-      <c r="DG21" s="23"/>
-      <c r="DH21" s="23"/>
-      <c r="DI21" s="23"/>
-      <c r="DJ21" s="23">
+      <c r="AE21" s="22"/>
+      <c r="AF21" s="22"/>
+      <c r="AG21" s="22"/>
+      <c r="AH21" s="22"/>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="22"/>
+      <c r="AM21" s="22"/>
+      <c r="AN21" s="22"/>
+      <c r="AO21" s="22"/>
+      <c r="AP21" s="22"/>
+      <c r="AQ21" s="22"/>
+      <c r="AR21" s="22"/>
+      <c r="AS21" s="22"/>
+      <c r="AT21" s="22"/>
+      <c r="AU21" s="23"/>
+      <c r="AV21" s="23"/>
+      <c r="AW21" s="24"/>
+      <c r="AX21" s="24"/>
+      <c r="AY21" s="24"/>
+      <c r="AZ21" s="24"/>
+      <c r="BA21" s="24"/>
+      <c r="BB21" s="24"/>
+      <c r="BC21" s="24"/>
+      <c r="BD21" s="24"/>
+      <c r="BE21" s="23"/>
+      <c r="BF21" s="24"/>
+      <c r="BG21" s="24"/>
+      <c r="BH21" s="24"/>
+      <c r="BI21" s="24"/>
+      <c r="BJ21" s="24"/>
+      <c r="BK21" s="24"/>
+      <c r="BL21" s="24"/>
+      <c r="BM21" s="24"/>
+      <c r="BN21" s="24"/>
+      <c r="BO21" s="24"/>
+      <c r="BP21" s="24"/>
+      <c r="BQ21" s="24"/>
+      <c r="BR21" s="24"/>
+      <c r="BS21" s="24"/>
+      <c r="BT21" s="24"/>
+      <c r="BU21" s="24"/>
+      <c r="BV21" s="24"/>
+      <c r="BW21" s="24"/>
+      <c r="BX21" s="24"/>
+      <c r="BY21" s="24"/>
+      <c r="BZ21" s="24"/>
+      <c r="CA21" s="24"/>
+      <c r="CB21" s="24"/>
+      <c r="CC21" s="24"/>
+      <c r="CD21" s="24"/>
+      <c r="CE21" s="24"/>
+      <c r="CF21" s="24"/>
+      <c r="CG21" s="24"/>
+      <c r="CH21" s="24"/>
+      <c r="CI21" s="24"/>
+      <c r="CJ21" s="24"/>
+      <c r="CK21" s="24"/>
+      <c r="CL21" s="24"/>
+      <c r="CM21" s="24"/>
+      <c r="CN21" s="24"/>
+      <c r="CO21" s="24"/>
+      <c r="CP21" s="24"/>
+      <c r="CQ21" s="24"/>
+      <c r="CR21" s="24"/>
+      <c r="CS21" s="24"/>
+      <c r="CT21" s="24"/>
+      <c r="CU21" s="24"/>
+      <c r="CV21" s="24"/>
+      <c r="CW21" s="23"/>
+      <c r="CX21" s="24"/>
+      <c r="CY21" s="24"/>
+      <c r="CZ21" s="24"/>
+      <c r="DA21" s="24"/>
+      <c r="DB21" s="24"/>
+      <c r="DC21" s="24"/>
+      <c r="DD21" s="24"/>
+      <c r="DE21" s="24"/>
+      <c r="DF21" s="24"/>
+      <c r="DG21" s="24"/>
+      <c r="DH21" s="24"/>
+      <c r="DI21" s="24"/>
+      <c r="DJ21" s="24">
         <v>2158.34</v>
       </c>
-      <c r="DK21" s="23">
+      <c r="DK21" s="24">
         <f>DL21-DJ21</f>
         <v>0</v>
       </c>
-      <c r="DL21" s="23">
+      <c r="DL21" s="24">
         <v>2158.34</v>
       </c>
-      <c r="DM21" s="23">
+      <c r="DM21" s="24">
         <f>DN21-DL21</f>
         <v>55.6999999999998</v>
       </c>
-      <c r="DN21" s="23">
+      <c r="DN21" s="24">
         <v>2214.04</v>
       </c>
-      <c r="DO21" s="22">
+      <c r="DO21" s="23">
         <f>DP21-DN21</f>
         <v>21.9099999999999</v>
       </c>
-      <c r="DP21" s="23">
+      <c r="DP21" s="24">
         <v>2235.95</v>
       </c>
-      <c r="DQ21" s="23">
+      <c r="DQ21" s="24">
         <f>DR21-DP21</f>
         <v>57.5800000000004</v>
       </c>
-      <c r="DR21" s="23">
+      <c r="DR21" s="24">
         <v>2293.53</v>
       </c>
-      <c r="DS21" s="23">
+      <c r="DS21" s="24">
         <f>DT21-DR21</f>
         <v>52.4899999999998</v>
       </c>
-      <c r="DT21" s="23">
+      <c r="DT21" s="24">
         <v>2346.02</v>
       </c>
-      <c r="DU21" s="23">
+      <c r="DU21" s="24">
         <f>DV21-DT21</f>
         <v>0.0399999999999636</v>
       </c>
-      <c r="DV21" s="23">
+      <c r="DV21" s="24">
         <v>2346.06</v>
       </c>
-      <c r="DW21" s="23">
+      <c r="DW21" s="24">
         <f>DX21-DV21</f>
         <v>0</v>
       </c>
-      <c r="DX21" s="23">
+      <c r="DX21" s="24">
         <v>2346.06</v>
       </c>
-      <c r="DY21" s="23">
+      <c r="DY21" s="24">
         <f>DZ21-DX21</f>
         <v>38.7600000000002</v>
       </c>
-      <c r="DZ21" s="23">
+      <c r="DZ21" s="24">
         <v>2384.82</v>
       </c>
-      <c r="EA21" s="23">
+      <c r="EA21" s="24">
         <f>EB21-DZ21</f>
         <v>41.4099999999999</v>
       </c>
-      <c r="EB21" s="23">
+      <c r="EB21" s="24">
         <v>2426.23</v>
       </c>
-      <c r="EC21" s="23">
+      <c r="EC21" s="24">
         <f>ED21-EB21</f>
         <v>149.86</v>
       </c>
-      <c r="ED21" s="23">
+      <c r="ED21" s="24">
         <v>2576.09</v>
       </c>
-      <c r="EE21" s="23">
+      <c r="EE21" s="24">
         <f>EF21-ED21</f>
         <v>79.1099999999997</v>
       </c>
-      <c r="EF21" s="23">
+      <c r="EF21" s="24">
         <v>2655.2</v>
       </c>
-      <c r="EG21" s="23">
+      <c r="EG21" s="24">
         <f>EH21-EF21</f>
         <v>43.48</v>
       </c>
-      <c r="EH21" s="23">
+      <c r="EH21" s="24">
         <v>2698.68</v>
       </c>
-      <c r="EI21" s="23">
+      <c r="EI21" s="24">
         <f>EJ21-EH21</f>
         <v>76.3099999999999</v>
       </c>
-      <c r="EJ21" s="23">
+      <c r="EJ21" s="24">
         <v>2774.99</v>
       </c>
-      <c r="EK21" s="23">
+      <c r="EK21" s="24">
         <f>EL21-EJ21</f>
         <v>65.2200000000003</v>
       </c>
-      <c r="EL21" s="23">
+      <c r="EL21" s="24">
         <v>2840.21</v>
       </c>
-      <c r="EM21" s="23">
+      <c r="EM21" s="24">
         <f>EN21-EL21</f>
         <v>84.2199999999998</v>
       </c>
-      <c r="EN21" s="23">
+      <c r="EN21" s="24">
         <v>2924.43</v>
       </c>
-      <c r="EO21" s="23">
+      <c r="EO21" s="24">
         <f>EP21-EN21</f>
         <v>40.5300000000002</v>
       </c>
-      <c r="EP21" s="23">
+      <c r="EP21" s="24">
         <v>2964.96</v>
       </c>
-      <c r="EQ21" s="23">
+      <c r="EQ21" s="24">
         <f>ER21-EP21</f>
         <v>43.6199999999999</v>
       </c>
-      <c r="ER21" s="23">
+      <c r="ER21" s="24">
         <v>3008.58</v>
       </c>
-      <c r="ES21" s="23">
+      <c r="ES21" s="24">
         <f>ET21-ER21</f>
         <v>27.79</v>
       </c>
-      <c r="ET21" s="23">
+      <c r="ET21" s="24">
         <v>3036.37</v>
       </c>
-      <c r="EU21" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="EV21" s="21">
-        <v>553.68</v>
-      </c>
-      <c r="EW21" s="21"/>
-      <c r="EX21" s="21"/>
-      <c r="EY21" s="8"/>
-      <c r="EZ21" s="8"/>
+      <c r="EU21" s="24">
+        <f>EV21-ET21</f>
+        <v>47.5500000000002</v>
+      </c>
+      <c r="EV21" s="24">
+        <v>3083.92</v>
+      </c>
+      <c r="EW21" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="EX21" s="22">
+        <v>600.73</v>
+      </c>
+      <c r="EY21" s="22"/>
+      <c r="EZ21" s="22"/>
       <c r="FA21" s="8"/>
-      <c r="FB21" s="9">
-        <f>2.41/(ET21/EV21)</f>
-        <v>0.439461857415269</v>
-      </c>
-      <c r="FC21" s="9"/>
+      <c r="FB21" s="8"/>
+      <c r="FC21" s="8"/>
+      <c r="FD21" s="9">
+        <f>2.79/(EV21/EX21)</f>
+        <v>0.543476062932891</v>
+      </c>
+      <c r="FE21" s="9"/>
     </row>
-    <row r="22" spans="1:159">
+    <row r="22" spans="1:161">
       <c r="A22" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D22" s="8">
         <v>848.93</v>
@@ -12746,14 +12895,14 @@
         <f>V22-T22</f>
         <v>32.7</v>
       </c>
-      <c r="V22" s="24">
+      <c r="V22" s="21">
         <v>1140.44</v>
       </c>
       <c r="W22" s="8">
         <f>X22-V22</f>
         <v>26.9299999999998</v>
       </c>
-      <c r="X22" s="24">
+      <c r="X22" s="21">
         <v>1167.37</v>
       </c>
       <c r="Y22" s="8">
@@ -12777,465 +12926,472 @@
       <c r="AD22" s="8">
         <v>1291.75</v>
       </c>
-      <c r="AE22" s="21">
+      <c r="AE22" s="22">
         <f>AF22-AD22</f>
         <v>23.99</v>
       </c>
-      <c r="AF22" s="21">
+      <c r="AF22" s="22">
         <v>1315.74</v>
       </c>
-      <c r="AG22" s="21">
+      <c r="AG22" s="22">
         <f>AH22-AF22</f>
         <v>29.53</v>
       </c>
-      <c r="AH22" s="21">
+      <c r="AH22" s="22">
         <v>1345.27</v>
       </c>
-      <c r="AI22" s="21">
+      <c r="AI22" s="22">
         <f>AJ22-AH22</f>
         <v>26.6100000000001</v>
       </c>
-      <c r="AJ22" s="21">
+      <c r="AJ22" s="22">
         <v>1371.88</v>
       </c>
-      <c r="AK22" s="21">
+      <c r="AK22" s="22">
         <f>AL22-AJ22</f>
         <v>40.3999999999999</v>
       </c>
-      <c r="AL22" s="21">
+      <c r="AL22" s="22">
         <v>1412.28</v>
       </c>
-      <c r="AM22" s="21">
+      <c r="AM22" s="22">
         <f>AN22-AL22</f>
         <v>19.74</v>
       </c>
-      <c r="AN22" s="21">
+      <c r="AN22" s="22">
         <v>1432.02</v>
       </c>
-      <c r="AO22" s="21">
+      <c r="AO22" s="22">
         <f>AP22-AN22</f>
         <v>53.23</v>
       </c>
-      <c r="AP22" s="21">
+      <c r="AP22" s="22">
         <v>1485.25</v>
       </c>
-      <c r="AQ22" s="21">
+      <c r="AQ22" s="22">
         <f>AR22-AP22</f>
         <v>21.1800000000001</v>
       </c>
-      <c r="AR22" s="21">
+      <c r="AR22" s="22">
         <v>1506.43</v>
       </c>
-      <c r="AS22" s="21">
+      <c r="AS22" s="22">
         <f>AT22-AR22</f>
         <v>17.1199999999999</v>
       </c>
-      <c r="AT22" s="21">
+      <c r="AT22" s="22">
         <v>1523.55</v>
       </c>
-      <c r="AU22" s="22">
+      <c r="AU22" s="23">
         <f>AV22-AT22</f>
         <v>52.4000000000001</v>
       </c>
-      <c r="AV22" s="22">
+      <c r="AV22" s="23">
         <v>1575.95</v>
       </c>
-      <c r="AW22" s="23">
+      <c r="AW22" s="24">
         <f>AX22-AV22</f>
         <v>22.8</v>
       </c>
-      <c r="AX22" s="23">
+      <c r="AX22" s="24">
         <v>1598.75</v>
       </c>
-      <c r="AY22" s="23">
+      <c r="AY22" s="24">
         <f>AZ22-AX22</f>
         <v>41.49</v>
       </c>
-      <c r="AZ22" s="23">
+      <c r="AZ22" s="24">
         <v>1640.24</v>
       </c>
-      <c r="BA22" s="23">
+      <c r="BA22" s="24">
         <f>BB22-AZ22</f>
         <v>17.73</v>
       </c>
-      <c r="BB22" s="23">
+      <c r="BB22" s="24">
         <v>1657.97</v>
       </c>
-      <c r="BC22" s="23">
+      <c r="BC22" s="24">
         <f>BD22-BB22</f>
         <v>17.8899999999999</v>
       </c>
-      <c r="BD22" s="23">
+      <c r="BD22" s="24">
         <v>1675.86</v>
       </c>
-      <c r="BE22" s="22">
+      <c r="BE22" s="23">
         <f>BF22-BD22</f>
         <v>36.3500000000001</v>
       </c>
-      <c r="BF22" s="23">
+      <c r="BF22" s="24">
         <v>1712.21</v>
       </c>
-      <c r="BG22" s="23">
+      <c r="BG22" s="24">
         <f>BH22-BF22</f>
         <v>39.54</v>
       </c>
-      <c r="BH22" s="23">
+      <c r="BH22" s="24">
         <v>1751.75</v>
       </c>
-      <c r="BI22" s="23">
+      <c r="BI22" s="24">
         <f>BJ22-BH22</f>
         <v>13.1800000000001</v>
       </c>
-      <c r="BJ22" s="23">
+      <c r="BJ22" s="24">
         <v>1764.93</v>
       </c>
-      <c r="BK22" s="23">
+      <c r="BK22" s="24">
         <f>BL22-BJ22</f>
         <v>13.76</v>
       </c>
-      <c r="BL22" s="23">
+      <c r="BL22" s="24">
         <v>1778.69</v>
       </c>
-      <c r="BM22" s="23">
+      <c r="BM22" s="24">
         <f>BN22-BL22</f>
         <v>13.1299999999999</v>
       </c>
-      <c r="BN22" s="23">
+      <c r="BN22" s="24">
         <v>1791.82</v>
       </c>
-      <c r="BO22" s="23">
+      <c r="BO22" s="24">
         <f>BP22-BN22</f>
         <v>24.24</v>
       </c>
-      <c r="BP22" s="23">
+      <c r="BP22" s="24">
         <v>1816.06</v>
       </c>
-      <c r="BQ22" s="23">
+      <c r="BQ22" s="24">
         <f>BR22-BP22</f>
         <v>16.3</v>
       </c>
-      <c r="BR22" s="23">
+      <c r="BR22" s="24">
         <v>1832.36</v>
       </c>
-      <c r="BS22" s="23">
+      <c r="BS22" s="24">
         <f>BT22-BR22</f>
         <v>33.98</v>
       </c>
-      <c r="BT22" s="23">
+      <c r="BT22" s="24">
         <v>1866.34</v>
       </c>
-      <c r="BU22" s="23">
+      <c r="BU22" s="24">
         <f>BV22-BT22</f>
         <v>15.5600000000002</v>
       </c>
-      <c r="BV22" s="23">
+      <c r="BV22" s="24">
         <v>1881.9</v>
       </c>
-      <c r="BW22" s="23">
+      <c r="BW22" s="24">
         <f>BX22-BV22</f>
         <v>34.51</v>
       </c>
-      <c r="BX22" s="23">
+      <c r="BX22" s="24">
         <v>1916.41</v>
       </c>
-      <c r="BY22" s="23">
+      <c r="BY22" s="24">
         <f>BZ22-BX22</f>
         <v>21.02</v>
       </c>
-      <c r="BZ22" s="23">
+      <c r="BZ22" s="24">
         <v>1937.43</v>
       </c>
-      <c r="CA22" s="23">
+      <c r="CA22" s="24">
         <f>CB22-BZ22</f>
         <v>34.8799999999999</v>
       </c>
-      <c r="CB22" s="23">
+      <c r="CB22" s="24">
         <v>1972.31</v>
       </c>
-      <c r="CC22" s="23">
+      <c r="CC22" s="24">
         <f>CD22-CB22</f>
         <v>30.26</v>
       </c>
-      <c r="CD22" s="23">
+      <c r="CD22" s="24">
         <v>2002.57</v>
       </c>
-      <c r="CE22" s="23">
+      <c r="CE22" s="24">
         <f>CF22-CD22</f>
         <v>22.74</v>
       </c>
-      <c r="CF22" s="23">
+      <c r="CF22" s="24">
         <v>2025.31</v>
       </c>
-      <c r="CG22" s="23">
+      <c r="CG22" s="24">
         <f>CH22-CF22</f>
         <v>47.1799999999998</v>
       </c>
-      <c r="CH22" s="23">
+      <c r="CH22" s="24">
         <v>2072.49</v>
       </c>
-      <c r="CI22" s="23">
+      <c r="CI22" s="24">
         <f>CJ22-CH22</f>
         <v>42.1100000000001</v>
       </c>
-      <c r="CJ22" s="23">
+      <c r="CJ22" s="24">
         <v>2114.6</v>
       </c>
-      <c r="CK22" s="23">
+      <c r="CK22" s="24">
         <f>CL22-CJ22</f>
         <v>16.4500000000003</v>
       </c>
-      <c r="CL22" s="23">
+      <c r="CL22" s="24">
         <v>2131.05</v>
       </c>
-      <c r="CM22" s="23">
+      <c r="CM22" s="24">
         <f>CN22-CL22</f>
         <v>11.02</v>
       </c>
-      <c r="CN22" s="23">
+      <c r="CN22" s="24">
         <v>2142.07</v>
       </c>
-      <c r="CO22" s="23">
+      <c r="CO22" s="24">
         <f>CP22-CN22</f>
         <v>4.62999999999965</v>
       </c>
-      <c r="CP22" s="23">
+      <c r="CP22" s="24">
         <v>2146.7</v>
       </c>
-      <c r="CQ22" s="23">
+      <c r="CQ22" s="24">
         <f>CR22-CP22</f>
         <v>26.1200000000003</v>
       </c>
-      <c r="CR22" s="23">
+      <c r="CR22" s="24">
         <v>2172.82</v>
       </c>
-      <c r="CS22" s="23">
+      <c r="CS22" s="24">
         <f>CT22-CR22</f>
         <v>85.5899999999997</v>
       </c>
-      <c r="CT22" s="23">
+      <c r="CT22" s="24">
         <v>2258.41</v>
       </c>
-      <c r="CU22" s="23">
+      <c r="CU22" s="24">
         <f>CV22-CT22</f>
         <v>28.8800000000001</v>
       </c>
-      <c r="CV22" s="23">
+      <c r="CV22" s="24">
         <v>2287.29</v>
       </c>
-      <c r="CW22" s="22">
+      <c r="CW22" s="23">
         <f>CX22-CV22</f>
         <v>20.4700000000003</v>
       </c>
-      <c r="CX22" s="23">
+      <c r="CX22" s="24">
         <v>2307.76</v>
       </c>
-      <c r="CY22" s="23">
+      <c r="CY22" s="24">
         <f>CZ22-CX22</f>
         <v>17.9299999999998</v>
       </c>
-      <c r="CZ22" s="23">
+      <c r="CZ22" s="24">
         <v>2325.69</v>
       </c>
-      <c r="DA22" s="23">
+      <c r="DA22" s="24">
         <f>DB22-CZ22</f>
         <v>20.1900000000001</v>
       </c>
-      <c r="DB22" s="23">
+      <c r="DB22" s="24">
         <v>2345.88</v>
       </c>
-      <c r="DC22" s="23">
+      <c r="DC22" s="24">
         <f>DD22-DB22</f>
         <v>29.1399999999999</v>
       </c>
-      <c r="DD22" s="23">
+      <c r="DD22" s="24">
         <v>2375.02</v>
       </c>
-      <c r="DE22" s="23">
+      <c r="DE22" s="24">
         <f>DF22-DD22</f>
         <v>31.1799999999998</v>
       </c>
-      <c r="DF22" s="23">
+      <c r="DF22" s="24">
         <v>2406.2</v>
       </c>
-      <c r="DG22" s="23">
+      <c r="DG22" s="24">
         <f>DH22-DF22</f>
         <v>18.8600000000001</v>
       </c>
-      <c r="DH22" s="23">
+      <c r="DH22" s="24">
         <v>2425.06</v>
       </c>
-      <c r="DI22" s="23">
+      <c r="DI22" s="24">
         <f>DJ22-DH22</f>
         <v>35.0900000000001</v>
       </c>
-      <c r="DJ22" s="23">
+      <c r="DJ22" s="24">
         <v>2460.15</v>
       </c>
-      <c r="DK22" s="23">
+      <c r="DK22" s="24">
         <f>DL22-DJ22</f>
         <v>14.3800000000001</v>
       </c>
-      <c r="DL22" s="23">
+      <c r="DL22" s="24">
         <v>2474.53</v>
       </c>
-      <c r="DM22" s="23">
+      <c r="DM22" s="24">
         <f>DN22-DL22</f>
         <v>21.7099999999996</v>
       </c>
-      <c r="DN22" s="23">
+      <c r="DN22" s="24">
         <v>2496.24</v>
       </c>
-      <c r="DO22" s="22">
+      <c r="DO22" s="23">
         <f>DP22-DN22</f>
         <v>21.0900000000001</v>
       </c>
-      <c r="DP22" s="23">
+      <c r="DP22" s="24">
         <v>2517.33</v>
       </c>
-      <c r="DQ22" s="23">
+      <c r="DQ22" s="24">
         <f>DR22-DP22</f>
         <v>23.04</v>
       </c>
-      <c r="DR22" s="23">
+      <c r="DR22" s="24">
         <v>2540.37</v>
       </c>
-      <c r="DS22" s="23">
+      <c r="DS22" s="24">
         <f>DT22-DR22</f>
         <v>17.1600000000003</v>
       </c>
-      <c r="DT22" s="23">
+      <c r="DT22" s="24">
         <v>2557.53</v>
       </c>
-      <c r="DU22" s="23">
+      <c r="DU22" s="24">
         <f>DV22-DT22</f>
         <v>24.04</v>
       </c>
-      <c r="DV22" s="23">
+      <c r="DV22" s="24">
         <v>2581.57</v>
       </c>
-      <c r="DW22" s="23">
+      <c r="DW22" s="24">
         <f>DX22-DV22</f>
         <v>18.5</v>
       </c>
-      <c r="DX22" s="23">
+      <c r="DX22" s="24">
         <v>2600.07</v>
       </c>
-      <c r="DY22" s="23">
+      <c r="DY22" s="24">
         <f>DZ22-DX22</f>
         <v>42.25</v>
       </c>
-      <c r="DZ22" s="23">
+      <c r="DZ22" s="24">
         <v>2642.32</v>
       </c>
-      <c r="EA22" s="23">
+      <c r="EA22" s="24">
         <f>EB22-DZ22</f>
         <v>5.78999999999996</v>
       </c>
-      <c r="EB22" s="23">
+      <c r="EB22" s="24">
         <v>2648.11</v>
       </c>
-      <c r="EC22" s="23">
+      <c r="EC22" s="24">
         <f>ED22-EB22</f>
         <v>9.62999999999965</v>
       </c>
-      <c r="ED22" s="23">
+      <c r="ED22" s="24">
         <v>2657.74</v>
       </c>
-      <c r="EE22" s="23">
+      <c r="EE22" s="24">
         <f>EF22-ED22</f>
         <v>15.6100000000001</v>
       </c>
-      <c r="EF22" s="23">
+      <c r="EF22" s="24">
         <v>2673.35</v>
       </c>
-      <c r="EG22" s="23">
+      <c r="EG22" s="24">
         <f>EH22-EF22</f>
         <v>2.74000000000024</v>
       </c>
-      <c r="EH22" s="23">
+      <c r="EH22" s="24">
         <v>2676.09</v>
       </c>
-      <c r="EI22" s="23">
+      <c r="EI22" s="24">
         <f>EJ22-EH22</f>
         <v>26.8699999999999</v>
       </c>
-      <c r="EJ22" s="23">
+      <c r="EJ22" s="24">
         <v>2702.96</v>
       </c>
-      <c r="EK22" s="23">
+      <c r="EK22" s="24">
         <f>EL22-EJ22</f>
         <v>35.9299999999998</v>
       </c>
-      <c r="EL22" s="23">
+      <c r="EL22" s="24">
         <v>2738.89</v>
       </c>
-      <c r="EM22" s="23">
+      <c r="EM22" s="24">
         <f>EN22-EL22</f>
         <v>5.05000000000018</v>
       </c>
-      <c r="EN22" s="23">
+      <c r="EN22" s="24">
         <v>2743.94</v>
       </c>
-      <c r="EO22" s="23">
+      <c r="EO22" s="24">
         <f>EP22-EN22</f>
         <v>15.4899999999998</v>
       </c>
-      <c r="EP22" s="23">
+      <c r="EP22" s="24">
         <v>2759.43</v>
       </c>
-      <c r="EQ22" s="23">
+      <c r="EQ22" s="24">
         <f>ER22-EP22</f>
         <v>0.460000000000036</v>
       </c>
-      <c r="ER22" s="23">
+      <c r="ER22" s="24">
         <v>2759.89</v>
       </c>
-      <c r="ES22" s="23">
+      <c r="ES22" s="24">
         <f>ET22-ER22</f>
         <v>1.38000000000011</v>
       </c>
-      <c r="ET22" s="23">
+      <c r="ET22" s="24">
         <v>2761.27</v>
       </c>
-      <c r="EU22" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="EV22" s="21">
-        <v>1196.17</v>
-      </c>
-      <c r="EW22" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="EX22" s="18">
+      <c r="EU22" s="24">
+        <f>EV22-ET22</f>
+        <v>3.98000000000002</v>
+      </c>
+      <c r="EV22" s="24">
+        <v>2765.25</v>
+      </c>
+      <c r="EW22" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="EX22" s="22">
+        <v>1206.37</v>
+      </c>
+      <c r="EY22" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="EZ22" s="18">
         <v>556.77</v>
       </c>
-      <c r="EY22" s="2">
+      <c r="FA22" s="2">
         <v>30</v>
       </c>
-      <c r="EZ22" s="2">
+      <c r="FB22" s="2">
         <v>3.2</v>
       </c>
-      <c r="FA22" s="2">
+      <c r="FC22" s="2">
         <v>78989</v>
       </c>
-      <c r="FB22" s="9">
-        <f>2.41/(ET22/EV22)</f>
-        <v>1.0440013834214</v>
-      </c>
-      <c r="FC22" s="9">
+      <c r="FD22" s="9">
+        <f>2.79/(EV22/EX22)</f>
+        <v>1.21716745321399</v>
+      </c>
+      <c r="FE22" s="9">
         <f>BP22-D22</f>
         <v>967.13</v>
       </c>
     </row>
-    <row r="23" spans="1:159">
+    <row r="23" spans="1:161">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" s="8">
         <v>363.88</v>
@@ -13300,14 +13456,14 @@
         <f>V23-T23</f>
         <v>19.3099999999999</v>
       </c>
-      <c r="V23" s="24">
+      <c r="V23" s="21">
         <v>521.92</v>
       </c>
       <c r="W23" s="8">
         <f>X23-V23</f>
         <v>29.5400000000001</v>
       </c>
-      <c r="X23" s="24">
+      <c r="X23" s="21">
         <v>551.46</v>
       </c>
       <c r="Y23" s="8">
@@ -13331,465 +13487,472 @@
       <c r="AD23" s="8">
         <v>627.05</v>
       </c>
-      <c r="AE23" s="21">
+      <c r="AE23" s="22">
         <f>AF23-AD23</f>
         <v>21.0500000000001</v>
       </c>
-      <c r="AF23" s="21">
+      <c r="AF23" s="22">
         <v>648.1</v>
       </c>
-      <c r="AG23" s="21">
+      <c r="AG23" s="22">
         <f>AH23-AF23</f>
         <v>37.27</v>
       </c>
-      <c r="AH23" s="21">
+      <c r="AH23" s="22">
         <v>685.37</v>
       </c>
-      <c r="AI23" s="21">
+      <c r="AI23" s="22">
         <f>AJ23-AH23</f>
         <v>25.0700000000001</v>
       </c>
-      <c r="AJ23" s="21">
+      <c r="AJ23" s="22">
         <v>710.44</v>
       </c>
-      <c r="AK23" s="21">
+      <c r="AK23" s="22">
         <f>AL23-AJ23</f>
         <v>22.64</v>
       </c>
-      <c r="AL23" s="21">
+      <c r="AL23" s="22">
         <v>733.08</v>
       </c>
-      <c r="AM23" s="21">
+      <c r="AM23" s="22">
         <f>AN23-AL23</f>
         <v>28.76</v>
       </c>
-      <c r="AN23" s="21">
+      <c r="AN23" s="22">
         <v>761.84</v>
       </c>
-      <c r="AO23" s="21">
+      <c r="AO23" s="22">
         <f>AP23-AN23</f>
         <v>12.24</v>
       </c>
-      <c r="AP23" s="21">
+      <c r="AP23" s="22">
         <v>774.08</v>
       </c>
-      <c r="AQ23" s="21">
+      <c r="AQ23" s="22">
         <f>AR23-AP23</f>
         <v>29.39</v>
       </c>
-      <c r="AR23" s="21">
+      <c r="AR23" s="22">
         <v>803.47</v>
       </c>
-      <c r="AS23" s="21">
+      <c r="AS23" s="22">
         <f>AT23-AR23</f>
         <v>33.97</v>
       </c>
-      <c r="AT23" s="21">
+      <c r="AT23" s="22">
         <v>837.44</v>
       </c>
-      <c r="AU23" s="22">
+      <c r="AU23" s="23">
         <f>AV23-AT23</f>
         <v>29.6999999999999</v>
       </c>
-      <c r="AV23" s="22">
+      <c r="AV23" s="23">
         <v>867.14</v>
       </c>
-      <c r="AW23" s="23">
+      <c r="AW23" s="24">
         <f>AX23-AV23</f>
         <v>21.75</v>
       </c>
-      <c r="AX23" s="23">
+      <c r="AX23" s="24">
         <v>888.89</v>
       </c>
-      <c r="AY23" s="23">
+      <c r="AY23" s="24">
         <f>AZ23-AX23</f>
         <v>37.0600000000001</v>
       </c>
-      <c r="AZ23" s="23">
+      <c r="AZ23" s="24">
         <v>925.95</v>
       </c>
-      <c r="BA23" s="23">
+      <c r="BA23" s="24">
         <f>BB23-AZ23</f>
         <v>14.3</v>
       </c>
-      <c r="BB23" s="23">
+      <c r="BB23" s="24">
         <v>940.25</v>
       </c>
-      <c r="BC23" s="23">
+      <c r="BC23" s="24">
         <f>BD23-BB23</f>
         <v>12.04</v>
       </c>
-      <c r="BD23" s="23">
+      <c r="BD23" s="24">
         <v>952.29</v>
       </c>
-      <c r="BE23" s="22">
+      <c r="BE23" s="23">
         <f>BF23-BD23</f>
         <v>39.5300000000001</v>
       </c>
-      <c r="BF23" s="23">
+      <c r="BF23" s="24">
         <v>991.82</v>
       </c>
-      <c r="BG23" s="23">
+      <c r="BG23" s="24">
         <f>BH23-BF23</f>
         <v>38.2599999999999</v>
       </c>
-      <c r="BH23" s="23">
+      <c r="BH23" s="24">
         <v>1030.08</v>
       </c>
-      <c r="BI23" s="23">
+      <c r="BI23" s="24">
         <f>BJ23-BH23</f>
         <v>35.53</v>
       </c>
-      <c r="BJ23" s="23">
+      <c r="BJ23" s="24">
         <v>1065.61</v>
       </c>
-      <c r="BK23" s="23">
+      <c r="BK23" s="24">
         <f>BL23-BJ23</f>
         <v>36.8300000000002</v>
       </c>
-      <c r="BL23" s="23">
+      <c r="BL23" s="24">
         <v>1102.44</v>
       </c>
-      <c r="BM23" s="23">
+      <c r="BM23" s="24">
         <f>BN23-BL23</f>
         <v>30.4199999999998</v>
       </c>
-      <c r="BN23" s="23">
+      <c r="BN23" s="24">
         <v>1132.86</v>
       </c>
-      <c r="BO23" s="23">
+      <c r="BO23" s="24">
         <f>BP23-BN23</f>
         <v>21.5400000000002</v>
       </c>
-      <c r="BP23" s="23">
+      <c r="BP23" s="24">
         <v>1154.4</v>
       </c>
-      <c r="BQ23" s="23">
+      <c r="BQ23" s="24">
         <f>BR23-BP23</f>
         <v>41.52</v>
       </c>
-      <c r="BR23" s="23">
+      <c r="BR23" s="24">
         <v>1195.92</v>
       </c>
-      <c r="BS23" s="23">
+      <c r="BS23" s="24">
         <f>BT23-BR23</f>
         <v>10.8</v>
       </c>
-      <c r="BT23" s="23">
+      <c r="BT23" s="24">
         <v>1206.72</v>
       </c>
-      <c r="BU23" s="23">
+      <c r="BU23" s="24">
         <f>BV23-BT23</f>
         <v>13.96</v>
       </c>
-      <c r="BV23" s="23">
+      <c r="BV23" s="24">
         <v>1220.68</v>
       </c>
-      <c r="BW23" s="23">
+      <c r="BW23" s="24">
         <f>BX23-BV23</f>
         <v>10.74</v>
       </c>
-      <c r="BX23" s="23">
+      <c r="BX23" s="24">
         <v>1231.42</v>
       </c>
-      <c r="BY23" s="23">
+      <c r="BY23" s="24">
         <f>BZ23-BX23</f>
         <v>28.03</v>
       </c>
-      <c r="BZ23" s="23">
+      <c r="BZ23" s="24">
         <v>1259.45</v>
       </c>
-      <c r="CA23" s="23">
+      <c r="CA23" s="24">
         <f>CB23-BZ23</f>
         <v>47.29</v>
       </c>
-      <c r="CB23" s="23">
+      <c r="CB23" s="24">
         <v>1306.74</v>
       </c>
-      <c r="CC23" s="23">
+      <c r="CC23" s="24">
         <f>CD23-CB23</f>
         <v>22.47</v>
       </c>
-      <c r="CD23" s="23">
+      <c r="CD23" s="24">
         <v>1329.21</v>
       </c>
-      <c r="CE23" s="23">
+      <c r="CE23" s="24">
         <f>CF23-CD23</f>
         <v>9.03999999999996</v>
       </c>
-      <c r="CF23" s="23">
+      <c r="CF23" s="24">
         <v>1338.25</v>
       </c>
-      <c r="CG23" s="23">
+      <c r="CG23" s="24">
         <f>CH23-CF23</f>
         <v>24.3599999999999</v>
       </c>
-      <c r="CH23" s="23">
+      <c r="CH23" s="24">
         <v>1362.61</v>
       </c>
-      <c r="CI23" s="23">
+      <c r="CI23" s="24">
         <f>CJ23-CH23</f>
         <v>22.9300000000001</v>
       </c>
-      <c r="CJ23" s="23">
+      <c r="CJ23" s="24">
         <v>1385.54</v>
       </c>
-      <c r="CK23" s="23">
+      <c r="CK23" s="24">
         <f>CL23-CJ23</f>
         <v>29.2</v>
       </c>
-      <c r="CL23" s="23">
+      <c r="CL23" s="24">
         <v>1414.74</v>
       </c>
-      <c r="CM23" s="23">
+      <c r="CM23" s="24">
         <f>CN23-CL23</f>
         <v>13.6700000000001</v>
       </c>
-      <c r="CN23" s="23">
+      <c r="CN23" s="24">
         <v>1428.41</v>
       </c>
-      <c r="CO23" s="23">
+      <c r="CO23" s="24">
         <f>CP23-CN23</f>
         <v>28.1699999999998</v>
       </c>
-      <c r="CP23" s="23">
+      <c r="CP23" s="24">
         <v>1456.58</v>
       </c>
-      <c r="CQ23" s="23">
+      <c r="CQ23" s="24">
         <f>CR23-CP23</f>
         <v>19.3000000000002</v>
       </c>
-      <c r="CR23" s="23">
+      <c r="CR23" s="24">
         <v>1475.88</v>
       </c>
-      <c r="CS23" s="23">
+      <c r="CS23" s="24">
         <f>CT23-CR23</f>
         <v>37.8199999999999</v>
       </c>
-      <c r="CT23" s="23">
+      <c r="CT23" s="24">
         <v>1513.7</v>
       </c>
-      <c r="CU23" s="23">
+      <c r="CU23" s="24">
         <f>CV23-CT23</f>
         <v>16.77</v>
       </c>
-      <c r="CV23" s="23">
+      <c r="CV23" s="24">
         <v>1530.47</v>
       </c>
-      <c r="CW23" s="22">
+      <c r="CW23" s="23">
         <f>CX23-CV23</f>
         <v>17.99</v>
       </c>
-      <c r="CX23" s="23">
+      <c r="CX23" s="24">
         <v>1548.46</v>
       </c>
-      <c r="CY23" s="23">
+      <c r="CY23" s="24">
         <f>CZ23-CX23</f>
         <v>13.6399999999999</v>
       </c>
-      <c r="CZ23" s="23">
+      <c r="CZ23" s="24">
         <v>1562.1</v>
       </c>
-      <c r="DA23" s="23">
+      <c r="DA23" s="24">
         <f>DB23-CZ23</f>
         <v>63.24</v>
       </c>
-      <c r="DB23" s="23">
+      <c r="DB23" s="24">
         <v>1625.34</v>
       </c>
-      <c r="DC23" s="23">
+      <c r="DC23" s="24">
         <f>DD23-DB23</f>
         <v>23.72</v>
       </c>
-      <c r="DD23" s="23">
+      <c r="DD23" s="24">
         <v>1649.06</v>
       </c>
-      <c r="DE23" s="23">
+      <c r="DE23" s="24">
         <f>DF23-DD23</f>
         <v>10.8099999999999</v>
       </c>
-      <c r="DF23" s="23">
+      <c r="DF23" s="24">
         <v>1659.87</v>
       </c>
-      <c r="DG23" s="23">
+      <c r="DG23" s="24">
         <f>DH23-DF23</f>
         <v>26.6400000000001</v>
       </c>
-      <c r="DH23" s="23">
+      <c r="DH23" s="24">
         <v>1686.51</v>
       </c>
-      <c r="DI23" s="23">
+      <c r="DI23" s="24">
         <f>DJ23-DH23</f>
         <v>20.54</v>
       </c>
-      <c r="DJ23" s="23">
+      <c r="DJ23" s="24">
         <v>1707.05</v>
       </c>
-      <c r="DK23" s="23">
+      <c r="DK23" s="24">
         <f>DL23-DJ23</f>
         <v>21.1100000000001</v>
       </c>
-      <c r="DL23" s="23">
+      <c r="DL23" s="24">
         <v>1728.16</v>
       </c>
-      <c r="DM23" s="23">
+      <c r="DM23" s="24">
         <f>DN23-DL23</f>
         <v>45.05</v>
       </c>
-      <c r="DN23" s="23">
+      <c r="DN23" s="24">
         <v>1773.21</v>
       </c>
-      <c r="DO23" s="22">
+      <c r="DO23" s="23">
         <f>DP23-DN23</f>
         <v>33.6599999999999</v>
       </c>
-      <c r="DP23" s="23">
+      <c r="DP23" s="24">
         <v>1806.87</v>
       </c>
-      <c r="DQ23" s="23">
+      <c r="DQ23" s="24">
         <f>DR23-DP23</f>
         <v>18.3400000000001</v>
       </c>
-      <c r="DR23" s="23">
+      <c r="DR23" s="24">
         <v>1825.21</v>
       </c>
-      <c r="DS23" s="23">
+      <c r="DS23" s="24">
         <f>DT23-DR23</f>
         <v>33.3499999999999</v>
       </c>
-      <c r="DT23" s="23">
+      <c r="DT23" s="24">
         <v>1858.56</v>
       </c>
-      <c r="DU23" s="23">
+      <c r="DU23" s="24">
         <f>DV23-DT23</f>
         <v>33.5</v>
       </c>
-      <c r="DV23" s="23">
+      <c r="DV23" s="24">
         <v>1892.06</v>
       </c>
-      <c r="DW23" s="23">
+      <c r="DW23" s="24">
         <f>DX23-DV23</f>
         <v>23.9200000000001</v>
       </c>
-      <c r="DX23" s="23">
+      <c r="DX23" s="24">
         <v>1915.98</v>
       </c>
-      <c r="DY23" s="23">
+      <c r="DY23" s="24">
         <f>DZ23-DX23</f>
         <v>19.04</v>
       </c>
-      <c r="DZ23" s="23">
+      <c r="DZ23" s="24">
         <v>1935.02</v>
       </c>
-      <c r="EA23" s="23">
+      <c r="EA23" s="24">
         <f>EB23-DZ23</f>
         <v>22.23</v>
       </c>
-      <c r="EB23" s="23">
+      <c r="EB23" s="24">
         <v>1957.25</v>
       </c>
-      <c r="EC23" s="23">
+      <c r="EC23" s="24">
         <f>ED23-EB23</f>
         <v>15.51</v>
       </c>
-      <c r="ED23" s="23">
+      <c r="ED23" s="24">
         <v>1972.76</v>
       </c>
-      <c r="EE23" s="23">
+      <c r="EE23" s="24">
         <f>EF23-ED23</f>
         <v>11.26</v>
       </c>
-      <c r="EF23" s="23">
+      <c r="EF23" s="24">
         <v>1984.02</v>
       </c>
-      <c r="EG23" s="23">
+      <c r="EG23" s="24">
         <f>EH23-EF23</f>
         <v>25.0699999999999</v>
       </c>
-      <c r="EH23" s="23">
+      <c r="EH23" s="24">
         <v>2009.09</v>
       </c>
-      <c r="EI23" s="23">
+      <c r="EI23" s="24">
         <f>EJ23-EH23</f>
         <v>23.4400000000001</v>
       </c>
-      <c r="EJ23" s="23">
+      <c r="EJ23" s="24">
         <v>2032.53</v>
       </c>
-      <c r="EK23" s="23">
+      <c r="EK23" s="24">
         <f>EL23-EJ23</f>
         <v>34.3300000000002</v>
       </c>
-      <c r="EL23" s="23">
+      <c r="EL23" s="24">
         <v>2066.86</v>
       </c>
-      <c r="EM23" s="23">
+      <c r="EM23" s="24">
         <f>EN23-EL23</f>
         <v>10.48</v>
       </c>
-      <c r="EN23" s="23">
+      <c r="EN23" s="24">
         <v>2077.34</v>
       </c>
-      <c r="EO23" s="23">
+      <c r="EO23" s="24">
         <f>EP23-EN23</f>
         <v>39.2399999999998</v>
       </c>
-      <c r="EP23" s="23">
+      <c r="EP23" s="24">
         <v>2116.58</v>
       </c>
-      <c r="EQ23" s="23">
+      <c r="EQ23" s="24">
         <f>ER23-EP23</f>
         <v>34.4200000000001</v>
       </c>
-      <c r="ER23" s="23">
+      <c r="ER23" s="24">
         <v>2151</v>
       </c>
-      <c r="ES23" s="23">
+      <c r="ES23" s="24">
         <f>ET23-ER23</f>
         <v>26.2399999999998</v>
       </c>
-      <c r="ET23" s="23">
+      <c r="ET23" s="24">
         <v>2177.24</v>
       </c>
-      <c r="EU23" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="EV23" s="21">
-        <v>718.12</v>
-      </c>
-      <c r="EW23" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="EX23" s="21">
+      <c r="EU23" s="24">
+        <f>EV23-ET23</f>
+        <v>29</v>
+      </c>
+      <c r="EV23" s="24">
+        <v>2206.24</v>
+      </c>
+      <c r="EW23" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="EX23" s="22">
+        <v>733.43</v>
+      </c>
+      <c r="EY23" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="EZ23" s="22">
         <v>368.34</v>
       </c>
-      <c r="EY23" s="8">
+      <c r="FA23" s="8">
         <v>0</v>
       </c>
-      <c r="EZ23" s="8">
+      <c r="FB23" s="8">
         <v>1</v>
       </c>
-      <c r="FA23" s="8">
+      <c r="FC23" s="8">
         <v>47256</v>
       </c>
-      <c r="FB23" s="9">
-        <f>2.41/(ET23/EV23)</f>
-        <v>0.794891330308097</v>
-      </c>
-      <c r="FC23" s="9">
+      <c r="FD23" s="9">
+        <f>2.79/(EV23/EX23)</f>
+        <v>0.927491886648778</v>
+      </c>
+      <c r="FE23" s="9">
         <f>BP23-D23</f>
         <v>790.52</v>
       </c>
     </row>
-    <row r="24" spans="1:159">
+    <row r="24" spans="1:161">
       <c r="A24" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -14205,39 +14368,46 @@
       <c r="ET24" s="28">
         <v>1794.4</v>
       </c>
-      <c r="EU24" s="27" t="s">
+      <c r="EU24" s="28">
+        <f>EV24-ET24</f>
+        <v>11.0899999999999</v>
+      </c>
+      <c r="EV24" s="28">
+        <v>1805.49</v>
+      </c>
+      <c r="EW24" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="EX24" s="26">
+        <v>399.87</v>
+      </c>
+      <c r="EY24" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="EV24" s="26">
-        <v>414.1</v>
-      </c>
-      <c r="EW24" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="EX24" s="21">
+      <c r="EZ24" s="22">
         <v>148.34</v>
       </c>
-      <c r="EY24" s="8"/>
-      <c r="EZ24" s="8"/>
       <c r="FA24" s="8"/>
-      <c r="FB24" s="9">
-        <f>2.41/(ET24/EV24)</f>
-        <v>0.556164177440927</v>
-      </c>
-      <c r="FC24" s="9">
+      <c r="FB24" s="8"/>
+      <c r="FC24" s="8"/>
+      <c r="FD24" s="9">
+        <f>2.79/(EV24/EX24)</f>
+        <v>0.617913862718708</v>
+      </c>
+      <c r="FE24" s="9">
         <f>BP24-D24</f>
         <v>897.4</v>
       </c>
     </row>
-    <row r="25" spans="1:159">
+    <row r="25" spans="1:161">
       <c r="A25" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -14653,39 +14823,46 @@
       <c r="ET25" s="28">
         <v>1727.63</v>
       </c>
-      <c r="EU25" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="EV25" s="26">
+      <c r="EU25" s="28">
+        <f>EV25-ET25</f>
+        <v>0</v>
+      </c>
+      <c r="EV25" s="28">
+        <v>1727.63</v>
+      </c>
+      <c r="EW25" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="EX25" s="26">
         <v>397.94</v>
       </c>
-      <c r="EW25" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="EX25" s="21">
+      <c r="EY25" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="EZ25" s="22">
         <v>184.85</v>
       </c>
-      <c r="EY25" s="8"/>
-      <c r="EZ25" s="8"/>
       <c r="FA25" s="8"/>
-      <c r="FB25" s="9">
-        <f>2.41/(ET25/EV25)</f>
-        <v>0.555116199649231</v>
-      </c>
-      <c r="FC25" s="9">
+      <c r="FB25" s="8"/>
+      <c r="FC25" s="8"/>
+      <c r="FD25" s="9">
+        <f>2.79/(EV25/EX25)</f>
+        <v>0.642644895029607</v>
+      </c>
+      <c r="FE25" s="9">
         <f>BP25-D25</f>
         <v>1045.05</v>
       </c>
     </row>
-    <row r="26" spans="1:159">
+    <row r="26" spans="1:161">
       <c r="A26" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="3">
         <v>407.35</v>
@@ -15201,45 +15378,52 @@
       <c r="ET26" s="28">
         <v>1428.59</v>
       </c>
-      <c r="EU26" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="EV26" s="26">
+      <c r="EU26" s="28">
+        <f>EV26-ET26</f>
+        <v>0</v>
+      </c>
+      <c r="EV26" s="28">
+        <v>1428.59</v>
+      </c>
+      <c r="EW26" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="EX26" s="26">
         <v>674.85</v>
       </c>
-      <c r="EW26" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="EX26" s="21">
+      <c r="EY26" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="EZ26" s="22">
         <v>293.75</v>
       </c>
-      <c r="EY26" s="8">
+      <c r="FA26" s="8">
         <v>30</v>
       </c>
-      <c r="EZ26" s="8">
+      <c r="FB26" s="8">
         <v>2.4</v>
       </c>
-      <c r="FA26" s="8">
+      <c r="FC26" s="8">
         <v>43895</v>
       </c>
-      <c r="FB26" s="9">
-        <f>2.41/(ET26/EV26)</f>
-        <v>1.13845715005705</v>
-      </c>
-      <c r="FC26" s="9">
+      <c r="FD26" s="9">
+        <f>2.79/(EV26/EX26)</f>
+        <v>1.31796491645609</v>
+      </c>
+      <c r="FE26" s="9">
         <f>BP26-D26</f>
         <v>517.61</v>
       </c>
     </row>
-    <row r="27" spans="1:159">
+    <row r="27" spans="1:161">
       <c r="A27" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D27" s="3">
         <v>552.79</v>
@@ -15755,42 +15939,49 @@
       <c r="ET27" s="28">
         <v>984.2</v>
       </c>
-      <c r="EU27" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="EV27" s="26">
-        <v>292.44</v>
-      </c>
-      <c r="EW27" s="26" t="s">
-        <v>138</v>
+      <c r="EU27" s="28">
+        <f>EV27-ET27</f>
+        <v>9.88999999999999</v>
+      </c>
+      <c r="EV27" s="28">
+        <v>994.09</v>
+      </c>
+      <c r="EW27" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="EX27" s="26">
+        <v>298.94</v>
+      </c>
+      <c r="EY27" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="EZ27" s="26">
         <v>171.75</v>
       </c>
-      <c r="EY27" s="3">
+      <c r="FA27" s="3">
         <v>0</v>
       </c>
-      <c r="EZ27" s="3">
+      <c r="FB27" s="3">
         <v>0.5</v>
       </c>
-      <c r="FA27" s="3">
+      <c r="FC27" s="3">
         <v>49654</v>
       </c>
-      <c r="FB27" s="9">
-        <f>2.41/(ET27/EV27)</f>
-        <v>0.716094696199959</v>
-      </c>
-      <c r="FC27" s="9">
+      <c r="FD27" s="9">
+        <f>2.79/(EV27/EX27)</f>
+        <v>0.839001096480198</v>
+      </c>
+      <c r="FE27" s="9">
         <f>BP27-D27</f>
         <v>175.03</v>
       </c>
     </row>
-    <row r="30" spans="1:159">
+    <row r="30" spans="1:161">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
@@ -15942,13 +16133,15 @@
       <c r="ET30" s="29"/>
       <c r="EU30" s="29"/>
       <c r="EV30" s="29"/>
+      <c r="EW30" s="29"/>
+      <c r="EX30" s="29"/>
     </row>
-    <row r="31" spans="1:159">
+    <row r="31" spans="1:161">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P31" s="29"/>
       <c r="Q31" s="29"/>
@@ -16090,21 +16283,23 @@
       <c r="EW31" s="29"/>
       <c r="EX31" s="29"/>
       <c r="EY31" s="29"/>
+      <c r="EZ31" s="29"/>
+      <c r="FA31" s="29"/>
     </row>
-    <row r="32" spans="1:159">
+    <row r="32" spans="1:161">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:151">
+    <row r="33" spans="1:153">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C33" s="29"/>
       <c r="D33" s="29"/>
@@ -16255,58 +16450,60 @@
       <c r="ES33" s="29"/>
       <c r="ET33" s="29"/>
       <c r="EU33" s="29"/>
+      <c r="EV33" s="29"/>
+      <c r="EW33" s="29"/>
     </row>
-    <row r="34" spans="1:151">
+    <row r="34" spans="1:153">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:151">
+    <row r="35" spans="1:153">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:151">
+    <row r="36" spans="1:153">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:151">
+    <row r="37" spans="1:153">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="38" spans="1:151">
+    <row r="38" spans="1:153">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:151">
+    <row r="39" spans="1:153">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:FC27">
-    <sortCondition ref="ET2" descending="1"/>
+  <sortState ref="A2:FE27">
+    <sortCondition ref="EV2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -16343,157 +16540,157 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="U1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="W1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="X1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AB1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AC1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AD1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AE1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AH1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AI1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AJ1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AK1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AR1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AS1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AT1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AU1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AV1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AW1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AX1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AY1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AZ1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:54">
@@ -17794,7 +17991,7 @@
     </row>
     <row r="14" spans="1:54">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B14">
         <f>SUM(B2:B9)</f>
@@ -18004,7 +18201,7 @@
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" spans="1:52">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:52">
@@ -19249,10 +19446,10 @@
     </row>
     <row r="29" spans="1:52">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AZ29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:52">
@@ -20985,7 +21182,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C31:L38 M31:M39 N31:AY38" formulaRange="1"/>
+    <ignoredError sqref="N31:AY38 M31:M39 C31:L38" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>